--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\RKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{82C2664D-B25D-45A5-832B-E371991628C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{5E5466EE-E6E1-429B-BCEC-F0A77692F222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="151">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -288,84 +288,9 @@
     <t>31022000  Sintelis</t>
   </si>
   <si>
-    <t>4112222200  Bbn Penystn Srana Perkeretaapian Fasilitas Dipo-By</t>
-  </si>
-  <si>
-    <t>4221221100  Perawatan Rel BMN</t>
-  </si>
-  <si>
-    <t>4221222200  Perawatan Wesel BMN</t>
-  </si>
-  <si>
-    <t>4221223300  Bbn Jasa Penambahan Balas BMN</t>
-  </si>
-  <si>
-    <t>4221224400  Pemasangan Bantalan BMN</t>
-  </si>
-  <si>
-    <t>4221225500  Perawatan Balas BMN</t>
-  </si>
-  <si>
-    <t>4221226000  Pemecokan BMN</t>
-  </si>
-  <si>
-    <t>4221226006  Perlintasan BMN</t>
-  </si>
-  <si>
-    <t>4221226008  Geometri BMN</t>
-  </si>
-  <si>
-    <t>4221226010  Perbaikan Periodik BMN</t>
-  </si>
-  <si>
-    <t>4221321010  Perawatan Baja Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221322010  Perawatan Cat Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221323010  Perawatan Batu Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221325010  Perawatan Cat Jembatan Kelas 2 BMN</t>
-  </si>
-  <si>
-    <t>4221325013  Perawatan Batu Jembatan Kelas 3 BMN</t>
-  </si>
-  <si>
-    <t>4221325014  Perawatan Beton Jembatan Kelas 3 BMN</t>
-  </si>
-  <si>
     <t>4221600000  Peralatan Khusus Prasarana Pemerintah</t>
   </si>
   <si>
-    <t>4222222200  Perawatan Wesel KAI</t>
-  </si>
-  <si>
-    <t>4231120000  PerjlDinas BebanUmum PerawatanPrasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231130000  LAT Beban Umum Perawatan Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231150010  Krt Beban Umum Perawatan Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231151710  Kerumahtanggaan UMDT Beban Umum Perawatan Pras BMN</t>
-  </si>
-  <si>
-    <t>4232152310  Tenaga PJL Alih Daya</t>
-  </si>
-  <si>
-    <t>4271100010  Gaji &amp;Tunjangan Pegawai Operasi Prasarana</t>
-  </si>
-  <si>
-    <t>4271500000  Pakaian Dinas Pegawai Operasi Prasarana</t>
-  </si>
-  <si>
-    <t>32020100  Prasarana</t>
-  </si>
-  <si>
     <t>4222421110  Transmisi Komunikasi KAI</t>
   </si>
   <si>
@@ -394,6 +319,165 @@
   </si>
   <si>
     <t>35022000  Sintelis Divre IV Tanjungkarang</t>
+  </si>
+  <si>
+    <t>1182000000 Persediaan Prasarana Perkeretaapian dan Umum</t>
+  </si>
+  <si>
+    <t>4112222200 Bbn Penystn Srana Perkeretaapian Fasilitas Dipo-By</t>
+  </si>
+  <si>
+    <t>4221221100 Perawatan Rel BMN</t>
+  </si>
+  <si>
+    <t>4221222200 Perawatan Wesel BMN</t>
+  </si>
+  <si>
+    <t>4221223300 Bbn Jasa Penambahan Balas BMN</t>
+  </si>
+  <si>
+    <t>4221224400 Pemasangan Bantalan BMN</t>
+  </si>
+  <si>
+    <t>4221225500 Perawatan Balas BMN</t>
+  </si>
+  <si>
+    <t>4221226000 Pemecokan BMN</t>
+  </si>
+  <si>
+    <t>4221226006 Perlintasan BMN</t>
+  </si>
+  <si>
+    <t>4221226008 Geometri BMN</t>
+  </si>
+  <si>
+    <t>4221226010 Perbaikan Periodik BMN</t>
+  </si>
+  <si>
+    <t>4221321010 Perawatan Baja Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221322010 Perawatan Cat Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221323010 Perawatan Batu Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221325010 Perawatan Cat Jembatan Kelas 2 BMN</t>
+  </si>
+  <si>
+    <t>4221325013 Perawatan Batu Jembatan Kelas 3 BMN</t>
+  </si>
+  <si>
+    <t>4221325014 Perawatan Beton Jembatan Kelas 3 BMN</t>
+  </si>
+  <si>
+    <t>4221424010 Peralatan Luar Sinyal Mekanik BMN</t>
+  </si>
+  <si>
+    <t>4221425010 Pengamanan Perlintasan Sebidang BMN</t>
+  </si>
+  <si>
+    <t>4221427010 Transmisi Komunikasi BMN</t>
+  </si>
+  <si>
+    <t>4221428010 Peralatan Pendukung Sintel BMN</t>
+  </si>
+  <si>
+    <t>4221428014 Catu Daya Sintel BMN</t>
+  </si>
+  <si>
+    <t>4221600000 Peralatan Khusus Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4222222200 Perawatan Wesel KAI</t>
+  </si>
+  <si>
+    <t>4222600000 Peralatan Khusus Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4222800000 Beban BBM Mekanik Prasarana</t>
+  </si>
+  <si>
+    <t>4231110000 Rapat&amp;Akomodasi BbnUmum Prwtn Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231120000 PerjlDinas BebanUmum PerawatanPrasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231130000 LAT Beban Umum Perawatan Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231150010 Krt Beban Umum Perawatan Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231151710 Kerumahtanggaan UMDT Beban Umum Perawatan Pras BMN</t>
+  </si>
+  <si>
+    <t>4232152310 Tenaga PJL Alih Daya</t>
+  </si>
+  <si>
+    <t>4233100000 Rapat&amp;Akomodasi Beban Umum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4233150010 Kerumahtanggaan Beban Umum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4233151710 Kerumahtanggaan UMDT Beban Umum Perawatan Pras KAI</t>
+  </si>
+  <si>
+    <t>4233160010 Inventaris Beban Umum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4233200000 Perjalanan Dinas BebanUmum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4233300000 LAT Beban Umum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4233400000 ATK Beban Umum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4241000000 Beban Penyusutan AT Prasarana Perkeretaapian</t>
+  </si>
+  <si>
+    <t>4242000000 Beban Penyusutan AT Bangunan Kantor</t>
+  </si>
+  <si>
+    <t>4271100010 Gaji &amp;Tunjangan Pegawai Operasi Prasarana</t>
+  </si>
+  <si>
+    <t>4271400000 Lembur dan Perangsang Pegawai Operasi Prasarana</t>
+  </si>
+  <si>
+    <t>4271500000 Pakaian Dinas Pegawai Operasi Prasarana</t>
+  </si>
+  <si>
+    <t>4272100010 Gaji &amp;Tunjangan PegawaiPerawatan Prasarana Unit JJ</t>
+  </si>
+  <si>
+    <t>4272200010 Iuran Pensiun Pegawai Perawatan Prasarana Unit JJ/</t>
+  </si>
+  <si>
+    <t>4272400000 Lembur dan Perangsang Peg PrwtnPrsrna unit JJ/Sntl</t>
+  </si>
+  <si>
+    <t>4272500000 PakaianDinas PegPrwtn PrasaranaUnit JJ/sntl/BY Pra</t>
+  </si>
+  <si>
+    <t>4273100010 Gaji &amp;Tunjangan Pegawai Renwas JJ/Sintel LAA</t>
+  </si>
+  <si>
+    <t>4273400000 Lembur dan Perangsang Pegawai Renwas JJ/Sintel LAA</t>
+  </si>
+  <si>
+    <t>4273500000 Pakaian Dinas Pegawai Renwas JJ/Sintel LAA</t>
+  </si>
+  <si>
+    <t>5400000000 Penyusutan AT Lainnya (Fasilitas Umum)</t>
+  </si>
+  <si>
+    <t>32020100 Prasarana</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1331,10 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="60.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="13.06640625" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.265625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1339,10 +1426,10 @@
         <v>57855713800</v>
       </c>
       <c r="D4" s="2">
-        <v>57455713800</v>
+        <v>52055713800</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>5400000000</v>
       </c>
       <c r="F4" s="2">
         <v>57455713800</v>
@@ -1443,16 +1530,16 @@
         <v>3947046000</v>
       </c>
       <c r="D8" s="2">
-        <v>0</v>
+        <v>39147500</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>39147500</v>
       </c>
       <c r="G8" s="2">
-        <v>3947046000</v>
+        <v>3907898500</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -1651,16 +1738,16 @@
         <v>1200000000</v>
       </c>
       <c r="D16" s="2">
-        <v>0</v>
+        <v>42457000</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>42457000</v>
       </c>
       <c r="G16" s="2">
-        <v>1200000000</v>
+        <v>1157543000</v>
       </c>
       <c r="H16" s="2">
         <v>400000000</v>
@@ -1671,10 +1758,10 @@
         <v>23</v>
       </c>
       <c r="B17" s="2">
-        <v>500000000</v>
+        <v>496414000</v>
       </c>
       <c r="C17" s="2">
-        <v>375000000</v>
+        <v>371414000</v>
       </c>
       <c r="D17" s="2">
         <v>20986164</v>
@@ -1686,7 +1773,7 @@
         <v>20986164</v>
       </c>
       <c r="G17" s="2">
-        <v>354013836</v>
+        <v>350427836</v>
       </c>
       <c r="H17" s="2">
         <v>125000000</v>
@@ -1862,13 +1949,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="2">
-        <v>193087500</v>
+        <v>204850000</v>
       </c>
       <c r="F24" s="2">
-        <v>193087500</v>
+        <v>204850000</v>
       </c>
       <c r="G24" s="2">
-        <v>1673605111</v>
+        <v>1661842611</v>
       </c>
       <c r="H24" s="2">
         <v>625000000</v>
@@ -1914,13 +2001,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="2">
-        <v>413857628</v>
+        <v>414390128</v>
       </c>
       <c r="F26" s="2">
-        <v>413857628</v>
+        <v>414390128</v>
       </c>
       <c r="G26" s="2">
-        <v>3042756576</v>
+        <v>3042224076</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -2217,22 +2304,22 @@
         <v>44</v>
       </c>
       <c r="B38" s="2">
-        <v>361729344454</v>
+        <v>361725758454</v>
       </c>
       <c r="C38" s="2">
-        <v>359311844454</v>
+        <v>359308258454</v>
       </c>
       <c r="D38" s="2">
-        <v>175461180890</v>
+        <v>170142785390</v>
       </c>
       <c r="E38" s="2">
-        <v>48780324773</v>
+        <v>54192619773</v>
       </c>
       <c r="F38" s="2">
-        <v>224241505663</v>
+        <v>224335405163</v>
       </c>
       <c r="G38" s="2">
-        <v>135070338791</v>
+        <v>134972853291</v>
       </c>
       <c r="H38" s="2">
         <v>2417500000</v>
@@ -2249,16 +2336,16 @@
         <v>25194775704</v>
       </c>
       <c r="D39" s="2">
-        <v>15690909964</v>
+        <v>16128909964</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>15690909964</v>
+        <v>16128909964</v>
       </c>
       <c r="G39" s="2">
-        <v>9503865740</v>
+        <v>9065865740</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -2509,10 +2596,10 @@
         <v>4260000000</v>
       </c>
       <c r="D49" s="2">
-        <v>587152114</v>
+        <v>579572114</v>
       </c>
       <c r="E49" s="2">
-        <v>389904675</v>
+        <v>397484675</v>
       </c>
       <c r="F49" s="2">
         <v>977056789</v>
@@ -3263,16 +3350,16 @@
         <v>110897810191</v>
       </c>
       <c r="D78" s="2">
-        <v>19485987003</v>
+        <v>19916407003</v>
       </c>
       <c r="E78" s="2">
-        <v>9035977927</v>
+        <v>9043557927</v>
       </c>
       <c r="F78" s="2">
-        <v>28521964930</v>
+        <v>28959964930</v>
       </c>
       <c r="G78" s="2">
-        <v>82375845261</v>
+        <v>81937845261</v>
       </c>
       <c r="H78" s="2">
         <v>671501500</v>
@@ -3289,16 +3376,16 @@
         <v>4044107500</v>
       </c>
       <c r="D79" s="2">
-        <v>644350000</v>
+        <v>1518071200</v>
       </c>
       <c r="E79" s="2">
         <v>585361000</v>
       </c>
       <c r="F79" s="2">
-        <v>1229711000</v>
+        <v>2103432200</v>
       </c>
       <c r="G79" s="2">
-        <v>2814396500</v>
+        <v>1940675300</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3497,10 +3584,10 @@
         <v>2796520000</v>
       </c>
       <c r="D87" s="2">
-        <v>437704607</v>
+        <v>382331307</v>
       </c>
       <c r="E87" s="2">
-        <v>541996241</v>
+        <v>597369541</v>
       </c>
       <c r="F87" s="2">
         <v>979700848</v>
@@ -3653,10 +3740,10 @@
         <v>1710494400</v>
       </c>
       <c r="D93" s="2">
-        <v>377862600</v>
+        <v>364436500</v>
       </c>
       <c r="E93" s="2">
-        <v>38993000</v>
+        <v>52419100</v>
       </c>
       <c r="F93" s="2">
         <v>416855600</v>
@@ -4173,16 +4260,16 @@
         <v>81718644736</v>
       </c>
       <c r="D113" s="2">
-        <v>18093184625</v>
+        <v>18898106425</v>
       </c>
       <c r="E113" s="2">
-        <v>15413951057</v>
+        <v>15482750457</v>
       </c>
       <c r="F113" s="2">
-        <v>33507135682</v>
+        <v>34380856882</v>
       </c>
       <c r="G113" s="2">
-        <v>48211509054</v>
+        <v>47337787854</v>
       </c>
       <c r="H113" s="2">
         <v>475697500</v>
@@ -4225,16 +4312,16 @@
         <v>435680000</v>
       </c>
       <c r="D115" s="2">
-        <v>8607111</v>
+        <v>39139111</v>
       </c>
       <c r="E115" s="2">
         <v>0</v>
       </c>
       <c r="F115" s="2">
-        <v>8607111</v>
+        <v>39139111</v>
       </c>
       <c r="G115" s="2">
-        <v>427072889</v>
+        <v>396540889</v>
       </c>
       <c r="H115" s="2">
         <v>0</v>
@@ -4563,16 +4650,16 @@
         <v>528750000</v>
       </c>
       <c r="D128" s="2">
-        <v>0</v>
+        <v>497734500</v>
       </c>
       <c r="E128" s="2">
         <v>0</v>
       </c>
       <c r="F128" s="2">
-        <v>0</v>
+        <v>497734500</v>
       </c>
       <c r="G128" s="2">
-        <v>528750000</v>
+        <v>31015500</v>
       </c>
       <c r="H128" s="2">
         <v>176250000</v>
@@ -4667,10 +4754,10 @@
         <v>265950000</v>
       </c>
       <c r="D132" s="2">
-        <v>44932500</v>
+        <v>33432500</v>
       </c>
       <c r="E132" s="2">
-        <v>34913500</v>
+        <v>46413500</v>
       </c>
       <c r="F132" s="2">
         <v>79846000</v>
@@ -5057,16 +5144,16 @@
         <v>50726099717</v>
       </c>
       <c r="D147" s="2">
-        <v>16105336153</v>
+        <v>16622102653</v>
       </c>
       <c r="E147" s="2">
-        <v>4348418620</v>
+        <v>4359918620</v>
       </c>
       <c r="F147" s="2">
-        <v>20453754773</v>
+        <v>20982021273</v>
       </c>
       <c r="G147" s="2">
-        <v>30272344944</v>
+        <v>29744078444</v>
       </c>
       <c r="H147" s="2">
         <v>411080000</v>
@@ -5077,10 +5164,10 @@
         <v>8</v>
       </c>
       <c r="B148" s="2">
-        <v>5691755500</v>
+        <v>11383511000</v>
       </c>
       <c r="C148" s="2">
-        <v>5691755500</v>
+        <v>11383511000</v>
       </c>
       <c r="D148" s="2">
         <v>5533217000</v>
@@ -5092,7 +5179,7 @@
         <v>5533217000</v>
       </c>
       <c r="G148" s="2">
-        <v>158538500</v>
+        <v>5850294000</v>
       </c>
       <c r="H148" s="2">
         <v>0</v>
@@ -5103,10 +5190,10 @@
         <v>11</v>
       </c>
       <c r="B149" s="2">
-        <v>874758000</v>
+        <v>1749516000</v>
       </c>
       <c r="C149" s="2">
-        <v>874758000</v>
+        <v>1749516000</v>
       </c>
       <c r="D149" s="2">
         <v>872621317</v>
@@ -5118,7 +5205,7 @@
         <v>872621317</v>
       </c>
       <c r="G149" s="2">
-        <v>2136683</v>
+        <v>876894683</v>
       </c>
       <c r="H149" s="2">
         <v>0</v>
@@ -5155,10 +5242,10 @@
         <v>13</v>
       </c>
       <c r="B151" s="2">
-        <v>249837500</v>
+        <v>499675000</v>
       </c>
       <c r="C151" s="2">
-        <v>249837500</v>
+        <v>499675000</v>
       </c>
       <c r="D151" s="2">
         <v>106240051</v>
@@ -5170,7 +5257,7 @@
         <v>106240051</v>
       </c>
       <c r="G151" s="2">
-        <v>143597449</v>
+        <v>393434949</v>
       </c>
       <c r="H151" s="2">
         <v>0</v>
@@ -5181,10 +5268,10 @@
         <v>14</v>
       </c>
       <c r="B152" s="2">
-        <v>435218500</v>
+        <v>870437000</v>
       </c>
       <c r="C152" s="2">
-        <v>435218500</v>
+        <v>870437000</v>
       </c>
       <c r="D152" s="2">
         <v>72346470</v>
@@ -5196,7 +5283,7 @@
         <v>80661470</v>
       </c>
       <c r="G152" s="2">
-        <v>354557030</v>
+        <v>789775530</v>
       </c>
       <c r="H152" s="2">
         <v>0</v>
@@ -5207,10 +5294,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="2">
-        <v>196881500</v>
+        <v>393763000</v>
       </c>
       <c r="C153" s="2">
-        <v>196881500</v>
+        <v>393763000</v>
       </c>
       <c r="D153" s="2">
         <v>0</v>
@@ -5222,7 +5309,7 @@
         <v>10224916</v>
       </c>
       <c r="G153" s="2">
-        <v>186656584</v>
+        <v>383538084</v>
       </c>
       <c r="H153" s="2">
         <v>0</v>
@@ -5233,10 +5320,10 @@
         <v>16</v>
       </c>
       <c r="B154" s="2">
-        <v>1155703000</v>
+        <v>1702406000</v>
       </c>
       <c r="C154" s="2">
-        <v>1155703000</v>
+        <v>1702406000</v>
       </c>
       <c r="D154" s="2">
         <v>297962777</v>
@@ -5248,7 +5335,7 @@
         <v>394640336</v>
       </c>
       <c r="G154" s="2">
-        <v>761062664</v>
+        <v>1307765664</v>
       </c>
       <c r="H154" s="2">
         <v>0</v>
@@ -5259,10 +5346,10 @@
         <v>49</v>
       </c>
       <c r="B155" s="2">
-        <v>231680000</v>
+        <v>463360000</v>
       </c>
       <c r="C155" s="2">
-        <v>231680000</v>
+        <v>463360000</v>
       </c>
       <c r="D155" s="2">
         <v>22153380</v>
@@ -5274,7 +5361,7 @@
         <v>22153380</v>
       </c>
       <c r="G155" s="2">
-        <v>209526620</v>
+        <v>441206620</v>
       </c>
       <c r="H155" s="2">
         <v>0</v>
@@ -5285,10 +5372,10 @@
         <v>50</v>
       </c>
       <c r="B156" s="2">
-        <v>498478000</v>
+        <v>996956000</v>
       </c>
       <c r="C156" s="2">
-        <v>498478000</v>
+        <v>996956000</v>
       </c>
       <c r="D156" s="2">
         <v>0</v>
@@ -5300,7 +5387,7 @@
         <v>0</v>
       </c>
       <c r="G156" s="2">
-        <v>498478000</v>
+        <v>996956000</v>
       </c>
       <c r="H156" s="2">
         <v>0</v>
@@ -5311,10 +5398,10 @@
         <v>51</v>
       </c>
       <c r="B157" s="2">
-        <v>158995000</v>
+        <v>317990000</v>
       </c>
       <c r="C157" s="2">
-        <v>158995000</v>
+        <v>317990000</v>
       </c>
       <c r="D157" s="2">
         <v>3857000</v>
@@ -5326,7 +5413,7 @@
         <v>3857000</v>
       </c>
       <c r="G157" s="2">
-        <v>155138000</v>
+        <v>314133000</v>
       </c>
       <c r="H157" s="2">
         <v>0</v>
@@ -5337,10 +5424,10 @@
         <v>52</v>
       </c>
       <c r="B158" s="2">
-        <v>1213930000</v>
+        <v>2427860000</v>
       </c>
       <c r="C158" s="2">
-        <v>1213930000</v>
+        <v>2427860000</v>
       </c>
       <c r="D158" s="2">
         <v>48285000</v>
@@ -5352,7 +5439,7 @@
         <v>48285000</v>
       </c>
       <c r="G158" s="2">
-        <v>1165645000</v>
+        <v>2379575000</v>
       </c>
       <c r="H158" s="2">
         <v>0</v>
@@ -5363,10 +5450,10 @@
         <v>54</v>
       </c>
       <c r="B159" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="C159" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="D159" s="2">
         <v>38082500</v>
@@ -5378,7 +5465,7 @@
         <v>46857638</v>
       </c>
       <c r="G159" s="2">
-        <v>203142362</v>
+        <v>453142362</v>
       </c>
       <c r="H159" s="2">
         <v>0</v>
@@ -5389,10 +5476,10 @@
         <v>77</v>
       </c>
       <c r="B160" s="2">
-        <v>39449000</v>
+        <v>78898000</v>
       </c>
       <c r="C160" s="2">
-        <v>39449000</v>
+        <v>78898000</v>
       </c>
       <c r="D160" s="2">
         <v>0</v>
@@ -5404,7 +5491,7 @@
         <v>0</v>
       </c>
       <c r="G160" s="2">
-        <v>39449000</v>
+        <v>78898000</v>
       </c>
       <c r="H160" s="2">
         <v>0</v>
@@ -5415,10 +5502,10 @@
         <v>56</v>
       </c>
       <c r="B161" s="2">
-        <v>433971000</v>
+        <v>867942000</v>
       </c>
       <c r="C161" s="2">
-        <v>433971000</v>
+        <v>867942000</v>
       </c>
       <c r="D161" s="2">
         <v>0</v>
@@ -5430,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="G161" s="2">
-        <v>433971000</v>
+        <v>867942000</v>
       </c>
       <c r="H161" s="2">
         <v>0</v>
@@ -5441,10 +5528,10 @@
         <v>22</v>
       </c>
       <c r="B162" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="C162" s="2">
-        <v>125000000</v>
+        <v>187500000</v>
       </c>
       <c r="D162" s="2">
         <v>0</v>
@@ -5456,10 +5543,10 @@
         <v>0</v>
       </c>
       <c r="G162" s="2">
-        <v>125000000</v>
+        <v>187500000</v>
       </c>
       <c r="H162" s="2">
-        <v>0</v>
+        <v>62500000</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.45">
@@ -5467,10 +5554,10 @@
         <v>57</v>
       </c>
       <c r="B163" s="2">
-        <v>45045000</v>
+        <v>90090000</v>
       </c>
       <c r="C163" s="2">
-        <v>45045000</v>
+        <v>90090000</v>
       </c>
       <c r="D163" s="2">
         <v>11205000</v>
@@ -5482,7 +5569,7 @@
         <v>11205000</v>
       </c>
       <c r="G163" s="2">
-        <v>33840000</v>
+        <v>78885000</v>
       </c>
       <c r="H163" s="2">
         <v>0</v>
@@ -5493,10 +5580,10 @@
         <v>24</v>
       </c>
       <c r="B164" s="2">
-        <v>33075000</v>
+        <v>132300000</v>
       </c>
       <c r="C164" s="2">
-        <v>33075000</v>
+        <v>132300000</v>
       </c>
       <c r="D164" s="2">
         <v>0</v>
@@ -5508,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="G164" s="2">
-        <v>33075000</v>
+        <v>132300000</v>
       </c>
       <c r="H164" s="2">
         <v>0</v>
@@ -5519,22 +5606,22 @@
         <v>58</v>
       </c>
       <c r="B165" s="2">
-        <v>592250000</v>
+        <v>2369000000</v>
       </c>
       <c r="C165" s="2">
-        <v>592250000</v>
+        <v>2369000000</v>
       </c>
       <c r="D165" s="2">
-        <v>269200</v>
+        <v>0</v>
       </c>
       <c r="E165" s="2">
-        <v>346245306</v>
+        <v>346514506</v>
       </c>
       <c r="F165" s="2">
         <v>346514506</v>
       </c>
       <c r="G165" s="2">
-        <v>245735494</v>
+        <v>2022485494</v>
       </c>
       <c r="H165" s="2">
         <v>0</v>
@@ -5545,10 +5632,10 @@
         <v>25</v>
       </c>
       <c r="B166" s="2">
-        <v>45000000</v>
+        <v>180000000</v>
       </c>
       <c r="C166" s="2">
-        <v>45000000</v>
+        <v>135000000</v>
       </c>
       <c r="D166" s="2">
         <v>28592500</v>
@@ -5560,10 +5647,10 @@
         <v>38592500</v>
       </c>
       <c r="G166" s="2">
-        <v>6407500</v>
+        <v>96407500</v>
       </c>
       <c r="H166" s="2">
-        <v>0</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.45">
@@ -5571,10 +5658,10 @@
         <v>26</v>
       </c>
       <c r="B167" s="2">
-        <v>136250000</v>
+        <v>545000000</v>
       </c>
       <c r="C167" s="2">
-        <v>136250000</v>
+        <v>408750000</v>
       </c>
       <c r="D167" s="2">
         <v>55881809</v>
@@ -5586,10 +5673,10 @@
         <v>134443944</v>
       </c>
       <c r="G167" s="2">
-        <v>1806056</v>
+        <v>274306056</v>
       </c>
       <c r="H167" s="2">
-        <v>0</v>
+        <v>136250000</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.45">
@@ -5597,10 +5684,10 @@
         <v>27</v>
       </c>
       <c r="B168" s="2">
-        <v>21750000</v>
+        <v>87000000</v>
       </c>
       <c r="C168" s="2">
-        <v>21750000</v>
+        <v>87000000</v>
       </c>
       <c r="D168" s="2">
         <v>0</v>
@@ -5612,7 +5699,7 @@
         <v>14461500</v>
       </c>
       <c r="G168" s="2">
-        <v>7288500</v>
+        <v>72538500</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
@@ -5623,10 +5710,10 @@
         <v>28</v>
       </c>
       <c r="B169" s="2">
-        <v>146550000</v>
+        <v>586200000</v>
       </c>
       <c r="C169" s="2">
-        <v>146550000</v>
+        <v>439650000</v>
       </c>
       <c r="D169" s="2">
         <v>114790302</v>
@@ -5638,10 +5725,10 @@
         <v>114790302</v>
       </c>
       <c r="G169" s="2">
-        <v>31759698</v>
+        <v>324859698</v>
       </c>
       <c r="H169" s="2">
-        <v>0</v>
+        <v>146550000</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.45">
@@ -5649,10 +5736,10 @@
         <v>29</v>
       </c>
       <c r="B170" s="2">
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
       <c r="C170" s="2">
-        <v>5000000</v>
+        <v>15000000</v>
       </c>
       <c r="D170" s="2">
         <v>0</v>
@@ -5664,10 +5751,10 @@
         <v>3000000</v>
       </c>
       <c r="G170" s="2">
-        <v>2000000</v>
+        <v>12000000</v>
       </c>
       <c r="H170" s="2">
-        <v>0</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.45">
@@ -5675,10 +5762,10 @@
         <v>30</v>
       </c>
       <c r="B171" s="2">
-        <v>54100500</v>
+        <v>216402000</v>
       </c>
       <c r="C171" s="2">
-        <v>54100500</v>
+        <v>162301500</v>
       </c>
       <c r="D171" s="2">
         <v>0</v>
@@ -5690,10 +5777,10 @@
         <v>37528000</v>
       </c>
       <c r="G171" s="2">
-        <v>16572500</v>
+        <v>124773500</v>
       </c>
       <c r="H171" s="2">
-        <v>0</v>
+        <v>54100500</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.45">
@@ -5701,10 +5788,10 @@
         <v>31</v>
       </c>
       <c r="B172" s="2">
-        <v>12000000</v>
+        <v>48000000</v>
       </c>
       <c r="C172" s="2">
-        <v>12000000</v>
+        <v>48000000</v>
       </c>
       <c r="D172" s="2">
         <v>6889220</v>
@@ -5716,7 +5803,7 @@
         <v>6889220</v>
       </c>
       <c r="G172" s="2">
-        <v>5110780</v>
+        <v>41110780</v>
       </c>
       <c r="H172" s="2">
         <v>0</v>
@@ -5935,25 +6022,25 @@
         <v>78</v>
       </c>
       <c r="B181" s="2">
-        <v>30446840487</v>
+        <v>44576468987</v>
       </c>
       <c r="C181" s="2">
-        <v>30446840487</v>
+        <v>44127068487</v>
       </c>
       <c r="D181" s="2">
-        <v>7212393526</v>
+        <v>7212124326</v>
       </c>
       <c r="E181" s="2">
-        <v>3268211908</v>
+        <v>3268481108</v>
       </c>
       <c r="F181" s="2">
         <v>10480605434</v>
       </c>
       <c r="G181" s="2">
-        <v>19966235053</v>
+        <v>33646463053</v>
       </c>
       <c r="H181" s="2">
-        <v>0</v>
+        <v>449400500</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.45">
@@ -5961,10 +6048,10 @@
         <v>8</v>
       </c>
       <c r="B182" s="2">
-        <v>3658728280</v>
+        <v>7317456560</v>
       </c>
       <c r="C182" s="2">
-        <v>3658728280</v>
+        <v>7317456560</v>
       </c>
       <c r="D182" s="2">
         <v>2851419420</v>
@@ -5976,7 +6063,7 @@
         <v>2851419420</v>
       </c>
       <c r="G182" s="2">
-        <v>807308860</v>
+        <v>4466037140</v>
       </c>
       <c r="H182" s="2">
         <v>0</v>
@@ -6065,10 +6152,10 @@
         <v>11</v>
       </c>
       <c r="B186" s="2">
-        <v>1515061000</v>
+        <v>3030122000</v>
       </c>
       <c r="C186" s="2">
-        <v>1515061000</v>
+        <v>3030122000</v>
       </c>
       <c r="D186" s="2">
         <v>461381691</v>
@@ -6080,7 +6167,7 @@
         <v>461381691</v>
       </c>
       <c r="G186" s="2">
-        <v>1053679309</v>
+        <v>2568740309</v>
       </c>
       <c r="H186" s="2">
         <v>0</v>
@@ -6091,10 +6178,10 @@
         <v>12</v>
       </c>
       <c r="B187" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="C187" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="D187" s="2">
         <v>0</v>
@@ -6106,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G187" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="H187" s="2">
         <v>0</v>
@@ -6117,10 +6204,10 @@
         <v>48</v>
       </c>
       <c r="B188" s="2">
-        <v>227500000</v>
+        <v>455000000</v>
       </c>
       <c r="C188" s="2">
-        <v>227500000</v>
+        <v>455000000</v>
       </c>
       <c r="D188" s="2">
         <v>5081445</v>
@@ -6132,7 +6219,7 @@
         <v>5081445</v>
       </c>
       <c r="G188" s="2">
-        <v>222418555</v>
+        <v>449918555</v>
       </c>
       <c r="H188" s="2">
         <v>0</v>
@@ -6143,22 +6230,22 @@
         <v>13</v>
       </c>
       <c r="B189" s="2">
-        <v>234500000</v>
+        <v>469000000</v>
       </c>
       <c r="C189" s="2">
-        <v>234500000</v>
+        <v>469000000</v>
       </c>
       <c r="D189" s="2">
-        <v>49635000</v>
+        <v>44160000</v>
       </c>
       <c r="E189" s="2">
-        <v>0</v>
+        <v>5475000</v>
       </c>
       <c r="F189" s="2">
         <v>49635000</v>
       </c>
       <c r="G189" s="2">
-        <v>184865000</v>
+        <v>419365000</v>
       </c>
       <c r="H189" s="2">
         <v>0</v>
@@ -6169,10 +6256,10 @@
         <v>14</v>
       </c>
       <c r="B190" s="2">
-        <v>200000000</v>
+        <v>400000000</v>
       </c>
       <c r="C190" s="2">
-        <v>200000000</v>
+        <v>400000000</v>
       </c>
       <c r="D190" s="2">
         <v>51500000</v>
@@ -6184,7 +6271,7 @@
         <v>51500000</v>
       </c>
       <c r="G190" s="2">
-        <v>148500000</v>
+        <v>348500000</v>
       </c>
       <c r="H190" s="2">
         <v>0</v>
@@ -6195,10 +6282,10 @@
         <v>15</v>
       </c>
       <c r="B191" s="2">
-        <v>304500000</v>
+        <v>609000000</v>
       </c>
       <c r="C191" s="2">
-        <v>304500000</v>
+        <v>609000000</v>
       </c>
       <c r="D191" s="2">
         <v>88477869</v>
@@ -6210,7 +6297,7 @@
         <v>135362869</v>
       </c>
       <c r="G191" s="2">
-        <v>169137131</v>
+        <v>473637131</v>
       </c>
       <c r="H191" s="2">
         <v>0</v>
@@ -6221,10 +6308,10 @@
         <v>16</v>
       </c>
       <c r="B192" s="2">
-        <v>931325000</v>
+        <v>1862650000</v>
       </c>
       <c r="C192" s="2">
-        <v>931325000</v>
+        <v>1862650000</v>
       </c>
       <c r="D192" s="2">
         <v>281432200</v>
@@ -6236,7 +6323,7 @@
         <v>341319546</v>
       </c>
       <c r="G192" s="2">
-        <v>590005454</v>
+        <v>1521330454</v>
       </c>
       <c r="H192" s="2">
         <v>0</v>
@@ -6247,10 +6334,10 @@
         <v>49</v>
       </c>
       <c r="B193" s="2">
-        <v>140500000</v>
+        <v>281000000</v>
       </c>
       <c r="C193" s="2">
-        <v>140500000</v>
+        <v>281000000</v>
       </c>
       <c r="D193" s="2">
         <v>30944688</v>
@@ -6262,7 +6349,7 @@
         <v>30944688</v>
       </c>
       <c r="G193" s="2">
-        <v>109555312</v>
+        <v>250055312</v>
       </c>
       <c r="H193" s="2">
         <v>0</v>
@@ -6273,10 +6360,10 @@
         <v>50</v>
       </c>
       <c r="B194" s="2">
-        <v>475000000</v>
+        <v>950000000</v>
       </c>
       <c r="C194" s="2">
-        <v>475000000</v>
+        <v>950000000</v>
       </c>
       <c r="D194" s="2">
         <v>0</v>
@@ -6288,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="G194" s="2">
-        <v>475000000</v>
+        <v>950000000</v>
       </c>
       <c r="H194" s="2">
         <v>0</v>
@@ -6299,10 +6386,10 @@
         <v>51</v>
       </c>
       <c r="B195" s="2">
-        <v>25000000</v>
+        <v>50000000</v>
       </c>
       <c r="C195" s="2">
-        <v>25000000</v>
+        <v>50000000</v>
       </c>
       <c r="D195" s="2">
         <v>4883000</v>
@@ -6314,7 +6401,7 @@
         <v>4883000</v>
       </c>
       <c r="G195" s="2">
-        <v>20117000</v>
+        <v>45117000</v>
       </c>
       <c r="H195" s="2">
         <v>0</v>
@@ -6325,10 +6412,10 @@
         <v>52</v>
       </c>
       <c r="B196" s="2">
-        <v>745637500</v>
+        <v>1491275000</v>
       </c>
       <c r="C196" s="2">
-        <v>745637500</v>
+        <v>1491275000</v>
       </c>
       <c r="D196" s="2">
         <v>599680000</v>
@@ -6340,7 +6427,7 @@
         <v>666445000</v>
       </c>
       <c r="G196" s="2">
-        <v>79192500</v>
+        <v>824830000</v>
       </c>
       <c r="H196" s="2">
         <v>0</v>
@@ -6351,10 +6438,10 @@
         <v>53</v>
       </c>
       <c r="B197" s="2">
-        <v>20000000</v>
+        <v>40000000</v>
       </c>
       <c r="C197" s="2">
-        <v>20000000</v>
+        <v>40000000</v>
       </c>
       <c r="D197" s="2">
         <v>6475000</v>
@@ -6366,7 +6453,7 @@
         <v>6475000</v>
       </c>
       <c r="G197" s="2">
-        <v>13525000</v>
+        <v>33525000</v>
       </c>
       <c r="H197" s="2">
         <v>0</v>
@@ -6377,10 +6464,10 @@
         <v>77</v>
       </c>
       <c r="B198" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="C198" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="D198" s="2">
         <v>0</v>
@@ -6392,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="G198" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="H198" s="2">
         <v>0</v>
@@ -6403,10 +6490,10 @@
         <v>56</v>
       </c>
       <c r="B199" s="2">
-        <v>254500000</v>
+        <v>509000000</v>
       </c>
       <c r="C199" s="2">
-        <v>254500000</v>
+        <v>509000000</v>
       </c>
       <c r="D199" s="2">
         <v>18232600</v>
@@ -6418,7 +6505,7 @@
         <v>18232600</v>
       </c>
       <c r="G199" s="2">
-        <v>236267400</v>
+        <v>490767400</v>
       </c>
       <c r="H199" s="2">
         <v>0</v>
@@ -6429,10 +6516,10 @@
         <v>22</v>
       </c>
       <c r="B200" s="2">
-        <v>75000000</v>
+        <v>150000000</v>
       </c>
       <c r="C200" s="2">
-        <v>75000000</v>
+        <v>112500000</v>
       </c>
       <c r="D200" s="2">
         <v>0</v>
@@ -6444,10 +6531,10 @@
         <v>41856000</v>
       </c>
       <c r="G200" s="2">
-        <v>33144000</v>
+        <v>70644000</v>
       </c>
       <c r="H200" s="2">
-        <v>0</v>
+        <v>37500000</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.45">
@@ -6455,22 +6542,22 @@
         <v>57</v>
       </c>
       <c r="B201" s="2">
-        <v>160050000</v>
+        <v>320100000</v>
       </c>
       <c r="C201" s="2">
-        <v>160050000</v>
+        <v>320100000</v>
       </c>
       <c r="D201" s="2">
-        <v>44525000</v>
+        <v>0</v>
       </c>
       <c r="E201" s="2">
-        <v>27250000</v>
+        <v>71775000</v>
       </c>
       <c r="F201" s="2">
         <v>71775000</v>
       </c>
       <c r="G201" s="2">
-        <v>88275000</v>
+        <v>248325000</v>
       </c>
       <c r="H201" s="2">
         <v>0</v>
@@ -6481,10 +6568,10 @@
         <v>58</v>
       </c>
       <c r="B202" s="2">
-        <v>642500000</v>
+        <v>2570000000</v>
       </c>
       <c r="C202" s="2">
-        <v>642500000</v>
+        <v>2570000000</v>
       </c>
       <c r="D202" s="2">
         <v>0</v>
@@ -6496,7 +6583,7 @@
         <v>394857596</v>
       </c>
       <c r="G202" s="2">
-        <v>247642404</v>
+        <v>2175142404</v>
       </c>
       <c r="H202" s="2">
         <v>0</v>
@@ -6507,10 +6594,10 @@
         <v>25</v>
       </c>
       <c r="B203" s="2">
-        <v>69718811</v>
+        <v>130000000</v>
       </c>
       <c r="C203" s="2">
-        <v>69718811</v>
+        <v>97500000</v>
       </c>
       <c r="D203" s="2">
         <v>3400000</v>
@@ -6522,10 +6609,10 @@
         <v>35818811</v>
       </c>
       <c r="G203" s="2">
-        <v>33900000</v>
+        <v>61681189</v>
       </c>
       <c r="H203" s="2">
-        <v>0</v>
+        <v>32500000</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.45">
@@ -6533,10 +6620,10 @@
         <v>26</v>
       </c>
       <c r="B204" s="2">
-        <v>128511500</v>
+        <v>514046000</v>
       </c>
       <c r="C204" s="2">
-        <v>128511500</v>
+        <v>385534500</v>
       </c>
       <c r="D204" s="2">
         <v>23159000</v>
@@ -6548,10 +6635,10 @@
         <v>74188500</v>
       </c>
       <c r="G204" s="2">
-        <v>54323000</v>
+        <v>311346000</v>
       </c>
       <c r="H204" s="2">
-        <v>0</v>
+        <v>128511500</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.45">
@@ -6559,10 +6646,10 @@
         <v>27</v>
       </c>
       <c r="B205" s="2">
-        <v>17500000</v>
+        <v>105000000</v>
       </c>
       <c r="C205" s="2">
-        <v>17500000</v>
+        <v>105000000</v>
       </c>
       <c r="D205" s="2">
         <v>0</v>
@@ -6574,7 +6661,7 @@
         <v>17500000</v>
       </c>
       <c r="G205" s="2">
-        <v>0</v>
+        <v>87500000</v>
       </c>
       <c r="H205" s="2">
         <v>0</v>
@@ -6585,25 +6672,25 @@
         <v>28</v>
       </c>
       <c r="B206" s="2">
-        <v>112500000</v>
+        <v>450000000</v>
       </c>
       <c r="C206" s="2">
-        <v>112500000</v>
+        <v>337500000</v>
       </c>
       <c r="D206" s="2">
-        <v>31837000</v>
+        <v>27515000</v>
       </c>
       <c r="E206" s="2">
-        <v>5730000</v>
+        <v>10052000</v>
       </c>
       <c r="F206" s="2">
         <v>37567000</v>
       </c>
       <c r="G206" s="2">
-        <v>74933000</v>
+        <v>299933000</v>
       </c>
       <c r="H206" s="2">
-        <v>0</v>
+        <v>112500000</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.45">
@@ -6611,25 +6698,25 @@
         <v>29</v>
       </c>
       <c r="B207" s="2">
+        <v>165000000</v>
+      </c>
+      <c r="C207" s="2">
+        <v>123750000</v>
+      </c>
+      <c r="D207" s="2">
+        <v>0</v>
+      </c>
+      <c r="E207" s="2">
+        <v>0</v>
+      </c>
+      <c r="F207" s="2">
+        <v>0</v>
+      </c>
+      <c r="G207" s="2">
+        <v>123750000</v>
+      </c>
+      <c r="H207" s="2">
         <v>41250000</v>
-      </c>
-      <c r="C207" s="2">
-        <v>41250000</v>
-      </c>
-      <c r="D207" s="2">
-        <v>0</v>
-      </c>
-      <c r="E207" s="2">
-        <v>0</v>
-      </c>
-      <c r="F207" s="2">
-        <v>0</v>
-      </c>
-      <c r="G207" s="2">
-        <v>41250000</v>
-      </c>
-      <c r="H207" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.45">
@@ -6637,10 +6724,10 @@
         <v>30</v>
       </c>
       <c r="B208" s="2">
-        <v>63000000</v>
+        <v>252000000</v>
       </c>
       <c r="C208" s="2">
-        <v>63000000</v>
+        <v>189000000</v>
       </c>
       <c r="D208" s="2">
         <v>0</v>
@@ -6652,10 +6739,10 @@
         <v>52728250</v>
       </c>
       <c r="G208" s="2">
-        <v>10271750</v>
+        <v>136271750</v>
       </c>
       <c r="H208" s="2">
-        <v>0</v>
+        <v>63000000</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.45">
@@ -6663,10 +6750,10 @@
         <v>79</v>
       </c>
       <c r="B209" s="2">
-        <v>4500000</v>
+        <v>18000000</v>
       </c>
       <c r="C209" s="2">
-        <v>4500000</v>
+        <v>18000000</v>
       </c>
       <c r="D209" s="2">
         <v>1245000</v>
@@ -6678,7 +6765,7 @@
         <v>3257160</v>
       </c>
       <c r="G209" s="2">
-        <v>1242840</v>
+        <v>14742840</v>
       </c>
       <c r="H209" s="2">
         <v>0</v>
@@ -6689,10 +6776,10 @@
         <v>31</v>
       </c>
       <c r="B210" s="2">
-        <v>12500000</v>
+        <v>50000000</v>
       </c>
       <c r="C210" s="2">
-        <v>12500000</v>
+        <v>50000000</v>
       </c>
       <c r="D210" s="2">
         <v>0</v>
@@ -6704,7 +6791,7 @@
         <v>12431950</v>
       </c>
       <c r="G210" s="2">
-        <v>68050</v>
+        <v>37568050</v>
       </c>
       <c r="H210" s="2">
         <v>0</v>
@@ -6923,25 +7010,25 @@
         <v>80</v>
       </c>
       <c r="B219" s="2">
-        <v>31465240899</v>
+        <v>43869608368</v>
       </c>
       <c r="C219" s="2">
-        <v>31465240899</v>
+        <v>43454346868</v>
       </c>
       <c r="D219" s="2">
-        <v>4553308913</v>
+        <v>4498986913</v>
       </c>
       <c r="E219" s="2">
-        <v>4277422190</v>
+        <v>4331744190</v>
       </c>
       <c r="F219" s="2">
         <v>8830731103</v>
       </c>
       <c r="G219" s="2">
-        <v>22634509796</v>
+        <v>34623615765</v>
       </c>
       <c r="H219" s="2">
-        <v>0</v>
+        <v>415261500</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.45">
@@ -6949,22 +7036,22 @@
         <v>8</v>
       </c>
       <c r="B220" s="2">
-        <v>11504360000</v>
+        <v>12264606000</v>
       </c>
       <c r="C220" s="2">
-        <v>11504360000</v>
+        <v>12264606000</v>
       </c>
       <c r="D220" s="2">
-        <v>8529167730</v>
+        <v>9573167730</v>
       </c>
       <c r="E220" s="2">
         <v>36030000</v>
       </c>
       <c r="F220" s="2">
-        <v>8565197730</v>
+        <v>9609197730</v>
       </c>
       <c r="G220" s="2">
-        <v>2939162270</v>
+        <v>2655408270</v>
       </c>
       <c r="H220" s="2">
         <v>0</v>
@@ -6975,10 +7062,10 @@
         <v>11</v>
       </c>
       <c r="B221" s="2">
-        <v>1171703000</v>
+        <v>1126306000</v>
       </c>
       <c r="C221" s="2">
-        <v>1171703000</v>
+        <v>1126306000</v>
       </c>
       <c r="D221" s="2">
         <v>617301007</v>
@@ -6990,7 +7077,7 @@
         <v>617301007</v>
       </c>
       <c r="G221" s="2">
-        <v>554401993</v>
+        <v>509004993</v>
       </c>
       <c r="H221" s="2">
         <v>0</v>
@@ -7001,10 +7088,10 @@
         <v>12</v>
       </c>
       <c r="B222" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="C222" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="D222" s="2">
         <v>0</v>
@@ -7016,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="G222" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="H222" s="2">
         <v>0</v>
@@ -7027,10 +7114,10 @@
         <v>48</v>
       </c>
       <c r="B223" s="2">
-        <v>247500000</v>
+        <v>495000000</v>
       </c>
       <c r="C223" s="2">
-        <v>247500000</v>
+        <v>495000000</v>
       </c>
       <c r="D223" s="2">
         <v>29117120</v>
@@ -7042,7 +7129,7 @@
         <v>29117120</v>
       </c>
       <c r="G223" s="2">
-        <v>218382880</v>
+        <v>465882880</v>
       </c>
       <c r="H223" s="2">
         <v>0</v>
@@ -7053,10 +7140,10 @@
         <v>13</v>
       </c>
       <c r="B224" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="C224" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="D224" s="2">
         <v>0</v>
@@ -7068,7 +7155,7 @@
         <v>0</v>
       </c>
       <c r="G224" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="H224" s="2">
         <v>0</v>
@@ -7079,10 +7166,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="2">
-        <v>655195500</v>
+        <v>1310391000</v>
       </c>
       <c r="C225" s="2">
-        <v>655195500</v>
+        <v>1310391000</v>
       </c>
       <c r="D225" s="2">
         <v>62324038</v>
@@ -7094,7 +7181,7 @@
         <v>162707588</v>
       </c>
       <c r="G225" s="2">
-        <v>492487912</v>
+        <v>1147683412</v>
       </c>
       <c r="H225" s="2">
         <v>0</v>
@@ -7105,10 +7192,10 @@
         <v>16</v>
       </c>
       <c r="B226" s="2">
-        <v>690000000</v>
+        <v>1380000000</v>
       </c>
       <c r="C226" s="2">
-        <v>690000000</v>
+        <v>1380000000</v>
       </c>
       <c r="D226" s="2">
         <v>321145216</v>
@@ -7120,7 +7207,7 @@
         <v>522187216</v>
       </c>
       <c r="G226" s="2">
-        <v>167812784</v>
+        <v>857812784</v>
       </c>
       <c r="H226" s="2">
         <v>0</v>
@@ -7131,10 +7218,10 @@
         <v>49</v>
       </c>
       <c r="B227" s="2">
-        <v>175000000</v>
+        <v>350000000</v>
       </c>
       <c r="C227" s="2">
-        <v>175000000</v>
+        <v>350000000</v>
       </c>
       <c r="D227" s="2">
         <v>0</v>
@@ -7146,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="G227" s="2">
-        <v>175000000</v>
+        <v>350000000</v>
       </c>
       <c r="H227" s="2">
         <v>0</v>
@@ -7157,22 +7244,22 @@
         <v>50</v>
       </c>
       <c r="B228" s="2">
+        <v>497000000</v>
+      </c>
+      <c r="C228" s="2">
+        <v>497000000</v>
+      </c>
+      <c r="D228" s="2">
         <v>496659494</v>
       </c>
-      <c r="C228" s="2">
+      <c r="E228" s="2">
+        <v>0</v>
+      </c>
+      <c r="F228" s="2">
         <v>496659494</v>
       </c>
-      <c r="D228" s="2">
-        <v>0</v>
-      </c>
-      <c r="E228" s="2">
-        <v>0</v>
-      </c>
-      <c r="F228" s="2">
-        <v>0</v>
-      </c>
       <c r="G228" s="2">
-        <v>496659494</v>
+        <v>340506</v>
       </c>
       <c r="H228" s="2">
         <v>0</v>
@@ -7183,10 +7270,10 @@
         <v>51</v>
       </c>
       <c r="B229" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="C229" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="D229" s="2">
         <v>6718000</v>
@@ -7198,7 +7285,7 @@
         <v>6718000</v>
       </c>
       <c r="G229" s="2">
-        <v>43282000</v>
+        <v>93282000</v>
       </c>
       <c r="H229" s="2">
         <v>0</v>
@@ -7209,22 +7296,22 @@
         <v>52</v>
       </c>
       <c r="B230" s="2">
-        <v>2471712500</v>
+        <v>2264065000</v>
       </c>
       <c r="C230" s="2">
-        <v>2471712500</v>
+        <v>2264065000</v>
       </c>
       <c r="D230" s="2">
-        <v>1339680000</v>
+        <v>1986680000</v>
       </c>
       <c r="E230" s="2">
         <v>0</v>
       </c>
       <c r="F230" s="2">
-        <v>1339680000</v>
+        <v>1986680000</v>
       </c>
       <c r="G230" s="2">
-        <v>1132032500</v>
+        <v>277385000</v>
       </c>
       <c r="H230" s="2">
         <v>0</v>
@@ -7235,10 +7322,10 @@
         <v>77</v>
       </c>
       <c r="B231" s="2">
-        <v>15000000</v>
+        <v>30000000</v>
       </c>
       <c r="C231" s="2">
-        <v>15000000</v>
+        <v>30000000</v>
       </c>
       <c r="D231" s="2">
         <v>0</v>
@@ -7250,7 +7337,7 @@
         <v>0</v>
       </c>
       <c r="G231" s="2">
-        <v>15000000</v>
+        <v>30000000</v>
       </c>
       <c r="H231" s="2">
         <v>0</v>
@@ -7261,10 +7348,10 @@
         <v>56</v>
       </c>
       <c r="B232" s="2">
-        <v>577500000</v>
+        <v>1155000000</v>
       </c>
       <c r="C232" s="2">
-        <v>577500000</v>
+        <v>1155000000</v>
       </c>
       <c r="D232" s="2">
         <v>495830000</v>
@@ -7276,7 +7363,7 @@
         <v>495830000</v>
       </c>
       <c r="G232" s="2">
-        <v>81670000</v>
+        <v>659170000</v>
       </c>
       <c r="H232" s="2">
         <v>0</v>
@@ -7287,10 +7374,10 @@
         <v>22</v>
       </c>
       <c r="B233" s="2">
-        <v>520000000</v>
+        <v>1040000000</v>
       </c>
       <c r="C233" s="2">
-        <v>520000000</v>
+        <v>780000000</v>
       </c>
       <c r="D233" s="2">
         <v>0</v>
@@ -7302,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="G233" s="2">
-        <v>520000000</v>
+        <v>780000000</v>
       </c>
       <c r="H233" s="2">
-        <v>0</v>
+        <v>260000000</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.45">
@@ -7313,22 +7400,22 @@
         <v>57</v>
       </c>
       <c r="B234" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="C234" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="D234" s="2">
+        <v>0</v>
+      </c>
+      <c r="E234" s="2">
         <v>32848750</v>
-      </c>
-      <c r="E234" s="2">
-        <v>0</v>
       </c>
       <c r="F234" s="2">
         <v>32848750</v>
       </c>
       <c r="G234" s="2">
-        <v>92151250</v>
+        <v>217151250</v>
       </c>
       <c r="H234" s="2">
         <v>0</v>
@@ -7339,10 +7426,10 @@
         <v>58</v>
       </c>
       <c r="B235" s="2">
-        <v>765894000</v>
+        <v>3063576000</v>
       </c>
       <c r="C235" s="2">
-        <v>765894000</v>
+        <v>3063576000</v>
       </c>
       <c r="D235" s="2">
         <v>0</v>
@@ -7354,7 +7441,7 @@
         <v>396859899</v>
       </c>
       <c r="G235" s="2">
-        <v>369034101</v>
+        <v>2666716101</v>
       </c>
       <c r="H235" s="2">
         <v>0</v>
@@ -7365,10 +7452,10 @@
         <v>25</v>
       </c>
       <c r="B236" s="2">
-        <v>36720850</v>
+        <v>146883400</v>
       </c>
       <c r="C236" s="2">
-        <v>36720850</v>
+        <v>110162550</v>
       </c>
       <c r="D236" s="2">
         <v>10311000</v>
@@ -7380,10 +7467,10 @@
         <v>20271000</v>
       </c>
       <c r="G236" s="2">
-        <v>16449850</v>
+        <v>89891550</v>
       </c>
       <c r="H236" s="2">
-        <v>0</v>
+        <v>36720850</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.45">
@@ -7391,10 +7478,10 @@
         <v>26</v>
       </c>
       <c r="B237" s="2">
-        <v>118079500</v>
+        <v>472318000</v>
       </c>
       <c r="C237" s="2">
-        <v>118079500</v>
+        <v>354238500</v>
       </c>
       <c r="D237" s="2">
         <v>29494000</v>
@@ -7406,10 +7493,10 @@
         <v>81611900</v>
       </c>
       <c r="G237" s="2">
-        <v>36467600</v>
+        <v>272626600</v>
       </c>
       <c r="H237" s="2">
-        <v>0</v>
+        <v>118079500</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.45">
@@ -7417,10 +7504,10 @@
         <v>27</v>
       </c>
       <c r="B238" s="2">
-        <v>24750000</v>
+        <v>99000000</v>
       </c>
       <c r="C238" s="2">
-        <v>24750000</v>
+        <v>99000000</v>
       </c>
       <c r="D238" s="2">
         <v>0</v>
@@ -7432,7 +7519,7 @@
         <v>16500000</v>
       </c>
       <c r="G238" s="2">
-        <v>8250000</v>
+        <v>82500000</v>
       </c>
       <c r="H238" s="2">
         <v>0</v>
@@ -7443,7 +7530,7 @@
         <v>28</v>
       </c>
       <c r="B239" s="2">
-        <v>732016185</v>
+        <v>775000000</v>
       </c>
       <c r="C239" s="2">
         <v>732016185</v>
@@ -7461,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="2">
-        <v>0</v>
+        <v>42983815</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.45">
@@ -7469,10 +7556,10 @@
         <v>30</v>
       </c>
       <c r="B240" s="2">
-        <v>67428000</v>
+        <v>269712000</v>
       </c>
       <c r="C240" s="2">
-        <v>67428000</v>
+        <v>202284000</v>
       </c>
       <c r="D240" s="2">
         <v>0</v>
@@ -7484,10 +7571,10 @@
         <v>50796750</v>
       </c>
       <c r="G240" s="2">
-        <v>16631250</v>
+        <v>151487250</v>
       </c>
       <c r="H240" s="2">
-        <v>0</v>
+        <v>67428000</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.45">
@@ -7495,10 +7582,10 @@
         <v>31</v>
       </c>
       <c r="B241" s="2">
-        <v>15000000</v>
+        <v>60000000</v>
       </c>
       <c r="C241" s="2">
-        <v>15000000</v>
+        <v>60000000</v>
       </c>
       <c r="D241" s="2">
         <v>14997987</v>
@@ -7510,7 +7597,7 @@
         <v>14997987</v>
       </c>
       <c r="G241" s="2">
-        <v>2013</v>
+        <v>45002013</v>
       </c>
       <c r="H241" s="2">
         <v>0</v>
@@ -7729,25 +7816,25 @@
         <v>81</v>
       </c>
       <c r="B250" s="2">
-        <v>42600646349</v>
+        <v>49439984720</v>
       </c>
       <c r="C250" s="2">
-        <v>42600646349</v>
+        <v>48914772555</v>
       </c>
       <c r="D250" s="2">
-        <v>12194794533</v>
+        <v>14349605277</v>
       </c>
       <c r="E250" s="2">
-        <v>4391651962</v>
+        <v>4424500712</v>
       </c>
       <c r="F250" s="2">
-        <v>16586446495</v>
+        <v>18774105989</v>
       </c>
       <c r="G250" s="2">
-        <v>26014199854</v>
+        <v>30140666566</v>
       </c>
       <c r="H250" s="2">
-        <v>0</v>
+        <v>525212165</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.45">
@@ -7943,16 +8030,16 @@
         <v>850000000</v>
       </c>
       <c r="D258" s="2">
-        <v>259809160</v>
+        <v>309489160</v>
       </c>
       <c r="E258" s="2">
         <v>74800000</v>
       </c>
       <c r="F258" s="2">
-        <v>334609160</v>
+        <v>384289160</v>
       </c>
       <c r="G258" s="2">
-        <v>515390840</v>
+        <v>465710840</v>
       </c>
       <c r="H258" s="2">
         <v>0</v>
@@ -8515,10 +8602,10 @@
         <v>13675500</v>
       </c>
       <c r="D280" s="2">
+        <v>0</v>
+      </c>
+      <c r="E280" s="2">
         <v>13582000</v>
-      </c>
-      <c r="E280" s="2">
-        <v>0</v>
       </c>
       <c r="F280" s="2">
         <v>13582000</v>
@@ -8775,16 +8862,16 @@
         <v>45434097707</v>
       </c>
       <c r="D290" s="2">
-        <v>6688481980</v>
+        <v>6724579980</v>
       </c>
       <c r="E290" s="2">
-        <v>5334064446</v>
+        <v>5347646446</v>
       </c>
       <c r="F290" s="2">
-        <v>12022546426</v>
+        <v>12072226426</v>
       </c>
       <c r="G290" s="2">
-        <v>33411551281</v>
+        <v>33361871281</v>
       </c>
       <c r="H290" s="2">
         <v>0</v>
@@ -8853,16 +8940,16 @@
         <v>488774000</v>
       </c>
       <c r="D293" s="2">
-        <v>0</v>
+        <v>472749437</v>
       </c>
       <c r="E293" s="2">
         <v>0</v>
       </c>
       <c r="F293" s="2">
-        <v>0</v>
+        <v>472749437</v>
       </c>
       <c r="G293" s="2">
-        <v>488774000</v>
+        <v>16024563</v>
       </c>
       <c r="H293" s="2">
         <v>0</v>
@@ -8879,16 +8966,16 @@
         <v>498000000</v>
       </c>
       <c r="D294" s="2">
-        <v>0</v>
+        <v>487985800</v>
       </c>
       <c r="E294" s="2">
         <v>0</v>
       </c>
       <c r="F294" s="2">
-        <v>0</v>
+        <v>487985800</v>
       </c>
       <c r="G294" s="2">
-        <v>498000000</v>
+        <v>10014200</v>
       </c>
       <c r="H294" s="2">
         <v>0</v>
@@ -8957,10 +9044,10 @@
         <v>1222108000</v>
       </c>
       <c r="D297" s="2">
-        <v>107724690</v>
+        <v>58082710</v>
       </c>
       <c r="E297" s="2">
-        <v>0</v>
+        <v>49641980</v>
       </c>
       <c r="F297" s="2">
         <v>107724690</v>
@@ -8983,10 +9070,10 @@
         <v>534300000</v>
       </c>
       <c r="D298" s="2">
-        <v>77914500</v>
+        <v>31132500</v>
       </c>
       <c r="E298" s="2">
-        <v>96550828</v>
+        <v>143332828</v>
       </c>
       <c r="F298" s="2">
         <v>174465328</v>
@@ -9087,16 +9174,16 @@
         <v>1882400000</v>
       </c>
       <c r="D302" s="2">
-        <v>210764000</v>
+        <v>1658705000</v>
       </c>
       <c r="E302" s="2">
         <v>0</v>
       </c>
       <c r="F302" s="2">
-        <v>210764000</v>
+        <v>1658705000</v>
       </c>
       <c r="G302" s="2">
-        <v>1671636000</v>
+        <v>223695000</v>
       </c>
       <c r="H302" s="2">
         <v>0</v>
@@ -9295,16 +9382,16 @@
         <v>82504500</v>
       </c>
       <c r="D310" s="2">
-        <v>6850000</v>
+        <v>36154000</v>
       </c>
       <c r="E310" s="2">
         <v>13891000</v>
       </c>
       <c r="F310" s="2">
-        <v>20741000</v>
+        <v>50045000</v>
       </c>
       <c r="G310" s="2">
-        <v>61763500</v>
+        <v>32459500</v>
       </c>
       <c r="H310" s="2">
         <v>27501500</v>
@@ -9347,16 +9434,16 @@
         <v>385800000</v>
       </c>
       <c r="D312" s="2">
-        <v>37890000</v>
+        <v>0</v>
       </c>
       <c r="E312" s="2">
-        <v>3485000</v>
+        <v>37922635</v>
       </c>
       <c r="F312" s="2">
-        <v>41375000</v>
+        <v>37922635</v>
       </c>
       <c r="G312" s="2">
-        <v>344425000</v>
+        <v>347877365</v>
       </c>
       <c r="H312" s="2">
         <v>128600000</v>
@@ -9376,13 +9463,13 @@
         <v>0</v>
       </c>
       <c r="E313" s="2">
-        <v>38303000</v>
+        <v>39065500</v>
       </c>
       <c r="F313" s="2">
-        <v>38303000</v>
+        <v>39065500</v>
       </c>
       <c r="G313" s="2">
-        <v>134197000</v>
+        <v>133434500</v>
       </c>
       <c r="H313" s="2">
         <v>57500000</v>
@@ -9428,13 +9515,13 @@
         <v>0</v>
       </c>
       <c r="E315" s="2">
-        <v>970906178</v>
+        <v>970917428</v>
       </c>
       <c r="F315" s="2">
-        <v>970906178</v>
+        <v>970917428</v>
       </c>
       <c r="G315" s="2">
-        <v>6082886087</v>
+        <v>6082874837</v>
       </c>
       <c r="H315" s="2">
         <v>0</v>
@@ -9633,16 +9720,16 @@
         <v>30454436960</v>
       </c>
       <c r="D323" s="2">
-        <v>2230133911</v>
+        <v>4533800168</v>
       </c>
       <c r="E323" s="2">
-        <v>3123500410</v>
+        <v>3255135775</v>
       </c>
       <c r="F323" s="2">
-        <v>5353634321</v>
+        <v>7788935943</v>
       </c>
       <c r="G323" s="2">
-        <v>25100802639</v>
+        <v>22665501017</v>
       </c>
       <c r="H323" s="2">
         <v>260139500</v>
@@ -9679,10 +9766,10 @@
         <v>11</v>
       </c>
       <c r="B325" s="2">
-        <v>2948978000</v>
+        <v>2948978291</v>
       </c>
       <c r="C325" s="2">
-        <v>2948978000</v>
+        <v>2948978291</v>
       </c>
       <c r="D325" s="2">
         <v>2788546174</v>
@@ -9694,7 +9781,7 @@
         <v>2837419124</v>
       </c>
       <c r="G325" s="2">
-        <v>111558876</v>
+        <v>111559167</v>
       </c>
       <c r="H325" s="2">
         <v>0</v>
@@ -9705,10 +9792,10 @@
         <v>12</v>
       </c>
       <c r="B326" s="2">
-        <v>223903500</v>
+        <v>447807006</v>
       </c>
       <c r="C326" s="2">
-        <v>223903500</v>
+        <v>447807006</v>
       </c>
       <c r="D326" s="2">
         <v>0</v>
@@ -9720,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="G326" s="2">
-        <v>223903500</v>
+        <v>447807006</v>
       </c>
       <c r="H326" s="2">
         <v>0</v>
@@ -9731,10 +9818,10 @@
         <v>48</v>
       </c>
       <c r="B327" s="2">
-        <v>1880742000</v>
+        <v>1880742104</v>
       </c>
       <c r="C327" s="2">
-        <v>1880742000</v>
+        <v>1880742104</v>
       </c>
       <c r="D327" s="2">
         <v>1395485871</v>
@@ -9746,7 +9833,7 @@
         <v>1395485871</v>
       </c>
       <c r="G327" s="2">
-        <v>485256129</v>
+        <v>485256233</v>
       </c>
       <c r="H327" s="2">
         <v>0</v>
@@ -9757,10 +9844,10 @@
         <v>13</v>
       </c>
       <c r="B328" s="2">
-        <v>106528224</v>
+        <v>213056448</v>
       </c>
       <c r="C328" s="2">
-        <v>106528224</v>
+        <v>213056448</v>
       </c>
       <c r="D328" s="2">
         <v>33060600</v>
@@ -9772,7 +9859,7 @@
         <v>33060600</v>
       </c>
       <c r="G328" s="2">
-        <v>73467624</v>
+        <v>179995848</v>
       </c>
       <c r="H328" s="2">
         <v>0</v>
@@ -9783,10 +9870,10 @@
         <v>14</v>
       </c>
       <c r="B329" s="2">
-        <v>428000000</v>
+        <v>687000000</v>
       </c>
       <c r="C329" s="2">
-        <v>428000000</v>
+        <v>687000000</v>
       </c>
       <c r="D329" s="2">
         <v>0</v>
@@ -9798,7 +9885,7 @@
         <v>141841100</v>
       </c>
       <c r="G329" s="2">
-        <v>286158900</v>
+        <v>545158900</v>
       </c>
       <c r="H329" s="2">
         <v>0</v>
@@ -9809,10 +9896,10 @@
         <v>15</v>
       </c>
       <c r="B330" s="2">
-        <v>1395999500</v>
+        <v>2791999194</v>
       </c>
       <c r="C330" s="2">
-        <v>1395999500</v>
+        <v>2791999194</v>
       </c>
       <c r="D330" s="2">
         <v>562101045</v>
@@ -9824,7 +9911,7 @@
         <v>698858425</v>
       </c>
       <c r="G330" s="2">
-        <v>697141075</v>
+        <v>2093140769</v>
       </c>
       <c r="H330" s="2">
         <v>0</v>
@@ -9835,22 +9922,22 @@
         <v>16</v>
       </c>
       <c r="B331" s="2">
-        <v>830172000</v>
+        <v>1660344000</v>
       </c>
       <c r="C331" s="2">
-        <v>830172000</v>
+        <v>1660344000</v>
       </c>
       <c r="D331" s="2">
-        <v>377887300</v>
+        <v>370874500</v>
       </c>
       <c r="E331" s="2">
-        <v>284002988</v>
+        <v>291015788</v>
       </c>
       <c r="F331" s="2">
         <v>661890288</v>
       </c>
       <c r="G331" s="2">
-        <v>168281712</v>
+        <v>998453712</v>
       </c>
       <c r="H331" s="2">
         <v>0</v>
@@ -9861,10 +9948,10 @@
         <v>49</v>
       </c>
       <c r="B332" s="2">
-        <v>163577500</v>
+        <v>327155000</v>
       </c>
       <c r="C332" s="2">
-        <v>163577500</v>
+        <v>327155000</v>
       </c>
       <c r="D332" s="2">
         <v>67275600</v>
@@ -9876,7 +9963,7 @@
         <v>67275600</v>
       </c>
       <c r="G332" s="2">
-        <v>96301900</v>
+        <v>259879400</v>
       </c>
       <c r="H332" s="2">
         <v>0</v>
@@ -9887,10 +9974,10 @@
         <v>50</v>
       </c>
       <c r="B333" s="2">
-        <v>415688000</v>
+        <v>831375509</v>
       </c>
       <c r="C333" s="2">
-        <v>415688000</v>
+        <v>831375509</v>
       </c>
       <c r="D333" s="2">
         <v>345662595</v>
@@ -9902,7 +9989,7 @@
         <v>345662595</v>
       </c>
       <c r="G333" s="2">
-        <v>70025405</v>
+        <v>485712914</v>
       </c>
       <c r="H333" s="2">
         <v>0</v>
@@ -9939,10 +10026,10 @@
         <v>77</v>
       </c>
       <c r="B335" s="2">
-        <v>300000000</v>
+        <v>600000000</v>
       </c>
       <c r="C335" s="2">
-        <v>300000000</v>
+        <v>600000000</v>
       </c>
       <c r="D335" s="2">
         <v>0</v>
@@ -9954,7 +10041,7 @@
         <v>0</v>
       </c>
       <c r="G335" s="2">
-        <v>300000000</v>
+        <v>600000000</v>
       </c>
       <c r="H335" s="2">
         <v>0</v>
@@ -9965,10 +10052,10 @@
         <v>56</v>
       </c>
       <c r="B336" s="2">
-        <v>500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="C336" s="2">
-        <v>500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D336" s="2">
         <v>0</v>
@@ -9980,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="G336" s="2">
-        <v>500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="H336" s="2">
         <v>0</v>
@@ -9991,10 +10078,10 @@
         <v>22</v>
       </c>
       <c r="B337" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="C337" s="2">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="D337" s="2">
         <v>0</v>
@@ -10006,10 +10093,10 @@
         <v>0</v>
       </c>
       <c r="G337" s="2">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="H337" s="2">
-        <v>0</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.45">
@@ -10017,22 +10104,22 @@
         <v>57</v>
       </c>
       <c r="B338" s="2">
-        <v>70775000</v>
+        <v>141550000</v>
       </c>
       <c r="C338" s="2">
-        <v>70775000</v>
+        <v>141550000</v>
       </c>
       <c r="D338" s="2">
-        <v>24082000</v>
+        <v>0</v>
       </c>
       <c r="E338" s="2">
-        <v>3970000</v>
+        <v>28052000</v>
       </c>
       <c r="F338" s="2">
         <v>28052000</v>
       </c>
       <c r="G338" s="2">
-        <v>42723000</v>
+        <v>113498000</v>
       </c>
       <c r="H338" s="2">
         <v>0</v>
@@ -10043,10 +10130,10 @@
         <v>58</v>
       </c>
       <c r="B339" s="2">
-        <v>880440000</v>
+        <v>2911760000</v>
       </c>
       <c r="C339" s="2">
-        <v>880440000</v>
+        <v>2911760000</v>
       </c>
       <c r="D339" s="2">
         <v>581770</v>
@@ -10058,7 +10145,7 @@
         <v>412137110</v>
       </c>
       <c r="G339" s="2">
-        <v>468302890</v>
+        <v>2499622890</v>
       </c>
       <c r="H339" s="2">
         <v>0</v>
@@ -10069,10 +10156,10 @@
         <v>25</v>
       </c>
       <c r="B340" s="2">
-        <v>77500000</v>
+        <v>180000000</v>
       </c>
       <c r="C340" s="2">
-        <v>77500000</v>
+        <v>135000000</v>
       </c>
       <c r="D340" s="2">
         <v>23940000</v>
@@ -10084,10 +10171,10 @@
         <v>37404500</v>
       </c>
       <c r="G340" s="2">
-        <v>40095500</v>
+        <v>97595500</v>
       </c>
       <c r="H340" s="2">
-        <v>0</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.45">
@@ -10095,25 +10182,25 @@
         <v>26</v>
       </c>
       <c r="B341" s="2">
-        <v>154250000</v>
+        <v>761439700</v>
       </c>
       <c r="C341" s="2">
-        <v>154250000</v>
+        <v>571079775</v>
       </c>
       <c r="D341" s="2">
-        <v>21601800</v>
+        <v>21171800</v>
       </c>
       <c r="E341" s="2">
-        <v>60021850</v>
+        <v>60451850</v>
       </c>
       <c r="F341" s="2">
         <v>81623650</v>
       </c>
       <c r="G341" s="2">
-        <v>72626350</v>
+        <v>489456125</v>
       </c>
       <c r="H341" s="2">
-        <v>0</v>
+        <v>190359925</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.45">
@@ -10121,10 +10208,10 @@
         <v>27</v>
       </c>
       <c r="B342" s="2">
-        <v>27750000</v>
+        <v>99900000</v>
       </c>
       <c r="C342" s="2">
-        <v>27750000</v>
+        <v>99900000</v>
       </c>
       <c r="D342" s="2">
         <v>0</v>
@@ -10136,7 +10223,7 @@
         <v>18500000</v>
       </c>
       <c r="G342" s="2">
-        <v>9250000</v>
+        <v>81400000</v>
       </c>
       <c r="H342" s="2">
         <v>0</v>
@@ -10147,10 +10234,10 @@
         <v>28</v>
       </c>
       <c r="B343" s="2">
-        <v>286250000</v>
+        <v>616500000</v>
       </c>
       <c r="C343" s="2">
-        <v>286250000</v>
+        <v>462375000</v>
       </c>
       <c r="D343" s="2">
         <v>16504900</v>
@@ -10162,10 +10249,10 @@
         <v>19527670</v>
       </c>
       <c r="G343" s="2">
-        <v>266722330</v>
+        <v>442847330</v>
       </c>
       <c r="H343" s="2">
-        <v>0</v>
+        <v>154125000</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.45">
@@ -10173,10 +10260,10 @@
         <v>30</v>
       </c>
       <c r="B344" s="2">
-        <v>108000000</v>
+        <v>347400000</v>
       </c>
       <c r="C344" s="2">
-        <v>108000000</v>
+        <v>260550000</v>
       </c>
       <c r="D344" s="2">
         <v>0</v>
@@ -10188,10 +10275,10 @@
         <v>52841500</v>
       </c>
       <c r="G344" s="2">
-        <v>55158500</v>
+        <v>207708500</v>
       </c>
       <c r="H344" s="2">
-        <v>0</v>
+        <v>86850000</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.45">
@@ -10199,10 +10286,10 @@
         <v>79</v>
       </c>
       <c r="B345" s="2">
-        <v>1500000</v>
+        <v>6000000</v>
       </c>
       <c r="C345" s="2">
-        <v>1500000</v>
+        <v>6000000</v>
       </c>
       <c r="D345" s="2">
         <v>384315</v>
@@ -10214,7 +10301,7 @@
         <v>384315</v>
       </c>
       <c r="G345" s="2">
-        <v>1115685</v>
+        <v>5615685</v>
       </c>
       <c r="H345" s="2">
         <v>0</v>
@@ -10225,10 +10312,10 @@
         <v>31</v>
       </c>
       <c r="B346" s="2">
-        <v>16379250</v>
+        <v>56157000</v>
       </c>
       <c r="C346" s="2">
-        <v>16379250</v>
+        <v>56157000</v>
       </c>
       <c r="D346" s="2">
         <v>0</v>
@@ -10240,7 +10327,7 @@
         <v>15178108</v>
       </c>
       <c r="G346" s="2">
-        <v>1201142</v>
+        <v>40978892</v>
       </c>
       <c r="H346" s="2">
         <v>0</v>
@@ -10459,25 +10546,25 @@
         <v>84</v>
       </c>
       <c r="B355" s="2">
-        <v>50160692946</v>
+        <v>57953424224</v>
       </c>
       <c r="C355" s="2">
-        <v>50160692946</v>
+        <v>57427089299</v>
       </c>
       <c r="D355" s="2">
-        <v>19306486525</v>
+        <v>19274961725</v>
       </c>
       <c r="E355" s="2">
-        <v>6016598991</v>
+        <v>6048123791</v>
       </c>
       <c r="F355" s="2">
         <v>25323085516</v>
       </c>
       <c r="G355" s="2">
-        <v>24837607430</v>
+        <v>32104003783</v>
       </c>
       <c r="H355" s="2">
-        <v>0</v>
+        <v>526334925</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.45">
@@ -10485,10 +10572,10 @@
         <v>8</v>
       </c>
       <c r="B356" s="2">
-        <v>1645662000</v>
+        <v>3291324000</v>
       </c>
       <c r="C356" s="2">
-        <v>1645662000</v>
+        <v>3291324000</v>
       </c>
       <c r="D356" s="2">
         <v>0</v>
@@ -10500,7 +10587,7 @@
         <v>0</v>
       </c>
       <c r="G356" s="2">
-        <v>1645662000</v>
+        <v>3291324000</v>
       </c>
       <c r="H356" s="2">
         <v>0</v>
@@ -10511,10 +10598,10 @@
         <v>12</v>
       </c>
       <c r="B357" s="2">
-        <v>945931000</v>
+        <v>1891862000</v>
       </c>
       <c r="C357" s="2">
-        <v>945931000</v>
+        <v>1891862000</v>
       </c>
       <c r="D357" s="2">
         <v>0</v>
@@ -10526,7 +10613,7 @@
         <v>0</v>
       </c>
       <c r="G357" s="2">
-        <v>945931000</v>
+        <v>1891862000</v>
       </c>
       <c r="H357" s="2">
         <v>0</v>
@@ -10537,22 +10624,22 @@
         <v>48</v>
       </c>
       <c r="B358" s="2">
-        <v>1122403500</v>
+        <v>2244807000</v>
       </c>
       <c r="C358" s="2">
-        <v>1122403500</v>
+        <v>2244807000</v>
       </c>
       <c r="D358" s="2">
-        <v>134933637</v>
+        <v>137918578</v>
       </c>
       <c r="E358" s="2">
         <v>137784161</v>
       </c>
       <c r="F358" s="2">
-        <v>272717798</v>
+        <v>275702739</v>
       </c>
       <c r="G358" s="2">
-        <v>849685702</v>
+        <v>1969104261</v>
       </c>
       <c r="H358" s="2">
         <v>0</v>
@@ -10563,10 +10650,10 @@
         <v>13</v>
       </c>
       <c r="B359" s="2">
-        <v>74888500</v>
+        <v>149777000</v>
       </c>
       <c r="C359" s="2">
-        <v>74888500</v>
+        <v>149777000</v>
       </c>
       <c r="D359" s="2">
         <v>3421001</v>
@@ -10578,7 +10665,7 @@
         <v>3421001</v>
       </c>
       <c r="G359" s="2">
-        <v>71467499</v>
+        <v>146355999</v>
       </c>
       <c r="H359" s="2">
         <v>0</v>
@@ -10589,10 +10676,10 @@
         <v>14</v>
       </c>
       <c r="B360" s="2">
-        <v>16624000</v>
+        <v>33248000</v>
       </c>
       <c r="C360" s="2">
-        <v>16624000</v>
+        <v>33248000</v>
       </c>
       <c r="D360" s="2">
         <v>0</v>
@@ -10604,7 +10691,7 @@
         <v>16623760</v>
       </c>
       <c r="G360" s="2">
-        <v>240</v>
+        <v>16624240</v>
       </c>
       <c r="H360" s="2">
         <v>0</v>
@@ -10615,10 +10702,10 @@
         <v>15</v>
       </c>
       <c r="B361" s="2">
-        <v>522368500</v>
+        <v>1044737000</v>
       </c>
       <c r="C361" s="2">
-        <v>522368500</v>
+        <v>1044737000</v>
       </c>
       <c r="D361" s="2">
         <v>81692227</v>
@@ -10630,7 +10717,7 @@
         <v>193507670</v>
       </c>
       <c r="G361" s="2">
-        <v>328860830</v>
+        <v>851229330</v>
       </c>
       <c r="H361" s="2">
         <v>0</v>
@@ -10641,10 +10728,10 @@
         <v>16</v>
       </c>
       <c r="B362" s="2">
-        <v>700000000</v>
+        <v>1400000000</v>
       </c>
       <c r="C362" s="2">
-        <v>700000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D362" s="2">
         <v>20715500</v>
@@ -10656,7 +10743,7 @@
         <v>172728050</v>
       </c>
       <c r="G362" s="2">
-        <v>527271950</v>
+        <v>1227271950</v>
       </c>
       <c r="H362" s="2">
         <v>0</v>
@@ -10667,10 +10754,10 @@
         <v>49</v>
       </c>
       <c r="B363" s="2">
-        <v>145275000</v>
+        <v>290550000</v>
       </c>
       <c r="C363" s="2">
-        <v>145275000</v>
+        <v>290550000</v>
       </c>
       <c r="D363" s="2">
         <v>0</v>
@@ -10682,7 +10769,7 @@
         <v>0</v>
       </c>
       <c r="G363" s="2">
-        <v>145275000</v>
+        <v>290550000</v>
       </c>
       <c r="H363" s="2">
         <v>0</v>
@@ -10693,10 +10780,10 @@
         <v>50</v>
       </c>
       <c r="B364" s="2">
-        <v>153214500</v>
+        <v>306429000</v>
       </c>
       <c r="C364" s="2">
-        <v>153214500</v>
+        <v>306429000</v>
       </c>
       <c r="D364" s="2">
         <v>0</v>
@@ -10708,7 +10795,7 @@
         <v>0</v>
       </c>
       <c r="G364" s="2">
-        <v>153214500</v>
+        <v>306429000</v>
       </c>
       <c r="H364" s="2">
         <v>0</v>
@@ -10719,10 +10806,10 @@
         <v>52</v>
       </c>
       <c r="B365" s="2">
-        <v>235100000</v>
+        <v>470200000</v>
       </c>
       <c r="C365" s="2">
-        <v>235100000</v>
+        <v>470200000</v>
       </c>
       <c r="D365" s="2">
         <v>0</v>
@@ -10734,7 +10821,7 @@
         <v>3229600</v>
       </c>
       <c r="G365" s="2">
-        <v>231870400</v>
+        <v>466970400</v>
       </c>
       <c r="H365" s="2">
         <v>0</v>
@@ -10745,10 +10832,10 @@
         <v>56</v>
       </c>
       <c r="B366" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="C366" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="D366" s="2">
         <v>0</v>
@@ -10760,7 +10847,7 @@
         <v>0</v>
       </c>
       <c r="G366" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="H366" s="2">
         <v>0</v>
@@ -10771,10 +10858,10 @@
         <v>22</v>
       </c>
       <c r="B367" s="2">
-        <v>100000000</v>
+        <v>110000000</v>
       </c>
       <c r="C367" s="2">
-        <v>100000000</v>
+        <v>82500000</v>
       </c>
       <c r="D367" s="2">
         <v>0</v>
@@ -10786,10 +10873,10 @@
         <v>0</v>
       </c>
       <c r="G367" s="2">
-        <v>100000000</v>
+        <v>82500000</v>
       </c>
       <c r="H367" s="2">
-        <v>0</v>
+        <v>27500000</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.45">
@@ -10797,10 +10884,10 @@
         <v>57</v>
       </c>
       <c r="B368" s="2">
-        <v>63030000</v>
+        <v>99980000</v>
       </c>
       <c r="C368" s="2">
-        <v>63030000</v>
+        <v>99980000</v>
       </c>
       <c r="D368" s="2">
         <v>19823200</v>
@@ -10812,7 +10899,7 @@
         <v>19823200</v>
       </c>
       <c r="G368" s="2">
-        <v>43206800</v>
+        <v>80156800</v>
       </c>
       <c r="H368" s="2">
         <v>0</v>
@@ -10823,10 +10910,10 @@
         <v>58</v>
       </c>
       <c r="B369" s="2">
-        <v>90000000</v>
+        <v>411080000</v>
       </c>
       <c r="C369" s="2">
-        <v>90000000</v>
+        <v>411080000</v>
       </c>
       <c r="D369" s="2">
         <v>1639740</v>
@@ -10838,7 +10925,7 @@
         <v>72536444</v>
       </c>
       <c r="G369" s="2">
-        <v>17463556</v>
+        <v>338543556</v>
       </c>
       <c r="H369" s="2">
         <v>0</v>
@@ -10849,10 +10936,10 @@
         <v>25</v>
       </c>
       <c r="B370" s="2">
-        <v>64000000</v>
+        <v>160000000</v>
       </c>
       <c r="C370" s="2">
-        <v>64000000</v>
+        <v>120000000</v>
       </c>
       <c r="D370" s="2">
         <v>6960000</v>
@@ -10864,10 +10951,10 @@
         <v>20447000</v>
       </c>
       <c r="G370" s="2">
-        <v>43553000</v>
+        <v>99553000</v>
       </c>
       <c r="H370" s="2">
-        <v>0</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.45">
@@ -10875,10 +10962,10 @@
         <v>26</v>
       </c>
       <c r="B371" s="2">
-        <v>300400000</v>
+        <v>400000000</v>
       </c>
       <c r="C371" s="2">
-        <v>300400000</v>
+        <v>300000000</v>
       </c>
       <c r="D371" s="2">
         <v>27274000</v>
@@ -10890,10 +10977,10 @@
         <v>105482462</v>
       </c>
       <c r="G371" s="2">
-        <v>194917538</v>
+        <v>194517538</v>
       </c>
       <c r="H371" s="2">
-        <v>0</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.45">
@@ -10901,10 +10988,10 @@
         <v>27</v>
       </c>
       <c r="B372" s="2">
-        <v>16500000</v>
+        <v>66000000</v>
       </c>
       <c r="C372" s="2">
-        <v>16500000</v>
+        <v>66000000</v>
       </c>
       <c r="D372" s="2">
         <v>0</v>
@@ -10916,7 +11003,7 @@
         <v>11000000</v>
       </c>
       <c r="G372" s="2">
-        <v>5500000</v>
+        <v>55000000</v>
       </c>
       <c r="H372" s="2">
         <v>0</v>
@@ -10927,10 +11014,10 @@
         <v>28</v>
       </c>
       <c r="B373" s="2">
-        <v>35000000</v>
+        <v>90000000</v>
       </c>
       <c r="C373" s="2">
-        <v>35000000</v>
+        <v>67500000</v>
       </c>
       <c r="D373" s="2">
         <v>0</v>
@@ -10942,10 +11029,10 @@
         <v>4415000</v>
       </c>
       <c r="G373" s="2">
-        <v>30585000</v>
+        <v>63085000</v>
       </c>
       <c r="H373" s="2">
-        <v>0</v>
+        <v>22500000</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.45">
@@ -10953,10 +11040,10 @@
         <v>30</v>
       </c>
       <c r="B374" s="2">
-        <v>42675000</v>
+        <v>170700000</v>
       </c>
       <c r="C374" s="2">
-        <v>42675000</v>
+        <v>128025000</v>
       </c>
       <c r="D374" s="2">
         <v>0</v>
@@ -10968,10 +11055,10 @@
         <v>39560000</v>
       </c>
       <c r="G374" s="2">
-        <v>3115000</v>
+        <v>88465000</v>
       </c>
       <c r="H374" s="2">
-        <v>0</v>
+        <v>42675000</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.45">
@@ -10979,10 +11066,10 @@
         <v>31</v>
       </c>
       <c r="B375" s="2">
-        <v>9000000</v>
+        <v>24000000</v>
       </c>
       <c r="C375" s="2">
-        <v>9000000</v>
+        <v>24000000</v>
       </c>
       <c r="D375" s="2">
         <v>0</v>
@@ -10994,7 +11081,7 @@
         <v>6736950</v>
       </c>
       <c r="G375" s="2">
-        <v>2263050</v>
+        <v>17263050</v>
       </c>
       <c r="H375" s="2">
         <v>0</v>
@@ -11239,25 +11326,25 @@
         <v>85</v>
       </c>
       <c r="B385" s="2">
-        <v>17495468591</v>
+        <v>23968090591</v>
       </c>
       <c r="C385" s="2">
-        <v>17495468591</v>
+        <v>23735415591</v>
       </c>
       <c r="D385" s="2">
-        <v>296459305</v>
+        <v>299444246</v>
       </c>
       <c r="E385" s="2">
         <v>2381235336</v>
       </c>
       <c r="F385" s="2">
-        <v>2677694641</v>
+        <v>2680679582</v>
       </c>
       <c r="G385" s="2">
-        <v>14817773950</v>
+        <v>21054736009</v>
       </c>
       <c r="H385" s="2">
-        <v>0</v>
+        <v>232675000</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.45">
@@ -11265,10 +11352,10 @@
         <v>8</v>
       </c>
       <c r="B386" s="2">
-        <v>1717513500</v>
+        <v>3435027000</v>
       </c>
       <c r="C386" s="2">
-        <v>1717513500</v>
+        <v>3435027000</v>
       </c>
       <c r="D386" s="2">
         <v>0</v>
@@ -11280,7 +11367,7 @@
         <v>0</v>
       </c>
       <c r="G386" s="2">
-        <v>1717513500</v>
+        <v>3435027000</v>
       </c>
       <c r="H386" s="2">
         <v>0</v>
@@ -11317,10 +11404,10 @@
         <v>12</v>
       </c>
       <c r="B388" s="2">
-        <v>233686000</v>
+        <v>467372000</v>
       </c>
       <c r="C388" s="2">
-        <v>233686000</v>
+        <v>467372000</v>
       </c>
       <c r="D388" s="2">
         <v>0</v>
@@ -11332,7 +11419,7 @@
         <v>0</v>
       </c>
       <c r="G388" s="2">
-        <v>233686000</v>
+        <v>467372000</v>
       </c>
       <c r="H388" s="2">
         <v>0</v>
@@ -11343,10 +11430,10 @@
         <v>48</v>
       </c>
       <c r="B389" s="2">
-        <v>445284000</v>
+        <v>890568000</v>
       </c>
       <c r="C389" s="2">
-        <v>445284000</v>
+        <v>890568000</v>
       </c>
       <c r="D389" s="2">
         <v>398086520</v>
@@ -11358,7 +11445,7 @@
         <v>398086520</v>
       </c>
       <c r="G389" s="2">
-        <v>47197480</v>
+        <v>492481480</v>
       </c>
       <c r="H389" s="2">
         <v>0</v>
@@ -11369,10 +11456,10 @@
         <v>13</v>
       </c>
       <c r="B390" s="2">
-        <v>78606000</v>
+        <v>157212000</v>
       </c>
       <c r="C390" s="2">
-        <v>78606000</v>
+        <v>157212000</v>
       </c>
       <c r="D390" s="2">
         <v>49855940</v>
@@ -11384,7 +11471,7 @@
         <v>49855940</v>
       </c>
       <c r="G390" s="2">
-        <v>28750060</v>
+        <v>107356060</v>
       </c>
       <c r="H390" s="2">
         <v>0</v>
@@ -11395,10 +11482,10 @@
         <v>14</v>
       </c>
       <c r="B391" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="C391" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="D391" s="2">
         <v>0</v>
@@ -11410,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="G391" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="H391" s="2">
         <v>0</v>
@@ -11421,10 +11508,10 @@
         <v>15</v>
       </c>
       <c r="B392" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="C392" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="D392" s="2">
         <v>0</v>
@@ -11436,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="G392" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="H392" s="2">
         <v>0</v>
@@ -11447,22 +11534,22 @@
         <v>16</v>
       </c>
       <c r="B393" s="2">
-        <v>345000000</v>
+        <v>690000000</v>
       </c>
       <c r="C393" s="2">
-        <v>345000000</v>
+        <v>690000000</v>
       </c>
       <c r="D393" s="2">
-        <v>202834780</v>
+        <v>103894080</v>
       </c>
       <c r="E393" s="2">
-        <v>0</v>
+        <v>98940700</v>
       </c>
       <c r="F393" s="2">
         <v>202834780</v>
       </c>
       <c r="G393" s="2">
-        <v>142165220</v>
+        <v>487165220</v>
       </c>
       <c r="H393" s="2">
         <v>0</v>
@@ -11473,10 +11560,10 @@
         <v>49</v>
       </c>
       <c r="B394" s="2">
-        <v>99350000</v>
+        <v>198700000</v>
       </c>
       <c r="C394" s="2">
-        <v>99350000</v>
+        <v>198700000</v>
       </c>
       <c r="D394" s="2">
         <v>91627175</v>
@@ -11488,7 +11575,7 @@
         <v>91627175</v>
       </c>
       <c r="G394" s="2">
-        <v>7722825</v>
+        <v>107072825</v>
       </c>
       <c r="H394" s="2">
         <v>0</v>
@@ -11499,10 +11586,10 @@
         <v>50</v>
       </c>
       <c r="B395" s="2">
-        <v>227565500</v>
+        <v>455131000</v>
       </c>
       <c r="C395" s="2">
-        <v>227565500</v>
+        <v>455131000</v>
       </c>
       <c r="D395" s="2">
         <v>0</v>
@@ -11514,7 +11601,7 @@
         <v>0</v>
       </c>
       <c r="G395" s="2">
-        <v>227565500</v>
+        <v>455131000</v>
       </c>
       <c r="H395" s="2">
         <v>0</v>
@@ -11525,10 +11612,10 @@
         <v>51</v>
       </c>
       <c r="B396" s="2">
-        <v>25000000</v>
+        <v>50000000</v>
       </c>
       <c r="C396" s="2">
-        <v>25000000</v>
+        <v>50000000</v>
       </c>
       <c r="D396" s="2">
         <v>0</v>
@@ -11540,7 +11627,7 @@
         <v>0</v>
       </c>
       <c r="G396" s="2">
-        <v>25000000</v>
+        <v>50000000</v>
       </c>
       <c r="H396" s="2">
         <v>0</v>
@@ -11551,10 +11638,10 @@
         <v>52</v>
       </c>
       <c r="B397" s="2">
-        <v>721780000</v>
+        <v>1443560000</v>
       </c>
       <c r="C397" s="2">
-        <v>721780000</v>
+        <v>1443560000</v>
       </c>
       <c r="D397" s="2">
         <v>0</v>
@@ -11566,7 +11653,7 @@
         <v>0</v>
       </c>
       <c r="G397" s="2">
-        <v>721780000</v>
+        <v>1443560000</v>
       </c>
       <c r="H397" s="2">
         <v>0</v>
@@ -11577,10 +11664,10 @@
         <v>53</v>
       </c>
       <c r="B398" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="C398" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="D398" s="2">
         <v>0</v>
@@ -11592,7 +11679,7 @@
         <v>0</v>
       </c>
       <c r="G398" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="H398" s="2">
         <v>0</v>
@@ -11603,10 +11690,10 @@
         <v>56</v>
       </c>
       <c r="B399" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="C399" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="D399" s="2">
         <v>0</v>
@@ -11618,7 +11705,7 @@
         <v>0</v>
       </c>
       <c r="G399" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="H399" s="2">
         <v>0</v>
@@ -11629,10 +11716,10 @@
         <v>22</v>
       </c>
       <c r="B400" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="C400" s="2">
-        <v>125000000</v>
+        <v>187500000</v>
       </c>
       <c r="D400" s="2">
         <v>0</v>
@@ -11644,10 +11731,10 @@
         <v>0</v>
       </c>
       <c r="G400" s="2">
-        <v>125000000</v>
+        <v>187500000</v>
       </c>
       <c r="H400" s="2">
-        <v>0</v>
+        <v>62500000</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.45">
@@ -11655,10 +11742,10 @@
         <v>57</v>
       </c>
       <c r="B401" s="2">
-        <v>158400000</v>
+        <v>316800000</v>
       </c>
       <c r="C401" s="2">
-        <v>158400000</v>
+        <v>316800000</v>
       </c>
       <c r="D401" s="2">
         <v>52208150</v>
@@ -11670,7 +11757,7 @@
         <v>52208150</v>
       </c>
       <c r="G401" s="2">
-        <v>106191850</v>
+        <v>264591850</v>
       </c>
       <c r="H401" s="2">
         <v>0</v>
@@ -11681,10 +11768,10 @@
         <v>58</v>
       </c>
       <c r="B402" s="2">
-        <v>637500000</v>
+        <v>2230000000</v>
       </c>
       <c r="C402" s="2">
-        <v>637500000</v>
+        <v>2230000000</v>
       </c>
       <c r="D402" s="2">
         <v>9815000</v>
@@ -11696,7 +11783,7 @@
         <v>227966545</v>
       </c>
       <c r="G402" s="2">
-        <v>409533455</v>
+        <v>2002033455</v>
       </c>
       <c r="H402" s="2">
         <v>0</v>
@@ -11707,10 +11794,10 @@
         <v>25</v>
       </c>
       <c r="B403" s="2">
-        <v>48400000</v>
+        <v>193600000</v>
       </c>
       <c r="C403" s="2">
-        <v>48400000</v>
+        <v>145200000</v>
       </c>
       <c r="D403" s="2">
         <v>21900000</v>
@@ -11722,10 +11809,10 @@
         <v>21900000</v>
       </c>
       <c r="G403" s="2">
-        <v>26500000</v>
+        <v>123300000</v>
       </c>
       <c r="H403" s="2">
-        <v>0</v>
+        <v>48400000</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.45">
@@ -11733,10 +11820,10 @@
         <v>26</v>
       </c>
       <c r="B404" s="2">
-        <v>170907750</v>
+        <v>593631000</v>
       </c>
       <c r="C404" s="2">
-        <v>170907750</v>
+        <v>445223250</v>
       </c>
       <c r="D404" s="2">
         <v>98217450</v>
@@ -11748,10 +11835,10 @@
         <v>166131450</v>
       </c>
       <c r="G404" s="2">
-        <v>4776300</v>
+        <v>279091800</v>
       </c>
       <c r="H404" s="2">
-        <v>0</v>
+        <v>148407750</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.45">
@@ -11759,10 +11846,10 @@
         <v>27</v>
       </c>
       <c r="B405" s="2">
-        <v>26250000</v>
+        <v>105000000</v>
       </c>
       <c r="C405" s="2">
-        <v>26250000</v>
+        <v>105000000</v>
       </c>
       <c r="D405" s="2">
         <v>0</v>
@@ -11774,7 +11861,7 @@
         <v>16500000</v>
       </c>
       <c r="G405" s="2">
-        <v>9750000</v>
+        <v>88500000</v>
       </c>
       <c r="H405" s="2">
         <v>0</v>
@@ -11785,10 +11872,10 @@
         <v>28</v>
       </c>
       <c r="B406" s="2">
-        <v>96500000</v>
+        <v>386000000</v>
       </c>
       <c r="C406" s="2">
-        <v>96500000</v>
+        <v>289500000</v>
       </c>
       <c r="D406" s="2">
         <v>2609000</v>
@@ -11800,10 +11887,10 @@
         <v>2609000</v>
       </c>
       <c r="G406" s="2">
-        <v>93891000</v>
+        <v>286891000</v>
       </c>
       <c r="H406" s="2">
-        <v>0</v>
+        <v>96500000</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.45">
@@ -11811,10 +11898,10 @@
         <v>30</v>
       </c>
       <c r="B407" s="2">
-        <v>117000000</v>
+        <v>468000000</v>
       </c>
       <c r="C407" s="2">
-        <v>117000000</v>
+        <v>351000000</v>
       </c>
       <c r="D407" s="2">
         <v>0</v>
@@ -11826,10 +11913,10 @@
         <v>65686596</v>
       </c>
       <c r="G407" s="2">
-        <v>51313404</v>
+        <v>285313404</v>
       </c>
       <c r="H407" s="2">
-        <v>0</v>
+        <v>117000000</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.45">
@@ -11837,10 +11924,10 @@
         <v>79</v>
       </c>
       <c r="B408" s="2">
-        <v>1500000</v>
+        <v>6000000</v>
       </c>
       <c r="C408" s="2">
-        <v>1500000</v>
+        <v>6000000</v>
       </c>
       <c r="D408" s="2">
         <v>0</v>
@@ -11852,7 +11939,7 @@
         <v>315000</v>
       </c>
       <c r="G408" s="2">
-        <v>1185000</v>
+        <v>5685000</v>
       </c>
       <c r="H408" s="2">
         <v>0</v>
@@ -11863,10 +11950,10 @@
         <v>31</v>
       </c>
       <c r="B409" s="2">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="C409" s="2">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="D409" s="2">
         <v>0</v>
@@ -11878,7 +11965,7 @@
         <v>0</v>
       </c>
       <c r="G409" s="2">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="H409" s="2">
         <v>0</v>
@@ -12123,30 +12210,30 @@
         <v>86</v>
       </c>
       <c r="B419" s="2">
-        <v>26293508870</v>
+        <v>34234867120</v>
       </c>
       <c r="C419" s="2">
-        <v>26293508870</v>
+        <v>33762059370</v>
       </c>
       <c r="D419" s="2">
-        <v>927154015</v>
+        <v>828213315</v>
       </c>
       <c r="E419" s="2">
-        <v>3465530767</v>
+        <v>3564471467</v>
       </c>
       <c r="F419" s="2">
         <v>4392684782</v>
       </c>
       <c r="G419" s="2">
-        <v>21900824088</v>
+        <v>29369374588</v>
       </c>
       <c r="H419" s="2">
-        <v>0</v>
+        <v>472807750</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A420" s="1" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="B420" s="3">
         <v>1871950730</v>
@@ -12155,7 +12242,6 @@
         <v>1871950730</v>
       </c>
       <c r="D420" s="3">
-        <f>F420-E420</f>
         <v>404935052</v>
       </c>
       <c r="E420" s="3">
@@ -12165,17 +12251,15 @@
         <v>483831830</v>
       </c>
       <c r="G420" s="3">
-        <f>C420-F420</f>
         <v>1388118900</v>
       </c>
       <c r="H420" s="3">
-        <f>B420-C420</f>
         <v>0</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A421" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -12187,7 +12271,7 @@
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A422" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -12199,7 +12283,7 @@
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A423" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -12211,7 +12295,7 @@
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A424" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -12223,7 +12307,7 @@
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A425" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -12235,7 +12319,7 @@
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A426" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -12247,7 +12331,7 @@
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A427" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -12259,7 +12343,7 @@
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A428" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -12271,7 +12355,7 @@
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A429" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -12283,7 +12367,7 @@
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A430" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -12295,7 +12379,7 @@
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A431" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -12307,7 +12391,7 @@
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A432" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -12319,7 +12403,7 @@
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A433" s="1" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -12331,7 +12415,7 @@
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A434" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -12343,7 +12427,7 @@
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A435" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -12355,7 +12439,7 @@
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A436" s="1" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -12367,7 +12451,7 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A437" s="1" t="s">
-        <v>48</v>
+        <v>115</v>
       </c>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -12379,7 +12463,7 @@
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A438" s="1" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -12391,7 +12475,7 @@
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A439" s="1" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -12403,7 +12487,7 @@
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A440" s="1" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -12415,7 +12499,7 @@
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A441" s="1" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -12427,7 +12511,7 @@
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A442" s="1" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -12439,7 +12523,7 @@
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A443" s="1" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -12451,7 +12535,7 @@
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A444" s="1" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B444" s="3">
         <v>60000000</v>
@@ -12460,7 +12544,6 @@
         <v>60000000</v>
       </c>
       <c r="D444" s="3">
-        <f>F444-E444</f>
         <v>9000000</v>
       </c>
       <c r="E444" s="3">
@@ -12470,17 +12553,15 @@
         <v>9000000</v>
       </c>
       <c r="G444" s="3">
-        <f>C444-F444</f>
         <v>51000000</v>
       </c>
       <c r="H444" s="3">
-        <f>B444-C444</f>
         <v>0</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A445" s="1" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="B445" s="3">
         <v>45150000</v>
@@ -12489,7 +12570,6 @@
         <v>45150000</v>
       </c>
       <c r="D445" s="3">
-        <f>F445-E445</f>
         <v>6423200</v>
       </c>
       <c r="E445" s="3">
@@ -12499,17 +12579,15 @@
         <v>12542600</v>
       </c>
       <c r="G445" s="3">
-        <f>C445-F445</f>
         <v>32607400</v>
       </c>
       <c r="H445" s="3">
-        <f>B445-C445</f>
         <v>0</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A446" s="1" t="s">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -12521,7 +12599,7 @@
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A447" s="1" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -12533,7 +12611,7 @@
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A448" s="1" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -12545,7 +12623,7 @@
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A449" s="1" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -12557,7 +12635,7 @@
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A450" s="1" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -12569,7 +12647,7 @@
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A451" s="1" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -12581,7 +12659,7 @@
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A452" s="1" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="B452" s="3">
         <v>372660000</v>
@@ -12590,7 +12668,6 @@
         <v>372660000</v>
       </c>
       <c r="D452" s="3">
-        <f>F452-E452</f>
         <v>8912700</v>
       </c>
       <c r="E452" s="3">
@@ -12600,17 +12677,15 @@
         <v>14517350</v>
       </c>
       <c r="G452" s="3">
-        <f>C452-F452</f>
         <v>358142650</v>
       </c>
       <c r="H452" s="3">
-        <f>B452-C452</f>
         <v>0</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A453" s="1" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -12622,7 +12697,7 @@
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A454" s="1" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -12634,7 +12709,7 @@
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A455" s="1" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -12646,7 +12721,7 @@
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A456" s="1" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -12658,7 +12733,7 @@
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A457" s="1" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -12670,7 +12745,7 @@
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A458" s="1" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -12682,7 +12757,7 @@
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A459" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -12694,7 +12769,7 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A460" s="1" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -12706,7 +12781,7 @@
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A461" s="1" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -12718,7 +12793,7 @@
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A462" s="1" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -12730,7 +12805,7 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A463" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -12742,7 +12817,7 @@
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A464" s="1" t="s">
-        <v>32</v>
+        <v>142</v>
       </c>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -12754,7 +12829,7 @@
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A465" s="1" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -12766,7 +12841,7 @@
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A466" s="1" t="s">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -12778,7 +12853,7 @@
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A467" s="1" t="s">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -12790,7 +12865,7 @@
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A468" s="1" t="s">
-        <v>36</v>
+        <v>146</v>
       </c>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -12802,7 +12877,7 @@
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A469" s="1" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -12814,7 +12889,7 @@
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A470" s="1" t="s">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -12826,7 +12901,7 @@
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A471" s="1" t="s">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -12838,34 +12913,27 @@
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A472" s="1" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="B472" s="3">
-        <f>SUM(B420:B471)</f>
         <v>2349760730</v>
       </c>
       <c r="C472" s="3">
-        <f t="shared" ref="C472:H472" si="0">SUM(C420:C471)</f>
         <v>2349760730</v>
       </c>
       <c r="D472" s="3">
-        <f t="shared" si="0"/>
         <v>429270952</v>
       </c>
       <c r="E472" s="3">
-        <f t="shared" si="0"/>
         <v>90620828</v>
       </c>
       <c r="F472" s="3">
-        <f t="shared" si="0"/>
         <v>519891780</v>
       </c>
       <c r="G472" s="3">
-        <f t="shared" si="0"/>
         <v>1829868950</v>
       </c>
       <c r="H472" s="3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -12874,22 +12942,22 @@
         <v>8</v>
       </c>
       <c r="B473" s="2">
-        <v>6121242000</v>
+        <v>10505111000</v>
       </c>
       <c r="C473" s="2">
-        <v>6121242000</v>
+        <v>10505111000</v>
       </c>
       <c r="D473" s="2">
-        <v>5458456599</v>
+        <v>7767056599</v>
       </c>
       <c r="E473" s="2">
         <v>0</v>
       </c>
       <c r="F473" s="2">
-        <v>5458456599</v>
+        <v>7767056599</v>
       </c>
       <c r="G473" s="2">
-        <v>662785401</v>
+        <v>2738054401</v>
       </c>
       <c r="H473" s="2">
         <v>0</v>
@@ -13027,7 +13095,7 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B479" s="2">
         <v>0</v>
@@ -13053,13 +13121,13 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="B480" s="2">
-        <v>1778331214</v>
+        <v>2312795000</v>
       </c>
       <c r="C480" s="2">
-        <v>1778331214</v>
+        <v>2312795000</v>
       </c>
       <c r="D480" s="2">
         <v>1778331214</v>
@@ -13071,7 +13139,7 @@
         <v>1778331214</v>
       </c>
       <c r="G480" s="2">
-        <v>0</v>
+        <v>534463786</v>
       </c>
       <c r="H480" s="2">
         <v>0</v>
@@ -13082,22 +13150,22 @@
         <v>53</v>
       </c>
       <c r="B481" s="2">
-        <v>2094950000</v>
+        <v>4989900000</v>
       </c>
       <c r="C481" s="2">
-        <v>2094950000</v>
+        <v>4989900000</v>
       </c>
       <c r="D481" s="2">
-        <v>897050889</v>
+        <v>805666889</v>
       </c>
       <c r="E481" s="2">
-        <v>235941248</v>
+        <v>333634248</v>
       </c>
       <c r="F481" s="2">
-        <v>1132992137</v>
+        <v>1139301137</v>
       </c>
       <c r="G481" s="2">
-        <v>961957863</v>
+        <v>3850598863</v>
       </c>
       <c r="H481" s="2">
         <v>0</v>
@@ -13105,7 +13173,7 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="B482" s="2">
         <v>0</v>
@@ -13134,10 +13202,10 @@
         <v>54</v>
       </c>
       <c r="B483" s="2">
-        <v>840000000</v>
+        <v>1680000000</v>
       </c>
       <c r="C483" s="2">
-        <v>840000000</v>
+        <v>1680000000</v>
       </c>
       <c r="D483" s="2">
         <v>353557050</v>
@@ -13149,7 +13217,7 @@
         <v>353557050</v>
       </c>
       <c r="G483" s="2">
-        <v>486442950</v>
+        <v>1326442950</v>
       </c>
       <c r="H483" s="2">
         <v>0</v>
@@ -13160,22 +13228,22 @@
         <v>77</v>
       </c>
       <c r="B484" s="2">
-        <v>246033000</v>
+        <v>492066000</v>
       </c>
       <c r="C484" s="2">
-        <v>246033000</v>
+        <v>492066000</v>
       </c>
       <c r="D484" s="2">
-        <v>4400000</v>
+        <v>31501365</v>
       </c>
       <c r="E484" s="2">
         <v>7785500</v>
       </c>
       <c r="F484" s="2">
-        <v>12185500</v>
+        <v>39286865</v>
       </c>
       <c r="G484" s="2">
-        <v>233847500</v>
+        <v>452779135</v>
       </c>
       <c r="H484" s="2">
         <v>0</v>
@@ -13183,13 +13251,13 @@
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="B485" s="2">
-        <v>312250000</v>
+        <v>624500000</v>
       </c>
       <c r="C485" s="2">
-        <v>312250000</v>
+        <v>624500000</v>
       </c>
       <c r="D485" s="2">
         <v>0</v>
@@ -13201,7 +13269,7 @@
         <v>0</v>
       </c>
       <c r="G485" s="2">
-        <v>312250000</v>
+        <v>624500000</v>
       </c>
       <c r="H485" s="2">
         <v>0</v>
@@ -13209,13 +13277,13 @@
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="B486" s="2">
-        <v>350000000</v>
+        <v>700000000</v>
       </c>
       <c r="C486" s="2">
-        <v>350000000</v>
+        <v>700000000</v>
       </c>
       <c r="D486" s="2">
         <v>0</v>
@@ -13227,7 +13295,7 @@
         <v>0</v>
       </c>
       <c r="G486" s="2">
-        <v>350000000</v>
+        <v>700000000</v>
       </c>
       <c r="H486" s="2">
         <v>0</v>
@@ -13235,7 +13303,7 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="B487" s="2">
         <v>0</v>
@@ -13261,25 +13329,25 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="B488" s="2">
-        <v>372500000</v>
+        <v>745000000</v>
       </c>
       <c r="C488" s="2">
-        <v>372500000</v>
+        <v>745000000</v>
       </c>
       <c r="D488" s="2">
-        <v>19421480</v>
+        <v>26235280</v>
       </c>
       <c r="E488" s="2">
         <v>32460000</v>
       </c>
       <c r="F488" s="2">
-        <v>51881480</v>
+        <v>58695280</v>
       </c>
       <c r="G488" s="2">
-        <v>320618520</v>
+        <v>686304720</v>
       </c>
       <c r="H488" s="2">
         <v>0</v>
@@ -13287,25 +13355,25 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="B489" s="2">
-        <v>2397799000</v>
+        <v>4029356000</v>
       </c>
       <c r="C489" s="2">
-        <v>2397799000</v>
+        <v>4029356000</v>
       </c>
       <c r="D489" s="2">
-        <v>459375000</v>
+        <v>2411599000</v>
       </c>
       <c r="E489" s="2">
         <v>29795000</v>
       </c>
       <c r="F489" s="2">
-        <v>489170000</v>
+        <v>2441394000</v>
       </c>
       <c r="G489" s="2">
-        <v>1908629000</v>
+        <v>1587962000</v>
       </c>
       <c r="H489" s="2">
         <v>0</v>
@@ -13313,13 +13381,13 @@
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="B490" s="2">
-        <v>1098750000</v>
+        <v>297500000</v>
       </c>
       <c r="C490" s="2">
-        <v>1098750000</v>
+        <v>297500000</v>
       </c>
       <c r="D490" s="2">
         <v>0</v>
@@ -13331,7 +13399,7 @@
         <v>0</v>
       </c>
       <c r="G490" s="2">
-        <v>1098750000</v>
+        <v>297500000</v>
       </c>
       <c r="H490" s="2">
         <v>0</v>
@@ -13342,10 +13410,10 @@
         <v>55</v>
       </c>
       <c r="B491" s="2">
-        <v>133125000</v>
+        <v>266250000</v>
       </c>
       <c r="C491" s="2">
-        <v>133125000</v>
+        <v>266250000</v>
       </c>
       <c r="D491" s="2">
         <v>0</v>
@@ -13357,7 +13425,7 @@
         <v>40800000</v>
       </c>
       <c r="G491" s="2">
-        <v>92325000</v>
+        <v>225450000</v>
       </c>
       <c r="H491" s="2">
         <v>0</v>
@@ -13368,10 +13436,10 @@
         <v>56</v>
       </c>
       <c r="B492" s="2">
-        <v>375000000</v>
+        <v>1350000000</v>
       </c>
       <c r="C492" s="2">
-        <v>375000000</v>
+        <v>1350000000</v>
       </c>
       <c r="D492" s="2">
         <v>0</v>
@@ -13383,7 +13451,7 @@
         <v>0</v>
       </c>
       <c r="G492" s="2">
-        <v>375000000</v>
+        <v>1350000000</v>
       </c>
       <c r="H492" s="2">
         <v>0</v>
@@ -13394,10 +13462,10 @@
         <v>22</v>
       </c>
       <c r="B493" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="C493" s="2">
-        <v>50000000</v>
+        <v>75000000</v>
       </c>
       <c r="D493" s="2">
         <v>0</v>
@@ -13409,10 +13477,10 @@
         <v>12720000</v>
       </c>
       <c r="G493" s="2">
-        <v>37280000</v>
+        <v>62280000</v>
       </c>
       <c r="H493" s="2">
-        <v>0</v>
+        <v>25000000</v>
       </c>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.45">
@@ -13420,10 +13488,10 @@
         <v>57</v>
       </c>
       <c r="B494" s="2">
-        <v>508075000</v>
+        <v>1016150000</v>
       </c>
       <c r="C494" s="2">
-        <v>508075000</v>
+        <v>1016150000</v>
       </c>
       <c r="D494" s="2">
         <v>34825000</v>
@@ -13435,7 +13503,7 @@
         <v>163165000</v>
       </c>
       <c r="G494" s="2">
-        <v>344910000</v>
+        <v>852985000</v>
       </c>
       <c r="H494" s="2">
         <v>0</v>
@@ -13446,10 +13514,10 @@
         <v>58</v>
       </c>
       <c r="B495" s="2">
-        <v>640000000</v>
+        <v>2560000000</v>
       </c>
       <c r="C495" s="2">
-        <v>640000000</v>
+        <v>2560000000</v>
       </c>
       <c r="D495" s="2">
         <v>8404406</v>
@@ -13461,7 +13529,7 @@
         <v>455035109</v>
       </c>
       <c r="G495" s="2">
-        <v>184964891</v>
+        <v>2104964891</v>
       </c>
       <c r="H495" s="2">
         <v>0</v>
@@ -13472,10 +13540,10 @@
         <v>25</v>
       </c>
       <c r="B496" s="2">
-        <v>222793250</v>
+        <v>891173000</v>
       </c>
       <c r="C496" s="2">
-        <v>222793250</v>
+        <v>668379750</v>
       </c>
       <c r="D496" s="2">
         <v>29693828</v>
@@ -13487,10 +13555,10 @@
         <v>52063828</v>
       </c>
       <c r="G496" s="2">
-        <v>170729422</v>
+        <v>616315922</v>
       </c>
       <c r="H496" s="2">
-        <v>0</v>
+        <v>222793250</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.45">
@@ -13498,10 +13566,10 @@
         <v>26</v>
       </c>
       <c r="B497" s="2">
-        <v>278081750</v>
+        <v>1160455000</v>
       </c>
       <c r="C497" s="2">
-        <v>278081750</v>
+        <v>870341250</v>
       </c>
       <c r="D497" s="2">
         <v>95838170</v>
@@ -13513,10 +13581,10 @@
         <v>272779430</v>
       </c>
       <c r="G497" s="2">
-        <v>5302320</v>
+        <v>597561820</v>
       </c>
       <c r="H497" s="2">
-        <v>0</v>
+        <v>290113750</v>
       </c>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.45">
@@ -13524,10 +13592,10 @@
         <v>27</v>
       </c>
       <c r="B498" s="2">
-        <v>23250000</v>
+        <v>93000000</v>
       </c>
       <c r="C498" s="2">
-        <v>23250000</v>
+        <v>93000000</v>
       </c>
       <c r="D498" s="2">
         <v>0</v>
@@ -13539,7 +13607,7 @@
         <v>14500000</v>
       </c>
       <c r="G498" s="2">
-        <v>8750000</v>
+        <v>78500000</v>
       </c>
       <c r="H498" s="2">
         <v>0</v>
@@ -13550,10 +13618,10 @@
         <v>28</v>
       </c>
       <c r="B499" s="2">
-        <v>163230750</v>
+        <v>562923000</v>
       </c>
       <c r="C499" s="2">
-        <v>163230750</v>
+        <v>422192250</v>
       </c>
       <c r="D499" s="2">
         <v>19366000</v>
@@ -13565,10 +13633,10 @@
         <v>32006000</v>
       </c>
       <c r="G499" s="2">
-        <v>131224750</v>
+        <v>390186250</v>
       </c>
       <c r="H499" s="2">
-        <v>0</v>
+        <v>140730750</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.45">
@@ -13576,25 +13644,25 @@
         <v>30</v>
       </c>
       <c r="B500" s="2">
-        <v>172144500</v>
+        <v>688578000</v>
       </c>
       <c r="C500" s="2">
-        <v>172144500</v>
+        <v>516433500</v>
       </c>
       <c r="D500" s="2">
         <v>35082547</v>
       </c>
       <c r="E500" s="2">
-        <v>77886880</v>
+        <v>77961880</v>
       </c>
       <c r="F500" s="2">
-        <v>112969427</v>
+        <v>113044427</v>
       </c>
       <c r="G500" s="2">
-        <v>59175073</v>
+        <v>403389073</v>
       </c>
       <c r="H500" s="2">
-        <v>0</v>
+        <v>172144500</v>
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.45">
@@ -13602,10 +13670,10 @@
         <v>79</v>
       </c>
       <c r="B501" s="2">
-        <v>9045000</v>
+        <v>36180000</v>
       </c>
       <c r="C501" s="2">
-        <v>9045000</v>
+        <v>36180000</v>
       </c>
       <c r="D501" s="2">
         <v>1720000</v>
@@ -13617,7 +13685,7 @@
         <v>7062537</v>
       </c>
       <c r="G501" s="2">
-        <v>1982463</v>
+        <v>29117463</v>
       </c>
       <c r="H501" s="2">
         <v>0</v>
@@ -13628,10 +13696,10 @@
         <v>31</v>
       </c>
       <c r="B502" s="2">
-        <v>40435250</v>
+        <v>61741000</v>
       </c>
       <c r="C502" s="2">
-        <v>40435250</v>
+        <v>61741000</v>
       </c>
       <c r="D502" s="2">
         <v>38255444</v>
@@ -13643,7 +13711,7 @@
         <v>38255444</v>
       </c>
       <c r="G502" s="2">
-        <v>2179806</v>
+        <v>23485556</v>
       </c>
       <c r="H502" s="2">
         <v>0</v>
@@ -13741,13 +13809,13 @@
         <v>0</v>
       </c>
       <c r="E506" s="2">
-        <v>1814032650</v>
+        <v>1814036400</v>
       </c>
       <c r="F506" s="2">
-        <v>1814032650</v>
+        <v>1814036400</v>
       </c>
       <c r="G506" s="2">
-        <v>10350249247</v>
+        <v>10350245497</v>
       </c>
       <c r="H506" s="2">
         <v>0</v>
@@ -13963,28 +14031,28 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="B515" s="2">
-        <v>44562890151</v>
+        <v>61498532437</v>
       </c>
       <c r="C515" s="2">
-        <v>44562890151</v>
+        <v>60647750187</v>
       </c>
       <c r="D515" s="2">
-        <v>9233777627</v>
+        <v>13437132792</v>
       </c>
       <c r="E515" s="2">
-        <v>5755634781</v>
+        <v>5853406531</v>
       </c>
       <c r="F515" s="2">
-        <v>14989412408</v>
+        <v>19290539323</v>
       </c>
       <c r="G515" s="2">
-        <v>29573477743</v>
+        <v>41357210864</v>
       </c>
       <c r="H515" s="2">
-        <v>0</v>
+        <v>850782250</v>
       </c>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.45">
@@ -13998,16 +14066,16 @@
         <v>5574698000</v>
       </c>
       <c r="D516" s="2">
-        <v>2595236997</v>
+        <v>5471087865</v>
       </c>
       <c r="E516" s="2">
         <v>0</v>
       </c>
       <c r="F516" s="2">
-        <v>2595236997</v>
+        <v>5471087865</v>
       </c>
       <c r="G516" s="2">
-        <v>2979461003</v>
+        <v>103610135</v>
       </c>
       <c r="H516" s="2">
         <v>0</v>
@@ -14024,16 +14092,16 @@
         <v>1521000000</v>
       </c>
       <c r="D517" s="2">
-        <v>0</v>
+        <v>1467022165</v>
       </c>
       <c r="E517" s="2">
         <v>3328300</v>
       </c>
       <c r="F517" s="2">
-        <v>3328300</v>
+        <v>1470350465</v>
       </c>
       <c r="G517" s="2">
-        <v>1517671700</v>
+        <v>50649535</v>
       </c>
       <c r="H517" s="2">
         <v>0</v>
@@ -14050,16 +14118,16 @@
         <v>1694175000</v>
       </c>
       <c r="D518" s="2">
-        <v>810860400</v>
+        <v>1694174158</v>
       </c>
       <c r="E518" s="2">
         <v>0</v>
       </c>
       <c r="F518" s="2">
-        <v>810860400</v>
+        <v>1694174158</v>
       </c>
       <c r="G518" s="2">
-        <v>883314600</v>
+        <v>842</v>
       </c>
       <c r="H518" s="2">
         <v>0</v>
@@ -14076,16 +14144,16 @@
         <v>2639000000</v>
       </c>
       <c r="D519" s="2">
-        <v>483429478</v>
+        <v>546436863</v>
       </c>
       <c r="E519" s="2">
         <v>129199870</v>
       </c>
       <c r="F519" s="2">
-        <v>612629348</v>
+        <v>675636733</v>
       </c>
       <c r="G519" s="2">
-        <v>2026370652</v>
+        <v>1963363267</v>
       </c>
       <c r="H519" s="2">
         <v>0</v>
@@ -14102,16 +14170,16 @@
         <v>150000000</v>
       </c>
       <c r="D520" s="2">
-        <v>0</v>
+        <v>9000000</v>
       </c>
       <c r="E520" s="2">
         <v>0</v>
       </c>
       <c r="F520" s="2">
-        <v>0</v>
+        <v>9000000</v>
       </c>
       <c r="G520" s="2">
-        <v>150000000</v>
+        <v>141000000</v>
       </c>
       <c r="H520" s="2">
         <v>0</v>
@@ -14128,16 +14196,16 @@
         <v>2721193000</v>
       </c>
       <c r="D521" s="2">
-        <v>777673392</v>
+        <v>2263795563</v>
       </c>
       <c r="E521" s="2">
         <v>0</v>
       </c>
       <c r="F521" s="2">
-        <v>777673392</v>
+        <v>2263795563</v>
       </c>
       <c r="G521" s="2">
-        <v>1943519608</v>
+        <v>457397437</v>
       </c>
       <c r="H521" s="2">
         <v>0</v>
@@ -14154,16 +14222,16 @@
         <v>9794675000</v>
       </c>
       <c r="D522" s="2">
-        <v>4877544282</v>
+        <v>8772973347</v>
       </c>
       <c r="E522" s="2">
         <v>3607897</v>
       </c>
       <c r="F522" s="2">
-        <v>4881152179</v>
+        <v>8776581244</v>
       </c>
       <c r="G522" s="2">
-        <v>4913522821</v>
+        <v>1018093756</v>
       </c>
       <c r="H522" s="2">
         <v>0</v>
@@ -14258,16 +14326,16 @@
         <v>915811000</v>
       </c>
       <c r="D526" s="2">
-        <v>0</v>
+        <v>715028125</v>
       </c>
       <c r="E526" s="2">
         <v>0</v>
       </c>
       <c r="F526" s="2">
-        <v>0</v>
+        <v>715028125</v>
       </c>
       <c r="G526" s="2">
-        <v>915811000</v>
+        <v>200782875</v>
       </c>
       <c r="H526" s="2">
         <v>0</v>
@@ -14284,16 +14352,16 @@
         <v>1750000000</v>
       </c>
       <c r="D527" s="2">
-        <v>498500000</v>
+        <v>957373034</v>
       </c>
       <c r="E527" s="2">
         <v>0</v>
       </c>
       <c r="F527" s="2">
-        <v>498500000</v>
+        <v>957373034</v>
       </c>
       <c r="G527" s="2">
-        <v>1251500000</v>
+        <v>792626966</v>
       </c>
       <c r="H527" s="2">
         <v>0</v>
@@ -14336,16 +14404,16 @@
         <v>483750000</v>
       </c>
       <c r="D529" s="2">
-        <v>14815000</v>
+        <v>114815000</v>
       </c>
       <c r="E529" s="2">
         <v>68355000</v>
       </c>
       <c r="F529" s="2">
-        <v>83170000</v>
+        <v>183170000</v>
       </c>
       <c r="G529" s="2">
-        <v>400580000</v>
+        <v>300580000</v>
       </c>
       <c r="H529" s="2">
         <v>161250000</v>
@@ -14521,13 +14589,13 @@
         <v>17298750</v>
       </c>
       <c r="E536" s="2">
-        <v>64965000</v>
+        <v>65252500</v>
       </c>
       <c r="F536" s="2">
-        <v>82263750</v>
+        <v>82551250</v>
       </c>
       <c r="G536" s="2">
-        <v>254538750</v>
+        <v>254251250</v>
       </c>
       <c r="H536" s="2">
         <v>112267500</v>
@@ -14599,13 +14667,13 @@
         <v>0</v>
       </c>
       <c r="E539" s="2">
-        <v>1592655254</v>
+        <v>1592659004</v>
       </c>
       <c r="F539" s="2">
-        <v>1592655254</v>
+        <v>1592659004</v>
       </c>
       <c r="G539" s="2">
-        <v>9096261612</v>
+        <v>9096257862</v>
       </c>
       <c r="H539" s="2">
         <v>0</v>
@@ -14795,7 +14863,7 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="B547" s="2">
         <v>58569240973</v>
@@ -14804,16 +14872,16 @@
         <v>57848682223</v>
       </c>
       <c r="D547" s="2">
-        <v>10131101660</v>
+        <v>22084748231</v>
       </c>
       <c r="E547" s="2">
-        <v>4495816582</v>
+        <v>4496107832</v>
       </c>
       <c r="F547" s="2">
-        <v>14626918242</v>
+        <v>26580856063</v>
       </c>
       <c r="G547" s="2">
-        <v>43221763981</v>
+        <v>31267826160</v>
       </c>
       <c r="H547" s="2">
         <v>720558750</v>
@@ -14821,5 +14889,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,15 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\RKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{5E5466EE-E6E1-429B-BCEC-F0A77692F222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7A97A4-4776-4D35-86D1-586F803A99F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget 3 Juni 2024" sheetId="1" r:id="rId1"/>
+    <sheet name="II PD" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="152">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -479,11 +489,18 @@
   <si>
     <t>32020100 Prasarana</t>
   </si>
+  <si>
+    <t>RKAO Disetujui</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -620,7 +637,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -806,6 +823,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -923,7 +946,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -966,14 +989,33 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1001,6 +1043,7 @@
     <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
     <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
@@ -1326,7 +1369,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H547"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -12236,327 +12279,824 @@
         <v>98</v>
       </c>
       <c r="B420" s="3">
-        <v>1871950730</v>
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>873740000</v>
       </c>
       <c r="C420" s="3">
-        <v>1871950730</v>
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>436870000</v>
       </c>
       <c r="D420" s="3">
-        <v>404935052</v>
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>404360000</v>
       </c>
       <c r="E420" s="3">
-        <v>78896778</v>
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>35605052</v>
       </c>
       <c r="F420" s="3">
-        <v>483831830</v>
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>439965052</v>
       </c>
       <c r="G420" s="3">
-        <v>1388118900</v>
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>-3095052</v>
       </c>
       <c r="H420" s="3">
-        <v>0</v>
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>436870000</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A421" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B421" s="3"/>
-      <c r="C421" s="3"/>
-      <c r="D421" s="3"/>
-      <c r="E421" s="3"/>
-      <c r="F421" s="3"/>
-      <c r="G421" s="3"/>
-      <c r="H421" s="3"/>
+      <c r="B421" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="C421" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="D421" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="E421" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="F421" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="G421" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="H421" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A422" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B422" s="3"/>
-      <c r="C422" s="3"/>
-      <c r="D422" s="3"/>
-      <c r="E422" s="3"/>
-      <c r="F422" s="3"/>
-      <c r="G422" s="3"/>
-      <c r="H422" s="3"/>
+      <c r="B422" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="C422" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="D422" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="E422" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="F422" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="G422" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="H422" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A423" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B423" s="3"/>
-      <c r="C423" s="3"/>
-      <c r="D423" s="3"/>
-      <c r="E423" s="3"/>
-      <c r="F423" s="3"/>
-      <c r="G423" s="3"/>
-      <c r="H423" s="3"/>
+      <c r="B423" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="C423" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="D423" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="E423" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="F423" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="G423" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="H423" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A424" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B424" s="3"/>
-      <c r="C424" s="3"/>
-      <c r="D424" s="3"/>
-      <c r="E424" s="3"/>
-      <c r="F424" s="3"/>
-      <c r="G424" s="3"/>
-      <c r="H424" s="3"/>
+      <c r="B424" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="C424" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="D424" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="E424" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="F424" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="G424" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="H424" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A425" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B425" s="3"/>
-      <c r="C425" s="3"/>
-      <c r="D425" s="3"/>
-      <c r="E425" s="3"/>
-      <c r="F425" s="3"/>
-      <c r="G425" s="3"/>
-      <c r="H425" s="3"/>
+      <c r="B425" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="C425" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="D425" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="E425" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="F425" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="G425" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="H425" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A426" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B426" s="3"/>
-      <c r="C426" s="3"/>
-      <c r="D426" s="3"/>
-      <c r="E426" s="3"/>
-      <c r="F426" s="3"/>
-      <c r="G426" s="3"/>
-      <c r="H426" s="3"/>
+      <c r="B426" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="C426" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="D426" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="E426" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="F426" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="G426" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="H426" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A427" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B427" s="3"/>
-      <c r="C427" s="3"/>
-      <c r="D427" s="3"/>
-      <c r="E427" s="3"/>
-      <c r="F427" s="3"/>
-      <c r="G427" s="3"/>
-      <c r="H427" s="3"/>
+      <c r="B427" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="C427" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="D427" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="E427" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="F427" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="G427" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="H427" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A428" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B428" s="3"/>
-      <c r="C428" s="3"/>
-      <c r="D428" s="3"/>
-      <c r="E428" s="3"/>
-      <c r="F428" s="3"/>
-      <c r="G428" s="3"/>
-      <c r="H428" s="3"/>
+      <c r="B428" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="C428" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="D428" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="E428" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="F428" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="G428" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="H428" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A429" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B429" s="3"/>
-      <c r="C429" s="3"/>
-      <c r="D429" s="3"/>
-      <c r="E429" s="3"/>
-      <c r="F429" s="3"/>
-      <c r="G429" s="3"/>
-      <c r="H429" s="3"/>
+      <c r="B429" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="C429" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="D429" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="E429" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="F429" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="G429" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="H429" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A430" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B430" s="3"/>
-      <c r="C430" s="3"/>
-      <c r="D430" s="3"/>
-      <c r="E430" s="3"/>
-      <c r="F430" s="3"/>
-      <c r="G430" s="3"/>
-      <c r="H430" s="3"/>
+      <c r="B430" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="C430" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="D430" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="E430" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="F430" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="G430" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="H430" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A431" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B431" s="3"/>
-      <c r="C431" s="3"/>
-      <c r="D431" s="3"/>
-      <c r="E431" s="3"/>
-      <c r="F431" s="3"/>
-      <c r="G431" s="3"/>
-      <c r="H431" s="3"/>
+      <c r="B431" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="C431" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="D431" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="E431" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="F431" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="G431" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="H431" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A432" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B432" s="3"/>
-      <c r="C432" s="3"/>
-      <c r="D432" s="3"/>
-      <c r="E432" s="3"/>
-      <c r="F432" s="3"/>
-      <c r="G432" s="3"/>
-      <c r="H432" s="3"/>
+      <c r="B432" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="C432" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="D432" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="E432" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="F432" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="G432" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="H432" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A433" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B433" s="3"/>
-      <c r="C433" s="3"/>
-      <c r="D433" s="3"/>
-      <c r="E433" s="3"/>
-      <c r="F433" s="3"/>
-      <c r="G433" s="3"/>
-      <c r="H433" s="3"/>
+      <c r="B433" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="C433" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="D433" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="E433" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="F433" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="G433" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="H433" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A434" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B434" s="3"/>
-      <c r="C434" s="3"/>
-      <c r="D434" s="3"/>
-      <c r="E434" s="3"/>
-      <c r="F434" s="3"/>
-      <c r="G434" s="3"/>
-      <c r="H434" s="3"/>
+      <c r="B434" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="C434" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="D434" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="E434" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="F434" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="G434" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="H434" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A435" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B435" s="3"/>
-      <c r="C435" s="3"/>
-      <c r="D435" s="3"/>
-      <c r="E435" s="3"/>
-      <c r="F435" s="3"/>
-      <c r="G435" s="3"/>
-      <c r="H435" s="3"/>
+      <c r="B435" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="C435" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="D435" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="E435" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="F435" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="G435" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="H435" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A436" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B436" s="3"/>
-      <c r="C436" s="3"/>
-      <c r="D436" s="3"/>
-      <c r="E436" s="3"/>
-      <c r="F436" s="3"/>
-      <c r="G436" s="3"/>
-      <c r="H436" s="3"/>
+      <c r="B436" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="C436" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="D436" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="E436" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="F436" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="G436" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="H436" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A437" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B437" s="3"/>
-      <c r="C437" s="3"/>
-      <c r="D437" s="3"/>
-      <c r="E437" s="3"/>
-      <c r="F437" s="3"/>
-      <c r="G437" s="3"/>
-      <c r="H437" s="3"/>
+      <c r="B437" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>474786000</v>
+      </c>
+      <c r="C437" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>237393000</v>
+      </c>
+      <c r="D437" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>0</v>
+      </c>
+      <c r="E437" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>0</v>
+      </c>
+      <c r="F437" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>0</v>
+      </c>
+      <c r="G437" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>237393000</v>
+      </c>
+      <c r="H437" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>237393000</v>
+      </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A438" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B438" s="3"/>
-      <c r="C438" s="3"/>
-      <c r="D438" s="3"/>
-      <c r="E438" s="3"/>
-      <c r="F438" s="3"/>
-      <c r="G438" s="3"/>
-      <c r="H438" s="3"/>
+      <c r="B438" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>208425000</v>
+      </c>
+      <c r="C438" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>104212500</v>
+      </c>
+      <c r="D438" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>0</v>
+      </c>
+      <c r="E438" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>0</v>
+      </c>
+      <c r="F438" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>0</v>
+      </c>
+      <c r="G438" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>104212500</v>
+      </c>
+      <c r="H438" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>104212500</v>
+      </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A439" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B439" s="3"/>
-      <c r="C439" s="3"/>
-      <c r="D439" s="3"/>
-      <c r="E439" s="3"/>
-      <c r="F439" s="3"/>
-      <c r="G439" s="3"/>
-      <c r="H439" s="3"/>
+      <c r="B439" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>20000000</v>
+      </c>
+      <c r="C439" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>13970000</v>
+      </c>
+      <c r="D439" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>13970000</v>
+      </c>
+      <c r="E439" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>0</v>
+      </c>
+      <c r="F439" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>13970000</v>
+      </c>
+      <c r="G439" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>0</v>
+      </c>
+      <c r="H439" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>6030000</v>
+      </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A440" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B440" s="3"/>
-      <c r="C440" s="3"/>
-      <c r="D440" s="3"/>
-      <c r="E440" s="3"/>
-      <c r="F440" s="3"/>
-      <c r="G440" s="3"/>
-      <c r="H440" s="3"/>
+      <c r="B440" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>220000000</v>
+      </c>
+      <c r="C440" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>110000000</v>
+      </c>
+      <c r="D440" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>0</v>
+      </c>
+      <c r="E440" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>29896778</v>
+      </c>
+      <c r="F440" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>29896778</v>
+      </c>
+      <c r="G440" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>80103222</v>
+      </c>
+      <c r="H440" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>110000000</v>
+      </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A441" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B441" s="3"/>
-      <c r="C441" s="3"/>
-      <c r="D441" s="3"/>
-      <c r="E441" s="3"/>
-      <c r="F441" s="3"/>
-      <c r="G441" s="3"/>
-      <c r="H441" s="3"/>
+      <c r="B441" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>75000000</v>
+      </c>
+      <c r="C441" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>37500000</v>
+      </c>
+      <c r="D441" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>0</v>
+      </c>
+      <c r="E441" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>0</v>
+      </c>
+      <c r="F441" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>0</v>
+      </c>
+      <c r="G441" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>37500000</v>
+      </c>
+      <c r="H441" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>37500000</v>
+      </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A442" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B442" s="3"/>
-      <c r="C442" s="3"/>
-      <c r="D442" s="3"/>
-      <c r="E442" s="3"/>
-      <c r="F442" s="3"/>
-      <c r="G442" s="3"/>
-      <c r="H442" s="3"/>
+      <c r="B442" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="C442" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="D442" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="E442" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="F442" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="G442" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="H442" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A443" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B443" s="3"/>
-      <c r="C443" s="3"/>
-      <c r="D443" s="3"/>
-      <c r="E443" s="3"/>
-      <c r="F443" s="3"/>
-      <c r="G443" s="3"/>
-      <c r="H443" s="3"/>
+      <c r="B443" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="C443" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="D443" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="E443" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="F443" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="G443" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="H443" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A444" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B444" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>60000000</v>
       </c>
       <c r="C444" s="3">
-        <v>60000000</v>
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
+        <v>30000000</v>
       </c>
       <c r="D444" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>9000000</v>
       </c>
       <c r="E444" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>0</v>
       </c>
       <c r="F444" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>9000000</v>
       </c>
       <c r="G444" s="3">
-        <v>51000000</v>
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
+        <v>21000000</v>
       </c>
       <c r="H444" s="3">
-        <v>0</v>
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
+        <v>30000000</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.45">
@@ -12564,377 +13104,923 @@
         <v>123</v>
       </c>
       <c r="B445" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>45150000</v>
       </c>
       <c r="C445" s="3">
-        <v>45150000</v>
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
+        <v>22575000</v>
       </c>
       <c r="D445" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>6423200</v>
       </c>
       <c r="E445" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>6119400</v>
       </c>
       <c r="F445" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>12542600</v>
       </c>
       <c r="G445" s="3">
-        <v>32607400</v>
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
+        <v>10032400</v>
       </c>
       <c r="H445" s="3">
-        <v>0</v>
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
+        <v>22575000</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A446" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B446" s="3"/>
-      <c r="C446" s="3"/>
-      <c r="D446" s="3"/>
-      <c r="E446" s="3"/>
-      <c r="F446" s="3"/>
-      <c r="G446" s="3"/>
-      <c r="H446" s="3"/>
+      <c r="B446" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="C446" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="D446" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="E446" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="F446" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="G446" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="H446" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A447" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B447" s="3"/>
-      <c r="C447" s="3"/>
-      <c r="D447" s="3"/>
-      <c r="E447" s="3"/>
-      <c r="F447" s="3"/>
-      <c r="G447" s="3"/>
-      <c r="H447" s="3"/>
+      <c r="B447" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="C447" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="D447" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="E447" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="F447" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="G447" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="H447" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A448" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B448" s="3"/>
-      <c r="C448" s="3"/>
-      <c r="D448" s="3"/>
-      <c r="E448" s="3"/>
-      <c r="F448" s="3"/>
-      <c r="G448" s="3"/>
-      <c r="H448" s="3"/>
+      <c r="B448" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="C448" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="D448" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="E448" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="F448" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="G448" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="H448" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A449" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B449" s="3"/>
-      <c r="C449" s="3"/>
-      <c r="D449" s="3"/>
-      <c r="E449" s="3"/>
-      <c r="F449" s="3"/>
-      <c r="G449" s="3"/>
-      <c r="H449" s="3"/>
+      <c r="B449" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="C449" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="D449" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="E449" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="F449" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="G449" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="H449" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A450" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B450" s="3"/>
-      <c r="C450" s="3"/>
-      <c r="D450" s="3"/>
-      <c r="E450" s="3"/>
-      <c r="F450" s="3"/>
-      <c r="G450" s="3"/>
-      <c r="H450" s="3"/>
+      <c r="B450" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="C450" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="D450" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="E450" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="F450" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="G450" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="H450" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A451" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B451" s="3"/>
-      <c r="C451" s="3"/>
-      <c r="D451" s="3"/>
-      <c r="E451" s="3"/>
-      <c r="F451" s="3"/>
-      <c r="G451" s="3"/>
-      <c r="H451" s="3"/>
+      <c r="B451" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="C451" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="D451" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="E451" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="F451" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="G451" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="H451" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A452" s="1" t="s">
         <v>130</v>
       </c>
       <c r="B452" s="3">
-        <v>372660000</v>
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>6000000</v>
       </c>
       <c r="C452" s="3">
-        <v>372660000</v>
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>1500000</v>
       </c>
       <c r="D452" s="3">
-        <v>8912700</v>
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>0</v>
       </c>
       <c r="E452" s="3">
-        <v>5604650</v>
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>0</v>
       </c>
       <c r="F452" s="3">
-        <v>14517350</v>
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>0</v>
       </c>
       <c r="G452" s="3">
-        <v>358142650</v>
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>1500000</v>
       </c>
       <c r="H452" s="3">
-        <v>0</v>
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>4500000</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A453" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B453" s="3"/>
-      <c r="C453" s="3"/>
-      <c r="D453" s="3"/>
-      <c r="E453" s="3"/>
-      <c r="F453" s="3"/>
-      <c r="G453" s="3"/>
-      <c r="H453" s="3"/>
+      <c r="B453" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>41000000</v>
+      </c>
+      <c r="C453" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>10250000</v>
+      </c>
+      <c r="D453" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>1997700</v>
+      </c>
+      <c r="E453" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>998400</v>
+      </c>
+      <c r="F453" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>2996100</v>
+      </c>
+      <c r="G453" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>7253900</v>
+      </c>
+      <c r="H453" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>30750000</v>
+      </c>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A454" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B454" s="3"/>
-      <c r="C454" s="3"/>
-      <c r="D454" s="3"/>
-      <c r="E454" s="3"/>
-      <c r="F454" s="3"/>
-      <c r="G454" s="3"/>
-      <c r="H454" s="3"/>
+      <c r="B454" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>12000000</v>
+      </c>
+      <c r="C454" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>3000000</v>
+      </c>
+      <c r="D454" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>0</v>
+      </c>
+      <c r="E454" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>0</v>
+      </c>
+      <c r="F454" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>0</v>
+      </c>
+      <c r="G454" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>3000000</v>
+      </c>
+      <c r="H454" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>9000000</v>
+      </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A455" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B455" s="3"/>
-      <c r="C455" s="3"/>
-      <c r="D455" s="3"/>
-      <c r="E455" s="3"/>
-      <c r="F455" s="3"/>
-      <c r="G455" s="3"/>
-      <c r="H455" s="3"/>
+      <c r="B455" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>171000000</v>
+      </c>
+      <c r="C455" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>42750000</v>
+      </c>
+      <c r="D455" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>5880000</v>
+      </c>
+      <c r="E455" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>0</v>
+      </c>
+      <c r="F455" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>5880000</v>
+      </c>
+      <c r="G455" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>36870000</v>
+      </c>
+      <c r="H455" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>128250000</v>
+      </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A456" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B456" s="3"/>
-      <c r="C456" s="3"/>
-      <c r="D456" s="3"/>
-      <c r="E456" s="3"/>
-      <c r="F456" s="3"/>
-      <c r="G456" s="3"/>
-      <c r="H456" s="3"/>
+      <c r="B456" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>130000000</v>
+      </c>
+      <c r="C456" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>32500000</v>
+      </c>
+      <c r="D456" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>0</v>
+      </c>
+      <c r="E456" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>7381250</v>
+      </c>
+      <c r="F456" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>7381250</v>
+      </c>
+      <c r="G456" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>25118750</v>
+      </c>
+      <c r="H456" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>97500000</v>
+      </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A457" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B457" s="3"/>
-      <c r="C457" s="3"/>
-      <c r="D457" s="3"/>
-      <c r="E457" s="3"/>
-      <c r="F457" s="3"/>
-      <c r="G457" s="3"/>
-      <c r="H457" s="3"/>
+      <c r="B457" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>6660000</v>
+      </c>
+      <c r="C457" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>1665000</v>
+      </c>
+      <c r="D457" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>1665000</v>
+      </c>
+      <c r="E457" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>0</v>
+      </c>
+      <c r="F457" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>1665000</v>
+      </c>
+      <c r="G457" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>0</v>
+      </c>
+      <c r="H457" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>4995000</v>
+      </c>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A458" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B458" s="3"/>
-      <c r="C458" s="3"/>
-      <c r="D458" s="3"/>
-      <c r="E458" s="3"/>
-      <c r="F458" s="3"/>
-      <c r="G458" s="3"/>
-      <c r="H458" s="3"/>
+      <c r="B458" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>6000000</v>
+      </c>
+      <c r="C458" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>1500000</v>
+      </c>
+      <c r="D458" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>0</v>
+      </c>
+      <c r="E458" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>0</v>
+      </c>
+      <c r="F458" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>0</v>
+      </c>
+      <c r="G458" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>1500000</v>
+      </c>
+      <c r="H458" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>4500000</v>
+      </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A459" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B459" s="3"/>
-      <c r="C459" s="3"/>
-      <c r="D459" s="3"/>
-      <c r="E459" s="3"/>
-      <c r="F459" s="3"/>
-      <c r="G459" s="3"/>
-      <c r="H459" s="3"/>
+      <c r="B459" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="C459" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="D459" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="E459" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="F459" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="G459" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="H459" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A460" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B460" s="3"/>
-      <c r="C460" s="3"/>
-      <c r="D460" s="3"/>
-      <c r="E460" s="3"/>
-      <c r="F460" s="3"/>
-      <c r="G460" s="3"/>
-      <c r="H460" s="3"/>
+      <c r="B460" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="C460" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="D460" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="E460" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="F460" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="G460" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="H460" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A461" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B461" s="3"/>
-      <c r="C461" s="3"/>
-      <c r="D461" s="3"/>
-      <c r="E461" s="3"/>
-      <c r="F461" s="3"/>
-      <c r="G461" s="3"/>
-      <c r="H461" s="3"/>
+      <c r="B461" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="C461" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="D461" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="E461" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="F461" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="G461" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="H461" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A462" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B462" s="3"/>
-      <c r="C462" s="3"/>
-      <c r="D462" s="3"/>
-      <c r="E462" s="3"/>
-      <c r="F462" s="3"/>
-      <c r="G462" s="3"/>
-      <c r="H462" s="3"/>
+      <c r="B462" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="C462" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="D462" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="E462" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="F462" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="G462" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="H462" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A463" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B463" s="3"/>
-      <c r="C463" s="3"/>
-      <c r="D463" s="3"/>
-      <c r="E463" s="3"/>
-      <c r="F463" s="3"/>
-      <c r="G463" s="3"/>
-      <c r="H463" s="3"/>
+      <c r="B463" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="C463" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="D463" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="E463" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="F463" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="G463" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="H463" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A464" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B464" s="3"/>
-      <c r="C464" s="3"/>
-      <c r="D464" s="3"/>
-      <c r="E464" s="3"/>
-      <c r="F464" s="3"/>
-      <c r="G464" s="3"/>
-      <c r="H464" s="3"/>
+      <c r="B464" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="C464" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="D464" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="E464" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="F464" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="G464" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="H464" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A465" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B465" s="3"/>
-      <c r="C465" s="3"/>
-      <c r="D465" s="3"/>
-      <c r="E465" s="3"/>
-      <c r="F465" s="3"/>
-      <c r="G465" s="3"/>
-      <c r="H465" s="3"/>
+      <c r="B465" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="C465" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="D465" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="E465" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="F465" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="G465" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="H465" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A466" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B466" s="3"/>
-      <c r="C466" s="3"/>
-      <c r="D466" s="3"/>
-      <c r="E466" s="3"/>
-      <c r="F466" s="3"/>
-      <c r="G466" s="3"/>
-      <c r="H466" s="3"/>
+      <c r="B466" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="C466" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="D466" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="E466" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="F466" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="G466" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="H466" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A467" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B467" s="3"/>
-      <c r="C467" s="3"/>
-      <c r="D467" s="3"/>
-      <c r="E467" s="3"/>
-      <c r="F467" s="3"/>
-      <c r="G467" s="3"/>
-      <c r="H467" s="3"/>
+      <c r="B467" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="C467" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="D467" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="E467" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="F467" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="G467" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="H467" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A468" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B468" s="3"/>
-      <c r="C468" s="3"/>
-      <c r="D468" s="3"/>
-      <c r="E468" s="3"/>
-      <c r="F468" s="3"/>
-      <c r="G468" s="3"/>
-      <c r="H468" s="3"/>
+      <c r="B468" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="C468" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="D468" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="E468" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="F468" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="G468" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="H468" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A469" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B469" s="3"/>
-      <c r="C469" s="3"/>
-      <c r="D469" s="3"/>
-      <c r="E469" s="3"/>
-      <c r="F469" s="3"/>
-      <c r="G469" s="3"/>
-      <c r="H469" s="3"/>
+      <c r="B469" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="C469" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="D469" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="E469" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="F469" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="G469" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="H469" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A470" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B470" s="3"/>
-      <c r="C470" s="3"/>
-      <c r="D470" s="3"/>
-      <c r="E470" s="3"/>
-      <c r="F470" s="3"/>
-      <c r="G470" s="3"/>
-      <c r="H470" s="3"/>
+      <c r="B470" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="C470" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="D470" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="E470" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="F470" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="G470" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="H470" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A471" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B471" s="3"/>
-      <c r="C471" s="3"/>
-      <c r="D471" s="3"/>
-      <c r="E471" s="3"/>
-      <c r="F471" s="3"/>
-      <c r="G471" s="3"/>
-      <c r="H471" s="3"/>
+      <c r="B471" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="C471" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="D471" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="E471" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="F471" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="G471" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="H471" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A472" s="1" t="s">
         <v>150</v>
       </c>
       <c r="B472" s="3">
-        <v>2349760730</v>
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>2349761000</v>
       </c>
       <c r="C472" s="3">
-        <v>2349760730</v>
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>1085685500</v>
       </c>
       <c r="D472" s="3">
-        <v>429270952</v>
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>443295900</v>
       </c>
       <c r="E472" s="3">
-        <v>90620828</v>
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>80000880</v>
       </c>
       <c r="F472" s="3">
-        <v>519891780</v>
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>523296780</v>
       </c>
       <c r="G472" s="3">
-        <v>1829868950</v>
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>562388720</v>
       </c>
       <c r="H472" s="3">
-        <v>0</v>
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>1264075500</v>
       </c>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.45">
@@ -14891,4 +15977,1489 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74037102-CAE5-4DA3-AC4F-276E222EA2EC}">
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.25" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="60.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="15.265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="15.265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="4">
+        <v>873740000</v>
+      </c>
+      <c r="C2" s="5">
+        <f>B2</f>
+        <v>873740000</v>
+      </c>
+      <c r="D2" s="5">
+        <f>C2/2</f>
+        <v>436870000</v>
+      </c>
+      <c r="E2" s="4">
+        <f>IF(B2="","",G2-F2)</f>
+        <v>404360000</v>
+      </c>
+      <c r="F2" s="5">
+        <v>35605052</v>
+      </c>
+      <c r="G2" s="5">
+        <v>439965052</v>
+      </c>
+      <c r="H2" s="4">
+        <f>IF(B2="","",D2-G2)</f>
+        <v>-3095052</v>
+      </c>
+      <c r="I2" s="4">
+        <f>IF(B2="","",C2-D2)</f>
+        <v>436870000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5">
+        <f t="shared" ref="C3:C27" si="0">B3</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <f t="shared" ref="D3:D27" si="1">C3/2</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="str">
+        <f t="shared" ref="E3:E53" si="2">IF(B3="","",G3-F3)</f>
+        <v/>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="4" t="str">
+        <f t="shared" ref="H3:H53" si="3">IF(B3="","",D3-G3)</f>
+        <v/>
+      </c>
+      <c r="I3" s="4" t="str">
+        <f t="shared" ref="I3:I53" si="4">IF(B3="","",C3-D3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I4" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I5" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I6" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I7" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I8" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I9" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I10" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I11" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I12" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I13" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I14" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I15" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I16" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I17" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I18" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="4">
+        <v>474786000</v>
+      </c>
+      <c r="C19" s="5">
+        <f t="shared" si="0"/>
+        <v>474786000</v>
+      </c>
+      <c r="D19" s="5">
+        <f t="shared" si="1"/>
+        <v>237393000</v>
+      </c>
+      <c r="E19" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="4">
+        <f t="shared" si="3"/>
+        <v>237393000</v>
+      </c>
+      <c r="I19" s="4">
+        <f t="shared" si="4"/>
+        <v>237393000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="4">
+        <v>208425000</v>
+      </c>
+      <c r="C20" s="5">
+        <f t="shared" si="0"/>
+        <v>208425000</v>
+      </c>
+      <c r="D20" s="5">
+        <f t="shared" si="1"/>
+        <v>104212500</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="4">
+        <f t="shared" si="3"/>
+        <v>104212500</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="4"/>
+        <v>104212500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="4">
+        <v>20000000</v>
+      </c>
+      <c r="C21" s="5">
+        <f>B21</f>
+        <v>20000000</v>
+      </c>
+      <c r="D21" s="5">
+        <v>13970000</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" si="2"/>
+        <v>13970000</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5">
+        <v>13970000</v>
+      </c>
+      <c r="H21" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="4">
+        <f t="shared" si="4"/>
+        <v>6030000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="4">
+        <v>220000000</v>
+      </c>
+      <c r="C22" s="5">
+        <f t="shared" si="0"/>
+        <v>220000000</v>
+      </c>
+      <c r="D22" s="5">
+        <f t="shared" si="1"/>
+        <v>110000000</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>29896778</v>
+      </c>
+      <c r="G22" s="5">
+        <v>29896778</v>
+      </c>
+      <c r="H22" s="4">
+        <f t="shared" si="3"/>
+        <v>80103222</v>
+      </c>
+      <c r="I22" s="4">
+        <f t="shared" si="4"/>
+        <v>110000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="4">
+        <v>75000000</v>
+      </c>
+      <c r="C23" s="5">
+        <f t="shared" si="0"/>
+        <v>75000000</v>
+      </c>
+      <c r="D23" s="5">
+        <f t="shared" si="1"/>
+        <v>37500000</v>
+      </c>
+      <c r="E23" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="4">
+        <f t="shared" si="3"/>
+        <v>37500000</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" si="4"/>
+        <v>37500000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I24" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D25" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I25" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="4">
+        <v>60000000</v>
+      </c>
+      <c r="C26" s="5">
+        <f t="shared" si="0"/>
+        <v>60000000</v>
+      </c>
+      <c r="D26" s="5">
+        <f t="shared" si="1"/>
+        <v>30000000</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="2"/>
+        <v>9000000</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5">
+        <v>9000000</v>
+      </c>
+      <c r="H26" s="4">
+        <f t="shared" si="3"/>
+        <v>21000000</v>
+      </c>
+      <c r="I26" s="4">
+        <f t="shared" si="4"/>
+        <v>30000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" s="4">
+        <v>45150000</v>
+      </c>
+      <c r="C27" s="5">
+        <f t="shared" si="0"/>
+        <v>45150000</v>
+      </c>
+      <c r="D27" s="5">
+        <f t="shared" si="1"/>
+        <v>22575000</v>
+      </c>
+      <c r="E27" s="4">
+        <f t="shared" si="2"/>
+        <v>6423200</v>
+      </c>
+      <c r="F27" s="5">
+        <v>6119400</v>
+      </c>
+      <c r="G27" s="5">
+        <v>12542600</v>
+      </c>
+      <c r="H27" s="4">
+        <f t="shared" si="3"/>
+        <v>10032400</v>
+      </c>
+      <c r="I27" s="4">
+        <f t="shared" si="4"/>
+        <v>22575000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I28" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I29" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I30" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I31" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I32" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I33" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="4">
+        <v>6000000</v>
+      </c>
+      <c r="C34" s="5">
+        <f>B34</f>
+        <v>6000000</v>
+      </c>
+      <c r="D34" s="5">
+        <f>C34/4</f>
+        <v>1500000</v>
+      </c>
+      <c r="E34" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="4">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="I34" s="4">
+        <f t="shared" si="4"/>
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="4">
+        <v>41000000</v>
+      </c>
+      <c r="C35" s="5">
+        <f t="shared" ref="C35:C40" si="5">B35</f>
+        <v>41000000</v>
+      </c>
+      <c r="D35" s="5">
+        <f t="shared" ref="D35:D40" si="6">C35/4</f>
+        <v>10250000</v>
+      </c>
+      <c r="E35" s="4">
+        <f t="shared" si="2"/>
+        <v>1997700</v>
+      </c>
+      <c r="F35" s="5">
+        <v>998400</v>
+      </c>
+      <c r="G35" s="5">
+        <v>2996100</v>
+      </c>
+      <c r="H35" s="4">
+        <f t="shared" si="3"/>
+        <v>7253900</v>
+      </c>
+      <c r="I35" s="4">
+        <f t="shared" si="4"/>
+        <v>30750000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" s="4">
+        <v>12000000</v>
+      </c>
+      <c r="C36" s="5">
+        <f t="shared" si="5"/>
+        <v>12000000</v>
+      </c>
+      <c r="D36" s="5">
+        <f t="shared" si="6"/>
+        <v>3000000</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="4">
+        <f t="shared" si="3"/>
+        <v>3000000</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="4"/>
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" s="4">
+        <v>171000000</v>
+      </c>
+      <c r="C37" s="5">
+        <f t="shared" si="5"/>
+        <v>171000000</v>
+      </c>
+      <c r="D37" s="5">
+        <f t="shared" si="6"/>
+        <v>42750000</v>
+      </c>
+      <c r="E37" s="4">
+        <f t="shared" si="2"/>
+        <v>5880000</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5">
+        <v>5880000</v>
+      </c>
+      <c r="H37" s="4">
+        <f t="shared" si="3"/>
+        <v>36870000</v>
+      </c>
+      <c r="I37" s="4">
+        <f t="shared" si="4"/>
+        <v>128250000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" s="4">
+        <v>130000000</v>
+      </c>
+      <c r="C38" s="5">
+        <f t="shared" si="5"/>
+        <v>130000000</v>
+      </c>
+      <c r="D38" s="5">
+        <f t="shared" si="6"/>
+        <v>32500000</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="5">
+        <v>7381250</v>
+      </c>
+      <c r="G38" s="5">
+        <v>7381250</v>
+      </c>
+      <c r="H38" s="4">
+        <f t="shared" si="3"/>
+        <v>25118750</v>
+      </c>
+      <c r="I38" s="4">
+        <f t="shared" si="4"/>
+        <v>97500000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="4">
+        <v>6660000</v>
+      </c>
+      <c r="C39" s="5">
+        <f t="shared" si="5"/>
+        <v>6660000</v>
+      </c>
+      <c r="D39" s="5">
+        <f t="shared" si="6"/>
+        <v>1665000</v>
+      </c>
+      <c r="E39" s="4">
+        <f t="shared" si="2"/>
+        <v>1665000</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5">
+        <v>1665000</v>
+      </c>
+      <c r="H39" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="4">
+        <f t="shared" si="4"/>
+        <v>4995000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" s="4">
+        <v>6000000</v>
+      </c>
+      <c r="C40" s="5">
+        <f t="shared" si="5"/>
+        <v>6000000</v>
+      </c>
+      <c r="D40" s="5">
+        <f t="shared" si="6"/>
+        <v>1500000</v>
+      </c>
+      <c r="E40" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="4">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="I40" s="4">
+        <f t="shared" si="4"/>
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I41" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>138</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I42" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>139</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I43" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I44" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I45" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I46" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>143</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I47" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I48" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>145</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I49" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I50" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I51" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>148</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I52" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I53" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B54" s="11">
+        <f>SUM(B2:B53)</f>
+        <v>2349761000</v>
+      </c>
+      <c r="C54" s="11">
+        <f t="shared" ref="C54:I54" si="7">SUM(C2:C53)</f>
+        <v>2349761000</v>
+      </c>
+      <c r="D54" s="11">
+        <f t="shared" si="7"/>
+        <v>1085685500</v>
+      </c>
+      <c r="E54" s="11">
+        <f t="shared" si="7"/>
+        <v>443295900</v>
+      </c>
+      <c r="F54" s="11">
+        <f t="shared" si="7"/>
+        <v>80000880</v>
+      </c>
+      <c r="G54" s="11">
+        <f t="shared" si="7"/>
+        <v>523296780</v>
+      </c>
+      <c r="H54" s="11">
+        <f t="shared" si="7"/>
+        <v>562388720</v>
+      </c>
+      <c r="I54" s="11">
+        <f t="shared" si="7"/>
+        <v>1264075500</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="1jAoxgEfH1v+py+BabjE1SWtZrOmBQzll5J+0nEkCC4zpdaAqkqUQlFy6oRCGkgRojK/rMDnTPHDGbW/CMwxXA==" saltValue="rHdoy6qRDxYzetfIY6x9cQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\RKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7A97A4-4776-4D35-86D1-586F803A99F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD2D7D5-BE50-43FE-A649-0B9F15EC4FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,25 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\RKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD2D7D5-BE50-43FE-A649-0B9F15EC4FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{82C2664D-B25D-45A5-832B-E371991628C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Budget 3 Juni 2024" sheetId="1" r:id="rId1"/>
-    <sheet name="II PD" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -35,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="123">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -298,7 +288,82 @@
     <t>31022000  Sintelis</t>
   </si>
   <si>
+    <t>4112222200  Bbn Penystn Srana Perkeretaapian Fasilitas Dipo-By</t>
+  </si>
+  <si>
+    <t>4221221100  Perawatan Rel BMN</t>
+  </si>
+  <si>
+    <t>4221222200  Perawatan Wesel BMN</t>
+  </si>
+  <si>
+    <t>4221223300  Bbn Jasa Penambahan Balas BMN</t>
+  </si>
+  <si>
+    <t>4221224400  Pemasangan Bantalan BMN</t>
+  </si>
+  <si>
+    <t>4221225500  Perawatan Balas BMN</t>
+  </si>
+  <si>
+    <t>4221226000  Pemecokan BMN</t>
+  </si>
+  <si>
+    <t>4221226006  Perlintasan BMN</t>
+  </si>
+  <si>
+    <t>4221226008  Geometri BMN</t>
+  </si>
+  <si>
+    <t>4221226010  Perbaikan Periodik BMN</t>
+  </si>
+  <si>
+    <t>4221321010  Perawatan Baja Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221322010  Perawatan Cat Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221323010  Perawatan Batu Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221325010  Perawatan Cat Jembatan Kelas 2 BMN</t>
+  </si>
+  <si>
+    <t>4221325013  Perawatan Batu Jembatan Kelas 3 BMN</t>
+  </si>
+  <si>
+    <t>4221325014  Perawatan Beton Jembatan Kelas 3 BMN</t>
+  </si>
+  <si>
     <t>4221600000  Peralatan Khusus Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4222222200  Perawatan Wesel KAI</t>
+  </si>
+  <si>
+    <t>4231120000  PerjlDinas BebanUmum PerawatanPrasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231130000  LAT Beban Umum Perawatan Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231150010  Krt Beban Umum Perawatan Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231151710  Kerumahtanggaan UMDT Beban Umum Perawatan Pras BMN</t>
+  </si>
+  <si>
+    <t>4232152310  Tenaga PJL Alih Daya</t>
+  </si>
+  <si>
+    <t>4271100010  Gaji &amp;Tunjangan Pegawai Operasi Prasarana</t>
+  </si>
+  <si>
+    <t>4271500000  Pakaian Dinas Pegawai Operasi Prasarana</t>
+  </si>
+  <si>
+    <t>32020100  Prasarana</t>
   </si>
   <si>
     <t>4222421110  Transmisi Komunikasi KAI</t>
@@ -330,177 +395,11 @@
   <si>
     <t>35022000  Sintelis Divre IV Tanjungkarang</t>
   </si>
-  <si>
-    <t>1182000000 Persediaan Prasarana Perkeretaapian dan Umum</t>
-  </si>
-  <si>
-    <t>4112222200 Bbn Penystn Srana Perkeretaapian Fasilitas Dipo-By</t>
-  </si>
-  <si>
-    <t>4221221100 Perawatan Rel BMN</t>
-  </si>
-  <si>
-    <t>4221222200 Perawatan Wesel BMN</t>
-  </si>
-  <si>
-    <t>4221223300 Bbn Jasa Penambahan Balas BMN</t>
-  </si>
-  <si>
-    <t>4221224400 Pemasangan Bantalan BMN</t>
-  </si>
-  <si>
-    <t>4221225500 Perawatan Balas BMN</t>
-  </si>
-  <si>
-    <t>4221226000 Pemecokan BMN</t>
-  </si>
-  <si>
-    <t>4221226006 Perlintasan BMN</t>
-  </si>
-  <si>
-    <t>4221226008 Geometri BMN</t>
-  </si>
-  <si>
-    <t>4221226010 Perbaikan Periodik BMN</t>
-  </si>
-  <si>
-    <t>4221321010 Perawatan Baja Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221322010 Perawatan Cat Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221323010 Perawatan Batu Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221325010 Perawatan Cat Jembatan Kelas 2 BMN</t>
-  </si>
-  <si>
-    <t>4221325013 Perawatan Batu Jembatan Kelas 3 BMN</t>
-  </si>
-  <si>
-    <t>4221325014 Perawatan Beton Jembatan Kelas 3 BMN</t>
-  </si>
-  <si>
-    <t>4221424010 Peralatan Luar Sinyal Mekanik BMN</t>
-  </si>
-  <si>
-    <t>4221425010 Pengamanan Perlintasan Sebidang BMN</t>
-  </si>
-  <si>
-    <t>4221427010 Transmisi Komunikasi BMN</t>
-  </si>
-  <si>
-    <t>4221428010 Peralatan Pendukung Sintel BMN</t>
-  </si>
-  <si>
-    <t>4221428014 Catu Daya Sintel BMN</t>
-  </si>
-  <si>
-    <t>4221600000 Peralatan Khusus Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4222222200 Perawatan Wesel KAI</t>
-  </si>
-  <si>
-    <t>4222600000 Peralatan Khusus Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4222800000 Beban BBM Mekanik Prasarana</t>
-  </si>
-  <si>
-    <t>4231110000 Rapat&amp;Akomodasi BbnUmum Prwtn Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231120000 PerjlDinas BebanUmum PerawatanPrasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231130000 LAT Beban Umum Perawatan Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231150010 Krt Beban Umum Perawatan Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231151710 Kerumahtanggaan UMDT Beban Umum Perawatan Pras BMN</t>
-  </si>
-  <si>
-    <t>4232152310 Tenaga PJL Alih Daya</t>
-  </si>
-  <si>
-    <t>4233100000 Rapat&amp;Akomodasi Beban Umum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4233150010 Kerumahtanggaan Beban Umum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4233151710 Kerumahtanggaan UMDT Beban Umum Perawatan Pras KAI</t>
-  </si>
-  <si>
-    <t>4233160010 Inventaris Beban Umum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4233200000 Perjalanan Dinas BebanUmum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4233300000 LAT Beban Umum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4233400000 ATK Beban Umum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4241000000 Beban Penyusutan AT Prasarana Perkeretaapian</t>
-  </si>
-  <si>
-    <t>4242000000 Beban Penyusutan AT Bangunan Kantor</t>
-  </si>
-  <si>
-    <t>4271100010 Gaji &amp;Tunjangan Pegawai Operasi Prasarana</t>
-  </si>
-  <si>
-    <t>4271400000 Lembur dan Perangsang Pegawai Operasi Prasarana</t>
-  </si>
-  <si>
-    <t>4271500000 Pakaian Dinas Pegawai Operasi Prasarana</t>
-  </si>
-  <si>
-    <t>4272100010 Gaji &amp;Tunjangan PegawaiPerawatan Prasarana Unit JJ</t>
-  </si>
-  <si>
-    <t>4272200010 Iuran Pensiun Pegawai Perawatan Prasarana Unit JJ/</t>
-  </si>
-  <si>
-    <t>4272400000 Lembur dan Perangsang Peg PrwtnPrsrna unit JJ/Sntl</t>
-  </si>
-  <si>
-    <t>4272500000 PakaianDinas PegPrwtn PrasaranaUnit JJ/sntl/BY Pra</t>
-  </si>
-  <si>
-    <t>4273100010 Gaji &amp;Tunjangan Pegawai Renwas JJ/Sintel LAA</t>
-  </si>
-  <si>
-    <t>4273400000 Lembur dan Perangsang Pegawai Renwas JJ/Sintel LAA</t>
-  </si>
-  <si>
-    <t>4273500000 Pakaian Dinas Pegawai Renwas JJ/Sintel LAA</t>
-  </si>
-  <si>
-    <t>5400000000 Penyusutan AT Lainnya (Fasilitas Umum)</t>
-  </si>
-  <si>
-    <t>32020100 Prasarana</t>
-  </si>
-  <si>
-    <t>RKAO Disetujui</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -637,7 +536,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -823,12 +722,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -946,7 +839,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -989,33 +882,14 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1043,7 +917,6 @@
     <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Comma" xfId="42" builtinId="3"/>
     <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
@@ -1369,15 +1242,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H547"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="60.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="15.265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="15.265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="13.06640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1469,10 +1339,10 @@
         <v>57855713800</v>
       </c>
       <c r="D4" s="2">
-        <v>52055713800</v>
+        <v>57455713800</v>
       </c>
       <c r="E4" s="2">
-        <v>5400000000</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
         <v>57455713800</v>
@@ -1573,16 +1443,16 @@
         <v>3947046000</v>
       </c>
       <c r="D8" s="2">
-        <v>39147500</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>39147500</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>3907898500</v>
+        <v>3947046000</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -1781,16 +1651,16 @@
         <v>1200000000</v>
       </c>
       <c r="D16" s="2">
-        <v>42457000</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>42457000</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2">
-        <v>1157543000</v>
+        <v>1200000000</v>
       </c>
       <c r="H16" s="2">
         <v>400000000</v>
@@ -1801,10 +1671,10 @@
         <v>23</v>
       </c>
       <c r="B17" s="2">
-        <v>496414000</v>
+        <v>500000000</v>
       </c>
       <c r="C17" s="2">
-        <v>371414000</v>
+        <v>375000000</v>
       </c>
       <c r="D17" s="2">
         <v>20986164</v>
@@ -1816,7 +1686,7 @@
         <v>20986164</v>
       </c>
       <c r="G17" s="2">
-        <v>350427836</v>
+        <v>354013836</v>
       </c>
       <c r="H17" s="2">
         <v>125000000</v>
@@ -1992,13 +1862,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="2">
-        <v>204850000</v>
+        <v>193087500</v>
       </c>
       <c r="F24" s="2">
-        <v>204850000</v>
+        <v>193087500</v>
       </c>
       <c r="G24" s="2">
-        <v>1661842611</v>
+        <v>1673605111</v>
       </c>
       <c r="H24" s="2">
         <v>625000000</v>
@@ -2044,13 +1914,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="2">
-        <v>414390128</v>
+        <v>413857628</v>
       </c>
       <c r="F26" s="2">
-        <v>414390128</v>
+        <v>413857628</v>
       </c>
       <c r="G26" s="2">
-        <v>3042224076</v>
+        <v>3042756576</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -2347,22 +2217,22 @@
         <v>44</v>
       </c>
       <c r="B38" s="2">
-        <v>361725758454</v>
+        <v>361729344454</v>
       </c>
       <c r="C38" s="2">
-        <v>359308258454</v>
+        <v>359311844454</v>
       </c>
       <c r="D38" s="2">
-        <v>170142785390</v>
+        <v>175461180890</v>
       </c>
       <c r="E38" s="2">
-        <v>54192619773</v>
+        <v>48780324773</v>
       </c>
       <c r="F38" s="2">
-        <v>224335405163</v>
+        <v>224241505663</v>
       </c>
       <c r="G38" s="2">
-        <v>134972853291</v>
+        <v>135070338791</v>
       </c>
       <c r="H38" s="2">
         <v>2417500000</v>
@@ -2379,16 +2249,16 @@
         <v>25194775704</v>
       </c>
       <c r="D39" s="2">
-        <v>16128909964</v>
+        <v>15690909964</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>16128909964</v>
+        <v>15690909964</v>
       </c>
       <c r="G39" s="2">
-        <v>9065865740</v>
+        <v>9503865740</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -2639,10 +2509,10 @@
         <v>4260000000</v>
       </c>
       <c r="D49" s="2">
-        <v>579572114</v>
+        <v>587152114</v>
       </c>
       <c r="E49" s="2">
-        <v>397484675</v>
+        <v>389904675</v>
       </c>
       <c r="F49" s="2">
         <v>977056789</v>
@@ -3393,16 +3263,16 @@
         <v>110897810191</v>
       </c>
       <c r="D78" s="2">
-        <v>19916407003</v>
+        <v>19485987003</v>
       </c>
       <c r="E78" s="2">
-        <v>9043557927</v>
+        <v>9035977927</v>
       </c>
       <c r="F78" s="2">
-        <v>28959964930</v>
+        <v>28521964930</v>
       </c>
       <c r="G78" s="2">
-        <v>81937845261</v>
+        <v>82375845261</v>
       </c>
       <c r="H78" s="2">
         <v>671501500</v>
@@ -3419,16 +3289,16 @@
         <v>4044107500</v>
       </c>
       <c r="D79" s="2">
-        <v>1518071200</v>
+        <v>644350000</v>
       </c>
       <c r="E79" s="2">
         <v>585361000</v>
       </c>
       <c r="F79" s="2">
-        <v>2103432200</v>
+        <v>1229711000</v>
       </c>
       <c r="G79" s="2">
-        <v>1940675300</v>
+        <v>2814396500</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3627,10 +3497,10 @@
         <v>2796520000</v>
       </c>
       <c r="D87" s="2">
-        <v>382331307</v>
+        <v>437704607</v>
       </c>
       <c r="E87" s="2">
-        <v>597369541</v>
+        <v>541996241</v>
       </c>
       <c r="F87" s="2">
         <v>979700848</v>
@@ -3783,10 +3653,10 @@
         <v>1710494400</v>
       </c>
       <c r="D93" s="2">
-        <v>364436500</v>
+        <v>377862600</v>
       </c>
       <c r="E93" s="2">
-        <v>52419100</v>
+        <v>38993000</v>
       </c>
       <c r="F93" s="2">
         <v>416855600</v>
@@ -4303,16 +4173,16 @@
         <v>81718644736</v>
       </c>
       <c r="D113" s="2">
-        <v>18898106425</v>
+        <v>18093184625</v>
       </c>
       <c r="E113" s="2">
-        <v>15482750457</v>
+        <v>15413951057</v>
       </c>
       <c r="F113" s="2">
-        <v>34380856882</v>
+        <v>33507135682</v>
       </c>
       <c r="G113" s="2">
-        <v>47337787854</v>
+        <v>48211509054</v>
       </c>
       <c r="H113" s="2">
         <v>475697500</v>
@@ -4355,16 +4225,16 @@
         <v>435680000</v>
       </c>
       <c r="D115" s="2">
-        <v>39139111</v>
+        <v>8607111</v>
       </c>
       <c r="E115" s="2">
         <v>0</v>
       </c>
       <c r="F115" s="2">
-        <v>39139111</v>
+        <v>8607111</v>
       </c>
       <c r="G115" s="2">
-        <v>396540889</v>
+        <v>427072889</v>
       </c>
       <c r="H115" s="2">
         <v>0</v>
@@ -4693,16 +4563,16 @@
         <v>528750000</v>
       </c>
       <c r="D128" s="2">
-        <v>497734500</v>
+        <v>0</v>
       </c>
       <c r="E128" s="2">
         <v>0</v>
       </c>
       <c r="F128" s="2">
-        <v>497734500</v>
+        <v>0</v>
       </c>
       <c r="G128" s="2">
-        <v>31015500</v>
+        <v>528750000</v>
       </c>
       <c r="H128" s="2">
         <v>176250000</v>
@@ -4797,10 +4667,10 @@
         <v>265950000</v>
       </c>
       <c r="D132" s="2">
-        <v>33432500</v>
+        <v>44932500</v>
       </c>
       <c r="E132" s="2">
-        <v>46413500</v>
+        <v>34913500</v>
       </c>
       <c r="F132" s="2">
         <v>79846000</v>
@@ -5187,16 +5057,16 @@
         <v>50726099717</v>
       </c>
       <c r="D147" s="2">
-        <v>16622102653</v>
+        <v>16105336153</v>
       </c>
       <c r="E147" s="2">
-        <v>4359918620</v>
+        <v>4348418620</v>
       </c>
       <c r="F147" s="2">
-        <v>20982021273</v>
+        <v>20453754773</v>
       </c>
       <c r="G147" s="2">
-        <v>29744078444</v>
+        <v>30272344944</v>
       </c>
       <c r="H147" s="2">
         <v>411080000</v>
@@ -5207,10 +5077,10 @@
         <v>8</v>
       </c>
       <c r="B148" s="2">
-        <v>11383511000</v>
+        <v>5691755500</v>
       </c>
       <c r="C148" s="2">
-        <v>11383511000</v>
+        <v>5691755500</v>
       </c>
       <c r="D148" s="2">
         <v>5533217000</v>
@@ -5222,7 +5092,7 @@
         <v>5533217000</v>
       </c>
       <c r="G148" s="2">
-        <v>5850294000</v>
+        <v>158538500</v>
       </c>
       <c r="H148" s="2">
         <v>0</v>
@@ -5233,10 +5103,10 @@
         <v>11</v>
       </c>
       <c r="B149" s="2">
-        <v>1749516000</v>
+        <v>874758000</v>
       </c>
       <c r="C149" s="2">
-        <v>1749516000</v>
+        <v>874758000</v>
       </c>
       <c r="D149" s="2">
         <v>872621317</v>
@@ -5248,7 +5118,7 @@
         <v>872621317</v>
       </c>
       <c r="G149" s="2">
-        <v>876894683</v>
+        <v>2136683</v>
       </c>
       <c r="H149" s="2">
         <v>0</v>
@@ -5285,10 +5155,10 @@
         <v>13</v>
       </c>
       <c r="B151" s="2">
-        <v>499675000</v>
+        <v>249837500</v>
       </c>
       <c r="C151" s="2">
-        <v>499675000</v>
+        <v>249837500</v>
       </c>
       <c r="D151" s="2">
         <v>106240051</v>
@@ -5300,7 +5170,7 @@
         <v>106240051</v>
       </c>
       <c r="G151" s="2">
-        <v>393434949</v>
+        <v>143597449</v>
       </c>
       <c r="H151" s="2">
         <v>0</v>
@@ -5311,10 +5181,10 @@
         <v>14</v>
       </c>
       <c r="B152" s="2">
-        <v>870437000</v>
+        <v>435218500</v>
       </c>
       <c r="C152" s="2">
-        <v>870437000</v>
+        <v>435218500</v>
       </c>
       <c r="D152" s="2">
         <v>72346470</v>
@@ -5326,7 +5196,7 @@
         <v>80661470</v>
       </c>
       <c r="G152" s="2">
-        <v>789775530</v>
+        <v>354557030</v>
       </c>
       <c r="H152" s="2">
         <v>0</v>
@@ -5337,10 +5207,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="2">
-        <v>393763000</v>
+        <v>196881500</v>
       </c>
       <c r="C153" s="2">
-        <v>393763000</v>
+        <v>196881500</v>
       </c>
       <c r="D153" s="2">
         <v>0</v>
@@ -5352,7 +5222,7 @@
         <v>10224916</v>
       </c>
       <c r="G153" s="2">
-        <v>383538084</v>
+        <v>186656584</v>
       </c>
       <c r="H153" s="2">
         <v>0</v>
@@ -5363,10 +5233,10 @@
         <v>16</v>
       </c>
       <c r="B154" s="2">
-        <v>1702406000</v>
+        <v>1155703000</v>
       </c>
       <c r="C154" s="2">
-        <v>1702406000</v>
+        <v>1155703000</v>
       </c>
       <c r="D154" s="2">
         <v>297962777</v>
@@ -5378,7 +5248,7 @@
         <v>394640336</v>
       </c>
       <c r="G154" s="2">
-        <v>1307765664</v>
+        <v>761062664</v>
       </c>
       <c r="H154" s="2">
         <v>0</v>
@@ -5389,10 +5259,10 @@
         <v>49</v>
       </c>
       <c r="B155" s="2">
-        <v>463360000</v>
+        <v>231680000</v>
       </c>
       <c r="C155" s="2">
-        <v>463360000</v>
+        <v>231680000</v>
       </c>
       <c r="D155" s="2">
         <v>22153380</v>
@@ -5404,7 +5274,7 @@
         <v>22153380</v>
       </c>
       <c r="G155" s="2">
-        <v>441206620</v>
+        <v>209526620</v>
       </c>
       <c r="H155" s="2">
         <v>0</v>
@@ -5415,10 +5285,10 @@
         <v>50</v>
       </c>
       <c r="B156" s="2">
-        <v>996956000</v>
+        <v>498478000</v>
       </c>
       <c r="C156" s="2">
-        <v>996956000</v>
+        <v>498478000</v>
       </c>
       <c r="D156" s="2">
         <v>0</v>
@@ -5430,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="G156" s="2">
-        <v>996956000</v>
+        <v>498478000</v>
       </c>
       <c r="H156" s="2">
         <v>0</v>
@@ -5441,10 +5311,10 @@
         <v>51</v>
       </c>
       <c r="B157" s="2">
-        <v>317990000</v>
+        <v>158995000</v>
       </c>
       <c r="C157" s="2">
-        <v>317990000</v>
+        <v>158995000</v>
       </c>
       <c r="D157" s="2">
         <v>3857000</v>
@@ -5456,7 +5326,7 @@
         <v>3857000</v>
       </c>
       <c r="G157" s="2">
-        <v>314133000</v>
+        <v>155138000</v>
       </c>
       <c r="H157" s="2">
         <v>0</v>
@@ -5467,10 +5337,10 @@
         <v>52</v>
       </c>
       <c r="B158" s="2">
-        <v>2427860000</v>
+        <v>1213930000</v>
       </c>
       <c r="C158" s="2">
-        <v>2427860000</v>
+        <v>1213930000</v>
       </c>
       <c r="D158" s="2">
         <v>48285000</v>
@@ -5482,7 +5352,7 @@
         <v>48285000</v>
       </c>
       <c r="G158" s="2">
-        <v>2379575000</v>
+        <v>1165645000</v>
       </c>
       <c r="H158" s="2">
         <v>0</v>
@@ -5493,10 +5363,10 @@
         <v>54</v>
       </c>
       <c r="B159" s="2">
-        <v>500000000</v>
+        <v>250000000</v>
       </c>
       <c r="C159" s="2">
-        <v>500000000</v>
+        <v>250000000</v>
       </c>
       <c r="D159" s="2">
         <v>38082500</v>
@@ -5508,7 +5378,7 @@
         <v>46857638</v>
       </c>
       <c r="G159" s="2">
-        <v>453142362</v>
+        <v>203142362</v>
       </c>
       <c r="H159" s="2">
         <v>0</v>
@@ -5519,10 +5389,10 @@
         <v>77</v>
       </c>
       <c r="B160" s="2">
-        <v>78898000</v>
+        <v>39449000</v>
       </c>
       <c r="C160" s="2">
-        <v>78898000</v>
+        <v>39449000</v>
       </c>
       <c r="D160" s="2">
         <v>0</v>
@@ -5534,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="G160" s="2">
-        <v>78898000</v>
+        <v>39449000</v>
       </c>
       <c r="H160" s="2">
         <v>0</v>
@@ -5545,10 +5415,10 @@
         <v>56</v>
       </c>
       <c r="B161" s="2">
-        <v>867942000</v>
+        <v>433971000</v>
       </c>
       <c r="C161" s="2">
-        <v>867942000</v>
+        <v>433971000</v>
       </c>
       <c r="D161" s="2">
         <v>0</v>
@@ -5560,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="G161" s="2">
-        <v>867942000</v>
+        <v>433971000</v>
       </c>
       <c r="H161" s="2">
         <v>0</v>
@@ -5571,10 +5441,10 @@
         <v>22</v>
       </c>
       <c r="B162" s="2">
-        <v>250000000</v>
+        <v>125000000</v>
       </c>
       <c r="C162" s="2">
-        <v>187500000</v>
+        <v>125000000</v>
       </c>
       <c r="D162" s="2">
         <v>0</v>
@@ -5586,10 +5456,10 @@
         <v>0</v>
       </c>
       <c r="G162" s="2">
-        <v>187500000</v>
+        <v>125000000</v>
       </c>
       <c r="H162" s="2">
-        <v>62500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.45">
@@ -5597,10 +5467,10 @@
         <v>57</v>
       </c>
       <c r="B163" s="2">
-        <v>90090000</v>
+        <v>45045000</v>
       </c>
       <c r="C163" s="2">
-        <v>90090000</v>
+        <v>45045000</v>
       </c>
       <c r="D163" s="2">
         <v>11205000</v>
@@ -5612,7 +5482,7 @@
         <v>11205000</v>
       </c>
       <c r="G163" s="2">
-        <v>78885000</v>
+        <v>33840000</v>
       </c>
       <c r="H163" s="2">
         <v>0</v>
@@ -5623,10 +5493,10 @@
         <v>24</v>
       </c>
       <c r="B164" s="2">
-        <v>132300000</v>
+        <v>33075000</v>
       </c>
       <c r="C164" s="2">
-        <v>132300000</v>
+        <v>33075000</v>
       </c>
       <c r="D164" s="2">
         <v>0</v>
@@ -5638,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="G164" s="2">
-        <v>132300000</v>
+        <v>33075000</v>
       </c>
       <c r="H164" s="2">
         <v>0</v>
@@ -5649,22 +5519,22 @@
         <v>58</v>
       </c>
       <c r="B165" s="2">
-        <v>2369000000</v>
+        <v>592250000</v>
       </c>
       <c r="C165" s="2">
-        <v>2369000000</v>
+        <v>592250000</v>
       </c>
       <c r="D165" s="2">
-        <v>0</v>
+        <v>269200</v>
       </c>
       <c r="E165" s="2">
-        <v>346514506</v>
+        <v>346245306</v>
       </c>
       <c r="F165" s="2">
         <v>346514506</v>
       </c>
       <c r="G165" s="2">
-        <v>2022485494</v>
+        <v>245735494</v>
       </c>
       <c r="H165" s="2">
         <v>0</v>
@@ -5675,10 +5545,10 @@
         <v>25</v>
       </c>
       <c r="B166" s="2">
-        <v>180000000</v>
+        <v>45000000</v>
       </c>
       <c r="C166" s="2">
-        <v>135000000</v>
+        <v>45000000</v>
       </c>
       <c r="D166" s="2">
         <v>28592500</v>
@@ -5690,10 +5560,10 @@
         <v>38592500</v>
       </c>
       <c r="G166" s="2">
-        <v>96407500</v>
+        <v>6407500</v>
       </c>
       <c r="H166" s="2">
-        <v>45000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.45">
@@ -5701,10 +5571,10 @@
         <v>26</v>
       </c>
       <c r="B167" s="2">
-        <v>545000000</v>
+        <v>136250000</v>
       </c>
       <c r="C167" s="2">
-        <v>408750000</v>
+        <v>136250000</v>
       </c>
       <c r="D167" s="2">
         <v>55881809</v>
@@ -5716,10 +5586,10 @@
         <v>134443944</v>
       </c>
       <c r="G167" s="2">
-        <v>274306056</v>
+        <v>1806056</v>
       </c>
       <c r="H167" s="2">
-        <v>136250000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.45">
@@ -5727,10 +5597,10 @@
         <v>27</v>
       </c>
       <c r="B168" s="2">
-        <v>87000000</v>
+        <v>21750000</v>
       </c>
       <c r="C168" s="2">
-        <v>87000000</v>
+        <v>21750000</v>
       </c>
       <c r="D168" s="2">
         <v>0</v>
@@ -5742,7 +5612,7 @@
         <v>14461500</v>
       </c>
       <c r="G168" s="2">
-        <v>72538500</v>
+        <v>7288500</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
@@ -5753,10 +5623,10 @@
         <v>28</v>
       </c>
       <c r="B169" s="2">
-        <v>586200000</v>
+        <v>146550000</v>
       </c>
       <c r="C169" s="2">
-        <v>439650000</v>
+        <v>146550000</v>
       </c>
       <c r="D169" s="2">
         <v>114790302</v>
@@ -5768,10 +5638,10 @@
         <v>114790302</v>
       </c>
       <c r="G169" s="2">
-        <v>324859698</v>
+        <v>31759698</v>
       </c>
       <c r="H169" s="2">
-        <v>146550000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.45">
@@ -5779,10 +5649,10 @@
         <v>29</v>
       </c>
       <c r="B170" s="2">
-        <v>20000000</v>
+        <v>5000000</v>
       </c>
       <c r="C170" s="2">
-        <v>15000000</v>
+        <v>5000000</v>
       </c>
       <c r="D170" s="2">
         <v>0</v>
@@ -5794,10 +5664,10 @@
         <v>3000000</v>
       </c>
       <c r="G170" s="2">
-        <v>12000000</v>
+        <v>2000000</v>
       </c>
       <c r="H170" s="2">
-        <v>5000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.45">
@@ -5805,10 +5675,10 @@
         <v>30</v>
       </c>
       <c r="B171" s="2">
-        <v>216402000</v>
+        <v>54100500</v>
       </c>
       <c r="C171" s="2">
-        <v>162301500</v>
+        <v>54100500</v>
       </c>
       <c r="D171" s="2">
         <v>0</v>
@@ -5820,10 +5690,10 @@
         <v>37528000</v>
       </c>
       <c r="G171" s="2">
-        <v>124773500</v>
+        <v>16572500</v>
       </c>
       <c r="H171" s="2">
-        <v>54100500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.45">
@@ -5831,10 +5701,10 @@
         <v>31</v>
       </c>
       <c r="B172" s="2">
-        <v>48000000</v>
+        <v>12000000</v>
       </c>
       <c r="C172" s="2">
-        <v>48000000</v>
+        <v>12000000</v>
       </c>
       <c r="D172" s="2">
         <v>6889220</v>
@@ -5846,7 +5716,7 @@
         <v>6889220</v>
       </c>
       <c r="G172" s="2">
-        <v>41110780</v>
+        <v>5110780</v>
       </c>
       <c r="H172" s="2">
         <v>0</v>
@@ -6065,25 +5935,25 @@
         <v>78</v>
       </c>
       <c r="B181" s="2">
-        <v>44576468987</v>
+        <v>30446840487</v>
       </c>
       <c r="C181" s="2">
-        <v>44127068487</v>
+        <v>30446840487</v>
       </c>
       <c r="D181" s="2">
-        <v>7212124326</v>
+        <v>7212393526</v>
       </c>
       <c r="E181" s="2">
-        <v>3268481108</v>
+        <v>3268211908</v>
       </c>
       <c r="F181" s="2">
         <v>10480605434</v>
       </c>
       <c r="G181" s="2">
-        <v>33646463053</v>
+        <v>19966235053</v>
       </c>
       <c r="H181" s="2">
-        <v>449400500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.45">
@@ -6091,10 +5961,10 @@
         <v>8</v>
       </c>
       <c r="B182" s="2">
-        <v>7317456560</v>
+        <v>3658728280</v>
       </c>
       <c r="C182" s="2">
-        <v>7317456560</v>
+        <v>3658728280</v>
       </c>
       <c r="D182" s="2">
         <v>2851419420</v>
@@ -6106,7 +5976,7 @@
         <v>2851419420</v>
       </c>
       <c r="G182" s="2">
-        <v>4466037140</v>
+        <v>807308860</v>
       </c>
       <c r="H182" s="2">
         <v>0</v>
@@ -6195,10 +6065,10 @@
         <v>11</v>
       </c>
       <c r="B186" s="2">
-        <v>3030122000</v>
+        <v>1515061000</v>
       </c>
       <c r="C186" s="2">
-        <v>3030122000</v>
+        <v>1515061000</v>
       </c>
       <c r="D186" s="2">
         <v>461381691</v>
@@ -6210,7 +6080,7 @@
         <v>461381691</v>
       </c>
       <c r="G186" s="2">
-        <v>2568740309</v>
+        <v>1053679309</v>
       </c>
       <c r="H186" s="2">
         <v>0</v>
@@ -6221,10 +6091,10 @@
         <v>12</v>
       </c>
       <c r="B187" s="2">
-        <v>450000000</v>
+        <v>225000000</v>
       </c>
       <c r="C187" s="2">
-        <v>450000000</v>
+        <v>225000000</v>
       </c>
       <c r="D187" s="2">
         <v>0</v>
@@ -6236,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="G187" s="2">
-        <v>450000000</v>
+        <v>225000000</v>
       </c>
       <c r="H187" s="2">
         <v>0</v>
@@ -6247,10 +6117,10 @@
         <v>48</v>
       </c>
       <c r="B188" s="2">
-        <v>455000000</v>
+        <v>227500000</v>
       </c>
       <c r="C188" s="2">
-        <v>455000000</v>
+        <v>227500000</v>
       </c>
       <c r="D188" s="2">
         <v>5081445</v>
@@ -6262,7 +6132,7 @@
         <v>5081445</v>
       </c>
       <c r="G188" s="2">
-        <v>449918555</v>
+        <v>222418555</v>
       </c>
       <c r="H188" s="2">
         <v>0</v>
@@ -6273,22 +6143,22 @@
         <v>13</v>
       </c>
       <c r="B189" s="2">
-        <v>469000000</v>
+        <v>234500000</v>
       </c>
       <c r="C189" s="2">
-        <v>469000000</v>
+        <v>234500000</v>
       </c>
       <c r="D189" s="2">
-        <v>44160000</v>
+        <v>49635000</v>
       </c>
       <c r="E189" s="2">
-        <v>5475000</v>
+        <v>0</v>
       </c>
       <c r="F189" s="2">
         <v>49635000</v>
       </c>
       <c r="G189" s="2">
-        <v>419365000</v>
+        <v>184865000</v>
       </c>
       <c r="H189" s="2">
         <v>0</v>
@@ -6299,10 +6169,10 @@
         <v>14</v>
       </c>
       <c r="B190" s="2">
-        <v>400000000</v>
+        <v>200000000</v>
       </c>
       <c r="C190" s="2">
-        <v>400000000</v>
+        <v>200000000</v>
       </c>
       <c r="D190" s="2">
         <v>51500000</v>
@@ -6314,7 +6184,7 @@
         <v>51500000</v>
       </c>
       <c r="G190" s="2">
-        <v>348500000</v>
+        <v>148500000</v>
       </c>
       <c r="H190" s="2">
         <v>0</v>
@@ -6325,10 +6195,10 @@
         <v>15</v>
       </c>
       <c r="B191" s="2">
-        <v>609000000</v>
+        <v>304500000</v>
       </c>
       <c r="C191" s="2">
-        <v>609000000</v>
+        <v>304500000</v>
       </c>
       <c r="D191" s="2">
         <v>88477869</v>
@@ -6340,7 +6210,7 @@
         <v>135362869</v>
       </c>
       <c r="G191" s="2">
-        <v>473637131</v>
+        <v>169137131</v>
       </c>
       <c r="H191" s="2">
         <v>0</v>
@@ -6351,10 +6221,10 @@
         <v>16</v>
       </c>
       <c r="B192" s="2">
-        <v>1862650000</v>
+        <v>931325000</v>
       </c>
       <c r="C192" s="2">
-        <v>1862650000</v>
+        <v>931325000</v>
       </c>
       <c r="D192" s="2">
         <v>281432200</v>
@@ -6366,7 +6236,7 @@
         <v>341319546</v>
       </c>
       <c r="G192" s="2">
-        <v>1521330454</v>
+        <v>590005454</v>
       </c>
       <c r="H192" s="2">
         <v>0</v>
@@ -6377,10 +6247,10 @@
         <v>49</v>
       </c>
       <c r="B193" s="2">
-        <v>281000000</v>
+        <v>140500000</v>
       </c>
       <c r="C193" s="2">
-        <v>281000000</v>
+        <v>140500000</v>
       </c>
       <c r="D193" s="2">
         <v>30944688</v>
@@ -6392,7 +6262,7 @@
         <v>30944688</v>
       </c>
       <c r="G193" s="2">
-        <v>250055312</v>
+        <v>109555312</v>
       </c>
       <c r="H193" s="2">
         <v>0</v>
@@ -6403,10 +6273,10 @@
         <v>50</v>
       </c>
       <c r="B194" s="2">
-        <v>950000000</v>
+        <v>475000000</v>
       </c>
       <c r="C194" s="2">
-        <v>950000000</v>
+        <v>475000000</v>
       </c>
       <c r="D194" s="2">
         <v>0</v>
@@ -6418,7 +6288,7 @@
         <v>0</v>
       </c>
       <c r="G194" s="2">
-        <v>950000000</v>
+        <v>475000000</v>
       </c>
       <c r="H194" s="2">
         <v>0</v>
@@ -6429,10 +6299,10 @@
         <v>51</v>
       </c>
       <c r="B195" s="2">
-        <v>50000000</v>
+        <v>25000000</v>
       </c>
       <c r="C195" s="2">
-        <v>50000000</v>
+        <v>25000000</v>
       </c>
       <c r="D195" s="2">
         <v>4883000</v>
@@ -6444,7 +6314,7 @@
         <v>4883000</v>
       </c>
       <c r="G195" s="2">
-        <v>45117000</v>
+        <v>20117000</v>
       </c>
       <c r="H195" s="2">
         <v>0</v>
@@ -6455,10 +6325,10 @@
         <v>52</v>
       </c>
       <c r="B196" s="2">
-        <v>1491275000</v>
+        <v>745637500</v>
       </c>
       <c r="C196" s="2">
-        <v>1491275000</v>
+        <v>745637500</v>
       </c>
       <c r="D196" s="2">
         <v>599680000</v>
@@ -6470,7 +6340,7 @@
         <v>666445000</v>
       </c>
       <c r="G196" s="2">
-        <v>824830000</v>
+        <v>79192500</v>
       </c>
       <c r="H196" s="2">
         <v>0</v>
@@ -6481,10 +6351,10 @@
         <v>53</v>
       </c>
       <c r="B197" s="2">
-        <v>40000000</v>
+        <v>20000000</v>
       </c>
       <c r="C197" s="2">
-        <v>40000000</v>
+        <v>20000000</v>
       </c>
       <c r="D197" s="2">
         <v>6475000</v>
@@ -6496,7 +6366,7 @@
         <v>6475000</v>
       </c>
       <c r="G197" s="2">
-        <v>33525000</v>
+        <v>13525000</v>
       </c>
       <c r="H197" s="2">
         <v>0</v>
@@ -6507,10 +6377,10 @@
         <v>77</v>
       </c>
       <c r="B198" s="2">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="C198" s="2">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="D198" s="2">
         <v>0</v>
@@ -6522,7 +6392,7 @@
         <v>0</v>
       </c>
       <c r="G198" s="2">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="H198" s="2">
         <v>0</v>
@@ -6533,10 +6403,10 @@
         <v>56</v>
       </c>
       <c r="B199" s="2">
-        <v>509000000</v>
+        <v>254500000</v>
       </c>
       <c r="C199" s="2">
-        <v>509000000</v>
+        <v>254500000</v>
       </c>
       <c r="D199" s="2">
         <v>18232600</v>
@@ -6548,7 +6418,7 @@
         <v>18232600</v>
       </c>
       <c r="G199" s="2">
-        <v>490767400</v>
+        <v>236267400</v>
       </c>
       <c r="H199" s="2">
         <v>0</v>
@@ -6559,10 +6429,10 @@
         <v>22</v>
       </c>
       <c r="B200" s="2">
-        <v>150000000</v>
+        <v>75000000</v>
       </c>
       <c r="C200" s="2">
-        <v>112500000</v>
+        <v>75000000</v>
       </c>
       <c r="D200" s="2">
         <v>0</v>
@@ -6574,10 +6444,10 @@
         <v>41856000</v>
       </c>
       <c r="G200" s="2">
-        <v>70644000</v>
+        <v>33144000</v>
       </c>
       <c r="H200" s="2">
-        <v>37500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.45">
@@ -6585,22 +6455,22 @@
         <v>57</v>
       </c>
       <c r="B201" s="2">
-        <v>320100000</v>
+        <v>160050000</v>
       </c>
       <c r="C201" s="2">
-        <v>320100000</v>
+        <v>160050000</v>
       </c>
       <c r="D201" s="2">
-        <v>0</v>
+        <v>44525000</v>
       </c>
       <c r="E201" s="2">
-        <v>71775000</v>
+        <v>27250000</v>
       </c>
       <c r="F201" s="2">
         <v>71775000</v>
       </c>
       <c r="G201" s="2">
-        <v>248325000</v>
+        <v>88275000</v>
       </c>
       <c r="H201" s="2">
         <v>0</v>
@@ -6611,10 +6481,10 @@
         <v>58</v>
       </c>
       <c r="B202" s="2">
-        <v>2570000000</v>
+        <v>642500000</v>
       </c>
       <c r="C202" s="2">
-        <v>2570000000</v>
+        <v>642500000</v>
       </c>
       <c r="D202" s="2">
         <v>0</v>
@@ -6626,7 +6496,7 @@
         <v>394857596</v>
       </c>
       <c r="G202" s="2">
-        <v>2175142404</v>
+        <v>247642404</v>
       </c>
       <c r="H202" s="2">
         <v>0</v>
@@ -6637,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="B203" s="2">
-        <v>130000000</v>
+        <v>69718811</v>
       </c>
       <c r="C203" s="2">
-        <v>97500000</v>
+        <v>69718811</v>
       </c>
       <c r="D203" s="2">
         <v>3400000</v>
@@ -6652,10 +6522,10 @@
         <v>35818811</v>
       </c>
       <c r="G203" s="2">
-        <v>61681189</v>
+        <v>33900000</v>
       </c>
       <c r="H203" s="2">
-        <v>32500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.45">
@@ -6663,10 +6533,10 @@
         <v>26</v>
       </c>
       <c r="B204" s="2">
-        <v>514046000</v>
+        <v>128511500</v>
       </c>
       <c r="C204" s="2">
-        <v>385534500</v>
+        <v>128511500</v>
       </c>
       <c r="D204" s="2">
         <v>23159000</v>
@@ -6678,10 +6548,10 @@
         <v>74188500</v>
       </c>
       <c r="G204" s="2">
-        <v>311346000</v>
+        <v>54323000</v>
       </c>
       <c r="H204" s="2">
-        <v>128511500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.45">
@@ -6689,10 +6559,10 @@
         <v>27</v>
       </c>
       <c r="B205" s="2">
-        <v>105000000</v>
+        <v>17500000</v>
       </c>
       <c r="C205" s="2">
-        <v>105000000</v>
+        <v>17500000</v>
       </c>
       <c r="D205" s="2">
         <v>0</v>
@@ -6704,7 +6574,7 @@
         <v>17500000</v>
       </c>
       <c r="G205" s="2">
-        <v>87500000</v>
+        <v>0</v>
       </c>
       <c r="H205" s="2">
         <v>0</v>
@@ -6715,25 +6585,25 @@
         <v>28</v>
       </c>
       <c r="B206" s="2">
-        <v>450000000</v>
+        <v>112500000</v>
       </c>
       <c r="C206" s="2">
-        <v>337500000</v>
+        <v>112500000</v>
       </c>
       <c r="D206" s="2">
-        <v>27515000</v>
+        <v>31837000</v>
       </c>
       <c r="E206" s="2">
-        <v>10052000</v>
+        <v>5730000</v>
       </c>
       <c r="F206" s="2">
         <v>37567000</v>
       </c>
       <c r="G206" s="2">
-        <v>299933000</v>
+        <v>74933000</v>
       </c>
       <c r="H206" s="2">
-        <v>112500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.45">
@@ -6741,10 +6611,10 @@
         <v>29</v>
       </c>
       <c r="B207" s="2">
-        <v>165000000</v>
+        <v>41250000</v>
       </c>
       <c r="C207" s="2">
-        <v>123750000</v>
+        <v>41250000</v>
       </c>
       <c r="D207" s="2">
         <v>0</v>
@@ -6756,10 +6626,10 @@
         <v>0</v>
       </c>
       <c r="G207" s="2">
-        <v>123750000</v>
+        <v>41250000</v>
       </c>
       <c r="H207" s="2">
-        <v>41250000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.45">
@@ -6767,10 +6637,10 @@
         <v>30</v>
       </c>
       <c r="B208" s="2">
-        <v>252000000</v>
+        <v>63000000</v>
       </c>
       <c r="C208" s="2">
-        <v>189000000</v>
+        <v>63000000</v>
       </c>
       <c r="D208" s="2">
         <v>0</v>
@@ -6782,10 +6652,10 @@
         <v>52728250</v>
       </c>
       <c r="G208" s="2">
-        <v>136271750</v>
+        <v>10271750</v>
       </c>
       <c r="H208" s="2">
-        <v>63000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.45">
@@ -6793,10 +6663,10 @@
         <v>79</v>
       </c>
       <c r="B209" s="2">
-        <v>18000000</v>
+        <v>4500000</v>
       </c>
       <c r="C209" s="2">
-        <v>18000000</v>
+        <v>4500000</v>
       </c>
       <c r="D209" s="2">
         <v>1245000</v>
@@ -6808,7 +6678,7 @@
         <v>3257160</v>
       </c>
       <c r="G209" s="2">
-        <v>14742840</v>
+        <v>1242840</v>
       </c>
       <c r="H209" s="2">
         <v>0</v>
@@ -6819,10 +6689,10 @@
         <v>31</v>
       </c>
       <c r="B210" s="2">
-        <v>50000000</v>
+        <v>12500000</v>
       </c>
       <c r="C210" s="2">
-        <v>50000000</v>
+        <v>12500000</v>
       </c>
       <c r="D210" s="2">
         <v>0</v>
@@ -6834,7 +6704,7 @@
         <v>12431950</v>
       </c>
       <c r="G210" s="2">
-        <v>37568050</v>
+        <v>68050</v>
       </c>
       <c r="H210" s="2">
         <v>0</v>
@@ -7053,25 +6923,25 @@
         <v>80</v>
       </c>
       <c r="B219" s="2">
-        <v>43869608368</v>
+        <v>31465240899</v>
       </c>
       <c r="C219" s="2">
-        <v>43454346868</v>
+        <v>31465240899</v>
       </c>
       <c r="D219" s="2">
-        <v>4498986913</v>
+        <v>4553308913</v>
       </c>
       <c r="E219" s="2">
-        <v>4331744190</v>
+        <v>4277422190</v>
       </c>
       <c r="F219" s="2">
         <v>8830731103</v>
       </c>
       <c r="G219" s="2">
-        <v>34623615765</v>
+        <v>22634509796</v>
       </c>
       <c r="H219" s="2">
-        <v>415261500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.45">
@@ -7079,22 +6949,22 @@
         <v>8</v>
       </c>
       <c r="B220" s="2">
-        <v>12264606000</v>
+        <v>11504360000</v>
       </c>
       <c r="C220" s="2">
-        <v>12264606000</v>
+        <v>11504360000</v>
       </c>
       <c r="D220" s="2">
-        <v>9573167730</v>
+        <v>8529167730</v>
       </c>
       <c r="E220" s="2">
         <v>36030000</v>
       </c>
       <c r="F220" s="2">
-        <v>9609197730</v>
+        <v>8565197730</v>
       </c>
       <c r="G220" s="2">
-        <v>2655408270</v>
+        <v>2939162270</v>
       </c>
       <c r="H220" s="2">
         <v>0</v>
@@ -7105,10 +6975,10 @@
         <v>11</v>
       </c>
       <c r="B221" s="2">
-        <v>1126306000</v>
+        <v>1171703000</v>
       </c>
       <c r="C221" s="2">
-        <v>1126306000</v>
+        <v>1171703000</v>
       </c>
       <c r="D221" s="2">
         <v>617301007</v>
@@ -7120,7 +6990,7 @@
         <v>617301007</v>
       </c>
       <c r="G221" s="2">
-        <v>509004993</v>
+        <v>554401993</v>
       </c>
       <c r="H221" s="2">
         <v>0</v>
@@ -7131,10 +7001,10 @@
         <v>12</v>
       </c>
       <c r="B222" s="2">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="C222" s="2">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="D222" s="2">
         <v>0</v>
@@ -7146,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="G222" s="2">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="H222" s="2">
         <v>0</v>
@@ -7157,10 +7027,10 @@
         <v>48</v>
       </c>
       <c r="B223" s="2">
-        <v>495000000</v>
+        <v>247500000</v>
       </c>
       <c r="C223" s="2">
-        <v>495000000</v>
+        <v>247500000</v>
       </c>
       <c r="D223" s="2">
         <v>29117120</v>
@@ -7172,7 +7042,7 @@
         <v>29117120</v>
       </c>
       <c r="G223" s="2">
-        <v>465882880</v>
+        <v>218382880</v>
       </c>
       <c r="H223" s="2">
         <v>0</v>
@@ -7183,10 +7053,10 @@
         <v>13</v>
       </c>
       <c r="B224" s="2">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="C224" s="2">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="D224" s="2">
         <v>0</v>
@@ -7198,7 +7068,7 @@
         <v>0</v>
       </c>
       <c r="G224" s="2">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="H224" s="2">
         <v>0</v>
@@ -7209,10 +7079,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="2">
-        <v>1310391000</v>
+        <v>655195500</v>
       </c>
       <c r="C225" s="2">
-        <v>1310391000</v>
+        <v>655195500</v>
       </c>
       <c r="D225" s="2">
         <v>62324038</v>
@@ -7224,7 +7094,7 @@
         <v>162707588</v>
       </c>
       <c r="G225" s="2">
-        <v>1147683412</v>
+        <v>492487912</v>
       </c>
       <c r="H225" s="2">
         <v>0</v>
@@ -7235,10 +7105,10 @@
         <v>16</v>
       </c>
       <c r="B226" s="2">
-        <v>1380000000</v>
+        <v>690000000</v>
       </c>
       <c r="C226" s="2">
-        <v>1380000000</v>
+        <v>690000000</v>
       </c>
       <c r="D226" s="2">
         <v>321145216</v>
@@ -7250,7 +7120,7 @@
         <v>522187216</v>
       </c>
       <c r="G226" s="2">
-        <v>857812784</v>
+        <v>167812784</v>
       </c>
       <c r="H226" s="2">
         <v>0</v>
@@ -7261,10 +7131,10 @@
         <v>49</v>
       </c>
       <c r="B227" s="2">
-        <v>350000000</v>
+        <v>175000000</v>
       </c>
       <c r="C227" s="2">
-        <v>350000000</v>
+        <v>175000000</v>
       </c>
       <c r="D227" s="2">
         <v>0</v>
@@ -7276,7 +7146,7 @@
         <v>0</v>
       </c>
       <c r="G227" s="2">
-        <v>350000000</v>
+        <v>175000000</v>
       </c>
       <c r="H227" s="2">
         <v>0</v>
@@ -7287,22 +7157,22 @@
         <v>50</v>
       </c>
       <c r="B228" s="2">
-        <v>497000000</v>
+        <v>496659494</v>
       </c>
       <c r="C228" s="2">
-        <v>497000000</v>
+        <v>496659494</v>
       </c>
       <c r="D228" s="2">
+        <v>0</v>
+      </c>
+      <c r="E228" s="2">
+        <v>0</v>
+      </c>
+      <c r="F228" s="2">
+        <v>0</v>
+      </c>
+      <c r="G228" s="2">
         <v>496659494</v>
-      </c>
-      <c r="E228" s="2">
-        <v>0</v>
-      </c>
-      <c r="F228" s="2">
-        <v>496659494</v>
-      </c>
-      <c r="G228" s="2">
-        <v>340506</v>
       </c>
       <c r="H228" s="2">
         <v>0</v>
@@ -7313,10 +7183,10 @@
         <v>51</v>
       </c>
       <c r="B229" s="2">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="C229" s="2">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="D229" s="2">
         <v>6718000</v>
@@ -7328,7 +7198,7 @@
         <v>6718000</v>
       </c>
       <c r="G229" s="2">
-        <v>93282000</v>
+        <v>43282000</v>
       </c>
       <c r="H229" s="2">
         <v>0</v>
@@ -7339,22 +7209,22 @@
         <v>52</v>
       </c>
       <c r="B230" s="2">
-        <v>2264065000</v>
+        <v>2471712500</v>
       </c>
       <c r="C230" s="2">
-        <v>2264065000</v>
+        <v>2471712500</v>
       </c>
       <c r="D230" s="2">
-        <v>1986680000</v>
+        <v>1339680000</v>
       </c>
       <c r="E230" s="2">
         <v>0</v>
       </c>
       <c r="F230" s="2">
-        <v>1986680000</v>
+        <v>1339680000</v>
       </c>
       <c r="G230" s="2">
-        <v>277385000</v>
+        <v>1132032500</v>
       </c>
       <c r="H230" s="2">
         <v>0</v>
@@ -7365,10 +7235,10 @@
         <v>77</v>
       </c>
       <c r="B231" s="2">
-        <v>30000000</v>
+        <v>15000000</v>
       </c>
       <c r="C231" s="2">
-        <v>30000000</v>
+        <v>15000000</v>
       </c>
       <c r="D231" s="2">
         <v>0</v>
@@ -7380,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="G231" s="2">
-        <v>30000000</v>
+        <v>15000000</v>
       </c>
       <c r="H231" s="2">
         <v>0</v>
@@ -7391,10 +7261,10 @@
         <v>56</v>
       </c>
       <c r="B232" s="2">
-        <v>1155000000</v>
+        <v>577500000</v>
       </c>
       <c r="C232" s="2">
-        <v>1155000000</v>
+        <v>577500000</v>
       </c>
       <c r="D232" s="2">
         <v>495830000</v>
@@ -7406,7 +7276,7 @@
         <v>495830000</v>
       </c>
       <c r="G232" s="2">
-        <v>659170000</v>
+        <v>81670000</v>
       </c>
       <c r="H232" s="2">
         <v>0</v>
@@ -7417,10 +7287,10 @@
         <v>22</v>
       </c>
       <c r="B233" s="2">
-        <v>1040000000</v>
+        <v>520000000</v>
       </c>
       <c r="C233" s="2">
-        <v>780000000</v>
+        <v>520000000</v>
       </c>
       <c r="D233" s="2">
         <v>0</v>
@@ -7432,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="G233" s="2">
-        <v>780000000</v>
+        <v>520000000</v>
       </c>
       <c r="H233" s="2">
-        <v>260000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.45">
@@ -7443,22 +7313,22 @@
         <v>57</v>
       </c>
       <c r="B234" s="2">
-        <v>250000000</v>
+        <v>125000000</v>
       </c>
       <c r="C234" s="2">
-        <v>250000000</v>
+        <v>125000000</v>
       </c>
       <c r="D234" s="2">
-        <v>0</v>
+        <v>32848750</v>
       </c>
       <c r="E234" s="2">
-        <v>32848750</v>
+        <v>0</v>
       </c>
       <c r="F234" s="2">
         <v>32848750</v>
       </c>
       <c r="G234" s="2">
-        <v>217151250</v>
+        <v>92151250</v>
       </c>
       <c r="H234" s="2">
         <v>0</v>
@@ -7469,10 +7339,10 @@
         <v>58</v>
       </c>
       <c r="B235" s="2">
-        <v>3063576000</v>
+        <v>765894000</v>
       </c>
       <c r="C235" s="2">
-        <v>3063576000</v>
+        <v>765894000</v>
       </c>
       <c r="D235" s="2">
         <v>0</v>
@@ -7484,7 +7354,7 @@
         <v>396859899</v>
       </c>
       <c r="G235" s="2">
-        <v>2666716101</v>
+        <v>369034101</v>
       </c>
       <c r="H235" s="2">
         <v>0</v>
@@ -7495,10 +7365,10 @@
         <v>25</v>
       </c>
       <c r="B236" s="2">
-        <v>146883400</v>
+        <v>36720850</v>
       </c>
       <c r="C236" s="2">
-        <v>110162550</v>
+        <v>36720850</v>
       </c>
       <c r="D236" s="2">
         <v>10311000</v>
@@ -7510,10 +7380,10 @@
         <v>20271000</v>
       </c>
       <c r="G236" s="2">
-        <v>89891550</v>
+        <v>16449850</v>
       </c>
       <c r="H236" s="2">
-        <v>36720850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.45">
@@ -7521,10 +7391,10 @@
         <v>26</v>
       </c>
       <c r="B237" s="2">
-        <v>472318000</v>
+        <v>118079500</v>
       </c>
       <c r="C237" s="2">
-        <v>354238500</v>
+        <v>118079500</v>
       </c>
       <c r="D237" s="2">
         <v>29494000</v>
@@ -7536,10 +7406,10 @@
         <v>81611900</v>
       </c>
       <c r="G237" s="2">
-        <v>272626600</v>
+        <v>36467600</v>
       </c>
       <c r="H237" s="2">
-        <v>118079500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.45">
@@ -7547,10 +7417,10 @@
         <v>27</v>
       </c>
       <c r="B238" s="2">
-        <v>99000000</v>
+        <v>24750000</v>
       </c>
       <c r="C238" s="2">
-        <v>99000000</v>
+        <v>24750000</v>
       </c>
       <c r="D238" s="2">
         <v>0</v>
@@ -7562,7 +7432,7 @@
         <v>16500000</v>
       </c>
       <c r="G238" s="2">
-        <v>82500000</v>
+        <v>8250000</v>
       </c>
       <c r="H238" s="2">
         <v>0</v>
@@ -7573,7 +7443,7 @@
         <v>28</v>
       </c>
       <c r="B239" s="2">
-        <v>775000000</v>
+        <v>732016185</v>
       </c>
       <c r="C239" s="2">
         <v>732016185</v>
@@ -7591,7 +7461,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="2">
-        <v>42983815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.45">
@@ -7599,10 +7469,10 @@
         <v>30</v>
       </c>
       <c r="B240" s="2">
-        <v>269712000</v>
+        <v>67428000</v>
       </c>
       <c r="C240" s="2">
-        <v>202284000</v>
+        <v>67428000</v>
       </c>
       <c r="D240" s="2">
         <v>0</v>
@@ -7614,10 +7484,10 @@
         <v>50796750</v>
       </c>
       <c r="G240" s="2">
-        <v>151487250</v>
+        <v>16631250</v>
       </c>
       <c r="H240" s="2">
-        <v>67428000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.45">
@@ -7625,10 +7495,10 @@
         <v>31</v>
       </c>
       <c r="B241" s="2">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="C241" s="2">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="D241" s="2">
         <v>14997987</v>
@@ -7640,7 +7510,7 @@
         <v>14997987</v>
       </c>
       <c r="G241" s="2">
-        <v>45002013</v>
+        <v>2013</v>
       </c>
       <c r="H241" s="2">
         <v>0</v>
@@ -7859,25 +7729,25 @@
         <v>81</v>
       </c>
       <c r="B250" s="2">
-        <v>49439984720</v>
+        <v>42600646349</v>
       </c>
       <c r="C250" s="2">
-        <v>48914772555</v>
+        <v>42600646349</v>
       </c>
       <c r="D250" s="2">
-        <v>14349605277</v>
+        <v>12194794533</v>
       </c>
       <c r="E250" s="2">
-        <v>4424500712</v>
+        <v>4391651962</v>
       </c>
       <c r="F250" s="2">
-        <v>18774105989</v>
+        <v>16586446495</v>
       </c>
       <c r="G250" s="2">
-        <v>30140666566</v>
+        <v>26014199854</v>
       </c>
       <c r="H250" s="2">
-        <v>525212165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.45">
@@ -8073,16 +7943,16 @@
         <v>850000000</v>
       </c>
       <c r="D258" s="2">
-        <v>309489160</v>
+        <v>259809160</v>
       </c>
       <c r="E258" s="2">
         <v>74800000</v>
       </c>
       <c r="F258" s="2">
-        <v>384289160</v>
+        <v>334609160</v>
       </c>
       <c r="G258" s="2">
-        <v>465710840</v>
+        <v>515390840</v>
       </c>
       <c r="H258" s="2">
         <v>0</v>
@@ -8645,10 +8515,10 @@
         <v>13675500</v>
       </c>
       <c r="D280" s="2">
-        <v>0</v>
+        <v>13582000</v>
       </c>
       <c r="E280" s="2">
-        <v>13582000</v>
+        <v>0</v>
       </c>
       <c r="F280" s="2">
         <v>13582000</v>
@@ -8905,16 +8775,16 @@
         <v>45434097707</v>
       </c>
       <c r="D290" s="2">
-        <v>6724579980</v>
+        <v>6688481980</v>
       </c>
       <c r="E290" s="2">
-        <v>5347646446</v>
+        <v>5334064446</v>
       </c>
       <c r="F290" s="2">
-        <v>12072226426</v>
+        <v>12022546426</v>
       </c>
       <c r="G290" s="2">
-        <v>33361871281</v>
+        <v>33411551281</v>
       </c>
       <c r="H290" s="2">
         <v>0</v>
@@ -8983,16 +8853,16 @@
         <v>488774000</v>
       </c>
       <c r="D293" s="2">
-        <v>472749437</v>
+        <v>0</v>
       </c>
       <c r="E293" s="2">
         <v>0</v>
       </c>
       <c r="F293" s="2">
-        <v>472749437</v>
+        <v>0</v>
       </c>
       <c r="G293" s="2">
-        <v>16024563</v>
+        <v>488774000</v>
       </c>
       <c r="H293" s="2">
         <v>0</v>
@@ -9009,16 +8879,16 @@
         <v>498000000</v>
       </c>
       <c r="D294" s="2">
-        <v>487985800</v>
+        <v>0</v>
       </c>
       <c r="E294" s="2">
         <v>0</v>
       </c>
       <c r="F294" s="2">
-        <v>487985800</v>
+        <v>0</v>
       </c>
       <c r="G294" s="2">
-        <v>10014200</v>
+        <v>498000000</v>
       </c>
       <c r="H294" s="2">
         <v>0</v>
@@ -9087,10 +8957,10 @@
         <v>1222108000</v>
       </c>
       <c r="D297" s="2">
-        <v>58082710</v>
+        <v>107724690</v>
       </c>
       <c r="E297" s="2">
-        <v>49641980</v>
+        <v>0</v>
       </c>
       <c r="F297" s="2">
         <v>107724690</v>
@@ -9113,10 +8983,10 @@
         <v>534300000</v>
       </c>
       <c r="D298" s="2">
-        <v>31132500</v>
+        <v>77914500</v>
       </c>
       <c r="E298" s="2">
-        <v>143332828</v>
+        <v>96550828</v>
       </c>
       <c r="F298" s="2">
         <v>174465328</v>
@@ -9217,16 +9087,16 @@
         <v>1882400000</v>
       </c>
       <c r="D302" s="2">
-        <v>1658705000</v>
+        <v>210764000</v>
       </c>
       <c r="E302" s="2">
         <v>0</v>
       </c>
       <c r="F302" s="2">
-        <v>1658705000</v>
+        <v>210764000</v>
       </c>
       <c r="G302" s="2">
-        <v>223695000</v>
+        <v>1671636000</v>
       </c>
       <c r="H302" s="2">
         <v>0</v>
@@ -9425,16 +9295,16 @@
         <v>82504500</v>
       </c>
       <c r="D310" s="2">
-        <v>36154000</v>
+        <v>6850000</v>
       </c>
       <c r="E310" s="2">
         <v>13891000</v>
       </c>
       <c r="F310" s="2">
-        <v>50045000</v>
+        <v>20741000</v>
       </c>
       <c r="G310" s="2">
-        <v>32459500</v>
+        <v>61763500</v>
       </c>
       <c r="H310" s="2">
         <v>27501500</v>
@@ -9477,16 +9347,16 @@
         <v>385800000</v>
       </c>
       <c r="D312" s="2">
-        <v>0</v>
+        <v>37890000</v>
       </c>
       <c r="E312" s="2">
-        <v>37922635</v>
+        <v>3485000</v>
       </c>
       <c r="F312" s="2">
-        <v>37922635</v>
+        <v>41375000</v>
       </c>
       <c r="G312" s="2">
-        <v>347877365</v>
+        <v>344425000</v>
       </c>
       <c r="H312" s="2">
         <v>128600000</v>
@@ -9506,13 +9376,13 @@
         <v>0</v>
       </c>
       <c r="E313" s="2">
-        <v>39065500</v>
+        <v>38303000</v>
       </c>
       <c r="F313" s="2">
-        <v>39065500</v>
+        <v>38303000</v>
       </c>
       <c r="G313" s="2">
-        <v>133434500</v>
+        <v>134197000</v>
       </c>
       <c r="H313" s="2">
         <v>57500000</v>
@@ -9558,13 +9428,13 @@
         <v>0</v>
       </c>
       <c r="E315" s="2">
-        <v>970917428</v>
+        <v>970906178</v>
       </c>
       <c r="F315" s="2">
-        <v>970917428</v>
+        <v>970906178</v>
       </c>
       <c r="G315" s="2">
-        <v>6082874837</v>
+        <v>6082886087</v>
       </c>
       <c r="H315" s="2">
         <v>0</v>
@@ -9763,16 +9633,16 @@
         <v>30454436960</v>
       </c>
       <c r="D323" s="2">
-        <v>4533800168</v>
+        <v>2230133911</v>
       </c>
       <c r="E323" s="2">
-        <v>3255135775</v>
+        <v>3123500410</v>
       </c>
       <c r="F323" s="2">
-        <v>7788935943</v>
+        <v>5353634321</v>
       </c>
       <c r="G323" s="2">
-        <v>22665501017</v>
+        <v>25100802639</v>
       </c>
       <c r="H323" s="2">
         <v>260139500</v>
@@ -9809,10 +9679,10 @@
         <v>11</v>
       </c>
       <c r="B325" s="2">
-        <v>2948978291</v>
+        <v>2948978000</v>
       </c>
       <c r="C325" s="2">
-        <v>2948978291</v>
+        <v>2948978000</v>
       </c>
       <c r="D325" s="2">
         <v>2788546174</v>
@@ -9824,7 +9694,7 @@
         <v>2837419124</v>
       </c>
       <c r="G325" s="2">
-        <v>111559167</v>
+        <v>111558876</v>
       </c>
       <c r="H325" s="2">
         <v>0</v>
@@ -9835,10 +9705,10 @@
         <v>12</v>
       </c>
       <c r="B326" s="2">
-        <v>447807006</v>
+        <v>223903500</v>
       </c>
       <c r="C326" s="2">
-        <v>447807006</v>
+        <v>223903500</v>
       </c>
       <c r="D326" s="2">
         <v>0</v>
@@ -9850,7 +9720,7 @@
         <v>0</v>
       </c>
       <c r="G326" s="2">
-        <v>447807006</v>
+        <v>223903500</v>
       </c>
       <c r="H326" s="2">
         <v>0</v>
@@ -9861,10 +9731,10 @@
         <v>48</v>
       </c>
       <c r="B327" s="2">
-        <v>1880742104</v>
+        <v>1880742000</v>
       </c>
       <c r="C327" s="2">
-        <v>1880742104</v>
+        <v>1880742000</v>
       </c>
       <c r="D327" s="2">
         <v>1395485871</v>
@@ -9876,7 +9746,7 @@
         <v>1395485871</v>
       </c>
       <c r="G327" s="2">
-        <v>485256233</v>
+        <v>485256129</v>
       </c>
       <c r="H327" s="2">
         <v>0</v>
@@ -9887,10 +9757,10 @@
         <v>13</v>
       </c>
       <c r="B328" s="2">
-        <v>213056448</v>
+        <v>106528224</v>
       </c>
       <c r="C328" s="2">
-        <v>213056448</v>
+        <v>106528224</v>
       </c>
       <c r="D328" s="2">
         <v>33060600</v>
@@ -9902,7 +9772,7 @@
         <v>33060600</v>
       </c>
       <c r="G328" s="2">
-        <v>179995848</v>
+        <v>73467624</v>
       </c>
       <c r="H328" s="2">
         <v>0</v>
@@ -9913,10 +9783,10 @@
         <v>14</v>
       </c>
       <c r="B329" s="2">
-        <v>687000000</v>
+        <v>428000000</v>
       </c>
       <c r="C329" s="2">
-        <v>687000000</v>
+        <v>428000000</v>
       </c>
       <c r="D329" s="2">
         <v>0</v>
@@ -9928,7 +9798,7 @@
         <v>141841100</v>
       </c>
       <c r="G329" s="2">
-        <v>545158900</v>
+        <v>286158900</v>
       </c>
       <c r="H329" s="2">
         <v>0</v>
@@ -9939,10 +9809,10 @@
         <v>15</v>
       </c>
       <c r="B330" s="2">
-        <v>2791999194</v>
+        <v>1395999500</v>
       </c>
       <c r="C330" s="2">
-        <v>2791999194</v>
+        <v>1395999500</v>
       </c>
       <c r="D330" s="2">
         <v>562101045</v>
@@ -9954,7 +9824,7 @@
         <v>698858425</v>
       </c>
       <c r="G330" s="2">
-        <v>2093140769</v>
+        <v>697141075</v>
       </c>
       <c r="H330" s="2">
         <v>0</v>
@@ -9965,22 +9835,22 @@
         <v>16</v>
       </c>
       <c r="B331" s="2">
-        <v>1660344000</v>
+        <v>830172000</v>
       </c>
       <c r="C331" s="2">
-        <v>1660344000</v>
+        <v>830172000</v>
       </c>
       <c r="D331" s="2">
-        <v>370874500</v>
+        <v>377887300</v>
       </c>
       <c r="E331" s="2">
-        <v>291015788</v>
+        <v>284002988</v>
       </c>
       <c r="F331" s="2">
         <v>661890288</v>
       </c>
       <c r="G331" s="2">
-        <v>998453712</v>
+        <v>168281712</v>
       </c>
       <c r="H331" s="2">
         <v>0</v>
@@ -9991,10 +9861,10 @@
         <v>49</v>
       </c>
       <c r="B332" s="2">
-        <v>327155000</v>
+        <v>163577500</v>
       </c>
       <c r="C332" s="2">
-        <v>327155000</v>
+        <v>163577500</v>
       </c>
       <c r="D332" s="2">
         <v>67275600</v>
@@ -10006,7 +9876,7 @@
         <v>67275600</v>
       </c>
       <c r="G332" s="2">
-        <v>259879400</v>
+        <v>96301900</v>
       </c>
       <c r="H332" s="2">
         <v>0</v>
@@ -10017,10 +9887,10 @@
         <v>50</v>
       </c>
       <c r="B333" s="2">
-        <v>831375509</v>
+        <v>415688000</v>
       </c>
       <c r="C333" s="2">
-        <v>831375509</v>
+        <v>415688000</v>
       </c>
       <c r="D333" s="2">
         <v>345662595</v>
@@ -10032,7 +9902,7 @@
         <v>345662595</v>
       </c>
       <c r="G333" s="2">
-        <v>485712914</v>
+        <v>70025405</v>
       </c>
       <c r="H333" s="2">
         <v>0</v>
@@ -10069,10 +9939,10 @@
         <v>77</v>
       </c>
       <c r="B335" s="2">
-        <v>600000000</v>
+        <v>300000000</v>
       </c>
       <c r="C335" s="2">
-        <v>600000000</v>
+        <v>300000000</v>
       </c>
       <c r="D335" s="2">
         <v>0</v>
@@ -10084,7 +9954,7 @@
         <v>0</v>
       </c>
       <c r="G335" s="2">
-        <v>600000000</v>
+        <v>300000000</v>
       </c>
       <c r="H335" s="2">
         <v>0</v>
@@ -10095,10 +9965,10 @@
         <v>56</v>
       </c>
       <c r="B336" s="2">
-        <v>1000000000</v>
+        <v>500000000</v>
       </c>
       <c r="C336" s="2">
-        <v>1000000000</v>
+        <v>500000000</v>
       </c>
       <c r="D336" s="2">
         <v>0</v>
@@ -10110,7 +9980,7 @@
         <v>0</v>
       </c>
       <c r="G336" s="2">
-        <v>1000000000</v>
+        <v>500000000</v>
       </c>
       <c r="H336" s="2">
         <v>0</v>
@@ -10121,10 +9991,10 @@
         <v>22</v>
       </c>
       <c r="B337" s="2">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="C337" s="2">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="D337" s="2">
         <v>0</v>
@@ -10136,10 +10006,10 @@
         <v>0</v>
       </c>
       <c r="G337" s="2">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="H337" s="2">
-        <v>50000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.45">
@@ -10147,22 +10017,22 @@
         <v>57</v>
       </c>
       <c r="B338" s="2">
-        <v>141550000</v>
+        <v>70775000</v>
       </c>
       <c r="C338" s="2">
-        <v>141550000</v>
+        <v>70775000</v>
       </c>
       <c r="D338" s="2">
-        <v>0</v>
+        <v>24082000</v>
       </c>
       <c r="E338" s="2">
-        <v>28052000</v>
+        <v>3970000</v>
       </c>
       <c r="F338" s="2">
         <v>28052000</v>
       </c>
       <c r="G338" s="2">
-        <v>113498000</v>
+        <v>42723000</v>
       </c>
       <c r="H338" s="2">
         <v>0</v>
@@ -10173,10 +10043,10 @@
         <v>58</v>
       </c>
       <c r="B339" s="2">
-        <v>2911760000</v>
+        <v>880440000</v>
       </c>
       <c r="C339" s="2">
-        <v>2911760000</v>
+        <v>880440000</v>
       </c>
       <c r="D339" s="2">
         <v>581770</v>
@@ -10188,7 +10058,7 @@
         <v>412137110</v>
       </c>
       <c r="G339" s="2">
-        <v>2499622890</v>
+        <v>468302890</v>
       </c>
       <c r="H339" s="2">
         <v>0</v>
@@ -10199,10 +10069,10 @@
         <v>25</v>
       </c>
       <c r="B340" s="2">
-        <v>180000000</v>
+        <v>77500000</v>
       </c>
       <c r="C340" s="2">
-        <v>135000000</v>
+        <v>77500000</v>
       </c>
       <c r="D340" s="2">
         <v>23940000</v>
@@ -10214,10 +10084,10 @@
         <v>37404500</v>
       </c>
       <c r="G340" s="2">
-        <v>97595500</v>
+        <v>40095500</v>
       </c>
       <c r="H340" s="2">
-        <v>45000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.45">
@@ -10225,25 +10095,25 @@
         <v>26</v>
       </c>
       <c r="B341" s="2">
-        <v>761439700</v>
+        <v>154250000</v>
       </c>
       <c r="C341" s="2">
-        <v>571079775</v>
+        <v>154250000</v>
       </c>
       <c r="D341" s="2">
-        <v>21171800</v>
+        <v>21601800</v>
       </c>
       <c r="E341" s="2">
-        <v>60451850</v>
+        <v>60021850</v>
       </c>
       <c r="F341" s="2">
         <v>81623650</v>
       </c>
       <c r="G341" s="2">
-        <v>489456125</v>
+        <v>72626350</v>
       </c>
       <c r="H341" s="2">
-        <v>190359925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.45">
@@ -10251,10 +10121,10 @@
         <v>27</v>
       </c>
       <c r="B342" s="2">
-        <v>99900000</v>
+        <v>27750000</v>
       </c>
       <c r="C342" s="2">
-        <v>99900000</v>
+        <v>27750000</v>
       </c>
       <c r="D342" s="2">
         <v>0</v>
@@ -10266,7 +10136,7 @@
         <v>18500000</v>
       </c>
       <c r="G342" s="2">
-        <v>81400000</v>
+        <v>9250000</v>
       </c>
       <c r="H342" s="2">
         <v>0</v>
@@ -10277,10 +10147,10 @@
         <v>28</v>
       </c>
       <c r="B343" s="2">
-        <v>616500000</v>
+        <v>286250000</v>
       </c>
       <c r="C343" s="2">
-        <v>462375000</v>
+        <v>286250000</v>
       </c>
       <c r="D343" s="2">
         <v>16504900</v>
@@ -10292,10 +10162,10 @@
         <v>19527670</v>
       </c>
       <c r="G343" s="2">
-        <v>442847330</v>
+        <v>266722330</v>
       </c>
       <c r="H343" s="2">
-        <v>154125000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.45">
@@ -10303,10 +10173,10 @@
         <v>30</v>
       </c>
       <c r="B344" s="2">
-        <v>347400000</v>
+        <v>108000000</v>
       </c>
       <c r="C344" s="2">
-        <v>260550000</v>
+        <v>108000000</v>
       </c>
       <c r="D344" s="2">
         <v>0</v>
@@ -10318,10 +10188,10 @@
         <v>52841500</v>
       </c>
       <c r="G344" s="2">
-        <v>207708500</v>
+        <v>55158500</v>
       </c>
       <c r="H344" s="2">
-        <v>86850000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.45">
@@ -10329,10 +10199,10 @@
         <v>79</v>
       </c>
       <c r="B345" s="2">
-        <v>6000000</v>
+        <v>1500000</v>
       </c>
       <c r="C345" s="2">
-        <v>6000000</v>
+        <v>1500000</v>
       </c>
       <c r="D345" s="2">
         <v>384315</v>
@@ -10344,7 +10214,7 @@
         <v>384315</v>
       </c>
       <c r="G345" s="2">
-        <v>5615685</v>
+        <v>1115685</v>
       </c>
       <c r="H345" s="2">
         <v>0</v>
@@ -10355,10 +10225,10 @@
         <v>31</v>
       </c>
       <c r="B346" s="2">
-        <v>56157000</v>
+        <v>16379250</v>
       </c>
       <c r="C346" s="2">
-        <v>56157000</v>
+        <v>16379250</v>
       </c>
       <c r="D346" s="2">
         <v>0</v>
@@ -10370,7 +10240,7 @@
         <v>15178108</v>
       </c>
       <c r="G346" s="2">
-        <v>40978892</v>
+        <v>1201142</v>
       </c>
       <c r="H346" s="2">
         <v>0</v>
@@ -10589,25 +10459,25 @@
         <v>84</v>
       </c>
       <c r="B355" s="2">
-        <v>57953424224</v>
+        <v>50160692946</v>
       </c>
       <c r="C355" s="2">
-        <v>57427089299</v>
+        <v>50160692946</v>
       </c>
       <c r="D355" s="2">
-        <v>19274961725</v>
+        <v>19306486525</v>
       </c>
       <c r="E355" s="2">
-        <v>6048123791</v>
+        <v>6016598991</v>
       </c>
       <c r="F355" s="2">
         <v>25323085516</v>
       </c>
       <c r="G355" s="2">
-        <v>32104003783</v>
+        <v>24837607430</v>
       </c>
       <c r="H355" s="2">
-        <v>526334925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.45">
@@ -10615,10 +10485,10 @@
         <v>8</v>
       </c>
       <c r="B356" s="2">
-        <v>3291324000</v>
+        <v>1645662000</v>
       </c>
       <c r="C356" s="2">
-        <v>3291324000</v>
+        <v>1645662000</v>
       </c>
       <c r="D356" s="2">
         <v>0</v>
@@ -10630,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="G356" s="2">
-        <v>3291324000</v>
+        <v>1645662000</v>
       </c>
       <c r="H356" s="2">
         <v>0</v>
@@ -10641,10 +10511,10 @@
         <v>12</v>
       </c>
       <c r="B357" s="2">
-        <v>1891862000</v>
+        <v>945931000</v>
       </c>
       <c r="C357" s="2">
-        <v>1891862000</v>
+        <v>945931000</v>
       </c>
       <c r="D357" s="2">
         <v>0</v>
@@ -10656,7 +10526,7 @@
         <v>0</v>
       </c>
       <c r="G357" s="2">
-        <v>1891862000</v>
+        <v>945931000</v>
       </c>
       <c r="H357" s="2">
         <v>0</v>
@@ -10667,22 +10537,22 @@
         <v>48</v>
       </c>
       <c r="B358" s="2">
-        <v>2244807000</v>
+        <v>1122403500</v>
       </c>
       <c r="C358" s="2">
-        <v>2244807000</v>
+        <v>1122403500</v>
       </c>
       <c r="D358" s="2">
-        <v>137918578</v>
+        <v>134933637</v>
       </c>
       <c r="E358" s="2">
         <v>137784161</v>
       </c>
       <c r="F358" s="2">
-        <v>275702739</v>
+        <v>272717798</v>
       </c>
       <c r="G358" s="2">
-        <v>1969104261</v>
+        <v>849685702</v>
       </c>
       <c r="H358" s="2">
         <v>0</v>
@@ -10693,10 +10563,10 @@
         <v>13</v>
       </c>
       <c r="B359" s="2">
-        <v>149777000</v>
+        <v>74888500</v>
       </c>
       <c r="C359" s="2">
-        <v>149777000</v>
+        <v>74888500</v>
       </c>
       <c r="D359" s="2">
         <v>3421001</v>
@@ -10708,7 +10578,7 @@
         <v>3421001</v>
       </c>
       <c r="G359" s="2">
-        <v>146355999</v>
+        <v>71467499</v>
       </c>
       <c r="H359" s="2">
         <v>0</v>
@@ -10719,10 +10589,10 @@
         <v>14</v>
       </c>
       <c r="B360" s="2">
-        <v>33248000</v>
+        <v>16624000</v>
       </c>
       <c r="C360" s="2">
-        <v>33248000</v>
+        <v>16624000</v>
       </c>
       <c r="D360" s="2">
         <v>0</v>
@@ -10734,7 +10604,7 @@
         <v>16623760</v>
       </c>
       <c r="G360" s="2">
-        <v>16624240</v>
+        <v>240</v>
       </c>
       <c r="H360" s="2">
         <v>0</v>
@@ -10745,10 +10615,10 @@
         <v>15</v>
       </c>
       <c r="B361" s="2">
-        <v>1044737000</v>
+        <v>522368500</v>
       </c>
       <c r="C361" s="2">
-        <v>1044737000</v>
+        <v>522368500</v>
       </c>
       <c r="D361" s="2">
         <v>81692227</v>
@@ -10760,7 +10630,7 @@
         <v>193507670</v>
       </c>
       <c r="G361" s="2">
-        <v>851229330</v>
+        <v>328860830</v>
       </c>
       <c r="H361" s="2">
         <v>0</v>
@@ -10771,10 +10641,10 @@
         <v>16</v>
       </c>
       <c r="B362" s="2">
-        <v>1400000000</v>
+        <v>700000000</v>
       </c>
       <c r="C362" s="2">
-        <v>1400000000</v>
+        <v>700000000</v>
       </c>
       <c r="D362" s="2">
         <v>20715500</v>
@@ -10786,7 +10656,7 @@
         <v>172728050</v>
       </c>
       <c r="G362" s="2">
-        <v>1227271950</v>
+        <v>527271950</v>
       </c>
       <c r="H362" s="2">
         <v>0</v>
@@ -10797,10 +10667,10 @@
         <v>49</v>
       </c>
       <c r="B363" s="2">
-        <v>290550000</v>
+        <v>145275000</v>
       </c>
       <c r="C363" s="2">
-        <v>290550000</v>
+        <v>145275000</v>
       </c>
       <c r="D363" s="2">
         <v>0</v>
@@ -10812,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="G363" s="2">
-        <v>290550000</v>
+        <v>145275000</v>
       </c>
       <c r="H363" s="2">
         <v>0</v>
@@ -10823,10 +10693,10 @@
         <v>50</v>
       </c>
       <c r="B364" s="2">
-        <v>306429000</v>
+        <v>153214500</v>
       </c>
       <c r="C364" s="2">
-        <v>306429000</v>
+        <v>153214500</v>
       </c>
       <c r="D364" s="2">
         <v>0</v>
@@ -10838,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G364" s="2">
-        <v>306429000</v>
+        <v>153214500</v>
       </c>
       <c r="H364" s="2">
         <v>0</v>
@@ -10849,10 +10719,10 @@
         <v>52</v>
       </c>
       <c r="B365" s="2">
-        <v>470200000</v>
+        <v>235100000</v>
       </c>
       <c r="C365" s="2">
-        <v>470200000</v>
+        <v>235100000</v>
       </c>
       <c r="D365" s="2">
         <v>0</v>
@@ -10864,7 +10734,7 @@
         <v>3229600</v>
       </c>
       <c r="G365" s="2">
-        <v>466970400</v>
+        <v>231870400</v>
       </c>
       <c r="H365" s="2">
         <v>0</v>
@@ -10875,10 +10745,10 @@
         <v>56</v>
       </c>
       <c r="B366" s="2">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="C366" s="2">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="D366" s="2">
         <v>0</v>
@@ -10890,7 +10760,7 @@
         <v>0</v>
       </c>
       <c r="G366" s="2">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="H366" s="2">
         <v>0</v>
@@ -10901,10 +10771,10 @@
         <v>22</v>
       </c>
       <c r="B367" s="2">
-        <v>110000000</v>
+        <v>100000000</v>
       </c>
       <c r="C367" s="2">
-        <v>82500000</v>
+        <v>100000000</v>
       </c>
       <c r="D367" s="2">
         <v>0</v>
@@ -10916,10 +10786,10 @@
         <v>0</v>
       </c>
       <c r="G367" s="2">
-        <v>82500000</v>
+        <v>100000000</v>
       </c>
       <c r="H367" s="2">
-        <v>27500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.45">
@@ -10927,10 +10797,10 @@
         <v>57</v>
       </c>
       <c r="B368" s="2">
-        <v>99980000</v>
+        <v>63030000</v>
       </c>
       <c r="C368" s="2">
-        <v>99980000</v>
+        <v>63030000</v>
       </c>
       <c r="D368" s="2">
         <v>19823200</v>
@@ -10942,7 +10812,7 @@
         <v>19823200</v>
       </c>
       <c r="G368" s="2">
-        <v>80156800</v>
+        <v>43206800</v>
       </c>
       <c r="H368" s="2">
         <v>0</v>
@@ -10953,10 +10823,10 @@
         <v>58</v>
       </c>
       <c r="B369" s="2">
-        <v>411080000</v>
+        <v>90000000</v>
       </c>
       <c r="C369" s="2">
-        <v>411080000</v>
+        <v>90000000</v>
       </c>
       <c r="D369" s="2">
         <v>1639740</v>
@@ -10968,7 +10838,7 @@
         <v>72536444</v>
       </c>
       <c r="G369" s="2">
-        <v>338543556</v>
+        <v>17463556</v>
       </c>
       <c r="H369" s="2">
         <v>0</v>
@@ -10979,10 +10849,10 @@
         <v>25</v>
       </c>
       <c r="B370" s="2">
-        <v>160000000</v>
+        <v>64000000</v>
       </c>
       <c r="C370" s="2">
-        <v>120000000</v>
+        <v>64000000</v>
       </c>
       <c r="D370" s="2">
         <v>6960000</v>
@@ -10994,10 +10864,10 @@
         <v>20447000</v>
       </c>
       <c r="G370" s="2">
-        <v>99553000</v>
+        <v>43553000</v>
       </c>
       <c r="H370" s="2">
-        <v>40000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.45">
@@ -11005,10 +10875,10 @@
         <v>26</v>
       </c>
       <c r="B371" s="2">
-        <v>400000000</v>
+        <v>300400000</v>
       </c>
       <c r="C371" s="2">
-        <v>300000000</v>
+        <v>300400000</v>
       </c>
       <c r="D371" s="2">
         <v>27274000</v>
@@ -11020,10 +10890,10 @@
         <v>105482462</v>
       </c>
       <c r="G371" s="2">
-        <v>194517538</v>
+        <v>194917538</v>
       </c>
       <c r="H371" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.45">
@@ -11031,10 +10901,10 @@
         <v>27</v>
       </c>
       <c r="B372" s="2">
-        <v>66000000</v>
+        <v>16500000</v>
       </c>
       <c r="C372" s="2">
-        <v>66000000</v>
+        <v>16500000</v>
       </c>
       <c r="D372" s="2">
         <v>0</v>
@@ -11046,7 +10916,7 @@
         <v>11000000</v>
       </c>
       <c r="G372" s="2">
-        <v>55000000</v>
+        <v>5500000</v>
       </c>
       <c r="H372" s="2">
         <v>0</v>
@@ -11057,10 +10927,10 @@
         <v>28</v>
       </c>
       <c r="B373" s="2">
-        <v>90000000</v>
+        <v>35000000</v>
       </c>
       <c r="C373" s="2">
-        <v>67500000</v>
+        <v>35000000</v>
       </c>
       <c r="D373" s="2">
         <v>0</v>
@@ -11072,10 +10942,10 @@
         <v>4415000</v>
       </c>
       <c r="G373" s="2">
-        <v>63085000</v>
+        <v>30585000</v>
       </c>
       <c r="H373" s="2">
-        <v>22500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.45">
@@ -11083,10 +10953,10 @@
         <v>30</v>
       </c>
       <c r="B374" s="2">
-        <v>170700000</v>
+        <v>42675000</v>
       </c>
       <c r="C374" s="2">
-        <v>128025000</v>
+        <v>42675000</v>
       </c>
       <c r="D374" s="2">
         <v>0</v>
@@ -11098,10 +10968,10 @@
         <v>39560000</v>
       </c>
       <c r="G374" s="2">
-        <v>88465000</v>
+        <v>3115000</v>
       </c>
       <c r="H374" s="2">
-        <v>42675000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.45">
@@ -11109,10 +10979,10 @@
         <v>31</v>
       </c>
       <c r="B375" s="2">
-        <v>24000000</v>
+        <v>9000000</v>
       </c>
       <c r="C375" s="2">
-        <v>24000000</v>
+        <v>9000000</v>
       </c>
       <c r="D375" s="2">
         <v>0</v>
@@ -11124,7 +10994,7 @@
         <v>6736950</v>
       </c>
       <c r="G375" s="2">
-        <v>17263050</v>
+        <v>2263050</v>
       </c>
       <c r="H375" s="2">
         <v>0</v>
@@ -11369,25 +11239,25 @@
         <v>85</v>
       </c>
       <c r="B385" s="2">
-        <v>23968090591</v>
+        <v>17495468591</v>
       </c>
       <c r="C385" s="2">
-        <v>23735415591</v>
+        <v>17495468591</v>
       </c>
       <c r="D385" s="2">
-        <v>299444246</v>
+        <v>296459305</v>
       </c>
       <c r="E385" s="2">
         <v>2381235336</v>
       </c>
       <c r="F385" s="2">
-        <v>2680679582</v>
+        <v>2677694641</v>
       </c>
       <c r="G385" s="2">
-        <v>21054736009</v>
+        <v>14817773950</v>
       </c>
       <c r="H385" s="2">
-        <v>232675000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.45">
@@ -11395,10 +11265,10 @@
         <v>8</v>
       </c>
       <c r="B386" s="2">
-        <v>3435027000</v>
+        <v>1717513500</v>
       </c>
       <c r="C386" s="2">
-        <v>3435027000</v>
+        <v>1717513500</v>
       </c>
       <c r="D386" s="2">
         <v>0</v>
@@ -11410,7 +11280,7 @@
         <v>0</v>
       </c>
       <c r="G386" s="2">
-        <v>3435027000</v>
+        <v>1717513500</v>
       </c>
       <c r="H386" s="2">
         <v>0</v>
@@ -11447,10 +11317,10 @@
         <v>12</v>
       </c>
       <c r="B388" s="2">
-        <v>467372000</v>
+        <v>233686000</v>
       </c>
       <c r="C388" s="2">
-        <v>467372000</v>
+        <v>233686000</v>
       </c>
       <c r="D388" s="2">
         <v>0</v>
@@ -11462,7 +11332,7 @@
         <v>0</v>
       </c>
       <c r="G388" s="2">
-        <v>467372000</v>
+        <v>233686000</v>
       </c>
       <c r="H388" s="2">
         <v>0</v>
@@ -11473,10 +11343,10 @@
         <v>48</v>
       </c>
       <c r="B389" s="2">
-        <v>890568000</v>
+        <v>445284000</v>
       </c>
       <c r="C389" s="2">
-        <v>890568000</v>
+        <v>445284000</v>
       </c>
       <c r="D389" s="2">
         <v>398086520</v>
@@ -11488,7 +11358,7 @@
         <v>398086520</v>
       </c>
       <c r="G389" s="2">
-        <v>492481480</v>
+        <v>47197480</v>
       </c>
       <c r="H389" s="2">
         <v>0</v>
@@ -11499,10 +11369,10 @@
         <v>13</v>
       </c>
       <c r="B390" s="2">
-        <v>157212000</v>
+        <v>78606000</v>
       </c>
       <c r="C390" s="2">
-        <v>157212000</v>
+        <v>78606000</v>
       </c>
       <c r="D390" s="2">
         <v>49855940</v>
@@ -11514,7 +11384,7 @@
         <v>49855940</v>
       </c>
       <c r="G390" s="2">
-        <v>107356060</v>
+        <v>28750060</v>
       </c>
       <c r="H390" s="2">
         <v>0</v>
@@ -11525,10 +11395,10 @@
         <v>14</v>
       </c>
       <c r="B391" s="2">
-        <v>450000000</v>
+        <v>225000000</v>
       </c>
       <c r="C391" s="2">
-        <v>450000000</v>
+        <v>225000000</v>
       </c>
       <c r="D391" s="2">
         <v>0</v>
@@ -11540,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="G391" s="2">
-        <v>450000000</v>
+        <v>225000000</v>
       </c>
       <c r="H391" s="2">
         <v>0</v>
@@ -11551,10 +11421,10 @@
         <v>15</v>
       </c>
       <c r="B392" s="2">
-        <v>500000000</v>
+        <v>250000000</v>
       </c>
       <c r="C392" s="2">
-        <v>500000000</v>
+        <v>250000000</v>
       </c>
       <c r="D392" s="2">
         <v>0</v>
@@ -11566,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="G392" s="2">
-        <v>500000000</v>
+        <v>250000000</v>
       </c>
       <c r="H392" s="2">
         <v>0</v>
@@ -11577,22 +11447,22 @@
         <v>16</v>
       </c>
       <c r="B393" s="2">
-        <v>690000000</v>
+        <v>345000000</v>
       </c>
       <c r="C393" s="2">
-        <v>690000000</v>
+        <v>345000000</v>
       </c>
       <c r="D393" s="2">
-        <v>103894080</v>
+        <v>202834780</v>
       </c>
       <c r="E393" s="2">
-        <v>98940700</v>
+        <v>0</v>
       </c>
       <c r="F393" s="2">
         <v>202834780</v>
       </c>
       <c r="G393" s="2">
-        <v>487165220</v>
+        <v>142165220</v>
       </c>
       <c r="H393" s="2">
         <v>0</v>
@@ -11603,10 +11473,10 @@
         <v>49</v>
       </c>
       <c r="B394" s="2">
-        <v>198700000</v>
+        <v>99350000</v>
       </c>
       <c r="C394" s="2">
-        <v>198700000</v>
+        <v>99350000</v>
       </c>
       <c r="D394" s="2">
         <v>91627175</v>
@@ -11618,7 +11488,7 @@
         <v>91627175</v>
       </c>
       <c r="G394" s="2">
-        <v>107072825</v>
+        <v>7722825</v>
       </c>
       <c r="H394" s="2">
         <v>0</v>
@@ -11629,10 +11499,10 @@
         <v>50</v>
       </c>
       <c r="B395" s="2">
-        <v>455131000</v>
+        <v>227565500</v>
       </c>
       <c r="C395" s="2">
-        <v>455131000</v>
+        <v>227565500</v>
       </c>
       <c r="D395" s="2">
         <v>0</v>
@@ -11644,7 +11514,7 @@
         <v>0</v>
       </c>
       <c r="G395" s="2">
-        <v>455131000</v>
+        <v>227565500</v>
       </c>
       <c r="H395" s="2">
         <v>0</v>
@@ -11655,10 +11525,10 @@
         <v>51</v>
       </c>
       <c r="B396" s="2">
-        <v>50000000</v>
+        <v>25000000</v>
       </c>
       <c r="C396" s="2">
-        <v>50000000</v>
+        <v>25000000</v>
       </c>
       <c r="D396" s="2">
         <v>0</v>
@@ -11670,7 +11540,7 @@
         <v>0</v>
       </c>
       <c r="G396" s="2">
-        <v>50000000</v>
+        <v>25000000</v>
       </c>
       <c r="H396" s="2">
         <v>0</v>
@@ -11681,10 +11551,10 @@
         <v>52</v>
       </c>
       <c r="B397" s="2">
-        <v>1443560000</v>
+        <v>721780000</v>
       </c>
       <c r="C397" s="2">
-        <v>1443560000</v>
+        <v>721780000</v>
       </c>
       <c r="D397" s="2">
         <v>0</v>
@@ -11696,7 +11566,7 @@
         <v>0</v>
       </c>
       <c r="G397" s="2">
-        <v>1443560000</v>
+        <v>721780000</v>
       </c>
       <c r="H397" s="2">
         <v>0</v>
@@ -11707,10 +11577,10 @@
         <v>53</v>
       </c>
       <c r="B398" s="2">
-        <v>500000000</v>
+        <v>250000000</v>
       </c>
       <c r="C398" s="2">
-        <v>500000000</v>
+        <v>250000000</v>
       </c>
       <c r="D398" s="2">
         <v>0</v>
@@ -11722,7 +11592,7 @@
         <v>0</v>
       </c>
       <c r="G398" s="2">
-        <v>500000000</v>
+        <v>250000000</v>
       </c>
       <c r="H398" s="2">
         <v>0</v>
@@ -11733,10 +11603,10 @@
         <v>56</v>
       </c>
       <c r="B399" s="2">
-        <v>250000000</v>
+        <v>125000000</v>
       </c>
       <c r="C399" s="2">
-        <v>250000000</v>
+        <v>125000000</v>
       </c>
       <c r="D399" s="2">
         <v>0</v>
@@ -11748,7 +11618,7 @@
         <v>0</v>
       </c>
       <c r="G399" s="2">
-        <v>250000000</v>
+        <v>125000000</v>
       </c>
       <c r="H399" s="2">
         <v>0</v>
@@ -11759,10 +11629,10 @@
         <v>22</v>
       </c>
       <c r="B400" s="2">
-        <v>250000000</v>
+        <v>125000000</v>
       </c>
       <c r="C400" s="2">
-        <v>187500000</v>
+        <v>125000000</v>
       </c>
       <c r="D400" s="2">
         <v>0</v>
@@ -11774,10 +11644,10 @@
         <v>0</v>
       </c>
       <c r="G400" s="2">
-        <v>187500000</v>
+        <v>125000000</v>
       </c>
       <c r="H400" s="2">
-        <v>62500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.45">
@@ -11785,10 +11655,10 @@
         <v>57</v>
       </c>
       <c r="B401" s="2">
-        <v>316800000</v>
+        <v>158400000</v>
       </c>
       <c r="C401" s="2">
-        <v>316800000</v>
+        <v>158400000</v>
       </c>
       <c r="D401" s="2">
         <v>52208150</v>
@@ -11800,7 +11670,7 @@
         <v>52208150</v>
       </c>
       <c r="G401" s="2">
-        <v>264591850</v>
+        <v>106191850</v>
       </c>
       <c r="H401" s="2">
         <v>0</v>
@@ -11811,10 +11681,10 @@
         <v>58</v>
       </c>
       <c r="B402" s="2">
-        <v>2230000000</v>
+        <v>637500000</v>
       </c>
       <c r="C402" s="2">
-        <v>2230000000</v>
+        <v>637500000</v>
       </c>
       <c r="D402" s="2">
         <v>9815000</v>
@@ -11826,7 +11696,7 @@
         <v>227966545</v>
       </c>
       <c r="G402" s="2">
-        <v>2002033455</v>
+        <v>409533455</v>
       </c>
       <c r="H402" s="2">
         <v>0</v>
@@ -11837,10 +11707,10 @@
         <v>25</v>
       </c>
       <c r="B403" s="2">
-        <v>193600000</v>
+        <v>48400000</v>
       </c>
       <c r="C403" s="2">
-        <v>145200000</v>
+        <v>48400000</v>
       </c>
       <c r="D403" s="2">
         <v>21900000</v>
@@ -11852,10 +11722,10 @@
         <v>21900000</v>
       </c>
       <c r="G403" s="2">
-        <v>123300000</v>
+        <v>26500000</v>
       </c>
       <c r="H403" s="2">
-        <v>48400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.45">
@@ -11863,10 +11733,10 @@
         <v>26</v>
       </c>
       <c r="B404" s="2">
-        <v>593631000</v>
+        <v>170907750</v>
       </c>
       <c r="C404" s="2">
-        <v>445223250</v>
+        <v>170907750</v>
       </c>
       <c r="D404" s="2">
         <v>98217450</v>
@@ -11878,10 +11748,10 @@
         <v>166131450</v>
       </c>
       <c r="G404" s="2">
-        <v>279091800</v>
+        <v>4776300</v>
       </c>
       <c r="H404" s="2">
-        <v>148407750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.45">
@@ -11889,10 +11759,10 @@
         <v>27</v>
       </c>
       <c r="B405" s="2">
-        <v>105000000</v>
+        <v>26250000</v>
       </c>
       <c r="C405" s="2">
-        <v>105000000</v>
+        <v>26250000</v>
       </c>
       <c r="D405" s="2">
         <v>0</v>
@@ -11904,7 +11774,7 @@
         <v>16500000</v>
       </c>
       <c r="G405" s="2">
-        <v>88500000</v>
+        <v>9750000</v>
       </c>
       <c r="H405" s="2">
         <v>0</v>
@@ -11915,10 +11785,10 @@
         <v>28</v>
       </c>
       <c r="B406" s="2">
-        <v>386000000</v>
+        <v>96500000</v>
       </c>
       <c r="C406" s="2">
-        <v>289500000</v>
+        <v>96500000</v>
       </c>
       <c r="D406" s="2">
         <v>2609000</v>
@@ -11930,10 +11800,10 @@
         <v>2609000</v>
       </c>
       <c r="G406" s="2">
-        <v>286891000</v>
+        <v>93891000</v>
       </c>
       <c r="H406" s="2">
-        <v>96500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.45">
@@ -11941,10 +11811,10 @@
         <v>30</v>
       </c>
       <c r="B407" s="2">
-        <v>468000000</v>
+        <v>117000000</v>
       </c>
       <c r="C407" s="2">
-        <v>351000000</v>
+        <v>117000000</v>
       </c>
       <c r="D407" s="2">
         <v>0</v>
@@ -11956,10 +11826,10 @@
         <v>65686596</v>
       </c>
       <c r="G407" s="2">
-        <v>285313404</v>
+        <v>51313404</v>
       </c>
       <c r="H407" s="2">
-        <v>117000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.45">
@@ -11967,10 +11837,10 @@
         <v>79</v>
       </c>
       <c r="B408" s="2">
-        <v>6000000</v>
+        <v>1500000</v>
       </c>
       <c r="C408" s="2">
-        <v>6000000</v>
+        <v>1500000</v>
       </c>
       <c r="D408" s="2">
         <v>0</v>
@@ -11982,7 +11852,7 @@
         <v>315000</v>
       </c>
       <c r="G408" s="2">
-        <v>5685000</v>
+        <v>1185000</v>
       </c>
       <c r="H408" s="2">
         <v>0</v>
@@ -11993,10 +11863,10 @@
         <v>31</v>
       </c>
       <c r="B409" s="2">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="C409" s="2">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="D409" s="2">
         <v>0</v>
@@ -12008,7 +11878,7 @@
         <v>0</v>
       </c>
       <c r="G409" s="2">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="H409" s="2">
         <v>0</v>
@@ -12253,1774 +12123,750 @@
         <v>86</v>
       </c>
       <c r="B419" s="2">
-        <v>34234867120</v>
+        <v>26293508870</v>
       </c>
       <c r="C419" s="2">
-        <v>33762059370</v>
+        <v>26293508870</v>
       </c>
       <c r="D419" s="2">
-        <v>828213315</v>
+        <v>927154015</v>
       </c>
       <c r="E419" s="2">
-        <v>3564471467</v>
+        <v>3465530767</v>
       </c>
       <c r="F419" s="2">
         <v>4392684782</v>
       </c>
       <c r="G419" s="2">
-        <v>29369374588</v>
+        <v>21900824088</v>
       </c>
       <c r="H419" s="2">
-        <v>472807750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A420" s="1" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="B420" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>873740000</v>
+        <v>1871950730</v>
       </c>
       <c r="C420" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>436870000</v>
+        <v>1871950730</v>
       </c>
       <c r="D420" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>404360000</v>
+        <f>F420-E420</f>
+        <v>404935052</v>
       </c>
       <c r="E420" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>35605052</v>
+        <v>78896778</v>
       </c>
       <c r="F420" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>439965052</v>
+        <v>483831830</v>
       </c>
       <c r="G420" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>-3095052</v>
+        <f>C420-F420</f>
+        <v>1388118900</v>
       </c>
       <c r="H420" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>436870000</v>
+        <f>B420-C420</f>
+        <v>0</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A421" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B421" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="C421" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="D421" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="E421" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="F421" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="G421" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="H421" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="B421" s="3"/>
+      <c r="C421" s="3"/>
+      <c r="D421" s="3"/>
+      <c r="E421" s="3"/>
+      <c r="F421" s="3"/>
+      <c r="G421" s="3"/>
+      <c r="H421" s="3"/>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A422" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B422" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="C422" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="D422" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="E422" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="F422" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="G422" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="H422" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="B422" s="3"/>
+      <c r="C422" s="3"/>
+      <c r="D422" s="3"/>
+      <c r="E422" s="3"/>
+      <c r="F422" s="3"/>
+      <c r="G422" s="3"/>
+      <c r="H422" s="3"/>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A423" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B423" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="C423" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="D423" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="E423" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="F423" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="G423" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="H423" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B423" s="3"/>
+      <c r="C423" s="3"/>
+      <c r="D423" s="3"/>
+      <c r="E423" s="3"/>
+      <c r="F423" s="3"/>
+      <c r="G423" s="3"/>
+      <c r="H423" s="3"/>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A424" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B424" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="C424" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="D424" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="E424" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="F424" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="G424" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="H424" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="B424" s="3"/>
+      <c r="C424" s="3"/>
+      <c r="D424" s="3"/>
+      <c r="E424" s="3"/>
+      <c r="F424" s="3"/>
+      <c r="G424" s="3"/>
+      <c r="H424" s="3"/>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A425" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B425" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="C425" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="D425" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="E425" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="F425" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="G425" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="H425" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B425" s="3"/>
+      <c r="C425" s="3"/>
+      <c r="D425" s="3"/>
+      <c r="E425" s="3"/>
+      <c r="F425" s="3"/>
+      <c r="G425" s="3"/>
+      <c r="H425" s="3"/>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A426" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B426" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="C426" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="D426" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="E426" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="F426" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="G426" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="H426" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="B426" s="3"/>
+      <c r="C426" s="3"/>
+      <c r="D426" s="3"/>
+      <c r="E426" s="3"/>
+      <c r="F426" s="3"/>
+      <c r="G426" s="3"/>
+      <c r="H426" s="3"/>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A427" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B427" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="C427" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="D427" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="E427" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="F427" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="G427" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="H427" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="B427" s="3"/>
+      <c r="C427" s="3"/>
+      <c r="D427" s="3"/>
+      <c r="E427" s="3"/>
+      <c r="F427" s="3"/>
+      <c r="G427" s="3"/>
+      <c r="H427" s="3"/>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A428" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B428" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="C428" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="D428" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="E428" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="F428" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="G428" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="H428" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B428" s="3"/>
+      <c r="C428" s="3"/>
+      <c r="D428" s="3"/>
+      <c r="E428" s="3"/>
+      <c r="F428" s="3"/>
+      <c r="G428" s="3"/>
+      <c r="H428" s="3"/>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A429" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B429" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="C429" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="D429" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="E429" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="F429" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="G429" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="H429" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="B429" s="3"/>
+      <c r="C429" s="3"/>
+      <c r="D429" s="3"/>
+      <c r="E429" s="3"/>
+      <c r="F429" s="3"/>
+      <c r="G429" s="3"/>
+      <c r="H429" s="3"/>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A430" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B430" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="C430" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="D430" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="E430" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="F430" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="G430" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="H430" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="B430" s="3"/>
+      <c r="C430" s="3"/>
+      <c r="D430" s="3"/>
+      <c r="E430" s="3"/>
+      <c r="F430" s="3"/>
+      <c r="G430" s="3"/>
+      <c r="H430" s="3"/>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A431" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B431" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="C431" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="D431" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="E431" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="F431" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="G431" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="H431" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="B431" s="3"/>
+      <c r="C431" s="3"/>
+      <c r="D431" s="3"/>
+      <c r="E431" s="3"/>
+      <c r="F431" s="3"/>
+      <c r="G431" s="3"/>
+      <c r="H431" s="3"/>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A432" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B432" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="C432" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="D432" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="E432" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="F432" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="G432" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="H432" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="B432" s="3"/>
+      <c r="C432" s="3"/>
+      <c r="D432" s="3"/>
+      <c r="E432" s="3"/>
+      <c r="F432" s="3"/>
+      <c r="G432" s="3"/>
+      <c r="H432" s="3"/>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A433" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B433" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="C433" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="D433" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="E433" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="F433" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="G433" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="H433" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="B433" s="3"/>
+      <c r="C433" s="3"/>
+      <c r="D433" s="3"/>
+      <c r="E433" s="3"/>
+      <c r="F433" s="3"/>
+      <c r="G433" s="3"/>
+      <c r="H433" s="3"/>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A434" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B434" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="C434" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="D434" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="E434" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="F434" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="G434" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="H434" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B434" s="3"/>
+      <c r="C434" s="3"/>
+      <c r="D434" s="3"/>
+      <c r="E434" s="3"/>
+      <c r="F434" s="3"/>
+      <c r="G434" s="3"/>
+      <c r="H434" s="3"/>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A435" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B435" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="C435" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="D435" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="E435" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="F435" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="G435" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="H435" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B435" s="3"/>
+      <c r="C435" s="3"/>
+      <c r="D435" s="3"/>
+      <c r="E435" s="3"/>
+      <c r="F435" s="3"/>
+      <c r="G435" s="3"/>
+      <c r="H435" s="3"/>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A436" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B436" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="C436" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="D436" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="E436" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="F436" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="G436" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="H436" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="B436" s="3"/>
+      <c r="C436" s="3"/>
+      <c r="D436" s="3"/>
+      <c r="E436" s="3"/>
+      <c r="F436" s="3"/>
+      <c r="G436" s="3"/>
+      <c r="H436" s="3"/>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A437" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B437" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>474786000</v>
-      </c>
-      <c r="C437" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>237393000</v>
-      </c>
-      <c r="D437" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>0</v>
-      </c>
-      <c r="E437" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>0</v>
-      </c>
-      <c r="F437" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>0</v>
-      </c>
-      <c r="G437" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>237393000</v>
-      </c>
-      <c r="H437" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>237393000</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B437" s="3"/>
+      <c r="C437" s="3"/>
+      <c r="D437" s="3"/>
+      <c r="E437" s="3"/>
+      <c r="F437" s="3"/>
+      <c r="G437" s="3"/>
+      <c r="H437" s="3"/>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A438" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B438" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>208425000</v>
-      </c>
-      <c r="C438" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>104212500</v>
-      </c>
-      <c r="D438" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>0</v>
-      </c>
-      <c r="E438" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>0</v>
-      </c>
-      <c r="F438" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>0</v>
-      </c>
-      <c r="G438" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>104212500</v>
-      </c>
-      <c r="H438" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>104212500</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B438" s="3"/>
+      <c r="C438" s="3"/>
+      <c r="D438" s="3"/>
+      <c r="E438" s="3"/>
+      <c r="F438" s="3"/>
+      <c r="G438" s="3"/>
+      <c r="H438" s="3"/>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A439" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B439" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>20000000</v>
-      </c>
-      <c r="C439" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>13970000</v>
-      </c>
-      <c r="D439" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>13970000</v>
-      </c>
-      <c r="E439" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>0</v>
-      </c>
-      <c r="F439" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>13970000</v>
-      </c>
-      <c r="G439" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>0</v>
-      </c>
-      <c r="H439" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>6030000</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B439" s="3"/>
+      <c r="C439" s="3"/>
+      <c r="D439" s="3"/>
+      <c r="E439" s="3"/>
+      <c r="F439" s="3"/>
+      <c r="G439" s="3"/>
+      <c r="H439" s="3"/>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A440" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B440" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>220000000</v>
-      </c>
-      <c r="C440" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>110000000</v>
-      </c>
-      <c r="D440" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>0</v>
-      </c>
-      <c r="E440" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>29896778</v>
-      </c>
-      <c r="F440" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>29896778</v>
-      </c>
-      <c r="G440" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>80103222</v>
-      </c>
-      <c r="H440" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>110000000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B440" s="3"/>
+      <c r="C440" s="3"/>
+      <c r="D440" s="3"/>
+      <c r="E440" s="3"/>
+      <c r="F440" s="3"/>
+      <c r="G440" s="3"/>
+      <c r="H440" s="3"/>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A441" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B441" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>75000000</v>
-      </c>
-      <c r="C441" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>37500000</v>
-      </c>
-      <c r="D441" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>0</v>
-      </c>
-      <c r="E441" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>0</v>
-      </c>
-      <c r="F441" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>0</v>
-      </c>
-      <c r="G441" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>37500000</v>
-      </c>
-      <c r="H441" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>37500000</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B441" s="3"/>
+      <c r="C441" s="3"/>
+      <c r="D441" s="3"/>
+      <c r="E441" s="3"/>
+      <c r="F441" s="3"/>
+      <c r="G441" s="3"/>
+      <c r="H441" s="3"/>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A442" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B442" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="C442" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="D442" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="E442" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="F442" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="G442" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="H442" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B442" s="3"/>
+      <c r="C442" s="3"/>
+      <c r="D442" s="3"/>
+      <c r="E442" s="3"/>
+      <c r="F442" s="3"/>
+      <c r="G442" s="3"/>
+      <c r="H442" s="3"/>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A443" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B443" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="C443" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="D443" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="E443" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="F443" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="G443" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="H443" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="B443" s="3"/>
+      <c r="C443" s="3"/>
+      <c r="D443" s="3"/>
+      <c r="E443" s="3"/>
+      <c r="F443" s="3"/>
+      <c r="G443" s="3"/>
+      <c r="H443" s="3"/>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A444" s="1" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="B444" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>60000000</v>
       </c>
       <c r="C444" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
-        <v>30000000</v>
+        <v>60000000</v>
       </c>
       <c r="D444" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
+        <f>F444-E444</f>
         <v>9000000</v>
       </c>
       <c r="E444" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>0</v>
       </c>
       <c r="F444" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>9000000</v>
       </c>
       <c r="G444" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
-        <v>21000000</v>
+        <f>C444-F444</f>
+        <v>51000000</v>
       </c>
       <c r="H444" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
-        <v>30000000</v>
+        <f>B444-C444</f>
+        <v>0</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A445" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="B445" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>45150000</v>
       </c>
       <c r="C445" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
-        <v>22575000</v>
+        <v>45150000</v>
       </c>
       <c r="D445" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
+        <f>F445-E445</f>
         <v>6423200</v>
       </c>
       <c r="E445" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>6119400</v>
       </c>
       <c r="F445" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>12542600</v>
       </c>
       <c r="G445" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
-        <v>10032400</v>
+        <f>C445-F445</f>
+        <v>32607400</v>
       </c>
       <c r="H445" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
-        <v>22575000</v>
+        <f>B445-C445</f>
+        <v>0</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A446" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B446" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="C446" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="D446" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="E446" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="F446" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="G446" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="H446" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B446" s="3"/>
+      <c r="C446" s="3"/>
+      <c r="D446" s="3"/>
+      <c r="E446" s="3"/>
+      <c r="F446" s="3"/>
+      <c r="G446" s="3"/>
+      <c r="H446" s="3"/>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A447" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B447" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="C447" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="D447" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="E447" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="F447" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="G447" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="H447" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="B447" s="3"/>
+      <c r="C447" s="3"/>
+      <c r="D447" s="3"/>
+      <c r="E447" s="3"/>
+      <c r="F447" s="3"/>
+      <c r="G447" s="3"/>
+      <c r="H447" s="3"/>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A448" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B448" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="C448" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="D448" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="E448" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="F448" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="G448" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="H448" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B448" s="3"/>
+      <c r="C448" s="3"/>
+      <c r="D448" s="3"/>
+      <c r="E448" s="3"/>
+      <c r="F448" s="3"/>
+      <c r="G448" s="3"/>
+      <c r="H448" s="3"/>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A449" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B449" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="C449" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="D449" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="E449" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="F449" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="G449" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="H449" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="B449" s="3"/>
+      <c r="C449" s="3"/>
+      <c r="D449" s="3"/>
+      <c r="E449" s="3"/>
+      <c r="F449" s="3"/>
+      <c r="G449" s="3"/>
+      <c r="H449" s="3"/>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A450" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B450" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="C450" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="D450" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="E450" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="F450" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="G450" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="H450" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B450" s="3"/>
+      <c r="C450" s="3"/>
+      <c r="D450" s="3"/>
+      <c r="E450" s="3"/>
+      <c r="F450" s="3"/>
+      <c r="G450" s="3"/>
+      <c r="H450" s="3"/>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A451" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B451" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="C451" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="D451" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="E451" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="F451" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="G451" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="H451" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B451" s="3"/>
+      <c r="C451" s="3"/>
+      <c r="D451" s="3"/>
+      <c r="E451" s="3"/>
+      <c r="F451" s="3"/>
+      <c r="G451" s="3"/>
+      <c r="H451" s="3"/>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A452" s="1" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="B452" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>6000000</v>
+        <v>372660000</v>
       </c>
       <c r="C452" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>1500000</v>
+        <v>372660000</v>
       </c>
       <c r="D452" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>0</v>
+        <f>F452-E452</f>
+        <v>8912700</v>
       </c>
       <c r="E452" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>0</v>
+        <v>5604650</v>
       </c>
       <c r="F452" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>0</v>
+        <v>14517350</v>
       </c>
       <c r="G452" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>1500000</v>
+        <f>C452-F452</f>
+        <v>358142650</v>
       </c>
       <c r="H452" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>4500000</v>
+        <f>B452-C452</f>
+        <v>0</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A453" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B453" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>41000000</v>
-      </c>
-      <c r="C453" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>10250000</v>
-      </c>
-      <c r="D453" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>1997700</v>
-      </c>
-      <c r="E453" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>998400</v>
-      </c>
-      <c r="F453" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>2996100</v>
-      </c>
-      <c r="G453" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>7253900</v>
-      </c>
-      <c r="H453" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>30750000</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B453" s="3"/>
+      <c r="C453" s="3"/>
+      <c r="D453" s="3"/>
+      <c r="E453" s="3"/>
+      <c r="F453" s="3"/>
+      <c r="G453" s="3"/>
+      <c r="H453" s="3"/>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A454" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B454" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>12000000</v>
-      </c>
-      <c r="C454" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>3000000</v>
-      </c>
-      <c r="D454" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>0</v>
-      </c>
-      <c r="E454" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>0</v>
-      </c>
-      <c r="F454" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>0</v>
-      </c>
-      <c r="G454" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>3000000</v>
-      </c>
-      <c r="H454" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>9000000</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B454" s="3"/>
+      <c r="C454" s="3"/>
+      <c r="D454" s="3"/>
+      <c r="E454" s="3"/>
+      <c r="F454" s="3"/>
+      <c r="G454" s="3"/>
+      <c r="H454" s="3"/>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A455" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B455" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>171000000</v>
-      </c>
-      <c r="C455" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>42750000</v>
-      </c>
-      <c r="D455" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>5880000</v>
-      </c>
-      <c r="E455" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>0</v>
-      </c>
-      <c r="F455" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>5880000</v>
-      </c>
-      <c r="G455" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>36870000</v>
-      </c>
-      <c r="H455" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>128250000</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B455" s="3"/>
+      <c r="C455" s="3"/>
+      <c r="D455" s="3"/>
+      <c r="E455" s="3"/>
+      <c r="F455" s="3"/>
+      <c r="G455" s="3"/>
+      <c r="H455" s="3"/>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A456" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B456" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>130000000</v>
-      </c>
-      <c r="C456" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>32500000</v>
-      </c>
-      <c r="D456" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>0</v>
-      </c>
-      <c r="E456" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>7381250</v>
-      </c>
-      <c r="F456" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>7381250</v>
-      </c>
-      <c r="G456" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>25118750</v>
-      </c>
-      <c r="H456" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>97500000</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B456" s="3"/>
+      <c r="C456" s="3"/>
+      <c r="D456" s="3"/>
+      <c r="E456" s="3"/>
+      <c r="F456" s="3"/>
+      <c r="G456" s="3"/>
+      <c r="H456" s="3"/>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A457" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B457" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>6660000</v>
-      </c>
-      <c r="C457" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>1665000</v>
-      </c>
-      <c r="D457" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>1665000</v>
-      </c>
-      <c r="E457" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>0</v>
-      </c>
-      <c r="F457" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>1665000</v>
-      </c>
-      <c r="G457" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>0</v>
-      </c>
-      <c r="H457" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>4995000</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="B457" s="3"/>
+      <c r="C457" s="3"/>
+      <c r="D457" s="3"/>
+      <c r="E457" s="3"/>
+      <c r="F457" s="3"/>
+      <c r="G457" s="3"/>
+      <c r="H457" s="3"/>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A458" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B458" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>6000000</v>
-      </c>
-      <c r="C458" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>1500000</v>
-      </c>
-      <c r="D458" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>0</v>
-      </c>
-      <c r="E458" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>0</v>
-      </c>
-      <c r="F458" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>0</v>
-      </c>
-      <c r="G458" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>1500000</v>
-      </c>
-      <c r="H458" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>4500000</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B458" s="3"/>
+      <c r="C458" s="3"/>
+      <c r="D458" s="3"/>
+      <c r="E458" s="3"/>
+      <c r="F458" s="3"/>
+      <c r="G458" s="3"/>
+      <c r="H458" s="3"/>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A459" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B459" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="C459" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="D459" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="E459" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="F459" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="G459" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="H459" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B459" s="3"/>
+      <c r="C459" s="3"/>
+      <c r="D459" s="3"/>
+      <c r="E459" s="3"/>
+      <c r="F459" s="3"/>
+      <c r="G459" s="3"/>
+      <c r="H459" s="3"/>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A460" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B460" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="C460" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="D460" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="E460" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="F460" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="G460" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="H460" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B460" s="3"/>
+      <c r="C460" s="3"/>
+      <c r="D460" s="3"/>
+      <c r="E460" s="3"/>
+      <c r="F460" s="3"/>
+      <c r="G460" s="3"/>
+      <c r="H460" s="3"/>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A461" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B461" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="C461" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="D461" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="E461" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="F461" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="G461" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="H461" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B461" s="3"/>
+      <c r="C461" s="3"/>
+      <c r="D461" s="3"/>
+      <c r="E461" s="3"/>
+      <c r="F461" s="3"/>
+      <c r="G461" s="3"/>
+      <c r="H461" s="3"/>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A462" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B462" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="C462" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="D462" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="E462" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="F462" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="G462" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="H462" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="B462" s="3"/>
+      <c r="C462" s="3"/>
+      <c r="D462" s="3"/>
+      <c r="E462" s="3"/>
+      <c r="F462" s="3"/>
+      <c r="G462" s="3"/>
+      <c r="H462" s="3"/>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A463" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B463" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="C463" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="D463" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="E463" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="F463" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="G463" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="H463" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B463" s="3"/>
+      <c r="C463" s="3"/>
+      <c r="D463" s="3"/>
+      <c r="E463" s="3"/>
+      <c r="F463" s="3"/>
+      <c r="G463" s="3"/>
+      <c r="H463" s="3"/>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A464" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B464" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="C464" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="D464" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="E464" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="F464" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="G464" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="H464" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B464" s="3"/>
+      <c r="C464" s="3"/>
+      <c r="D464" s="3"/>
+      <c r="E464" s="3"/>
+      <c r="F464" s="3"/>
+      <c r="G464" s="3"/>
+      <c r="H464" s="3"/>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A465" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B465" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="C465" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="D465" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="E465" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="F465" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="G465" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="H465" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B465" s="3"/>
+      <c r="C465" s="3"/>
+      <c r="D465" s="3"/>
+      <c r="E465" s="3"/>
+      <c r="F465" s="3"/>
+      <c r="G465" s="3"/>
+      <c r="H465" s="3"/>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A466" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B466" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="C466" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="D466" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="E466" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="F466" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="G466" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="H466" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B466" s="3"/>
+      <c r="C466" s="3"/>
+      <c r="D466" s="3"/>
+      <c r="E466" s="3"/>
+      <c r="F466" s="3"/>
+      <c r="G466" s="3"/>
+      <c r="H466" s="3"/>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A467" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B467" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="C467" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="D467" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="E467" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="F467" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="G467" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="H467" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B467" s="3"/>
+      <c r="C467" s="3"/>
+      <c r="D467" s="3"/>
+      <c r="E467" s="3"/>
+      <c r="F467" s="3"/>
+      <c r="G467" s="3"/>
+      <c r="H467" s="3"/>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A468" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B468" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="C468" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="D468" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="E468" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="F468" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="G468" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="H468" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B468" s="3"/>
+      <c r="C468" s="3"/>
+      <c r="D468" s="3"/>
+      <c r="E468" s="3"/>
+      <c r="F468" s="3"/>
+      <c r="G468" s="3"/>
+      <c r="H468" s="3"/>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A469" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B469" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="C469" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="D469" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="E469" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="F469" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="G469" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="H469" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B469" s="3"/>
+      <c r="C469" s="3"/>
+      <c r="D469" s="3"/>
+      <c r="E469" s="3"/>
+      <c r="F469" s="3"/>
+      <c r="G469" s="3"/>
+      <c r="H469" s="3"/>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A470" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B470" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="C470" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="D470" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="E470" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="F470" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="G470" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="H470" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B470" s="3"/>
+      <c r="C470" s="3"/>
+      <c r="D470" s="3"/>
+      <c r="E470" s="3"/>
+      <c r="F470" s="3"/>
+      <c r="G470" s="3"/>
+      <c r="H470" s="3"/>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A471" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B471" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="C471" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="D471" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="E471" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="F471" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="G471" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="H471" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B471" s="3"/>
+      <c r="C471" s="3"/>
+      <c r="D471" s="3"/>
+      <c r="E471" s="3"/>
+      <c r="F471" s="3"/>
+      <c r="G471" s="3"/>
+      <c r="H471" s="3"/>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A472" s="1" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="B472" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>2349761000</v>
+        <f>SUM(B420:B471)</f>
+        <v>2349760730</v>
       </c>
       <c r="C472" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>1085685500</v>
+        <f t="shared" ref="C472:H472" si="0">SUM(C420:C471)</f>
+        <v>2349760730</v>
       </c>
       <c r="D472" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>443295900</v>
+        <f t="shared" si="0"/>
+        <v>429270952</v>
       </c>
       <c r="E472" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>80000880</v>
+        <f t="shared" si="0"/>
+        <v>90620828</v>
       </c>
       <c r="F472" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>523296780</v>
+        <f t="shared" si="0"/>
+        <v>519891780</v>
       </c>
       <c r="G472" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>562388720</v>
+        <f t="shared" si="0"/>
+        <v>1829868950</v>
       </c>
       <c r="H472" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>1264075500</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.45">
@@ -14028,22 +12874,22 @@
         <v>8</v>
       </c>
       <c r="B473" s="2">
-        <v>10505111000</v>
+        <v>6121242000</v>
       </c>
       <c r="C473" s="2">
-        <v>10505111000</v>
+        <v>6121242000</v>
       </c>
       <c r="D473" s="2">
-        <v>7767056599</v>
+        <v>5458456599</v>
       </c>
       <c r="E473" s="2">
         <v>0</v>
       </c>
       <c r="F473" s="2">
-        <v>7767056599</v>
+        <v>5458456599</v>
       </c>
       <c r="G473" s="2">
-        <v>2738054401</v>
+        <v>662785401</v>
       </c>
       <c r="H473" s="2">
         <v>0</v>
@@ -14181,7 +13027,7 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B479" s="2">
         <v>0</v>
@@ -14207,13 +13053,13 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="B480" s="2">
-        <v>2312795000</v>
+        <v>1778331214</v>
       </c>
       <c r="C480" s="2">
-        <v>2312795000</v>
+        <v>1778331214</v>
       </c>
       <c r="D480" s="2">
         <v>1778331214</v>
@@ -14225,7 +13071,7 @@
         <v>1778331214</v>
       </c>
       <c r="G480" s="2">
-        <v>534463786</v>
+        <v>0</v>
       </c>
       <c r="H480" s="2">
         <v>0</v>
@@ -14236,22 +13082,22 @@
         <v>53</v>
       </c>
       <c r="B481" s="2">
-        <v>4989900000</v>
+        <v>2094950000</v>
       </c>
       <c r="C481" s="2">
-        <v>4989900000</v>
+        <v>2094950000</v>
       </c>
       <c r="D481" s="2">
-        <v>805666889</v>
+        <v>897050889</v>
       </c>
       <c r="E481" s="2">
-        <v>333634248</v>
+        <v>235941248</v>
       </c>
       <c r="F481" s="2">
-        <v>1139301137</v>
+        <v>1132992137</v>
       </c>
       <c r="G481" s="2">
-        <v>3850598863</v>
+        <v>961957863</v>
       </c>
       <c r="H481" s="2">
         <v>0</v>
@@ -14259,7 +13105,7 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="B482" s="2">
         <v>0</v>
@@ -14288,10 +13134,10 @@
         <v>54</v>
       </c>
       <c r="B483" s="2">
-        <v>1680000000</v>
+        <v>840000000</v>
       </c>
       <c r="C483" s="2">
-        <v>1680000000</v>
+        <v>840000000</v>
       </c>
       <c r="D483" s="2">
         <v>353557050</v>
@@ -14303,7 +13149,7 @@
         <v>353557050</v>
       </c>
       <c r="G483" s="2">
-        <v>1326442950</v>
+        <v>486442950</v>
       </c>
       <c r="H483" s="2">
         <v>0</v>
@@ -14314,22 +13160,22 @@
         <v>77</v>
       </c>
       <c r="B484" s="2">
-        <v>492066000</v>
+        <v>246033000</v>
       </c>
       <c r="C484" s="2">
-        <v>492066000</v>
+        <v>246033000</v>
       </c>
       <c r="D484" s="2">
-        <v>31501365</v>
+        <v>4400000</v>
       </c>
       <c r="E484" s="2">
         <v>7785500</v>
       </c>
       <c r="F484" s="2">
-        <v>39286865</v>
+        <v>12185500</v>
       </c>
       <c r="G484" s="2">
-        <v>452779135</v>
+        <v>233847500</v>
       </c>
       <c r="H484" s="2">
         <v>0</v>
@@ -14337,13 +13183,13 @@
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="B485" s="2">
-        <v>624500000</v>
+        <v>312250000</v>
       </c>
       <c r="C485" s="2">
-        <v>624500000</v>
+        <v>312250000</v>
       </c>
       <c r="D485" s="2">
         <v>0</v>
@@ -14355,7 +13201,7 @@
         <v>0</v>
       </c>
       <c r="G485" s="2">
-        <v>624500000</v>
+        <v>312250000</v>
       </c>
       <c r="H485" s="2">
         <v>0</v>
@@ -14363,13 +13209,13 @@
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B486" s="2">
-        <v>700000000</v>
+        <v>350000000</v>
       </c>
       <c r="C486" s="2">
-        <v>700000000</v>
+        <v>350000000</v>
       </c>
       <c r="D486" s="2">
         <v>0</v>
@@ -14381,7 +13227,7 @@
         <v>0</v>
       </c>
       <c r="G486" s="2">
-        <v>700000000</v>
+        <v>350000000</v>
       </c>
       <c r="H486" s="2">
         <v>0</v>
@@ -14389,7 +13235,7 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B487" s="2">
         <v>0</v>
@@ -14415,25 +13261,25 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="B488" s="2">
-        <v>745000000</v>
+        <v>372500000</v>
       </c>
       <c r="C488" s="2">
-        <v>745000000</v>
+        <v>372500000</v>
       </c>
       <c r="D488" s="2">
-        <v>26235280</v>
+        <v>19421480</v>
       </c>
       <c r="E488" s="2">
         <v>32460000</v>
       </c>
       <c r="F488" s="2">
-        <v>58695280</v>
+        <v>51881480</v>
       </c>
       <c r="G488" s="2">
-        <v>686304720</v>
+        <v>320618520</v>
       </c>
       <c r="H488" s="2">
         <v>0</v>
@@ -14441,25 +13287,25 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="B489" s="2">
-        <v>4029356000</v>
+        <v>2397799000</v>
       </c>
       <c r="C489" s="2">
-        <v>4029356000</v>
+        <v>2397799000</v>
       </c>
       <c r="D489" s="2">
-        <v>2411599000</v>
+        <v>459375000</v>
       </c>
       <c r="E489" s="2">
         <v>29795000</v>
       </c>
       <c r="F489" s="2">
-        <v>2441394000</v>
+        <v>489170000</v>
       </c>
       <c r="G489" s="2">
-        <v>1587962000</v>
+        <v>1908629000</v>
       </c>
       <c r="H489" s="2">
         <v>0</v>
@@ -14467,13 +13313,13 @@
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="B490" s="2">
-        <v>297500000</v>
+        <v>1098750000</v>
       </c>
       <c r="C490" s="2">
-        <v>297500000</v>
+        <v>1098750000</v>
       </c>
       <c r="D490" s="2">
         <v>0</v>
@@ -14485,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="G490" s="2">
-        <v>297500000</v>
+        <v>1098750000</v>
       </c>
       <c r="H490" s="2">
         <v>0</v>
@@ -14496,10 +13342,10 @@
         <v>55</v>
       </c>
       <c r="B491" s="2">
-        <v>266250000</v>
+        <v>133125000</v>
       </c>
       <c r="C491" s="2">
-        <v>266250000</v>
+        <v>133125000</v>
       </c>
       <c r="D491" s="2">
         <v>0</v>
@@ -14511,7 +13357,7 @@
         <v>40800000</v>
       </c>
       <c r="G491" s="2">
-        <v>225450000</v>
+        <v>92325000</v>
       </c>
       <c r="H491" s="2">
         <v>0</v>
@@ -14522,10 +13368,10 @@
         <v>56</v>
       </c>
       <c r="B492" s="2">
-        <v>1350000000</v>
+        <v>375000000</v>
       </c>
       <c r="C492" s="2">
-        <v>1350000000</v>
+        <v>375000000</v>
       </c>
       <c r="D492" s="2">
         <v>0</v>
@@ -14537,7 +13383,7 @@
         <v>0</v>
       </c>
       <c r="G492" s="2">
-        <v>1350000000</v>
+        <v>375000000</v>
       </c>
       <c r="H492" s="2">
         <v>0</v>
@@ -14548,10 +13394,10 @@
         <v>22</v>
       </c>
       <c r="B493" s="2">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="C493" s="2">
-        <v>75000000</v>
+        <v>50000000</v>
       </c>
       <c r="D493" s="2">
         <v>0</v>
@@ -14563,10 +13409,10 @@
         <v>12720000</v>
       </c>
       <c r="G493" s="2">
-        <v>62280000</v>
+        <v>37280000</v>
       </c>
       <c r="H493" s="2">
-        <v>25000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.45">
@@ -14574,10 +13420,10 @@
         <v>57</v>
       </c>
       <c r="B494" s="2">
-        <v>1016150000</v>
+        <v>508075000</v>
       </c>
       <c r="C494" s="2">
-        <v>1016150000</v>
+        <v>508075000</v>
       </c>
       <c r="D494" s="2">
         <v>34825000</v>
@@ -14589,7 +13435,7 @@
         <v>163165000</v>
       </c>
       <c r="G494" s="2">
-        <v>852985000</v>
+        <v>344910000</v>
       </c>
       <c r="H494" s="2">
         <v>0</v>
@@ -14600,10 +13446,10 @@
         <v>58</v>
       </c>
       <c r="B495" s="2">
-        <v>2560000000</v>
+        <v>640000000</v>
       </c>
       <c r="C495" s="2">
-        <v>2560000000</v>
+        <v>640000000</v>
       </c>
       <c r="D495" s="2">
         <v>8404406</v>
@@ -14615,7 +13461,7 @@
         <v>455035109</v>
       </c>
       <c r="G495" s="2">
-        <v>2104964891</v>
+        <v>184964891</v>
       </c>
       <c r="H495" s="2">
         <v>0</v>
@@ -14626,10 +13472,10 @@
         <v>25</v>
       </c>
       <c r="B496" s="2">
-        <v>891173000</v>
+        <v>222793250</v>
       </c>
       <c r="C496" s="2">
-        <v>668379750</v>
+        <v>222793250</v>
       </c>
       <c r="D496" s="2">
         <v>29693828</v>
@@ -14641,10 +13487,10 @@
         <v>52063828</v>
       </c>
       <c r="G496" s="2">
-        <v>616315922</v>
+        <v>170729422</v>
       </c>
       <c r="H496" s="2">
-        <v>222793250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.45">
@@ -14652,10 +13498,10 @@
         <v>26</v>
       </c>
       <c r="B497" s="2">
-        <v>1160455000</v>
+        <v>278081750</v>
       </c>
       <c r="C497" s="2">
-        <v>870341250</v>
+        <v>278081750</v>
       </c>
       <c r="D497" s="2">
         <v>95838170</v>
@@ -14667,10 +13513,10 @@
         <v>272779430</v>
       </c>
       <c r="G497" s="2">
-        <v>597561820</v>
+        <v>5302320</v>
       </c>
       <c r="H497" s="2">
-        <v>290113750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.45">
@@ -14678,10 +13524,10 @@
         <v>27</v>
       </c>
       <c r="B498" s="2">
-        <v>93000000</v>
+        <v>23250000</v>
       </c>
       <c r="C498" s="2">
-        <v>93000000</v>
+        <v>23250000</v>
       </c>
       <c r="D498" s="2">
         <v>0</v>
@@ -14693,7 +13539,7 @@
         <v>14500000</v>
       </c>
       <c r="G498" s="2">
-        <v>78500000</v>
+        <v>8750000</v>
       </c>
       <c r="H498" s="2">
         <v>0</v>
@@ -14704,10 +13550,10 @@
         <v>28</v>
       </c>
       <c r="B499" s="2">
-        <v>562923000</v>
+        <v>163230750</v>
       </c>
       <c r="C499" s="2">
-        <v>422192250</v>
+        <v>163230750</v>
       </c>
       <c r="D499" s="2">
         <v>19366000</v>
@@ -14719,10 +13565,10 @@
         <v>32006000</v>
       </c>
       <c r="G499" s="2">
-        <v>390186250</v>
+        <v>131224750</v>
       </c>
       <c r="H499" s="2">
-        <v>140730750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.45">
@@ -14730,25 +13576,25 @@
         <v>30</v>
       </c>
       <c r="B500" s="2">
-        <v>688578000</v>
+        <v>172144500</v>
       </c>
       <c r="C500" s="2">
-        <v>516433500</v>
+        <v>172144500</v>
       </c>
       <c r="D500" s="2">
         <v>35082547</v>
       </c>
       <c r="E500" s="2">
-        <v>77961880</v>
+        <v>77886880</v>
       </c>
       <c r="F500" s="2">
-        <v>113044427</v>
+        <v>112969427</v>
       </c>
       <c r="G500" s="2">
-        <v>403389073</v>
+        <v>59175073</v>
       </c>
       <c r="H500" s="2">
-        <v>172144500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.45">
@@ -14756,10 +13602,10 @@
         <v>79</v>
       </c>
       <c r="B501" s="2">
-        <v>36180000</v>
+        <v>9045000</v>
       </c>
       <c r="C501" s="2">
-        <v>36180000</v>
+        <v>9045000</v>
       </c>
       <c r="D501" s="2">
         <v>1720000</v>
@@ -14771,7 +13617,7 @@
         <v>7062537</v>
       </c>
       <c r="G501" s="2">
-        <v>29117463</v>
+        <v>1982463</v>
       </c>
       <c r="H501" s="2">
         <v>0</v>
@@ -14782,10 +13628,10 @@
         <v>31</v>
       </c>
       <c r="B502" s="2">
-        <v>61741000</v>
+        <v>40435250</v>
       </c>
       <c r="C502" s="2">
-        <v>61741000</v>
+        <v>40435250</v>
       </c>
       <c r="D502" s="2">
         <v>38255444</v>
@@ -14797,7 +13643,7 @@
         <v>38255444</v>
       </c>
       <c r="G502" s="2">
-        <v>23485556</v>
+        <v>2179806</v>
       </c>
       <c r="H502" s="2">
         <v>0</v>
@@ -14895,13 +13741,13 @@
         <v>0</v>
       </c>
       <c r="E506" s="2">
-        <v>1814036400</v>
+        <v>1814032650</v>
       </c>
       <c r="F506" s="2">
-        <v>1814036400</v>
+        <v>1814032650</v>
       </c>
       <c r="G506" s="2">
-        <v>10350245497</v>
+        <v>10350249247</v>
       </c>
       <c r="H506" s="2">
         <v>0</v>
@@ -15117,28 +13963,28 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="B515" s="2">
-        <v>61498532437</v>
+        <v>44562890151</v>
       </c>
       <c r="C515" s="2">
-        <v>60647750187</v>
+        <v>44562890151</v>
       </c>
       <c r="D515" s="2">
-        <v>13437132792</v>
+        <v>9233777627</v>
       </c>
       <c r="E515" s="2">
-        <v>5853406531</v>
+        <v>5755634781</v>
       </c>
       <c r="F515" s="2">
-        <v>19290539323</v>
+        <v>14989412408</v>
       </c>
       <c r="G515" s="2">
-        <v>41357210864</v>
+        <v>29573477743</v>
       </c>
       <c r="H515" s="2">
-        <v>850782250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.45">
@@ -15152,16 +13998,16 @@
         <v>5574698000</v>
       </c>
       <c r="D516" s="2">
-        <v>5471087865</v>
+        <v>2595236997</v>
       </c>
       <c r="E516" s="2">
         <v>0</v>
       </c>
       <c r="F516" s="2">
-        <v>5471087865</v>
+        <v>2595236997</v>
       </c>
       <c r="G516" s="2">
-        <v>103610135</v>
+        <v>2979461003</v>
       </c>
       <c r="H516" s="2">
         <v>0</v>
@@ -15178,16 +14024,16 @@
         <v>1521000000</v>
       </c>
       <c r="D517" s="2">
-        <v>1467022165</v>
+        <v>0</v>
       </c>
       <c r="E517" s="2">
         <v>3328300</v>
       </c>
       <c r="F517" s="2">
-        <v>1470350465</v>
+        <v>3328300</v>
       </c>
       <c r="G517" s="2">
-        <v>50649535</v>
+        <v>1517671700</v>
       </c>
       <c r="H517" s="2">
         <v>0</v>
@@ -15204,16 +14050,16 @@
         <v>1694175000</v>
       </c>
       <c r="D518" s="2">
-        <v>1694174158</v>
+        <v>810860400</v>
       </c>
       <c r="E518" s="2">
         <v>0</v>
       </c>
       <c r="F518" s="2">
-        <v>1694174158</v>
+        <v>810860400</v>
       </c>
       <c r="G518" s="2">
-        <v>842</v>
+        <v>883314600</v>
       </c>
       <c r="H518" s="2">
         <v>0</v>
@@ -15230,16 +14076,16 @@
         <v>2639000000</v>
       </c>
       <c r="D519" s="2">
-        <v>546436863</v>
+        <v>483429478</v>
       </c>
       <c r="E519" s="2">
         <v>129199870</v>
       </c>
       <c r="F519" s="2">
-        <v>675636733</v>
+        <v>612629348</v>
       </c>
       <c r="G519" s="2">
-        <v>1963363267</v>
+        <v>2026370652</v>
       </c>
       <c r="H519" s="2">
         <v>0</v>
@@ -15256,16 +14102,16 @@
         <v>150000000</v>
       </c>
       <c r="D520" s="2">
-        <v>9000000</v>
+        <v>0</v>
       </c>
       <c r="E520" s="2">
         <v>0</v>
       </c>
       <c r="F520" s="2">
-        <v>9000000</v>
+        <v>0</v>
       </c>
       <c r="G520" s="2">
-        <v>141000000</v>
+        <v>150000000</v>
       </c>
       <c r="H520" s="2">
         <v>0</v>
@@ -15282,16 +14128,16 @@
         <v>2721193000</v>
       </c>
       <c r="D521" s="2">
-        <v>2263795563</v>
+        <v>777673392</v>
       </c>
       <c r="E521" s="2">
         <v>0</v>
       </c>
       <c r="F521" s="2">
-        <v>2263795563</v>
+        <v>777673392</v>
       </c>
       <c r="G521" s="2">
-        <v>457397437</v>
+        <v>1943519608</v>
       </c>
       <c r="H521" s="2">
         <v>0</v>
@@ -15308,16 +14154,16 @@
         <v>9794675000</v>
       </c>
       <c r="D522" s="2">
-        <v>8772973347</v>
+        <v>4877544282</v>
       </c>
       <c r="E522" s="2">
         <v>3607897</v>
       </c>
       <c r="F522" s="2">
-        <v>8776581244</v>
+        <v>4881152179</v>
       </c>
       <c r="G522" s="2">
-        <v>1018093756</v>
+        <v>4913522821</v>
       </c>
       <c r="H522" s="2">
         <v>0</v>
@@ -15412,16 +14258,16 @@
         <v>915811000</v>
       </c>
       <c r="D526" s="2">
-        <v>715028125</v>
+        <v>0</v>
       </c>
       <c r="E526" s="2">
         <v>0</v>
       </c>
       <c r="F526" s="2">
-        <v>715028125</v>
+        <v>0</v>
       </c>
       <c r="G526" s="2">
-        <v>200782875</v>
+        <v>915811000</v>
       </c>
       <c r="H526" s="2">
         <v>0</v>
@@ -15438,16 +14284,16 @@
         <v>1750000000</v>
       </c>
       <c r="D527" s="2">
-        <v>957373034</v>
+        <v>498500000</v>
       </c>
       <c r="E527" s="2">
         <v>0</v>
       </c>
       <c r="F527" s="2">
-        <v>957373034</v>
+        <v>498500000</v>
       </c>
       <c r="G527" s="2">
-        <v>792626966</v>
+        <v>1251500000</v>
       </c>
       <c r="H527" s="2">
         <v>0</v>
@@ -15490,16 +14336,16 @@
         <v>483750000</v>
       </c>
       <c r="D529" s="2">
-        <v>114815000</v>
+        <v>14815000</v>
       </c>
       <c r="E529" s="2">
         <v>68355000</v>
       </c>
       <c r="F529" s="2">
-        <v>183170000</v>
+        <v>83170000</v>
       </c>
       <c r="G529" s="2">
-        <v>300580000</v>
+        <v>400580000</v>
       </c>
       <c r="H529" s="2">
         <v>161250000</v>
@@ -15675,13 +14521,13 @@
         <v>17298750</v>
       </c>
       <c r="E536" s="2">
-        <v>65252500</v>
+        <v>64965000</v>
       </c>
       <c r="F536" s="2">
-        <v>82551250</v>
+        <v>82263750</v>
       </c>
       <c r="G536" s="2">
-        <v>254251250</v>
+        <v>254538750</v>
       </c>
       <c r="H536" s="2">
         <v>112267500</v>
@@ -15753,13 +14599,13 @@
         <v>0</v>
       </c>
       <c r="E539" s="2">
-        <v>1592659004</v>
+        <v>1592655254</v>
       </c>
       <c r="F539" s="2">
-        <v>1592659004</v>
+        <v>1592655254</v>
       </c>
       <c r="G539" s="2">
-        <v>9096257862</v>
+        <v>9096261612</v>
       </c>
       <c r="H539" s="2">
         <v>0</v>
@@ -15949,7 +14795,7 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B547" s="2">
         <v>58569240973</v>
@@ -15958,16 +14804,16 @@
         <v>57848682223</v>
       </c>
       <c r="D547" s="2">
-        <v>22084748231</v>
+        <v>10131101660</v>
       </c>
       <c r="E547" s="2">
-        <v>4496107832</v>
+        <v>4495816582</v>
       </c>
       <c r="F547" s="2">
-        <v>26580856063</v>
+        <v>14626918242</v>
       </c>
       <c r="G547" s="2">
-        <v>31267826160</v>
+        <v>43221763981</v>
       </c>
       <c r="H547" s="2">
         <v>720558750</v>
@@ -15975,1491 +14821,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74037102-CAE5-4DA3-AC4F-276E222EA2EC}">
-  <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.25" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="60.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="15.265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="15.265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" hidden="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="4">
-        <v>873740000</v>
-      </c>
-      <c r="C2" s="5">
-        <f>B2</f>
-        <v>873740000</v>
-      </c>
-      <c r="D2" s="5">
-        <f>C2/2</f>
-        <v>436870000</v>
-      </c>
-      <c r="E2" s="4">
-        <f>IF(B2="","",G2-F2)</f>
-        <v>404360000</v>
-      </c>
-      <c r="F2" s="5">
-        <v>35605052</v>
-      </c>
-      <c r="G2" s="5">
-        <v>439965052</v>
-      </c>
-      <c r="H2" s="4">
-        <f>IF(B2="","",D2-G2)</f>
-        <v>-3095052</v>
-      </c>
-      <c r="I2" s="4">
-        <f>IF(B2="","",C2-D2)</f>
-        <v>436870000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5">
-        <f t="shared" ref="C3:C27" si="0">B3</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="5">
-        <f t="shared" ref="D3:D27" si="1">C3/2</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="4" t="str">
-        <f t="shared" ref="E3:E53" si="2">IF(B3="","",G3-F3)</f>
-        <v/>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="4" t="str">
-        <f t="shared" ref="H3:H53" si="3">IF(B3="","",D3-G3)</f>
-        <v/>
-      </c>
-      <c r="I3" s="4" t="str">
-        <f t="shared" ref="I3:I53" si="4">IF(B3="","",C3-D3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E4" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I4" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D5" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I5" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I6" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I7" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I8" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D9" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E9" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I9" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D10" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E10" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I10" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D11" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I11" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D12" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I12" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D13" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I13" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D14" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D15" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I15" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D16" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D17" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E17" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I17" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D18" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E18" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B19" s="4">
-        <v>474786000</v>
-      </c>
-      <c r="C19" s="5">
-        <f t="shared" si="0"/>
-        <v>474786000</v>
-      </c>
-      <c r="D19" s="5">
-        <f t="shared" si="1"/>
-        <v>237393000</v>
-      </c>
-      <c r="E19" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="4">
-        <f t="shared" si="3"/>
-        <v>237393000</v>
-      </c>
-      <c r="I19" s="4">
-        <f t="shared" si="4"/>
-        <v>237393000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B20" s="4">
-        <v>208425000</v>
-      </c>
-      <c r="C20" s="5">
-        <f t="shared" si="0"/>
-        <v>208425000</v>
-      </c>
-      <c r="D20" s="5">
-        <f t="shared" si="1"/>
-        <v>104212500</v>
-      </c>
-      <c r="E20" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="4">
-        <f t="shared" si="3"/>
-        <v>104212500</v>
-      </c>
-      <c r="I20" s="4">
-        <f t="shared" si="4"/>
-        <v>104212500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="4">
-        <v>20000000</v>
-      </c>
-      <c r="C21" s="5">
-        <f>B21</f>
-        <v>20000000</v>
-      </c>
-      <c r="D21" s="5">
-        <v>13970000</v>
-      </c>
-      <c r="E21" s="4">
-        <f t="shared" si="2"/>
-        <v>13970000</v>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5">
-        <v>13970000</v>
-      </c>
-      <c r="H21" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="4">
-        <f t="shared" si="4"/>
-        <v>6030000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>118</v>
-      </c>
-      <c r="B22" s="4">
-        <v>220000000</v>
-      </c>
-      <c r="C22" s="5">
-        <f t="shared" si="0"/>
-        <v>220000000</v>
-      </c>
-      <c r="D22" s="5">
-        <f t="shared" si="1"/>
-        <v>110000000</v>
-      </c>
-      <c r="E22" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="5">
-        <v>29896778</v>
-      </c>
-      <c r="G22" s="5">
-        <v>29896778</v>
-      </c>
-      <c r="H22" s="4">
-        <f t="shared" si="3"/>
-        <v>80103222</v>
-      </c>
-      <c r="I22" s="4">
-        <f t="shared" si="4"/>
-        <v>110000000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>119</v>
-      </c>
-      <c r="B23" s="4">
-        <v>75000000</v>
-      </c>
-      <c r="C23" s="5">
-        <f t="shared" si="0"/>
-        <v>75000000</v>
-      </c>
-      <c r="D23" s="5">
-        <f t="shared" si="1"/>
-        <v>37500000</v>
-      </c>
-      <c r="E23" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="4">
-        <f t="shared" si="3"/>
-        <v>37500000</v>
-      </c>
-      <c r="I23" s="4">
-        <f t="shared" si="4"/>
-        <v>37500000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D24" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E24" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D25" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E25" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I25" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="4">
-        <v>60000000</v>
-      </c>
-      <c r="C26" s="5">
-        <f t="shared" si="0"/>
-        <v>60000000</v>
-      </c>
-      <c r="D26" s="5">
-        <f t="shared" si="1"/>
-        <v>30000000</v>
-      </c>
-      <c r="E26" s="4">
-        <f t="shared" si="2"/>
-        <v>9000000</v>
-      </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5">
-        <v>9000000</v>
-      </c>
-      <c r="H26" s="4">
-        <f t="shared" si="3"/>
-        <v>21000000</v>
-      </c>
-      <c r="I26" s="4">
-        <f t="shared" si="4"/>
-        <v>30000000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>123</v>
-      </c>
-      <c r="B27" s="4">
-        <v>45150000</v>
-      </c>
-      <c r="C27" s="5">
-        <f t="shared" si="0"/>
-        <v>45150000</v>
-      </c>
-      <c r="D27" s="5">
-        <f t="shared" si="1"/>
-        <v>22575000</v>
-      </c>
-      <c r="E27" s="4">
-        <f t="shared" si="2"/>
-        <v>6423200</v>
-      </c>
-      <c r="F27" s="5">
-        <v>6119400</v>
-      </c>
-      <c r="G27" s="5">
-        <v>12542600</v>
-      </c>
-      <c r="H27" s="4">
-        <f t="shared" si="3"/>
-        <v>10032400</v>
-      </c>
-      <c r="I27" s="4">
-        <f t="shared" si="4"/>
-        <v>22575000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I29" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>126</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I31" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>128</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I33" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>130</v>
-      </c>
-      <c r="B34" s="4">
-        <v>6000000</v>
-      </c>
-      <c r="C34" s="5">
-        <f>B34</f>
-        <v>6000000</v>
-      </c>
-      <c r="D34" s="5">
-        <f>C34/4</f>
-        <v>1500000</v>
-      </c>
-      <c r="E34" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="4">
-        <f t="shared" si="3"/>
-        <v>1500000</v>
-      </c>
-      <c r="I34" s="4">
-        <f t="shared" si="4"/>
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>131</v>
-      </c>
-      <c r="B35" s="4">
-        <v>41000000</v>
-      </c>
-      <c r="C35" s="5">
-        <f t="shared" ref="C35:C40" si="5">B35</f>
-        <v>41000000</v>
-      </c>
-      <c r="D35" s="5">
-        <f t="shared" ref="D35:D40" si="6">C35/4</f>
-        <v>10250000</v>
-      </c>
-      <c r="E35" s="4">
-        <f t="shared" si="2"/>
-        <v>1997700</v>
-      </c>
-      <c r="F35" s="5">
-        <v>998400</v>
-      </c>
-      <c r="G35" s="5">
-        <v>2996100</v>
-      </c>
-      <c r="H35" s="4">
-        <f t="shared" si="3"/>
-        <v>7253900</v>
-      </c>
-      <c r="I35" s="4">
-        <f t="shared" si="4"/>
-        <v>30750000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>132</v>
-      </c>
-      <c r="B36" s="4">
-        <v>12000000</v>
-      </c>
-      <c r="C36" s="5">
-        <f t="shared" si="5"/>
-        <v>12000000</v>
-      </c>
-      <c r="D36" s="5">
-        <f t="shared" si="6"/>
-        <v>3000000</v>
-      </c>
-      <c r="E36" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="4">
-        <f t="shared" si="3"/>
-        <v>3000000</v>
-      </c>
-      <c r="I36" s="4">
-        <f t="shared" si="4"/>
-        <v>9000000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>133</v>
-      </c>
-      <c r="B37" s="4">
-        <v>171000000</v>
-      </c>
-      <c r="C37" s="5">
-        <f t="shared" si="5"/>
-        <v>171000000</v>
-      </c>
-      <c r="D37" s="5">
-        <f t="shared" si="6"/>
-        <v>42750000</v>
-      </c>
-      <c r="E37" s="4">
-        <f t="shared" si="2"/>
-        <v>5880000</v>
-      </c>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5">
-        <v>5880000</v>
-      </c>
-      <c r="H37" s="4">
-        <f t="shared" si="3"/>
-        <v>36870000</v>
-      </c>
-      <c r="I37" s="4">
-        <f t="shared" si="4"/>
-        <v>128250000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>134</v>
-      </c>
-      <c r="B38" s="4">
-        <v>130000000</v>
-      </c>
-      <c r="C38" s="5">
-        <f t="shared" si="5"/>
-        <v>130000000</v>
-      </c>
-      <c r="D38" s="5">
-        <f t="shared" si="6"/>
-        <v>32500000</v>
-      </c>
-      <c r="E38" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="5">
-        <v>7381250</v>
-      </c>
-      <c r="G38" s="5">
-        <v>7381250</v>
-      </c>
-      <c r="H38" s="4">
-        <f t="shared" si="3"/>
-        <v>25118750</v>
-      </c>
-      <c r="I38" s="4">
-        <f t="shared" si="4"/>
-        <v>97500000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>135</v>
-      </c>
-      <c r="B39" s="4">
-        <v>6660000</v>
-      </c>
-      <c r="C39" s="5">
-        <f t="shared" si="5"/>
-        <v>6660000</v>
-      </c>
-      <c r="D39" s="5">
-        <f t="shared" si="6"/>
-        <v>1665000</v>
-      </c>
-      <c r="E39" s="4">
-        <f t="shared" si="2"/>
-        <v>1665000</v>
-      </c>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5">
-        <v>1665000</v>
-      </c>
-      <c r="H39" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="4">
-        <f t="shared" si="4"/>
-        <v>4995000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>136</v>
-      </c>
-      <c r="B40" s="4">
-        <v>6000000</v>
-      </c>
-      <c r="C40" s="5">
-        <f t="shared" si="5"/>
-        <v>6000000</v>
-      </c>
-      <c r="D40" s="5">
-        <f t="shared" si="6"/>
-        <v>1500000</v>
-      </c>
-      <c r="E40" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="4">
-        <f t="shared" si="3"/>
-        <v>1500000</v>
-      </c>
-      <c r="I40" s="4">
-        <f t="shared" si="4"/>
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>137</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I41" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>138</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I42" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>139</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I43" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>140</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I44" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>141</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I45" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>142</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I46" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>143</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I47" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>144</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I48" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>145</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I49" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>146</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I50" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>147</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I51" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>148</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I52" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>149</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I53" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="B54" s="11">
-        <f>SUM(B2:B53)</f>
-        <v>2349761000</v>
-      </c>
-      <c r="C54" s="11">
-        <f t="shared" ref="C54:I54" si="7">SUM(C2:C53)</f>
-        <v>2349761000</v>
-      </c>
-      <c r="D54" s="11">
-        <f t="shared" si="7"/>
-        <v>1085685500</v>
-      </c>
-      <c r="E54" s="11">
-        <f t="shared" si="7"/>
-        <v>443295900</v>
-      </c>
-      <c r="F54" s="11">
-        <f t="shared" si="7"/>
-        <v>80000880</v>
-      </c>
-      <c r="G54" s="11">
-        <f t="shared" si="7"/>
-        <v>523296780</v>
-      </c>
-      <c r="H54" s="11">
-        <f t="shared" si="7"/>
-        <v>562388720</v>
-      </c>
-      <c r="I54" s="11">
-        <f t="shared" si="7"/>
-        <v>1264075500</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1jAoxgEfH1v+py+BabjE1SWtZrOmBQzll5J+0nEkCC4zpdaAqkqUQlFy6oRCGkgRojK/rMDnTPHDGbW/CMwxXA==" saltValue="rHdoy6qRDxYzetfIY6x9cQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,15 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\RKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{82C2664D-B25D-45A5-832B-E371991628C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD2D7D5-BE50-43FE-A649-0B9F15EC4FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget 3 Juni 2024" sheetId="1" r:id="rId1"/>
+    <sheet name="II PD" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="152">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -288,82 +298,7 @@
     <t>31022000  Sintelis</t>
   </si>
   <si>
-    <t>4112222200  Bbn Penystn Srana Perkeretaapian Fasilitas Dipo-By</t>
-  </si>
-  <si>
-    <t>4221221100  Perawatan Rel BMN</t>
-  </si>
-  <si>
-    <t>4221222200  Perawatan Wesel BMN</t>
-  </si>
-  <si>
-    <t>4221223300  Bbn Jasa Penambahan Balas BMN</t>
-  </si>
-  <si>
-    <t>4221224400  Pemasangan Bantalan BMN</t>
-  </si>
-  <si>
-    <t>4221225500  Perawatan Balas BMN</t>
-  </si>
-  <si>
-    <t>4221226000  Pemecokan BMN</t>
-  </si>
-  <si>
-    <t>4221226006  Perlintasan BMN</t>
-  </si>
-  <si>
-    <t>4221226008  Geometri BMN</t>
-  </si>
-  <si>
-    <t>4221226010  Perbaikan Periodik BMN</t>
-  </si>
-  <si>
-    <t>4221321010  Perawatan Baja Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221322010  Perawatan Cat Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221323010  Perawatan Batu Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221325010  Perawatan Cat Jembatan Kelas 2 BMN</t>
-  </si>
-  <si>
-    <t>4221325013  Perawatan Batu Jembatan Kelas 3 BMN</t>
-  </si>
-  <si>
-    <t>4221325014  Perawatan Beton Jembatan Kelas 3 BMN</t>
-  </si>
-  <si>
     <t>4221600000  Peralatan Khusus Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4222222200  Perawatan Wesel KAI</t>
-  </si>
-  <si>
-    <t>4231120000  PerjlDinas BebanUmum PerawatanPrasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231130000  LAT Beban Umum Perawatan Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231150010  Krt Beban Umum Perawatan Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231151710  Kerumahtanggaan UMDT Beban Umum Perawatan Pras BMN</t>
-  </si>
-  <si>
-    <t>4232152310  Tenaga PJL Alih Daya</t>
-  </si>
-  <si>
-    <t>4271100010  Gaji &amp;Tunjangan Pegawai Operasi Prasarana</t>
-  </si>
-  <si>
-    <t>4271500000  Pakaian Dinas Pegawai Operasi Prasarana</t>
-  </si>
-  <si>
-    <t>32020100  Prasarana</t>
   </si>
   <si>
     <t>4222421110  Transmisi Komunikasi KAI</t>
@@ -395,11 +330,177 @@
   <si>
     <t>35022000  Sintelis Divre IV Tanjungkarang</t>
   </si>
+  <si>
+    <t>1182000000 Persediaan Prasarana Perkeretaapian dan Umum</t>
+  </si>
+  <si>
+    <t>4112222200 Bbn Penystn Srana Perkeretaapian Fasilitas Dipo-By</t>
+  </si>
+  <si>
+    <t>4221221100 Perawatan Rel BMN</t>
+  </si>
+  <si>
+    <t>4221222200 Perawatan Wesel BMN</t>
+  </si>
+  <si>
+    <t>4221223300 Bbn Jasa Penambahan Balas BMN</t>
+  </si>
+  <si>
+    <t>4221224400 Pemasangan Bantalan BMN</t>
+  </si>
+  <si>
+    <t>4221225500 Perawatan Balas BMN</t>
+  </si>
+  <si>
+    <t>4221226000 Pemecokan BMN</t>
+  </si>
+  <si>
+    <t>4221226006 Perlintasan BMN</t>
+  </si>
+  <si>
+    <t>4221226008 Geometri BMN</t>
+  </si>
+  <si>
+    <t>4221226010 Perbaikan Periodik BMN</t>
+  </si>
+  <si>
+    <t>4221321010 Perawatan Baja Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221322010 Perawatan Cat Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221323010 Perawatan Batu Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221325010 Perawatan Cat Jembatan Kelas 2 BMN</t>
+  </si>
+  <si>
+    <t>4221325013 Perawatan Batu Jembatan Kelas 3 BMN</t>
+  </si>
+  <si>
+    <t>4221325014 Perawatan Beton Jembatan Kelas 3 BMN</t>
+  </si>
+  <si>
+    <t>4221424010 Peralatan Luar Sinyal Mekanik BMN</t>
+  </si>
+  <si>
+    <t>4221425010 Pengamanan Perlintasan Sebidang BMN</t>
+  </si>
+  <si>
+    <t>4221427010 Transmisi Komunikasi BMN</t>
+  </si>
+  <si>
+    <t>4221428010 Peralatan Pendukung Sintel BMN</t>
+  </si>
+  <si>
+    <t>4221428014 Catu Daya Sintel BMN</t>
+  </si>
+  <si>
+    <t>4221600000 Peralatan Khusus Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4222222200 Perawatan Wesel KAI</t>
+  </si>
+  <si>
+    <t>4222600000 Peralatan Khusus Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4222800000 Beban BBM Mekanik Prasarana</t>
+  </si>
+  <si>
+    <t>4231110000 Rapat&amp;Akomodasi BbnUmum Prwtn Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231120000 PerjlDinas BebanUmum PerawatanPrasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231130000 LAT Beban Umum Perawatan Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231150010 Krt Beban Umum Perawatan Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231151710 Kerumahtanggaan UMDT Beban Umum Perawatan Pras BMN</t>
+  </si>
+  <si>
+    <t>4232152310 Tenaga PJL Alih Daya</t>
+  </si>
+  <si>
+    <t>4233100000 Rapat&amp;Akomodasi Beban Umum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4233150010 Kerumahtanggaan Beban Umum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4233151710 Kerumahtanggaan UMDT Beban Umum Perawatan Pras KAI</t>
+  </si>
+  <si>
+    <t>4233160010 Inventaris Beban Umum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4233200000 Perjalanan Dinas BebanUmum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4233300000 LAT Beban Umum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4233400000 ATK Beban Umum Perawatan Prasarana KAI</t>
+  </si>
+  <si>
+    <t>4241000000 Beban Penyusutan AT Prasarana Perkeretaapian</t>
+  </si>
+  <si>
+    <t>4242000000 Beban Penyusutan AT Bangunan Kantor</t>
+  </si>
+  <si>
+    <t>4271100010 Gaji &amp;Tunjangan Pegawai Operasi Prasarana</t>
+  </si>
+  <si>
+    <t>4271400000 Lembur dan Perangsang Pegawai Operasi Prasarana</t>
+  </si>
+  <si>
+    <t>4271500000 Pakaian Dinas Pegawai Operasi Prasarana</t>
+  </si>
+  <si>
+    <t>4272100010 Gaji &amp;Tunjangan PegawaiPerawatan Prasarana Unit JJ</t>
+  </si>
+  <si>
+    <t>4272200010 Iuran Pensiun Pegawai Perawatan Prasarana Unit JJ/</t>
+  </si>
+  <si>
+    <t>4272400000 Lembur dan Perangsang Peg PrwtnPrsrna unit JJ/Sntl</t>
+  </si>
+  <si>
+    <t>4272500000 PakaianDinas PegPrwtn PrasaranaUnit JJ/sntl/BY Pra</t>
+  </si>
+  <si>
+    <t>4273100010 Gaji &amp;Tunjangan Pegawai Renwas JJ/Sintel LAA</t>
+  </si>
+  <si>
+    <t>4273400000 Lembur dan Perangsang Pegawai Renwas JJ/Sintel LAA</t>
+  </si>
+  <si>
+    <t>4273500000 Pakaian Dinas Pegawai Renwas JJ/Sintel LAA</t>
+  </si>
+  <si>
+    <t>5400000000 Penyusutan AT Lainnya (Fasilitas Umum)</t>
+  </si>
+  <si>
+    <t>32020100 Prasarana</t>
+  </si>
+  <si>
+    <t>RKAO Disetujui</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -536,7 +637,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -722,6 +823,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -839,7 +946,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -882,14 +989,33 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -917,6 +1043,7 @@
     <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
     <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
@@ -1242,12 +1369,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H547"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="60.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="13.06640625" style="2" customWidth="1"/>
+    <col min="2" max="4" width="15.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.265625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1339,10 +1469,10 @@
         <v>57855713800</v>
       </c>
       <c r="D4" s="2">
-        <v>57455713800</v>
+        <v>52055713800</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>5400000000</v>
       </c>
       <c r="F4" s="2">
         <v>57455713800</v>
@@ -1443,16 +1573,16 @@
         <v>3947046000</v>
       </c>
       <c r="D8" s="2">
-        <v>0</v>
+        <v>39147500</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>39147500</v>
       </c>
       <c r="G8" s="2">
-        <v>3947046000</v>
+        <v>3907898500</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -1651,16 +1781,16 @@
         <v>1200000000</v>
       </c>
       <c r="D16" s="2">
-        <v>0</v>
+        <v>42457000</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>42457000</v>
       </c>
       <c r="G16" s="2">
-        <v>1200000000</v>
+        <v>1157543000</v>
       </c>
       <c r="H16" s="2">
         <v>400000000</v>
@@ -1671,10 +1801,10 @@
         <v>23</v>
       </c>
       <c r="B17" s="2">
-        <v>500000000</v>
+        <v>496414000</v>
       </c>
       <c r="C17" s="2">
-        <v>375000000</v>
+        <v>371414000</v>
       </c>
       <c r="D17" s="2">
         <v>20986164</v>
@@ -1686,7 +1816,7 @@
         <v>20986164</v>
       </c>
       <c r="G17" s="2">
-        <v>354013836</v>
+        <v>350427836</v>
       </c>
       <c r="H17" s="2">
         <v>125000000</v>
@@ -1862,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="2">
-        <v>193087500</v>
+        <v>204850000</v>
       </c>
       <c r="F24" s="2">
-        <v>193087500</v>
+        <v>204850000</v>
       </c>
       <c r="G24" s="2">
-        <v>1673605111</v>
+        <v>1661842611</v>
       </c>
       <c r="H24" s="2">
         <v>625000000</v>
@@ -1914,13 +2044,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="2">
-        <v>413857628</v>
+        <v>414390128</v>
       </c>
       <c r="F26" s="2">
-        <v>413857628</v>
+        <v>414390128</v>
       </c>
       <c r="G26" s="2">
-        <v>3042756576</v>
+        <v>3042224076</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -2217,22 +2347,22 @@
         <v>44</v>
       </c>
       <c r="B38" s="2">
-        <v>361729344454</v>
+        <v>361725758454</v>
       </c>
       <c r="C38" s="2">
-        <v>359311844454</v>
+        <v>359308258454</v>
       </c>
       <c r="D38" s="2">
-        <v>175461180890</v>
+        <v>170142785390</v>
       </c>
       <c r="E38" s="2">
-        <v>48780324773</v>
+        <v>54192619773</v>
       </c>
       <c r="F38" s="2">
-        <v>224241505663</v>
+        <v>224335405163</v>
       </c>
       <c r="G38" s="2">
-        <v>135070338791</v>
+        <v>134972853291</v>
       </c>
       <c r="H38" s="2">
         <v>2417500000</v>
@@ -2249,16 +2379,16 @@
         <v>25194775704</v>
       </c>
       <c r="D39" s="2">
-        <v>15690909964</v>
+        <v>16128909964</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>15690909964</v>
+        <v>16128909964</v>
       </c>
       <c r="G39" s="2">
-        <v>9503865740</v>
+        <v>9065865740</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -2509,10 +2639,10 @@
         <v>4260000000</v>
       </c>
       <c r="D49" s="2">
-        <v>587152114</v>
+        <v>579572114</v>
       </c>
       <c r="E49" s="2">
-        <v>389904675</v>
+        <v>397484675</v>
       </c>
       <c r="F49" s="2">
         <v>977056789</v>
@@ -3263,16 +3393,16 @@
         <v>110897810191</v>
       </c>
       <c r="D78" s="2">
-        <v>19485987003</v>
+        <v>19916407003</v>
       </c>
       <c r="E78" s="2">
-        <v>9035977927</v>
+        <v>9043557927</v>
       </c>
       <c r="F78" s="2">
-        <v>28521964930</v>
+        <v>28959964930</v>
       </c>
       <c r="G78" s="2">
-        <v>82375845261</v>
+        <v>81937845261</v>
       </c>
       <c r="H78" s="2">
         <v>671501500</v>
@@ -3289,16 +3419,16 @@
         <v>4044107500</v>
       </c>
       <c r="D79" s="2">
-        <v>644350000</v>
+        <v>1518071200</v>
       </c>
       <c r="E79" s="2">
         <v>585361000</v>
       </c>
       <c r="F79" s="2">
-        <v>1229711000</v>
+        <v>2103432200</v>
       </c>
       <c r="G79" s="2">
-        <v>2814396500</v>
+        <v>1940675300</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3497,10 +3627,10 @@
         <v>2796520000</v>
       </c>
       <c r="D87" s="2">
-        <v>437704607</v>
+        <v>382331307</v>
       </c>
       <c r="E87" s="2">
-        <v>541996241</v>
+        <v>597369541</v>
       </c>
       <c r="F87" s="2">
         <v>979700848</v>
@@ -3653,10 +3783,10 @@
         <v>1710494400</v>
       </c>
       <c r="D93" s="2">
-        <v>377862600</v>
+        <v>364436500</v>
       </c>
       <c r="E93" s="2">
-        <v>38993000</v>
+        <v>52419100</v>
       </c>
       <c r="F93" s="2">
         <v>416855600</v>
@@ -4173,16 +4303,16 @@
         <v>81718644736</v>
       </c>
       <c r="D113" s="2">
-        <v>18093184625</v>
+        <v>18898106425</v>
       </c>
       <c r="E113" s="2">
-        <v>15413951057</v>
+        <v>15482750457</v>
       </c>
       <c r="F113" s="2">
-        <v>33507135682</v>
+        <v>34380856882</v>
       </c>
       <c r="G113" s="2">
-        <v>48211509054</v>
+        <v>47337787854</v>
       </c>
       <c r="H113" s="2">
         <v>475697500</v>
@@ -4225,16 +4355,16 @@
         <v>435680000</v>
       </c>
       <c r="D115" s="2">
-        <v>8607111</v>
+        <v>39139111</v>
       </c>
       <c r="E115" s="2">
         <v>0</v>
       </c>
       <c r="F115" s="2">
-        <v>8607111</v>
+        <v>39139111</v>
       </c>
       <c r="G115" s="2">
-        <v>427072889</v>
+        <v>396540889</v>
       </c>
       <c r="H115" s="2">
         <v>0</v>
@@ -4563,16 +4693,16 @@
         <v>528750000</v>
       </c>
       <c r="D128" s="2">
-        <v>0</v>
+        <v>497734500</v>
       </c>
       <c r="E128" s="2">
         <v>0</v>
       </c>
       <c r="F128" s="2">
-        <v>0</v>
+        <v>497734500</v>
       </c>
       <c r="G128" s="2">
-        <v>528750000</v>
+        <v>31015500</v>
       </c>
       <c r="H128" s="2">
         <v>176250000</v>
@@ -4667,10 +4797,10 @@
         <v>265950000</v>
       </c>
       <c r="D132" s="2">
-        <v>44932500</v>
+        <v>33432500</v>
       </c>
       <c r="E132" s="2">
-        <v>34913500</v>
+        <v>46413500</v>
       </c>
       <c r="F132" s="2">
         <v>79846000</v>
@@ -5057,16 +5187,16 @@
         <v>50726099717</v>
       </c>
       <c r="D147" s="2">
-        <v>16105336153</v>
+        <v>16622102653</v>
       </c>
       <c r="E147" s="2">
-        <v>4348418620</v>
+        <v>4359918620</v>
       </c>
       <c r="F147" s="2">
-        <v>20453754773</v>
+        <v>20982021273</v>
       </c>
       <c r="G147" s="2">
-        <v>30272344944</v>
+        <v>29744078444</v>
       </c>
       <c r="H147" s="2">
         <v>411080000</v>
@@ -5077,10 +5207,10 @@
         <v>8</v>
       </c>
       <c r="B148" s="2">
-        <v>5691755500</v>
+        <v>11383511000</v>
       </c>
       <c r="C148" s="2">
-        <v>5691755500</v>
+        <v>11383511000</v>
       </c>
       <c r="D148" s="2">
         <v>5533217000</v>
@@ -5092,7 +5222,7 @@
         <v>5533217000</v>
       </c>
       <c r="G148" s="2">
-        <v>158538500</v>
+        <v>5850294000</v>
       </c>
       <c r="H148" s="2">
         <v>0</v>
@@ -5103,10 +5233,10 @@
         <v>11</v>
       </c>
       <c r="B149" s="2">
-        <v>874758000</v>
+        <v>1749516000</v>
       </c>
       <c r="C149" s="2">
-        <v>874758000</v>
+        <v>1749516000</v>
       </c>
       <c r="D149" s="2">
         <v>872621317</v>
@@ -5118,7 +5248,7 @@
         <v>872621317</v>
       </c>
       <c r="G149" s="2">
-        <v>2136683</v>
+        <v>876894683</v>
       </c>
       <c r="H149" s="2">
         <v>0</v>
@@ -5155,10 +5285,10 @@
         <v>13</v>
       </c>
       <c r="B151" s="2">
-        <v>249837500</v>
+        <v>499675000</v>
       </c>
       <c r="C151" s="2">
-        <v>249837500</v>
+        <v>499675000</v>
       </c>
       <c r="D151" s="2">
         <v>106240051</v>
@@ -5170,7 +5300,7 @@
         <v>106240051</v>
       </c>
       <c r="G151" s="2">
-        <v>143597449</v>
+        <v>393434949</v>
       </c>
       <c r="H151" s="2">
         <v>0</v>
@@ -5181,10 +5311,10 @@
         <v>14</v>
       </c>
       <c r="B152" s="2">
-        <v>435218500</v>
+        <v>870437000</v>
       </c>
       <c r="C152" s="2">
-        <v>435218500</v>
+        <v>870437000</v>
       </c>
       <c r="D152" s="2">
         <v>72346470</v>
@@ -5196,7 +5326,7 @@
         <v>80661470</v>
       </c>
       <c r="G152" s="2">
-        <v>354557030</v>
+        <v>789775530</v>
       </c>
       <c r="H152" s="2">
         <v>0</v>
@@ -5207,10 +5337,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="2">
-        <v>196881500</v>
+        <v>393763000</v>
       </c>
       <c r="C153" s="2">
-        <v>196881500</v>
+        <v>393763000</v>
       </c>
       <c r="D153" s="2">
         <v>0</v>
@@ -5222,7 +5352,7 @@
         <v>10224916</v>
       </c>
       <c r="G153" s="2">
-        <v>186656584</v>
+        <v>383538084</v>
       </c>
       <c r="H153" s="2">
         <v>0</v>
@@ -5233,10 +5363,10 @@
         <v>16</v>
       </c>
       <c r="B154" s="2">
-        <v>1155703000</v>
+        <v>1702406000</v>
       </c>
       <c r="C154" s="2">
-        <v>1155703000</v>
+        <v>1702406000</v>
       </c>
       <c r="D154" s="2">
         <v>297962777</v>
@@ -5248,7 +5378,7 @@
         <v>394640336</v>
       </c>
       <c r="G154" s="2">
-        <v>761062664</v>
+        <v>1307765664</v>
       </c>
       <c r="H154" s="2">
         <v>0</v>
@@ -5259,10 +5389,10 @@
         <v>49</v>
       </c>
       <c r="B155" s="2">
-        <v>231680000</v>
+        <v>463360000</v>
       </c>
       <c r="C155" s="2">
-        <v>231680000</v>
+        <v>463360000</v>
       </c>
       <c r="D155" s="2">
         <v>22153380</v>
@@ -5274,7 +5404,7 @@
         <v>22153380</v>
       </c>
       <c r="G155" s="2">
-        <v>209526620</v>
+        <v>441206620</v>
       </c>
       <c r="H155" s="2">
         <v>0</v>
@@ -5285,10 +5415,10 @@
         <v>50</v>
       </c>
       <c r="B156" s="2">
-        <v>498478000</v>
+        <v>996956000</v>
       </c>
       <c r="C156" s="2">
-        <v>498478000</v>
+        <v>996956000</v>
       </c>
       <c r="D156" s="2">
         <v>0</v>
@@ -5300,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="G156" s="2">
-        <v>498478000</v>
+        <v>996956000</v>
       </c>
       <c r="H156" s="2">
         <v>0</v>
@@ -5311,10 +5441,10 @@
         <v>51</v>
       </c>
       <c r="B157" s="2">
-        <v>158995000</v>
+        <v>317990000</v>
       </c>
       <c r="C157" s="2">
-        <v>158995000</v>
+        <v>317990000</v>
       </c>
       <c r="D157" s="2">
         <v>3857000</v>
@@ -5326,7 +5456,7 @@
         <v>3857000</v>
       </c>
       <c r="G157" s="2">
-        <v>155138000</v>
+        <v>314133000</v>
       </c>
       <c r="H157" s="2">
         <v>0</v>
@@ -5337,10 +5467,10 @@
         <v>52</v>
       </c>
       <c r="B158" s="2">
-        <v>1213930000</v>
+        <v>2427860000</v>
       </c>
       <c r="C158" s="2">
-        <v>1213930000</v>
+        <v>2427860000</v>
       </c>
       <c r="D158" s="2">
         <v>48285000</v>
@@ -5352,7 +5482,7 @@
         <v>48285000</v>
       </c>
       <c r="G158" s="2">
-        <v>1165645000</v>
+        <v>2379575000</v>
       </c>
       <c r="H158" s="2">
         <v>0</v>
@@ -5363,10 +5493,10 @@
         <v>54</v>
       </c>
       <c r="B159" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="C159" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="D159" s="2">
         <v>38082500</v>
@@ -5378,7 +5508,7 @@
         <v>46857638</v>
       </c>
       <c r="G159" s="2">
-        <v>203142362</v>
+        <v>453142362</v>
       </c>
       <c r="H159" s="2">
         <v>0</v>
@@ -5389,10 +5519,10 @@
         <v>77</v>
       </c>
       <c r="B160" s="2">
-        <v>39449000</v>
+        <v>78898000</v>
       </c>
       <c r="C160" s="2">
-        <v>39449000</v>
+        <v>78898000</v>
       </c>
       <c r="D160" s="2">
         <v>0</v>
@@ -5404,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="G160" s="2">
-        <v>39449000</v>
+        <v>78898000</v>
       </c>
       <c r="H160" s="2">
         <v>0</v>
@@ -5415,10 +5545,10 @@
         <v>56</v>
       </c>
       <c r="B161" s="2">
-        <v>433971000</v>
+        <v>867942000</v>
       </c>
       <c r="C161" s="2">
-        <v>433971000</v>
+        <v>867942000</v>
       </c>
       <c r="D161" s="2">
         <v>0</v>
@@ -5430,7 +5560,7 @@
         <v>0</v>
       </c>
       <c r="G161" s="2">
-        <v>433971000</v>
+        <v>867942000</v>
       </c>
       <c r="H161" s="2">
         <v>0</v>
@@ -5441,10 +5571,10 @@
         <v>22</v>
       </c>
       <c r="B162" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="C162" s="2">
-        <v>125000000</v>
+        <v>187500000</v>
       </c>
       <c r="D162" s="2">
         <v>0</v>
@@ -5456,10 +5586,10 @@
         <v>0</v>
       </c>
       <c r="G162" s="2">
-        <v>125000000</v>
+        <v>187500000</v>
       </c>
       <c r="H162" s="2">
-        <v>0</v>
+        <v>62500000</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.45">
@@ -5467,10 +5597,10 @@
         <v>57</v>
       </c>
       <c r="B163" s="2">
-        <v>45045000</v>
+        <v>90090000</v>
       </c>
       <c r="C163" s="2">
-        <v>45045000</v>
+        <v>90090000</v>
       </c>
       <c r="D163" s="2">
         <v>11205000</v>
@@ -5482,7 +5612,7 @@
         <v>11205000</v>
       </c>
       <c r="G163" s="2">
-        <v>33840000</v>
+        <v>78885000</v>
       </c>
       <c r="H163" s="2">
         <v>0</v>
@@ -5493,10 +5623,10 @@
         <v>24</v>
       </c>
       <c r="B164" s="2">
-        <v>33075000</v>
+        <v>132300000</v>
       </c>
       <c r="C164" s="2">
-        <v>33075000</v>
+        <v>132300000</v>
       </c>
       <c r="D164" s="2">
         <v>0</v>
@@ -5508,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="G164" s="2">
-        <v>33075000</v>
+        <v>132300000</v>
       </c>
       <c r="H164" s="2">
         <v>0</v>
@@ -5519,22 +5649,22 @@
         <v>58</v>
       </c>
       <c r="B165" s="2">
-        <v>592250000</v>
+        <v>2369000000</v>
       </c>
       <c r="C165" s="2">
-        <v>592250000</v>
+        <v>2369000000</v>
       </c>
       <c r="D165" s="2">
-        <v>269200</v>
+        <v>0</v>
       </c>
       <c r="E165" s="2">
-        <v>346245306</v>
+        <v>346514506</v>
       </c>
       <c r="F165" s="2">
         <v>346514506</v>
       </c>
       <c r="G165" s="2">
-        <v>245735494</v>
+        <v>2022485494</v>
       </c>
       <c r="H165" s="2">
         <v>0</v>
@@ -5545,10 +5675,10 @@
         <v>25</v>
       </c>
       <c r="B166" s="2">
-        <v>45000000</v>
+        <v>180000000</v>
       </c>
       <c r="C166" s="2">
-        <v>45000000</v>
+        <v>135000000</v>
       </c>
       <c r="D166" s="2">
         <v>28592500</v>
@@ -5560,10 +5690,10 @@
         <v>38592500</v>
       </c>
       <c r="G166" s="2">
-        <v>6407500</v>
+        <v>96407500</v>
       </c>
       <c r="H166" s="2">
-        <v>0</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.45">
@@ -5571,10 +5701,10 @@
         <v>26</v>
       </c>
       <c r="B167" s="2">
-        <v>136250000</v>
+        <v>545000000</v>
       </c>
       <c r="C167" s="2">
-        <v>136250000</v>
+        <v>408750000</v>
       </c>
       <c r="D167" s="2">
         <v>55881809</v>
@@ -5586,10 +5716,10 @@
         <v>134443944</v>
       </c>
       <c r="G167" s="2">
-        <v>1806056</v>
+        <v>274306056</v>
       </c>
       <c r="H167" s="2">
-        <v>0</v>
+        <v>136250000</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.45">
@@ -5597,10 +5727,10 @@
         <v>27</v>
       </c>
       <c r="B168" s="2">
-        <v>21750000</v>
+        <v>87000000</v>
       </c>
       <c r="C168" s="2">
-        <v>21750000</v>
+        <v>87000000</v>
       </c>
       <c r="D168" s="2">
         <v>0</v>
@@ -5612,7 +5742,7 @@
         <v>14461500</v>
       </c>
       <c r="G168" s="2">
-        <v>7288500</v>
+        <v>72538500</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
@@ -5623,10 +5753,10 @@
         <v>28</v>
       </c>
       <c r="B169" s="2">
-        <v>146550000</v>
+        <v>586200000</v>
       </c>
       <c r="C169" s="2">
-        <v>146550000</v>
+        <v>439650000</v>
       </c>
       <c r="D169" s="2">
         <v>114790302</v>
@@ -5638,10 +5768,10 @@
         <v>114790302</v>
       </c>
       <c r="G169" s="2">
-        <v>31759698</v>
+        <v>324859698</v>
       </c>
       <c r="H169" s="2">
-        <v>0</v>
+        <v>146550000</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.45">
@@ -5649,10 +5779,10 @@
         <v>29</v>
       </c>
       <c r="B170" s="2">
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
       <c r="C170" s="2">
-        <v>5000000</v>
+        <v>15000000</v>
       </c>
       <c r="D170" s="2">
         <v>0</v>
@@ -5664,10 +5794,10 @@
         <v>3000000</v>
       </c>
       <c r="G170" s="2">
-        <v>2000000</v>
+        <v>12000000</v>
       </c>
       <c r="H170" s="2">
-        <v>0</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.45">
@@ -5675,10 +5805,10 @@
         <v>30</v>
       </c>
       <c r="B171" s="2">
-        <v>54100500</v>
+        <v>216402000</v>
       </c>
       <c r="C171" s="2">
-        <v>54100500</v>
+        <v>162301500</v>
       </c>
       <c r="D171" s="2">
         <v>0</v>
@@ -5690,10 +5820,10 @@
         <v>37528000</v>
       </c>
       <c r="G171" s="2">
-        <v>16572500</v>
+        <v>124773500</v>
       </c>
       <c r="H171" s="2">
-        <v>0</v>
+        <v>54100500</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.45">
@@ -5701,10 +5831,10 @@
         <v>31</v>
       </c>
       <c r="B172" s="2">
-        <v>12000000</v>
+        <v>48000000</v>
       </c>
       <c r="C172" s="2">
-        <v>12000000</v>
+        <v>48000000</v>
       </c>
       <c r="D172" s="2">
         <v>6889220</v>
@@ -5716,7 +5846,7 @@
         <v>6889220</v>
       </c>
       <c r="G172" s="2">
-        <v>5110780</v>
+        <v>41110780</v>
       </c>
       <c r="H172" s="2">
         <v>0</v>
@@ -5935,25 +6065,25 @@
         <v>78</v>
       </c>
       <c r="B181" s="2">
-        <v>30446840487</v>
+        <v>44576468987</v>
       </c>
       <c r="C181" s="2">
-        <v>30446840487</v>
+        <v>44127068487</v>
       </c>
       <c r="D181" s="2">
-        <v>7212393526</v>
+        <v>7212124326</v>
       </c>
       <c r="E181" s="2">
-        <v>3268211908</v>
+        <v>3268481108</v>
       </c>
       <c r="F181" s="2">
         <v>10480605434</v>
       </c>
       <c r="G181" s="2">
-        <v>19966235053</v>
+        <v>33646463053</v>
       </c>
       <c r="H181" s="2">
-        <v>0</v>
+        <v>449400500</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.45">
@@ -5961,10 +6091,10 @@
         <v>8</v>
       </c>
       <c r="B182" s="2">
-        <v>3658728280</v>
+        <v>7317456560</v>
       </c>
       <c r="C182" s="2">
-        <v>3658728280</v>
+        <v>7317456560</v>
       </c>
       <c r="D182" s="2">
         <v>2851419420</v>
@@ -5976,7 +6106,7 @@
         <v>2851419420</v>
       </c>
       <c r="G182" s="2">
-        <v>807308860</v>
+        <v>4466037140</v>
       </c>
       <c r="H182" s="2">
         <v>0</v>
@@ -6065,10 +6195,10 @@
         <v>11</v>
       </c>
       <c r="B186" s="2">
-        <v>1515061000</v>
+        <v>3030122000</v>
       </c>
       <c r="C186" s="2">
-        <v>1515061000</v>
+        <v>3030122000</v>
       </c>
       <c r="D186" s="2">
         <v>461381691</v>
@@ -6080,7 +6210,7 @@
         <v>461381691</v>
       </c>
       <c r="G186" s="2">
-        <v>1053679309</v>
+        <v>2568740309</v>
       </c>
       <c r="H186" s="2">
         <v>0</v>
@@ -6091,10 +6221,10 @@
         <v>12</v>
       </c>
       <c r="B187" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="C187" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="D187" s="2">
         <v>0</v>
@@ -6106,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G187" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="H187" s="2">
         <v>0</v>
@@ -6117,10 +6247,10 @@
         <v>48</v>
       </c>
       <c r="B188" s="2">
-        <v>227500000</v>
+        <v>455000000</v>
       </c>
       <c r="C188" s="2">
-        <v>227500000</v>
+        <v>455000000</v>
       </c>
       <c r="D188" s="2">
         <v>5081445</v>
@@ -6132,7 +6262,7 @@
         <v>5081445</v>
       </c>
       <c r="G188" s="2">
-        <v>222418555</v>
+        <v>449918555</v>
       </c>
       <c r="H188" s="2">
         <v>0</v>
@@ -6143,22 +6273,22 @@
         <v>13</v>
       </c>
       <c r="B189" s="2">
-        <v>234500000</v>
+        <v>469000000</v>
       </c>
       <c r="C189" s="2">
-        <v>234500000</v>
+        <v>469000000</v>
       </c>
       <c r="D189" s="2">
-        <v>49635000</v>
+        <v>44160000</v>
       </c>
       <c r="E189" s="2">
-        <v>0</v>
+        <v>5475000</v>
       </c>
       <c r="F189" s="2">
         <v>49635000</v>
       </c>
       <c r="G189" s="2">
-        <v>184865000</v>
+        <v>419365000</v>
       </c>
       <c r="H189" s="2">
         <v>0</v>
@@ -6169,10 +6299,10 @@
         <v>14</v>
       </c>
       <c r="B190" s="2">
-        <v>200000000</v>
+        <v>400000000</v>
       </c>
       <c r="C190" s="2">
-        <v>200000000</v>
+        <v>400000000</v>
       </c>
       <c r="D190" s="2">
         <v>51500000</v>
@@ -6184,7 +6314,7 @@
         <v>51500000</v>
       </c>
       <c r="G190" s="2">
-        <v>148500000</v>
+        <v>348500000</v>
       </c>
       <c r="H190" s="2">
         <v>0</v>
@@ -6195,10 +6325,10 @@
         <v>15</v>
       </c>
       <c r="B191" s="2">
-        <v>304500000</v>
+        <v>609000000</v>
       </c>
       <c r="C191" s="2">
-        <v>304500000</v>
+        <v>609000000</v>
       </c>
       <c r="D191" s="2">
         <v>88477869</v>
@@ -6210,7 +6340,7 @@
         <v>135362869</v>
       </c>
       <c r="G191" s="2">
-        <v>169137131</v>
+        <v>473637131</v>
       </c>
       <c r="H191" s="2">
         <v>0</v>
@@ -6221,10 +6351,10 @@
         <v>16</v>
       </c>
       <c r="B192" s="2">
-        <v>931325000</v>
+        <v>1862650000</v>
       </c>
       <c r="C192" s="2">
-        <v>931325000</v>
+        <v>1862650000</v>
       </c>
       <c r="D192" s="2">
         <v>281432200</v>
@@ -6236,7 +6366,7 @@
         <v>341319546</v>
       </c>
       <c r="G192" s="2">
-        <v>590005454</v>
+        <v>1521330454</v>
       </c>
       <c r="H192" s="2">
         <v>0</v>
@@ -6247,10 +6377,10 @@
         <v>49</v>
       </c>
       <c r="B193" s="2">
-        <v>140500000</v>
+        <v>281000000</v>
       </c>
       <c r="C193" s="2">
-        <v>140500000</v>
+        <v>281000000</v>
       </c>
       <c r="D193" s="2">
         <v>30944688</v>
@@ -6262,7 +6392,7 @@
         <v>30944688</v>
       </c>
       <c r="G193" s="2">
-        <v>109555312</v>
+        <v>250055312</v>
       </c>
       <c r="H193" s="2">
         <v>0</v>
@@ -6273,10 +6403,10 @@
         <v>50</v>
       </c>
       <c r="B194" s="2">
-        <v>475000000</v>
+        <v>950000000</v>
       </c>
       <c r="C194" s="2">
-        <v>475000000</v>
+        <v>950000000</v>
       </c>
       <c r="D194" s="2">
         <v>0</v>
@@ -6288,7 +6418,7 @@
         <v>0</v>
       </c>
       <c r="G194" s="2">
-        <v>475000000</v>
+        <v>950000000</v>
       </c>
       <c r="H194" s="2">
         <v>0</v>
@@ -6299,10 +6429,10 @@
         <v>51</v>
       </c>
       <c r="B195" s="2">
-        <v>25000000</v>
+        <v>50000000</v>
       </c>
       <c r="C195" s="2">
-        <v>25000000</v>
+        <v>50000000</v>
       </c>
       <c r="D195" s="2">
         <v>4883000</v>
@@ -6314,7 +6444,7 @@
         <v>4883000</v>
       </c>
       <c r="G195" s="2">
-        <v>20117000</v>
+        <v>45117000</v>
       </c>
       <c r="H195" s="2">
         <v>0</v>
@@ -6325,10 +6455,10 @@
         <v>52</v>
       </c>
       <c r="B196" s="2">
-        <v>745637500</v>
+        <v>1491275000</v>
       </c>
       <c r="C196" s="2">
-        <v>745637500</v>
+        <v>1491275000</v>
       </c>
       <c r="D196" s="2">
         <v>599680000</v>
@@ -6340,7 +6470,7 @@
         <v>666445000</v>
       </c>
       <c r="G196" s="2">
-        <v>79192500</v>
+        <v>824830000</v>
       </c>
       <c r="H196" s="2">
         <v>0</v>
@@ -6351,10 +6481,10 @@
         <v>53</v>
       </c>
       <c r="B197" s="2">
-        <v>20000000</v>
+        <v>40000000</v>
       </c>
       <c r="C197" s="2">
-        <v>20000000</v>
+        <v>40000000</v>
       </c>
       <c r="D197" s="2">
         <v>6475000</v>
@@ -6366,7 +6496,7 @@
         <v>6475000</v>
       </c>
       <c r="G197" s="2">
-        <v>13525000</v>
+        <v>33525000</v>
       </c>
       <c r="H197" s="2">
         <v>0</v>
@@ -6377,10 +6507,10 @@
         <v>77</v>
       </c>
       <c r="B198" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="C198" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="D198" s="2">
         <v>0</v>
@@ -6392,7 +6522,7 @@
         <v>0</v>
       </c>
       <c r="G198" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="H198" s="2">
         <v>0</v>
@@ -6403,10 +6533,10 @@
         <v>56</v>
       </c>
       <c r="B199" s="2">
-        <v>254500000</v>
+        <v>509000000</v>
       </c>
       <c r="C199" s="2">
-        <v>254500000</v>
+        <v>509000000</v>
       </c>
       <c r="D199" s="2">
         <v>18232600</v>
@@ -6418,7 +6548,7 @@
         <v>18232600</v>
       </c>
       <c r="G199" s="2">
-        <v>236267400</v>
+        <v>490767400</v>
       </c>
       <c r="H199" s="2">
         <v>0</v>
@@ -6429,10 +6559,10 @@
         <v>22</v>
       </c>
       <c r="B200" s="2">
-        <v>75000000</v>
+        <v>150000000</v>
       </c>
       <c r="C200" s="2">
-        <v>75000000</v>
+        <v>112500000</v>
       </c>
       <c r="D200" s="2">
         <v>0</v>
@@ -6444,10 +6574,10 @@
         <v>41856000</v>
       </c>
       <c r="G200" s="2">
-        <v>33144000</v>
+        <v>70644000</v>
       </c>
       <c r="H200" s="2">
-        <v>0</v>
+        <v>37500000</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.45">
@@ -6455,22 +6585,22 @@
         <v>57</v>
       </c>
       <c r="B201" s="2">
-        <v>160050000</v>
+        <v>320100000</v>
       </c>
       <c r="C201" s="2">
-        <v>160050000</v>
+        <v>320100000</v>
       </c>
       <c r="D201" s="2">
-        <v>44525000</v>
+        <v>0</v>
       </c>
       <c r="E201" s="2">
-        <v>27250000</v>
+        <v>71775000</v>
       </c>
       <c r="F201" s="2">
         <v>71775000</v>
       </c>
       <c r="G201" s="2">
-        <v>88275000</v>
+        <v>248325000</v>
       </c>
       <c r="H201" s="2">
         <v>0</v>
@@ -6481,10 +6611,10 @@
         <v>58</v>
       </c>
       <c r="B202" s="2">
-        <v>642500000</v>
+        <v>2570000000</v>
       </c>
       <c r="C202" s="2">
-        <v>642500000</v>
+        <v>2570000000</v>
       </c>
       <c r="D202" s="2">
         <v>0</v>
@@ -6496,7 +6626,7 @@
         <v>394857596</v>
       </c>
       <c r="G202" s="2">
-        <v>247642404</v>
+        <v>2175142404</v>
       </c>
       <c r="H202" s="2">
         <v>0</v>
@@ -6507,10 +6637,10 @@
         <v>25</v>
       </c>
       <c r="B203" s="2">
-        <v>69718811</v>
+        <v>130000000</v>
       </c>
       <c r="C203" s="2">
-        <v>69718811</v>
+        <v>97500000</v>
       </c>
       <c r="D203" s="2">
         <v>3400000</v>
@@ -6522,10 +6652,10 @@
         <v>35818811</v>
       </c>
       <c r="G203" s="2">
-        <v>33900000</v>
+        <v>61681189</v>
       </c>
       <c r="H203" s="2">
-        <v>0</v>
+        <v>32500000</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.45">
@@ -6533,10 +6663,10 @@
         <v>26</v>
       </c>
       <c r="B204" s="2">
-        <v>128511500</v>
+        <v>514046000</v>
       </c>
       <c r="C204" s="2">
-        <v>128511500</v>
+        <v>385534500</v>
       </c>
       <c r="D204" s="2">
         <v>23159000</v>
@@ -6548,10 +6678,10 @@
         <v>74188500</v>
       </c>
       <c r="G204" s="2">
-        <v>54323000</v>
+        <v>311346000</v>
       </c>
       <c r="H204" s="2">
-        <v>0</v>
+        <v>128511500</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.45">
@@ -6559,10 +6689,10 @@
         <v>27</v>
       </c>
       <c r="B205" s="2">
-        <v>17500000</v>
+        <v>105000000</v>
       </c>
       <c r="C205" s="2">
-        <v>17500000</v>
+        <v>105000000</v>
       </c>
       <c r="D205" s="2">
         <v>0</v>
@@ -6574,7 +6704,7 @@
         <v>17500000</v>
       </c>
       <c r="G205" s="2">
-        <v>0</v>
+        <v>87500000</v>
       </c>
       <c r="H205" s="2">
         <v>0</v>
@@ -6585,25 +6715,25 @@
         <v>28</v>
       </c>
       <c r="B206" s="2">
-        <v>112500000</v>
+        <v>450000000</v>
       </c>
       <c r="C206" s="2">
-        <v>112500000</v>
+        <v>337500000</v>
       </c>
       <c r="D206" s="2">
-        <v>31837000</v>
+        <v>27515000</v>
       </c>
       <c r="E206" s="2">
-        <v>5730000</v>
+        <v>10052000</v>
       </c>
       <c r="F206" s="2">
         <v>37567000</v>
       </c>
       <c r="G206" s="2">
-        <v>74933000</v>
+        <v>299933000</v>
       </c>
       <c r="H206" s="2">
-        <v>0</v>
+        <v>112500000</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.45">
@@ -6611,25 +6741,25 @@
         <v>29</v>
       </c>
       <c r="B207" s="2">
+        <v>165000000</v>
+      </c>
+      <c r="C207" s="2">
+        <v>123750000</v>
+      </c>
+      <c r="D207" s="2">
+        <v>0</v>
+      </c>
+      <c r="E207" s="2">
+        <v>0</v>
+      </c>
+      <c r="F207" s="2">
+        <v>0</v>
+      </c>
+      <c r="G207" s="2">
+        <v>123750000</v>
+      </c>
+      <c r="H207" s="2">
         <v>41250000</v>
-      </c>
-      <c r="C207" s="2">
-        <v>41250000</v>
-      </c>
-      <c r="D207" s="2">
-        <v>0</v>
-      </c>
-      <c r="E207" s="2">
-        <v>0</v>
-      </c>
-      <c r="F207" s="2">
-        <v>0</v>
-      </c>
-      <c r="G207" s="2">
-        <v>41250000</v>
-      </c>
-      <c r="H207" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.45">
@@ -6637,10 +6767,10 @@
         <v>30</v>
       </c>
       <c r="B208" s="2">
-        <v>63000000</v>
+        <v>252000000</v>
       </c>
       <c r="C208" s="2">
-        <v>63000000</v>
+        <v>189000000</v>
       </c>
       <c r="D208" s="2">
         <v>0</v>
@@ -6652,10 +6782,10 @@
         <v>52728250</v>
       </c>
       <c r="G208" s="2">
-        <v>10271750</v>
+        <v>136271750</v>
       </c>
       <c r="H208" s="2">
-        <v>0</v>
+        <v>63000000</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.45">
@@ -6663,10 +6793,10 @@
         <v>79</v>
       </c>
       <c r="B209" s="2">
-        <v>4500000</v>
+        <v>18000000</v>
       </c>
       <c r="C209" s="2">
-        <v>4500000</v>
+        <v>18000000</v>
       </c>
       <c r="D209" s="2">
         <v>1245000</v>
@@ -6678,7 +6808,7 @@
         <v>3257160</v>
       </c>
       <c r="G209" s="2">
-        <v>1242840</v>
+        <v>14742840</v>
       </c>
       <c r="H209" s="2">
         <v>0</v>
@@ -6689,10 +6819,10 @@
         <v>31</v>
       </c>
       <c r="B210" s="2">
-        <v>12500000</v>
+        <v>50000000</v>
       </c>
       <c r="C210" s="2">
-        <v>12500000</v>
+        <v>50000000</v>
       </c>
       <c r="D210" s="2">
         <v>0</v>
@@ -6704,7 +6834,7 @@
         <v>12431950</v>
       </c>
       <c r="G210" s="2">
-        <v>68050</v>
+        <v>37568050</v>
       </c>
       <c r="H210" s="2">
         <v>0</v>
@@ -6923,25 +7053,25 @@
         <v>80</v>
       </c>
       <c r="B219" s="2">
-        <v>31465240899</v>
+        <v>43869608368</v>
       </c>
       <c r="C219" s="2">
-        <v>31465240899</v>
+        <v>43454346868</v>
       </c>
       <c r="D219" s="2">
-        <v>4553308913</v>
+        <v>4498986913</v>
       </c>
       <c r="E219" s="2">
-        <v>4277422190</v>
+        <v>4331744190</v>
       </c>
       <c r="F219" s="2">
         <v>8830731103</v>
       </c>
       <c r="G219" s="2">
-        <v>22634509796</v>
+        <v>34623615765</v>
       </c>
       <c r="H219" s="2">
-        <v>0</v>
+        <v>415261500</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.45">
@@ -6949,22 +7079,22 @@
         <v>8</v>
       </c>
       <c r="B220" s="2">
-        <v>11504360000</v>
+        <v>12264606000</v>
       </c>
       <c r="C220" s="2">
-        <v>11504360000</v>
+        <v>12264606000</v>
       </c>
       <c r="D220" s="2">
-        <v>8529167730</v>
+        <v>9573167730</v>
       </c>
       <c r="E220" s="2">
         <v>36030000</v>
       </c>
       <c r="F220" s="2">
-        <v>8565197730</v>
+        <v>9609197730</v>
       </c>
       <c r="G220" s="2">
-        <v>2939162270</v>
+        <v>2655408270</v>
       </c>
       <c r="H220" s="2">
         <v>0</v>
@@ -6975,10 +7105,10 @@
         <v>11</v>
       </c>
       <c r="B221" s="2">
-        <v>1171703000</v>
+        <v>1126306000</v>
       </c>
       <c r="C221" s="2">
-        <v>1171703000</v>
+        <v>1126306000</v>
       </c>
       <c r="D221" s="2">
         <v>617301007</v>
@@ -6990,7 +7120,7 @@
         <v>617301007</v>
       </c>
       <c r="G221" s="2">
-        <v>554401993</v>
+        <v>509004993</v>
       </c>
       <c r="H221" s="2">
         <v>0</v>
@@ -7001,10 +7131,10 @@
         <v>12</v>
       </c>
       <c r="B222" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="C222" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="D222" s="2">
         <v>0</v>
@@ -7016,7 +7146,7 @@
         <v>0</v>
       </c>
       <c r="G222" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="H222" s="2">
         <v>0</v>
@@ -7027,10 +7157,10 @@
         <v>48</v>
       </c>
       <c r="B223" s="2">
-        <v>247500000</v>
+        <v>495000000</v>
       </c>
       <c r="C223" s="2">
-        <v>247500000</v>
+        <v>495000000</v>
       </c>
       <c r="D223" s="2">
         <v>29117120</v>
@@ -7042,7 +7172,7 @@
         <v>29117120</v>
       </c>
       <c r="G223" s="2">
-        <v>218382880</v>
+        <v>465882880</v>
       </c>
       <c r="H223" s="2">
         <v>0</v>
@@ -7053,10 +7183,10 @@
         <v>13</v>
       </c>
       <c r="B224" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="C224" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="D224" s="2">
         <v>0</v>
@@ -7068,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="G224" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="H224" s="2">
         <v>0</v>
@@ -7079,10 +7209,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="2">
-        <v>655195500</v>
+        <v>1310391000</v>
       </c>
       <c r="C225" s="2">
-        <v>655195500</v>
+        <v>1310391000</v>
       </c>
       <c r="D225" s="2">
         <v>62324038</v>
@@ -7094,7 +7224,7 @@
         <v>162707588</v>
       </c>
       <c r="G225" s="2">
-        <v>492487912</v>
+        <v>1147683412</v>
       </c>
       <c r="H225" s="2">
         <v>0</v>
@@ -7105,10 +7235,10 @@
         <v>16</v>
       </c>
       <c r="B226" s="2">
-        <v>690000000</v>
+        <v>1380000000</v>
       </c>
       <c r="C226" s="2">
-        <v>690000000</v>
+        <v>1380000000</v>
       </c>
       <c r="D226" s="2">
         <v>321145216</v>
@@ -7120,7 +7250,7 @@
         <v>522187216</v>
       </c>
       <c r="G226" s="2">
-        <v>167812784</v>
+        <v>857812784</v>
       </c>
       <c r="H226" s="2">
         <v>0</v>
@@ -7131,10 +7261,10 @@
         <v>49</v>
       </c>
       <c r="B227" s="2">
-        <v>175000000</v>
+        <v>350000000</v>
       </c>
       <c r="C227" s="2">
-        <v>175000000</v>
+        <v>350000000</v>
       </c>
       <c r="D227" s="2">
         <v>0</v>
@@ -7146,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="G227" s="2">
-        <v>175000000</v>
+        <v>350000000</v>
       </c>
       <c r="H227" s="2">
         <v>0</v>
@@ -7157,22 +7287,22 @@
         <v>50</v>
       </c>
       <c r="B228" s="2">
+        <v>497000000</v>
+      </c>
+      <c r="C228" s="2">
+        <v>497000000</v>
+      </c>
+      <c r="D228" s="2">
         <v>496659494</v>
       </c>
-      <c r="C228" s="2">
+      <c r="E228" s="2">
+        <v>0</v>
+      </c>
+      <c r="F228" s="2">
         <v>496659494</v>
       </c>
-      <c r="D228" s="2">
-        <v>0</v>
-      </c>
-      <c r="E228" s="2">
-        <v>0</v>
-      </c>
-      <c r="F228" s="2">
-        <v>0</v>
-      </c>
       <c r="G228" s="2">
-        <v>496659494</v>
+        <v>340506</v>
       </c>
       <c r="H228" s="2">
         <v>0</v>
@@ -7183,10 +7313,10 @@
         <v>51</v>
       </c>
       <c r="B229" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="C229" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="D229" s="2">
         <v>6718000</v>
@@ -7198,7 +7328,7 @@
         <v>6718000</v>
       </c>
       <c r="G229" s="2">
-        <v>43282000</v>
+        <v>93282000</v>
       </c>
       <c r="H229" s="2">
         <v>0</v>
@@ -7209,22 +7339,22 @@
         <v>52</v>
       </c>
       <c r="B230" s="2">
-        <v>2471712500</v>
+        <v>2264065000</v>
       </c>
       <c r="C230" s="2">
-        <v>2471712500</v>
+        <v>2264065000</v>
       </c>
       <c r="D230" s="2">
-        <v>1339680000</v>
+        <v>1986680000</v>
       </c>
       <c r="E230" s="2">
         <v>0</v>
       </c>
       <c r="F230" s="2">
-        <v>1339680000</v>
+        <v>1986680000</v>
       </c>
       <c r="G230" s="2">
-        <v>1132032500</v>
+        <v>277385000</v>
       </c>
       <c r="H230" s="2">
         <v>0</v>
@@ -7235,10 +7365,10 @@
         <v>77</v>
       </c>
       <c r="B231" s="2">
-        <v>15000000</v>
+        <v>30000000</v>
       </c>
       <c r="C231" s="2">
-        <v>15000000</v>
+        <v>30000000</v>
       </c>
       <c r="D231" s="2">
         <v>0</v>
@@ -7250,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="G231" s="2">
-        <v>15000000</v>
+        <v>30000000</v>
       </c>
       <c r="H231" s="2">
         <v>0</v>
@@ -7261,10 +7391,10 @@
         <v>56</v>
       </c>
       <c r="B232" s="2">
-        <v>577500000</v>
+        <v>1155000000</v>
       </c>
       <c r="C232" s="2">
-        <v>577500000</v>
+        <v>1155000000</v>
       </c>
       <c r="D232" s="2">
         <v>495830000</v>
@@ -7276,7 +7406,7 @@
         <v>495830000</v>
       </c>
       <c r="G232" s="2">
-        <v>81670000</v>
+        <v>659170000</v>
       </c>
       <c r="H232" s="2">
         <v>0</v>
@@ -7287,10 +7417,10 @@
         <v>22</v>
       </c>
       <c r="B233" s="2">
-        <v>520000000</v>
+        <v>1040000000</v>
       </c>
       <c r="C233" s="2">
-        <v>520000000</v>
+        <v>780000000</v>
       </c>
       <c r="D233" s="2">
         <v>0</v>
@@ -7302,10 +7432,10 @@
         <v>0</v>
       </c>
       <c r="G233" s="2">
-        <v>520000000</v>
+        <v>780000000</v>
       </c>
       <c r="H233" s="2">
-        <v>0</v>
+        <v>260000000</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.45">
@@ -7313,22 +7443,22 @@
         <v>57</v>
       </c>
       <c r="B234" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="C234" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="D234" s="2">
+        <v>0</v>
+      </c>
+      <c r="E234" s="2">
         <v>32848750</v>
-      </c>
-      <c r="E234" s="2">
-        <v>0</v>
       </c>
       <c r="F234" s="2">
         <v>32848750</v>
       </c>
       <c r="G234" s="2">
-        <v>92151250</v>
+        <v>217151250</v>
       </c>
       <c r="H234" s="2">
         <v>0</v>
@@ -7339,10 +7469,10 @@
         <v>58</v>
       </c>
       <c r="B235" s="2">
-        <v>765894000</v>
+        <v>3063576000</v>
       </c>
       <c r="C235" s="2">
-        <v>765894000</v>
+        <v>3063576000</v>
       </c>
       <c r="D235" s="2">
         <v>0</v>
@@ -7354,7 +7484,7 @@
         <v>396859899</v>
       </c>
       <c r="G235" s="2">
-        <v>369034101</v>
+        <v>2666716101</v>
       </c>
       <c r="H235" s="2">
         <v>0</v>
@@ -7365,10 +7495,10 @@
         <v>25</v>
       </c>
       <c r="B236" s="2">
-        <v>36720850</v>
+        <v>146883400</v>
       </c>
       <c r="C236" s="2">
-        <v>36720850</v>
+        <v>110162550</v>
       </c>
       <c r="D236" s="2">
         <v>10311000</v>
@@ -7380,10 +7510,10 @@
         <v>20271000</v>
       </c>
       <c r="G236" s="2">
-        <v>16449850</v>
+        <v>89891550</v>
       </c>
       <c r="H236" s="2">
-        <v>0</v>
+        <v>36720850</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.45">
@@ -7391,10 +7521,10 @@
         <v>26</v>
       </c>
       <c r="B237" s="2">
-        <v>118079500</v>
+        <v>472318000</v>
       </c>
       <c r="C237" s="2">
-        <v>118079500</v>
+        <v>354238500</v>
       </c>
       <c r="D237" s="2">
         <v>29494000</v>
@@ -7406,10 +7536,10 @@
         <v>81611900</v>
       </c>
       <c r="G237" s="2">
-        <v>36467600</v>
+        <v>272626600</v>
       </c>
       <c r="H237" s="2">
-        <v>0</v>
+        <v>118079500</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.45">
@@ -7417,10 +7547,10 @@
         <v>27</v>
       </c>
       <c r="B238" s="2">
-        <v>24750000</v>
+        <v>99000000</v>
       </c>
       <c r="C238" s="2">
-        <v>24750000</v>
+        <v>99000000</v>
       </c>
       <c r="D238" s="2">
         <v>0</v>
@@ -7432,7 +7562,7 @@
         <v>16500000</v>
       </c>
       <c r="G238" s="2">
-        <v>8250000</v>
+        <v>82500000</v>
       </c>
       <c r="H238" s="2">
         <v>0</v>
@@ -7443,7 +7573,7 @@
         <v>28</v>
       </c>
       <c r="B239" s="2">
-        <v>732016185</v>
+        <v>775000000</v>
       </c>
       <c r="C239" s="2">
         <v>732016185</v>
@@ -7461,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="2">
-        <v>0</v>
+        <v>42983815</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.45">
@@ -7469,10 +7599,10 @@
         <v>30</v>
       </c>
       <c r="B240" s="2">
-        <v>67428000</v>
+        <v>269712000</v>
       </c>
       <c r="C240" s="2">
-        <v>67428000</v>
+        <v>202284000</v>
       </c>
       <c r="D240" s="2">
         <v>0</v>
@@ -7484,10 +7614,10 @@
         <v>50796750</v>
       </c>
       <c r="G240" s="2">
-        <v>16631250</v>
+        <v>151487250</v>
       </c>
       <c r="H240" s="2">
-        <v>0</v>
+        <v>67428000</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.45">
@@ -7495,10 +7625,10 @@
         <v>31</v>
       </c>
       <c r="B241" s="2">
-        <v>15000000</v>
+        <v>60000000</v>
       </c>
       <c r="C241" s="2">
-        <v>15000000</v>
+        <v>60000000</v>
       </c>
       <c r="D241" s="2">
         <v>14997987</v>
@@ -7510,7 +7640,7 @@
         <v>14997987</v>
       </c>
       <c r="G241" s="2">
-        <v>2013</v>
+        <v>45002013</v>
       </c>
       <c r="H241" s="2">
         <v>0</v>
@@ -7729,25 +7859,25 @@
         <v>81</v>
       </c>
       <c r="B250" s="2">
-        <v>42600646349</v>
+        <v>49439984720</v>
       </c>
       <c r="C250" s="2">
-        <v>42600646349</v>
+        <v>48914772555</v>
       </c>
       <c r="D250" s="2">
-        <v>12194794533</v>
+        <v>14349605277</v>
       </c>
       <c r="E250" s="2">
-        <v>4391651962</v>
+        <v>4424500712</v>
       </c>
       <c r="F250" s="2">
-        <v>16586446495</v>
+        <v>18774105989</v>
       </c>
       <c r="G250" s="2">
-        <v>26014199854</v>
+        <v>30140666566</v>
       </c>
       <c r="H250" s="2">
-        <v>0</v>
+        <v>525212165</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.45">
@@ -7943,16 +8073,16 @@
         <v>850000000</v>
       </c>
       <c r="D258" s="2">
-        <v>259809160</v>
+        <v>309489160</v>
       </c>
       <c r="E258" s="2">
         <v>74800000</v>
       </c>
       <c r="F258" s="2">
-        <v>334609160</v>
+        <v>384289160</v>
       </c>
       <c r="G258" s="2">
-        <v>515390840</v>
+        <v>465710840</v>
       </c>
       <c r="H258" s="2">
         <v>0</v>
@@ -8515,10 +8645,10 @@
         <v>13675500</v>
       </c>
       <c r="D280" s="2">
+        <v>0</v>
+      </c>
+      <c r="E280" s="2">
         <v>13582000</v>
-      </c>
-      <c r="E280" s="2">
-        <v>0</v>
       </c>
       <c r="F280" s="2">
         <v>13582000</v>
@@ -8775,16 +8905,16 @@
         <v>45434097707</v>
       </c>
       <c r="D290" s="2">
-        <v>6688481980</v>
+        <v>6724579980</v>
       </c>
       <c r="E290" s="2">
-        <v>5334064446</v>
+        <v>5347646446</v>
       </c>
       <c r="F290" s="2">
-        <v>12022546426</v>
+        <v>12072226426</v>
       </c>
       <c r="G290" s="2">
-        <v>33411551281</v>
+        <v>33361871281</v>
       </c>
       <c r="H290" s="2">
         <v>0</v>
@@ -8853,16 +8983,16 @@
         <v>488774000</v>
       </c>
       <c r="D293" s="2">
-        <v>0</v>
+        <v>472749437</v>
       </c>
       <c r="E293" s="2">
         <v>0</v>
       </c>
       <c r="F293" s="2">
-        <v>0</v>
+        <v>472749437</v>
       </c>
       <c r="G293" s="2">
-        <v>488774000</v>
+        <v>16024563</v>
       </c>
       <c r="H293" s="2">
         <v>0</v>
@@ -8879,16 +9009,16 @@
         <v>498000000</v>
       </c>
       <c r="D294" s="2">
-        <v>0</v>
+        <v>487985800</v>
       </c>
       <c r="E294" s="2">
         <v>0</v>
       </c>
       <c r="F294" s="2">
-        <v>0</v>
+        <v>487985800</v>
       </c>
       <c r="G294" s="2">
-        <v>498000000</v>
+        <v>10014200</v>
       </c>
       <c r="H294" s="2">
         <v>0</v>
@@ -8957,10 +9087,10 @@
         <v>1222108000</v>
       </c>
       <c r="D297" s="2">
-        <v>107724690</v>
+        <v>58082710</v>
       </c>
       <c r="E297" s="2">
-        <v>0</v>
+        <v>49641980</v>
       </c>
       <c r="F297" s="2">
         <v>107724690</v>
@@ -8983,10 +9113,10 @@
         <v>534300000</v>
       </c>
       <c r="D298" s="2">
-        <v>77914500</v>
+        <v>31132500</v>
       </c>
       <c r="E298" s="2">
-        <v>96550828</v>
+        <v>143332828</v>
       </c>
       <c r="F298" s="2">
         <v>174465328</v>
@@ -9087,16 +9217,16 @@
         <v>1882400000</v>
       </c>
       <c r="D302" s="2">
-        <v>210764000</v>
+        <v>1658705000</v>
       </c>
       <c r="E302" s="2">
         <v>0</v>
       </c>
       <c r="F302" s="2">
-        <v>210764000</v>
+        <v>1658705000</v>
       </c>
       <c r="G302" s="2">
-        <v>1671636000</v>
+        <v>223695000</v>
       </c>
       <c r="H302" s="2">
         <v>0</v>
@@ -9295,16 +9425,16 @@
         <v>82504500</v>
       </c>
       <c r="D310" s="2">
-        <v>6850000</v>
+        <v>36154000</v>
       </c>
       <c r="E310" s="2">
         <v>13891000</v>
       </c>
       <c r="F310" s="2">
-        <v>20741000</v>
+        <v>50045000</v>
       </c>
       <c r="G310" s="2">
-        <v>61763500</v>
+        <v>32459500</v>
       </c>
       <c r="H310" s="2">
         <v>27501500</v>
@@ -9347,16 +9477,16 @@
         <v>385800000</v>
       </c>
       <c r="D312" s="2">
-        <v>37890000</v>
+        <v>0</v>
       </c>
       <c r="E312" s="2">
-        <v>3485000</v>
+        <v>37922635</v>
       </c>
       <c r="F312" s="2">
-        <v>41375000</v>
+        <v>37922635</v>
       </c>
       <c r="G312" s="2">
-        <v>344425000</v>
+        <v>347877365</v>
       </c>
       <c r="H312" s="2">
         <v>128600000</v>
@@ -9376,13 +9506,13 @@
         <v>0</v>
       </c>
       <c r="E313" s="2">
-        <v>38303000</v>
+        <v>39065500</v>
       </c>
       <c r="F313" s="2">
-        <v>38303000</v>
+        <v>39065500</v>
       </c>
       <c r="G313" s="2">
-        <v>134197000</v>
+        <v>133434500</v>
       </c>
       <c r="H313" s="2">
         <v>57500000</v>
@@ -9428,13 +9558,13 @@
         <v>0</v>
       </c>
       <c r="E315" s="2">
-        <v>970906178</v>
+        <v>970917428</v>
       </c>
       <c r="F315" s="2">
-        <v>970906178</v>
+        <v>970917428</v>
       </c>
       <c r="G315" s="2">
-        <v>6082886087</v>
+        <v>6082874837</v>
       </c>
       <c r="H315" s="2">
         <v>0</v>
@@ -9633,16 +9763,16 @@
         <v>30454436960</v>
       </c>
       <c r="D323" s="2">
-        <v>2230133911</v>
+        <v>4533800168</v>
       </c>
       <c r="E323" s="2">
-        <v>3123500410</v>
+        <v>3255135775</v>
       </c>
       <c r="F323" s="2">
-        <v>5353634321</v>
+        <v>7788935943</v>
       </c>
       <c r="G323" s="2">
-        <v>25100802639</v>
+        <v>22665501017</v>
       </c>
       <c r="H323" s="2">
         <v>260139500</v>
@@ -9679,10 +9809,10 @@
         <v>11</v>
       </c>
       <c r="B325" s="2">
-        <v>2948978000</v>
+        <v>2948978291</v>
       </c>
       <c r="C325" s="2">
-        <v>2948978000</v>
+        <v>2948978291</v>
       </c>
       <c r="D325" s="2">
         <v>2788546174</v>
@@ -9694,7 +9824,7 @@
         <v>2837419124</v>
       </c>
       <c r="G325" s="2">
-        <v>111558876</v>
+        <v>111559167</v>
       </c>
       <c r="H325" s="2">
         <v>0</v>
@@ -9705,10 +9835,10 @@
         <v>12</v>
       </c>
       <c r="B326" s="2">
-        <v>223903500</v>
+        <v>447807006</v>
       </c>
       <c r="C326" s="2">
-        <v>223903500</v>
+        <v>447807006</v>
       </c>
       <c r="D326" s="2">
         <v>0</v>
@@ -9720,7 +9850,7 @@
         <v>0</v>
       </c>
       <c r="G326" s="2">
-        <v>223903500</v>
+        <v>447807006</v>
       </c>
       <c r="H326" s="2">
         <v>0</v>
@@ -9731,10 +9861,10 @@
         <v>48</v>
       </c>
       <c r="B327" s="2">
-        <v>1880742000</v>
+        <v>1880742104</v>
       </c>
       <c r="C327" s="2">
-        <v>1880742000</v>
+        <v>1880742104</v>
       </c>
       <c r="D327" s="2">
         <v>1395485871</v>
@@ -9746,7 +9876,7 @@
         <v>1395485871</v>
       </c>
       <c r="G327" s="2">
-        <v>485256129</v>
+        <v>485256233</v>
       </c>
       <c r="H327" s="2">
         <v>0</v>
@@ -9757,10 +9887,10 @@
         <v>13</v>
       </c>
       <c r="B328" s="2">
-        <v>106528224</v>
+        <v>213056448</v>
       </c>
       <c r="C328" s="2">
-        <v>106528224</v>
+        <v>213056448</v>
       </c>
       <c r="D328" s="2">
         <v>33060600</v>
@@ -9772,7 +9902,7 @@
         <v>33060600</v>
       </c>
       <c r="G328" s="2">
-        <v>73467624</v>
+        <v>179995848</v>
       </c>
       <c r="H328" s="2">
         <v>0</v>
@@ -9783,10 +9913,10 @@
         <v>14</v>
       </c>
       <c r="B329" s="2">
-        <v>428000000</v>
+        <v>687000000</v>
       </c>
       <c r="C329" s="2">
-        <v>428000000</v>
+        <v>687000000</v>
       </c>
       <c r="D329" s="2">
         <v>0</v>
@@ -9798,7 +9928,7 @@
         <v>141841100</v>
       </c>
       <c r="G329" s="2">
-        <v>286158900</v>
+        <v>545158900</v>
       </c>
       <c r="H329" s="2">
         <v>0</v>
@@ -9809,10 +9939,10 @@
         <v>15</v>
       </c>
       <c r="B330" s="2">
-        <v>1395999500</v>
+        <v>2791999194</v>
       </c>
       <c r="C330" s="2">
-        <v>1395999500</v>
+        <v>2791999194</v>
       </c>
       <c r="D330" s="2">
         <v>562101045</v>
@@ -9824,7 +9954,7 @@
         <v>698858425</v>
       </c>
       <c r="G330" s="2">
-        <v>697141075</v>
+        <v>2093140769</v>
       </c>
       <c r="H330" s="2">
         <v>0</v>
@@ -9835,22 +9965,22 @@
         <v>16</v>
       </c>
       <c r="B331" s="2">
-        <v>830172000</v>
+        <v>1660344000</v>
       </c>
       <c r="C331" s="2">
-        <v>830172000</v>
+        <v>1660344000</v>
       </c>
       <c r="D331" s="2">
-        <v>377887300</v>
+        <v>370874500</v>
       </c>
       <c r="E331" s="2">
-        <v>284002988</v>
+        <v>291015788</v>
       </c>
       <c r="F331" s="2">
         <v>661890288</v>
       </c>
       <c r="G331" s="2">
-        <v>168281712</v>
+        <v>998453712</v>
       </c>
       <c r="H331" s="2">
         <v>0</v>
@@ -9861,10 +9991,10 @@
         <v>49</v>
       </c>
       <c r="B332" s="2">
-        <v>163577500</v>
+        <v>327155000</v>
       </c>
       <c r="C332" s="2">
-        <v>163577500</v>
+        <v>327155000</v>
       </c>
       <c r="D332" s="2">
         <v>67275600</v>
@@ -9876,7 +10006,7 @@
         <v>67275600</v>
       </c>
       <c r="G332" s="2">
-        <v>96301900</v>
+        <v>259879400</v>
       </c>
       <c r="H332" s="2">
         <v>0</v>
@@ -9887,10 +10017,10 @@
         <v>50</v>
       </c>
       <c r="B333" s="2">
-        <v>415688000</v>
+        <v>831375509</v>
       </c>
       <c r="C333" s="2">
-        <v>415688000</v>
+        <v>831375509</v>
       </c>
       <c r="D333" s="2">
         <v>345662595</v>
@@ -9902,7 +10032,7 @@
         <v>345662595</v>
       </c>
       <c r="G333" s="2">
-        <v>70025405</v>
+        <v>485712914</v>
       </c>
       <c r="H333" s="2">
         <v>0</v>
@@ -9939,10 +10069,10 @@
         <v>77</v>
       </c>
       <c r="B335" s="2">
-        <v>300000000</v>
+        <v>600000000</v>
       </c>
       <c r="C335" s="2">
-        <v>300000000</v>
+        <v>600000000</v>
       </c>
       <c r="D335" s="2">
         <v>0</v>
@@ -9954,7 +10084,7 @@
         <v>0</v>
       </c>
       <c r="G335" s="2">
-        <v>300000000</v>
+        <v>600000000</v>
       </c>
       <c r="H335" s="2">
         <v>0</v>
@@ -9965,10 +10095,10 @@
         <v>56</v>
       </c>
       <c r="B336" s="2">
-        <v>500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="C336" s="2">
-        <v>500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D336" s="2">
         <v>0</v>
@@ -9980,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="G336" s="2">
-        <v>500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="H336" s="2">
         <v>0</v>
@@ -9991,10 +10121,10 @@
         <v>22</v>
       </c>
       <c r="B337" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="C337" s="2">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="D337" s="2">
         <v>0</v>
@@ -10006,10 +10136,10 @@
         <v>0</v>
       </c>
       <c r="G337" s="2">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="H337" s="2">
-        <v>0</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.45">
@@ -10017,22 +10147,22 @@
         <v>57</v>
       </c>
       <c r="B338" s="2">
-        <v>70775000</v>
+        <v>141550000</v>
       </c>
       <c r="C338" s="2">
-        <v>70775000</v>
+        <v>141550000</v>
       </c>
       <c r="D338" s="2">
-        <v>24082000</v>
+        <v>0</v>
       </c>
       <c r="E338" s="2">
-        <v>3970000</v>
+        <v>28052000</v>
       </c>
       <c r="F338" s="2">
         <v>28052000</v>
       </c>
       <c r="G338" s="2">
-        <v>42723000</v>
+        <v>113498000</v>
       </c>
       <c r="H338" s="2">
         <v>0</v>
@@ -10043,10 +10173,10 @@
         <v>58</v>
       </c>
       <c r="B339" s="2">
-        <v>880440000</v>
+        <v>2911760000</v>
       </c>
       <c r="C339" s="2">
-        <v>880440000</v>
+        <v>2911760000</v>
       </c>
       <c r="D339" s="2">
         <v>581770</v>
@@ -10058,7 +10188,7 @@
         <v>412137110</v>
       </c>
       <c r="G339" s="2">
-        <v>468302890</v>
+        <v>2499622890</v>
       </c>
       <c r="H339" s="2">
         <v>0</v>
@@ -10069,10 +10199,10 @@
         <v>25</v>
       </c>
       <c r="B340" s="2">
-        <v>77500000</v>
+        <v>180000000</v>
       </c>
       <c r="C340" s="2">
-        <v>77500000</v>
+        <v>135000000</v>
       </c>
       <c r="D340" s="2">
         <v>23940000</v>
@@ -10084,10 +10214,10 @@
         <v>37404500</v>
       </c>
       <c r="G340" s="2">
-        <v>40095500</v>
+        <v>97595500</v>
       </c>
       <c r="H340" s="2">
-        <v>0</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.45">
@@ -10095,25 +10225,25 @@
         <v>26</v>
       </c>
       <c r="B341" s="2">
-        <v>154250000</v>
+        <v>761439700</v>
       </c>
       <c r="C341" s="2">
-        <v>154250000</v>
+        <v>571079775</v>
       </c>
       <c r="D341" s="2">
-        <v>21601800</v>
+        <v>21171800</v>
       </c>
       <c r="E341" s="2">
-        <v>60021850</v>
+        <v>60451850</v>
       </c>
       <c r="F341" s="2">
         <v>81623650</v>
       </c>
       <c r="G341" s="2">
-        <v>72626350</v>
+        <v>489456125</v>
       </c>
       <c r="H341" s="2">
-        <v>0</v>
+        <v>190359925</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.45">
@@ -10121,10 +10251,10 @@
         <v>27</v>
       </c>
       <c r="B342" s="2">
-        <v>27750000</v>
+        <v>99900000</v>
       </c>
       <c r="C342" s="2">
-        <v>27750000</v>
+        <v>99900000</v>
       </c>
       <c r="D342" s="2">
         <v>0</v>
@@ -10136,7 +10266,7 @@
         <v>18500000</v>
       </c>
       <c r="G342" s="2">
-        <v>9250000</v>
+        <v>81400000</v>
       </c>
       <c r="H342" s="2">
         <v>0</v>
@@ -10147,10 +10277,10 @@
         <v>28</v>
       </c>
       <c r="B343" s="2">
-        <v>286250000</v>
+        <v>616500000</v>
       </c>
       <c r="C343" s="2">
-        <v>286250000</v>
+        <v>462375000</v>
       </c>
       <c r="D343" s="2">
         <v>16504900</v>
@@ -10162,10 +10292,10 @@
         <v>19527670</v>
       </c>
       <c r="G343" s="2">
-        <v>266722330</v>
+        <v>442847330</v>
       </c>
       <c r="H343" s="2">
-        <v>0</v>
+        <v>154125000</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.45">
@@ -10173,10 +10303,10 @@
         <v>30</v>
       </c>
       <c r="B344" s="2">
-        <v>108000000</v>
+        <v>347400000</v>
       </c>
       <c r="C344" s="2">
-        <v>108000000</v>
+        <v>260550000</v>
       </c>
       <c r="D344" s="2">
         <v>0</v>
@@ -10188,10 +10318,10 @@
         <v>52841500</v>
       </c>
       <c r="G344" s="2">
-        <v>55158500</v>
+        <v>207708500</v>
       </c>
       <c r="H344" s="2">
-        <v>0</v>
+        <v>86850000</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.45">
@@ -10199,10 +10329,10 @@
         <v>79</v>
       </c>
       <c r="B345" s="2">
-        <v>1500000</v>
+        <v>6000000</v>
       </c>
       <c r="C345" s="2">
-        <v>1500000</v>
+        <v>6000000</v>
       </c>
       <c r="D345" s="2">
         <v>384315</v>
@@ -10214,7 +10344,7 @@
         <v>384315</v>
       </c>
       <c r="G345" s="2">
-        <v>1115685</v>
+        <v>5615685</v>
       </c>
       <c r="H345" s="2">
         <v>0</v>
@@ -10225,10 +10355,10 @@
         <v>31</v>
       </c>
       <c r="B346" s="2">
-        <v>16379250</v>
+        <v>56157000</v>
       </c>
       <c r="C346" s="2">
-        <v>16379250</v>
+        <v>56157000</v>
       </c>
       <c r="D346" s="2">
         <v>0</v>
@@ -10240,7 +10370,7 @@
         <v>15178108</v>
       </c>
       <c r="G346" s="2">
-        <v>1201142</v>
+        <v>40978892</v>
       </c>
       <c r="H346" s="2">
         <v>0</v>
@@ -10459,25 +10589,25 @@
         <v>84</v>
       </c>
       <c r="B355" s="2">
-        <v>50160692946</v>
+        <v>57953424224</v>
       </c>
       <c r="C355" s="2">
-        <v>50160692946</v>
+        <v>57427089299</v>
       </c>
       <c r="D355" s="2">
-        <v>19306486525</v>
+        <v>19274961725</v>
       </c>
       <c r="E355" s="2">
-        <v>6016598991</v>
+        <v>6048123791</v>
       </c>
       <c r="F355" s="2">
         <v>25323085516</v>
       </c>
       <c r="G355" s="2">
-        <v>24837607430</v>
+        <v>32104003783</v>
       </c>
       <c r="H355" s="2">
-        <v>0</v>
+        <v>526334925</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.45">
@@ -10485,10 +10615,10 @@
         <v>8</v>
       </c>
       <c r="B356" s="2">
-        <v>1645662000</v>
+        <v>3291324000</v>
       </c>
       <c r="C356" s="2">
-        <v>1645662000</v>
+        <v>3291324000</v>
       </c>
       <c r="D356" s="2">
         <v>0</v>
@@ -10500,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="G356" s="2">
-        <v>1645662000</v>
+        <v>3291324000</v>
       </c>
       <c r="H356" s="2">
         <v>0</v>
@@ -10511,10 +10641,10 @@
         <v>12</v>
       </c>
       <c r="B357" s="2">
-        <v>945931000</v>
+        <v>1891862000</v>
       </c>
       <c r="C357" s="2">
-        <v>945931000</v>
+        <v>1891862000</v>
       </c>
       <c r="D357" s="2">
         <v>0</v>
@@ -10526,7 +10656,7 @@
         <v>0</v>
       </c>
       <c r="G357" s="2">
-        <v>945931000</v>
+        <v>1891862000</v>
       </c>
       <c r="H357" s="2">
         <v>0</v>
@@ -10537,22 +10667,22 @@
         <v>48</v>
       </c>
       <c r="B358" s="2">
-        <v>1122403500</v>
+        <v>2244807000</v>
       </c>
       <c r="C358" s="2">
-        <v>1122403500</v>
+        <v>2244807000</v>
       </c>
       <c r="D358" s="2">
-        <v>134933637</v>
+        <v>137918578</v>
       </c>
       <c r="E358" s="2">
         <v>137784161</v>
       </c>
       <c r="F358" s="2">
-        <v>272717798</v>
+        <v>275702739</v>
       </c>
       <c r="G358" s="2">
-        <v>849685702</v>
+        <v>1969104261</v>
       </c>
       <c r="H358" s="2">
         <v>0</v>
@@ -10563,10 +10693,10 @@
         <v>13</v>
       </c>
       <c r="B359" s="2">
-        <v>74888500</v>
+        <v>149777000</v>
       </c>
       <c r="C359" s="2">
-        <v>74888500</v>
+        <v>149777000</v>
       </c>
       <c r="D359" s="2">
         <v>3421001</v>
@@ -10578,7 +10708,7 @@
         <v>3421001</v>
       </c>
       <c r="G359" s="2">
-        <v>71467499</v>
+        <v>146355999</v>
       </c>
       <c r="H359" s="2">
         <v>0</v>
@@ -10589,10 +10719,10 @@
         <v>14</v>
       </c>
       <c r="B360" s="2">
-        <v>16624000</v>
+        <v>33248000</v>
       </c>
       <c r="C360" s="2">
-        <v>16624000</v>
+        <v>33248000</v>
       </c>
       <c r="D360" s="2">
         <v>0</v>
@@ -10604,7 +10734,7 @@
         <v>16623760</v>
       </c>
       <c r="G360" s="2">
-        <v>240</v>
+        <v>16624240</v>
       </c>
       <c r="H360" s="2">
         <v>0</v>
@@ -10615,10 +10745,10 @@
         <v>15</v>
       </c>
       <c r="B361" s="2">
-        <v>522368500</v>
+        <v>1044737000</v>
       </c>
       <c r="C361" s="2">
-        <v>522368500</v>
+        <v>1044737000</v>
       </c>
       <c r="D361" s="2">
         <v>81692227</v>
@@ -10630,7 +10760,7 @@
         <v>193507670</v>
       </c>
       <c r="G361" s="2">
-        <v>328860830</v>
+        <v>851229330</v>
       </c>
       <c r="H361" s="2">
         <v>0</v>
@@ -10641,10 +10771,10 @@
         <v>16</v>
       </c>
       <c r="B362" s="2">
-        <v>700000000</v>
+        <v>1400000000</v>
       </c>
       <c r="C362" s="2">
-        <v>700000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D362" s="2">
         <v>20715500</v>
@@ -10656,7 +10786,7 @@
         <v>172728050</v>
       </c>
       <c r="G362" s="2">
-        <v>527271950</v>
+        <v>1227271950</v>
       </c>
       <c r="H362" s="2">
         <v>0</v>
@@ -10667,10 +10797,10 @@
         <v>49</v>
       </c>
       <c r="B363" s="2">
-        <v>145275000</v>
+        <v>290550000</v>
       </c>
       <c r="C363" s="2">
-        <v>145275000</v>
+        <v>290550000</v>
       </c>
       <c r="D363" s="2">
         <v>0</v>
@@ -10682,7 +10812,7 @@
         <v>0</v>
       </c>
       <c r="G363" s="2">
-        <v>145275000</v>
+        <v>290550000</v>
       </c>
       <c r="H363" s="2">
         <v>0</v>
@@ -10693,10 +10823,10 @@
         <v>50</v>
       </c>
       <c r="B364" s="2">
-        <v>153214500</v>
+        <v>306429000</v>
       </c>
       <c r="C364" s="2">
-        <v>153214500</v>
+        <v>306429000</v>
       </c>
       <c r="D364" s="2">
         <v>0</v>
@@ -10708,7 +10838,7 @@
         <v>0</v>
       </c>
       <c r="G364" s="2">
-        <v>153214500</v>
+        <v>306429000</v>
       </c>
       <c r="H364" s="2">
         <v>0</v>
@@ -10719,10 +10849,10 @@
         <v>52</v>
       </c>
       <c r="B365" s="2">
-        <v>235100000</v>
+        <v>470200000</v>
       </c>
       <c r="C365" s="2">
-        <v>235100000</v>
+        <v>470200000</v>
       </c>
       <c r="D365" s="2">
         <v>0</v>
@@ -10734,7 +10864,7 @@
         <v>3229600</v>
       </c>
       <c r="G365" s="2">
-        <v>231870400</v>
+        <v>466970400</v>
       </c>
       <c r="H365" s="2">
         <v>0</v>
@@ -10745,10 +10875,10 @@
         <v>56</v>
       </c>
       <c r="B366" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="C366" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="D366" s="2">
         <v>0</v>
@@ -10760,7 +10890,7 @@
         <v>0</v>
       </c>
       <c r="G366" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="H366" s="2">
         <v>0</v>
@@ -10771,10 +10901,10 @@
         <v>22</v>
       </c>
       <c r="B367" s="2">
-        <v>100000000</v>
+        <v>110000000</v>
       </c>
       <c r="C367" s="2">
-        <v>100000000</v>
+        <v>82500000</v>
       </c>
       <c r="D367" s="2">
         <v>0</v>
@@ -10786,10 +10916,10 @@
         <v>0</v>
       </c>
       <c r="G367" s="2">
-        <v>100000000</v>
+        <v>82500000</v>
       </c>
       <c r="H367" s="2">
-        <v>0</v>
+        <v>27500000</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.45">
@@ -10797,10 +10927,10 @@
         <v>57</v>
       </c>
       <c r="B368" s="2">
-        <v>63030000</v>
+        <v>99980000</v>
       </c>
       <c r="C368" s="2">
-        <v>63030000</v>
+        <v>99980000</v>
       </c>
       <c r="D368" s="2">
         <v>19823200</v>
@@ -10812,7 +10942,7 @@
         <v>19823200</v>
       </c>
       <c r="G368" s="2">
-        <v>43206800</v>
+        <v>80156800</v>
       </c>
       <c r="H368" s="2">
         <v>0</v>
@@ -10823,10 +10953,10 @@
         <v>58</v>
       </c>
       <c r="B369" s="2">
-        <v>90000000</v>
+        <v>411080000</v>
       </c>
       <c r="C369" s="2">
-        <v>90000000</v>
+        <v>411080000</v>
       </c>
       <c r="D369" s="2">
         <v>1639740</v>
@@ -10838,7 +10968,7 @@
         <v>72536444</v>
       </c>
       <c r="G369" s="2">
-        <v>17463556</v>
+        <v>338543556</v>
       </c>
       <c r="H369" s="2">
         <v>0</v>
@@ -10849,10 +10979,10 @@
         <v>25</v>
       </c>
       <c r="B370" s="2">
-        <v>64000000</v>
+        <v>160000000</v>
       </c>
       <c r="C370" s="2">
-        <v>64000000</v>
+        <v>120000000</v>
       </c>
       <c r="D370" s="2">
         <v>6960000</v>
@@ -10864,10 +10994,10 @@
         <v>20447000</v>
       </c>
       <c r="G370" s="2">
-        <v>43553000</v>
+        <v>99553000</v>
       </c>
       <c r="H370" s="2">
-        <v>0</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.45">
@@ -10875,10 +11005,10 @@
         <v>26</v>
       </c>
       <c r="B371" s="2">
-        <v>300400000</v>
+        <v>400000000</v>
       </c>
       <c r="C371" s="2">
-        <v>300400000</v>
+        <v>300000000</v>
       </c>
       <c r="D371" s="2">
         <v>27274000</v>
@@ -10890,10 +11020,10 @@
         <v>105482462</v>
       </c>
       <c r="G371" s="2">
-        <v>194917538</v>
+        <v>194517538</v>
       </c>
       <c r="H371" s="2">
-        <v>0</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.45">
@@ -10901,10 +11031,10 @@
         <v>27</v>
       </c>
       <c r="B372" s="2">
-        <v>16500000</v>
+        <v>66000000</v>
       </c>
       <c r="C372" s="2">
-        <v>16500000</v>
+        <v>66000000</v>
       </c>
       <c r="D372" s="2">
         <v>0</v>
@@ -10916,7 +11046,7 @@
         <v>11000000</v>
       </c>
       <c r="G372" s="2">
-        <v>5500000</v>
+        <v>55000000</v>
       </c>
       <c r="H372" s="2">
         <v>0</v>
@@ -10927,10 +11057,10 @@
         <v>28</v>
       </c>
       <c r="B373" s="2">
-        <v>35000000</v>
+        <v>90000000</v>
       </c>
       <c r="C373" s="2">
-        <v>35000000</v>
+        <v>67500000</v>
       </c>
       <c r="D373" s="2">
         <v>0</v>
@@ -10942,10 +11072,10 @@
         <v>4415000</v>
       </c>
       <c r="G373" s="2">
-        <v>30585000</v>
+        <v>63085000</v>
       </c>
       <c r="H373" s="2">
-        <v>0</v>
+        <v>22500000</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.45">
@@ -10953,10 +11083,10 @@
         <v>30</v>
       </c>
       <c r="B374" s="2">
-        <v>42675000</v>
+        <v>170700000</v>
       </c>
       <c r="C374" s="2">
-        <v>42675000</v>
+        <v>128025000</v>
       </c>
       <c r="D374" s="2">
         <v>0</v>
@@ -10968,10 +11098,10 @@
         <v>39560000</v>
       </c>
       <c r="G374" s="2">
-        <v>3115000</v>
+        <v>88465000</v>
       </c>
       <c r="H374" s="2">
-        <v>0</v>
+        <v>42675000</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.45">
@@ -10979,10 +11109,10 @@
         <v>31</v>
       </c>
       <c r="B375" s="2">
-        <v>9000000</v>
+        <v>24000000</v>
       </c>
       <c r="C375" s="2">
-        <v>9000000</v>
+        <v>24000000</v>
       </c>
       <c r="D375" s="2">
         <v>0</v>
@@ -10994,7 +11124,7 @@
         <v>6736950</v>
       </c>
       <c r="G375" s="2">
-        <v>2263050</v>
+        <v>17263050</v>
       </c>
       <c r="H375" s="2">
         <v>0</v>
@@ -11239,25 +11369,25 @@
         <v>85</v>
       </c>
       <c r="B385" s="2">
-        <v>17495468591</v>
+        <v>23968090591</v>
       </c>
       <c r="C385" s="2">
-        <v>17495468591</v>
+        <v>23735415591</v>
       </c>
       <c r="D385" s="2">
-        <v>296459305</v>
+        <v>299444246</v>
       </c>
       <c r="E385" s="2">
         <v>2381235336</v>
       </c>
       <c r="F385" s="2">
-        <v>2677694641</v>
+        <v>2680679582</v>
       </c>
       <c r="G385" s="2">
-        <v>14817773950</v>
+        <v>21054736009</v>
       </c>
       <c r="H385" s="2">
-        <v>0</v>
+        <v>232675000</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.45">
@@ -11265,10 +11395,10 @@
         <v>8</v>
       </c>
       <c r="B386" s="2">
-        <v>1717513500</v>
+        <v>3435027000</v>
       </c>
       <c r="C386" s="2">
-        <v>1717513500</v>
+        <v>3435027000</v>
       </c>
       <c r="D386" s="2">
         <v>0</v>
@@ -11280,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="G386" s="2">
-        <v>1717513500</v>
+        <v>3435027000</v>
       </c>
       <c r="H386" s="2">
         <v>0</v>
@@ -11317,10 +11447,10 @@
         <v>12</v>
       </c>
       <c r="B388" s="2">
-        <v>233686000</v>
+        <v>467372000</v>
       </c>
       <c r="C388" s="2">
-        <v>233686000</v>
+        <v>467372000</v>
       </c>
       <c r="D388" s="2">
         <v>0</v>
@@ -11332,7 +11462,7 @@
         <v>0</v>
       </c>
       <c r="G388" s="2">
-        <v>233686000</v>
+        <v>467372000</v>
       </c>
       <c r="H388" s="2">
         <v>0</v>
@@ -11343,10 +11473,10 @@
         <v>48</v>
       </c>
       <c r="B389" s="2">
-        <v>445284000</v>
+        <v>890568000</v>
       </c>
       <c r="C389" s="2">
-        <v>445284000</v>
+        <v>890568000</v>
       </c>
       <c r="D389" s="2">
         <v>398086520</v>
@@ -11358,7 +11488,7 @@
         <v>398086520</v>
       </c>
       <c r="G389" s="2">
-        <v>47197480</v>
+        <v>492481480</v>
       </c>
       <c r="H389" s="2">
         <v>0</v>
@@ -11369,10 +11499,10 @@
         <v>13</v>
       </c>
       <c r="B390" s="2">
-        <v>78606000</v>
+        <v>157212000</v>
       </c>
       <c r="C390" s="2">
-        <v>78606000</v>
+        <v>157212000</v>
       </c>
       <c r="D390" s="2">
         <v>49855940</v>
@@ -11384,7 +11514,7 @@
         <v>49855940</v>
       </c>
       <c r="G390" s="2">
-        <v>28750060</v>
+        <v>107356060</v>
       </c>
       <c r="H390" s="2">
         <v>0</v>
@@ -11395,10 +11525,10 @@
         <v>14</v>
       </c>
       <c r="B391" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="C391" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="D391" s="2">
         <v>0</v>
@@ -11410,7 +11540,7 @@
         <v>0</v>
       </c>
       <c r="G391" s="2">
-        <v>225000000</v>
+        <v>450000000</v>
       </c>
       <c r="H391" s="2">
         <v>0</v>
@@ -11421,10 +11551,10 @@
         <v>15</v>
       </c>
       <c r="B392" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="C392" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="D392" s="2">
         <v>0</v>
@@ -11436,7 +11566,7 @@
         <v>0</v>
       </c>
       <c r="G392" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="H392" s="2">
         <v>0</v>
@@ -11447,22 +11577,22 @@
         <v>16</v>
       </c>
       <c r="B393" s="2">
-        <v>345000000</v>
+        <v>690000000</v>
       </c>
       <c r="C393" s="2">
-        <v>345000000</v>
+        <v>690000000</v>
       </c>
       <c r="D393" s="2">
-        <v>202834780</v>
+        <v>103894080</v>
       </c>
       <c r="E393" s="2">
-        <v>0</v>
+        <v>98940700</v>
       </c>
       <c r="F393" s="2">
         <v>202834780</v>
       </c>
       <c r="G393" s="2">
-        <v>142165220</v>
+        <v>487165220</v>
       </c>
       <c r="H393" s="2">
         <v>0</v>
@@ -11473,10 +11603,10 @@
         <v>49</v>
       </c>
       <c r="B394" s="2">
-        <v>99350000</v>
+        <v>198700000</v>
       </c>
       <c r="C394" s="2">
-        <v>99350000</v>
+        <v>198700000</v>
       </c>
       <c r="D394" s="2">
         <v>91627175</v>
@@ -11488,7 +11618,7 @@
         <v>91627175</v>
       </c>
       <c r="G394" s="2">
-        <v>7722825</v>
+        <v>107072825</v>
       </c>
       <c r="H394" s="2">
         <v>0</v>
@@ -11499,10 +11629,10 @@
         <v>50</v>
       </c>
       <c r="B395" s="2">
-        <v>227565500</v>
+        <v>455131000</v>
       </c>
       <c r="C395" s="2">
-        <v>227565500</v>
+        <v>455131000</v>
       </c>
       <c r="D395" s="2">
         <v>0</v>
@@ -11514,7 +11644,7 @@
         <v>0</v>
       </c>
       <c r="G395" s="2">
-        <v>227565500</v>
+        <v>455131000</v>
       </c>
       <c r="H395" s="2">
         <v>0</v>
@@ -11525,10 +11655,10 @@
         <v>51</v>
       </c>
       <c r="B396" s="2">
-        <v>25000000</v>
+        <v>50000000</v>
       </c>
       <c r="C396" s="2">
-        <v>25000000</v>
+        <v>50000000</v>
       </c>
       <c r="D396" s="2">
         <v>0</v>
@@ -11540,7 +11670,7 @@
         <v>0</v>
       </c>
       <c r="G396" s="2">
-        <v>25000000</v>
+        <v>50000000</v>
       </c>
       <c r="H396" s="2">
         <v>0</v>
@@ -11551,10 +11681,10 @@
         <v>52</v>
       </c>
       <c r="B397" s="2">
-        <v>721780000</v>
+        <v>1443560000</v>
       </c>
       <c r="C397" s="2">
-        <v>721780000</v>
+        <v>1443560000</v>
       </c>
       <c r="D397" s="2">
         <v>0</v>
@@ -11566,7 +11696,7 @@
         <v>0</v>
       </c>
       <c r="G397" s="2">
-        <v>721780000</v>
+        <v>1443560000</v>
       </c>
       <c r="H397" s="2">
         <v>0</v>
@@ -11577,10 +11707,10 @@
         <v>53</v>
       </c>
       <c r="B398" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="C398" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="D398" s="2">
         <v>0</v>
@@ -11592,7 +11722,7 @@
         <v>0</v>
       </c>
       <c r="G398" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="H398" s="2">
         <v>0</v>
@@ -11603,10 +11733,10 @@
         <v>56</v>
       </c>
       <c r="B399" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="C399" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="D399" s="2">
         <v>0</v>
@@ -11618,7 +11748,7 @@
         <v>0</v>
       </c>
       <c r="G399" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="H399" s="2">
         <v>0</v>
@@ -11629,10 +11759,10 @@
         <v>22</v>
       </c>
       <c r="B400" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="C400" s="2">
-        <v>125000000</v>
+        <v>187500000</v>
       </c>
       <c r="D400" s="2">
         <v>0</v>
@@ -11644,10 +11774,10 @@
         <v>0</v>
       </c>
       <c r="G400" s="2">
-        <v>125000000</v>
+        <v>187500000</v>
       </c>
       <c r="H400" s="2">
-        <v>0</v>
+        <v>62500000</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.45">
@@ -11655,10 +11785,10 @@
         <v>57</v>
       </c>
       <c r="B401" s="2">
-        <v>158400000</v>
+        <v>316800000</v>
       </c>
       <c r="C401" s="2">
-        <v>158400000</v>
+        <v>316800000</v>
       </c>
       <c r="D401" s="2">
         <v>52208150</v>
@@ -11670,7 +11800,7 @@
         <v>52208150</v>
       </c>
       <c r="G401" s="2">
-        <v>106191850</v>
+        <v>264591850</v>
       </c>
       <c r="H401" s="2">
         <v>0</v>
@@ -11681,10 +11811,10 @@
         <v>58</v>
       </c>
       <c r="B402" s="2">
-        <v>637500000</v>
+        <v>2230000000</v>
       </c>
       <c r="C402" s="2">
-        <v>637500000</v>
+        <v>2230000000</v>
       </c>
       <c r="D402" s="2">
         <v>9815000</v>
@@ -11696,7 +11826,7 @@
         <v>227966545</v>
       </c>
       <c r="G402" s="2">
-        <v>409533455</v>
+        <v>2002033455</v>
       </c>
       <c r="H402" s="2">
         <v>0</v>
@@ -11707,10 +11837,10 @@
         <v>25</v>
       </c>
       <c r="B403" s="2">
-        <v>48400000</v>
+        <v>193600000</v>
       </c>
       <c r="C403" s="2">
-        <v>48400000</v>
+        <v>145200000</v>
       </c>
       <c r="D403" s="2">
         <v>21900000</v>
@@ -11722,10 +11852,10 @@
         <v>21900000</v>
       </c>
       <c r="G403" s="2">
-        <v>26500000</v>
+        <v>123300000</v>
       </c>
       <c r="H403" s="2">
-        <v>0</v>
+        <v>48400000</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.45">
@@ -11733,10 +11863,10 @@
         <v>26</v>
       </c>
       <c r="B404" s="2">
-        <v>170907750</v>
+        <v>593631000</v>
       </c>
       <c r="C404" s="2">
-        <v>170907750</v>
+        <v>445223250</v>
       </c>
       <c r="D404" s="2">
         <v>98217450</v>
@@ -11748,10 +11878,10 @@
         <v>166131450</v>
       </c>
       <c r="G404" s="2">
-        <v>4776300</v>
+        <v>279091800</v>
       </c>
       <c r="H404" s="2">
-        <v>0</v>
+        <v>148407750</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.45">
@@ -11759,10 +11889,10 @@
         <v>27</v>
       </c>
       <c r="B405" s="2">
-        <v>26250000</v>
+        <v>105000000</v>
       </c>
       <c r="C405" s="2">
-        <v>26250000</v>
+        <v>105000000</v>
       </c>
       <c r="D405" s="2">
         <v>0</v>
@@ -11774,7 +11904,7 @@
         <v>16500000</v>
       </c>
       <c r="G405" s="2">
-        <v>9750000</v>
+        <v>88500000</v>
       </c>
       <c r="H405" s="2">
         <v>0</v>
@@ -11785,10 +11915,10 @@
         <v>28</v>
       </c>
       <c r="B406" s="2">
-        <v>96500000</v>
+        <v>386000000</v>
       </c>
       <c r="C406" s="2">
-        <v>96500000</v>
+        <v>289500000</v>
       </c>
       <c r="D406" s="2">
         <v>2609000</v>
@@ -11800,10 +11930,10 @@
         <v>2609000</v>
       </c>
       <c r="G406" s="2">
-        <v>93891000</v>
+        <v>286891000</v>
       </c>
       <c r="H406" s="2">
-        <v>0</v>
+        <v>96500000</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.45">
@@ -11811,10 +11941,10 @@
         <v>30</v>
       </c>
       <c r="B407" s="2">
-        <v>117000000</v>
+        <v>468000000</v>
       </c>
       <c r="C407" s="2">
-        <v>117000000</v>
+        <v>351000000</v>
       </c>
       <c r="D407" s="2">
         <v>0</v>
@@ -11826,10 +11956,10 @@
         <v>65686596</v>
       </c>
       <c r="G407" s="2">
-        <v>51313404</v>
+        <v>285313404</v>
       </c>
       <c r="H407" s="2">
-        <v>0</v>
+        <v>117000000</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.45">
@@ -11837,10 +11967,10 @@
         <v>79</v>
       </c>
       <c r="B408" s="2">
-        <v>1500000</v>
+        <v>6000000</v>
       </c>
       <c r="C408" s="2">
-        <v>1500000</v>
+        <v>6000000</v>
       </c>
       <c r="D408" s="2">
         <v>0</v>
@@ -11852,7 +11982,7 @@
         <v>315000</v>
       </c>
       <c r="G408" s="2">
-        <v>1185000</v>
+        <v>5685000</v>
       </c>
       <c r="H408" s="2">
         <v>0</v>
@@ -11863,10 +11993,10 @@
         <v>31</v>
       </c>
       <c r="B409" s="2">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="C409" s="2">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="D409" s="2">
         <v>0</v>
@@ -11878,7 +12008,7 @@
         <v>0</v>
       </c>
       <c r="G409" s="2">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="H409" s="2">
         <v>0</v>
@@ -12123,750 +12253,1774 @@
         <v>86</v>
       </c>
       <c r="B419" s="2">
-        <v>26293508870</v>
+        <v>34234867120</v>
       </c>
       <c r="C419" s="2">
-        <v>26293508870</v>
+        <v>33762059370</v>
       </c>
       <c r="D419" s="2">
-        <v>927154015</v>
+        <v>828213315</v>
       </c>
       <c r="E419" s="2">
-        <v>3465530767</v>
+        <v>3564471467</v>
       </c>
       <c r="F419" s="2">
         <v>4392684782</v>
       </c>
       <c r="G419" s="2">
-        <v>21900824088</v>
+        <v>29369374588</v>
       </c>
       <c r="H419" s="2">
-        <v>0</v>
+        <v>472807750</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A420" s="1" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="B420" s="3">
-        <v>1871950730</v>
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>873740000</v>
       </c>
       <c r="C420" s="3">
-        <v>1871950730</v>
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>436870000</v>
       </c>
       <c r="D420" s="3">
-        <f>F420-E420</f>
-        <v>404935052</v>
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>404360000</v>
       </c>
       <c r="E420" s="3">
-        <v>78896778</v>
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>35605052</v>
       </c>
       <c r="F420" s="3">
-        <v>483831830</v>
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>439965052</v>
       </c>
       <c r="G420" s="3">
-        <f>C420-F420</f>
-        <v>1388118900</v>
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>-3095052</v>
       </c>
       <c r="H420" s="3">
-        <f>B420-C420</f>
-        <v>0</v>
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
+        <v>436870000</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A421" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B421" s="3"/>
-      <c r="C421" s="3"/>
-      <c r="D421" s="3"/>
-      <c r="E421" s="3"/>
-      <c r="F421" s="3"/>
-      <c r="G421" s="3"/>
-      <c r="H421" s="3"/>
+        <v>99</v>
+      </c>
+      <c r="B421" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="C421" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="D421" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="E421" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="F421" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="G421" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
+      <c r="H421" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A422" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B422" s="3"/>
-      <c r="C422" s="3"/>
-      <c r="D422" s="3"/>
-      <c r="E422" s="3"/>
-      <c r="F422" s="3"/>
-      <c r="G422" s="3"/>
-      <c r="H422" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="B422" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="C422" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="D422" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="E422" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="F422" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="G422" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
+      <c r="H422" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A423" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B423" s="3"/>
-      <c r="C423" s="3"/>
-      <c r="D423" s="3"/>
-      <c r="E423" s="3"/>
-      <c r="F423" s="3"/>
-      <c r="G423" s="3"/>
-      <c r="H423" s="3"/>
+        <v>101</v>
+      </c>
+      <c r="B423" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="C423" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="D423" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="E423" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="F423" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="G423" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
+      <c r="H423" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A424" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B424" s="3"/>
-      <c r="C424" s="3"/>
-      <c r="D424" s="3"/>
-      <c r="E424" s="3"/>
-      <c r="F424" s="3"/>
-      <c r="G424" s="3"/>
-      <c r="H424" s="3"/>
+        <v>102</v>
+      </c>
+      <c r="B424" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="C424" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="D424" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="E424" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="F424" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="G424" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
+      <c r="H424" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A425" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B425" s="3"/>
-      <c r="C425" s="3"/>
-      <c r="D425" s="3"/>
-      <c r="E425" s="3"/>
-      <c r="F425" s="3"/>
-      <c r="G425" s="3"/>
-      <c r="H425" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="B425" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="C425" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="D425" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="E425" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="F425" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="G425" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
+      <c r="H425" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A426" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B426" s="3"/>
-      <c r="C426" s="3"/>
-      <c r="D426" s="3"/>
-      <c r="E426" s="3"/>
-      <c r="F426" s="3"/>
-      <c r="G426" s="3"/>
-      <c r="H426" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="B426" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="C426" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="D426" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="E426" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="F426" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="G426" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
+      <c r="H426" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A427" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B427" s="3"/>
-      <c r="C427" s="3"/>
-      <c r="D427" s="3"/>
-      <c r="E427" s="3"/>
-      <c r="F427" s="3"/>
-      <c r="G427" s="3"/>
-      <c r="H427" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="B427" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="C427" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="D427" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="E427" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="F427" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="G427" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
+      <c r="H427" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A428" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B428" s="3"/>
-      <c r="C428" s="3"/>
-      <c r="D428" s="3"/>
-      <c r="E428" s="3"/>
-      <c r="F428" s="3"/>
-      <c r="G428" s="3"/>
-      <c r="H428" s="3"/>
+        <v>106</v>
+      </c>
+      <c r="B428" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="C428" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="D428" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="E428" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="F428" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="G428" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
+      <c r="H428" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A429" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B429" s="3"/>
-      <c r="C429" s="3"/>
-      <c r="D429" s="3"/>
-      <c r="E429" s="3"/>
-      <c r="F429" s="3"/>
-      <c r="G429" s="3"/>
-      <c r="H429" s="3"/>
+        <v>107</v>
+      </c>
+      <c r="B429" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="C429" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="D429" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="E429" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="F429" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="G429" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
+      <c r="H429" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A430" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B430" s="3"/>
-      <c r="C430" s="3"/>
-      <c r="D430" s="3"/>
-      <c r="E430" s="3"/>
-      <c r="F430" s="3"/>
-      <c r="G430" s="3"/>
-      <c r="H430" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="B430" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="C430" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="D430" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="E430" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="F430" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="G430" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
+      <c r="H430" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A431" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B431" s="3"/>
-      <c r="C431" s="3"/>
-      <c r="D431" s="3"/>
-      <c r="E431" s="3"/>
-      <c r="F431" s="3"/>
-      <c r="G431" s="3"/>
-      <c r="H431" s="3"/>
+        <v>109</v>
+      </c>
+      <c r="B431" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="C431" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="D431" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="E431" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="F431" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="G431" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
+      <c r="H431" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A432" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B432" s="3"/>
-      <c r="C432" s="3"/>
-      <c r="D432" s="3"/>
-      <c r="E432" s="3"/>
-      <c r="F432" s="3"/>
-      <c r="G432" s="3"/>
-      <c r="H432" s="3"/>
+        <v>110</v>
+      </c>
+      <c r="B432" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="C432" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="D432" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="E432" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="F432" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="G432" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
+      <c r="H432" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A433" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B433" s="3"/>
-      <c r="C433" s="3"/>
-      <c r="D433" s="3"/>
-      <c r="E433" s="3"/>
-      <c r="F433" s="3"/>
-      <c r="G433" s="3"/>
-      <c r="H433" s="3"/>
+        <v>111</v>
+      </c>
+      <c r="B433" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="C433" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="D433" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="E433" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="F433" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="G433" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
+      <c r="H433" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A434" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B434" s="3"/>
-      <c r="C434" s="3"/>
-      <c r="D434" s="3"/>
-      <c r="E434" s="3"/>
-      <c r="F434" s="3"/>
-      <c r="G434" s="3"/>
-      <c r="H434" s="3"/>
+        <v>112</v>
+      </c>
+      <c r="B434" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="C434" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="D434" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="E434" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="F434" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="G434" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
+      <c r="H434" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A435" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B435" s="3"/>
-      <c r="C435" s="3"/>
-      <c r="D435" s="3"/>
-      <c r="E435" s="3"/>
-      <c r="F435" s="3"/>
-      <c r="G435" s="3"/>
-      <c r="H435" s="3"/>
+        <v>113</v>
+      </c>
+      <c r="B435" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="C435" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="D435" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="E435" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="F435" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="G435" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
+      <c r="H435" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A436" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B436" s="3"/>
-      <c r="C436" s="3"/>
-      <c r="D436" s="3"/>
-      <c r="E436" s="3"/>
-      <c r="F436" s="3"/>
-      <c r="G436" s="3"/>
-      <c r="H436" s="3"/>
+        <v>114</v>
+      </c>
+      <c r="B436" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="C436" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="D436" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="E436" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="F436" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="G436" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
+      <c r="H436" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A437" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B437" s="3"/>
-      <c r="C437" s="3"/>
-      <c r="D437" s="3"/>
-      <c r="E437" s="3"/>
-      <c r="F437" s="3"/>
-      <c r="G437" s="3"/>
-      <c r="H437" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="B437" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>474786000</v>
+      </c>
+      <c r="C437" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>237393000</v>
+      </c>
+      <c r="D437" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>0</v>
+      </c>
+      <c r="E437" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>0</v>
+      </c>
+      <c r="F437" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>0</v>
+      </c>
+      <c r="G437" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>237393000</v>
+      </c>
+      <c r="H437" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
+        <v>237393000</v>
+      </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A438" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B438" s="3"/>
-      <c r="C438" s="3"/>
-      <c r="D438" s="3"/>
-      <c r="E438" s="3"/>
-      <c r="F438" s="3"/>
-      <c r="G438" s="3"/>
-      <c r="H438" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="B438" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>208425000</v>
+      </c>
+      <c r="C438" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>104212500</v>
+      </c>
+      <c r="D438" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>0</v>
+      </c>
+      <c r="E438" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>0</v>
+      </c>
+      <c r="F438" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>0</v>
+      </c>
+      <c r="G438" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>104212500</v>
+      </c>
+      <c r="H438" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
+        <v>104212500</v>
+      </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A439" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B439" s="3"/>
-      <c r="C439" s="3"/>
-      <c r="D439" s="3"/>
-      <c r="E439" s="3"/>
-      <c r="F439" s="3"/>
-      <c r="G439" s="3"/>
-      <c r="H439" s="3"/>
+        <v>117</v>
+      </c>
+      <c r="B439" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>20000000</v>
+      </c>
+      <c r="C439" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>13970000</v>
+      </c>
+      <c r="D439" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>13970000</v>
+      </c>
+      <c r="E439" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>0</v>
+      </c>
+      <c r="F439" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>13970000</v>
+      </c>
+      <c r="G439" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>0</v>
+      </c>
+      <c r="H439" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
+        <v>6030000</v>
+      </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A440" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B440" s="3"/>
-      <c r="C440" s="3"/>
-      <c r="D440" s="3"/>
-      <c r="E440" s="3"/>
-      <c r="F440" s="3"/>
-      <c r="G440" s="3"/>
-      <c r="H440" s="3"/>
+        <v>118</v>
+      </c>
+      <c r="B440" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>220000000</v>
+      </c>
+      <c r="C440" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>110000000</v>
+      </c>
+      <c r="D440" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>0</v>
+      </c>
+      <c r="E440" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>29896778</v>
+      </c>
+      <c r="F440" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>29896778</v>
+      </c>
+      <c r="G440" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>80103222</v>
+      </c>
+      <c r="H440" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
+        <v>110000000</v>
+      </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A441" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B441" s="3"/>
-      <c r="C441" s="3"/>
-      <c r="D441" s="3"/>
-      <c r="E441" s="3"/>
-      <c r="F441" s="3"/>
-      <c r="G441" s="3"/>
-      <c r="H441" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="B441" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>75000000</v>
+      </c>
+      <c r="C441" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>37500000</v>
+      </c>
+      <c r="D441" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>0</v>
+      </c>
+      <c r="E441" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>0</v>
+      </c>
+      <c r="F441" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>0</v>
+      </c>
+      <c r="G441" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>37500000</v>
+      </c>
+      <c r="H441" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
+        <v>37500000</v>
+      </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A442" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B442" s="3"/>
-      <c r="C442" s="3"/>
-      <c r="D442" s="3"/>
-      <c r="E442" s="3"/>
-      <c r="F442" s="3"/>
-      <c r="G442" s="3"/>
-      <c r="H442" s="3"/>
+        <v>120</v>
+      </c>
+      <c r="B442" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="C442" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="D442" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="E442" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="F442" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="G442" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
+      <c r="H442" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A443" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B443" s="3"/>
-      <c r="C443" s="3"/>
-      <c r="D443" s="3"/>
-      <c r="E443" s="3"/>
-      <c r="F443" s="3"/>
-      <c r="G443" s="3"/>
-      <c r="H443" s="3"/>
+        <v>121</v>
+      </c>
+      <c r="B443" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="C443" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="D443" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="E443" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="F443" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="G443" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
+      <c r="H443" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A444" s="1" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B444" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>60000000</v>
       </c>
       <c r="C444" s="3">
-        <v>60000000</v>
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
+        <v>30000000</v>
       </c>
       <c r="D444" s="3">
-        <f>F444-E444</f>
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>9000000</v>
       </c>
       <c r="E444" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>0</v>
       </c>
       <c r="F444" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>9000000</v>
       </c>
       <c r="G444" s="3">
-        <f>C444-F444</f>
-        <v>51000000</v>
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
+        <v>21000000</v>
       </c>
       <c r="H444" s="3">
-        <f>B444-C444</f>
-        <v>0</v>
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
+        <v>30000000</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A445" s="1" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="B445" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>45150000</v>
       </c>
       <c r="C445" s="3">
-        <v>45150000</v>
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
+        <v>22575000</v>
       </c>
       <c r="D445" s="3">
-        <f>F445-E445</f>
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>6423200</v>
       </c>
       <c r="E445" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>6119400</v>
       </c>
       <c r="F445" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>12542600</v>
       </c>
       <c r="G445" s="3">
-        <f>C445-F445</f>
-        <v>32607400</v>
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
+        <v>10032400</v>
       </c>
       <c r="H445" s="3">
-        <f>B445-C445</f>
-        <v>0</v>
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
+        <v>22575000</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A446" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B446" s="3"/>
-      <c r="C446" s="3"/>
-      <c r="D446" s="3"/>
-      <c r="E446" s="3"/>
-      <c r="F446" s="3"/>
-      <c r="G446" s="3"/>
-      <c r="H446" s="3"/>
+        <v>124</v>
+      </c>
+      <c r="B446" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="C446" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="D446" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="E446" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="F446" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="G446" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
+      <c r="H446" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A447" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B447" s="3"/>
-      <c r="C447" s="3"/>
-      <c r="D447" s="3"/>
-      <c r="E447" s="3"/>
-      <c r="F447" s="3"/>
-      <c r="G447" s="3"/>
-      <c r="H447" s="3"/>
+        <v>125</v>
+      </c>
+      <c r="B447" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="C447" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="D447" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="E447" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="F447" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="G447" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
+      <c r="H447" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A448" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B448" s="3"/>
-      <c r="C448" s="3"/>
-      <c r="D448" s="3"/>
-      <c r="E448" s="3"/>
-      <c r="F448" s="3"/>
-      <c r="G448" s="3"/>
-      <c r="H448" s="3"/>
+        <v>126</v>
+      </c>
+      <c r="B448" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="C448" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="D448" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="E448" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="F448" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="G448" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
+      <c r="H448" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A449" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B449" s="3"/>
-      <c r="C449" s="3"/>
-      <c r="D449" s="3"/>
-      <c r="E449" s="3"/>
-      <c r="F449" s="3"/>
-      <c r="G449" s="3"/>
-      <c r="H449" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="B449" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="C449" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="D449" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="E449" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="F449" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="G449" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
+      <c r="H449" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A450" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B450" s="3"/>
-      <c r="C450" s="3"/>
-      <c r="D450" s="3"/>
-      <c r="E450" s="3"/>
-      <c r="F450" s="3"/>
-      <c r="G450" s="3"/>
-      <c r="H450" s="3"/>
+        <v>128</v>
+      </c>
+      <c r="B450" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="C450" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="D450" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="E450" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="F450" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="G450" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
+      <c r="H450" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A451" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B451" s="3"/>
-      <c r="C451" s="3"/>
-      <c r="D451" s="3"/>
-      <c r="E451" s="3"/>
-      <c r="F451" s="3"/>
-      <c r="G451" s="3"/>
-      <c r="H451" s="3"/>
+        <v>129</v>
+      </c>
+      <c r="B451" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="C451" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="D451" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="E451" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="F451" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="G451" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
+      <c r="H451" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A452" s="1" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="B452" s="3">
-        <v>372660000</v>
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>6000000</v>
       </c>
       <c r="C452" s="3">
-        <v>372660000</v>
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>1500000</v>
       </c>
       <c r="D452" s="3">
-        <f>F452-E452</f>
-        <v>8912700</v>
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>0</v>
       </c>
       <c r="E452" s="3">
-        <v>5604650</v>
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>0</v>
       </c>
       <c r="F452" s="3">
-        <v>14517350</v>
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>0</v>
       </c>
       <c r="G452" s="3">
-        <f>C452-F452</f>
-        <v>358142650</v>
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>1500000</v>
       </c>
       <c r="H452" s="3">
-        <f>B452-C452</f>
-        <v>0</v>
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
+        <v>4500000</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A453" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B453" s="3"/>
-      <c r="C453" s="3"/>
-      <c r="D453" s="3"/>
-      <c r="E453" s="3"/>
-      <c r="F453" s="3"/>
-      <c r="G453" s="3"/>
-      <c r="H453" s="3"/>
+        <v>131</v>
+      </c>
+      <c r="B453" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>41000000</v>
+      </c>
+      <c r="C453" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>10250000</v>
+      </c>
+      <c r="D453" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>1997700</v>
+      </c>
+      <c r="E453" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>998400</v>
+      </c>
+      <c r="F453" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>2996100</v>
+      </c>
+      <c r="G453" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>7253900</v>
+      </c>
+      <c r="H453" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
+        <v>30750000</v>
+      </c>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A454" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B454" s="3"/>
-      <c r="C454" s="3"/>
-      <c r="D454" s="3"/>
-      <c r="E454" s="3"/>
-      <c r="F454" s="3"/>
-      <c r="G454" s="3"/>
-      <c r="H454" s="3"/>
+        <v>132</v>
+      </c>
+      <c r="B454" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>12000000</v>
+      </c>
+      <c r="C454" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>3000000</v>
+      </c>
+      <c r="D454" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>0</v>
+      </c>
+      <c r="E454" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>0</v>
+      </c>
+      <c r="F454" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>0</v>
+      </c>
+      <c r="G454" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>3000000</v>
+      </c>
+      <c r="H454" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
+        <v>9000000</v>
+      </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A455" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B455" s="3"/>
-      <c r="C455" s="3"/>
-      <c r="D455" s="3"/>
-      <c r="E455" s="3"/>
-      <c r="F455" s="3"/>
-      <c r="G455" s="3"/>
-      <c r="H455" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="B455" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>171000000</v>
+      </c>
+      <c r="C455" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>42750000</v>
+      </c>
+      <c r="D455" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>5880000</v>
+      </c>
+      <c r="E455" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>0</v>
+      </c>
+      <c r="F455" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>5880000</v>
+      </c>
+      <c r="G455" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>36870000</v>
+      </c>
+      <c r="H455" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
+        <v>128250000</v>
+      </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A456" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B456" s="3"/>
-      <c r="C456" s="3"/>
-      <c r="D456" s="3"/>
-      <c r="E456" s="3"/>
-      <c r="F456" s="3"/>
-      <c r="G456" s="3"/>
-      <c r="H456" s="3"/>
+        <v>134</v>
+      </c>
+      <c r="B456" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>130000000</v>
+      </c>
+      <c r="C456" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>32500000</v>
+      </c>
+      <c r="D456" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>0</v>
+      </c>
+      <c r="E456" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>7381250</v>
+      </c>
+      <c r="F456" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>7381250</v>
+      </c>
+      <c r="G456" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>25118750</v>
+      </c>
+      <c r="H456" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
+        <v>97500000</v>
+      </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A457" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B457" s="3"/>
-      <c r="C457" s="3"/>
-      <c r="D457" s="3"/>
-      <c r="E457" s="3"/>
-      <c r="F457" s="3"/>
-      <c r="G457" s="3"/>
-      <c r="H457" s="3"/>
+        <v>135</v>
+      </c>
+      <c r="B457" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>6660000</v>
+      </c>
+      <c r="C457" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>1665000</v>
+      </c>
+      <c r="D457" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>1665000</v>
+      </c>
+      <c r="E457" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>0</v>
+      </c>
+      <c r="F457" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>1665000</v>
+      </c>
+      <c r="G457" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>0</v>
+      </c>
+      <c r="H457" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
+        <v>4995000</v>
+      </c>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A458" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B458" s="3"/>
-      <c r="C458" s="3"/>
-      <c r="D458" s="3"/>
-      <c r="E458" s="3"/>
-      <c r="F458" s="3"/>
-      <c r="G458" s="3"/>
-      <c r="H458" s="3"/>
+        <v>136</v>
+      </c>
+      <c r="B458" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>6000000</v>
+      </c>
+      <c r="C458" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>1500000</v>
+      </c>
+      <c r="D458" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>0</v>
+      </c>
+      <c r="E458" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>0</v>
+      </c>
+      <c r="F458" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>0</v>
+      </c>
+      <c r="G458" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>1500000</v>
+      </c>
+      <c r="H458" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
+        <v>4500000</v>
+      </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A459" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B459" s="3"/>
-      <c r="C459" s="3"/>
-      <c r="D459" s="3"/>
-      <c r="E459" s="3"/>
-      <c r="F459" s="3"/>
-      <c r="G459" s="3"/>
-      <c r="H459" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="B459" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="C459" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="D459" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="E459" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="F459" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="G459" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
+      <c r="H459" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A460" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B460" s="3"/>
-      <c r="C460" s="3"/>
-      <c r="D460" s="3"/>
-      <c r="E460" s="3"/>
-      <c r="F460" s="3"/>
-      <c r="G460" s="3"/>
-      <c r="H460" s="3"/>
+        <v>138</v>
+      </c>
+      <c r="B460" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="C460" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="D460" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="E460" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="F460" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="G460" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
+      <c r="H460" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A461" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B461" s="3"/>
-      <c r="C461" s="3"/>
-      <c r="D461" s="3"/>
-      <c r="E461" s="3"/>
-      <c r="F461" s="3"/>
-      <c r="G461" s="3"/>
-      <c r="H461" s="3"/>
+        <v>139</v>
+      </c>
+      <c r="B461" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="C461" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="D461" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="E461" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="F461" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="G461" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
+      <c r="H461" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A462" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B462" s="3"/>
-      <c r="C462" s="3"/>
-      <c r="D462" s="3"/>
-      <c r="E462" s="3"/>
-      <c r="F462" s="3"/>
-      <c r="G462" s="3"/>
-      <c r="H462" s="3"/>
+        <v>140</v>
+      </c>
+      <c r="B462" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="C462" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="D462" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="E462" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="F462" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="G462" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
+      <c r="H462" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A463" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B463" s="3"/>
-      <c r="C463" s="3"/>
-      <c r="D463" s="3"/>
-      <c r="E463" s="3"/>
-      <c r="F463" s="3"/>
-      <c r="G463" s="3"/>
-      <c r="H463" s="3"/>
+        <v>141</v>
+      </c>
+      <c r="B463" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="C463" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="D463" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="E463" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="F463" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="G463" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
+      <c r="H463" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A464" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B464" s="3"/>
-      <c r="C464" s="3"/>
-      <c r="D464" s="3"/>
-      <c r="E464" s="3"/>
-      <c r="F464" s="3"/>
-      <c r="G464" s="3"/>
-      <c r="H464" s="3"/>
+        <v>142</v>
+      </c>
+      <c r="B464" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="C464" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="D464" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="E464" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="F464" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="G464" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
+      <c r="H464" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A465" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B465" s="3"/>
-      <c r="C465" s="3"/>
-      <c r="D465" s="3"/>
-      <c r="E465" s="3"/>
-      <c r="F465" s="3"/>
-      <c r="G465" s="3"/>
-      <c r="H465" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="B465" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="C465" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="D465" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="E465" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="F465" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="G465" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
+      <c r="H465" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A466" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B466" s="3"/>
-      <c r="C466" s="3"/>
-      <c r="D466" s="3"/>
-      <c r="E466" s="3"/>
-      <c r="F466" s="3"/>
-      <c r="G466" s="3"/>
-      <c r="H466" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="B466" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="C466" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="D466" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="E466" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="F466" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="G466" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
+      <c r="H466" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A467" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B467" s="3"/>
-      <c r="C467" s="3"/>
-      <c r="D467" s="3"/>
-      <c r="E467" s="3"/>
-      <c r="F467" s="3"/>
-      <c r="G467" s="3"/>
-      <c r="H467" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="B467" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="C467" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="D467" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="E467" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="F467" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="G467" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
+      <c r="H467" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A468" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B468" s="3"/>
-      <c r="C468" s="3"/>
-      <c r="D468" s="3"/>
-      <c r="E468" s="3"/>
-      <c r="F468" s="3"/>
-      <c r="G468" s="3"/>
-      <c r="H468" s="3"/>
+        <v>146</v>
+      </c>
+      <c r="B468" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="C468" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="D468" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="E468" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="F468" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="G468" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
+      <c r="H468" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A469" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B469" s="3"/>
-      <c r="C469" s="3"/>
-      <c r="D469" s="3"/>
-      <c r="E469" s="3"/>
-      <c r="F469" s="3"/>
-      <c r="G469" s="3"/>
-      <c r="H469" s="3"/>
+        <v>147</v>
+      </c>
+      <c r="B469" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="C469" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="D469" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="E469" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="F469" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="G469" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
+      <c r="H469" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A470" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B470" s="3"/>
-      <c r="C470" s="3"/>
-      <c r="D470" s="3"/>
-      <c r="E470" s="3"/>
-      <c r="F470" s="3"/>
-      <c r="G470" s="3"/>
-      <c r="H470" s="3"/>
+        <v>148</v>
+      </c>
+      <c r="B470" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="C470" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="D470" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="E470" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="F470" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="G470" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
+      <c r="H470" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A471" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B471" s="3"/>
-      <c r="C471" s="3"/>
-      <c r="D471" s="3"/>
-      <c r="E471" s="3"/>
-      <c r="F471" s="3"/>
-      <c r="G471" s="3"/>
-      <c r="H471" s="3"/>
+        <v>149</v>
+      </c>
+      <c r="B471" s="3">
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="C471" s="3">
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="D471" s="3">
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="E471" s="3">
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="F471" s="3">
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="G471" s="3">
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
+      <c r="H471" s="3">
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A472" s="1" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="B472" s="3">
-        <f>SUM(B420:B471)</f>
-        <v>2349760730</v>
+        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>2349761000</v>
       </c>
       <c r="C472" s="3">
-        <f t="shared" ref="C472:H472" si="0">SUM(C420:C471)</f>
-        <v>2349760730</v>
+        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>1085685500</v>
       </c>
       <c r="D472" s="3">
-        <f t="shared" si="0"/>
-        <v>429270952</v>
+        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>443295900</v>
       </c>
       <c r="E472" s="3">
-        <f t="shared" si="0"/>
-        <v>90620828</v>
+        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>80000880</v>
       </c>
       <c r="F472" s="3">
-        <f t="shared" si="0"/>
-        <v>519891780</v>
+        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>523296780</v>
       </c>
       <c r="G472" s="3">
-        <f t="shared" si="0"/>
-        <v>1829868950</v>
+        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>562388720</v>
       </c>
       <c r="H472" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
+        <v>1264075500</v>
       </c>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.45">
@@ -12874,22 +14028,22 @@
         <v>8</v>
       </c>
       <c r="B473" s="2">
-        <v>6121242000</v>
+        <v>10505111000</v>
       </c>
       <c r="C473" s="2">
-        <v>6121242000</v>
+        <v>10505111000</v>
       </c>
       <c r="D473" s="2">
-        <v>5458456599</v>
+        <v>7767056599</v>
       </c>
       <c r="E473" s="2">
         <v>0</v>
       </c>
       <c r="F473" s="2">
-        <v>5458456599</v>
+        <v>7767056599</v>
       </c>
       <c r="G473" s="2">
-        <v>662785401</v>
+        <v>2738054401</v>
       </c>
       <c r="H473" s="2">
         <v>0</v>
@@ -13027,7 +14181,7 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B479" s="2">
         <v>0</v>
@@ -13053,13 +14207,13 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="B480" s="2">
-        <v>1778331214</v>
+        <v>2312795000</v>
       </c>
       <c r="C480" s="2">
-        <v>1778331214</v>
+        <v>2312795000</v>
       </c>
       <c r="D480" s="2">
         <v>1778331214</v>
@@ -13071,7 +14225,7 @@
         <v>1778331214</v>
       </c>
       <c r="G480" s="2">
-        <v>0</v>
+        <v>534463786</v>
       </c>
       <c r="H480" s="2">
         <v>0</v>
@@ -13082,22 +14236,22 @@
         <v>53</v>
       </c>
       <c r="B481" s="2">
-        <v>2094950000</v>
+        <v>4989900000</v>
       </c>
       <c r="C481" s="2">
-        <v>2094950000</v>
+        <v>4989900000</v>
       </c>
       <c r="D481" s="2">
-        <v>897050889</v>
+        <v>805666889</v>
       </c>
       <c r="E481" s="2">
-        <v>235941248</v>
+        <v>333634248</v>
       </c>
       <c r="F481" s="2">
-        <v>1132992137</v>
+        <v>1139301137</v>
       </c>
       <c r="G481" s="2">
-        <v>961957863</v>
+        <v>3850598863</v>
       </c>
       <c r="H481" s="2">
         <v>0</v>
@@ -13105,7 +14259,7 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="B482" s="2">
         <v>0</v>
@@ -13134,10 +14288,10 @@
         <v>54</v>
       </c>
       <c r="B483" s="2">
-        <v>840000000</v>
+        <v>1680000000</v>
       </c>
       <c r="C483" s="2">
-        <v>840000000</v>
+        <v>1680000000</v>
       </c>
       <c r="D483" s="2">
         <v>353557050</v>
@@ -13149,7 +14303,7 @@
         <v>353557050</v>
       </c>
       <c r="G483" s="2">
-        <v>486442950</v>
+        <v>1326442950</v>
       </c>
       <c r="H483" s="2">
         <v>0</v>
@@ -13160,22 +14314,22 @@
         <v>77</v>
       </c>
       <c r="B484" s="2">
-        <v>246033000</v>
+        <v>492066000</v>
       </c>
       <c r="C484" s="2">
-        <v>246033000</v>
+        <v>492066000</v>
       </c>
       <c r="D484" s="2">
-        <v>4400000</v>
+        <v>31501365</v>
       </c>
       <c r="E484" s="2">
         <v>7785500</v>
       </c>
       <c r="F484" s="2">
-        <v>12185500</v>
+        <v>39286865</v>
       </c>
       <c r="G484" s="2">
-        <v>233847500</v>
+        <v>452779135</v>
       </c>
       <c r="H484" s="2">
         <v>0</v>
@@ -13183,13 +14337,13 @@
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="B485" s="2">
-        <v>312250000</v>
+        <v>624500000</v>
       </c>
       <c r="C485" s="2">
-        <v>312250000</v>
+        <v>624500000</v>
       </c>
       <c r="D485" s="2">
         <v>0</v>
@@ -13201,7 +14355,7 @@
         <v>0</v>
       </c>
       <c r="G485" s="2">
-        <v>312250000</v>
+        <v>624500000</v>
       </c>
       <c r="H485" s="2">
         <v>0</v>
@@ -13209,13 +14363,13 @@
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="B486" s="2">
-        <v>350000000</v>
+        <v>700000000</v>
       </c>
       <c r="C486" s="2">
-        <v>350000000</v>
+        <v>700000000</v>
       </c>
       <c r="D486" s="2">
         <v>0</v>
@@ -13227,7 +14381,7 @@
         <v>0</v>
       </c>
       <c r="G486" s="2">
-        <v>350000000</v>
+        <v>700000000</v>
       </c>
       <c r="H486" s="2">
         <v>0</v>
@@ -13235,7 +14389,7 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="B487" s="2">
         <v>0</v>
@@ -13261,25 +14415,25 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="B488" s="2">
-        <v>372500000</v>
+        <v>745000000</v>
       </c>
       <c r="C488" s="2">
-        <v>372500000</v>
+        <v>745000000</v>
       </c>
       <c r="D488" s="2">
-        <v>19421480</v>
+        <v>26235280</v>
       </c>
       <c r="E488" s="2">
         <v>32460000</v>
       </c>
       <c r="F488" s="2">
-        <v>51881480</v>
+        <v>58695280</v>
       </c>
       <c r="G488" s="2">
-        <v>320618520</v>
+        <v>686304720</v>
       </c>
       <c r="H488" s="2">
         <v>0</v>
@@ -13287,25 +14441,25 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="B489" s="2">
-        <v>2397799000</v>
+        <v>4029356000</v>
       </c>
       <c r="C489" s="2">
-        <v>2397799000</v>
+        <v>4029356000</v>
       </c>
       <c r="D489" s="2">
-        <v>459375000</v>
+        <v>2411599000</v>
       </c>
       <c r="E489" s="2">
         <v>29795000</v>
       </c>
       <c r="F489" s="2">
-        <v>489170000</v>
+        <v>2441394000</v>
       </c>
       <c r="G489" s="2">
-        <v>1908629000</v>
+        <v>1587962000</v>
       </c>
       <c r="H489" s="2">
         <v>0</v>
@@ -13313,13 +14467,13 @@
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="B490" s="2">
-        <v>1098750000</v>
+        <v>297500000</v>
       </c>
       <c r="C490" s="2">
-        <v>1098750000</v>
+        <v>297500000</v>
       </c>
       <c r="D490" s="2">
         <v>0</v>
@@ -13331,7 +14485,7 @@
         <v>0</v>
       </c>
       <c r="G490" s="2">
-        <v>1098750000</v>
+        <v>297500000</v>
       </c>
       <c r="H490" s="2">
         <v>0</v>
@@ -13342,10 +14496,10 @@
         <v>55</v>
       </c>
       <c r="B491" s="2">
-        <v>133125000</v>
+        <v>266250000</v>
       </c>
       <c r="C491" s="2">
-        <v>133125000</v>
+        <v>266250000</v>
       </c>
       <c r="D491" s="2">
         <v>0</v>
@@ -13357,7 +14511,7 @@
         <v>40800000</v>
       </c>
       <c r="G491" s="2">
-        <v>92325000</v>
+        <v>225450000</v>
       </c>
       <c r="H491" s="2">
         <v>0</v>
@@ -13368,10 +14522,10 @@
         <v>56</v>
       </c>
       <c r="B492" s="2">
-        <v>375000000</v>
+        <v>1350000000</v>
       </c>
       <c r="C492" s="2">
-        <v>375000000</v>
+        <v>1350000000</v>
       </c>
       <c r="D492" s="2">
         <v>0</v>
@@ -13383,7 +14537,7 @@
         <v>0</v>
       </c>
       <c r="G492" s="2">
-        <v>375000000</v>
+        <v>1350000000</v>
       </c>
       <c r="H492" s="2">
         <v>0</v>
@@ -13394,10 +14548,10 @@
         <v>22</v>
       </c>
       <c r="B493" s="2">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="C493" s="2">
-        <v>50000000</v>
+        <v>75000000</v>
       </c>
       <c r="D493" s="2">
         <v>0</v>
@@ -13409,10 +14563,10 @@
         <v>12720000</v>
       </c>
       <c r="G493" s="2">
-        <v>37280000</v>
+        <v>62280000</v>
       </c>
       <c r="H493" s="2">
-        <v>0</v>
+        <v>25000000</v>
       </c>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.45">
@@ -13420,10 +14574,10 @@
         <v>57</v>
       </c>
       <c r="B494" s="2">
-        <v>508075000</v>
+        <v>1016150000</v>
       </c>
       <c r="C494" s="2">
-        <v>508075000</v>
+        <v>1016150000</v>
       </c>
       <c r="D494" s="2">
         <v>34825000</v>
@@ -13435,7 +14589,7 @@
         <v>163165000</v>
       </c>
       <c r="G494" s="2">
-        <v>344910000</v>
+        <v>852985000</v>
       </c>
       <c r="H494" s="2">
         <v>0</v>
@@ -13446,10 +14600,10 @@
         <v>58</v>
       </c>
       <c r="B495" s="2">
-        <v>640000000</v>
+        <v>2560000000</v>
       </c>
       <c r="C495" s="2">
-        <v>640000000</v>
+        <v>2560000000</v>
       </c>
       <c r="D495" s="2">
         <v>8404406</v>
@@ -13461,7 +14615,7 @@
         <v>455035109</v>
       </c>
       <c r="G495" s="2">
-        <v>184964891</v>
+        <v>2104964891</v>
       </c>
       <c r="H495" s="2">
         <v>0</v>
@@ -13472,10 +14626,10 @@
         <v>25</v>
       </c>
       <c r="B496" s="2">
-        <v>222793250</v>
+        <v>891173000</v>
       </c>
       <c r="C496" s="2">
-        <v>222793250</v>
+        <v>668379750</v>
       </c>
       <c r="D496" s="2">
         <v>29693828</v>
@@ -13487,10 +14641,10 @@
         <v>52063828</v>
       </c>
       <c r="G496" s="2">
-        <v>170729422</v>
+        <v>616315922</v>
       </c>
       <c r="H496" s="2">
-        <v>0</v>
+        <v>222793250</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.45">
@@ -13498,10 +14652,10 @@
         <v>26</v>
       </c>
       <c r="B497" s="2">
-        <v>278081750</v>
+        <v>1160455000</v>
       </c>
       <c r="C497" s="2">
-        <v>278081750</v>
+        <v>870341250</v>
       </c>
       <c r="D497" s="2">
         <v>95838170</v>
@@ -13513,10 +14667,10 @@
         <v>272779430</v>
       </c>
       <c r="G497" s="2">
-        <v>5302320</v>
+        <v>597561820</v>
       </c>
       <c r="H497" s="2">
-        <v>0</v>
+        <v>290113750</v>
       </c>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.45">
@@ -13524,10 +14678,10 @@
         <v>27</v>
       </c>
       <c r="B498" s="2">
-        <v>23250000</v>
+        <v>93000000</v>
       </c>
       <c r="C498" s="2">
-        <v>23250000</v>
+        <v>93000000</v>
       </c>
       <c r="D498" s="2">
         <v>0</v>
@@ -13539,7 +14693,7 @@
         <v>14500000</v>
       </c>
       <c r="G498" s="2">
-        <v>8750000</v>
+        <v>78500000</v>
       </c>
       <c r="H498" s="2">
         <v>0</v>
@@ -13550,10 +14704,10 @@
         <v>28</v>
       </c>
       <c r="B499" s="2">
-        <v>163230750</v>
+        <v>562923000</v>
       </c>
       <c r="C499" s="2">
-        <v>163230750</v>
+        <v>422192250</v>
       </c>
       <c r="D499" s="2">
         <v>19366000</v>
@@ -13565,10 +14719,10 @@
         <v>32006000</v>
       </c>
       <c r="G499" s="2">
-        <v>131224750</v>
+        <v>390186250</v>
       </c>
       <c r="H499" s="2">
-        <v>0</v>
+        <v>140730750</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.45">
@@ -13576,25 +14730,25 @@
         <v>30</v>
       </c>
       <c r="B500" s="2">
-        <v>172144500</v>
+        <v>688578000</v>
       </c>
       <c r="C500" s="2">
-        <v>172144500</v>
+        <v>516433500</v>
       </c>
       <c r="D500" s="2">
         <v>35082547</v>
       </c>
       <c r="E500" s="2">
-        <v>77886880</v>
+        <v>77961880</v>
       </c>
       <c r="F500" s="2">
-        <v>112969427</v>
+        <v>113044427</v>
       </c>
       <c r="G500" s="2">
-        <v>59175073</v>
+        <v>403389073</v>
       </c>
       <c r="H500" s="2">
-        <v>0</v>
+        <v>172144500</v>
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.45">
@@ -13602,10 +14756,10 @@
         <v>79</v>
       </c>
       <c r="B501" s="2">
-        <v>9045000</v>
+        <v>36180000</v>
       </c>
       <c r="C501" s="2">
-        <v>9045000</v>
+        <v>36180000</v>
       </c>
       <c r="D501" s="2">
         <v>1720000</v>
@@ -13617,7 +14771,7 @@
         <v>7062537</v>
       </c>
       <c r="G501" s="2">
-        <v>1982463</v>
+        <v>29117463</v>
       </c>
       <c r="H501" s="2">
         <v>0</v>
@@ -13628,10 +14782,10 @@
         <v>31</v>
       </c>
       <c r="B502" s="2">
-        <v>40435250</v>
+        <v>61741000</v>
       </c>
       <c r="C502" s="2">
-        <v>40435250</v>
+        <v>61741000</v>
       </c>
       <c r="D502" s="2">
         <v>38255444</v>
@@ -13643,7 +14797,7 @@
         <v>38255444</v>
       </c>
       <c r="G502" s="2">
-        <v>2179806</v>
+        <v>23485556</v>
       </c>
       <c r="H502" s="2">
         <v>0</v>
@@ -13741,13 +14895,13 @@
         <v>0</v>
       </c>
       <c r="E506" s="2">
-        <v>1814032650</v>
+        <v>1814036400</v>
       </c>
       <c r="F506" s="2">
-        <v>1814032650</v>
+        <v>1814036400</v>
       </c>
       <c r="G506" s="2">
-        <v>10350249247</v>
+        <v>10350245497</v>
       </c>
       <c r="H506" s="2">
         <v>0</v>
@@ -13963,28 +15117,28 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="B515" s="2">
-        <v>44562890151</v>
+        <v>61498532437</v>
       </c>
       <c r="C515" s="2">
-        <v>44562890151</v>
+        <v>60647750187</v>
       </c>
       <c r="D515" s="2">
-        <v>9233777627</v>
+        <v>13437132792</v>
       </c>
       <c r="E515" s="2">
-        <v>5755634781</v>
+        <v>5853406531</v>
       </c>
       <c r="F515" s="2">
-        <v>14989412408</v>
+        <v>19290539323</v>
       </c>
       <c r="G515" s="2">
-        <v>29573477743</v>
+        <v>41357210864</v>
       </c>
       <c r="H515" s="2">
-        <v>0</v>
+        <v>850782250</v>
       </c>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.45">
@@ -13998,16 +15152,16 @@
         <v>5574698000</v>
       </c>
       <c r="D516" s="2">
-        <v>2595236997</v>
+        <v>5471087865</v>
       </c>
       <c r="E516" s="2">
         <v>0</v>
       </c>
       <c r="F516" s="2">
-        <v>2595236997</v>
+        <v>5471087865</v>
       </c>
       <c r="G516" s="2">
-        <v>2979461003</v>
+        <v>103610135</v>
       </c>
       <c r="H516" s="2">
         <v>0</v>
@@ -14024,16 +15178,16 @@
         <v>1521000000</v>
       </c>
       <c r="D517" s="2">
-        <v>0</v>
+        <v>1467022165</v>
       </c>
       <c r="E517" s="2">
         <v>3328300</v>
       </c>
       <c r="F517" s="2">
-        <v>3328300</v>
+        <v>1470350465</v>
       </c>
       <c r="G517" s="2">
-        <v>1517671700</v>
+        <v>50649535</v>
       </c>
       <c r="H517" s="2">
         <v>0</v>
@@ -14050,16 +15204,16 @@
         <v>1694175000</v>
       </c>
       <c r="D518" s="2">
-        <v>810860400</v>
+        <v>1694174158</v>
       </c>
       <c r="E518" s="2">
         <v>0</v>
       </c>
       <c r="F518" s="2">
-        <v>810860400</v>
+        <v>1694174158</v>
       </c>
       <c r="G518" s="2">
-        <v>883314600</v>
+        <v>842</v>
       </c>
       <c r="H518" s="2">
         <v>0</v>
@@ -14076,16 +15230,16 @@
         <v>2639000000</v>
       </c>
       <c r="D519" s="2">
-        <v>483429478</v>
+        <v>546436863</v>
       </c>
       <c r="E519" s="2">
         <v>129199870</v>
       </c>
       <c r="F519" s="2">
-        <v>612629348</v>
+        <v>675636733</v>
       </c>
       <c r="G519" s="2">
-        <v>2026370652</v>
+        <v>1963363267</v>
       </c>
       <c r="H519" s="2">
         <v>0</v>
@@ -14102,16 +15256,16 @@
         <v>150000000</v>
       </c>
       <c r="D520" s="2">
-        <v>0</v>
+        <v>9000000</v>
       </c>
       <c r="E520" s="2">
         <v>0</v>
       </c>
       <c r="F520" s="2">
-        <v>0</v>
+        <v>9000000</v>
       </c>
       <c r="G520" s="2">
-        <v>150000000</v>
+        <v>141000000</v>
       </c>
       <c r="H520" s="2">
         <v>0</v>
@@ -14128,16 +15282,16 @@
         <v>2721193000</v>
       </c>
       <c r="D521" s="2">
-        <v>777673392</v>
+        <v>2263795563</v>
       </c>
       <c r="E521" s="2">
         <v>0</v>
       </c>
       <c r="F521" s="2">
-        <v>777673392</v>
+        <v>2263795563</v>
       </c>
       <c r="G521" s="2">
-        <v>1943519608</v>
+        <v>457397437</v>
       </c>
       <c r="H521" s="2">
         <v>0</v>
@@ -14154,16 +15308,16 @@
         <v>9794675000</v>
       </c>
       <c r="D522" s="2">
-        <v>4877544282</v>
+        <v>8772973347</v>
       </c>
       <c r="E522" s="2">
         <v>3607897</v>
       </c>
       <c r="F522" s="2">
-        <v>4881152179</v>
+        <v>8776581244</v>
       </c>
       <c r="G522" s="2">
-        <v>4913522821</v>
+        <v>1018093756</v>
       </c>
       <c r="H522" s="2">
         <v>0</v>
@@ -14258,16 +15412,16 @@
         <v>915811000</v>
       </c>
       <c r="D526" s="2">
-        <v>0</v>
+        <v>715028125</v>
       </c>
       <c r="E526" s="2">
         <v>0</v>
       </c>
       <c r="F526" s="2">
-        <v>0</v>
+        <v>715028125</v>
       </c>
       <c r="G526" s="2">
-        <v>915811000</v>
+        <v>200782875</v>
       </c>
       <c r="H526" s="2">
         <v>0</v>
@@ -14284,16 +15438,16 @@
         <v>1750000000</v>
       </c>
       <c r="D527" s="2">
-        <v>498500000</v>
+        <v>957373034</v>
       </c>
       <c r="E527" s="2">
         <v>0</v>
       </c>
       <c r="F527" s="2">
-        <v>498500000</v>
+        <v>957373034</v>
       </c>
       <c r="G527" s="2">
-        <v>1251500000</v>
+        <v>792626966</v>
       </c>
       <c r="H527" s="2">
         <v>0</v>
@@ -14336,16 +15490,16 @@
         <v>483750000</v>
       </c>
       <c r="D529" s="2">
-        <v>14815000</v>
+        <v>114815000</v>
       </c>
       <c r="E529" s="2">
         <v>68355000</v>
       </c>
       <c r="F529" s="2">
-        <v>83170000</v>
+        <v>183170000</v>
       </c>
       <c r="G529" s="2">
-        <v>400580000</v>
+        <v>300580000</v>
       </c>
       <c r="H529" s="2">
         <v>161250000</v>
@@ -14521,13 +15675,13 @@
         <v>17298750</v>
       </c>
       <c r="E536" s="2">
-        <v>64965000</v>
+        <v>65252500</v>
       </c>
       <c r="F536" s="2">
-        <v>82263750</v>
+        <v>82551250</v>
       </c>
       <c r="G536" s="2">
-        <v>254538750</v>
+        <v>254251250</v>
       </c>
       <c r="H536" s="2">
         <v>112267500</v>
@@ -14599,13 +15753,13 @@
         <v>0</v>
       </c>
       <c r="E539" s="2">
-        <v>1592655254</v>
+        <v>1592659004</v>
       </c>
       <c r="F539" s="2">
-        <v>1592655254</v>
+        <v>1592659004</v>
       </c>
       <c r="G539" s="2">
-        <v>9096261612</v>
+        <v>9096257862</v>
       </c>
       <c r="H539" s="2">
         <v>0</v>
@@ -14795,7 +15949,7 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="B547" s="2">
         <v>58569240973</v>
@@ -14804,16 +15958,16 @@
         <v>57848682223</v>
       </c>
       <c r="D547" s="2">
-        <v>10131101660</v>
+        <v>22084748231</v>
       </c>
       <c r="E547" s="2">
-        <v>4495816582</v>
+        <v>4496107832</v>
       </c>
       <c r="F547" s="2">
-        <v>14626918242</v>
+        <v>26580856063</v>
       </c>
       <c r="G547" s="2">
-        <v>43221763981</v>
+        <v>31267826160</v>
       </c>
       <c r="H547" s="2">
         <v>720558750</v>
@@ -14821,5 +15975,1491 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74037102-CAE5-4DA3-AC4F-276E222EA2EC}">
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.25" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="60.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="15.265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="15.265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="4">
+        <v>873740000</v>
+      </c>
+      <c r="C2" s="5">
+        <f>B2</f>
+        <v>873740000</v>
+      </c>
+      <c r="D2" s="5">
+        <f>C2/2</f>
+        <v>436870000</v>
+      </c>
+      <c r="E2" s="4">
+        <f>IF(B2="","",G2-F2)</f>
+        <v>404360000</v>
+      </c>
+      <c r="F2" s="5">
+        <v>35605052</v>
+      </c>
+      <c r="G2" s="5">
+        <v>439965052</v>
+      </c>
+      <c r="H2" s="4">
+        <f>IF(B2="","",D2-G2)</f>
+        <v>-3095052</v>
+      </c>
+      <c r="I2" s="4">
+        <f>IF(B2="","",C2-D2)</f>
+        <v>436870000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5">
+        <f t="shared" ref="C3:C27" si="0">B3</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <f t="shared" ref="D3:D27" si="1">C3/2</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="str">
+        <f t="shared" ref="E3:E53" si="2">IF(B3="","",G3-F3)</f>
+        <v/>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="4" t="str">
+        <f t="shared" ref="H3:H53" si="3">IF(B3="","",D3-G3)</f>
+        <v/>
+      </c>
+      <c r="I3" s="4" t="str">
+        <f t="shared" ref="I3:I53" si="4">IF(B3="","",C3-D3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I4" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I5" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I6" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I7" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I8" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I9" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I10" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I11" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I12" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I13" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I14" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I15" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I16" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I17" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I18" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="4">
+        <v>474786000</v>
+      </c>
+      <c r="C19" s="5">
+        <f t="shared" si="0"/>
+        <v>474786000</v>
+      </c>
+      <c r="D19" s="5">
+        <f t="shared" si="1"/>
+        <v>237393000</v>
+      </c>
+      <c r="E19" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="4">
+        <f t="shared" si="3"/>
+        <v>237393000</v>
+      </c>
+      <c r="I19" s="4">
+        <f t="shared" si="4"/>
+        <v>237393000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="4">
+        <v>208425000</v>
+      </c>
+      <c r="C20" s="5">
+        <f t="shared" si="0"/>
+        <v>208425000</v>
+      </c>
+      <c r="D20" s="5">
+        <f t="shared" si="1"/>
+        <v>104212500</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="4">
+        <f t="shared" si="3"/>
+        <v>104212500</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="4"/>
+        <v>104212500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="4">
+        <v>20000000</v>
+      </c>
+      <c r="C21" s="5">
+        <f>B21</f>
+        <v>20000000</v>
+      </c>
+      <c r="D21" s="5">
+        <v>13970000</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" si="2"/>
+        <v>13970000</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5">
+        <v>13970000</v>
+      </c>
+      <c r="H21" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="4">
+        <f t="shared" si="4"/>
+        <v>6030000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="4">
+        <v>220000000</v>
+      </c>
+      <c r="C22" s="5">
+        <f t="shared" si="0"/>
+        <v>220000000</v>
+      </c>
+      <c r="D22" s="5">
+        <f t="shared" si="1"/>
+        <v>110000000</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>29896778</v>
+      </c>
+      <c r="G22" s="5">
+        <v>29896778</v>
+      </c>
+      <c r="H22" s="4">
+        <f t="shared" si="3"/>
+        <v>80103222</v>
+      </c>
+      <c r="I22" s="4">
+        <f t="shared" si="4"/>
+        <v>110000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="4">
+        <v>75000000</v>
+      </c>
+      <c r="C23" s="5">
+        <f t="shared" si="0"/>
+        <v>75000000</v>
+      </c>
+      <c r="D23" s="5">
+        <f t="shared" si="1"/>
+        <v>37500000</v>
+      </c>
+      <c r="E23" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="4">
+        <f t="shared" si="3"/>
+        <v>37500000</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" si="4"/>
+        <v>37500000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I24" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D25" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I25" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="4">
+        <v>60000000</v>
+      </c>
+      <c r="C26" s="5">
+        <f t="shared" si="0"/>
+        <v>60000000</v>
+      </c>
+      <c r="D26" s="5">
+        <f t="shared" si="1"/>
+        <v>30000000</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="2"/>
+        <v>9000000</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5">
+        <v>9000000</v>
+      </c>
+      <c r="H26" s="4">
+        <f t="shared" si="3"/>
+        <v>21000000</v>
+      </c>
+      <c r="I26" s="4">
+        <f t="shared" si="4"/>
+        <v>30000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" s="4">
+        <v>45150000</v>
+      </c>
+      <c r="C27" s="5">
+        <f t="shared" si="0"/>
+        <v>45150000</v>
+      </c>
+      <c r="D27" s="5">
+        <f t="shared" si="1"/>
+        <v>22575000</v>
+      </c>
+      <c r="E27" s="4">
+        <f t="shared" si="2"/>
+        <v>6423200</v>
+      </c>
+      <c r="F27" s="5">
+        <v>6119400</v>
+      </c>
+      <c r="G27" s="5">
+        <v>12542600</v>
+      </c>
+      <c r="H27" s="4">
+        <f t="shared" si="3"/>
+        <v>10032400</v>
+      </c>
+      <c r="I27" s="4">
+        <f t="shared" si="4"/>
+        <v>22575000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I28" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I29" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I30" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I31" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I32" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I33" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="4">
+        <v>6000000</v>
+      </c>
+      <c r="C34" s="5">
+        <f>B34</f>
+        <v>6000000</v>
+      </c>
+      <c r="D34" s="5">
+        <f>C34/4</f>
+        <v>1500000</v>
+      </c>
+      <c r="E34" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="4">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="I34" s="4">
+        <f t="shared" si="4"/>
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="4">
+        <v>41000000</v>
+      </c>
+      <c r="C35" s="5">
+        <f t="shared" ref="C35:C40" si="5">B35</f>
+        <v>41000000</v>
+      </c>
+      <c r="D35" s="5">
+        <f t="shared" ref="D35:D40" si="6">C35/4</f>
+        <v>10250000</v>
+      </c>
+      <c r="E35" s="4">
+        <f t="shared" si="2"/>
+        <v>1997700</v>
+      </c>
+      <c r="F35" s="5">
+        <v>998400</v>
+      </c>
+      <c r="G35" s="5">
+        <v>2996100</v>
+      </c>
+      <c r="H35" s="4">
+        <f t="shared" si="3"/>
+        <v>7253900</v>
+      </c>
+      <c r="I35" s="4">
+        <f t="shared" si="4"/>
+        <v>30750000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" s="4">
+        <v>12000000</v>
+      </c>
+      <c r="C36" s="5">
+        <f t="shared" si="5"/>
+        <v>12000000</v>
+      </c>
+      <c r="D36" s="5">
+        <f t="shared" si="6"/>
+        <v>3000000</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="4">
+        <f t="shared" si="3"/>
+        <v>3000000</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="4"/>
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" s="4">
+        <v>171000000</v>
+      </c>
+      <c r="C37" s="5">
+        <f t="shared" si="5"/>
+        <v>171000000</v>
+      </c>
+      <c r="D37" s="5">
+        <f t="shared" si="6"/>
+        <v>42750000</v>
+      </c>
+      <c r="E37" s="4">
+        <f t="shared" si="2"/>
+        <v>5880000</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5">
+        <v>5880000</v>
+      </c>
+      <c r="H37" s="4">
+        <f t="shared" si="3"/>
+        <v>36870000</v>
+      </c>
+      <c r="I37" s="4">
+        <f t="shared" si="4"/>
+        <v>128250000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" s="4">
+        <v>130000000</v>
+      </c>
+      <c r="C38" s="5">
+        <f t="shared" si="5"/>
+        <v>130000000</v>
+      </c>
+      <c r="D38" s="5">
+        <f t="shared" si="6"/>
+        <v>32500000</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="5">
+        <v>7381250</v>
+      </c>
+      <c r="G38" s="5">
+        <v>7381250</v>
+      </c>
+      <c r="H38" s="4">
+        <f t="shared" si="3"/>
+        <v>25118750</v>
+      </c>
+      <c r="I38" s="4">
+        <f t="shared" si="4"/>
+        <v>97500000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="4">
+        <v>6660000</v>
+      </c>
+      <c r="C39" s="5">
+        <f t="shared" si="5"/>
+        <v>6660000</v>
+      </c>
+      <c r="D39" s="5">
+        <f t="shared" si="6"/>
+        <v>1665000</v>
+      </c>
+      <c r="E39" s="4">
+        <f t="shared" si="2"/>
+        <v>1665000</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5">
+        <v>1665000</v>
+      </c>
+      <c r="H39" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="4">
+        <f t="shared" si="4"/>
+        <v>4995000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" s="4">
+        <v>6000000</v>
+      </c>
+      <c r="C40" s="5">
+        <f t="shared" si="5"/>
+        <v>6000000</v>
+      </c>
+      <c r="D40" s="5">
+        <f t="shared" si="6"/>
+        <v>1500000</v>
+      </c>
+      <c r="E40" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="4">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="I40" s="4">
+        <f t="shared" si="4"/>
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I41" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>138</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I42" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>139</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I43" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I44" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I45" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I46" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>143</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I47" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I48" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>145</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I49" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I50" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I51" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>148</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I52" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I53" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B54" s="11">
+        <f>SUM(B2:B53)</f>
+        <v>2349761000</v>
+      </c>
+      <c r="C54" s="11">
+        <f t="shared" ref="C54:I54" si="7">SUM(C2:C53)</f>
+        <v>2349761000</v>
+      </c>
+      <c r="D54" s="11">
+        <f t="shared" si="7"/>
+        <v>1085685500</v>
+      </c>
+      <c r="E54" s="11">
+        <f t="shared" si="7"/>
+        <v>443295900</v>
+      </c>
+      <c r="F54" s="11">
+        <f t="shared" si="7"/>
+        <v>80000880</v>
+      </c>
+      <c r="G54" s="11">
+        <f t="shared" si="7"/>
+        <v>523296780</v>
+      </c>
+      <c r="H54" s="11">
+        <f t="shared" si="7"/>
+        <v>562388720</v>
+      </c>
+      <c r="I54" s="11">
+        <f t="shared" si="7"/>
+        <v>1264075500</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="1jAoxgEfH1v+py+BabjE1SWtZrOmBQzll5J+0nEkCC4zpdaAqkqUQlFy6oRCGkgRojK/rMDnTPHDGbW/CMwxXA==" saltValue="rHdoy6qRDxYzetfIY6x9cQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\RKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD2D7D5-BE50-43FE-A649-0B9F15EC4FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA9959E-ACCC-44C4-8B08-EB081C68924F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget 3 Juni 2024" sheetId="1" r:id="rId1"/>
-    <sheet name="II PD" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="126">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -298,7 +297,91 @@
     <t>31022000  Sintelis</t>
   </si>
   <si>
+    <t>4112222200  Bbn Penystn Srana Perkeretaapian Fasilitas Dipo-By</t>
+  </si>
+  <si>
+    <t>4221221100  Perawatan Rel BMN</t>
+  </si>
+  <si>
+    <t>4221222200  Perawatan Wesel BMN</t>
+  </si>
+  <si>
+    <t>4221223300  Bbn Jasa Penambahan Balas BMN</t>
+  </si>
+  <si>
+    <t>4221224400  Pemasangan Bantalan BMN</t>
+  </si>
+  <si>
+    <t>4221225500  Perawatan Balas BMN</t>
+  </si>
+  <si>
+    <t>4221226000  Pemecokan BMN</t>
+  </si>
+  <si>
+    <t>4221226006  Perlintasan BMN</t>
+  </si>
+  <si>
+    <t>4221226008  Geometri BMN</t>
+  </si>
+  <si>
+    <t>4221226010  Perbaikan Periodik BMN</t>
+  </si>
+  <si>
+    <t>4221321010  Perawatan Baja Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221322010  Perawatan Cat Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221323010  Perawatan Batu Jembatan Kelas 1 BMN</t>
+  </si>
+  <si>
+    <t>4221325010  Perawatan Cat Jembatan Kelas 2 BMN</t>
+  </si>
+  <si>
+    <t>4221325013  Perawatan Batu Jembatan Kelas 3 BMN</t>
+  </si>
+  <si>
+    <t>4221325014  Perawatan Beton Jembatan Kelas 3 BMN</t>
+  </si>
+  <si>
     <t>4221600000  Peralatan Khusus Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4222222200  Perawatan Wesel KAI</t>
+  </si>
+  <si>
+    <t>4231120000  PerjlDinas BebanUmum PerawatanPrasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231130000  LAT Beban Umum Perawatan Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231140010  ATK Beban Umum Perawatan Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231150010  Krt Beban Umum Perawatan Prasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231151710  Kerumahtanggaan UMDT Beban Umum Perawatan Pras BMN</t>
+  </si>
+  <si>
+    <t>4231160010  Inventaris BebanUmum PerawatanPrasarana Pemerintah</t>
+  </si>
+  <si>
+    <t>4231180010  Pengiriman Prasarana BMN</t>
+  </si>
+  <si>
+    <t>4232152310  Tenaga PJL Alih Daya</t>
+  </si>
+  <si>
+    <t>4271100010  Gaji &amp;Tunjangan Pegawai Operasi Prasarana</t>
+  </si>
+  <si>
+    <t>4271500000  Pakaian Dinas Pegawai Operasi Prasarana</t>
+  </si>
+  <si>
+    <t>32020100  Prasarana</t>
   </si>
   <si>
     <t>4222421110  Transmisi Komunikasi KAI</t>
@@ -330,177 +413,11 @@
   <si>
     <t>35022000  Sintelis Divre IV Tanjungkarang</t>
   </si>
-  <si>
-    <t>1182000000 Persediaan Prasarana Perkeretaapian dan Umum</t>
-  </si>
-  <si>
-    <t>4112222200 Bbn Penystn Srana Perkeretaapian Fasilitas Dipo-By</t>
-  </si>
-  <si>
-    <t>4221221100 Perawatan Rel BMN</t>
-  </si>
-  <si>
-    <t>4221222200 Perawatan Wesel BMN</t>
-  </si>
-  <si>
-    <t>4221223300 Bbn Jasa Penambahan Balas BMN</t>
-  </si>
-  <si>
-    <t>4221224400 Pemasangan Bantalan BMN</t>
-  </si>
-  <si>
-    <t>4221225500 Perawatan Balas BMN</t>
-  </si>
-  <si>
-    <t>4221226000 Pemecokan BMN</t>
-  </si>
-  <si>
-    <t>4221226006 Perlintasan BMN</t>
-  </si>
-  <si>
-    <t>4221226008 Geometri BMN</t>
-  </si>
-  <si>
-    <t>4221226010 Perbaikan Periodik BMN</t>
-  </si>
-  <si>
-    <t>4221321010 Perawatan Baja Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221322010 Perawatan Cat Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221323010 Perawatan Batu Jembatan Kelas 1 BMN</t>
-  </si>
-  <si>
-    <t>4221325010 Perawatan Cat Jembatan Kelas 2 BMN</t>
-  </si>
-  <si>
-    <t>4221325013 Perawatan Batu Jembatan Kelas 3 BMN</t>
-  </si>
-  <si>
-    <t>4221325014 Perawatan Beton Jembatan Kelas 3 BMN</t>
-  </si>
-  <si>
-    <t>4221424010 Peralatan Luar Sinyal Mekanik BMN</t>
-  </si>
-  <si>
-    <t>4221425010 Pengamanan Perlintasan Sebidang BMN</t>
-  </si>
-  <si>
-    <t>4221427010 Transmisi Komunikasi BMN</t>
-  </si>
-  <si>
-    <t>4221428010 Peralatan Pendukung Sintel BMN</t>
-  </si>
-  <si>
-    <t>4221428014 Catu Daya Sintel BMN</t>
-  </si>
-  <si>
-    <t>4221600000 Peralatan Khusus Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4222222200 Perawatan Wesel KAI</t>
-  </si>
-  <si>
-    <t>4222600000 Peralatan Khusus Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4222800000 Beban BBM Mekanik Prasarana</t>
-  </si>
-  <si>
-    <t>4231110000 Rapat&amp;Akomodasi BbnUmum Prwtn Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231120000 PerjlDinas BebanUmum PerawatanPrasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231130000 LAT Beban Umum Perawatan Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231150010 Krt Beban Umum Perawatan Prasarana Pemerintah</t>
-  </si>
-  <si>
-    <t>4231151710 Kerumahtanggaan UMDT Beban Umum Perawatan Pras BMN</t>
-  </si>
-  <si>
-    <t>4232152310 Tenaga PJL Alih Daya</t>
-  </si>
-  <si>
-    <t>4233100000 Rapat&amp;Akomodasi Beban Umum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4233150010 Kerumahtanggaan Beban Umum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4233151710 Kerumahtanggaan UMDT Beban Umum Perawatan Pras KAI</t>
-  </si>
-  <si>
-    <t>4233160010 Inventaris Beban Umum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4233200000 Perjalanan Dinas BebanUmum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4233300000 LAT Beban Umum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4233400000 ATK Beban Umum Perawatan Prasarana KAI</t>
-  </si>
-  <si>
-    <t>4241000000 Beban Penyusutan AT Prasarana Perkeretaapian</t>
-  </si>
-  <si>
-    <t>4242000000 Beban Penyusutan AT Bangunan Kantor</t>
-  </si>
-  <si>
-    <t>4271100010 Gaji &amp;Tunjangan Pegawai Operasi Prasarana</t>
-  </si>
-  <si>
-    <t>4271400000 Lembur dan Perangsang Pegawai Operasi Prasarana</t>
-  </si>
-  <si>
-    <t>4271500000 Pakaian Dinas Pegawai Operasi Prasarana</t>
-  </si>
-  <si>
-    <t>4272100010 Gaji &amp;Tunjangan PegawaiPerawatan Prasarana Unit JJ</t>
-  </si>
-  <si>
-    <t>4272200010 Iuran Pensiun Pegawai Perawatan Prasarana Unit JJ/</t>
-  </si>
-  <si>
-    <t>4272400000 Lembur dan Perangsang Peg PrwtnPrsrna unit JJ/Sntl</t>
-  </si>
-  <si>
-    <t>4272500000 PakaianDinas PegPrwtn PrasaranaUnit JJ/sntl/BY Pra</t>
-  </si>
-  <si>
-    <t>4273100010 Gaji &amp;Tunjangan Pegawai Renwas JJ/Sintel LAA</t>
-  </si>
-  <si>
-    <t>4273400000 Lembur dan Perangsang Pegawai Renwas JJ/Sintel LAA</t>
-  </si>
-  <si>
-    <t>4273500000 Pakaian Dinas Pegawai Renwas JJ/Sintel LAA</t>
-  </si>
-  <si>
-    <t>5400000000 Penyusutan AT Lainnya (Fasilitas Umum)</t>
-  </si>
-  <si>
-    <t>32020100 Prasarana</t>
-  </si>
-  <si>
-    <t>RKAO Disetujui</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -637,7 +554,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -823,12 +740,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -946,7 +857,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -989,33 +900,14 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1043,7 +935,6 @@
     <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Comma" xfId="42" builtinId="3"/>
     <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
@@ -1370,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H547"/>
+  <dimension ref="A1:H550"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="60.796875" bestFit="1" customWidth="1"/>
@@ -1723,10 +1614,10 @@
         <v>20</v>
       </c>
       <c r="B14" s="2">
-        <v>1175883000</v>
+        <v>4308413000</v>
       </c>
       <c r="C14" s="2">
-        <v>1175883000</v>
+        <v>4308413000</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
@@ -1738,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2">
-        <v>1175883000</v>
+        <v>4308413000</v>
       </c>
       <c r="H14" s="2">
         <v>0</v>
@@ -1801,10 +1692,10 @@
         <v>23</v>
       </c>
       <c r="B17" s="2">
-        <v>496414000</v>
+        <v>492289000</v>
       </c>
       <c r="C17" s="2">
-        <v>371414000</v>
+        <v>367289000</v>
       </c>
       <c r="D17" s="2">
         <v>20986164</v>
@@ -1816,7 +1707,7 @@
         <v>20986164</v>
       </c>
       <c r="G17" s="2">
-        <v>350427836</v>
+        <v>346302836</v>
       </c>
       <c r="H17" s="2">
         <v>125000000</v>
@@ -2347,10 +2238,10 @@
         <v>44</v>
       </c>
       <c r="B38" s="2">
-        <v>361725758454</v>
+        <v>364854163454</v>
       </c>
       <c r="C38" s="2">
-        <v>359308258454</v>
+        <v>362436663454</v>
       </c>
       <c r="D38" s="2">
         <v>170142785390</v>
@@ -2362,7 +2253,7 @@
         <v>224335405163</v>
       </c>
       <c r="G38" s="2">
-        <v>134972853291</v>
+        <v>138101258291</v>
       </c>
       <c r="H38" s="2">
         <v>2417500000</v>
@@ -2379,16 +2270,16 @@
         <v>25194775704</v>
       </c>
       <c r="D39" s="2">
-        <v>16128909964</v>
+        <v>17081409964</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>16128909964</v>
+        <v>17081409964</v>
       </c>
       <c r="G39" s="2">
-        <v>9065865740</v>
+        <v>8113365740</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -2951,10 +2842,10 @@
         <v>417000000</v>
       </c>
       <c r="D61" s="2">
-        <v>30265575</v>
+        <v>22698575</v>
       </c>
       <c r="E61" s="2">
-        <v>27969350</v>
+        <v>35536350</v>
       </c>
       <c r="F61" s="2">
         <v>58234925</v>
@@ -3393,16 +3284,16 @@
         <v>110897810191</v>
       </c>
       <c r="D78" s="2">
-        <v>19916407003</v>
+        <v>20861340003</v>
       </c>
       <c r="E78" s="2">
-        <v>9043557927</v>
+        <v>9051124927</v>
       </c>
       <c r="F78" s="2">
-        <v>28959964930</v>
+        <v>29912464930</v>
       </c>
       <c r="G78" s="2">
-        <v>81937845261</v>
+        <v>80985345261</v>
       </c>
       <c r="H78" s="2">
         <v>671501500</v>
@@ -3835,16 +3726,16 @@
         <v>419475000</v>
       </c>
       <c r="D95" s="2">
-        <v>30610000</v>
+        <v>20563000</v>
       </c>
       <c r="E95" s="2">
-        <v>2008000</v>
+        <v>8717850</v>
       </c>
       <c r="F95" s="2">
-        <v>32618000</v>
+        <v>29280850</v>
       </c>
       <c r="G95" s="2">
-        <v>386857000</v>
+        <v>390194150</v>
       </c>
       <c r="H95" s="2">
         <v>139825000</v>
@@ -3861,10 +3752,10 @@
         <v>255960000</v>
       </c>
       <c r="D96" s="2">
-        <v>19700000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="2">
-        <v>27200000</v>
+        <v>46900000</v>
       </c>
       <c r="F96" s="2">
         <v>46900000</v>
@@ -4303,16 +4194,16 @@
         <v>81718644736</v>
       </c>
       <c r="D113" s="2">
-        <v>18898106425</v>
+        <v>18868359425</v>
       </c>
       <c r="E113" s="2">
-        <v>15482750457</v>
+        <v>15509160307</v>
       </c>
       <c r="F113" s="2">
-        <v>34380856882</v>
+        <v>34377519732</v>
       </c>
       <c r="G113" s="2">
-        <v>47337787854</v>
+        <v>47341125004</v>
       </c>
       <c r="H113" s="2">
         <v>475697500</v>
@@ -4329,10 +4220,10 @@
         <v>8995670000</v>
       </c>
       <c r="D114" s="2">
-        <v>7795034312</v>
+        <v>7317523312</v>
       </c>
       <c r="E114" s="2">
-        <v>0</v>
+        <v>477511000</v>
       </c>
       <c r="F114" s="2">
         <v>7795034312</v>
@@ -4511,10 +4402,10 @@
         <v>1665000000</v>
       </c>
       <c r="D121" s="2">
-        <v>261038644</v>
+        <v>259288644</v>
       </c>
       <c r="E121" s="2">
-        <v>142557241</v>
+        <v>144307241</v>
       </c>
       <c r="F121" s="2">
         <v>403595885</v>
@@ -4719,10 +4610,10 @@
         <v>118875000</v>
       </c>
       <c r="D129" s="2">
-        <v>11725000</v>
+        <v>8255000</v>
       </c>
       <c r="E129" s="2">
-        <v>4050000</v>
+        <v>7520000</v>
       </c>
       <c r="F129" s="2">
         <v>15775000</v>
@@ -4771,10 +4662,10 @@
         <v>75000000</v>
       </c>
       <c r="D131" s="2">
-        <v>9515280</v>
+        <v>6000000</v>
       </c>
       <c r="E131" s="2">
-        <v>18812609</v>
+        <v>22327889</v>
       </c>
       <c r="F131" s="2">
         <v>28327889</v>
@@ -5187,10 +5078,10 @@
         <v>50726099717</v>
       </c>
       <c r="D147" s="2">
-        <v>16622102653</v>
+        <v>16135856373</v>
       </c>
       <c r="E147" s="2">
-        <v>4359918620</v>
+        <v>4846164900</v>
       </c>
       <c r="F147" s="2">
         <v>20982021273</v>
@@ -5369,10 +5260,10 @@
         <v>1702406000</v>
       </c>
       <c r="D154" s="2">
-        <v>297962777</v>
+        <v>288060277</v>
       </c>
       <c r="E154" s="2">
-        <v>96677559</v>
+        <v>106580059</v>
       </c>
       <c r="F154" s="2">
         <v>394640336</v>
@@ -5814,13 +5705,13 @@
         <v>0</v>
       </c>
       <c r="E171" s="2">
-        <v>37528000</v>
+        <v>38784250</v>
       </c>
       <c r="F171" s="2">
-        <v>37528000</v>
+        <v>38784250</v>
       </c>
       <c r="G171" s="2">
-        <v>124773500</v>
+        <v>123517250</v>
       </c>
       <c r="H171" s="2">
         <v>54100500</v>
@@ -5866,13 +5757,13 @@
         <v>0</v>
       </c>
       <c r="E173" s="2">
-        <v>1069019840</v>
+        <v>1069032027</v>
       </c>
       <c r="F173" s="2">
-        <v>1069019840</v>
+        <v>1069032027</v>
       </c>
       <c r="G173" s="2">
-        <v>6435703538</v>
+        <v>6435691351</v>
       </c>
       <c r="H173" s="2">
         <v>0</v>
@@ -6071,16 +5962,16 @@
         <v>44127068487</v>
       </c>
       <c r="D181" s="2">
-        <v>7212124326</v>
+        <v>7202221826</v>
       </c>
       <c r="E181" s="2">
-        <v>3268481108</v>
+        <v>3279652045</v>
       </c>
       <c r="F181" s="2">
-        <v>10480605434</v>
+        <v>10481873871</v>
       </c>
       <c r="G181" s="2">
-        <v>33646463053</v>
+        <v>33645194616</v>
       </c>
       <c r="H181" s="2">
         <v>449400500</v>
@@ -7241,16 +7132,16 @@
         <v>1380000000</v>
       </c>
       <c r="D226" s="2">
-        <v>321145216</v>
+        <v>341396016</v>
       </c>
       <c r="E226" s="2">
         <v>201042000</v>
       </c>
       <c r="F226" s="2">
-        <v>522187216</v>
+        <v>542438016</v>
       </c>
       <c r="G226" s="2">
-        <v>857812784</v>
+        <v>837561984</v>
       </c>
       <c r="H226" s="2">
         <v>0</v>
@@ -7527,16 +7418,16 @@
         <v>354238500</v>
       </c>
       <c r="D237" s="2">
-        <v>29494000</v>
+        <v>14842000</v>
       </c>
       <c r="E237" s="2">
-        <v>52117900</v>
+        <v>65317900</v>
       </c>
       <c r="F237" s="2">
-        <v>81611900</v>
+        <v>80159900</v>
       </c>
       <c r="G237" s="2">
-        <v>272626600</v>
+        <v>274078600</v>
       </c>
       <c r="H237" s="2">
         <v>118079500</v>
@@ -7579,16 +7470,16 @@
         <v>732016185</v>
       </c>
       <c r="D239" s="2">
-        <v>705859685</v>
+        <v>654645750</v>
       </c>
       <c r="E239" s="2">
-        <v>26156500</v>
+        <v>72295180</v>
       </c>
       <c r="F239" s="2">
-        <v>732016185</v>
+        <v>726940930</v>
       </c>
       <c r="G239" s="2">
-        <v>0</v>
+        <v>5075255</v>
       </c>
       <c r="H239" s="2">
         <v>42983815</v>
@@ -7865,16 +7756,16 @@
         <v>48914772555</v>
       </c>
       <c r="D250" s="2">
-        <v>14349605277</v>
+        <v>14303990142</v>
       </c>
       <c r="E250" s="2">
-        <v>4424500712</v>
+        <v>4483839392</v>
       </c>
       <c r="F250" s="2">
-        <v>18774105989</v>
+        <v>18787829534</v>
       </c>
       <c r="G250" s="2">
-        <v>30140666566</v>
+        <v>30126943021</v>
       </c>
       <c r="H250" s="2">
         <v>525212165</v>
@@ -7885,10 +7776,10 @@
         <v>8</v>
       </c>
       <c r="B251" s="2">
-        <v>2847534500</v>
+        <v>5695069150</v>
       </c>
       <c r="C251" s="2">
-        <v>2847534500</v>
+        <v>5695069150</v>
       </c>
       <c r="D251" s="2">
         <v>718522000</v>
@@ -7900,7 +7791,7 @@
         <v>718522000</v>
       </c>
       <c r="G251" s="2">
-        <v>2129012500</v>
+        <v>4976547150</v>
       </c>
       <c r="H251" s="2">
         <v>0</v>
@@ -7911,10 +7802,10 @@
         <v>11</v>
       </c>
       <c r="B252" s="2">
-        <v>770000000</v>
+        <v>1540000000</v>
       </c>
       <c r="C252" s="2">
-        <v>770000000</v>
+        <v>1540000000</v>
       </c>
       <c r="D252" s="2">
         <v>731199517</v>
@@ -7926,7 +7817,7 @@
         <v>731199517</v>
       </c>
       <c r="G252" s="2">
-        <v>38800483</v>
+        <v>808800483</v>
       </c>
       <c r="H252" s="2">
         <v>0</v>
@@ -7937,10 +7828,10 @@
         <v>12</v>
       </c>
       <c r="B253" s="2">
-        <v>179171000</v>
+        <v>358342000</v>
       </c>
       <c r="C253" s="2">
-        <v>179171000</v>
+        <v>358342000</v>
       </c>
       <c r="D253" s="2">
         <v>0</v>
@@ -7952,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="G253" s="2">
-        <v>179171000</v>
+        <v>358342000</v>
       </c>
       <c r="H253" s="2">
         <v>0</v>
@@ -7963,10 +7854,10 @@
         <v>48</v>
       </c>
       <c r="B254" s="2">
-        <v>75000000</v>
+        <v>150000000</v>
       </c>
       <c r="C254" s="2">
-        <v>75000000</v>
+        <v>150000000</v>
       </c>
       <c r="D254" s="2">
         <v>0</v>
@@ -7978,7 +7869,7 @@
         <v>0</v>
       </c>
       <c r="G254" s="2">
-        <v>75000000</v>
+        <v>150000000</v>
       </c>
       <c r="H254" s="2">
         <v>0</v>
@@ -7989,10 +7880,10 @@
         <v>13</v>
       </c>
       <c r="B255" s="2">
-        <v>437500000</v>
+        <v>875000000</v>
       </c>
       <c r="C255" s="2">
-        <v>437500000</v>
+        <v>875000000</v>
       </c>
       <c r="D255" s="2">
         <v>0</v>
@@ -8004,7 +7895,7 @@
         <v>6817000</v>
       </c>
       <c r="G255" s="2">
-        <v>430683000</v>
+        <v>868183000</v>
       </c>
       <c r="H255" s="2">
         <v>0</v>
@@ -8015,10 +7906,10 @@
         <v>14</v>
       </c>
       <c r="B256" s="2">
-        <v>1634991000</v>
+        <v>3269982000</v>
       </c>
       <c r="C256" s="2">
-        <v>1634991000</v>
+        <v>3269982000</v>
       </c>
       <c r="D256" s="2">
         <v>197080000</v>
@@ -8030,7 +7921,7 @@
         <v>296910000</v>
       </c>
       <c r="G256" s="2">
-        <v>1338081000</v>
+        <v>2973072000</v>
       </c>
       <c r="H256" s="2">
         <v>0</v>
@@ -8041,10 +7932,10 @@
         <v>15</v>
       </c>
       <c r="B257" s="2">
-        <v>245566500</v>
+        <v>491133000</v>
       </c>
       <c r="C257" s="2">
-        <v>245566500</v>
+        <v>491133000</v>
       </c>
       <c r="D257" s="2">
         <v>0</v>
@@ -8056,7 +7947,7 @@
         <v>98325000</v>
       </c>
       <c r="G257" s="2">
-        <v>147241500</v>
+        <v>392808000</v>
       </c>
       <c r="H257" s="2">
         <v>0</v>
@@ -8067,10 +7958,10 @@
         <v>16</v>
       </c>
       <c r="B258" s="2">
-        <v>850000000</v>
+        <v>1700000000</v>
       </c>
       <c r="C258" s="2">
-        <v>850000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D258" s="2">
         <v>309489160</v>
@@ -8082,7 +7973,7 @@
         <v>384289160</v>
       </c>
       <c r="G258" s="2">
-        <v>465710840</v>
+        <v>1315710840</v>
       </c>
       <c r="H258" s="2">
         <v>0</v>
@@ -8093,10 +7984,10 @@
         <v>49</v>
       </c>
       <c r="B259" s="2">
-        <v>200000000</v>
+        <v>400000000</v>
       </c>
       <c r="C259" s="2">
-        <v>200000000</v>
+        <v>400000000</v>
       </c>
       <c r="D259" s="2">
         <v>0</v>
@@ -8108,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G259" s="2">
-        <v>200000000</v>
+        <v>400000000</v>
       </c>
       <c r="H259" s="2">
         <v>0</v>
@@ -8119,10 +8010,10 @@
         <v>50</v>
       </c>
       <c r="B260" s="2">
-        <v>620000000</v>
+        <v>1240000000</v>
       </c>
       <c r="C260" s="2">
-        <v>620000000</v>
+        <v>1240000000</v>
       </c>
       <c r="D260" s="2">
         <v>49633664</v>
@@ -8134,7 +8025,7 @@
         <v>49633664</v>
       </c>
       <c r="G260" s="2">
-        <v>570366336</v>
+        <v>1190366336</v>
       </c>
       <c r="H260" s="2">
         <v>0</v>
@@ -8145,10 +8036,10 @@
         <v>51</v>
       </c>
       <c r="B261" s="2">
-        <v>75000000</v>
+        <v>150000000</v>
       </c>
       <c r="C261" s="2">
-        <v>75000000</v>
+        <v>150000000</v>
       </c>
       <c r="D261" s="2">
         <v>0</v>
@@ -8160,7 +8051,7 @@
         <v>0</v>
       </c>
       <c r="G261" s="2">
-        <v>75000000</v>
+        <v>150000000</v>
       </c>
       <c r="H261" s="2">
         <v>0</v>
@@ -8171,10 +8062,10 @@
         <v>52</v>
       </c>
       <c r="B262" s="2">
-        <v>1334151500</v>
+        <v>2668302662</v>
       </c>
       <c r="C262" s="2">
-        <v>1334151500</v>
+        <v>2668302662</v>
       </c>
       <c r="D262" s="2">
         <v>1190000000</v>
@@ -8186,7 +8077,7 @@
         <v>1190000000</v>
       </c>
       <c r="G262" s="2">
-        <v>144151500</v>
+        <v>1478302662</v>
       </c>
       <c r="H262" s="2">
         <v>0</v>
@@ -8197,10 +8088,10 @@
         <v>18</v>
       </c>
       <c r="B263" s="2">
-        <v>273768000</v>
+        <v>547536000</v>
       </c>
       <c r="C263" s="2">
-        <v>273768000</v>
+        <v>547536000</v>
       </c>
       <c r="D263" s="2">
         <v>0</v>
@@ -8212,7 +8103,7 @@
         <v>0</v>
       </c>
       <c r="G263" s="2">
-        <v>273768000</v>
+        <v>547536000</v>
       </c>
       <c r="H263" s="2">
         <v>0</v>
@@ -8223,10 +8114,10 @@
         <v>19</v>
       </c>
       <c r="B264" s="2">
-        <v>2633662000</v>
+        <v>5267324000</v>
       </c>
       <c r="C264" s="2">
-        <v>2633662000</v>
+        <v>5267324000</v>
       </c>
       <c r="D264" s="2">
         <v>2627635958</v>
@@ -8238,7 +8129,7 @@
         <v>2627635958</v>
       </c>
       <c r="G264" s="2">
-        <v>6026042</v>
+        <v>2639688042</v>
       </c>
       <c r="H264" s="2">
         <v>0</v>
@@ -8249,10 +8140,10 @@
         <v>64</v>
       </c>
       <c r="B265" s="2">
-        <v>575500000</v>
+        <v>1151000000</v>
       </c>
       <c r="C265" s="2">
-        <v>575500000</v>
+        <v>1151000000</v>
       </c>
       <c r="D265" s="2">
         <v>316539281</v>
@@ -8264,7 +8155,7 @@
         <v>316539281</v>
       </c>
       <c r="G265" s="2">
-        <v>258960719</v>
+        <v>834460719</v>
       </c>
       <c r="H265" s="2">
         <v>0</v>
@@ -8275,10 +8166,10 @@
         <v>66</v>
       </c>
       <c r="B266" s="2">
-        <v>387500000</v>
+        <v>775000000</v>
       </c>
       <c r="C266" s="2">
-        <v>387500000</v>
+        <v>775000000</v>
       </c>
       <c r="D266" s="2">
         <v>49450000</v>
@@ -8290,7 +8181,7 @@
         <v>49450000</v>
       </c>
       <c r="G266" s="2">
-        <v>338050000</v>
+        <v>725550000</v>
       </c>
       <c r="H266" s="2">
         <v>0</v>
@@ -8301,10 +8192,10 @@
         <v>67</v>
       </c>
       <c r="B267" s="2">
-        <v>1130000000</v>
+        <v>2260000000</v>
       </c>
       <c r="C267" s="2">
-        <v>1130000000</v>
+        <v>2260000000</v>
       </c>
       <c r="D267" s="2">
         <v>447600900</v>
@@ -8316,7 +8207,7 @@
         <v>447600900</v>
       </c>
       <c r="G267" s="2">
-        <v>682399100</v>
+        <v>1812399100</v>
       </c>
       <c r="H267" s="2">
         <v>0</v>
@@ -8327,10 +8218,10 @@
         <v>77</v>
       </c>
       <c r="B268" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="C268" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="D268" s="2">
         <v>0</v>
@@ -8342,7 +8233,7 @@
         <v>0</v>
       </c>
       <c r="G268" s="2">
-        <v>125000000</v>
+        <v>250000000</v>
       </c>
       <c r="H268" s="2">
         <v>0</v>
@@ -8353,10 +8244,10 @@
         <v>56</v>
       </c>
       <c r="B269" s="2">
-        <v>375000000</v>
+        <v>750000000</v>
       </c>
       <c r="C269" s="2">
-        <v>375000000</v>
+        <v>750000000</v>
       </c>
       <c r="D269" s="2">
         <v>8959000</v>
@@ -8368,7 +8259,7 @@
         <v>45459000</v>
       </c>
       <c r="G269" s="2">
-        <v>329541000</v>
+        <v>704541000</v>
       </c>
       <c r="H269" s="2">
         <v>0</v>
@@ -8379,10 +8270,10 @@
         <v>72</v>
       </c>
       <c r="B270" s="2">
-        <v>621000000</v>
+        <v>1242000000</v>
       </c>
       <c r="C270" s="2">
-        <v>621000000</v>
+        <v>1242000000</v>
       </c>
       <c r="D270" s="2">
         <v>0</v>
@@ -8394,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="G270" s="2">
-        <v>621000000</v>
+        <v>1242000000</v>
       </c>
       <c r="H270" s="2">
         <v>0</v>
@@ -8405,10 +8296,10 @@
         <v>22</v>
       </c>
       <c r="B271" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="C271" s="2">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="D271" s="2">
         <v>0</v>
@@ -8420,10 +8311,10 @@
         <v>0</v>
       </c>
       <c r="G271" s="2">
-        <v>100000000</v>
+        <v>150000000</v>
       </c>
       <c r="H271" s="2">
-        <v>0</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.45">
@@ -8431,10 +8322,10 @@
         <v>57</v>
       </c>
       <c r="B272" s="2">
-        <v>173189000</v>
+        <v>346377600</v>
       </c>
       <c r="C272" s="2">
-        <v>173189000</v>
+        <v>346377600</v>
       </c>
       <c r="D272" s="2">
         <v>1160000</v>
@@ -8446,7 +8337,7 @@
         <v>63260000</v>
       </c>
       <c r="G272" s="2">
-        <v>109929000</v>
+        <v>283117600</v>
       </c>
       <c r="H272" s="2">
         <v>0</v>
@@ -8457,10 +8348,10 @@
         <v>58</v>
       </c>
       <c r="B273" s="2">
-        <v>546340018</v>
+        <v>1952349292</v>
       </c>
       <c r="C273" s="2">
-        <v>546340018</v>
+        <v>1952349292</v>
       </c>
       <c r="D273" s="2">
         <v>0</v>
@@ -8472,7 +8363,7 @@
         <v>320371955</v>
       </c>
       <c r="G273" s="2">
-        <v>225968063</v>
+        <v>1631977337</v>
       </c>
       <c r="H273" s="2">
         <v>0</v>
@@ -8483,25 +8374,25 @@
         <v>25</v>
       </c>
       <c r="B274" s="2">
-        <v>24334750</v>
+        <v>82737800</v>
       </c>
       <c r="C274" s="2">
-        <v>24334750</v>
+        <v>62053350</v>
       </c>
       <c r="D274" s="2">
-        <v>6000000</v>
+        <v>13489250</v>
       </c>
       <c r="E274" s="2">
         <v>9188377</v>
       </c>
       <c r="F274" s="2">
-        <v>15188377</v>
+        <v>22677627</v>
       </c>
       <c r="G274" s="2">
-        <v>9146373</v>
+        <v>39375723</v>
       </c>
       <c r="H274" s="2">
-        <v>0</v>
+        <v>20684450</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.45">
@@ -8509,10 +8400,10 @@
         <v>26</v>
       </c>
       <c r="B275" s="2">
-        <v>97531500</v>
+        <v>627208851</v>
       </c>
       <c r="C275" s="2">
-        <v>97531500</v>
+        <v>470406638</v>
       </c>
       <c r="D275" s="2">
         <v>12164000</v>
@@ -8524,10 +8415,10 @@
         <v>91001733</v>
       </c>
       <c r="G275" s="2">
-        <v>6529767</v>
+        <v>379404905</v>
       </c>
       <c r="H275" s="2">
-        <v>0</v>
+        <v>156802213</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.45">
@@ -8535,10 +8426,10 @@
         <v>27</v>
       </c>
       <c r="B276" s="2">
-        <v>37950000</v>
+        <v>151800000</v>
       </c>
       <c r="C276" s="2">
-        <v>37950000</v>
+        <v>151800000</v>
       </c>
       <c r="D276" s="2">
         <v>0</v>
@@ -8550,7 +8441,7 @@
         <v>20461500</v>
       </c>
       <c r="G276" s="2">
-        <v>17488500</v>
+        <v>131338500</v>
       </c>
       <c r="H276" s="2">
         <v>0</v>
@@ -8561,10 +8452,10 @@
         <v>28</v>
       </c>
       <c r="B277" s="2">
-        <v>302334250</v>
+        <v>942936000</v>
       </c>
       <c r="C277" s="2">
-        <v>302334250</v>
+        <v>707202000</v>
       </c>
       <c r="D277" s="2">
         <v>59146500</v>
@@ -8576,10 +8467,10 @@
         <v>59146500</v>
       </c>
       <c r="G277" s="2">
-        <v>243187750</v>
+        <v>648055500</v>
       </c>
       <c r="H277" s="2">
-        <v>0</v>
+        <v>235734000</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.45">
@@ -8587,25 +8478,25 @@
         <v>30</v>
       </c>
       <c r="B278" s="2">
-        <v>79793750</v>
+        <v>271299000</v>
       </c>
       <c r="C278" s="2">
-        <v>79793750</v>
+        <v>203474250</v>
       </c>
       <c r="D278" s="2">
         <v>0</v>
       </c>
       <c r="E278" s="2">
-        <v>57649750</v>
+        <v>59174750</v>
       </c>
       <c r="F278" s="2">
-        <v>57649750</v>
+        <v>59174750</v>
       </c>
       <c r="G278" s="2">
-        <v>22144000</v>
+        <v>144299500</v>
       </c>
       <c r="H278" s="2">
-        <v>0</v>
+        <v>67824750</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.45">
@@ -8613,10 +8504,10 @@
         <v>79</v>
       </c>
       <c r="B279" s="2">
-        <v>13812750</v>
+        <v>181144082</v>
       </c>
       <c r="C279" s="2">
-        <v>13812750</v>
+        <v>181144082</v>
       </c>
       <c r="D279" s="2">
         <v>0</v>
@@ -8628,7 +8519,7 @@
         <v>13464055</v>
       </c>
       <c r="G279" s="2">
-        <v>348695</v>
+        <v>167680027</v>
       </c>
       <c r="H279" s="2">
         <v>0</v>
@@ -8639,10 +8530,10 @@
         <v>31</v>
       </c>
       <c r="B280" s="2">
-        <v>13675500</v>
+        <v>46497000</v>
       </c>
       <c r="C280" s="2">
-        <v>13675500</v>
+        <v>46497000</v>
       </c>
       <c r="D280" s="2">
         <v>0</v>
@@ -8654,7 +8545,7 @@
         <v>13582000</v>
       </c>
       <c r="G280" s="2">
-        <v>93500</v>
+        <v>32915000</v>
       </c>
       <c r="H280" s="2">
         <v>0</v>
@@ -8700,13 +8591,13 @@
         <v>0</v>
       </c>
       <c r="E282" s="2">
-        <v>1810519600</v>
+        <v>1810542100</v>
       </c>
       <c r="F282" s="2">
-        <v>1810519600</v>
+        <v>1810542100</v>
       </c>
       <c r="G282" s="2">
-        <v>10812099327</v>
+        <v>10812076827</v>
       </c>
       <c r="H282" s="2">
         <v>0</v>
@@ -8899,25 +8790,25 @@
         <v>82</v>
       </c>
       <c r="B290" s="2">
-        <v>45434097707</v>
+        <v>64237830126</v>
       </c>
       <c r="C290" s="2">
-        <v>45434097707</v>
+        <v>63706784713</v>
       </c>
       <c r="D290" s="2">
-        <v>6724579980</v>
+        <v>6732069230</v>
       </c>
       <c r="E290" s="2">
-        <v>5347646446</v>
+        <v>5349193946</v>
       </c>
       <c r="F290" s="2">
-        <v>12072226426</v>
+        <v>12081263176</v>
       </c>
       <c r="G290" s="2">
-        <v>33361871281</v>
+        <v>51625521537</v>
       </c>
       <c r="H290" s="2">
-        <v>0</v>
+        <v>531045413</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.45">
@@ -8931,16 +8822,16 @@
         <v>3628073000</v>
       </c>
       <c r="D291" s="2">
-        <v>1708500760</v>
+        <v>3299963760</v>
       </c>
       <c r="E291" s="2">
         <v>0</v>
       </c>
       <c r="F291" s="2">
-        <v>1708500760</v>
+        <v>3299963760</v>
       </c>
       <c r="G291" s="2">
-        <v>1919572240</v>
+        <v>328109240</v>
       </c>
       <c r="H291" s="2">
         <v>0</v>
@@ -9087,16 +8978,16 @@
         <v>1222108000</v>
       </c>
       <c r="D297" s="2">
-        <v>58082710</v>
+        <v>884313681</v>
       </c>
       <c r="E297" s="2">
-        <v>49641980</v>
+        <v>93397015</v>
       </c>
       <c r="F297" s="2">
-        <v>107724690</v>
+        <v>977710696</v>
       </c>
       <c r="G297" s="2">
-        <v>1114383310</v>
+        <v>244397304</v>
       </c>
       <c r="H297" s="2">
         <v>0</v>
@@ -9399,16 +9290,16 @@
         <v>64614000</v>
       </c>
       <c r="D309" s="2">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E309" s="2">
-        <v>8264001</v>
+        <v>13214001</v>
       </c>
       <c r="F309" s="2">
-        <v>13264001</v>
+        <v>13214001</v>
       </c>
       <c r="G309" s="2">
-        <v>51349999</v>
+        <v>51399999</v>
       </c>
       <c r="H309" s="2">
         <v>21538000</v>
@@ -9763,16 +9654,16 @@
         <v>30454436960</v>
       </c>
       <c r="D323" s="2">
-        <v>4533800168</v>
+        <v>6946494139</v>
       </c>
       <c r="E323" s="2">
-        <v>3255135775</v>
+        <v>3303840810</v>
       </c>
       <c r="F323" s="2">
-        <v>7788935943</v>
+        <v>10250334949</v>
       </c>
       <c r="G323" s="2">
-        <v>22665501017</v>
+        <v>20204102011</v>
       </c>
       <c r="H323" s="2">
         <v>260139500</v>
@@ -10179,16 +10070,16 @@
         <v>2911760000</v>
       </c>
       <c r="D339" s="2">
-        <v>581770</v>
+        <v>1038540</v>
       </c>
       <c r="E339" s="2">
         <v>411555340</v>
       </c>
       <c r="F339" s="2">
-        <v>412137110</v>
+        <v>412593880</v>
       </c>
       <c r="G339" s="2">
-        <v>2499622890</v>
+        <v>2499166120</v>
       </c>
       <c r="H339" s="2">
         <v>0</v>
@@ -10595,16 +10486,16 @@
         <v>57427089299</v>
       </c>
       <c r="D355" s="2">
-        <v>19274961725</v>
+        <v>19275418495</v>
       </c>
       <c r="E355" s="2">
         <v>6048123791</v>
       </c>
       <c r="F355" s="2">
-        <v>25323085516</v>
+        <v>25323542286</v>
       </c>
       <c r="G355" s="2">
-        <v>32104003783</v>
+        <v>32103547013</v>
       </c>
       <c r="H355" s="2">
         <v>526334925</v>
@@ -10907,16 +10798,16 @@
         <v>82500000</v>
       </c>
       <c r="D367" s="2">
-        <v>0</v>
+        <v>11000000</v>
       </c>
       <c r="E367" s="2">
         <v>0</v>
       </c>
       <c r="F367" s="2">
-        <v>0</v>
+        <v>11000000</v>
       </c>
       <c r="G367" s="2">
-        <v>82500000</v>
+        <v>71500000</v>
       </c>
       <c r="H367" s="2">
         <v>27500000</v>
@@ -10959,16 +10850,16 @@
         <v>411080000</v>
       </c>
       <c r="D369" s="2">
-        <v>1639740</v>
+        <v>41598790</v>
       </c>
       <c r="E369" s="2">
-        <v>70896704</v>
+        <v>72045654</v>
       </c>
       <c r="F369" s="2">
-        <v>72536444</v>
+        <v>113644444</v>
       </c>
       <c r="G369" s="2">
-        <v>338543556</v>
+        <v>297435556</v>
       </c>
       <c r="H369" s="2">
         <v>0</v>
@@ -10985,16 +10876,16 @@
         <v>120000000</v>
       </c>
       <c r="D370" s="2">
-        <v>6960000</v>
+        <v>22960000</v>
       </c>
       <c r="E370" s="2">
         <v>13487000</v>
       </c>
       <c r="F370" s="2">
-        <v>20447000</v>
+        <v>36447000</v>
       </c>
       <c r="G370" s="2">
-        <v>99553000</v>
+        <v>83553000</v>
       </c>
       <c r="H370" s="2">
         <v>40000000</v>
@@ -11011,16 +10902,16 @@
         <v>300000000</v>
       </c>
       <c r="D371" s="2">
-        <v>27274000</v>
+        <v>60824000</v>
       </c>
       <c r="E371" s="2">
-        <v>78208462</v>
+        <v>84658462</v>
       </c>
       <c r="F371" s="2">
-        <v>105482462</v>
+        <v>145482462</v>
       </c>
       <c r="G371" s="2">
-        <v>194517538</v>
+        <v>154517538</v>
       </c>
       <c r="H371" s="2">
         <v>100000000</v>
@@ -11037,16 +10928,16 @@
         <v>66000000</v>
       </c>
       <c r="D372" s="2">
-        <v>0</v>
+        <v>6600000</v>
       </c>
       <c r="E372" s="2">
         <v>11000000</v>
       </c>
       <c r="F372" s="2">
-        <v>11000000</v>
+        <v>17600000</v>
       </c>
       <c r="G372" s="2">
-        <v>55000000</v>
+        <v>48400000</v>
       </c>
       <c r="H372" s="2">
         <v>0</v>
@@ -11063,16 +10954,16 @@
         <v>67500000</v>
       </c>
       <c r="D373" s="2">
-        <v>0</v>
+        <v>9000000</v>
       </c>
       <c r="E373" s="2">
         <v>4415000</v>
       </c>
       <c r="F373" s="2">
-        <v>4415000</v>
+        <v>13415000</v>
       </c>
       <c r="G373" s="2">
-        <v>63085000</v>
+        <v>54085000</v>
       </c>
       <c r="H373" s="2">
         <v>22500000</v>
@@ -11089,16 +10980,16 @@
         <v>128025000</v>
       </c>
       <c r="D374" s="2">
-        <v>0</v>
+        <v>17070000</v>
       </c>
       <c r="E374" s="2">
-        <v>39560000</v>
+        <v>41510000</v>
       </c>
       <c r="F374" s="2">
-        <v>39560000</v>
+        <v>58580000</v>
       </c>
       <c r="G374" s="2">
-        <v>88465000</v>
+        <v>69445000</v>
       </c>
       <c r="H374" s="2">
         <v>42675000</v>
@@ -11115,16 +11006,16 @@
         <v>24000000</v>
       </c>
       <c r="D375" s="2">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="E375" s="2">
         <v>6736950</v>
       </c>
       <c r="F375" s="2">
-        <v>6736950</v>
+        <v>9136950</v>
       </c>
       <c r="G375" s="2">
-        <v>17263050</v>
+        <v>14863050</v>
       </c>
       <c r="H375" s="2">
         <v>0</v>
@@ -11170,13 +11061,13 @@
         <v>0</v>
       </c>
       <c r="E377" s="2">
-        <v>663188048</v>
+        <v>663248048</v>
       </c>
       <c r="F377" s="2">
-        <v>663188048</v>
+        <v>663248048</v>
       </c>
       <c r="G377" s="2">
-        <v>3876618870</v>
+        <v>3876558870</v>
       </c>
       <c r="H377" s="2">
         <v>0</v>
@@ -11375,16 +11266,16 @@
         <v>23735415591</v>
       </c>
       <c r="D385" s="2">
-        <v>299444246</v>
+        <v>435023296</v>
       </c>
       <c r="E385" s="2">
-        <v>2381235336</v>
+        <v>2390844286</v>
       </c>
       <c r="F385" s="2">
-        <v>2680679582</v>
+        <v>2825867582</v>
       </c>
       <c r="G385" s="2">
-        <v>21054736009</v>
+        <v>20909548009</v>
       </c>
       <c r="H385" s="2">
         <v>232675000</v>
@@ -11557,16 +11448,16 @@
         <v>500000000</v>
       </c>
       <c r="D392" s="2">
-        <v>0</v>
+        <v>49811800</v>
       </c>
       <c r="E392" s="2">
         <v>0</v>
       </c>
       <c r="F392" s="2">
-        <v>0</v>
+        <v>49811800</v>
       </c>
       <c r="G392" s="2">
-        <v>500000000</v>
+        <v>450188200</v>
       </c>
       <c r="H392" s="2">
         <v>0</v>
@@ -11583,16 +11474,16 @@
         <v>690000000</v>
       </c>
       <c r="D393" s="2">
-        <v>103894080</v>
+        <v>152359150</v>
       </c>
       <c r="E393" s="2">
         <v>98940700</v>
       </c>
       <c r="F393" s="2">
-        <v>202834780</v>
+        <v>251299850</v>
       </c>
       <c r="G393" s="2">
-        <v>487165220</v>
+        <v>438700150</v>
       </c>
       <c r="H393" s="2">
         <v>0</v>
@@ -11817,16 +11708,16 @@
         <v>2230000000</v>
       </c>
       <c r="D402" s="2">
-        <v>9815000</v>
+        <v>19315000</v>
       </c>
       <c r="E402" s="2">
         <v>218151545</v>
       </c>
       <c r="F402" s="2">
-        <v>227966545</v>
+        <v>237466545</v>
       </c>
       <c r="G402" s="2">
-        <v>2002033455</v>
+        <v>1992533455</v>
       </c>
       <c r="H402" s="2">
         <v>0</v>
@@ -11869,16 +11760,16 @@
         <v>445223250</v>
       </c>
       <c r="D404" s="2">
-        <v>98217450</v>
+        <v>121017450</v>
       </c>
       <c r="E404" s="2">
         <v>67914000</v>
       </c>
       <c r="F404" s="2">
-        <v>166131450</v>
+        <v>188931450</v>
       </c>
       <c r="G404" s="2">
-        <v>279091800</v>
+        <v>256291800</v>
       </c>
       <c r="H404" s="2">
         <v>148407750</v>
@@ -11947,16 +11838,16 @@
         <v>351000000</v>
       </c>
       <c r="D407" s="2">
-        <v>0</v>
+        <v>17664766</v>
       </c>
       <c r="E407" s="2">
         <v>65686596</v>
       </c>
       <c r="F407" s="2">
-        <v>65686596</v>
+        <v>83351362</v>
       </c>
       <c r="G407" s="2">
-        <v>285313404</v>
+        <v>267648638</v>
       </c>
       <c r="H407" s="2">
         <v>117000000</v>
@@ -12259,16 +12150,16 @@
         <v>33762059370</v>
       </c>
       <c r="D419" s="2">
-        <v>828213315</v>
+        <v>976454951</v>
       </c>
       <c r="E419" s="2">
         <v>3564471467</v>
       </c>
       <c r="F419" s="2">
-        <v>4392684782</v>
+        <v>4540926418</v>
       </c>
       <c r="G419" s="2">
-        <v>29369374588</v>
+        <v>29221132952</v>
       </c>
       <c r="H419" s="2">
         <v>472807750</v>
@@ -12276,1852 +12167,786 @@
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A420" s="1" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="B420" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>873740000</v>
+        <v>1871950730</v>
       </c>
       <c r="C420" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>436870000</v>
+        <v>1871950730</v>
       </c>
       <c r="D420" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>404360000</v>
+        <f>F420-E420</f>
+        <v>404935052</v>
       </c>
       <c r="E420" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>35605052</v>
+        <v>78896778</v>
       </c>
       <c r="F420" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>439965052</v>
+        <v>483831830</v>
       </c>
       <c r="G420" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>-3095052</v>
+        <f>C420-F420</f>
+        <v>1388118900</v>
       </c>
       <c r="H420" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A420)</f>
-        <v>436870000</v>
+        <f>B420-C420</f>
+        <v>0</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A421" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B421" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="C421" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="D421" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="E421" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="F421" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="G421" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
-      <c r="H421" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A421)</f>
-        <v>0</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="B421" s="3"/>
+      <c r="C421" s="3"/>
+      <c r="D421" s="3"/>
+      <c r="E421" s="3"/>
+      <c r="F421" s="3"/>
+      <c r="G421" s="3"/>
+      <c r="H421" s="3"/>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A422" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B422" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="C422" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="D422" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="E422" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="F422" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="G422" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
-      <c r="H422" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A422)</f>
-        <v>0</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="B422" s="3"/>
+      <c r="C422" s="3"/>
+      <c r="D422" s="3"/>
+      <c r="E422" s="3"/>
+      <c r="F422" s="3"/>
+      <c r="G422" s="3"/>
+      <c r="H422" s="3"/>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A423" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B423" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="C423" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="D423" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="E423" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="F423" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="G423" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
-      <c r="H423" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A423)</f>
-        <v>0</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B423" s="3"/>
+      <c r="C423" s="3"/>
+      <c r="D423" s="3"/>
+      <c r="E423" s="3"/>
+      <c r="F423" s="3"/>
+      <c r="G423" s="3"/>
+      <c r="H423" s="3"/>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A424" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B424" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="C424" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="D424" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="E424" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="F424" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="G424" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
-      <c r="H424" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A424)</f>
-        <v>0</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="B424" s="3"/>
+      <c r="C424" s="3"/>
+      <c r="D424" s="3"/>
+      <c r="E424" s="3"/>
+      <c r="F424" s="3"/>
+      <c r="G424" s="3"/>
+      <c r="H424" s="3"/>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A425" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B425" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="C425" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="D425" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="E425" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="F425" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="G425" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
-      <c r="H425" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A425)</f>
-        <v>0</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B425" s="3"/>
+      <c r="C425" s="3"/>
+      <c r="D425" s="3"/>
+      <c r="E425" s="3"/>
+      <c r="F425" s="3"/>
+      <c r="G425" s="3"/>
+      <c r="H425" s="3"/>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A426" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B426" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="C426" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="D426" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="E426" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="F426" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="G426" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
-      <c r="H426" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A426)</f>
-        <v>0</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="B426" s="3"/>
+      <c r="C426" s="3"/>
+      <c r="D426" s="3"/>
+      <c r="E426" s="3"/>
+      <c r="F426" s="3"/>
+      <c r="G426" s="3"/>
+      <c r="H426" s="3"/>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A427" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B427" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="C427" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="D427" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="E427" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="F427" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="G427" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
-      <c r="H427" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A427)</f>
-        <v>0</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="B427" s="3"/>
+      <c r="C427" s="3"/>
+      <c r="D427" s="3"/>
+      <c r="E427" s="3"/>
+      <c r="F427" s="3"/>
+      <c r="G427" s="3"/>
+      <c r="H427" s="3"/>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A428" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B428" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="C428" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="D428" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="E428" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="F428" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="G428" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
-      <c r="H428" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A428)</f>
-        <v>0</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B428" s="3"/>
+      <c r="C428" s="3"/>
+      <c r="D428" s="3"/>
+      <c r="E428" s="3"/>
+      <c r="F428" s="3"/>
+      <c r="G428" s="3"/>
+      <c r="H428" s="3"/>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A429" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B429" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="C429" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="D429" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="E429" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="F429" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="G429" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
-      <c r="H429" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A429)</f>
-        <v>0</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="B429" s="3"/>
+      <c r="C429" s="3"/>
+      <c r="D429" s="3"/>
+      <c r="E429" s="3"/>
+      <c r="F429" s="3"/>
+      <c r="G429" s="3"/>
+      <c r="H429" s="3"/>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A430" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B430" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="C430" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="D430" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="E430" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="F430" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="G430" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
-      <c r="H430" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A430)</f>
-        <v>0</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="B430" s="3"/>
+      <c r="C430" s="3"/>
+      <c r="D430" s="3"/>
+      <c r="E430" s="3"/>
+      <c r="F430" s="3"/>
+      <c r="G430" s="3"/>
+      <c r="H430" s="3"/>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A431" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B431" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="C431" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="D431" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="E431" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="F431" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="G431" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
-      <c r="H431" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A431)</f>
-        <v>0</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="B431" s="3"/>
+      <c r="C431" s="3"/>
+      <c r="D431" s="3"/>
+      <c r="E431" s="3"/>
+      <c r="F431" s="3"/>
+      <c r="G431" s="3"/>
+      <c r="H431" s="3"/>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A432" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B432" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="C432" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="D432" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="E432" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="F432" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="G432" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
-      <c r="H432" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A432)</f>
-        <v>0</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="B432" s="3"/>
+      <c r="C432" s="3"/>
+      <c r="D432" s="3"/>
+      <c r="E432" s="3"/>
+      <c r="F432" s="3"/>
+      <c r="G432" s="3"/>
+      <c r="H432" s="3"/>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A433" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B433" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="C433" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="D433" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="E433" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="F433" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="G433" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
-      <c r="H433" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A433)</f>
-        <v>0</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="B433" s="3"/>
+      <c r="C433" s="3"/>
+      <c r="D433" s="3"/>
+      <c r="E433" s="3"/>
+      <c r="F433" s="3"/>
+      <c r="G433" s="3"/>
+      <c r="H433" s="3"/>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A434" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B434" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="C434" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="D434" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="E434" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="F434" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="G434" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
-      <c r="H434" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A434)</f>
-        <v>0</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B434" s="3"/>
+      <c r="C434" s="3"/>
+      <c r="D434" s="3"/>
+      <c r="E434" s="3"/>
+      <c r="F434" s="3"/>
+      <c r="G434" s="3"/>
+      <c r="H434" s="3"/>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A435" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B435" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="C435" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="D435" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="E435" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="F435" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="G435" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
-      <c r="H435" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A435)</f>
-        <v>0</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B435" s="3"/>
+      <c r="C435" s="3"/>
+      <c r="D435" s="3"/>
+      <c r="E435" s="3"/>
+      <c r="F435" s="3"/>
+      <c r="G435" s="3"/>
+      <c r="H435" s="3"/>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A436" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B436" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="C436" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="D436" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="E436" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="F436" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="G436" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
-      <c r="H436" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A436)</f>
-        <v>0</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="B436" s="3"/>
+      <c r="C436" s="3"/>
+      <c r="D436" s="3"/>
+      <c r="E436" s="3"/>
+      <c r="F436" s="3"/>
+      <c r="G436" s="3"/>
+      <c r="H436" s="3"/>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A437" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B437" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>474786000</v>
-      </c>
-      <c r="C437" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>237393000</v>
-      </c>
-      <c r="D437" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>0</v>
-      </c>
-      <c r="E437" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>0</v>
-      </c>
-      <c r="F437" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>0</v>
-      </c>
-      <c r="G437" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>237393000</v>
-      </c>
-      <c r="H437" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A437)</f>
-        <v>237393000</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B437" s="3"/>
+      <c r="C437" s="3"/>
+      <c r="D437" s="3"/>
+      <c r="E437" s="3"/>
+      <c r="F437" s="3"/>
+      <c r="G437" s="3"/>
+      <c r="H437" s="3"/>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A438" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B438" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>208425000</v>
-      </c>
-      <c r="C438" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>104212500</v>
-      </c>
-      <c r="D438" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>0</v>
-      </c>
-      <c r="E438" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>0</v>
-      </c>
-      <c r="F438" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>0</v>
-      </c>
-      <c r="G438" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>104212500</v>
-      </c>
-      <c r="H438" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A438)</f>
-        <v>104212500</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B438" s="3"/>
+      <c r="C438" s="3"/>
+      <c r="D438" s="3"/>
+      <c r="E438" s="3"/>
+      <c r="F438" s="3"/>
+      <c r="G438" s="3"/>
+      <c r="H438" s="3"/>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A439" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B439" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>20000000</v>
-      </c>
-      <c r="C439" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>13970000</v>
-      </c>
-      <c r="D439" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>13970000</v>
-      </c>
-      <c r="E439" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>0</v>
-      </c>
-      <c r="F439" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>13970000</v>
-      </c>
-      <c r="G439" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>0</v>
-      </c>
-      <c r="H439" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A439)</f>
-        <v>6030000</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B439" s="3"/>
+      <c r="C439" s="3"/>
+      <c r="D439" s="3"/>
+      <c r="E439" s="3"/>
+      <c r="F439" s="3"/>
+      <c r="G439" s="3"/>
+      <c r="H439" s="3"/>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A440" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B440" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>220000000</v>
-      </c>
-      <c r="C440" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>110000000</v>
-      </c>
-      <c r="D440" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>0</v>
-      </c>
-      <c r="E440" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>29896778</v>
-      </c>
-      <c r="F440" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>29896778</v>
-      </c>
-      <c r="G440" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>80103222</v>
-      </c>
-      <c r="H440" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A440)</f>
-        <v>110000000</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B440" s="3"/>
+      <c r="C440" s="3"/>
+      <c r="D440" s="3"/>
+      <c r="E440" s="3"/>
+      <c r="F440" s="3"/>
+      <c r="G440" s="3"/>
+      <c r="H440" s="3"/>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A441" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B441" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>75000000</v>
-      </c>
-      <c r="C441" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>37500000</v>
-      </c>
-      <c r="D441" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>0</v>
-      </c>
-      <c r="E441" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>0</v>
-      </c>
-      <c r="F441" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>0</v>
-      </c>
-      <c r="G441" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>37500000</v>
-      </c>
-      <c r="H441" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A441)</f>
-        <v>37500000</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B441" s="3"/>
+      <c r="C441" s="3"/>
+      <c r="D441" s="3"/>
+      <c r="E441" s="3"/>
+      <c r="F441" s="3"/>
+      <c r="G441" s="3"/>
+      <c r="H441" s="3"/>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A442" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B442" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="C442" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="D442" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="E442" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="F442" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="G442" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
-      <c r="H442" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A442)</f>
-        <v>0</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B442" s="3"/>
+      <c r="C442" s="3"/>
+      <c r="D442" s="3"/>
+      <c r="E442" s="3"/>
+      <c r="F442" s="3"/>
+      <c r="G442" s="3"/>
+      <c r="H442" s="3"/>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A443" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B443" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="C443" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="D443" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="E443" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="F443" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="G443" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
-      <c r="H443" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A443)</f>
-        <v>0</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="B443" s="3"/>
+      <c r="C443" s="3"/>
+      <c r="D443" s="3"/>
+      <c r="E443" s="3"/>
+      <c r="F443" s="3"/>
+      <c r="G443" s="3"/>
+      <c r="H443" s="3"/>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A444" s="1" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="B444" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>60000000</v>
       </c>
       <c r="C444" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
-        <v>30000000</v>
+        <v>60000000</v>
       </c>
       <c r="D444" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
+        <f>F444-E444</f>
         <v>9000000</v>
       </c>
       <c r="E444" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>0</v>
       </c>
       <c r="F444" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
         <v>9000000</v>
       </c>
       <c r="G444" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
-        <v>21000000</v>
+        <f>C444-F444</f>
+        <v>51000000</v>
       </c>
       <c r="H444" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A444)</f>
-        <v>30000000</v>
+        <f>B444-C444</f>
+        <v>0</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A445" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="B445" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>45150000</v>
       </c>
       <c r="C445" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
-        <v>22575000</v>
+        <v>45150000</v>
       </c>
       <c r="D445" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
+        <f>F445-E445</f>
         <v>6423200</v>
       </c>
       <c r="E445" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>6119400</v>
       </c>
       <c r="F445" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
         <v>12542600</v>
       </c>
       <c r="G445" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
-        <v>10032400</v>
+        <f>C445-F445</f>
+        <v>32607400</v>
       </c>
       <c r="H445" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A445)</f>
-        <v>22575000</v>
+        <f>B445-C445</f>
+        <v>0</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A446" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B446" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="C446" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="D446" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="E446" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="F446" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="G446" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
-      <c r="H446" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A446)</f>
-        <v>0</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B446" s="3"/>
+      <c r="C446" s="3"/>
+      <c r="D446" s="3"/>
+      <c r="E446" s="3"/>
+      <c r="F446" s="3"/>
+      <c r="G446" s="3"/>
+      <c r="H446" s="3"/>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A447" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B447" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="C447" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="D447" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="E447" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="F447" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="G447" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
-      <c r="H447" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A447)</f>
-        <v>0</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="B447" s="3"/>
+      <c r="C447" s="3"/>
+      <c r="D447" s="3"/>
+      <c r="E447" s="3"/>
+      <c r="F447" s="3"/>
+      <c r="G447" s="3"/>
+      <c r="H447" s="3"/>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A448" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B448" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="C448" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="D448" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="E448" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="F448" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="G448" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
-      <c r="H448" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A448)</f>
-        <v>0</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B448" s="3"/>
+      <c r="C448" s="3"/>
+      <c r="D448" s="3"/>
+      <c r="E448" s="3"/>
+      <c r="F448" s="3"/>
+      <c r="G448" s="3"/>
+      <c r="H448" s="3"/>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A449" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B449" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="C449" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="D449" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="E449" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="F449" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="G449" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
-      <c r="H449" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A449)</f>
-        <v>0</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="B449" s="3"/>
+      <c r="C449" s="3"/>
+      <c r="D449" s="3"/>
+      <c r="E449" s="3"/>
+      <c r="F449" s="3"/>
+      <c r="G449" s="3"/>
+      <c r="H449" s="3"/>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A450" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B450" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="C450" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="D450" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="E450" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="F450" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="G450" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
-      <c r="H450" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A450)</f>
-        <v>0</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B450" s="3"/>
+      <c r="C450" s="3"/>
+      <c r="D450" s="3"/>
+      <c r="E450" s="3"/>
+      <c r="F450" s="3"/>
+      <c r="G450" s="3"/>
+      <c r="H450" s="3"/>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A451" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B451" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="C451" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="D451" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="E451" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="F451" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="G451" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
-      <c r="H451" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A451)</f>
-        <v>0</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B451" s="3"/>
+      <c r="C451" s="3"/>
+      <c r="D451" s="3"/>
+      <c r="E451" s="3"/>
+      <c r="F451" s="3"/>
+      <c r="G451" s="3"/>
+      <c r="H451" s="3"/>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A452" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B452" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>6000000</v>
-      </c>
-      <c r="C452" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>1500000</v>
-      </c>
-      <c r="D452" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>0</v>
-      </c>
-      <c r="E452" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>0</v>
-      </c>
-      <c r="F452" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>0</v>
-      </c>
-      <c r="G452" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>1500000</v>
-      </c>
-      <c r="H452" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A452)</f>
-        <v>4500000</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B452" s="3"/>
+      <c r="C452" s="3"/>
+      <c r="D452" s="3"/>
+      <c r="E452" s="3"/>
+      <c r="F452" s="3"/>
+      <c r="G452" s="3"/>
+      <c r="H452" s="3"/>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A453" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B453" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>41000000</v>
-      </c>
-      <c r="C453" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>10250000</v>
-      </c>
-      <c r="D453" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>1997700</v>
-      </c>
-      <c r="E453" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>998400</v>
-      </c>
-      <c r="F453" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>2996100</v>
-      </c>
-      <c r="G453" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>7253900</v>
-      </c>
-      <c r="H453" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A453)</f>
-        <v>30750000</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B453" s="3"/>
+      <c r="C453" s="3"/>
+      <c r="D453" s="3"/>
+      <c r="E453" s="3"/>
+      <c r="F453" s="3"/>
+      <c r="G453" s="3"/>
+      <c r="H453" s="3"/>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A454" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B454" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>12000000</v>
-      </c>
-      <c r="C454" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>3000000</v>
-      </c>
-      <c r="D454" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>0</v>
-      </c>
-      <c r="E454" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>0</v>
-      </c>
-      <c r="F454" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>0</v>
-      </c>
-      <c r="G454" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>3000000</v>
-      </c>
-      <c r="H454" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A454)</f>
-        <v>9000000</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="B454" s="3"/>
+      <c r="C454" s="3"/>
+      <c r="D454" s="3"/>
+      <c r="E454" s="3"/>
+      <c r="F454" s="3"/>
+      <c r="G454" s="3"/>
+      <c r="H454" s="3"/>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A455" s="1" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="B455" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>171000000</v>
+        <v>372660000</v>
       </c>
       <c r="C455" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>42750000</v>
+        <v>372660000</v>
       </c>
       <c r="D455" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>5880000</v>
+        <f>F455-E455</f>
+        <v>8912700</v>
       </c>
       <c r="E455" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>0</v>
+        <v>5604650</v>
       </c>
       <c r="F455" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>5880000</v>
+        <v>14517350</v>
       </c>
       <c r="G455" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>36870000</v>
+        <f>C455-F455</f>
+        <v>358142650</v>
       </c>
       <c r="H455" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A455)</f>
-        <v>128250000</v>
+        <f>B455-C455</f>
+        <v>0</v>
       </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A456" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B456" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>130000000</v>
-      </c>
-      <c r="C456" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>32500000</v>
-      </c>
-      <c r="D456" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>0</v>
-      </c>
-      <c r="E456" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>7381250</v>
-      </c>
-      <c r="F456" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>7381250</v>
-      </c>
-      <c r="G456" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>25118750</v>
-      </c>
-      <c r="H456" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A456)</f>
-        <v>97500000</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B456" s="3"/>
+      <c r="C456" s="3"/>
+      <c r="D456" s="3"/>
+      <c r="E456" s="3"/>
+      <c r="F456" s="3"/>
+      <c r="G456" s="3"/>
+      <c r="H456" s="3"/>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A457" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B457" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>6660000</v>
-      </c>
-      <c r="C457" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>1665000</v>
-      </c>
-      <c r="D457" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>1665000</v>
-      </c>
-      <c r="E457" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>0</v>
-      </c>
-      <c r="F457" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>1665000</v>
-      </c>
-      <c r="G457" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>0</v>
-      </c>
-      <c r="H457" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A457)</f>
-        <v>4995000</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B457" s="3"/>
+      <c r="C457" s="3"/>
+      <c r="D457" s="3"/>
+      <c r="E457" s="3"/>
+      <c r="F457" s="3"/>
+      <c r="G457" s="3"/>
+      <c r="H457" s="3"/>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A458" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B458" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>6000000</v>
-      </c>
-      <c r="C458" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>1500000</v>
-      </c>
-      <c r="D458" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>0</v>
-      </c>
-      <c r="E458" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>0</v>
-      </c>
-      <c r="F458" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>0</v>
-      </c>
-      <c r="G458" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>1500000</v>
-      </c>
-      <c r="H458" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A458)</f>
-        <v>4500000</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B458" s="3"/>
+      <c r="C458" s="3"/>
+      <c r="D458" s="3"/>
+      <c r="E458" s="3"/>
+      <c r="F458" s="3"/>
+      <c r="G458" s="3"/>
+      <c r="H458" s="3"/>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A459" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B459" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="C459" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="D459" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="E459" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="F459" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="G459" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
-      <c r="H459" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A459)</f>
-        <v>0</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B459" s="3"/>
+      <c r="C459" s="3"/>
+      <c r="D459" s="3"/>
+      <c r="E459" s="3"/>
+      <c r="F459" s="3"/>
+      <c r="G459" s="3"/>
+      <c r="H459" s="3"/>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A460" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B460" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="C460" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="D460" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="E460" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="F460" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="G460" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
-      <c r="H460" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A460)</f>
-        <v>0</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="B460" s="3"/>
+      <c r="C460" s="3"/>
+      <c r="D460" s="3"/>
+      <c r="E460" s="3"/>
+      <c r="F460" s="3"/>
+      <c r="G460" s="3"/>
+      <c r="H460" s="3"/>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A461" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B461" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="C461" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="D461" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="E461" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="F461" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="G461" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
-      <c r="H461" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A461)</f>
-        <v>0</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B461" s="3"/>
+      <c r="C461" s="3"/>
+      <c r="D461" s="3"/>
+      <c r="E461" s="3"/>
+      <c r="F461" s="3"/>
+      <c r="G461" s="3"/>
+      <c r="H461" s="3"/>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A462" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B462" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="C462" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="D462" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="E462" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="F462" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="G462" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
-      <c r="H462" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A462)</f>
-        <v>0</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B462" s="3"/>
+      <c r="C462" s="3"/>
+      <c r="D462" s="3"/>
+      <c r="E462" s="3"/>
+      <c r="F462" s="3"/>
+      <c r="G462" s="3"/>
+      <c r="H462" s="3"/>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A463" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B463" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="C463" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="D463" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="E463" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="F463" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="G463" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
-      <c r="H463" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A463)</f>
-        <v>0</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B463" s="3"/>
+      <c r="C463" s="3"/>
+      <c r="D463" s="3"/>
+      <c r="E463" s="3"/>
+      <c r="F463" s="3"/>
+      <c r="G463" s="3"/>
+      <c r="H463" s="3"/>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A464" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B464" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="C464" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="D464" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="E464" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="F464" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="G464" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
-      <c r="H464" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A464)</f>
-        <v>0</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="B464" s="3"/>
+      <c r="C464" s="3"/>
+      <c r="D464" s="3"/>
+      <c r="E464" s="3"/>
+      <c r="F464" s="3"/>
+      <c r="G464" s="3"/>
+      <c r="H464" s="3"/>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A465" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B465" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="C465" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="D465" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="E465" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="F465" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="G465" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
-      <c r="H465" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A465)</f>
-        <v>0</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="B465" s="3"/>
+      <c r="C465" s="3"/>
+      <c r="D465" s="3"/>
+      <c r="E465" s="3"/>
+      <c r="F465" s="3"/>
+      <c r="G465" s="3"/>
+      <c r="H465" s="3"/>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A466" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B466" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="C466" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="D466" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="E466" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="F466" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="G466" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
-      <c r="H466" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A466)</f>
-        <v>0</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B466" s="3"/>
+      <c r="C466" s="3"/>
+      <c r="D466" s="3"/>
+      <c r="E466" s="3"/>
+      <c r="F466" s="3"/>
+      <c r="G466" s="3"/>
+      <c r="H466" s="3"/>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A467" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B467" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="C467" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="D467" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="E467" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="F467" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="G467" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
-      <c r="H467" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A467)</f>
-        <v>0</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B467" s="3"/>
+      <c r="C467" s="3"/>
+      <c r="D467" s="3"/>
+      <c r="E467" s="3"/>
+      <c r="F467" s="3"/>
+      <c r="G467" s="3"/>
+      <c r="H467" s="3"/>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A468" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B468" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="C468" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="D468" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="E468" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="F468" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="G468" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
-      <c r="H468" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A468)</f>
-        <v>0</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B468" s="3"/>
+      <c r="C468" s="3"/>
+      <c r="D468" s="3"/>
+      <c r="E468" s="3"/>
+      <c r="F468" s="3"/>
+      <c r="G468" s="3"/>
+      <c r="H468" s="3"/>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A469" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B469" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="C469" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="D469" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="E469" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="F469" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="G469" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
-      <c r="H469" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A469)</f>
-        <v>0</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B469" s="3"/>
+      <c r="C469" s="3"/>
+      <c r="D469" s="3"/>
+      <c r="E469" s="3"/>
+      <c r="F469" s="3"/>
+      <c r="G469" s="3"/>
+      <c r="H469" s="3"/>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A470" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B470" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="C470" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="D470" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="E470" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="F470" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="G470" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
-      <c r="H470" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A470)</f>
-        <v>0</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B470" s="3"/>
+      <c r="C470" s="3"/>
+      <c r="D470" s="3"/>
+      <c r="E470" s="3"/>
+      <c r="F470" s="3"/>
+      <c r="G470" s="3"/>
+      <c r="H470" s="3"/>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A471" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B471" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="C471" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="D471" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="E471" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="F471" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="G471" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
-      <c r="H471" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A471)</f>
-        <v>0</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B471" s="3"/>
+      <c r="C471" s="3"/>
+      <c r="D471" s="3"/>
+      <c r="E471" s="3"/>
+      <c r="F471" s="3"/>
+      <c r="G471" s="3"/>
+      <c r="H471" s="3"/>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A472" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B472" s="3">
-        <f>SUMIFS('II PD'!C:C,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>2349761000</v>
-      </c>
-      <c r="C472" s="3">
-        <f>SUMIFS('II PD'!D:D,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>1085685500</v>
-      </c>
-      <c r="D472" s="3">
-        <f>SUMIFS('II PD'!E:E,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>443295900</v>
-      </c>
-      <c r="E472" s="3">
-        <f>SUMIFS('II PD'!F:F,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>80000880</v>
-      </c>
-      <c r="F472" s="3">
-        <f>SUMIFS('II PD'!G:G,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>523296780</v>
-      </c>
-      <c r="G472" s="3">
-        <f>SUMIFS('II PD'!H:H,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>562388720</v>
-      </c>
-      <c r="H472" s="3">
-        <f>SUMIFS('II PD'!I:I,'II PD'!A:A,'Budget 3 Juni 2024'!A472)</f>
-        <v>1264075500</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B472" s="3"/>
+      <c r="C472" s="3"/>
+      <c r="D472" s="3"/>
+      <c r="E472" s="3"/>
+      <c r="F472" s="3"/>
+      <c r="G472" s="3"/>
+      <c r="H472" s="3"/>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A473" t="s">
-        <v>8</v>
-      </c>
-      <c r="B473" s="2">
-        <v>10505111000</v>
-      </c>
-      <c r="C473" s="2">
-        <v>10505111000</v>
-      </c>
-      <c r="D473" s="2">
-        <v>7767056599</v>
-      </c>
-      <c r="E473" s="2">
-        <v>0</v>
-      </c>
-      <c r="F473" s="2">
-        <v>7767056599</v>
-      </c>
-      <c r="G473" s="2">
-        <v>2738054401</v>
-      </c>
-      <c r="H473" s="2">
-        <v>0</v>
-      </c>
+      <c r="A473" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B473" s="3"/>
+      <c r="C473" s="3"/>
+      <c r="D473" s="3"/>
+      <c r="E473" s="3"/>
+      <c r="F473" s="3"/>
+      <c r="G473" s="3"/>
+      <c r="H473" s="3"/>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A474" t="s">
-        <v>10</v>
-      </c>
-      <c r="B474" s="2">
-        <v>0</v>
-      </c>
-      <c r="C474" s="2">
-        <v>0</v>
-      </c>
-      <c r="D474" s="2">
-        <v>0</v>
-      </c>
-      <c r="E474" s="2">
-        <v>0</v>
-      </c>
-      <c r="F474" s="2">
-        <v>0</v>
-      </c>
-      <c r="G474" s="2">
-        <v>0</v>
-      </c>
-      <c r="H474" s="2">
-        <v>0</v>
-      </c>
+      <c r="A474" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B474" s="3"/>
+      <c r="C474" s="3"/>
+      <c r="D474" s="3"/>
+      <c r="E474" s="3"/>
+      <c r="F474" s="3"/>
+      <c r="G474" s="3"/>
+      <c r="H474" s="3"/>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A475" t="s">
-        <v>11</v>
-      </c>
-      <c r="B475" s="2">
-        <v>0</v>
-      </c>
-      <c r="C475" s="2">
-        <v>0</v>
-      </c>
-      <c r="D475" s="2">
-        <v>0</v>
-      </c>
-      <c r="E475" s="2">
-        <v>0</v>
-      </c>
-      <c r="F475" s="2">
-        <v>0</v>
-      </c>
-      <c r="G475" s="2">
-        <v>0</v>
-      </c>
-      <c r="H475" s="2">
+      <c r="A475" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B475" s="3">
+        <f>SUM(B420:B474)</f>
+        <v>2349760730</v>
+      </c>
+      <c r="C475" s="3">
+        <f t="shared" ref="C475:H475" si="0">SUM(C420:C474)</f>
+        <v>2349760730</v>
+      </c>
+      <c r="D475" s="3">
+        <f t="shared" si="0"/>
+        <v>429270952</v>
+      </c>
+      <c r="E475" s="3">
+        <f t="shared" si="0"/>
+        <v>90620828</v>
+      </c>
+      <c r="F475" s="3">
+        <f t="shared" si="0"/>
+        <v>519891780</v>
+      </c>
+      <c r="G475" s="3">
+        <f t="shared" si="0"/>
+        <v>1829868950</v>
+      </c>
+      <c r="H475" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B476" s="2">
-        <v>0</v>
+        <v>10505111000</v>
       </c>
       <c r="C476" s="2">
-        <v>0</v>
+        <v>10505111000</v>
       </c>
       <c r="D476" s="2">
-        <v>0</v>
+        <v>7759691599</v>
       </c>
       <c r="E476" s="2">
         <v>0</v>
       </c>
       <c r="F476" s="2">
-        <v>0</v>
+        <v>7759691599</v>
       </c>
       <c r="G476" s="2">
-        <v>0</v>
+        <v>2745419401</v>
       </c>
       <c r="H476" s="2">
         <v>0</v>
@@ -14129,7 +12954,7 @@
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B477" s="2">
         <v>0</v>
@@ -14155,7 +12980,7 @@
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B478" s="2">
         <v>0</v>
@@ -14181,7 +13006,7 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B479" s="2">
         <v>0</v>
@@ -14207,25 +13032,25 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="B480" s="2">
-        <v>2312795000</v>
+        <v>0</v>
       </c>
       <c r="C480" s="2">
-        <v>2312795000</v>
+        <v>0</v>
       </c>
       <c r="D480" s="2">
-        <v>1778331214</v>
+        <v>0</v>
       </c>
       <c r="E480" s="2">
         <v>0</v>
       </c>
       <c r="F480" s="2">
-        <v>1778331214</v>
+        <v>0</v>
       </c>
       <c r="G480" s="2">
-        <v>534463786</v>
+        <v>0</v>
       </c>
       <c r="H480" s="2">
         <v>0</v>
@@ -14233,25 +13058,25 @@
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="B481" s="2">
-        <v>4989900000</v>
+        <v>0</v>
       </c>
       <c r="C481" s="2">
-        <v>4989900000</v>
+        <v>0</v>
       </c>
       <c r="D481" s="2">
-        <v>805666889</v>
+        <v>0</v>
       </c>
       <c r="E481" s="2">
-        <v>333634248</v>
+        <v>0</v>
       </c>
       <c r="F481" s="2">
-        <v>1139301137</v>
+        <v>0</v>
       </c>
       <c r="G481" s="2">
-        <v>3850598863</v>
+        <v>0</v>
       </c>
       <c r="H481" s="2">
         <v>0</v>
@@ -14259,7 +13084,7 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B482" s="2">
         <v>0</v>
@@ -14285,25 +13110,25 @@
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="B483" s="2">
-        <v>1680000000</v>
+        <v>2312795000</v>
       </c>
       <c r="C483" s="2">
-        <v>1680000000</v>
+        <v>2312795000</v>
       </c>
       <c r="D483" s="2">
-        <v>353557050</v>
+        <v>1778331214</v>
       </c>
       <c r="E483" s="2">
         <v>0</v>
       </c>
       <c r="F483" s="2">
-        <v>353557050</v>
+        <v>1778331214</v>
       </c>
       <c r="G483" s="2">
-        <v>1326442950</v>
+        <v>534463786</v>
       </c>
       <c r="H483" s="2">
         <v>0</v>
@@ -14311,25 +13136,25 @@
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="B484" s="2">
-        <v>492066000</v>
+        <v>4989900000</v>
       </c>
       <c r="C484" s="2">
-        <v>492066000</v>
+        <v>4989900000</v>
       </c>
       <c r="D484" s="2">
-        <v>31501365</v>
+        <v>805366889</v>
       </c>
       <c r="E484" s="2">
-        <v>7785500</v>
+        <v>333634248</v>
       </c>
       <c r="F484" s="2">
-        <v>39286865</v>
+        <v>1139001137</v>
       </c>
       <c r="G484" s="2">
-        <v>452779135</v>
+        <v>3850898863</v>
       </c>
       <c r="H484" s="2">
         <v>0</v>
@@ -14337,13 +13162,13 @@
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="B485" s="2">
-        <v>624500000</v>
+        <v>0</v>
       </c>
       <c r="C485" s="2">
-        <v>624500000</v>
+        <v>0</v>
       </c>
       <c r="D485" s="2">
         <v>0</v>
@@ -14355,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G485" s="2">
-        <v>624500000</v>
+        <v>0</v>
       </c>
       <c r="H485" s="2">
         <v>0</v>
@@ -14363,25 +13188,25 @@
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="B486" s="2">
-        <v>700000000</v>
+        <v>1680000000</v>
       </c>
       <c r="C486" s="2">
-        <v>700000000</v>
+        <v>1680000000</v>
       </c>
       <c r="D486" s="2">
-        <v>0</v>
+        <v>353557050</v>
       </c>
       <c r="E486" s="2">
         <v>0</v>
       </c>
       <c r="F486" s="2">
-        <v>0</v>
+        <v>353557050</v>
       </c>
       <c r="G486" s="2">
-        <v>700000000</v>
+        <v>1326442950</v>
       </c>
       <c r="H486" s="2">
         <v>0</v>
@@ -14389,25 +13214,25 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="B487" s="2">
-        <v>0</v>
+        <v>492066000</v>
       </c>
       <c r="C487" s="2">
-        <v>0</v>
+        <v>492066000</v>
       </c>
       <c r="D487" s="2">
-        <v>0</v>
+        <v>31501365</v>
       </c>
       <c r="E487" s="2">
-        <v>0</v>
+        <v>7785500</v>
       </c>
       <c r="F487" s="2">
-        <v>0</v>
+        <v>39286865</v>
       </c>
       <c r="G487" s="2">
-        <v>0</v>
+        <v>452779135</v>
       </c>
       <c r="H487" s="2">
         <v>0</v>
@@ -14415,25 +13240,25 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="B488" s="2">
-        <v>745000000</v>
+        <v>624500000</v>
       </c>
       <c r="C488" s="2">
-        <v>745000000</v>
+        <v>624500000</v>
       </c>
       <c r="D488" s="2">
-        <v>26235280</v>
+        <v>0</v>
       </c>
       <c r="E488" s="2">
-        <v>32460000</v>
+        <v>0</v>
       </c>
       <c r="F488" s="2">
-        <v>58695280</v>
+        <v>0</v>
       </c>
       <c r="G488" s="2">
-        <v>686304720</v>
+        <v>624500000</v>
       </c>
       <c r="H488" s="2">
         <v>0</v>
@@ -14441,25 +13266,25 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="B489" s="2">
-        <v>4029356000</v>
+        <v>700000000</v>
       </c>
       <c r="C489" s="2">
-        <v>4029356000</v>
+        <v>700000000</v>
       </c>
       <c r="D489" s="2">
-        <v>2411599000</v>
+        <v>0</v>
       </c>
       <c r="E489" s="2">
-        <v>29795000</v>
+        <v>0</v>
       </c>
       <c r="F489" s="2">
-        <v>2441394000</v>
+        <v>0</v>
       </c>
       <c r="G489" s="2">
-        <v>1587962000</v>
+        <v>700000000</v>
       </c>
       <c r="H489" s="2">
         <v>0</v>
@@ -14467,13 +13292,13 @@
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="B490" s="2">
-        <v>297500000</v>
+        <v>0</v>
       </c>
       <c r="C490" s="2">
-        <v>297500000</v>
+        <v>0</v>
       </c>
       <c r="D490" s="2">
         <v>0</v>
@@ -14485,7 +13310,7 @@
         <v>0</v>
       </c>
       <c r="G490" s="2">
-        <v>297500000</v>
+        <v>0</v>
       </c>
       <c r="H490" s="2">
         <v>0</v>
@@ -14493,25 +13318,25 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="B491" s="2">
-        <v>266250000</v>
+        <v>745000000</v>
       </c>
       <c r="C491" s="2">
-        <v>266250000</v>
+        <v>745000000</v>
       </c>
       <c r="D491" s="2">
-        <v>0</v>
+        <v>26235280</v>
       </c>
       <c r="E491" s="2">
-        <v>40800000</v>
+        <v>32460000</v>
       </c>
       <c r="F491" s="2">
-        <v>40800000</v>
+        <v>58695280</v>
       </c>
       <c r="G491" s="2">
-        <v>225450000</v>
+        <v>686304720</v>
       </c>
       <c r="H491" s="2">
         <v>0</v>
@@ -14519,25 +13344,25 @@
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="B492" s="2">
-        <v>1350000000</v>
+        <v>4029356000</v>
       </c>
       <c r="C492" s="2">
-        <v>1350000000</v>
+        <v>4029356000</v>
       </c>
       <c r="D492" s="2">
-        <v>0</v>
+        <v>2411599000</v>
       </c>
       <c r="E492" s="2">
-        <v>0</v>
+        <v>29795000</v>
       </c>
       <c r="F492" s="2">
-        <v>0</v>
+        <v>2441394000</v>
       </c>
       <c r="G492" s="2">
-        <v>1350000000</v>
+        <v>1587962000</v>
       </c>
       <c r="H492" s="2">
         <v>0</v>
@@ -14545,51 +13370,51 @@
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="B493" s="2">
-        <v>100000000</v>
+        <v>297500000</v>
       </c>
       <c r="C493" s="2">
-        <v>75000000</v>
+        <v>297500000</v>
       </c>
       <c r="D493" s="2">
         <v>0</v>
       </c>
       <c r="E493" s="2">
-        <v>12720000</v>
+        <v>0</v>
       </c>
       <c r="F493" s="2">
-        <v>12720000</v>
+        <v>0</v>
       </c>
       <c r="G493" s="2">
-        <v>62280000</v>
+        <v>297500000</v>
       </c>
       <c r="H493" s="2">
-        <v>25000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B494" s="2">
-        <v>1016150000</v>
+        <v>266250000</v>
       </c>
       <c r="C494" s="2">
-        <v>1016150000</v>
+        <v>266250000</v>
       </c>
       <c r="D494" s="2">
-        <v>34825000</v>
+        <v>0</v>
       </c>
       <c r="E494" s="2">
-        <v>128340000</v>
+        <v>40800000</v>
       </c>
       <c r="F494" s="2">
-        <v>163165000</v>
+        <v>40800000</v>
       </c>
       <c r="G494" s="2">
-        <v>852985000</v>
+        <v>225450000</v>
       </c>
       <c r="H494" s="2">
         <v>0</v>
@@ -14597,25 +13422,25 @@
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B495" s="2">
-        <v>2560000000</v>
+        <v>1350000000</v>
       </c>
       <c r="C495" s="2">
-        <v>2560000000</v>
+        <v>1350000000</v>
       </c>
       <c r="D495" s="2">
-        <v>8404406</v>
+        <v>0</v>
       </c>
       <c r="E495" s="2">
-        <v>446630703</v>
+        <v>0</v>
       </c>
       <c r="F495" s="2">
-        <v>455035109</v>
+        <v>0</v>
       </c>
       <c r="G495" s="2">
-        <v>2104964891</v>
+        <v>1350000000</v>
       </c>
       <c r="H495" s="2">
         <v>0</v>
@@ -14623,77 +13448,77 @@
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B496" s="2">
-        <v>891173000</v>
+        <v>100000000</v>
       </c>
       <c r="C496" s="2">
-        <v>668379750</v>
+        <v>75000000</v>
       </c>
       <c r="D496" s="2">
-        <v>29693828</v>
+        <v>0</v>
       </c>
       <c r="E496" s="2">
-        <v>22370000</v>
+        <v>12720000</v>
       </c>
       <c r="F496" s="2">
-        <v>52063828</v>
+        <v>12720000</v>
       </c>
       <c r="G496" s="2">
-        <v>616315922</v>
+        <v>62280000</v>
       </c>
       <c r="H496" s="2">
-        <v>222793250</v>
+        <v>25000000</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="B497" s="2">
-        <v>1160455000</v>
+        <v>1016150000</v>
       </c>
       <c r="C497" s="2">
-        <v>870341250</v>
+        <v>1016150000</v>
       </c>
       <c r="D497" s="2">
-        <v>95838170</v>
+        <v>34825000</v>
       </c>
       <c r="E497" s="2">
-        <v>176941260</v>
+        <v>128340000</v>
       </c>
       <c r="F497" s="2">
-        <v>272779430</v>
+        <v>163165000</v>
       </c>
       <c r="G497" s="2">
-        <v>597561820</v>
+        <v>852985000</v>
       </c>
       <c r="H497" s="2">
-        <v>290113750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B498" s="2">
-        <v>93000000</v>
+        <v>2560000000</v>
       </c>
       <c r="C498" s="2">
-        <v>93000000</v>
+        <v>2560000000</v>
       </c>
       <c r="D498" s="2">
-        <v>0</v>
+        <v>8404406</v>
       </c>
       <c r="E498" s="2">
-        <v>14500000</v>
+        <v>446630703</v>
       </c>
       <c r="F498" s="2">
-        <v>14500000</v>
+        <v>455035109</v>
       </c>
       <c r="G498" s="2">
-        <v>78500000</v>
+        <v>2104964891</v>
       </c>
       <c r="H498" s="2">
         <v>0</v>
@@ -14701,77 +13526,77 @@
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B499" s="2">
-        <v>562923000</v>
+        <v>891173000</v>
       </c>
       <c r="C499" s="2">
-        <v>422192250</v>
+        <v>668379750</v>
       </c>
       <c r="D499" s="2">
-        <v>19366000</v>
+        <v>29693828</v>
       </c>
       <c r="E499" s="2">
-        <v>12640000</v>
+        <v>22370000</v>
       </c>
       <c r="F499" s="2">
-        <v>32006000</v>
+        <v>52063828</v>
       </c>
       <c r="G499" s="2">
-        <v>390186250</v>
+        <v>616315922</v>
       </c>
       <c r="H499" s="2">
-        <v>140730750</v>
+        <v>222793250</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B500" s="2">
-        <v>688578000</v>
+        <v>1160455000</v>
       </c>
       <c r="C500" s="2">
-        <v>516433500</v>
+        <v>870341250</v>
       </c>
       <c r="D500" s="2">
-        <v>35082547</v>
+        <v>95838170</v>
       </c>
       <c r="E500" s="2">
-        <v>77961880</v>
+        <v>176941260</v>
       </c>
       <c r="F500" s="2">
-        <v>113044427</v>
+        <v>272779430</v>
       </c>
       <c r="G500" s="2">
-        <v>403389073</v>
+        <v>597561820</v>
       </c>
       <c r="H500" s="2">
-        <v>172144500</v>
+        <v>290113750</v>
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="B501" s="2">
-        <v>36180000</v>
+        <v>93000000</v>
       </c>
       <c r="C501" s="2">
-        <v>36180000</v>
+        <v>93000000</v>
       </c>
       <c r="D501" s="2">
-        <v>1720000</v>
+        <v>0</v>
       </c>
       <c r="E501" s="2">
-        <v>5342537</v>
+        <v>14500000</v>
       </c>
       <c r="F501" s="2">
-        <v>7062537</v>
+        <v>14500000</v>
       </c>
       <c r="G501" s="2">
-        <v>29117463</v>
+        <v>78500000</v>
       </c>
       <c r="H501" s="2">
         <v>0</v>
@@ -14779,77 +13604,77 @@
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B502" s="2">
-        <v>61741000</v>
+        <v>562923000</v>
       </c>
       <c r="C502" s="2">
-        <v>61741000</v>
+        <v>422192250</v>
       </c>
       <c r="D502" s="2">
-        <v>38255444</v>
+        <v>19366000</v>
       </c>
       <c r="E502" s="2">
-        <v>0</v>
+        <v>12640000</v>
       </c>
       <c r="F502" s="2">
-        <v>38255444</v>
+        <v>32006000</v>
       </c>
       <c r="G502" s="2">
-        <v>23485556</v>
+        <v>390186250</v>
       </c>
       <c r="H502" s="2">
-        <v>0</v>
+        <v>140730750</v>
       </c>
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="B503" s="2">
-        <v>0</v>
+        <v>688578000</v>
       </c>
       <c r="C503" s="2">
-        <v>0</v>
+        <v>516433500</v>
       </c>
       <c r="D503" s="2">
-        <v>0</v>
+        <v>35082547</v>
       </c>
       <c r="E503" s="2">
-        <v>84819308</v>
+        <v>78343130</v>
       </c>
       <c r="F503" s="2">
-        <v>84819308</v>
+        <v>113425677</v>
       </c>
       <c r="G503" s="2">
-        <v>-84819308</v>
+        <v>403007823</v>
       </c>
       <c r="H503" s="2">
-        <v>0</v>
+        <v>172144500</v>
       </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="B504" s="2">
-        <v>0</v>
+        <v>36180000</v>
       </c>
       <c r="C504" s="2">
-        <v>0</v>
+        <v>36180000</v>
       </c>
       <c r="D504" s="2">
-        <v>0</v>
+        <v>1720000</v>
       </c>
       <c r="E504" s="2">
-        <v>60889862</v>
+        <v>5342537</v>
       </c>
       <c r="F504" s="2">
-        <v>60889862</v>
+        <v>7062537</v>
       </c>
       <c r="G504" s="2">
-        <v>-60889862</v>
+        <v>29117463</v>
       </c>
       <c r="H504" s="2">
         <v>0</v>
@@ -14857,25 +13682,25 @@
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B505" s="2">
-        <v>0</v>
+        <v>61741000</v>
       </c>
       <c r="C505" s="2">
-        <v>0</v>
+        <v>61741000</v>
       </c>
       <c r="D505" s="2">
-        <v>0</v>
+        <v>38255444</v>
       </c>
       <c r="E505" s="2">
-        <v>51753310</v>
+        <v>0</v>
       </c>
       <c r="F505" s="2">
-        <v>51753310</v>
+        <v>38255444</v>
       </c>
       <c r="G505" s="2">
-        <v>-51753310</v>
+        <v>23485556</v>
       </c>
       <c r="H505" s="2">
         <v>0</v>
@@ -14883,25 +13708,25 @@
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="B506" s="2">
-        <v>12164281897</v>
+        <v>0</v>
       </c>
       <c r="C506" s="2">
-        <v>12164281897</v>
+        <v>0</v>
       </c>
       <c r="D506" s="2">
         <v>0</v>
       </c>
       <c r="E506" s="2">
-        <v>1814036400</v>
+        <v>84819308</v>
       </c>
       <c r="F506" s="2">
-        <v>1814036400</v>
+        <v>84819308</v>
       </c>
       <c r="G506" s="2">
-        <v>10350245497</v>
+        <v>-84819308</v>
       </c>
       <c r="H506" s="2">
         <v>0</v>
@@ -14909,25 +13734,25 @@
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B507" s="2">
-        <v>111508199</v>
+        <v>0</v>
       </c>
       <c r="C507" s="2">
-        <v>111508199</v>
+        <v>0</v>
       </c>
       <c r="D507" s="2">
         <v>0</v>
       </c>
       <c r="E507" s="2">
-        <v>18414338</v>
+        <v>60889862</v>
       </c>
       <c r="F507" s="2">
-        <v>18414338</v>
+        <v>60889862</v>
       </c>
       <c r="G507" s="2">
-        <v>93093861</v>
+        <v>-60889862</v>
       </c>
       <c r="H507" s="2">
         <v>0</v>
@@ -14935,25 +13760,25 @@
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B508" s="2">
-        <v>10801404197</v>
+        <v>0</v>
       </c>
       <c r="C508" s="2">
-        <v>10801404197</v>
+        <v>0</v>
       </c>
       <c r="D508" s="2">
         <v>0</v>
       </c>
       <c r="E508" s="2">
-        <v>1944632685</v>
+        <v>51753310</v>
       </c>
       <c r="F508" s="2">
-        <v>1944632685</v>
+        <v>51753310</v>
       </c>
       <c r="G508" s="2">
-        <v>8856771512</v>
+        <v>-51753310</v>
       </c>
       <c r="H508" s="2">
         <v>0</v>
@@ -14961,25 +13786,25 @@
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B509" s="2">
-        <v>68210418</v>
+        <v>12164281897</v>
       </c>
       <c r="C509" s="2">
-        <v>68210418</v>
+        <v>12164281897</v>
       </c>
       <c r="D509" s="2">
         <v>0</v>
       </c>
       <c r="E509" s="2">
-        <v>0</v>
+        <v>1814043899</v>
       </c>
       <c r="F509" s="2">
-        <v>0</v>
+        <v>1814043899</v>
       </c>
       <c r="G509" s="2">
-        <v>68210418</v>
+        <v>10350237998</v>
       </c>
       <c r="H509" s="2">
         <v>0</v>
@@ -14987,25 +13812,25 @@
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B510" s="2">
-        <v>1452685239</v>
+        <v>111508199</v>
       </c>
       <c r="C510" s="2">
-        <v>1452685239</v>
+        <v>111508199</v>
       </c>
       <c r="D510" s="2">
         <v>0</v>
       </c>
       <c r="E510" s="2">
-        <v>135898412</v>
+        <v>18414338</v>
       </c>
       <c r="F510" s="2">
-        <v>135898412</v>
+        <v>18414338</v>
       </c>
       <c r="G510" s="2">
-        <v>1316786827</v>
+        <v>93093861</v>
       </c>
       <c r="H510" s="2">
         <v>0</v>
@@ -15013,25 +13838,25 @@
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B511" s="2">
-        <v>35165398</v>
+        <v>10801404197</v>
       </c>
       <c r="C511" s="2">
-        <v>35165398</v>
+        <v>10801404197</v>
       </c>
       <c r="D511" s="2">
         <v>0</v>
       </c>
       <c r="E511" s="2">
-        <v>3651448</v>
+        <v>1944632685</v>
       </c>
       <c r="F511" s="2">
-        <v>3651448</v>
+        <v>1944632685</v>
       </c>
       <c r="G511" s="2">
-        <v>31513950</v>
+        <v>8856771512</v>
       </c>
       <c r="H511" s="2">
         <v>0</v>
@@ -15039,25 +13864,25 @@
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B512" s="2">
-        <v>1698748501</v>
+        <v>68210418</v>
       </c>
       <c r="C512" s="2">
-        <v>1698748501</v>
+        <v>68210418</v>
       </c>
       <c r="D512" s="2">
         <v>0</v>
       </c>
       <c r="E512" s="2">
-        <v>259412564</v>
+        <v>0</v>
       </c>
       <c r="F512" s="2">
-        <v>259412564</v>
+        <v>0</v>
       </c>
       <c r="G512" s="2">
-        <v>1439335937</v>
+        <v>68210418</v>
       </c>
       <c r="H512" s="2">
         <v>0</v>
@@ -15065,25 +13890,25 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B513" s="2">
-        <v>3850588</v>
+        <v>1452685239</v>
       </c>
       <c r="C513" s="2">
-        <v>3850588</v>
+        <v>1452685239</v>
       </c>
       <c r="D513" s="2">
         <v>0</v>
       </c>
       <c r="E513" s="2">
-        <v>0</v>
+        <v>135898412</v>
       </c>
       <c r="F513" s="2">
-        <v>0</v>
+        <v>135898412</v>
       </c>
       <c r="G513" s="2">
-        <v>3850588</v>
+        <v>1316786827</v>
       </c>
       <c r="H513" s="2">
         <v>0</v>
@@ -15091,25 +13916,25 @@
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B514" s="2">
-        <v>0</v>
+        <v>35165398</v>
       </c>
       <c r="C514" s="2">
-        <v>0</v>
+        <v>35165398</v>
       </c>
       <c r="D514" s="2">
         <v>0</v>
       </c>
       <c r="E514" s="2">
-        <v>137977076</v>
+        <v>3651448</v>
       </c>
       <c r="F514" s="2">
-        <v>137977076</v>
+        <v>3651448</v>
       </c>
       <c r="G514" s="2">
-        <v>-137977076</v>
+        <v>31513950</v>
       </c>
       <c r="H514" s="2">
         <v>0</v>
@@ -15117,51 +13942,51 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="B515" s="2">
-        <v>61498532437</v>
+        <v>1698748501</v>
       </c>
       <c r="C515" s="2">
-        <v>60647750187</v>
+        <v>1698748501</v>
       </c>
       <c r="D515" s="2">
-        <v>13437132792</v>
+        <v>0</v>
       </c>
       <c r="E515" s="2">
-        <v>5853406531</v>
+        <v>259412564</v>
       </c>
       <c r="F515" s="2">
-        <v>19290539323</v>
+        <v>259412564</v>
       </c>
       <c r="G515" s="2">
-        <v>41357210864</v>
+        <v>1439335937</v>
       </c>
       <c r="H515" s="2">
-        <v>850782250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B516" s="2">
-        <v>5574698000</v>
+        <v>3850588</v>
       </c>
       <c r="C516" s="2">
-        <v>5574698000</v>
+        <v>3850588</v>
       </c>
       <c r="D516" s="2">
-        <v>5471087865</v>
+        <v>0</v>
       </c>
       <c r="E516" s="2">
         <v>0</v>
       </c>
       <c r="F516" s="2">
-        <v>5471087865</v>
+        <v>0</v>
       </c>
       <c r="G516" s="2">
-        <v>103610135</v>
+        <v>3850588</v>
       </c>
       <c r="H516" s="2">
         <v>0</v>
@@ -15169,25 +13994,25 @@
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B517" s="2">
-        <v>1521000000</v>
+        <v>0</v>
       </c>
       <c r="C517" s="2">
-        <v>1521000000</v>
+        <v>0</v>
       </c>
       <c r="D517" s="2">
-        <v>1467022165</v>
+        <v>0</v>
       </c>
       <c r="E517" s="2">
-        <v>3328300</v>
+        <v>137977076</v>
       </c>
       <c r="F517" s="2">
-        <v>1470350465</v>
+        <v>137977076</v>
       </c>
       <c r="G517" s="2">
-        <v>50649535</v>
+        <v>-137977076</v>
       </c>
       <c r="H517" s="2">
         <v>0</v>
@@ -15195,51 +14020,51 @@
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="B518" s="2">
-        <v>1694175000</v>
+        <v>61498532437</v>
       </c>
       <c r="C518" s="2">
-        <v>1694175000</v>
+        <v>60647750187</v>
       </c>
       <c r="D518" s="2">
-        <v>1694174158</v>
+        <v>13429467792</v>
       </c>
       <c r="E518" s="2">
-        <v>0</v>
+        <v>5853795280</v>
       </c>
       <c r="F518" s="2">
-        <v>1694174158</v>
+        <v>19283263072</v>
       </c>
       <c r="G518" s="2">
-        <v>842</v>
+        <v>41364487115</v>
       </c>
       <c r="H518" s="2">
-        <v>0</v>
+        <v>850782250</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="B519" s="2">
-        <v>2639000000</v>
+        <v>5574698000</v>
       </c>
       <c r="C519" s="2">
-        <v>2639000000</v>
+        <v>5574698000</v>
       </c>
       <c r="D519" s="2">
-        <v>546436863</v>
+        <v>5471087865</v>
       </c>
       <c r="E519" s="2">
-        <v>129199870</v>
+        <v>0</v>
       </c>
       <c r="F519" s="2">
-        <v>675636733</v>
+        <v>5471087865</v>
       </c>
       <c r="G519" s="2">
-        <v>1963363267</v>
+        <v>103610135</v>
       </c>
       <c r="H519" s="2">
         <v>0</v>
@@ -15247,25 +14072,25 @@
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B520" s="2">
-        <v>150000000</v>
+        <v>1521000000</v>
       </c>
       <c r="C520" s="2">
-        <v>150000000</v>
+        <v>1521000000</v>
       </c>
       <c r="D520" s="2">
-        <v>9000000</v>
+        <v>1467022165</v>
       </c>
       <c r="E520" s="2">
-        <v>0</v>
+        <v>3328300</v>
       </c>
       <c r="F520" s="2">
-        <v>9000000</v>
+        <v>1470350465</v>
       </c>
       <c r="G520" s="2">
-        <v>141000000</v>
+        <v>50649535</v>
       </c>
       <c r="H520" s="2">
         <v>0</v>
@@ -15273,25 +14098,25 @@
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B521" s="2">
-        <v>2721193000</v>
+        <v>1694175000</v>
       </c>
       <c r="C521" s="2">
-        <v>2721193000</v>
+        <v>1694175000</v>
       </c>
       <c r="D521" s="2">
-        <v>2263795563</v>
+        <v>1694174158</v>
       </c>
       <c r="E521" s="2">
         <v>0</v>
       </c>
       <c r="F521" s="2">
-        <v>2263795563</v>
+        <v>1694174158</v>
       </c>
       <c r="G521" s="2">
-        <v>457397437</v>
+        <v>842</v>
       </c>
       <c r="H521" s="2">
         <v>0</v>
@@ -15299,25 +14124,25 @@
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B522" s="2">
-        <v>9794675000</v>
+        <v>2639000000</v>
       </c>
       <c r="C522" s="2">
-        <v>9794675000</v>
+        <v>2639000000</v>
       </c>
       <c r="D522" s="2">
-        <v>8772973347</v>
+        <v>512463123</v>
       </c>
       <c r="E522" s="2">
-        <v>3607897</v>
+        <v>163173610</v>
       </c>
       <c r="F522" s="2">
-        <v>8776581244</v>
+        <v>675636733</v>
       </c>
       <c r="G522" s="2">
-        <v>1018093756</v>
+        <v>1963363267</v>
       </c>
       <c r="H522" s="2">
         <v>0</v>
@@ -15325,25 +14150,25 @@
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B523" s="2">
-        <v>2114698000</v>
+        <v>150000000</v>
       </c>
       <c r="C523" s="2">
-        <v>2114698000</v>
+        <v>150000000</v>
       </c>
       <c r="D523" s="2">
-        <v>0</v>
+        <v>9000000</v>
       </c>
       <c r="E523" s="2">
-        <v>162049240</v>
+        <v>0</v>
       </c>
       <c r="F523" s="2">
-        <v>162049240</v>
+        <v>9000000</v>
       </c>
       <c r="G523" s="2">
-        <v>1952648760</v>
+        <v>141000000</v>
       </c>
       <c r="H523" s="2">
         <v>0</v>
@@ -15351,25 +14176,25 @@
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B524" s="2">
-        <v>1450000000</v>
+        <v>2721193000</v>
       </c>
       <c r="C524" s="2">
-        <v>1450000000</v>
+        <v>2721193000</v>
       </c>
       <c r="D524" s="2">
-        <v>0</v>
+        <v>2263795563</v>
       </c>
       <c r="E524" s="2">
         <v>0</v>
       </c>
       <c r="F524" s="2">
-        <v>0</v>
+        <v>2263795563</v>
       </c>
       <c r="G524" s="2">
-        <v>1450000000</v>
+        <v>457397437</v>
       </c>
       <c r="H524" s="2">
         <v>0</v>
@@ -15377,25 +14202,25 @@
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B525" s="2">
-        <v>0</v>
+        <v>9794675000</v>
       </c>
       <c r="C525" s="2">
-        <v>0</v>
+        <v>9794675000</v>
       </c>
       <c r="D525" s="2">
-        <v>0</v>
+        <v>8772973347</v>
       </c>
       <c r="E525" s="2">
-        <v>0</v>
+        <v>3607897</v>
       </c>
       <c r="F525" s="2">
-        <v>0</v>
+        <v>8776581244</v>
       </c>
       <c r="G525" s="2">
-        <v>0</v>
+        <v>1018093756</v>
       </c>
       <c r="H525" s="2">
         <v>0</v>
@@ -15403,25 +14228,25 @@
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="B526" s="2">
-        <v>915811000</v>
+        <v>2114698000</v>
       </c>
       <c r="C526" s="2">
-        <v>915811000</v>
+        <v>2114698000</v>
       </c>
       <c r="D526" s="2">
-        <v>715028125</v>
+        <v>0</v>
       </c>
       <c r="E526" s="2">
-        <v>0</v>
+        <v>162049240</v>
       </c>
       <c r="F526" s="2">
-        <v>715028125</v>
+        <v>162049240</v>
       </c>
       <c r="G526" s="2">
-        <v>200782875</v>
+        <v>1952648760</v>
       </c>
       <c r="H526" s="2">
         <v>0</v>
@@ -15429,25 +14254,25 @@
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B527" s="2">
-        <v>1750000000</v>
+        <v>1450000000</v>
       </c>
       <c r="C527" s="2">
-        <v>1750000000</v>
+        <v>1450000000</v>
       </c>
       <c r="D527" s="2">
-        <v>957373034</v>
+        <v>0</v>
       </c>
       <c r="E527" s="2">
         <v>0</v>
       </c>
       <c r="F527" s="2">
-        <v>957373034</v>
+        <v>0</v>
       </c>
       <c r="G527" s="2">
-        <v>792626966</v>
+        <v>1450000000</v>
       </c>
       <c r="H527" s="2">
         <v>0</v>
@@ -15455,25 +14280,25 @@
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B528" s="2">
-        <v>300000000</v>
+        <v>0</v>
       </c>
       <c r="C528" s="2">
-        <v>300000000</v>
+        <v>0</v>
       </c>
       <c r="D528" s="2">
-        <v>4951687</v>
+        <v>0</v>
       </c>
       <c r="E528" s="2">
         <v>0</v>
       </c>
       <c r="F528" s="2">
-        <v>4951687</v>
+        <v>0</v>
       </c>
       <c r="G528" s="2">
-        <v>295048313</v>
+        <v>0</v>
       </c>
       <c r="H528" s="2">
         <v>0</v>
@@ -15481,51 +14306,51 @@
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B529" s="2">
-        <v>645000000</v>
+        <v>915811000</v>
       </c>
       <c r="C529" s="2">
-        <v>483750000</v>
+        <v>915811000</v>
       </c>
       <c r="D529" s="2">
-        <v>114815000</v>
+        <v>715028125</v>
       </c>
       <c r="E529" s="2">
-        <v>68355000</v>
+        <v>0</v>
       </c>
       <c r="F529" s="2">
-        <v>183170000</v>
+        <v>715028125</v>
       </c>
       <c r="G529" s="2">
-        <v>300580000</v>
+        <v>200782875</v>
       </c>
       <c r="H529" s="2">
-        <v>161250000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="B530" s="2">
-        <v>285978663</v>
+        <v>1750000000</v>
       </c>
       <c r="C530" s="2">
-        <v>285978663</v>
+        <v>1750000000</v>
       </c>
       <c r="D530" s="2">
-        <v>23285000</v>
+        <v>957373034</v>
       </c>
       <c r="E530" s="2">
-        <v>32200000</v>
+        <v>0</v>
       </c>
       <c r="F530" s="2">
-        <v>55485000</v>
+        <v>957373034</v>
       </c>
       <c r="G530" s="2">
-        <v>230493663</v>
+        <v>792626966</v>
       </c>
       <c r="H530" s="2">
         <v>0</v>
@@ -15533,25 +14358,25 @@
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B531" s="2">
-        <v>1539315000</v>
+        <v>300000000</v>
       </c>
       <c r="C531" s="2">
-        <v>1539315000</v>
+        <v>300000000</v>
       </c>
       <c r="D531" s="2">
-        <v>3649654</v>
+        <v>4951687</v>
       </c>
       <c r="E531" s="2">
-        <v>230704071</v>
+        <v>0</v>
       </c>
       <c r="F531" s="2">
-        <v>234353725</v>
+        <v>4951687</v>
       </c>
       <c r="G531" s="2">
-        <v>1304961275</v>
+        <v>295048313</v>
       </c>
       <c r="H531" s="2">
         <v>0</v>
@@ -15559,77 +14384,77 @@
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B532" s="2">
-        <v>550000000</v>
+        <v>645000000</v>
       </c>
       <c r="C532" s="2">
-        <v>412500000</v>
+        <v>483750000</v>
       </c>
       <c r="D532" s="2">
-        <v>6056400</v>
+        <v>114815000</v>
       </c>
       <c r="E532" s="2">
-        <v>12632800</v>
+        <v>68355000</v>
       </c>
       <c r="F532" s="2">
-        <v>18689200</v>
+        <v>183170000</v>
       </c>
       <c r="G532" s="2">
-        <v>393810800</v>
+        <v>300580000</v>
       </c>
       <c r="H532" s="2">
-        <v>137500000</v>
+        <v>161250000</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="B533" s="2">
-        <v>710500000</v>
+        <v>285978663</v>
       </c>
       <c r="C533" s="2">
-        <v>532875000</v>
+        <v>285978663</v>
       </c>
       <c r="D533" s="2">
-        <v>17800620</v>
+        <v>23285000</v>
       </c>
       <c r="E533" s="2">
-        <v>49382229</v>
+        <v>32200000</v>
       </c>
       <c r="F533" s="2">
-        <v>67182849</v>
+        <v>55485000</v>
       </c>
       <c r="G533" s="2">
-        <v>465692151</v>
+        <v>230493663</v>
       </c>
       <c r="H533" s="2">
-        <v>177625000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B534" s="2">
-        <v>95700000</v>
+        <v>1539315000</v>
       </c>
       <c r="C534" s="2">
-        <v>95700000</v>
+        <v>1539315000</v>
       </c>
       <c r="D534" s="2">
-        <v>0</v>
+        <v>3649654</v>
       </c>
       <c r="E534" s="2">
-        <v>13500000</v>
+        <v>230704071</v>
       </c>
       <c r="F534" s="2">
-        <v>13500000</v>
+        <v>234353725</v>
       </c>
       <c r="G534" s="2">
-        <v>82200000</v>
+        <v>1304961275</v>
       </c>
       <c r="H534" s="2">
         <v>0</v>
@@ -15637,77 +14462,77 @@
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B535" s="2">
-        <v>527665000</v>
+        <v>550000000</v>
       </c>
       <c r="C535" s="2">
-        <v>395748750</v>
+        <v>412500000</v>
       </c>
       <c r="D535" s="2">
-        <v>0</v>
+        <v>6056400</v>
       </c>
       <c r="E535" s="2">
-        <v>0</v>
+        <v>12632800</v>
       </c>
       <c r="F535" s="2">
-        <v>0</v>
+        <v>18689200</v>
       </c>
       <c r="G535" s="2">
-        <v>395748750</v>
+        <v>393810800</v>
       </c>
       <c r="H535" s="2">
-        <v>131916250</v>
+        <v>137500000</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B536" s="2">
-        <v>449070000</v>
+        <v>710500000</v>
       </c>
       <c r="C536" s="2">
-        <v>336802500</v>
+        <v>532875000</v>
       </c>
       <c r="D536" s="2">
-        <v>17298750</v>
+        <v>17800620</v>
       </c>
       <c r="E536" s="2">
-        <v>65252500</v>
+        <v>49382229</v>
       </c>
       <c r="F536" s="2">
-        <v>82551250</v>
+        <v>67182849</v>
       </c>
       <c r="G536" s="2">
-        <v>254251250</v>
+        <v>465692151</v>
       </c>
       <c r="H536" s="2">
-        <v>112267500</v>
+        <v>177625000</v>
       </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B537" s="2">
-        <v>68288000</v>
+        <v>95700000</v>
       </c>
       <c r="C537" s="2">
-        <v>68288000</v>
+        <v>95700000</v>
       </c>
       <c r="D537" s="2">
         <v>0</v>
       </c>
       <c r="E537" s="2">
-        <v>0</v>
+        <v>13500000</v>
       </c>
       <c r="F537" s="2">
-        <v>0</v>
+        <v>13500000</v>
       </c>
       <c r="G537" s="2">
-        <v>68288000</v>
+        <v>82200000</v>
       </c>
       <c r="H537" s="2">
         <v>0</v>
@@ -15715,77 +14540,77 @@
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="B538" s="2">
-        <v>0</v>
+        <v>527665000</v>
       </c>
       <c r="C538" s="2">
-        <v>0</v>
+        <v>395748750</v>
       </c>
       <c r="D538" s="2">
         <v>0</v>
       </c>
       <c r="E538" s="2">
-        <v>5592872</v>
+        <v>0</v>
       </c>
       <c r="F538" s="2">
-        <v>5592872</v>
+        <v>0</v>
       </c>
       <c r="G538" s="2">
-        <v>-5592872</v>
+        <v>395748750</v>
       </c>
       <c r="H538" s="2">
-        <v>0</v>
+        <v>131916250</v>
       </c>
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B539" s="2">
-        <v>10688916866</v>
+        <v>449070000</v>
       </c>
       <c r="C539" s="2">
-        <v>10688916866</v>
+        <v>336802500</v>
       </c>
       <c r="D539" s="2">
         <v>0</v>
       </c>
       <c r="E539" s="2">
-        <v>1592659004</v>
+        <v>82551250</v>
       </c>
       <c r="F539" s="2">
-        <v>1592659004</v>
+        <v>82551250</v>
       </c>
       <c r="G539" s="2">
-        <v>9096257862</v>
+        <v>254251250</v>
       </c>
       <c r="H539" s="2">
-        <v>0</v>
+        <v>112267500</v>
       </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B540" s="2">
-        <v>106116051</v>
+        <v>68288000</v>
       </c>
       <c r="C540" s="2">
-        <v>106116051</v>
+        <v>68288000</v>
       </c>
       <c r="D540" s="2">
         <v>0</v>
       </c>
       <c r="E540" s="2">
-        <v>18102841</v>
+        <v>0</v>
       </c>
       <c r="F540" s="2">
-        <v>18102841</v>
+        <v>0</v>
       </c>
       <c r="G540" s="2">
-        <v>88013210</v>
+        <v>68288000</v>
       </c>
       <c r="H540" s="2">
         <v>0</v>
@@ -15793,25 +14618,25 @@
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="B541" s="2">
-        <v>9218326343</v>
+        <v>0</v>
       </c>
       <c r="C541" s="2">
-        <v>9218326343</v>
+        <v>0</v>
       </c>
       <c r="D541" s="2">
         <v>0</v>
       </c>
       <c r="E541" s="2">
-        <v>1626624682</v>
+        <v>5592872</v>
       </c>
       <c r="F541" s="2">
-        <v>1626624682</v>
+        <v>5592872</v>
       </c>
       <c r="G541" s="2">
-        <v>7591701661</v>
+        <v>-5592872</v>
       </c>
       <c r="H541" s="2">
         <v>0</v>
@@ -15819,25 +14644,25 @@
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B542" s="2">
-        <v>58858990</v>
+        <v>10688916866</v>
       </c>
       <c r="C542" s="2">
-        <v>58858990</v>
+        <v>10688916866</v>
       </c>
       <c r="D542" s="2">
         <v>0</v>
       </c>
       <c r="E542" s="2">
-        <v>0</v>
+        <v>1592659004</v>
       </c>
       <c r="F542" s="2">
-        <v>0</v>
+        <v>1592659004</v>
       </c>
       <c r="G542" s="2">
-        <v>58858990</v>
+        <v>9096257862</v>
       </c>
       <c r="H542" s="2">
         <v>0</v>
@@ -15845,25 +14670,25 @@
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B543" s="2">
-        <v>1422805953</v>
+        <v>106116051</v>
       </c>
       <c r="C543" s="2">
-        <v>1422805953</v>
+        <v>106116051</v>
       </c>
       <c r="D543" s="2">
         <v>0</v>
       </c>
       <c r="E543" s="2">
-        <v>179659734</v>
+        <v>18102841</v>
       </c>
       <c r="F543" s="2">
-        <v>179659734</v>
+        <v>18102841</v>
       </c>
       <c r="G543" s="2">
-        <v>1243146219</v>
+        <v>88013210</v>
       </c>
       <c r="H543" s="2">
         <v>0</v>
@@ -15871,25 +14696,25 @@
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B544" s="2">
-        <v>13916758</v>
+        <v>9218326343</v>
       </c>
       <c r="C544" s="2">
-        <v>13916758</v>
+        <v>9218326343</v>
       </c>
       <c r="D544" s="2">
         <v>0</v>
       </c>
       <c r="E544" s="2">
-        <v>2273980</v>
+        <v>1626624682</v>
       </c>
       <c r="F544" s="2">
-        <v>2273980</v>
+        <v>1626624682</v>
       </c>
       <c r="G544" s="2">
-        <v>11642778</v>
+        <v>7591701661</v>
       </c>
       <c r="H544" s="2">
         <v>0</v>
@@ -15897,25 +14722,25 @@
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B545" s="2">
-        <v>1559682761</v>
+        <v>58858990</v>
       </c>
       <c r="C545" s="2">
-        <v>1559682761</v>
+        <v>58858990</v>
       </c>
       <c r="D545" s="2">
         <v>0</v>
       </c>
       <c r="E545" s="2">
-        <v>300982812</v>
+        <v>0</v>
       </c>
       <c r="F545" s="2">
-        <v>300982812</v>
+        <v>0</v>
       </c>
       <c r="G545" s="2">
-        <v>1258699949</v>
+        <v>58858990</v>
       </c>
       <c r="H545" s="2">
         <v>0</v>
@@ -15923,25 +14748,25 @@
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B546" s="2">
-        <v>3850588</v>
+        <v>1422805953</v>
       </c>
       <c r="C546" s="2">
-        <v>3850588</v>
+        <v>1422805953</v>
       </c>
       <c r="D546" s="2">
         <v>0</v>
       </c>
       <c r="E546" s="2">
-        <v>0</v>
+        <v>179659734</v>
       </c>
       <c r="F546" s="2">
-        <v>0</v>
+        <v>179659734</v>
       </c>
       <c r="G546" s="2">
-        <v>3850588</v>
+        <v>1243146219</v>
       </c>
       <c r="H546" s="2">
         <v>0</v>
@@ -15949,1517 +14774,109 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="B547" s="2">
+        <v>13916758</v>
+      </c>
+      <c r="C547" s="2">
+        <v>13916758</v>
+      </c>
+      <c r="D547" s="2">
+        <v>0</v>
+      </c>
+      <c r="E547" s="2">
+        <v>2273980</v>
+      </c>
+      <c r="F547" s="2">
+        <v>2273980</v>
+      </c>
+      <c r="G547" s="2">
+        <v>11642778</v>
+      </c>
+      <c r="H547" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A548" t="s">
+        <v>38</v>
+      </c>
+      <c r="B548" s="2">
+        <v>1559682761</v>
+      </c>
+      <c r="C548" s="2">
+        <v>1559682761</v>
+      </c>
+      <c r="D548" s="2">
+        <v>0</v>
+      </c>
+      <c r="E548" s="2">
+        <v>300982812</v>
+      </c>
+      <c r="F548" s="2">
+        <v>300982812</v>
+      </c>
+      <c r="G548" s="2">
+        <v>1258699949</v>
+      </c>
+      <c r="H548" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A549" t="s">
+        <v>39</v>
+      </c>
+      <c r="B549" s="2">
+        <v>3850588</v>
+      </c>
+      <c r="C549" s="2">
+        <v>3850588</v>
+      </c>
+      <c r="D549" s="2">
+        <v>0</v>
+      </c>
+      <c r="E549" s="2">
+        <v>0</v>
+      </c>
+      <c r="F549" s="2">
+        <v>0</v>
+      </c>
+      <c r="G549" s="2">
+        <v>3850588</v>
+      </c>
+      <c r="H549" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A550" t="s">
+        <v>125</v>
+      </c>
+      <c r="B550" s="2">
         <v>58569240973</v>
       </c>
-      <c r="C547" s="2">
+      <c r="C550" s="2">
         <v>57848682223</v>
       </c>
-      <c r="D547" s="2">
-        <v>22084748231</v>
-      </c>
-      <c r="E547" s="2">
-        <v>4496107832</v>
-      </c>
-      <c r="F547" s="2">
+      <c r="D550" s="2">
+        <v>22033475741</v>
+      </c>
+      <c r="E550" s="2">
+        <v>4547380322</v>
+      </c>
+      <c r="F550" s="2">
         <v>26580856063</v>
       </c>
-      <c r="G547" s="2">
+      <c r="G550" s="2">
         <v>31267826160</v>
       </c>
-      <c r="H547" s="2">
+      <c r="H550" s="2">
         <v>720558750</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74037102-CAE5-4DA3-AC4F-276E222EA2EC}">
-  <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.25" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="60.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="15.265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="15.265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" hidden="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="4">
-        <v>873740000</v>
-      </c>
-      <c r="C2" s="5">
-        <f>B2</f>
-        <v>873740000</v>
-      </c>
-      <c r="D2" s="5">
-        <f>C2/2</f>
-        <v>436870000</v>
-      </c>
-      <c r="E2" s="4">
-        <f>IF(B2="","",G2-F2)</f>
-        <v>404360000</v>
-      </c>
-      <c r="F2" s="5">
-        <v>35605052</v>
-      </c>
-      <c r="G2" s="5">
-        <v>439965052</v>
-      </c>
-      <c r="H2" s="4">
-        <f>IF(B2="","",D2-G2)</f>
-        <v>-3095052</v>
-      </c>
-      <c r="I2" s="4">
-        <f>IF(B2="","",C2-D2)</f>
-        <v>436870000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5">
-        <f t="shared" ref="C3:C27" si="0">B3</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="5">
-        <f t="shared" ref="D3:D27" si="1">C3/2</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="4" t="str">
-        <f t="shared" ref="E3:E53" si="2">IF(B3="","",G3-F3)</f>
-        <v/>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="4" t="str">
-        <f t="shared" ref="H3:H53" si="3">IF(B3="","",D3-G3)</f>
-        <v/>
-      </c>
-      <c r="I3" s="4" t="str">
-        <f t="shared" ref="I3:I53" si="4">IF(B3="","",C3-D3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E4" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I4" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D5" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I5" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I6" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I7" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I8" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D9" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E9" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I9" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D10" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E10" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I10" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D11" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I11" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D12" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I12" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D13" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I13" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D14" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D15" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I15" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D16" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D17" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E17" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I17" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D18" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E18" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B19" s="4">
-        <v>474786000</v>
-      </c>
-      <c r="C19" s="5">
-        <f t="shared" si="0"/>
-        <v>474786000</v>
-      </c>
-      <c r="D19" s="5">
-        <f t="shared" si="1"/>
-        <v>237393000</v>
-      </c>
-      <c r="E19" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="4">
-        <f t="shared" si="3"/>
-        <v>237393000</v>
-      </c>
-      <c r="I19" s="4">
-        <f t="shared" si="4"/>
-        <v>237393000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B20" s="4">
-        <v>208425000</v>
-      </c>
-      <c r="C20" s="5">
-        <f t="shared" si="0"/>
-        <v>208425000</v>
-      </c>
-      <c r="D20" s="5">
-        <f t="shared" si="1"/>
-        <v>104212500</v>
-      </c>
-      <c r="E20" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="4">
-        <f t="shared" si="3"/>
-        <v>104212500</v>
-      </c>
-      <c r="I20" s="4">
-        <f t="shared" si="4"/>
-        <v>104212500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="4">
-        <v>20000000</v>
-      </c>
-      <c r="C21" s="5">
-        <f>B21</f>
-        <v>20000000</v>
-      </c>
-      <c r="D21" s="5">
-        <v>13970000</v>
-      </c>
-      <c r="E21" s="4">
-        <f t="shared" si="2"/>
-        <v>13970000</v>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5">
-        <v>13970000</v>
-      </c>
-      <c r="H21" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="4">
-        <f t="shared" si="4"/>
-        <v>6030000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>118</v>
-      </c>
-      <c r="B22" s="4">
-        <v>220000000</v>
-      </c>
-      <c r="C22" s="5">
-        <f t="shared" si="0"/>
-        <v>220000000</v>
-      </c>
-      <c r="D22" s="5">
-        <f t="shared" si="1"/>
-        <v>110000000</v>
-      </c>
-      <c r="E22" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="5">
-        <v>29896778</v>
-      </c>
-      <c r="G22" s="5">
-        <v>29896778</v>
-      </c>
-      <c r="H22" s="4">
-        <f t="shared" si="3"/>
-        <v>80103222</v>
-      </c>
-      <c r="I22" s="4">
-        <f t="shared" si="4"/>
-        <v>110000000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>119</v>
-      </c>
-      <c r="B23" s="4">
-        <v>75000000</v>
-      </c>
-      <c r="C23" s="5">
-        <f t="shared" si="0"/>
-        <v>75000000</v>
-      </c>
-      <c r="D23" s="5">
-        <f t="shared" si="1"/>
-        <v>37500000</v>
-      </c>
-      <c r="E23" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="4">
-        <f t="shared" si="3"/>
-        <v>37500000</v>
-      </c>
-      <c r="I23" s="4">
-        <f t="shared" si="4"/>
-        <v>37500000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D24" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E24" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D25" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E25" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I25" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="4">
-        <v>60000000</v>
-      </c>
-      <c r="C26" s="5">
-        <f t="shared" si="0"/>
-        <v>60000000</v>
-      </c>
-      <c r="D26" s="5">
-        <f t="shared" si="1"/>
-        <v>30000000</v>
-      </c>
-      <c r="E26" s="4">
-        <f t="shared" si="2"/>
-        <v>9000000</v>
-      </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5">
-        <v>9000000</v>
-      </c>
-      <c r="H26" s="4">
-        <f t="shared" si="3"/>
-        <v>21000000</v>
-      </c>
-      <c r="I26" s="4">
-        <f t="shared" si="4"/>
-        <v>30000000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>123</v>
-      </c>
-      <c r="B27" s="4">
-        <v>45150000</v>
-      </c>
-      <c r="C27" s="5">
-        <f t="shared" si="0"/>
-        <v>45150000</v>
-      </c>
-      <c r="D27" s="5">
-        <f t="shared" si="1"/>
-        <v>22575000</v>
-      </c>
-      <c r="E27" s="4">
-        <f t="shared" si="2"/>
-        <v>6423200</v>
-      </c>
-      <c r="F27" s="5">
-        <v>6119400</v>
-      </c>
-      <c r="G27" s="5">
-        <v>12542600</v>
-      </c>
-      <c r="H27" s="4">
-        <f t="shared" si="3"/>
-        <v>10032400</v>
-      </c>
-      <c r="I27" s="4">
-        <f t="shared" si="4"/>
-        <v>22575000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I29" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>126</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I31" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>128</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I33" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>130</v>
-      </c>
-      <c r="B34" s="4">
-        <v>6000000</v>
-      </c>
-      <c r="C34" s="5">
-        <f>B34</f>
-        <v>6000000</v>
-      </c>
-      <c r="D34" s="5">
-        <f>C34/4</f>
-        <v>1500000</v>
-      </c>
-      <c r="E34" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="4">
-        <f t="shared" si="3"/>
-        <v>1500000</v>
-      </c>
-      <c r="I34" s="4">
-        <f t="shared" si="4"/>
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>131</v>
-      </c>
-      <c r="B35" s="4">
-        <v>41000000</v>
-      </c>
-      <c r="C35" s="5">
-        <f t="shared" ref="C35:C40" si="5">B35</f>
-        <v>41000000</v>
-      </c>
-      <c r="D35" s="5">
-        <f t="shared" ref="D35:D40" si="6">C35/4</f>
-        <v>10250000</v>
-      </c>
-      <c r="E35" s="4">
-        <f t="shared" si="2"/>
-        <v>1997700</v>
-      </c>
-      <c r="F35" s="5">
-        <v>998400</v>
-      </c>
-      <c r="G35" s="5">
-        <v>2996100</v>
-      </c>
-      <c r="H35" s="4">
-        <f t="shared" si="3"/>
-        <v>7253900</v>
-      </c>
-      <c r="I35" s="4">
-        <f t="shared" si="4"/>
-        <v>30750000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>132</v>
-      </c>
-      <c r="B36" s="4">
-        <v>12000000</v>
-      </c>
-      <c r="C36" s="5">
-        <f t="shared" si="5"/>
-        <v>12000000</v>
-      </c>
-      <c r="D36" s="5">
-        <f t="shared" si="6"/>
-        <v>3000000</v>
-      </c>
-      <c r="E36" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="4">
-        <f t="shared" si="3"/>
-        <v>3000000</v>
-      </c>
-      <c r="I36" s="4">
-        <f t="shared" si="4"/>
-        <v>9000000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>133</v>
-      </c>
-      <c r="B37" s="4">
-        <v>171000000</v>
-      </c>
-      <c r="C37" s="5">
-        <f t="shared" si="5"/>
-        <v>171000000</v>
-      </c>
-      <c r="D37" s="5">
-        <f t="shared" si="6"/>
-        <v>42750000</v>
-      </c>
-      <c r="E37" s="4">
-        <f t="shared" si="2"/>
-        <v>5880000</v>
-      </c>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5">
-        <v>5880000</v>
-      </c>
-      <c r="H37" s="4">
-        <f t="shared" si="3"/>
-        <v>36870000</v>
-      </c>
-      <c r="I37" s="4">
-        <f t="shared" si="4"/>
-        <v>128250000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>134</v>
-      </c>
-      <c r="B38" s="4">
-        <v>130000000</v>
-      </c>
-      <c r="C38" s="5">
-        <f t="shared" si="5"/>
-        <v>130000000</v>
-      </c>
-      <c r="D38" s="5">
-        <f t="shared" si="6"/>
-        <v>32500000</v>
-      </c>
-      <c r="E38" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="5">
-        <v>7381250</v>
-      </c>
-      <c r="G38" s="5">
-        <v>7381250</v>
-      </c>
-      <c r="H38" s="4">
-        <f t="shared" si="3"/>
-        <v>25118750</v>
-      </c>
-      <c r="I38" s="4">
-        <f t="shared" si="4"/>
-        <v>97500000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>135</v>
-      </c>
-      <c r="B39" s="4">
-        <v>6660000</v>
-      </c>
-      <c r="C39" s="5">
-        <f t="shared" si="5"/>
-        <v>6660000</v>
-      </c>
-      <c r="D39" s="5">
-        <f t="shared" si="6"/>
-        <v>1665000</v>
-      </c>
-      <c r="E39" s="4">
-        <f t="shared" si="2"/>
-        <v>1665000</v>
-      </c>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5">
-        <v>1665000</v>
-      </c>
-      <c r="H39" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="4">
-        <f t="shared" si="4"/>
-        <v>4995000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>136</v>
-      </c>
-      <c r="B40" s="4">
-        <v>6000000</v>
-      </c>
-      <c r="C40" s="5">
-        <f t="shared" si="5"/>
-        <v>6000000</v>
-      </c>
-      <c r="D40" s="5">
-        <f t="shared" si="6"/>
-        <v>1500000</v>
-      </c>
-      <c r="E40" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="4">
-        <f t="shared" si="3"/>
-        <v>1500000</v>
-      </c>
-      <c r="I40" s="4">
-        <f t="shared" si="4"/>
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>137</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I41" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>138</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I42" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>139</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I43" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>140</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I44" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>141</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I45" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>142</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I46" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>143</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I47" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>144</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I48" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>145</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I49" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>146</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I50" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>147</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I51" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>148</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I52" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>149</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I53" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="B54" s="11">
-        <f>SUM(B2:B53)</f>
-        <v>2349761000</v>
-      </c>
-      <c r="C54" s="11">
-        <f t="shared" ref="C54:I54" si="7">SUM(C2:C53)</f>
-        <v>2349761000</v>
-      </c>
-      <c r="D54" s="11">
-        <f t="shared" si="7"/>
-        <v>1085685500</v>
-      </c>
-      <c r="E54" s="11">
-        <f t="shared" si="7"/>
-        <v>443295900</v>
-      </c>
-      <c r="F54" s="11">
-        <f t="shared" si="7"/>
-        <v>80000880</v>
-      </c>
-      <c r="G54" s="11">
-        <f t="shared" si="7"/>
-        <v>523296780</v>
-      </c>
-      <c r="H54" s="11">
-        <f t="shared" si="7"/>
-        <v>562388720</v>
-      </c>
-      <c r="I54" s="11">
-        <f t="shared" si="7"/>
-        <v>1264075500</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1jAoxgEfH1v+py+BabjE1SWtZrOmBQzll5J+0nEkCC4zpdaAqkqUQlFy6oRCGkgRojK/rMDnTPHDGbW/CMwxXA==" saltValue="rHdoy6qRDxYzetfIY6x9cQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,15 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\3. Mar\KP\RKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{73E4957F-4AA3-4344-8014-DC3669CF43A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137605FE-A4EA-4011-BE5F-6CC347F38DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget 3 Juni 2024" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Budget 3 Juni 2024'!$A$1:$H$551</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="126">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -404,14 +416,11 @@
   <si>
     <t>35022000  Sintelis Divre IV Tanjungkarang</t>
   </si>
-  <si>
-    <t>FdsCtr/CmmtItem</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -895,9 +904,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1252,8 +1262,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H551"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H550"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="60.796875" bestFit="1" customWidth="1"/>
@@ -1614,16 +1624,16 @@
         <v>4308413000</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>3604880000</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>3604880000</v>
       </c>
       <c r="G14">
-        <v>4308413000</v>
+        <v>703533000</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1666,16 +1676,16 @@
         <v>1200000000</v>
       </c>
       <c r="D16">
-        <v>42457000</v>
+        <v>46821500</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>42457000</v>
+        <v>46821500</v>
       </c>
       <c r="G16">
-        <v>1157543000</v>
+        <v>1153178500</v>
       </c>
       <c r="H16">
         <v>400000000</v>
@@ -1770,16 +1780,16 @@
         <v>551510000</v>
       </c>
       <c r="D20">
-        <v>23486714</v>
+        <v>24039539</v>
       </c>
       <c r="E20">
         <v>28810450</v>
       </c>
       <c r="F20">
-        <v>52297164</v>
+        <v>52849989</v>
       </c>
       <c r="G20">
-        <v>499212836</v>
+        <v>498660011</v>
       </c>
       <c r="H20">
         <v>192500000</v>
@@ -1848,16 +1858,16 @@
         <v>600000000</v>
       </c>
       <c r="D23">
-        <v>56042500</v>
+        <v>101442500</v>
       </c>
       <c r="E23">
         <v>49833500</v>
       </c>
       <c r="F23">
-        <v>105876000</v>
+        <v>151276000</v>
       </c>
       <c r="G23">
-        <v>494124000</v>
+        <v>448724000</v>
       </c>
       <c r="H23">
         <v>200000000</v>
@@ -1877,13 +1887,13 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>223550000</v>
+        <v>227237500</v>
       </c>
       <c r="F24">
-        <v>223550000</v>
+        <v>227237500</v>
       </c>
       <c r="G24">
-        <v>1643142611</v>
+        <v>1639455111</v>
       </c>
       <c r="H24">
         <v>625000000</v>
@@ -1929,13 +1939,13 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>707255149</v>
+        <v>707446399</v>
       </c>
       <c r="F26">
-        <v>707255149</v>
+        <v>707446399</v>
       </c>
       <c r="G26">
-        <v>2749359055</v>
+        <v>2749167805</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2137,13 +2147,13 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>-10748637</v>
+        <v>-15098637</v>
       </c>
       <c r="F34">
-        <v>-10748637</v>
+        <v>-15098637</v>
       </c>
       <c r="G34">
-        <v>10748637</v>
+        <v>15098637</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2238,16 +2248,16 @@
         <v>360188138914</v>
       </c>
       <c r="D38">
-        <v>241340293336</v>
+        <v>244995490661</v>
       </c>
       <c r="E38">
-        <v>56192569755</v>
+        <v>56192098505</v>
       </c>
       <c r="F38">
-        <v>297532863091</v>
+        <v>301187589166</v>
       </c>
       <c r="G38">
-        <v>62655275823</v>
+        <v>59000549748</v>
       </c>
       <c r="H38">
         <v>2417500000</v>
@@ -2524,10 +2534,10 @@
         <v>4260000000</v>
       </c>
       <c r="D49">
-        <v>480263597</v>
+        <v>452348997</v>
       </c>
       <c r="E49">
-        <v>496793192</v>
+        <v>524707792</v>
       </c>
       <c r="F49">
         <v>977056789</v>
@@ -2576,16 +2586,16 @@
         <v>2500000000</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>491395700</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>491395700</v>
       </c>
       <c r="G51">
-        <v>2500000000</v>
+        <v>2008604300</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -2628,16 +2638,16 @@
         <v>6850000000</v>
       </c>
       <c r="D53">
-        <v>49949500</v>
+        <v>99675500</v>
       </c>
       <c r="E53">
         <v>207269960</v>
       </c>
       <c r="F53">
-        <v>257219460</v>
+        <v>306945460</v>
       </c>
       <c r="G53">
-        <v>6592780540</v>
+        <v>6543054540</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -2706,16 +2716,16 @@
         <v>500000000</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>499699800</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>499699800</v>
       </c>
       <c r="G56">
-        <v>500000000</v>
+        <v>300200</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -3278,16 +3288,16 @@
         <v>110897810191</v>
       </c>
       <c r="D78">
-        <v>21437086131</v>
+        <v>22449993031</v>
       </c>
       <c r="E78">
-        <v>12533163050</v>
+        <v>12561077650</v>
       </c>
       <c r="F78">
-        <v>33970249181</v>
+        <v>35011070681</v>
       </c>
       <c r="G78">
-        <v>76927561010</v>
+        <v>75886739510</v>
       </c>
       <c r="H78">
         <v>671501500</v>
@@ -3304,16 +3314,16 @@
         <v>4044107500</v>
       </c>
       <c r="D79">
-        <v>1518071200</v>
+        <v>2709071200</v>
       </c>
       <c r="E79">
         <v>585361000</v>
       </c>
       <c r="F79">
-        <v>2103432200</v>
+        <v>3294432200</v>
       </c>
       <c r="G79">
-        <v>1940675300</v>
+        <v>749675300</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3382,16 +3392,16 @@
         <v>30639775739</v>
       </c>
       <c r="D82">
-        <v>16588171728</v>
+        <v>16832083844</v>
       </c>
       <c r="E82">
-        <v>7766359971</v>
+        <v>7531243687</v>
       </c>
       <c r="F82">
-        <v>24354531699</v>
+        <v>24363327531</v>
       </c>
       <c r="G82">
-        <v>6285244040</v>
+        <v>6276448208</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -3668,16 +3678,16 @@
         <v>1710494400</v>
       </c>
       <c r="D93">
-        <v>364436500</v>
+        <v>569695780</v>
       </c>
       <c r="E93">
         <v>52419100</v>
       </c>
       <c r="F93">
-        <v>416855600</v>
+        <v>622114880</v>
       </c>
       <c r="G93">
-        <v>1293638800</v>
+        <v>1088379520</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -3720,16 +3730,16 @@
         <v>419475000</v>
       </c>
       <c r="D95">
-        <v>30610000</v>
+        <v>109570000</v>
       </c>
       <c r="E95">
         <v>8717850</v>
       </c>
       <c r="F95">
-        <v>39327850</v>
+        <v>118287850</v>
       </c>
       <c r="G95">
-        <v>380147150</v>
+        <v>301187150</v>
       </c>
       <c r="H95">
         <v>139825000</v>
@@ -3746,16 +3756,16 @@
         <v>255960000</v>
       </c>
       <c r="D96">
-        <v>47161500</v>
+        <v>85081500</v>
       </c>
       <c r="E96">
         <v>46900000</v>
       </c>
       <c r="F96">
-        <v>94061500</v>
+        <v>131981500</v>
       </c>
       <c r="G96">
-        <v>161898500</v>
+        <v>123978500</v>
       </c>
       <c r="H96">
         <v>85320000</v>
@@ -3798,16 +3808,16 @@
         <v>291600000</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>70800000</v>
       </c>
       <c r="E98">
         <v>0</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>70800000</v>
       </c>
       <c r="G98">
-        <v>291600000</v>
+        <v>220800000</v>
       </c>
       <c r="H98">
         <v>97200000</v>
@@ -3824,16 +3834,16 @@
         <v>15000000</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="E99">
         <v>0</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="G99">
-        <v>15000000</v>
+        <v>12600000</v>
       </c>
       <c r="H99">
         <v>5000000</v>
@@ -3850,16 +3860,16 @@
         <v>295057500</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>49693920</v>
       </c>
       <c r="E100">
-        <v>79589000</v>
+        <v>79964000</v>
       </c>
       <c r="F100">
-        <v>79589000</v>
+        <v>129657920</v>
       </c>
       <c r="G100">
-        <v>215468500</v>
+        <v>165399580</v>
       </c>
       <c r="H100">
         <v>98352500</v>
@@ -3876,16 +3886,16 @@
         <v>91080000</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>11880000</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>11880000</v>
       </c>
       <c r="G101">
-        <v>91080000</v>
+        <v>79200000</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -3983,13 +3993,13 @@
         <v>0</v>
       </c>
       <c r="E105">
-        <v>3829024628</v>
+        <v>3829043378</v>
       </c>
       <c r="F105">
-        <v>3829024628</v>
+        <v>3829043378</v>
       </c>
       <c r="G105">
-        <v>12394620225</v>
+        <v>12394601475</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -4188,16 +4198,16 @@
         <v>81718644736</v>
       </c>
       <c r="D113">
-        <v>19288629705</v>
+        <v>21180455021</v>
       </c>
       <c r="E113">
-        <v>17882709562</v>
+        <v>17647987028</v>
       </c>
       <c r="F113">
-        <v>37171339267</v>
+        <v>38828442049</v>
       </c>
       <c r="G113">
-        <v>44547305469</v>
+        <v>42890202687</v>
       </c>
       <c r="H113">
         <v>475697500</v>
@@ -4344,16 +4354,16 @@
         <v>818532000</v>
       </c>
       <c r="D119">
-        <v>277500000</v>
+        <v>287074500</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119">
-        <v>277500000</v>
+        <v>287074500</v>
       </c>
       <c r="G119">
-        <v>541032000</v>
+        <v>531457500</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -4370,16 +4380,16 @@
         <v>4824864000</v>
       </c>
       <c r="D120">
-        <v>4422334413</v>
+        <v>4469509093</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>4422334413</v>
+        <v>4469509093</v>
       </c>
       <c r="G120">
-        <v>402529587</v>
+        <v>355354907</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -4474,10 +4484,10 @@
         <v>2233168000</v>
       </c>
       <c r="D124">
-        <v>1955857840</v>
+        <v>1267539700</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>688318140</v>
       </c>
       <c r="F124">
         <v>1955857840</v>
@@ -4604,16 +4614,16 @@
         <v>118875000</v>
       </c>
       <c r="D129">
-        <v>8255000</v>
+        <v>3762500</v>
       </c>
       <c r="E129">
-        <v>7520000</v>
+        <v>15775000</v>
       </c>
       <c r="F129">
-        <v>15775000</v>
+        <v>19537500</v>
       </c>
       <c r="G129">
-        <v>103100000</v>
+        <v>99337500</v>
       </c>
       <c r="H129">
         <v>0</v>
@@ -4682,16 +4692,16 @@
         <v>265950000</v>
       </c>
       <c r="D132">
-        <v>33432500</v>
+        <v>32877500</v>
       </c>
       <c r="E132">
-        <v>46413500</v>
+        <v>46913500</v>
       </c>
       <c r="F132">
-        <v>79846000</v>
+        <v>79791000</v>
       </c>
       <c r="G132">
-        <v>186104000</v>
+        <v>186159000</v>
       </c>
       <c r="H132">
         <v>88650000</v>
@@ -5072,16 +5082,16 @@
         <v>50726099717</v>
       </c>
       <c r="D147">
-        <v>16754436741</v>
+        <v>16117820281</v>
       </c>
       <c r="E147">
-        <v>6421214806</v>
+        <v>7118287946</v>
       </c>
       <c r="F147">
-        <v>23175651547</v>
+        <v>23236108227</v>
       </c>
       <c r="G147">
-        <v>27550448170</v>
+        <v>27489991490</v>
       </c>
       <c r="H147">
         <v>411080000</v>
@@ -5124,16 +5134,16 @@
         <v>3998040540</v>
       </c>
       <c r="D149">
-        <v>865634917</v>
+        <v>858720112</v>
       </c>
       <c r="E149">
-        <v>6986400</v>
+        <v>52786400</v>
       </c>
       <c r="F149">
-        <v>872621317</v>
+        <v>911506512</v>
       </c>
       <c r="G149">
-        <v>3125419223</v>
+        <v>3086534028</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -5202,16 +5212,16 @@
         <v>870437000</v>
       </c>
       <c r="D152">
-        <v>72346470</v>
+        <v>525525845</v>
       </c>
       <c r="E152">
         <v>8315000</v>
       </c>
       <c r="F152">
-        <v>80661470</v>
+        <v>533840845</v>
       </c>
       <c r="G152">
-        <v>789775530</v>
+        <v>336596155</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -5254,10 +5264,10 @@
         <v>1702406000</v>
       </c>
       <c r="D154">
-        <v>288060277</v>
+        <v>253750000</v>
       </c>
       <c r="E154">
-        <v>106580059</v>
+        <v>140890336</v>
       </c>
       <c r="F154">
         <v>394640336</v>
@@ -5332,10 +5342,10 @@
         <v>317990000</v>
       </c>
       <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="E157">
         <v>3857000</v>
-      </c>
-      <c r="E157">
-        <v>0</v>
       </c>
       <c r="F157">
         <v>3857000</v>
@@ -5566,16 +5576,16 @@
         <v>135000000</v>
       </c>
       <c r="D166">
-        <v>10000000</v>
+        <v>16244591</v>
       </c>
       <c r="E166">
         <v>10000000</v>
       </c>
       <c r="F166">
-        <v>20000000</v>
+        <v>26244591</v>
       </c>
       <c r="G166">
-        <v>115000000</v>
+        <v>108755409</v>
       </c>
       <c r="H166">
         <v>45000000</v>
@@ -5592,10 +5602,10 @@
         <v>408750000</v>
       </c>
       <c r="D167">
-        <v>64994809</v>
+        <v>61779809</v>
       </c>
       <c r="E167">
-        <v>88041635</v>
+        <v>91256635</v>
       </c>
       <c r="F167">
         <v>153036444</v>
@@ -5956,16 +5966,16 @@
         <v>46375593027</v>
       </c>
       <c r="D181">
-        <v>11360522923</v>
+        <v>11771649807</v>
       </c>
       <c r="E181">
-        <v>4573989269</v>
+        <v>4661171546</v>
       </c>
       <c r="F181">
-        <v>15934512192</v>
+        <v>16432821353</v>
       </c>
       <c r="G181">
-        <v>30441080835</v>
+        <v>29942771674</v>
       </c>
       <c r="H181">
         <v>449400500</v>
@@ -6086,16 +6096,16 @@
         <v>3030122000</v>
       </c>
       <c r="D186">
-        <v>461381691</v>
+        <v>453597000</v>
       </c>
       <c r="E186">
         <v>0</v>
       </c>
       <c r="F186">
-        <v>461381691</v>
+        <v>453597000</v>
       </c>
       <c r="G186">
-        <v>2568740309</v>
+        <v>2576525000</v>
       </c>
       <c r="H186">
         <v>0</v>
@@ -6242,10 +6252,10 @@
         <v>1862650000</v>
       </c>
       <c r="D192">
-        <v>735987201</v>
+        <v>666075701</v>
       </c>
       <c r="E192">
-        <v>75332346</v>
+        <v>145243846</v>
       </c>
       <c r="F192">
         <v>811319547</v>
@@ -6346,10 +6356,10 @@
         <v>1491275000</v>
       </c>
       <c r="D196">
-        <v>1090050000</v>
+        <v>1081200000</v>
       </c>
       <c r="E196">
-        <v>69795000</v>
+        <v>78645000</v>
       </c>
       <c r="F196">
         <v>1159845000</v>
@@ -6944,16 +6954,16 @@
         <v>43454346868</v>
       </c>
       <c r="D219">
-        <v>9344569914</v>
+        <v>9258023723</v>
       </c>
       <c r="E219">
-        <v>5909133223</v>
+        <v>5987894723</v>
       </c>
       <c r="F219">
-        <v>15253703137</v>
+        <v>15245918446</v>
       </c>
       <c r="G219">
-        <v>28200643731</v>
+        <v>28208428422</v>
       </c>
       <c r="H219">
         <v>415261500</v>
@@ -6970,16 +6980,16 @@
         <v>12264606000</v>
       </c>
       <c r="D220">
-        <v>9573167730</v>
+        <v>9583562730</v>
       </c>
       <c r="E220">
         <v>36030000</v>
       </c>
       <c r="F220">
-        <v>9609197730</v>
+        <v>9619592730</v>
       </c>
       <c r="G220">
-        <v>2655408270</v>
+        <v>2645013270</v>
       </c>
       <c r="H220">
         <v>0</v>
@@ -7126,16 +7136,16 @@
         <v>1380000000</v>
       </c>
       <c r="D226">
-        <v>341396016</v>
+        <v>396302016</v>
       </c>
       <c r="E226">
         <v>201042000</v>
       </c>
       <c r="F226">
-        <v>542438016</v>
+        <v>597344016</v>
       </c>
       <c r="G226">
-        <v>837561984</v>
+        <v>782655984</v>
       </c>
       <c r="H226">
         <v>0</v>
@@ -7750,16 +7760,16 @@
         <v>48914772555</v>
       </c>
       <c r="D250">
-        <v>14334527142</v>
+        <v>14399828142</v>
       </c>
       <c r="E250">
         <v>6067685934</v>
       </c>
       <c r="F250">
-        <v>20402213076</v>
+        <v>20467514076</v>
       </c>
       <c r="G250">
-        <v>28512559479</v>
+        <v>28447258479</v>
       </c>
       <c r="H250">
         <v>525212165</v>
@@ -7776,16 +7786,16 @@
         <v>5695069150</v>
       </c>
       <c r="D251">
-        <v>3653645019</v>
+        <v>4878823525</v>
       </c>
       <c r="E251">
         <v>0</v>
       </c>
       <c r="F251">
-        <v>3653645019</v>
+        <v>4878823525</v>
       </c>
       <c r="G251">
-        <v>2041424131</v>
+        <v>816245625</v>
       </c>
       <c r="H251">
         <v>0</v>
@@ -7906,16 +7916,16 @@
         <v>3269982000</v>
       </c>
       <c r="D256">
-        <v>197080000</v>
+        <v>239080000</v>
       </c>
       <c r="E256">
         <v>99830000</v>
       </c>
       <c r="F256">
-        <v>296910000</v>
+        <v>338910000</v>
       </c>
       <c r="G256">
-        <v>2973072000</v>
+        <v>2931072000</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -8114,10 +8124,10 @@
         <v>5267324000</v>
       </c>
       <c r="D264">
-        <v>3682715131</v>
+        <v>3639215131</v>
       </c>
       <c r="E264">
-        <v>125320040</v>
+        <v>168820040</v>
       </c>
       <c r="F264">
         <v>3808035171</v>
@@ -8192,10 +8202,10 @@
         <v>2260000000</v>
       </c>
       <c r="D267">
-        <v>447600900</v>
+        <v>437604300</v>
       </c>
       <c r="E267">
-        <v>0</v>
+        <v>9996600</v>
       </c>
       <c r="F267">
         <v>447600900</v>
@@ -8481,13 +8491,13 @@
         <v>0</v>
       </c>
       <c r="E278">
-        <v>59174750</v>
+        <v>78182750</v>
       </c>
       <c r="F278">
-        <v>59174750</v>
+        <v>78182750</v>
       </c>
       <c r="G278">
-        <v>144299500</v>
+        <v>125291500</v>
       </c>
       <c r="H278">
         <v>67824750</v>
@@ -8504,10 +8514,10 @@
         <v>181144082</v>
       </c>
       <c r="D279">
-        <v>5683583</v>
+        <v>1986100</v>
       </c>
       <c r="E279">
-        <v>19555332</v>
+        <v>23252815</v>
       </c>
       <c r="F279">
         <v>25238915</v>
@@ -8585,13 +8595,13 @@
         <v>0</v>
       </c>
       <c r="E282">
-        <v>2910916196</v>
+        <v>2912210896</v>
       </c>
       <c r="F282">
-        <v>2910916196</v>
+        <v>2912210896</v>
       </c>
       <c r="G282">
-        <v>9711702731</v>
+        <v>9710408031</v>
       </c>
       <c r="H282">
         <v>0</v>
@@ -8790,16 +8800,16 @@
         <v>63706784713</v>
       </c>
       <c r="D290">
-        <v>12451888892</v>
+        <v>13661873315</v>
       </c>
       <c r="E290">
-        <v>7425405485</v>
+        <v>7502902268</v>
       </c>
       <c r="F290">
-        <v>19877294377</v>
+        <v>21164775583</v>
       </c>
       <c r="G290">
-        <v>43829490336</v>
+        <v>42542009130</v>
       </c>
       <c r="H290">
         <v>531045413</v>
@@ -9908,16 +9918,16 @@
         <v>831375509</v>
       </c>
       <c r="D333">
-        <v>345662595</v>
+        <v>340477000</v>
       </c>
       <c r="E333">
         <v>0</v>
       </c>
       <c r="F333">
-        <v>345662595</v>
+        <v>340477000</v>
       </c>
       <c r="G333">
-        <v>485712914</v>
+        <v>490898509</v>
       </c>
       <c r="H333">
         <v>0</v>
@@ -10012,16 +10022,16 @@
         <v>150000000</v>
       </c>
       <c r="D337">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="E337">
         <v>0</v>
       </c>
       <c r="F337">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="G337">
-        <v>150000000</v>
+        <v>130000000</v>
       </c>
       <c r="H337">
         <v>50000000</v>
@@ -10064,16 +10074,16 @@
         <v>2911760000</v>
       </c>
       <c r="D339">
-        <v>456770</v>
+        <v>292232770</v>
       </c>
       <c r="E339">
         <v>600310622</v>
       </c>
       <c r="F339">
-        <v>600767392</v>
+        <v>892543392</v>
       </c>
       <c r="G339">
-        <v>2310992608</v>
+        <v>2019216608</v>
       </c>
       <c r="H339">
         <v>0</v>
@@ -10116,16 +10126,16 @@
         <v>571079775</v>
       </c>
       <c r="D341">
-        <v>21171800</v>
+        <v>227311470</v>
       </c>
       <c r="E341">
         <v>60451850</v>
       </c>
       <c r="F341">
-        <v>81623650</v>
+        <v>287763320</v>
       </c>
       <c r="G341">
-        <v>489456125</v>
+        <v>283316455</v>
       </c>
       <c r="H341">
         <v>190359925</v>
@@ -10480,16 +10490,16 @@
         <v>57427089299</v>
       </c>
       <c r="D355">
-        <v>19251682068</v>
+        <v>19764412143</v>
       </c>
       <c r="E355">
         <v>7741803892</v>
       </c>
       <c r="F355">
-        <v>26993485960</v>
+        <v>27506216035</v>
       </c>
       <c r="G355">
-        <v>30433603339</v>
+        <v>29920873264</v>
       </c>
       <c r="H355">
         <v>526334925</v>
@@ -10977,13 +10987,13 @@
         <v>17070000</v>
       </c>
       <c r="E374">
-        <v>41510000</v>
+        <v>45760000</v>
       </c>
       <c r="F374">
-        <v>58580000</v>
+        <v>62830000</v>
       </c>
       <c r="G374">
-        <v>69445000</v>
+        <v>65195000</v>
       </c>
       <c r="H374">
         <v>42675000</v>
@@ -11055,13 +11065,13 @@
         <v>0</v>
       </c>
       <c r="E377">
-        <v>1047785781</v>
+        <v>1047842031</v>
       </c>
       <c r="F377">
-        <v>1047785781</v>
+        <v>1047842031</v>
       </c>
       <c r="G377">
-        <v>3492021137</v>
+        <v>3491964887</v>
       </c>
       <c r="H377">
         <v>0</v>
@@ -11263,13 +11273,13 @@
         <v>907728296</v>
       </c>
       <c r="E385">
-        <v>3099490609</v>
+        <v>3103796859</v>
       </c>
       <c r="F385">
-        <v>4007218905</v>
+        <v>4011525155</v>
       </c>
       <c r="G385">
-        <v>19728196686</v>
+        <v>19723890436</v>
       </c>
       <c r="H385">
         <v>232675000</v>
@@ -11468,16 +11478,16 @@
         <v>690000000</v>
       </c>
       <c r="D393">
-        <v>152359150</v>
+        <v>475576990</v>
       </c>
       <c r="E393">
-        <v>98940700</v>
+        <v>110531650</v>
       </c>
       <c r="F393">
-        <v>251299850</v>
+        <v>586108640</v>
       </c>
       <c r="G393">
-        <v>438700150</v>
+        <v>103891360</v>
       </c>
       <c r="H393">
         <v>0</v>
@@ -11702,16 +11712,16 @@
         <v>2230000000</v>
       </c>
       <c r="D402">
-        <v>19000000</v>
+        <v>28033828</v>
       </c>
       <c r="E402">
         <v>329979818</v>
       </c>
       <c r="F402">
-        <v>348979818</v>
+        <v>358013646</v>
       </c>
       <c r="G402">
-        <v>1881020182</v>
+        <v>1871986354</v>
       </c>
       <c r="H402">
         <v>0</v>
@@ -11754,10 +11764,10 @@
         <v>445223250</v>
       </c>
       <c r="D404">
-        <v>121017450</v>
+        <v>98217450</v>
       </c>
       <c r="E404">
-        <v>67914000</v>
+        <v>90714000</v>
       </c>
       <c r="F404">
         <v>188931450</v>
@@ -12144,16 +12154,16 @@
         <v>33762059370</v>
       </c>
       <c r="D419">
-        <v>932294048</v>
+        <v>1241745716</v>
       </c>
       <c r="E419">
-        <v>4963443138</v>
+        <v>4997834088</v>
       </c>
       <c r="F419">
-        <v>5895737186</v>
+        <v>6239579804</v>
       </c>
       <c r="G419">
-        <v>27866322184</v>
+        <v>27522479566</v>
       </c>
       <c r="H419">
         <v>472807750</v>
@@ -13034,57 +13044,50 @@
         <v>115</v>
       </c>
       <c r="B475" s="1">
-        <f>SUM(B420:B474)</f>
         <v>2349760730</v>
       </c>
       <c r="C475" s="1">
-        <f t="shared" ref="C475:H475" si="0">SUM(C420:C474)</f>
         <v>2247760730</v>
       </c>
       <c r="D475" s="1">
-        <f t="shared" si="0"/>
         <v>443295900</v>
       </c>
       <c r="E475" s="1">
-        <f t="shared" si="0"/>
         <v>81050880</v>
       </c>
       <c r="F475" s="1">
-        <f t="shared" si="0"/>
         <v>524346780</v>
       </c>
       <c r="G475" s="1">
-        <f t="shared" si="0"/>
         <v>1723413950</v>
       </c>
       <c r="H475" s="1">
-        <f t="shared" si="0"/>
         <v>102000000</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A476" t="s">
+      <c r="A476" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B476">
+      <c r="B476" s="2">
         <v>10505111000</v>
       </c>
-      <c r="C476">
+      <c r="C476" s="2">
         <v>10505111000</v>
       </c>
-      <c r="D476">
-        <v>7759691599</v>
-      </c>
-      <c r="E476">
-        <v>0</v>
-      </c>
-      <c r="F476">
-        <v>7759691599</v>
-      </c>
-      <c r="G476">
-        <v>2745419401</v>
-      </c>
-      <c r="H476">
+      <c r="D476" s="2">
+        <v>8256418500</v>
+      </c>
+      <c r="E476" s="2">
+        <v>0</v>
+      </c>
+      <c r="F476" s="2">
+        <v>8256418500</v>
+      </c>
+      <c r="G476" s="2">
+        <v>2248692500</v>
+      </c>
+      <c r="H476" s="2">
         <v>0</v>
       </c>
     </row>
@@ -13281,10 +13284,10 @@
         <v>4989900000</v>
       </c>
       <c r="D484">
-        <v>805366889</v>
+        <v>738815888</v>
       </c>
       <c r="E484">
-        <v>333634248</v>
+        <v>400185249</v>
       </c>
       <c r="F484">
         <v>1139001137</v>
@@ -13463,10 +13466,10 @@
         <v>745000000</v>
       </c>
       <c r="D491">
-        <v>26235280</v>
+        <v>6813800</v>
       </c>
       <c r="E491">
-        <v>32460000</v>
+        <v>51881480</v>
       </c>
       <c r="F491">
         <v>58695280</v>
@@ -13489,10 +13492,10 @@
         <v>4029356000</v>
       </c>
       <c r="D492">
-        <v>2411599000</v>
+        <v>2406199000</v>
       </c>
       <c r="E492">
-        <v>29795000</v>
+        <v>35195000</v>
       </c>
       <c r="F492">
         <v>2441394000</v>
@@ -13567,16 +13570,16 @@
         <v>1350000000</v>
       </c>
       <c r="D495">
-        <v>0</v>
+        <v>240865000</v>
       </c>
       <c r="E495">
         <v>0</v>
       </c>
       <c r="F495">
-        <v>0</v>
+        <v>240865000</v>
       </c>
       <c r="G495">
-        <v>1350000000</v>
+        <v>1109135000</v>
       </c>
       <c r="H495">
         <v>0</v>
@@ -13671,10 +13674,10 @@
         <v>668379750</v>
       </c>
       <c r="D499">
-        <v>29693828</v>
+        <v>27955000</v>
       </c>
       <c r="E499">
-        <v>22370000</v>
+        <v>24108828</v>
       </c>
       <c r="F499">
         <v>52063828</v>
@@ -13775,10 +13778,10 @@
         <v>516433500</v>
       </c>
       <c r="D503">
-        <v>35082547</v>
+        <v>9803310</v>
       </c>
       <c r="E503">
-        <v>78343130</v>
+        <v>103622367</v>
       </c>
       <c r="F503">
         <v>113425677</v>
@@ -13827,10 +13830,10 @@
         <v>61741000</v>
       </c>
       <c r="D505">
-        <v>38255444</v>
+        <v>36196764</v>
       </c>
       <c r="E505">
-        <v>0</v>
+        <v>2058680</v>
       </c>
       <c r="F505">
         <v>38255444</v>
@@ -14165,16 +14168,16 @@
         <v>60647750187</v>
       </c>
       <c r="D518">
-        <v>13442447419</v>
+        <v>14059590094</v>
       </c>
       <c r="E518">
-        <v>7718566344</v>
+        <v>7839015570</v>
       </c>
       <c r="F518">
-        <v>21161013763</v>
+        <v>21898605664</v>
       </c>
       <c r="G518">
-        <v>39486736424</v>
+        <v>38749144523</v>
       </c>
       <c r="H518">
         <v>850782250</v>
@@ -14581,10 +14584,10 @@
         <v>1539315000</v>
       </c>
       <c r="D534">
-        <v>6649654</v>
+        <v>6305960</v>
       </c>
       <c r="E534">
-        <v>331100876</v>
+        <v>331444570</v>
       </c>
       <c r="F534">
         <v>337750530</v>
@@ -14997,10 +15000,10 @@
         <v>57848682223</v>
       </c>
       <c r="D550">
-        <v>22615145411</v>
+        <v>22614801717</v>
       </c>
       <c r="E550">
-        <v>6647322342</v>
+        <v>6647666036</v>
       </c>
       <c r="F550">
         <v>29262467753</v>
@@ -15012,33 +15015,8 @@
         <v>720558750</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A551" t="s">
-        <v>126</v>
-      </c>
-      <c r="B551">
-        <v>1118709871725</v>
-      </c>
-      <c r="C551">
-        <v>1109177594403</v>
-      </c>
-      <c r="D551">
-        <v>415977958056</v>
-      </c>
-      <c r="E551">
-        <v>157884365737</v>
-      </c>
-      <c r="F551">
-        <v>573862323793</v>
-      </c>
-      <c r="G551">
-        <v>535315270610</v>
-      </c>
-      <c r="H551">
-        <v>9532277322</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:H551" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\5. Mei\RKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDBC842-59D7-4578-9EFE-787165858BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9E4795-F752-447D-9B27-F741A05991AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -960,7 +960,16 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1274,7 +1283,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="60.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="16.06640625" style="1" customWidth="1"/>
+    <col min="2" max="8" width="15.1328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1730,16 +1739,16 @@
         <v>4500000000</v>
       </c>
       <c r="D18" s="1">
-        <v>73981319</v>
+        <v>100436319</v>
       </c>
       <c r="E18" s="1">
         <v>994362605</v>
       </c>
       <c r="F18" s="1">
-        <v>1068343924</v>
+        <v>1094798924</v>
       </c>
       <c r="G18" s="1">
-        <v>3431656076</v>
+        <v>3405201076</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -1889,13 +1898,13 @@
         <v>52169339</v>
       </c>
       <c r="E24" s="1">
-        <v>450192742</v>
+        <v>467105242</v>
       </c>
       <c r="F24" s="1">
-        <v>502362081</v>
+        <v>519274581</v>
       </c>
       <c r="G24" s="1">
-        <v>1337513110</v>
+        <v>1320600610</v>
       </c>
       <c r="H24" s="1">
         <v>625000000</v>
@@ -1967,13 +1976,13 @@
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>977702797</v>
+        <v>978429360</v>
       </c>
       <c r="F27" s="1">
-        <v>977702797</v>
+        <v>978429360</v>
       </c>
       <c r="G27" s="1">
-        <v>2478911407</v>
+        <v>2478184844</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -2019,13 +2028,13 @@
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>979768190</v>
+        <v>985576190</v>
       </c>
       <c r="F29" s="1">
-        <v>979768190</v>
+        <v>985576190</v>
       </c>
       <c r="G29" s="1">
-        <v>3098501845</v>
+        <v>3092693845</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -2123,13 +2132,13 @@
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>3400439574</v>
+        <v>3404189574</v>
       </c>
       <c r="F33" s="1">
-        <v>3400439574</v>
+        <v>3404189574</v>
       </c>
       <c r="G33" s="1">
-        <v>10569626472</v>
+        <v>10565876472</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2276,16 +2285,16 @@
         <v>357965647047</v>
       </c>
       <c r="D39" s="1">
-        <v>223490414272</v>
+        <v>223516869272</v>
       </c>
       <c r="E39" s="1">
-        <v>62641127411</v>
+        <v>62668324474</v>
       </c>
       <c r="F39" s="1">
-        <v>286131541683</v>
+        <v>286185193746</v>
       </c>
       <c r="G39" s="1">
-        <v>71834105364</v>
+        <v>71780453301</v>
       </c>
       <c r="H39" s="1">
         <v>2417500000</v>
@@ -2302,10 +2311,10 @@
         <v>25194775704</v>
       </c>
       <c r="D40" s="1">
-        <v>21257338430</v>
+        <v>20927663430</v>
       </c>
       <c r="E40" s="1">
-        <v>1718760000</v>
+        <v>2048435000</v>
       </c>
       <c r="F40" s="1">
         <v>22976098430</v>
@@ -2562,16 +2571,16 @@
         <v>6000000000</v>
       </c>
       <c r="D50" s="1">
-        <v>2462176901</v>
+        <v>2487006191</v>
       </c>
       <c r="E50" s="1">
         <v>61105000</v>
       </c>
       <c r="F50" s="1">
-        <v>2523281901</v>
+        <v>2548111191</v>
       </c>
       <c r="G50" s="1">
-        <v>3476718099</v>
+        <v>3451888809</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -2718,16 +2727,16 @@
         <v>2620000000</v>
       </c>
       <c r="D56" s="1">
-        <v>348900000</v>
+        <v>375022000</v>
       </c>
       <c r="E56" s="1">
         <v>216520000</v>
       </c>
       <c r="F56" s="1">
-        <v>565420000</v>
+        <v>591542000</v>
       </c>
       <c r="G56" s="1">
-        <v>2054580000</v>
+        <v>2028458000</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -2900,10 +2909,10 @@
         <v>417000000</v>
       </c>
       <c r="D63" s="1">
-        <v>86897510</v>
+        <v>79167010</v>
       </c>
       <c r="E63" s="1">
-        <v>58234925</v>
+        <v>65965425</v>
       </c>
       <c r="F63" s="1">
         <v>145132435</v>
@@ -2926,10 +2935,10 @@
         <v>335175000</v>
       </c>
       <c r="D64" s="1">
-        <v>95330000</v>
+        <v>80257000</v>
       </c>
       <c r="E64" s="1">
-        <v>79432416</v>
+        <v>94505416</v>
       </c>
       <c r="F64" s="1">
         <v>174762416</v>
@@ -3033,13 +3042,13 @@
         <v>56676000</v>
       </c>
       <c r="E68" s="1">
-        <v>137864250</v>
+        <v>142339250</v>
       </c>
       <c r="F68" s="1">
-        <v>194540250</v>
+        <v>199015250</v>
       </c>
       <c r="G68" s="1">
-        <v>159684750</v>
+        <v>155209750</v>
       </c>
       <c r="H68" s="1">
         <v>118075000</v>
@@ -3056,16 +3065,16 @@
         <v>80000000</v>
       </c>
       <c r="D69" s="1">
-        <v>9600000</v>
+        <v>11100000</v>
       </c>
       <c r="E69" s="1">
         <v>35332700</v>
       </c>
       <c r="F69" s="1">
-        <v>44932700</v>
+        <v>46432700</v>
       </c>
       <c r="G69" s="1">
-        <v>35067300</v>
+        <v>33567300</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
@@ -3111,13 +3120,13 @@
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>7032001241</v>
+        <v>7032055616</v>
       </c>
       <c r="F71" s="1">
-        <v>7032001241</v>
+        <v>7032055616</v>
       </c>
       <c r="G71" s="1">
-        <v>15899605988</v>
+        <v>15899551613</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -3160,10 +3169,10 @@
         <v>20967421530</v>
       </c>
       <c r="D73" s="1">
-        <v>53146854</v>
+        <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>5302491519</v>
+        <v>5355638373</v>
       </c>
       <c r="F73" s="1">
         <v>5355638373</v>
@@ -3264,10 +3273,10 @@
         <v>1937118528</v>
       </c>
       <c r="D77" s="1">
-        <v>1006122</v>
+        <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>593441519</v>
+        <v>594447641</v>
       </c>
       <c r="F77" s="1">
         <v>594447641</v>
@@ -3342,16 +3351,16 @@
         <v>110897810191</v>
       </c>
       <c r="D80" s="1">
-        <v>27519799267</v>
+        <v>27165619081</v>
       </c>
       <c r="E80" s="1">
-        <v>18002774050</v>
+        <v>18413934901</v>
       </c>
       <c r="F80" s="1">
-        <v>45522573317</v>
+        <v>45579553982</v>
       </c>
       <c r="G80" s="1">
-        <v>65375236874</v>
+        <v>65318256209</v>
       </c>
       <c r="H80" s="1">
         <v>671501500</v>
@@ -3368,16 +3377,16 @@
         <v>4044107500</v>
       </c>
       <c r="D81" s="1">
-        <v>2897907200</v>
+        <v>2808247200</v>
       </c>
       <c r="E81" s="1">
-        <v>1033361000</v>
+        <v>1229711000</v>
       </c>
       <c r="F81" s="1">
-        <v>3931268200</v>
+        <v>4037958200</v>
       </c>
       <c r="G81" s="1">
-        <v>112839300</v>
+        <v>6149300</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
@@ -3420,10 +3429,10 @@
         <v>1657269514</v>
       </c>
       <c r="D83" s="1">
-        <v>44350000</v>
+        <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>125198600</v>
+        <v>169548600</v>
       </c>
       <c r="F83" s="1">
         <v>169548600</v>
@@ -3446,10 +3455,10 @@
         <v>30639775739</v>
       </c>
       <c r="D84" s="1">
-        <v>16871416836</v>
+        <v>16742103702</v>
       </c>
       <c r="E84" s="1">
-        <v>7612427997</v>
+        <v>7741741131</v>
       </c>
       <c r="F84" s="1">
         <v>24483844833</v>
@@ -3576,16 +3585,16 @@
         <v>2796520000</v>
       </c>
       <c r="D89" s="1">
-        <v>351401610</v>
+        <v>335502505</v>
       </c>
       <c r="E89" s="1">
-        <v>1227146248</v>
+        <v>1292764498</v>
       </c>
       <c r="F89" s="1">
-        <v>1578547858</v>
+        <v>1628267003</v>
       </c>
       <c r="G89" s="1">
-        <v>1217972142</v>
+        <v>1168252997</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -3732,16 +3741,16 @@
         <v>1710494400</v>
       </c>
       <c r="D95" s="1">
-        <v>1105694186</v>
+        <v>1119786280</v>
       </c>
       <c r="E95" s="1">
-        <v>63755600</v>
+        <v>102361506</v>
       </c>
       <c r="F95" s="1">
-        <v>1169449786</v>
+        <v>1222147786</v>
       </c>
       <c r="G95" s="1">
-        <v>541044614</v>
+        <v>488346614</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -3784,16 +3793,16 @@
         <v>419475000</v>
       </c>
       <c r="D97" s="1">
-        <v>119617000</v>
+        <v>125717000</v>
       </c>
       <c r="E97" s="1">
         <v>8717850</v>
       </c>
       <c r="F97" s="1">
-        <v>128334850</v>
+        <v>134434850</v>
       </c>
       <c r="G97" s="1">
-        <v>291140150</v>
+        <v>285040150</v>
       </c>
       <c r="H97" s="1">
         <v>139825000</v>
@@ -3810,16 +3819,16 @@
         <v>255960000</v>
       </c>
       <c r="D98" s="1">
-        <v>109781500</v>
+        <v>124323900</v>
       </c>
       <c r="E98" s="1">
         <v>46900000</v>
       </c>
       <c r="F98" s="1">
-        <v>156681500</v>
+        <v>171223900</v>
       </c>
       <c r="G98" s="1">
-        <v>99278500</v>
+        <v>84736100</v>
       </c>
       <c r="H98" s="1">
         <v>85320000</v>
@@ -3862,16 +3871,16 @@
         <v>291600000</v>
       </c>
       <c r="D100" s="1">
-        <v>70800000</v>
+        <v>98879000</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
       </c>
       <c r="F100" s="1">
-        <v>70800000</v>
+        <v>98879000</v>
       </c>
       <c r="G100" s="1">
-        <v>220800000</v>
+        <v>192721000</v>
       </c>
       <c r="H100" s="1">
         <v>97200000</v>
@@ -3917,13 +3926,13 @@
         <v>49693920</v>
       </c>
       <c r="E102" s="1">
-        <v>241020568</v>
+        <v>241645568</v>
       </c>
       <c r="F102" s="1">
-        <v>290714488</v>
+        <v>291339488</v>
       </c>
       <c r="G102" s="1">
-        <v>4343012</v>
+        <v>3718012</v>
       </c>
       <c r="H102" s="1">
         <v>98352500</v>
@@ -3940,16 +3949,16 @@
         <v>91080000</v>
       </c>
       <c r="D103" s="1">
-        <v>11880000</v>
+        <v>50807400</v>
       </c>
       <c r="E103" s="1">
         <v>0</v>
       </c>
       <c r="F103" s="1">
-        <v>11880000</v>
+        <v>50807400</v>
       </c>
       <c r="G103" s="1">
-        <v>79200000</v>
+        <v>40272600</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -4047,13 +4056,13 @@
         <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>5013572969</v>
+        <v>5013595469</v>
       </c>
       <c r="F107" s="1">
-        <v>5013572969</v>
+        <v>5013595469</v>
       </c>
       <c r="G107" s="1">
-        <v>11210071884</v>
+        <v>11210049384</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -4096,10 +4105,10 @@
         <v>14498179948</v>
       </c>
       <c r="D109" s="1">
-        <v>44020227</v>
+        <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>3799662410</v>
+        <v>3843682637</v>
       </c>
       <c r="F109" s="1">
         <v>3843682637</v>
@@ -4200,10 +4209,10 @@
         <v>1928660874</v>
       </c>
       <c r="D113" s="1">
-        <v>203046</v>
+        <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>486975235</v>
+        <v>487178281</v>
       </c>
       <c r="F113" s="1">
         <v>487178281</v>
@@ -4252,16 +4261,16 @@
         <v>81718644736</v>
       </c>
       <c r="D115" s="1">
-        <v>21819709129</v>
+        <v>21598004511</v>
       </c>
       <c r="E115" s="1">
-        <v>21187763879</v>
+        <v>21706871942</v>
       </c>
       <c r="F115" s="1">
-        <v>43007473008</v>
+        <v>43304876453</v>
       </c>
       <c r="G115" s="1">
-        <v>38711171728</v>
+        <v>38413768283</v>
       </c>
       <c r="H115" s="1">
         <v>475697500</v>
@@ -4382,10 +4391,10 @@
         <v>1200699000</v>
       </c>
       <c r="D120" s="1">
-        <v>75246975</v>
+        <v>40248300</v>
       </c>
       <c r="E120" s="1">
-        <v>0</v>
+        <v>34998675</v>
       </c>
       <c r="F120" s="1">
         <v>75246975</v>
@@ -4434,16 +4443,16 @@
         <v>4824864000</v>
       </c>
       <c r="D122" s="1">
-        <v>3237020465</v>
+        <v>3239428035</v>
       </c>
       <c r="E122" s="1">
         <v>1246505408</v>
       </c>
       <c r="F122" s="1">
-        <v>4483525873</v>
+        <v>4485933443</v>
       </c>
       <c r="G122" s="1">
-        <v>341338127</v>
+        <v>338930557</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
@@ -4590,16 +4599,16 @@
         <v>450000000</v>
       </c>
       <c r="D128" s="1">
-        <v>11438550</v>
+        <v>0</v>
       </c>
       <c r="E128" s="1">
-        <v>49168907</v>
+        <v>59473907</v>
       </c>
       <c r="F128" s="1">
-        <v>60607457</v>
+        <v>59473907</v>
       </c>
       <c r="G128" s="1">
-        <v>389392543</v>
+        <v>390526093</v>
       </c>
       <c r="H128" s="1">
         <v>0</v>
@@ -4616,16 +4625,16 @@
         <v>700000000</v>
       </c>
       <c r="D129" s="1">
+        <v>311421224</v>
+      </c>
+      <c r="E129" s="1">
         <v>388459396</v>
       </c>
-      <c r="E129" s="1">
-        <v>0</v>
-      </c>
       <c r="F129" s="1">
-        <v>388459396</v>
+        <v>699880620</v>
       </c>
       <c r="G129" s="1">
-        <v>311540604</v>
+        <v>119380</v>
       </c>
       <c r="H129" s="1">
         <v>0</v>
@@ -4668,16 +4677,16 @@
         <v>118875000</v>
       </c>
       <c r="D131" s="1">
-        <v>5280000</v>
+        <v>10802000</v>
       </c>
       <c r="E131" s="1">
         <v>19537500</v>
       </c>
       <c r="F131" s="1">
-        <v>24817500</v>
+        <v>30339500</v>
       </c>
       <c r="G131" s="1">
-        <v>94057500</v>
+        <v>88535500</v>
       </c>
       <c r="H131" s="1">
         <v>0</v>
@@ -4827,13 +4836,13 @@
         <v>0</v>
       </c>
       <c r="E137" s="1">
-        <v>80136250</v>
+        <v>80798750</v>
       </c>
       <c r="F137" s="1">
-        <v>80136250</v>
+        <v>80798750</v>
       </c>
       <c r="G137" s="1">
-        <v>79853750</v>
+        <v>79191250</v>
       </c>
       <c r="H137" s="1">
         <v>53330000</v>
@@ -4905,13 +4914,13 @@
         <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>3029075183</v>
+        <v>3029083621</v>
       </c>
       <c r="F140" s="1">
-        <v>3029075183</v>
+        <v>3029083621</v>
       </c>
       <c r="G140" s="1">
-        <v>6920018900</v>
+        <v>6920010462</v>
       </c>
       <c r="H140" s="1">
         <v>0</v>
@@ -4954,10 +4963,10 @@
         <v>9769849891</v>
       </c>
       <c r="D142" s="1">
-        <v>29399670</v>
+        <v>0</v>
       </c>
       <c r="E142" s="1">
-        <v>2390113860</v>
+        <v>2419513530</v>
       </c>
       <c r="F142" s="1">
         <v>2419513530</v>
@@ -5058,10 +5067,10 @@
         <v>1330317539</v>
       </c>
       <c r="D146" s="1">
-        <v>1412619</v>
+        <v>0</v>
       </c>
       <c r="E146" s="1">
-        <v>339317075</v>
+        <v>340729694</v>
       </c>
       <c r="F146" s="1">
         <v>340729694</v>
@@ -5136,16 +5145,16 @@
         <v>50726099717</v>
       </c>
       <c r="D149" s="1">
-        <v>12848236935</v>
+        <v>12701878819</v>
       </c>
       <c r="E149" s="1">
-        <v>12361145245</v>
+        <v>12826391543</v>
       </c>
       <c r="F149" s="1">
-        <v>25209382180</v>
+        <v>25528270362</v>
       </c>
       <c r="G149" s="1">
-        <v>25516717537</v>
+        <v>25197829355</v>
       </c>
       <c r="H149" s="1">
         <v>411080000</v>
@@ -5266,16 +5275,16 @@
         <v>870437000</v>
       </c>
       <c r="D154" s="1">
-        <v>508384000</v>
+        <v>626814000</v>
       </c>
       <c r="E154" s="1">
         <v>73492000</v>
       </c>
       <c r="F154" s="1">
-        <v>581876000</v>
+        <v>700306000</v>
       </c>
       <c r="G154" s="1">
-        <v>288561000</v>
+        <v>170131000</v>
       </c>
       <c r="H154" s="1">
         <v>0</v>
@@ -5500,16 +5509,16 @@
         <v>867942000</v>
       </c>
       <c r="D163" s="1">
-        <v>0</v>
+        <v>413512000</v>
       </c>
       <c r="E163" s="1">
         <v>0</v>
       </c>
       <c r="F163" s="1">
-        <v>0</v>
+        <v>413512000</v>
       </c>
       <c r="G163" s="1">
-        <v>867942000</v>
+        <v>454430000</v>
       </c>
       <c r="H163" s="1">
         <v>0</v>
@@ -5763,13 +5772,13 @@
         <v>0</v>
       </c>
       <c r="E173" s="1">
-        <v>67628750</v>
+        <v>68578750</v>
       </c>
       <c r="F173" s="1">
-        <v>67628750</v>
+        <v>68578750</v>
       </c>
       <c r="G173" s="1">
-        <v>94672750</v>
+        <v>93722750</v>
       </c>
       <c r="H173" s="1">
         <v>54100500</v>
@@ -5815,13 +5824,13 @@
         <v>0</v>
       </c>
       <c r="E175" s="1">
-        <v>2256768431</v>
+        <v>2256779681</v>
       </c>
       <c r="F175" s="1">
-        <v>2256768431</v>
+        <v>2256779681</v>
       </c>
       <c r="G175" s="1">
-        <v>5247954947</v>
+        <v>5247943697</v>
       </c>
       <c r="H175" s="1">
         <v>0</v>
@@ -6020,16 +6029,16 @@
         <v>46375593027</v>
       </c>
       <c r="D183" s="1">
-        <v>17114166900</v>
+        <v>17646108900</v>
       </c>
       <c r="E183" s="1">
-        <v>6925224521</v>
+        <v>6926185771</v>
       </c>
       <c r="F183" s="1">
-        <v>24039391421</v>
+        <v>24572294671</v>
       </c>
       <c r="G183" s="1">
-        <v>22336201606</v>
+        <v>21803298356</v>
       </c>
       <c r="H183" s="1">
         <v>449400500</v>
@@ -6332,16 +6341,16 @@
         <v>1862650000</v>
       </c>
       <c r="D195" s="1">
-        <v>365468434</v>
+        <v>430644210</v>
       </c>
       <c r="E195" s="1">
         <v>658976213</v>
       </c>
       <c r="F195" s="1">
-        <v>1024444647</v>
+        <v>1089620423</v>
       </c>
       <c r="G195" s="1">
-        <v>838205353</v>
+        <v>773029577</v>
       </c>
       <c r="H195" s="1">
         <v>0</v>
@@ -6540,16 +6549,16 @@
         <v>112500000</v>
       </c>
       <c r="D203" s="1">
-        <v>31500000</v>
+        <v>34965000</v>
       </c>
       <c r="E203" s="1">
         <v>41856000</v>
       </c>
       <c r="F203" s="1">
-        <v>73356000</v>
+        <v>76821000</v>
       </c>
       <c r="G203" s="1">
-        <v>39144000</v>
+        <v>35679000</v>
       </c>
       <c r="H203" s="1">
         <v>37500000</v>
@@ -6566,16 +6575,16 @@
         <v>320100000</v>
       </c>
       <c r="D204" s="1">
-        <v>0</v>
+        <v>134900000</v>
       </c>
       <c r="E204" s="1">
         <v>71775000</v>
       </c>
       <c r="F204" s="1">
-        <v>71775000</v>
+        <v>206675000</v>
       </c>
       <c r="G204" s="1">
-        <v>248325000</v>
+        <v>113425000</v>
       </c>
       <c r="H204" s="1">
         <v>0</v>
@@ -6618,10 +6627,10 @@
         <v>97500000</v>
       </c>
       <c r="D206" s="1">
-        <v>9008000</v>
+        <v>5608000</v>
       </c>
       <c r="E206" s="1">
-        <v>35818811</v>
+        <v>39218811</v>
       </c>
       <c r="F206" s="1">
         <v>44826811</v>
@@ -6644,16 +6653,16 @@
         <v>385534500</v>
       </c>
       <c r="D207" s="1">
-        <v>58788000</v>
+        <v>47798000</v>
       </c>
       <c r="E207" s="1">
-        <v>81188500</v>
+        <v>96188500</v>
       </c>
       <c r="F207" s="1">
-        <v>139976500</v>
+        <v>143986500</v>
       </c>
       <c r="G207" s="1">
-        <v>245558000</v>
+        <v>241548000</v>
       </c>
       <c r="H207" s="1">
         <v>128511500</v>
@@ -6696,16 +6705,16 @@
         <v>337500000</v>
       </c>
       <c r="D209" s="1">
-        <v>31222300</v>
+        <v>40690300</v>
       </c>
       <c r="E209" s="1">
         <v>37567000</v>
       </c>
       <c r="F209" s="1">
-        <v>68789300</v>
+        <v>78257300</v>
       </c>
       <c r="G209" s="1">
-        <v>268710700</v>
+        <v>259242700</v>
       </c>
       <c r="H209" s="1">
         <v>112500000</v>
@@ -6751,13 +6760,13 @@
         <v>0</v>
       </c>
       <c r="E211" s="1">
-        <v>106692500</v>
+        <v>108592500</v>
       </c>
       <c r="F211" s="1">
-        <v>106692500</v>
+        <v>108592500</v>
       </c>
       <c r="G211" s="1">
-        <v>82307500</v>
+        <v>80407500</v>
       </c>
       <c r="H211" s="1">
         <v>63000000</v>
@@ -6829,13 +6838,13 @@
         <v>0</v>
       </c>
       <c r="E214" s="1">
-        <v>2995789193</v>
+        <v>2995813569</v>
       </c>
       <c r="F214" s="1">
-        <v>2995789193</v>
+        <v>2995813569</v>
       </c>
       <c r="G214" s="1">
-        <v>6827372933</v>
+        <v>6827348557</v>
       </c>
       <c r="H214" s="1">
         <v>0</v>
@@ -7034,16 +7043,16 @@
         <v>45147208545</v>
       </c>
       <c r="D222" s="1">
-        <v>11912591984</v>
+        <v>12111210760</v>
       </c>
       <c r="E222" s="1">
-        <v>9592547034</v>
+        <v>9612871410</v>
       </c>
       <c r="F222" s="1">
-        <v>21505139018</v>
+        <v>21724082170</v>
       </c>
       <c r="G222" s="1">
-        <v>23642069527</v>
+        <v>23423126375</v>
       </c>
       <c r="H222" s="1">
         <v>415261500</v>
@@ -7060,16 +7069,16 @@
         <v>12264606000</v>
       </c>
       <c r="D223" s="1">
-        <v>10582642730</v>
+        <v>10818958730</v>
       </c>
       <c r="E223" s="1">
         <v>73650000</v>
       </c>
       <c r="F223" s="1">
-        <v>10656292730</v>
+        <v>10892608730</v>
       </c>
       <c r="G223" s="1">
-        <v>1608313270</v>
+        <v>1371997270</v>
       </c>
       <c r="H223" s="1">
         <v>0</v>
@@ -7164,10 +7173,10 @@
         <v>200000000</v>
       </c>
       <c r="D227" s="1">
-        <v>39555315</v>
+        <v>6887500</v>
       </c>
       <c r="E227" s="1">
-        <v>0</v>
+        <v>32667815</v>
       </c>
       <c r="F227" s="1">
         <v>39555315</v>
@@ -7216,16 +7225,16 @@
         <v>1380000000</v>
       </c>
       <c r="D229" s="1">
-        <v>121139200</v>
+        <v>74785700</v>
       </c>
       <c r="E229" s="1">
-        <v>610640516</v>
+        <v>666865516</v>
       </c>
       <c r="F229" s="1">
-        <v>731779716</v>
+        <v>741651216</v>
       </c>
       <c r="G229" s="1">
-        <v>648220284</v>
+        <v>638348784</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
@@ -7268,16 +7277,16 @@
         <v>497000000</v>
       </c>
       <c r="D231" s="1">
-        <v>496659494</v>
+        <v>488479196</v>
       </c>
       <c r="E231" s="1">
         <v>0</v>
       </c>
       <c r="F231" s="1">
-        <v>496659494</v>
+        <v>488479196</v>
       </c>
       <c r="G231" s="1">
-        <v>340506</v>
+        <v>8520804</v>
       </c>
       <c r="H231" s="1">
         <v>0</v>
@@ -7476,16 +7485,16 @@
         <v>110162550</v>
       </c>
       <c r="D239" s="1">
-        <v>10310000</v>
+        <v>11170000</v>
       </c>
       <c r="E239" s="1">
         <v>25251000</v>
       </c>
       <c r="F239" s="1">
-        <v>35561000</v>
+        <v>36421000</v>
       </c>
       <c r="G239" s="1">
-        <v>74601550</v>
+        <v>73741550</v>
       </c>
       <c r="H239" s="1">
         <v>36720850</v>
@@ -7583,13 +7592,13 @@
         <v>0</v>
       </c>
       <c r="E243" s="1">
-        <v>86706250</v>
+        <v>90143750</v>
       </c>
       <c r="F243" s="1">
-        <v>86706250</v>
+        <v>90143750</v>
       </c>
       <c r="G243" s="1">
-        <v>115577750</v>
+        <v>112140250</v>
       </c>
       <c r="H243" s="1">
         <v>67428000</v>
@@ -7635,13 +7644,13 @@
         <v>0</v>
       </c>
       <c r="E245" s="1">
-        <v>2991037827</v>
+        <v>2991125952</v>
       </c>
       <c r="F245" s="1">
-        <v>2991037827</v>
+        <v>2991125952</v>
       </c>
       <c r="G245" s="1">
-        <v>6834918343</v>
+        <v>6834830218</v>
       </c>
       <c r="H245" s="1">
         <v>0</v>
@@ -7840,16 +7849,16 @@
         <v>48914772555</v>
       </c>
       <c r="D253" s="1">
-        <v>15516260836</v>
+        <v>15666235223</v>
       </c>
       <c r="E253" s="1">
-        <v>8229860121</v>
+        <v>8322278561</v>
       </c>
       <c r="F253" s="1">
-        <v>23746120957</v>
+        <v>23988513784</v>
       </c>
       <c r="G253" s="1">
-        <v>25168651598</v>
+        <v>24926258771</v>
       </c>
       <c r="H253" s="1">
         <v>525212165</v>
@@ -7996,16 +8005,16 @@
         <v>3269982000</v>
       </c>
       <c r="D259" s="1">
-        <v>711931344</v>
+        <v>690105560</v>
       </c>
       <c r="E259" s="1">
-        <v>141830000</v>
+        <v>179825784</v>
       </c>
       <c r="F259" s="1">
-        <v>853761344</v>
+        <v>869931344</v>
       </c>
       <c r="G259" s="1">
-        <v>2416220656</v>
+        <v>2400050656</v>
       </c>
       <c r="H259" s="1">
         <v>0</v>
@@ -8048,16 +8057,16 @@
         <v>1700000000</v>
       </c>
       <c r="D261" s="1">
-        <v>118223472</v>
+        <v>158028595</v>
       </c>
       <c r="E261" s="1">
         <v>407850160</v>
       </c>
       <c r="F261" s="1">
-        <v>526073632</v>
+        <v>565878755</v>
       </c>
       <c r="G261" s="1">
-        <v>1173926368</v>
+        <v>1134121245</v>
       </c>
       <c r="H261" s="1">
         <v>0</v>
@@ -8204,10 +8213,10 @@
         <v>5267324000</v>
       </c>
       <c r="D267" s="1">
-        <v>4624306263</v>
+        <v>4176930459</v>
       </c>
       <c r="E267" s="1">
-        <v>276745930</v>
+        <v>724121734</v>
       </c>
       <c r="F267" s="1">
         <v>4901052193</v>
@@ -8282,10 +8291,10 @@
         <v>2260000000</v>
       </c>
       <c r="D270" s="1">
-        <v>1137567229</v>
+        <v>846036229</v>
       </c>
       <c r="E270" s="1">
-        <v>156069900</v>
+        <v>447600900</v>
       </c>
       <c r="F270" s="1">
         <v>1293637129</v>
@@ -8438,16 +8447,16 @@
         <v>1952349292</v>
       </c>
       <c r="D276" s="1">
-        <v>740750</v>
+        <v>326800</v>
       </c>
       <c r="E276" s="1">
-        <v>628827451</v>
+        <v>629568201</v>
       </c>
       <c r="F276" s="1">
-        <v>629568201</v>
+        <v>629895001</v>
       </c>
       <c r="G276" s="1">
-        <v>1322781091</v>
+        <v>1322454291</v>
       </c>
       <c r="H276" s="1">
         <v>0</v>
@@ -8464,16 +8473,16 @@
         <v>62053350</v>
       </c>
       <c r="D277" s="1">
-        <v>29948186</v>
+        <v>29634186</v>
       </c>
       <c r="E277" s="1">
         <v>22676627</v>
       </c>
       <c r="F277" s="1">
-        <v>52624813</v>
+        <v>52310813</v>
       </c>
       <c r="G277" s="1">
-        <v>9428537</v>
+        <v>9742537</v>
       </c>
       <c r="H277" s="1">
         <v>20684450</v>
@@ -8490,16 +8499,16 @@
         <v>470406638</v>
       </c>
       <c r="D278" s="1">
-        <v>338224619</v>
+        <v>75278600</v>
       </c>
       <c r="E278" s="1">
-        <v>128965733</v>
+        <v>142465733</v>
       </c>
       <c r="F278" s="1">
-        <v>467190352</v>
+        <v>217744333</v>
       </c>
       <c r="G278" s="1">
-        <v>3216286</v>
+        <v>252662305</v>
       </c>
       <c r="H278" s="1">
         <v>156802213</v>
@@ -8542,16 +8551,16 @@
         <v>707202000</v>
       </c>
       <c r="D280" s="1">
-        <v>36818000</v>
+        <v>328818000</v>
       </c>
       <c r="E280" s="1">
         <v>59146500</v>
       </c>
       <c r="F280" s="1">
-        <v>95964500</v>
+        <v>387964500</v>
       </c>
       <c r="G280" s="1">
-        <v>611237500</v>
+        <v>319237500</v>
       </c>
       <c r="H280" s="1">
         <v>235734000</v>
@@ -8571,13 +8580,13 @@
         <v>0</v>
       </c>
       <c r="E281" s="1">
-        <v>104919500</v>
+        <v>125591250</v>
       </c>
       <c r="F281" s="1">
-        <v>104919500</v>
+        <v>125591250</v>
       </c>
       <c r="G281" s="1">
-        <v>98554750</v>
+        <v>77883000</v>
       </c>
       <c r="H281" s="1">
         <v>67824750</v>
@@ -8594,16 +8603,16 @@
         <v>181144082</v>
       </c>
       <c r="D282" s="1">
-        <v>1986100</v>
+        <v>599000</v>
       </c>
       <c r="E282" s="1">
-        <v>31389636</v>
+        <v>33375736</v>
       </c>
       <c r="F282" s="1">
-        <v>33375736</v>
+        <v>33974736</v>
       </c>
       <c r="G282" s="1">
-        <v>147768346</v>
+        <v>147169346</v>
       </c>
       <c r="H282" s="1">
         <v>0</v>
@@ -8675,13 +8684,13 @@
         <v>0</v>
       </c>
       <c r="E285" s="1">
-        <v>3819955742</v>
+        <v>3821260193</v>
       </c>
       <c r="F285" s="1">
-        <v>3819955742</v>
+        <v>3821260193</v>
       </c>
       <c r="G285" s="1">
-        <v>8802663185</v>
+        <v>8801358734</v>
       </c>
       <c r="H285" s="1">
         <v>0</v>
@@ -8727,13 +8736,13 @@
         <v>0</v>
       </c>
       <c r="E287" s="1">
-        <v>3129107241</v>
+        <v>3166892844</v>
       </c>
       <c r="F287" s="1">
-        <v>3129107241</v>
+        <v>3166892844</v>
       </c>
       <c r="G287" s="1">
-        <v>9782610174</v>
+        <v>9744824571</v>
       </c>
       <c r="H287" s="1">
         <v>0</v>
@@ -8831,13 +8840,13 @@
         <v>0</v>
       </c>
       <c r="E291" s="1">
-        <v>409599444</v>
+        <v>410198938</v>
       </c>
       <c r="F291" s="1">
-        <v>409599444</v>
+        <v>410198938</v>
       </c>
       <c r="G291" s="1">
-        <v>1150729393</v>
+        <v>1150129899</v>
       </c>
       <c r="H291" s="1">
         <v>0</v>
@@ -8880,16 +8889,16 @@
         <v>63706784713</v>
       </c>
       <c r="D293" s="1">
-        <v>17682832170</v>
+        <v>16988843636</v>
       </c>
       <c r="E293" s="1">
-        <v>10149630008</v>
+        <v>11003120744</v>
       </c>
       <c r="F293" s="1">
-        <v>27832462178</v>
+        <v>27991964380</v>
       </c>
       <c r="G293" s="1">
-        <v>35874322535</v>
+        <v>35714820333</v>
       </c>
       <c r="H293" s="1">
         <v>531045413</v>
@@ -9140,10 +9149,10 @@
         <v>174000000</v>
       </c>
       <c r="D303" s="1">
-        <v>56914309</v>
+        <v>36995453</v>
       </c>
       <c r="E303" s="1">
-        <v>0</v>
+        <v>19918856</v>
       </c>
       <c r="F303" s="1">
         <v>56914309</v>
@@ -9452,16 +9461,16 @@
         <v>385800000</v>
       </c>
       <c r="D315" s="1">
-        <v>20759000</v>
+        <v>30759000</v>
       </c>
       <c r="E315" s="1">
         <v>38875635</v>
       </c>
       <c r="F315" s="1">
-        <v>59634635</v>
+        <v>69634635</v>
       </c>
       <c r="G315" s="1">
-        <v>326165365</v>
+        <v>316165365</v>
       </c>
       <c r="H315" s="1">
         <v>128600000</v>
@@ -9481,13 +9490,13 @@
         <v>0</v>
       </c>
       <c r="E316" s="1">
-        <v>59654000</v>
+        <v>73617500</v>
       </c>
       <c r="F316" s="1">
-        <v>59654000</v>
+        <v>73617500</v>
       </c>
       <c r="G316" s="1">
-        <v>112846000</v>
+        <v>98882500</v>
       </c>
       <c r="H316" s="1">
         <v>57500000</v>
@@ -9533,13 +9542,13 @@
         <v>0</v>
       </c>
       <c r="E318" s="1">
-        <v>2056351934</v>
+        <v>2057104708</v>
       </c>
       <c r="F318" s="1">
-        <v>2056351934</v>
+        <v>2057104708</v>
       </c>
       <c r="G318" s="1">
-        <v>4997440331</v>
+        <v>4996687557</v>
       </c>
       <c r="H318" s="1">
         <v>0</v>
@@ -9582,10 +9591,10 @@
         <v>7015042421</v>
       </c>
       <c r="D320" s="1">
-        <v>18962865</v>
+        <v>0</v>
       </c>
       <c r="E320" s="1">
-        <v>1741508986</v>
+        <v>1760471851</v>
       </c>
       <c r="F320" s="1">
         <v>1760471851</v>
@@ -9686,10 +9695,10 @@
         <v>1449712379</v>
       </c>
       <c r="D324" s="1">
-        <v>609685</v>
+        <v>0</v>
       </c>
       <c r="E324" s="1">
-        <v>356928658</v>
+        <v>357538343</v>
       </c>
       <c r="F324" s="1">
         <v>357538343</v>
@@ -9738,16 +9747,16 @@
         <v>30454436960</v>
       </c>
       <c r="D326" s="1">
-        <v>6877097773</v>
+        <v>6847606367</v>
       </c>
       <c r="E326" s="1">
-        <v>6432206992</v>
+        <v>6486414672</v>
       </c>
       <c r="F326" s="1">
-        <v>13309304765</v>
+        <v>13334021039</v>
       </c>
       <c r="G326" s="1">
-        <v>17145132195</v>
+        <v>17120415921</v>
       </c>
       <c r="H326" s="1">
         <v>260139500</v>
@@ -9764,10 +9773,10 @@
         <v>13755471000</v>
       </c>
       <c r="D327" s="1">
-        <v>12511161555</v>
+        <v>11275789700</v>
       </c>
       <c r="E327" s="1">
-        <v>1185507500</v>
+        <v>2420879355</v>
       </c>
       <c r="F327" s="1">
         <v>13696669055</v>
@@ -9790,10 +9799,10 @@
         <v>2948978291</v>
       </c>
       <c r="D328" s="1">
-        <v>2748481531</v>
+        <v>2698981531</v>
       </c>
       <c r="E328" s="1">
-        <v>104119950</v>
+        <v>153619950</v>
       </c>
       <c r="F328" s="1">
         <v>2852601481</v>
@@ -9894,10 +9903,10 @@
         <v>687000000</v>
       </c>
       <c r="D332" s="1">
-        <v>209727000</v>
+        <v>111157000</v>
       </c>
       <c r="E332" s="1">
-        <v>141841100</v>
+        <v>240411100</v>
       </c>
       <c r="F332" s="1">
         <v>351568100</v>
@@ -9946,16 +9955,16 @@
         <v>1660344000</v>
       </c>
       <c r="D334" s="1">
-        <v>412863160</v>
+        <v>479465130</v>
       </c>
       <c r="E334" s="1">
         <v>457330268</v>
       </c>
       <c r="F334" s="1">
-        <v>870193428</v>
+        <v>936795398</v>
       </c>
       <c r="G334" s="1">
-        <v>790150572</v>
+        <v>723548602</v>
       </c>
       <c r="H334" s="1">
         <v>0</v>
@@ -9972,16 +9981,16 @@
         <v>327155000</v>
       </c>
       <c r="D335" s="1">
-        <v>49966000</v>
+        <v>99726180</v>
       </c>
       <c r="E335" s="1">
         <v>160280500</v>
       </c>
       <c r="F335" s="1">
-        <v>210246500</v>
+        <v>260006680</v>
       </c>
       <c r="G335" s="1">
-        <v>116908500</v>
+        <v>67148320</v>
       </c>
       <c r="H335" s="1">
         <v>0</v>
@@ -9998,10 +10007,10 @@
         <v>831375509</v>
       </c>
       <c r="D336" s="1">
+        <v>0</v>
+      </c>
+      <c r="E336" s="1">
         <v>340477000</v>
-      </c>
-      <c r="E336" s="1">
-        <v>0</v>
       </c>
       <c r="F336" s="1">
         <v>340477000</v>
@@ -10024,10 +10033,10 @@
         <v>1039505000</v>
       </c>
       <c r="D337" s="1">
-        <v>1806000</v>
+        <v>0</v>
       </c>
       <c r="E337" s="1">
-        <v>1019420000</v>
+        <v>1021226000</v>
       </c>
       <c r="F337" s="1">
         <v>1021226000</v>
@@ -10076,16 +10085,16 @@
         <v>1000000000</v>
       </c>
       <c r="D339" s="1">
-        <v>0</v>
+        <v>43200000</v>
       </c>
       <c r="E339" s="1">
         <v>0</v>
       </c>
       <c r="F339" s="1">
-        <v>0</v>
+        <v>43200000</v>
       </c>
       <c r="G339" s="1">
-        <v>1000000000</v>
+        <v>956800000</v>
       </c>
       <c r="H339" s="1">
         <v>0</v>
@@ -10180,16 +10189,16 @@
         <v>135000000</v>
       </c>
       <c r="D343" s="1">
-        <v>0</v>
+        <v>8633000</v>
       </c>
       <c r="E343" s="1">
         <v>43404500</v>
       </c>
       <c r="F343" s="1">
-        <v>43404500</v>
+        <v>52037500</v>
       </c>
       <c r="G343" s="1">
-        <v>91595500</v>
+        <v>82962500</v>
       </c>
       <c r="H343" s="1">
         <v>45000000</v>
@@ -10206,16 +10215,16 @@
         <v>571079775</v>
       </c>
       <c r="D344" s="1">
-        <v>248525646</v>
+        <v>287464589</v>
       </c>
       <c r="E344" s="1">
-        <v>83916075</v>
+        <v>91484075</v>
       </c>
       <c r="F344" s="1">
-        <v>332441721</v>
+        <v>378948664</v>
       </c>
       <c r="G344" s="1">
-        <v>238638054</v>
+        <v>192131111</v>
       </c>
       <c r="H344" s="1">
         <v>190359925</v>
@@ -10287,13 +10296,13 @@
         <v>0</v>
       </c>
       <c r="E347" s="1">
-        <v>90472500</v>
+        <v>94935000</v>
       </c>
       <c r="F347" s="1">
-        <v>90472500</v>
+        <v>94935000</v>
       </c>
       <c r="G347" s="1">
-        <v>170077500</v>
+        <v>165615000</v>
       </c>
       <c r="H347" s="1">
         <v>86850000</v>
@@ -10365,13 +10374,13 @@
         <v>0</v>
       </c>
       <c r="E350" s="1">
-        <v>3161594051</v>
+        <v>3161658739</v>
       </c>
       <c r="F350" s="1">
-        <v>3161594051</v>
+        <v>3161658739</v>
       </c>
       <c r="G350" s="1">
-        <v>7553321962</v>
+        <v>7553257274</v>
       </c>
       <c r="H350" s="1">
         <v>0</v>
@@ -10570,16 +10579,16 @@
         <v>57427089299</v>
       </c>
       <c r="D358" s="1">
-        <v>17163100231</v>
+        <v>15644509469</v>
       </c>
       <c r="E358" s="1">
-        <v>13040671307</v>
+        <v>14778491350</v>
       </c>
       <c r="F358" s="1">
-        <v>30203771538</v>
+        <v>30423000819</v>
       </c>
       <c r="G358" s="1">
-        <v>27223317761</v>
+        <v>27004088480</v>
       </c>
       <c r="H358" s="1">
         <v>526334925</v>
@@ -10596,16 +10605,16 @@
         <v>3291324000</v>
       </c>
       <c r="D359" s="1">
-        <v>1785804253</v>
+        <v>1762085126</v>
       </c>
       <c r="E359" s="1">
         <v>1254739500</v>
       </c>
       <c r="F359" s="1">
-        <v>3040543753</v>
+        <v>3016824626</v>
       </c>
       <c r="G359" s="1">
-        <v>250780247</v>
+        <v>274499374</v>
       </c>
       <c r="H359" s="1">
         <v>0</v>
@@ -10648,10 +10657,10 @@
         <v>2244807000</v>
       </c>
       <c r="D361" s="1">
-        <v>142532198</v>
+        <v>92567876</v>
       </c>
       <c r="E361" s="1">
-        <v>233128782</v>
+        <v>283093104</v>
       </c>
       <c r="F361" s="1">
         <v>375660980</v>
@@ -10674,10 +10683,10 @@
         <v>149777000</v>
       </c>
       <c r="D362" s="1">
-        <v>11331820</v>
+        <v>0</v>
       </c>
       <c r="E362" s="1">
-        <v>40169574</v>
+        <v>51501394</v>
       </c>
       <c r="F362" s="1">
         <v>51501394</v>
@@ -10830,16 +10839,16 @@
         <v>470200000</v>
       </c>
       <c r="D368" s="1">
-        <v>433300000</v>
+        <v>421680000</v>
       </c>
       <c r="E368" s="1">
         <v>3229600</v>
       </c>
       <c r="F368" s="1">
-        <v>436529600</v>
+        <v>424909600</v>
       </c>
       <c r="G368" s="1">
-        <v>33670400</v>
+        <v>45290400</v>
       </c>
       <c r="H368" s="1">
         <v>0</v>
@@ -10960,16 +10969,16 @@
         <v>120000000</v>
       </c>
       <c r="D373" s="1">
-        <v>19212500</v>
+        <v>22021000</v>
       </c>
       <c r="E373" s="1">
         <v>19702000</v>
       </c>
       <c r="F373" s="1">
-        <v>38914500</v>
+        <v>41723000</v>
       </c>
       <c r="G373" s="1">
-        <v>81085500</v>
+        <v>78277000</v>
       </c>
       <c r="H373" s="1">
         <v>40000000</v>
@@ -11376,16 +11385,16 @@
         <v>23735415591</v>
       </c>
       <c r="D389" s="1">
-        <v>3782123455</v>
+        <v>3688296686</v>
       </c>
       <c r="E389" s="1">
-        <v>5421478587</v>
+        <v>5482774729</v>
       </c>
       <c r="F389" s="1">
-        <v>9203602042</v>
+        <v>9171071415</v>
       </c>
       <c r="G389" s="1">
-        <v>14531813549</v>
+        <v>14564344176</v>
       </c>
       <c r="H389" s="1">
         <v>232675000</v>
@@ -11402,16 +11411,16 @@
         <v>3435027000</v>
       </c>
       <c r="D390" s="1">
-        <v>2144569170</v>
+        <v>2447406361</v>
       </c>
       <c r="E390" s="1">
         <v>0</v>
       </c>
       <c r="F390" s="1">
-        <v>2144569170</v>
+        <v>2447406361</v>
       </c>
       <c r="G390" s="1">
-        <v>1290457830</v>
+        <v>987620639</v>
       </c>
       <c r="H390" s="1">
         <v>0</v>
@@ -11480,16 +11489,16 @@
         <v>890568000</v>
       </c>
       <c r="D393" s="1">
-        <v>683526590</v>
+        <v>722380790</v>
       </c>
       <c r="E393" s="1">
         <v>99478446</v>
       </c>
       <c r="F393" s="1">
-        <v>783005036</v>
+        <v>821859236</v>
       </c>
       <c r="G393" s="1">
-        <v>107562964</v>
+        <v>68708764</v>
       </c>
       <c r="H393" s="1">
         <v>0</v>
@@ -11558,16 +11567,16 @@
         <v>500000000</v>
       </c>
       <c r="D396" s="1">
-        <v>422130004</v>
+        <v>440292504</v>
       </c>
       <c r="E396" s="1">
         <v>49811800</v>
       </c>
       <c r="F396" s="1">
-        <v>471941804</v>
+        <v>490104304</v>
       </c>
       <c r="G396" s="1">
-        <v>28058196</v>
+        <v>9895696</v>
       </c>
       <c r="H396" s="1">
         <v>0</v>
@@ -11951,13 +11960,13 @@
         <v>0</v>
       </c>
       <c r="E411" s="1">
-        <v>114861362</v>
+        <v>115811362</v>
       </c>
       <c r="F411" s="1">
-        <v>114861362</v>
+        <v>115811362</v>
       </c>
       <c r="G411" s="1">
-        <v>236138638</v>
+        <v>235188638</v>
       </c>
       <c r="H411" s="1">
         <v>117000000</v>
@@ -11974,16 +11983,16 @@
         <v>6000000</v>
       </c>
       <c r="D412" s="1">
-        <v>0</v>
+        <v>315000</v>
       </c>
       <c r="E412" s="1">
         <v>315000</v>
       </c>
       <c r="F412" s="1">
-        <v>315000</v>
+        <v>630000</v>
       </c>
       <c r="G412" s="1">
-        <v>5685000</v>
+        <v>5370000</v>
       </c>
       <c r="H412" s="1">
         <v>0</v>
@@ -12055,13 +12064,13 @@
         <v>0</v>
       </c>
       <c r="E415" s="1">
-        <v>2599048903</v>
+        <v>2599060153</v>
       </c>
       <c r="F415" s="1">
-        <v>2599048903</v>
+        <v>2599060153</v>
       </c>
       <c r="G415" s="1">
-        <v>6042296808</v>
+        <v>6042285558</v>
       </c>
       <c r="H415" s="1">
         <v>0</v>
@@ -12260,16 +12269,16 @@
         <v>34261412640</v>
       </c>
       <c r="D423" s="1">
-        <v>6904527743</v>
+        <v>7264696634</v>
       </c>
       <c r="E423" s="1">
-        <v>6850199357</v>
+        <v>6851160607</v>
       </c>
       <c r="F423" s="1">
-        <v>13754727100</v>
+        <v>14115857241</v>
       </c>
       <c r="G423" s="1">
-        <v>20506685540</v>
+        <v>20145555399</v>
       </c>
       <c r="H423" s="1">
         <v>472807750</v>
@@ -13167,16 +13176,16 @@
         <v>10505111000</v>
       </c>
       <c r="D480" s="1">
-        <v>8956732568</v>
+        <v>8960656568</v>
       </c>
       <c r="E480" s="1">
         <v>0</v>
       </c>
       <c r="F480" s="1">
-        <v>8956732568</v>
+        <v>8960656568</v>
       </c>
       <c r="G480" s="1">
-        <v>1548378432</v>
+        <v>1544454432</v>
       </c>
       <c r="H480" s="1">
         <v>0</v>
@@ -13375,10 +13384,10 @@
         <v>4989900000</v>
       </c>
       <c r="D488" s="1">
-        <v>692518465</v>
+        <v>320362500</v>
       </c>
       <c r="E488" s="1">
-        <v>535471147</v>
+        <v>907627112</v>
       </c>
       <c r="F488" s="1">
         <v>1227989612</v>
@@ -13872,13 +13881,13 @@
         <v>23459914</v>
       </c>
       <c r="E507" s="1">
-        <v>141303067</v>
+        <v>142103067</v>
       </c>
       <c r="F507" s="1">
-        <v>164762981</v>
+        <v>165562981</v>
       </c>
       <c r="G507" s="1">
-        <v>351670519</v>
+        <v>350870519</v>
       </c>
       <c r="H507" s="1">
         <v>172144500</v>
@@ -14028,13 +14037,13 @@
         <v>0</v>
       </c>
       <c r="E513" s="1">
-        <v>3846785245</v>
+        <v>3846803995</v>
       </c>
       <c r="F513" s="1">
-        <v>3846785245</v>
+        <v>3846803995</v>
       </c>
       <c r="G513" s="1">
-        <v>8317496652</v>
+        <v>8317477902</v>
       </c>
       <c r="H513" s="1">
         <v>0</v>
@@ -14259,16 +14268,16 @@
         <v>60647750187</v>
       </c>
       <c r="D522" s="1">
-        <v>15394543896</v>
+        <v>15026311931</v>
       </c>
       <c r="E522" s="1">
-        <v>10404843700</v>
+        <v>10777818415</v>
       </c>
       <c r="F522" s="1">
-        <v>25799387596</v>
+        <v>25804130346</v>
       </c>
       <c r="G522" s="1">
-        <v>34848362591</v>
+        <v>34843619841</v>
       </c>
       <c r="H522" s="1">
         <v>850782250</v>
@@ -14285,10 +14294,10 @@
         <v>5574698000</v>
       </c>
       <c r="D523" s="1">
-        <v>4633018338</v>
+        <v>4212276338</v>
       </c>
       <c r="E523" s="1">
-        <v>789738000</v>
+        <v>1210480000</v>
       </c>
       <c r="F523" s="1">
         <v>5422756338</v>
@@ -14337,10 +14346,10 @@
         <v>1694175000</v>
       </c>
       <c r="D525" s="1">
-        <v>1674171093</v>
+        <v>1290186093</v>
       </c>
       <c r="E525" s="1">
-        <v>0</v>
+        <v>383985000</v>
       </c>
       <c r="F525" s="1">
         <v>1674171093</v>
@@ -14363,16 +14372,16 @@
         <v>2639000000</v>
       </c>
       <c r="D526" s="1">
-        <v>1806145524</v>
+        <v>1801111464</v>
       </c>
       <c r="E526" s="1">
         <v>231626548</v>
       </c>
       <c r="F526" s="1">
-        <v>2037772072</v>
+        <v>2032738012</v>
       </c>
       <c r="G526" s="1">
-        <v>601227928</v>
+        <v>606261988</v>
       </c>
       <c r="H526" s="1">
         <v>0</v>
@@ -14415,16 +14424,16 @@
         <v>2721193000</v>
       </c>
       <c r="D528" s="1">
-        <v>1842047719</v>
+        <v>2143543628</v>
       </c>
       <c r="E528" s="1">
-        <v>426675124</v>
+        <v>517475124</v>
       </c>
       <c r="F528" s="1">
-        <v>2268722843</v>
+        <v>2661018752</v>
       </c>
       <c r="G528" s="1">
-        <v>452470157</v>
+        <v>60174248</v>
       </c>
       <c r="H528" s="1">
         <v>0</v>
@@ -14441,16 +14450,16 @@
         <v>9794675000</v>
       </c>
       <c r="D529" s="1">
-        <v>8722341898</v>
+        <v>8961749000</v>
       </c>
       <c r="E529" s="1">
         <v>3607897</v>
       </c>
       <c r="F529" s="1">
-        <v>8725949795</v>
+        <v>8965356897</v>
       </c>
       <c r="G529" s="1">
-        <v>1068725205</v>
+        <v>829318103</v>
       </c>
       <c r="H529" s="1">
         <v>0</v>
@@ -14493,16 +14502,16 @@
         <v>1450000000</v>
       </c>
       <c r="D531" s="1">
-        <v>149647827</v>
+        <v>199024427</v>
       </c>
       <c r="E531" s="1">
         <v>49530000</v>
       </c>
       <c r="F531" s="1">
-        <v>199177827</v>
+        <v>248554427</v>
       </c>
       <c r="G531" s="1">
-        <v>1250822173</v>
+        <v>1201445573</v>
       </c>
       <c r="H531" s="1">
         <v>0</v>
@@ -14571,10 +14580,10 @@
         <v>1750000000</v>
       </c>
       <c r="D534" s="1">
-        <v>1335802734</v>
+        <v>848260734</v>
       </c>
       <c r="E534" s="1">
-        <v>0</v>
+        <v>487542000</v>
       </c>
       <c r="F534" s="1">
         <v>1335802734</v>
@@ -14623,16 +14632,16 @@
         <v>483750000</v>
       </c>
       <c r="D536" s="1">
-        <v>292535000</v>
+        <v>307470000</v>
       </c>
       <c r="E536" s="1">
         <v>83170000</v>
       </c>
       <c r="F536" s="1">
-        <v>375705000</v>
+        <v>390640000</v>
       </c>
       <c r="G536" s="1">
-        <v>108045000</v>
+        <v>93110000</v>
       </c>
       <c r="H536" s="1">
         <v>161250000</v>
@@ -14649,10 +14658,10 @@
         <v>285978663</v>
       </c>
       <c r="D537" s="1">
-        <v>94484100</v>
+        <v>78384100</v>
       </c>
       <c r="E537" s="1">
-        <v>55485000</v>
+        <v>71585000</v>
       </c>
       <c r="F537" s="1">
         <v>149969100</v>
@@ -14701,10 +14710,10 @@
         <v>412500000</v>
       </c>
       <c r="D539" s="1">
-        <v>41887175</v>
+        <v>35830775</v>
       </c>
       <c r="E539" s="1">
-        <v>34529200</v>
+        <v>40585600</v>
       </c>
       <c r="F539" s="1">
         <v>76416375</v>
@@ -14727,16 +14736,16 @@
         <v>532875000</v>
       </c>
       <c r="D540" s="1">
-        <v>34917940</v>
+        <v>18923970</v>
       </c>
       <c r="E540" s="1">
-        <v>67182849</v>
+        <v>84176819</v>
       </c>
       <c r="F540" s="1">
-        <v>102100789</v>
+        <v>103100789</v>
       </c>
       <c r="G540" s="1">
-        <v>430774211</v>
+        <v>429774211</v>
       </c>
       <c r="H540" s="1">
         <v>177625000</v>
@@ -14779,16 +14788,16 @@
         <v>395748750</v>
       </c>
       <c r="D542" s="1">
-        <v>28490669</v>
+        <v>211687498</v>
       </c>
       <c r="E542" s="1">
-        <v>0</v>
+        <v>3769950</v>
       </c>
       <c r="F542" s="1">
-        <v>28490669</v>
+        <v>215457448</v>
       </c>
       <c r="G542" s="1">
-        <v>367258081</v>
+        <v>180291302</v>
       </c>
       <c r="H542" s="1">
         <v>131916250</v>
@@ -14808,13 +14817,13 @@
         <v>2743600</v>
       </c>
       <c r="E543" s="1">
-        <v>128577500</v>
+        <v>128865000</v>
       </c>
       <c r="F543" s="1">
-        <v>131321100</v>
+        <v>131608600</v>
       </c>
       <c r="G543" s="1">
-        <v>205481400</v>
+        <v>205193900</v>
       </c>
       <c r="H543" s="1">
         <v>112267500</v>
@@ -14886,13 +14895,13 @@
         <v>0</v>
       </c>
       <c r="E546" s="1">
-        <v>3418950513</v>
+        <v>3418954263</v>
       </c>
       <c r="F546" s="1">
-        <v>3418950513</v>
+        <v>3418954263</v>
       </c>
       <c r="G546" s="1">
-        <v>7269966353</v>
+        <v>7269962603</v>
       </c>
       <c r="H546" s="1">
         <v>0</v>
@@ -15091,16 +15100,16 @@
         <v>57848682223</v>
       </c>
       <c r="D554" s="1">
-        <v>22957134638</v>
+        <v>22410092648</v>
       </c>
       <c r="E554" s="1">
-        <v>9214727816</v>
+        <v>10641008386</v>
       </c>
       <c r="F554" s="1">
-        <v>32171862454</v>
+        <v>33051101034</v>
       </c>
       <c r="G554" s="1">
-        <v>25676819769</v>
+        <v>24797581189</v>
       </c>
       <c r="H554" s="1">
         <v>720558750</v>
@@ -15117,23 +15126,23 @@
         <v>1109252930979</v>
       </c>
       <c r="D555" s="1">
-        <v>429400129520</v>
+        <v>426904792892</v>
       </c>
       <c r="E555" s="1">
-        <v>209640566298</v>
+        <v>215733876675</v>
       </c>
       <c r="F555" s="1">
-        <v>639040695818</v>
+        <v>642638669567</v>
       </c>
       <c r="G555" s="1">
-        <v>470212235161</v>
+        <v>466614261412</v>
       </c>
       <c r="H555" s="1">
         <v>9532277322</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H555" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H555" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\6. Jun\KP\RKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{CAA38511-821A-4090-823B-633E33DFE365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{380F5882-9538-4E40-A05C-930DF4331D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975"/>
   </bookViews>
@@ -1263,7 +1263,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="60.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="14.265625" style="1" customWidth="1"/>
+    <col min="2" max="8" width="15.796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1303,16 +1303,16 @@
         <v>108319375668</v>
       </c>
       <c r="D2" s="1">
-        <v>107275365970</v>
+        <v>107767160029</v>
       </c>
       <c r="E2" s="1">
         <v>46437298</v>
       </c>
       <c r="F2" s="1">
-        <v>107321803268</v>
+        <v>107813597327</v>
       </c>
       <c r="G2" s="1">
-        <v>997572400</v>
+        <v>505778341</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
@@ -1349,10 +1349,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="1">
-        <v>40348220966</v>
+        <v>36976485833</v>
       </c>
       <c r="C4" s="1">
-        <v>40348220966</v>
+        <v>36976485833</v>
       </c>
       <c r="D4" s="1">
         <v>30600000000</v>
@@ -1364,7 +1364,7 @@
         <v>36000000000</v>
       </c>
       <c r="G4" s="1">
-        <v>4348220966</v>
+        <v>976485833</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
@@ -1459,16 +1459,16 @@
         <v>3726972261</v>
       </c>
       <c r="D8" s="1">
-        <v>3649807421</v>
+        <v>3648429493</v>
       </c>
       <c r="E8" s="1">
         <v>77164840</v>
       </c>
       <c r="F8" s="1">
-        <v>3726972261</v>
+        <v>3725594333</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>1377928</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -1615,16 +1615,16 @@
         <v>9802162250</v>
       </c>
       <c r="D14" s="1">
-        <v>3604880000</v>
+        <v>9098629250</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>3604880000</v>
+        <v>9098629250</v>
       </c>
       <c r="G14" s="1">
-        <v>6197282250</v>
+        <v>703533000</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -1719,10 +1719,10 @@
         <v>4500000000</v>
       </c>
       <c r="D18" s="1">
-        <v>411964419</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>1391432211</v>
+        <v>1803396630</v>
       </c>
       <c r="F18" s="1">
         <v>1803396630</v>
@@ -1771,16 +1771,16 @@
         <v>510385000</v>
       </c>
       <c r="D20" s="1">
-        <v>51703075</v>
+        <v>54873275</v>
       </c>
       <c r="E20" s="1">
         <v>52611240</v>
       </c>
       <c r="F20" s="1">
-        <v>104314315</v>
+        <v>107484515</v>
       </c>
       <c r="G20" s="1">
-        <v>406070685</v>
+        <v>402900485</v>
       </c>
       <c r="H20" s="1">
         <v>192500000</v>
@@ -1823,16 +1823,16 @@
         <v>622597314</v>
       </c>
       <c r="D22" s="1">
-        <v>106802794</v>
+        <v>518139520</v>
       </c>
       <c r="E22" s="1">
-        <v>0</v>
+        <v>95725294</v>
       </c>
       <c r="F22" s="1">
-        <v>106802794</v>
+        <v>613864814</v>
       </c>
       <c r="G22" s="1">
-        <v>515794520</v>
+        <v>8732500</v>
       </c>
       <c r="H22" s="1">
         <v>125000000</v>
@@ -1875,16 +1875,16 @@
         <v>1758555793</v>
       </c>
       <c r="D24" s="1">
-        <v>203293298</v>
+        <v>93542038</v>
       </c>
       <c r="E24" s="1">
-        <v>615082797</v>
+        <v>748802807</v>
       </c>
       <c r="F24" s="1">
-        <v>818376095</v>
+        <v>842344845</v>
       </c>
       <c r="G24" s="1">
-        <v>940179698</v>
+        <v>916210948</v>
       </c>
       <c r="H24" s="1">
         <v>625000000</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>1408183303</v>
+        <v>1755600895</v>
       </c>
       <c r="F27" s="1">
-        <v>1408183303</v>
+        <v>1755600895</v>
       </c>
       <c r="G27" s="1">
-        <v>2048430901</v>
+        <v>1701013309</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>24099495</v>
+        <v>32914812</v>
       </c>
       <c r="F28" s="1">
-        <v>24099495</v>
+        <v>32914812</v>
       </c>
       <c r="G28" s="1">
-        <v>28729128</v>
+        <v>19913811</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>1654124227</v>
+        <v>1866408727</v>
       </c>
       <c r="F29" s="1">
-        <v>1654124227</v>
+        <v>1866408727</v>
       </c>
       <c r="G29" s="1">
-        <v>2424145808</v>
+        <v>2211861308</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>3424185765</v>
+        <v>3942404244</v>
       </c>
       <c r="F31" s="1">
-        <v>3424185765</v>
+        <v>3942404244</v>
       </c>
       <c r="G31" s="1">
-        <v>7523289490</v>
+        <v>7005071011</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>109921024</v>
+        <v>131299737</v>
       </c>
       <c r="F32" s="1">
-        <v>109921024</v>
+        <v>131299737</v>
       </c>
       <c r="G32" s="1">
-        <v>138168978</v>
+        <v>116790265</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>4898235133</v>
+        <v>5505846633</v>
       </c>
       <c r="F33" s="1">
-        <v>4898235133</v>
+        <v>5505846633</v>
       </c>
       <c r="G33" s="1">
-        <v>9071830913</v>
+        <v>8464219413</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2259,22 +2259,22 @@
         <v>45</v>
       </c>
       <c r="B39" s="1">
-        <v>355784332764</v>
+        <v>352412597631</v>
       </c>
       <c r="C39" s="1">
-        <v>353366832764</v>
+        <v>349995097631</v>
       </c>
       <c r="D39" s="1">
-        <v>235321014107</v>
+        <v>241197970735</v>
       </c>
       <c r="E39" s="1">
-        <v>67440094284</v>
+        <v>69797230108</v>
       </c>
       <c r="F39" s="1">
-        <v>302761108391</v>
+        <v>310995200843</v>
       </c>
       <c r="G39" s="1">
-        <v>50605724373</v>
+        <v>38999896788</v>
       </c>
       <c r="H39" s="1">
         <v>2417500000</v>
@@ -2291,16 +2291,16 @@
         <v>25194775704</v>
       </c>
       <c r="D40" s="1">
-        <v>19851866530</v>
+        <v>21258870770</v>
       </c>
       <c r="E40" s="1">
         <v>3568529000</v>
       </c>
       <c r="F40" s="1">
-        <v>23420395530</v>
+        <v>24827399770</v>
       </c>
       <c r="G40" s="1">
-        <v>1774380174</v>
+        <v>367375934</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -2525,16 +2525,16 @@
         <v>1300000000</v>
       </c>
       <c r="D49" s="1">
-        <v>456944400</v>
+        <v>928382636</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
       </c>
       <c r="F49" s="1">
-        <v>456944400</v>
+        <v>928382636</v>
       </c>
       <c r="G49" s="1">
-        <v>843055600</v>
+        <v>371617364</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
@@ -2551,16 +2551,16 @@
         <v>6000000000</v>
       </c>
       <c r="D50" s="1">
-        <v>2027275226</v>
+        <v>4456872739</v>
       </c>
       <c r="E50" s="1">
         <v>520835965</v>
       </c>
       <c r="F50" s="1">
-        <v>2548111191</v>
+        <v>4977708704</v>
       </c>
       <c r="G50" s="1">
-        <v>3451888809</v>
+        <v>1022291296</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -2577,16 +2577,16 @@
         <v>4260000000</v>
       </c>
       <c r="D51" s="1">
-        <v>1476751248</v>
+        <v>1336601748</v>
       </c>
       <c r="E51" s="1">
-        <v>770878553</v>
+        <v>1218256553</v>
       </c>
       <c r="F51" s="1">
-        <v>2247629801</v>
+        <v>2554858301</v>
       </c>
       <c r="G51" s="1">
-        <v>2012370199</v>
+        <v>1705141699</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -2681,16 +2681,16 @@
         <v>6850000000</v>
       </c>
       <c r="D55" s="1">
-        <v>4461217920</v>
+        <v>4498321280</v>
       </c>
       <c r="E55" s="1">
         <v>306945460</v>
       </c>
       <c r="F55" s="1">
-        <v>4768163380</v>
+        <v>4805266740</v>
       </c>
       <c r="G55" s="1">
-        <v>2081836620</v>
+        <v>2044733260</v>
       </c>
       <c r="H55" s="1">
         <v>0</v>
@@ -2707,16 +2707,16 @@
         <v>2620000000</v>
       </c>
       <c r="D56" s="1">
-        <v>682796367</v>
+        <v>632438367</v>
       </c>
       <c r="E56" s="1">
-        <v>277142000</v>
+        <v>377142000</v>
       </c>
       <c r="F56" s="1">
-        <v>959938367</v>
+        <v>1009580367</v>
       </c>
       <c r="G56" s="1">
-        <v>1660061633</v>
+        <v>1610419633</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -2866,13 +2866,13 @@
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>1177480517</v>
+        <v>1446333891</v>
       </c>
       <c r="F62" s="1">
-        <v>1177480517</v>
+        <v>1446333891</v>
       </c>
       <c r="G62" s="1">
-        <v>2322519483</v>
+        <v>2053666109</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
@@ -2889,16 +2889,16 @@
         <v>417000000</v>
       </c>
       <c r="D63" s="1">
-        <v>119904664</v>
+        <v>125424200</v>
       </c>
       <c r="E63" s="1">
-        <v>83141758</v>
+        <v>93752722</v>
       </c>
       <c r="F63" s="1">
-        <v>203046422</v>
+        <v>219176922</v>
       </c>
       <c r="G63" s="1">
-        <v>213953578</v>
+        <v>197823078</v>
       </c>
       <c r="H63" s="1">
         <v>139000000</v>
@@ -2915,16 +2915,16 @@
         <v>335175000</v>
       </c>
       <c r="D64" s="1">
-        <v>111036111</v>
+        <v>105264609</v>
       </c>
       <c r="E64" s="1">
-        <v>109730916</v>
+        <v>124168416</v>
       </c>
       <c r="F64" s="1">
-        <v>220767027</v>
+        <v>229433025</v>
       </c>
       <c r="G64" s="1">
-        <v>114407973</v>
+        <v>105741975</v>
       </c>
       <c r="H64" s="1">
         <v>111725000</v>
@@ -2967,16 +2967,16 @@
         <v>608104500</v>
       </c>
       <c r="D66" s="1">
-        <v>97296720</v>
+        <v>144996720</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
       </c>
       <c r="F66" s="1">
-        <v>97296720</v>
+        <v>144996720</v>
       </c>
       <c r="G66" s="1">
-        <v>510807780</v>
+        <v>463107780</v>
       </c>
       <c r="H66" s="1">
         <v>202701500</v>
@@ -3022,13 +3022,13 @@
         <v>56676000</v>
       </c>
       <c r="E68" s="1">
-        <v>158651750</v>
+        <v>183381750</v>
       </c>
       <c r="F68" s="1">
-        <v>215327750</v>
+        <v>240057750</v>
       </c>
       <c r="G68" s="1">
-        <v>138897250</v>
+        <v>114167250</v>
       </c>
       <c r="H68" s="1">
         <v>118075000</v>
@@ -3045,10 +3045,10 @@
         <v>80000000</v>
       </c>
       <c r="D69" s="1">
-        <v>11100000</v>
+        <v>9600000</v>
       </c>
       <c r="E69" s="1">
-        <v>35332700</v>
+        <v>36832700</v>
       </c>
       <c r="F69" s="1">
         <v>46432700</v>
@@ -3100,13 +3100,13 @@
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>9372537685</v>
+        <v>11033259293</v>
       </c>
       <c r="F71" s="1">
-        <v>9372537685</v>
+        <v>11033259293</v>
       </c>
       <c r="G71" s="1">
-        <v>13559069544</v>
+        <v>11898347936</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -3126,13 +3126,13 @@
         <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>220535518</v>
+        <v>263841279</v>
       </c>
       <c r="F72" s="1">
-        <v>220535518</v>
+        <v>263841279</v>
       </c>
       <c r="G72" s="1">
-        <v>384419639</v>
+        <v>341113878</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -3152,13 +3152,13 @@
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>8892632944</v>
+        <v>9664725944</v>
       </c>
       <c r="F73" s="1">
-        <v>8892632944</v>
+        <v>9664725944</v>
       </c>
       <c r="G73" s="1">
-        <v>12074788586</v>
+        <v>11302695586</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -3204,13 +3204,13 @@
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>727711050</v>
+        <v>855595328</v>
       </c>
       <c r="F75" s="1">
-        <v>727711050</v>
+        <v>855595328</v>
       </c>
       <c r="G75" s="1">
-        <v>921715535</v>
+        <v>793831257</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -3230,13 +3230,13 @@
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>27410976</v>
+        <v>32902472</v>
       </c>
       <c r="F76" s="1">
-        <v>27410976</v>
+        <v>32902472</v>
       </c>
       <c r="G76" s="1">
-        <v>26249147</v>
+        <v>20757651</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>888796953</v>
+        <v>990659453</v>
       </c>
       <c r="F77" s="1">
-        <v>888796953</v>
+        <v>990659453</v>
       </c>
       <c r="G77" s="1">
-        <v>1048321575</v>
+        <v>946459075</v>
       </c>
       <c r="H77" s="1">
         <v>0</v>
@@ -3331,16 +3331,16 @@
         <v>110897810191</v>
       </c>
       <c r="D80" s="1">
-        <v>33499519195</v>
+        <v>37700103078</v>
       </c>
       <c r="E80" s="1">
-        <v>27324965207</v>
+        <v>30903833688</v>
       </c>
       <c r="F80" s="1">
-        <v>60824484402</v>
+        <v>68603936766</v>
       </c>
       <c r="G80" s="1">
-        <v>50073325789</v>
+        <v>42293873425</v>
       </c>
       <c r="H80" s="1">
         <v>671501500</v>
@@ -3357,10 +3357,10 @@
         <v>4044107500</v>
       </c>
       <c r="D81" s="1">
-        <v>1134017200</v>
+        <v>260296000</v>
       </c>
       <c r="E81" s="1">
-        <v>2899911000</v>
+        <v>3773632200</v>
       </c>
       <c r="F81" s="1">
         <v>4033928200</v>
@@ -3435,16 +3435,16 @@
         <v>30639775739</v>
       </c>
       <c r="D84" s="1">
-        <v>17344849790</v>
+        <v>17703310896</v>
       </c>
       <c r="E84" s="1">
         <v>7827327106</v>
       </c>
       <c r="F84" s="1">
-        <v>25172176896</v>
+        <v>25530638002</v>
       </c>
       <c r="G84" s="1">
-        <v>5467598843</v>
+        <v>5109137737</v>
       </c>
       <c r="H84" s="1">
         <v>0</v>
@@ -3565,16 +3565,16 @@
         <v>2796520000</v>
       </c>
       <c r="D89" s="1">
-        <v>544849034</v>
+        <v>562935834</v>
       </c>
       <c r="E89" s="1">
-        <v>1532824603</v>
+        <v>1619349003</v>
       </c>
       <c r="F89" s="1">
-        <v>2077673637</v>
+        <v>2182284837</v>
       </c>
       <c r="G89" s="1">
-        <v>718846363</v>
+        <v>614235163</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -3643,16 +3643,16 @@
         <v>400000000</v>
       </c>
       <c r="D92" s="1">
-        <v>110683500</v>
+        <v>116598400</v>
       </c>
       <c r="E92" s="1">
         <v>150059977</v>
       </c>
       <c r="F92" s="1">
-        <v>260743477</v>
+        <v>266658377</v>
       </c>
       <c r="G92" s="1">
-        <v>139256523</v>
+        <v>133341623</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -3721,16 +3721,16 @@
         <v>1710494400</v>
       </c>
       <c r="D95" s="1">
-        <v>1034894280</v>
+        <v>686359280</v>
       </c>
       <c r="E95" s="1">
-        <v>187253506</v>
+        <v>536888506</v>
       </c>
       <c r="F95" s="1">
-        <v>1222147786</v>
+        <v>1223247786</v>
       </c>
       <c r="G95" s="1">
-        <v>488346614</v>
+        <v>487246614</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -3773,16 +3773,16 @@
         <v>419475000</v>
       </c>
       <c r="D97" s="1">
-        <v>130154000</v>
+        <v>140201000</v>
       </c>
       <c r="E97" s="1">
         <v>39327850</v>
       </c>
       <c r="F97" s="1">
-        <v>169481850</v>
+        <v>179528850</v>
       </c>
       <c r="G97" s="1">
-        <v>249993150</v>
+        <v>239946150</v>
       </c>
       <c r="H97" s="1">
         <v>139825000</v>
@@ -3799,16 +3799,16 @@
         <v>255960000</v>
       </c>
       <c r="D98" s="1">
-        <v>102292900</v>
+        <v>116992900</v>
       </c>
       <c r="E98" s="1">
-        <v>90926500</v>
+        <v>95926500</v>
       </c>
       <c r="F98" s="1">
-        <v>193219400</v>
+        <v>212919400</v>
       </c>
       <c r="G98" s="1">
-        <v>62740600</v>
+        <v>43040600</v>
       </c>
       <c r="H98" s="1">
         <v>85320000</v>
@@ -3851,16 +3851,16 @@
         <v>291600000</v>
       </c>
       <c r="D100" s="1">
-        <v>70800000</v>
+        <v>97394900</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
       </c>
       <c r="F100" s="1">
-        <v>70800000</v>
+        <v>97394900</v>
       </c>
       <c r="G100" s="1">
-        <v>220800000</v>
+        <v>194205100</v>
       </c>
       <c r="H100" s="1">
         <v>97200000</v>
@@ -3929,10 +3929,10 @@
         <v>91080000</v>
       </c>
       <c r="D103" s="1">
-        <v>50807400</v>
+        <v>11880000</v>
       </c>
       <c r="E103" s="1">
-        <v>0</v>
+        <v>38927400</v>
       </c>
       <c r="F103" s="1">
         <v>50807400</v>
@@ -4036,13 +4036,13 @@
         <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>6713688684</v>
+        <v>8061542393</v>
       </c>
       <c r="F107" s="1">
-        <v>6713688684</v>
+        <v>8061542393</v>
       </c>
       <c r="G107" s="1">
-        <v>9509956169</v>
+        <v>8162102460</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -4062,13 +4062,13 @@
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>82611752</v>
+        <v>98408130</v>
       </c>
       <c r="F108" s="1">
-        <v>82611752</v>
+        <v>98408130</v>
       </c>
       <c r="G108" s="1">
-        <v>118979310</v>
+        <v>103182932</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
@@ -4088,13 +4088,13 @@
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>6425542005</v>
+        <v>6946507338</v>
       </c>
       <c r="F109" s="1">
-        <v>6425542005</v>
+        <v>6946507338</v>
       </c>
       <c r="G109" s="1">
-        <v>8072637943</v>
+        <v>7551672610</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
@@ -4140,13 +4140,13 @@
         <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>550321338</v>
+        <v>648492006</v>
       </c>
       <c r="F111" s="1">
-        <v>550321338</v>
+        <v>648492006</v>
       </c>
       <c r="G111" s="1">
-        <v>1414151658</v>
+        <v>1315980990</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -4166,13 +4166,13 @@
         <v>0</v>
       </c>
       <c r="E112" s="1">
-        <v>16781055</v>
+        <v>20146384</v>
       </c>
       <c r="F112" s="1">
-        <v>16781055</v>
+        <v>20146384</v>
       </c>
       <c r="G112" s="1">
-        <v>24131561</v>
+        <v>20766232</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -4192,13 +4192,13 @@
         <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>717492570</v>
+        <v>803417570</v>
       </c>
       <c r="F113" s="1">
-        <v>717492570</v>
+        <v>803417570</v>
       </c>
       <c r="G113" s="1">
-        <v>1211168304</v>
+        <v>1125243304</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -4241,16 +4241,16 @@
         <v>81718644736</v>
       </c>
       <c r="D115" s="1">
-        <v>20909876531</v>
+        <v>20082497637</v>
       </c>
       <c r="E115" s="1">
-        <v>28730957184</v>
+        <v>32156841601</v>
       </c>
       <c r="F115" s="1">
-        <v>49640833715</v>
+        <v>52239339238</v>
       </c>
       <c r="G115" s="1">
-        <v>32077811021</v>
+        <v>29479305498</v>
       </c>
       <c r="H115" s="1">
         <v>475697500</v>
@@ -4267,10 +4267,10 @@
         <v>8995670000</v>
       </c>
       <c r="D116" s="1">
-        <v>5740822700</v>
+        <v>5252712520</v>
       </c>
       <c r="E116" s="1">
-        <v>2043913612</v>
+        <v>2532023792</v>
       </c>
       <c r="F116" s="1">
         <v>7784736312</v>
@@ -4293,16 +4293,16 @@
         <v>435680000</v>
       </c>
       <c r="D117" s="1">
-        <v>0</v>
+        <v>39345200</v>
       </c>
       <c r="E117" s="1">
         <v>88238511</v>
       </c>
       <c r="F117" s="1">
-        <v>88238511</v>
+        <v>127583711</v>
       </c>
       <c r="G117" s="1">
-        <v>347441489</v>
+        <v>308096289</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>1665000000</v>
       </c>
       <c r="D123" s="1">
-        <v>214186905</v>
+        <v>203599905</v>
       </c>
       <c r="E123" s="1">
-        <v>411335837</v>
+        <v>421922837</v>
       </c>
       <c r="F123" s="1">
         <v>625522742</v>
@@ -4527,16 +4527,16 @@
         <v>2233168000</v>
       </c>
       <c r="D126" s="1">
-        <v>1460344748</v>
+        <v>1454935000</v>
       </c>
       <c r="E126" s="1">
-        <v>746780696</v>
+        <v>759375444</v>
       </c>
       <c r="F126" s="1">
-        <v>2207125444</v>
+        <v>2214310444</v>
       </c>
       <c r="G126" s="1">
-        <v>26042556</v>
+        <v>18857556</v>
       </c>
       <c r="H126" s="1">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>528750000</v>
       </c>
       <c r="D130" s="1">
+        <v>0</v>
+      </c>
+      <c r="E130" s="1">
         <v>491500000</v>
-      </c>
-      <c r="E130" s="1">
-        <v>0</v>
       </c>
       <c r="F130" s="1">
         <v>491500000</v>
@@ -4657,10 +4657,10 @@
         <v>118875000</v>
       </c>
       <c r="D131" s="1">
-        <v>31675900</v>
+        <v>28885900</v>
       </c>
       <c r="E131" s="1">
-        <v>30339500</v>
+        <v>33129500</v>
       </c>
       <c r="F131" s="1">
         <v>62015400</v>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="E132" s="1">
-        <v>801245795</v>
+        <v>967128932</v>
       </c>
       <c r="F132" s="1">
-        <v>801245795</v>
+        <v>967128932</v>
       </c>
       <c r="G132" s="1">
-        <v>1458754205</v>
+        <v>1292871068</v>
       </c>
       <c r="H132" s="1">
         <v>0</v>
@@ -4735,16 +4735,16 @@
         <v>265950000</v>
       </c>
       <c r="D134" s="1">
-        <v>19900000</v>
+        <v>15494900</v>
       </c>
       <c r="E134" s="1">
-        <v>124064300</v>
+        <v>129464300</v>
       </c>
       <c r="F134" s="1">
-        <v>143964300</v>
+        <v>144959200</v>
       </c>
       <c r="G134" s="1">
-        <v>121985700</v>
+        <v>120990800</v>
       </c>
       <c r="H134" s="1">
         <v>88650000</v>
@@ -4787,16 +4787,16 @@
         <v>203550000</v>
       </c>
       <c r="D136" s="1">
-        <v>34112000</v>
+        <v>55041500</v>
       </c>
       <c r="E136" s="1">
-        <v>92753500</v>
+        <v>120385932</v>
       </c>
       <c r="F136" s="1">
-        <v>126865500</v>
+        <v>175427432</v>
       </c>
       <c r="G136" s="1">
-        <v>76684500</v>
+        <v>28122568</v>
       </c>
       <c r="H136" s="1">
         <v>67850000</v>
@@ -4816,13 +4816,13 @@
         <v>0</v>
       </c>
       <c r="E137" s="1">
-        <v>97342250</v>
+        <v>98367250</v>
       </c>
       <c r="F137" s="1">
-        <v>97342250</v>
+        <v>98367250</v>
       </c>
       <c r="G137" s="1">
-        <v>62647750</v>
+        <v>61622750</v>
       </c>
       <c r="H137" s="1">
         <v>53330000</v>
@@ -4894,13 +4894,13 @@
         <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>4014625467</v>
+        <v>4728277928</v>
       </c>
       <c r="F140" s="1">
-        <v>4014625467</v>
+        <v>4728277928</v>
       </c>
       <c r="G140" s="1">
-        <v>5934468616</v>
+        <v>5220816155</v>
       </c>
       <c r="H140" s="1">
         <v>0</v>
@@ -4920,13 +4920,13 @@
         <v>0</v>
       </c>
       <c r="E141" s="1">
-        <v>160207011</v>
+        <v>192290838</v>
       </c>
       <c r="F141" s="1">
-        <v>160207011</v>
+        <v>192290838</v>
       </c>
       <c r="G141" s="1">
-        <v>226358391</v>
+        <v>194274564</v>
       </c>
       <c r="H141" s="1">
         <v>0</v>
@@ -4946,13 +4946,13 @@
         <v>0</v>
       </c>
       <c r="E142" s="1">
-        <v>4055636096</v>
+        <v>4403618596</v>
       </c>
       <c r="F142" s="1">
-        <v>4055636096</v>
+        <v>4403618596</v>
       </c>
       <c r="G142" s="1">
-        <v>5714213795</v>
+        <v>5366231295</v>
       </c>
       <c r="H142" s="1">
         <v>0</v>
@@ -4998,13 +4998,13 @@
         <v>0</v>
       </c>
       <c r="E144" s="1">
-        <v>404076153</v>
+        <v>477550123</v>
       </c>
       <c r="F144" s="1">
-        <v>404076153</v>
+        <v>477550123</v>
       </c>
       <c r="G144" s="1">
-        <v>1004435850</v>
+        <v>930961880</v>
       </c>
       <c r="H144" s="1">
         <v>0</v>
@@ -5024,13 +5024,13 @@
         <v>0</v>
       </c>
       <c r="E145" s="1">
-        <v>10781770</v>
+        <v>12938124</v>
       </c>
       <c r="F145" s="1">
-        <v>10781770</v>
+        <v>12938124</v>
       </c>
       <c r="G145" s="1">
-        <v>27537619</v>
+        <v>25381265</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
@@ -5050,13 +5050,13 @@
         <v>0</v>
       </c>
       <c r="E146" s="1">
-        <v>515582044</v>
+        <v>573602044</v>
       </c>
       <c r="F146" s="1">
-        <v>515582044</v>
+        <v>573602044</v>
       </c>
       <c r="G146" s="1">
-        <v>814735495</v>
+        <v>756715495</v>
       </c>
       <c r="H146" s="1">
         <v>0</v>
@@ -5125,16 +5125,16 @@
         <v>50726099717</v>
       </c>
       <c r="D149" s="1">
-        <v>11931707784</v>
+        <v>10989180456</v>
       </c>
       <c r="E149" s="1">
-        <v>18074705920</v>
+        <v>20507597529</v>
       </c>
       <c r="F149" s="1">
-        <v>30006413704</v>
+        <v>31496777985</v>
       </c>
       <c r="G149" s="1">
-        <v>20719686013</v>
+        <v>19229321732</v>
       </c>
       <c r="H149" s="1">
         <v>411080000</v>
@@ -5151,10 +5151,10 @@
         <v>11383511000</v>
       </c>
       <c r="D150" s="1">
-        <v>8020426052</v>
+        <v>6184426052</v>
       </c>
       <c r="E150" s="1">
-        <v>2404465838</v>
+        <v>4240465838</v>
       </c>
       <c r="F150" s="1">
         <v>10424891890</v>
@@ -5255,10 +5255,10 @@
         <v>870437000</v>
       </c>
       <c r="D154" s="1">
-        <v>620820000</v>
+        <v>172820000</v>
       </c>
       <c r="E154" s="1">
-        <v>78892000</v>
+        <v>526892000</v>
       </c>
       <c r="F154" s="1">
         <v>699712000</v>
@@ -5359,16 +5359,16 @@
         <v>996956000</v>
       </c>
       <c r="D158" s="1">
-        <v>526765158</v>
+        <v>541984090</v>
       </c>
       <c r="E158" s="1">
         <v>8750000</v>
       </c>
       <c r="F158" s="1">
-        <v>535515158</v>
+        <v>550734090</v>
       </c>
       <c r="G158" s="1">
-        <v>461440842</v>
+        <v>446221910</v>
       </c>
       <c r="H158" s="1">
         <v>0</v>
@@ -5596,13 +5596,13 @@
         <v>0</v>
       </c>
       <c r="E167" s="1">
-        <v>839823475</v>
+        <v>1021791897</v>
       </c>
       <c r="F167" s="1">
-        <v>839823475</v>
+        <v>1021791897</v>
       </c>
       <c r="G167" s="1">
-        <v>1529176525</v>
+        <v>1347208103</v>
       </c>
       <c r="H167" s="1">
         <v>0</v>
@@ -5619,16 +5619,16 @@
         <v>135000000</v>
       </c>
       <c r="D168" s="1">
-        <v>15000000</v>
+        <v>20000000</v>
       </c>
       <c r="E168" s="1">
         <v>21244591</v>
       </c>
       <c r="F168" s="1">
-        <v>36244591</v>
+        <v>41244591</v>
       </c>
       <c r="G168" s="1">
-        <v>98755409</v>
+        <v>93755409</v>
       </c>
       <c r="H168" s="1">
         <v>45000000</v>
@@ -5645,16 +5645,16 @@
         <v>408750000</v>
       </c>
       <c r="D169" s="1">
-        <v>69429600</v>
+        <v>98178350</v>
       </c>
       <c r="E169" s="1">
         <v>149383644</v>
       </c>
       <c r="F169" s="1">
-        <v>218813244</v>
+        <v>247561994</v>
       </c>
       <c r="G169" s="1">
-        <v>189936756</v>
+        <v>161188006</v>
       </c>
       <c r="H169" s="1">
         <v>136250000</v>
@@ -5752,13 +5752,13 @@
         <v>0</v>
       </c>
       <c r="E173" s="1">
-        <v>81434750</v>
+        <v>83109750</v>
       </c>
       <c r="F173" s="1">
-        <v>81434750</v>
+        <v>83109750</v>
       </c>
       <c r="G173" s="1">
-        <v>80866750</v>
+        <v>79191750</v>
       </c>
       <c r="H173" s="1">
         <v>54100500</v>
@@ -5804,13 +5804,13 @@
         <v>0</v>
       </c>
       <c r="E175" s="1">
-        <v>3009041688</v>
+        <v>3530399915</v>
       </c>
       <c r="F175" s="1">
-        <v>3009041688</v>
+        <v>3530399915</v>
       </c>
       <c r="G175" s="1">
-        <v>4495681690</v>
+        <v>3974323463</v>
       </c>
       <c r="H175" s="1">
         <v>0</v>
@@ -5830,13 +5830,13 @@
         <v>0</v>
       </c>
       <c r="E176" s="1">
-        <v>91584244</v>
+        <v>107638248</v>
       </c>
       <c r="F176" s="1">
-        <v>91584244</v>
+        <v>107638248</v>
       </c>
       <c r="G176" s="1">
-        <v>134751826</v>
+        <v>118697822</v>
       </c>
       <c r="H176" s="1">
         <v>0</v>
@@ -5856,13 +5856,13 @@
         <v>0</v>
       </c>
       <c r="E177" s="1">
-        <v>2860378666</v>
+        <v>3117486166</v>
       </c>
       <c r="F177" s="1">
-        <v>2860378666</v>
+        <v>3117486166</v>
       </c>
       <c r="G177" s="1">
-        <v>4468259834</v>
+        <v>4211152334</v>
       </c>
       <c r="H177" s="1">
         <v>0</v>
@@ -5908,13 +5908,13 @@
         <v>0</v>
       </c>
       <c r="E179" s="1">
-        <v>396560698</v>
+        <v>469983993</v>
       </c>
       <c r="F179" s="1">
-        <v>396560698</v>
+        <v>469983993</v>
       </c>
       <c r="G179" s="1">
-        <v>889458635</v>
+        <v>816035340</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0</v>
       </c>
       <c r="E180" s="1">
-        <v>11278248</v>
+        <v>12414117</v>
       </c>
       <c r="F180" s="1">
-        <v>11278248</v>
+        <v>12414117</v>
       </c>
       <c r="G180" s="1">
-        <v>25540492</v>
+        <v>24404623</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
@@ -5960,13 +5960,13 @@
         <v>0</v>
       </c>
       <c r="E181" s="1">
-        <v>504629542</v>
+        <v>564180542</v>
       </c>
       <c r="F181" s="1">
-        <v>504629542</v>
+        <v>564180542</v>
       </c>
       <c r="G181" s="1">
-        <v>866790367</v>
+        <v>807239367</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
@@ -6009,16 +6009,16 @@
         <v>46375593027</v>
       </c>
       <c r="D183" s="1">
-        <v>15638612625</v>
+        <v>13403580307</v>
       </c>
       <c r="E183" s="1">
-        <v>11992689583</v>
+        <v>15388962900</v>
       </c>
       <c r="F183" s="1">
-        <v>27631302208</v>
+        <v>28792543207</v>
       </c>
       <c r="G183" s="1">
-        <v>18744290819</v>
+        <v>17583049820</v>
       </c>
       <c r="H183" s="1">
         <v>449400500</v>
@@ -6133,22 +6133,22 @@
         <v>10</v>
       </c>
       <c r="B188" s="1">
-        <v>803320000</v>
+        <v>296447320</v>
       </c>
       <c r="C188" s="1">
-        <v>803320000</v>
+        <v>296447320</v>
       </c>
       <c r="D188" s="1">
-        <v>1200000</v>
+        <v>293960000</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
       </c>
       <c r="F188" s="1">
-        <v>1200000</v>
+        <v>293960000</v>
       </c>
       <c r="G188" s="1">
-        <v>802120000</v>
+        <v>2487320</v>
       </c>
       <c r="H188" s="1">
         <v>0</v>
@@ -6243,16 +6243,16 @@
         <v>469000000</v>
       </c>
       <c r="D192" s="1">
-        <v>0</v>
+        <v>4360000</v>
       </c>
       <c r="E192" s="1">
         <v>49635000</v>
       </c>
       <c r="F192" s="1">
-        <v>49635000</v>
+        <v>53995000</v>
       </c>
       <c r="G192" s="1">
-        <v>419365000</v>
+        <v>415005000</v>
       </c>
       <c r="H192" s="1">
         <v>0</v>
@@ -6269,16 +6269,16 @@
         <v>400000000</v>
       </c>
       <c r="D193" s="1">
-        <v>0</v>
+        <v>99076000</v>
       </c>
       <c r="E193" s="1">
         <v>51500000</v>
       </c>
       <c r="F193" s="1">
-        <v>51500000</v>
+        <v>150576000</v>
       </c>
       <c r="G193" s="1">
-        <v>348500000</v>
+        <v>249424000</v>
       </c>
       <c r="H193" s="1">
         <v>0</v>
@@ -6295,16 +6295,16 @@
         <v>609000000</v>
       </c>
       <c r="D194" s="1">
-        <v>357111350</v>
+        <v>365196350</v>
       </c>
       <c r="E194" s="1">
         <v>189017975</v>
       </c>
       <c r="F194" s="1">
-        <v>546129325</v>
+        <v>554214325</v>
       </c>
       <c r="G194" s="1">
-        <v>62870675</v>
+        <v>54785675</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
@@ -6321,10 +6321,10 @@
         <v>1862650000</v>
       </c>
       <c r="D195" s="1">
-        <v>408270210</v>
+        <v>403070210</v>
       </c>
       <c r="E195" s="1">
-        <v>925591089</v>
+        <v>930791089</v>
       </c>
       <c r="F195" s="1">
         <v>1333861299</v>
@@ -6347,16 +6347,16 @@
         <v>281000000</v>
       </c>
       <c r="D196" s="1">
-        <v>0</v>
+        <v>17423256</v>
       </c>
       <c r="E196" s="1">
         <v>30944688</v>
       </c>
       <c r="F196" s="1">
-        <v>30944688</v>
+        <v>48367944</v>
       </c>
       <c r="G196" s="1">
-        <v>250055312</v>
+        <v>232632056</v>
       </c>
       <c r="H196" s="1">
         <v>0</v>
@@ -6373,16 +6373,16 @@
         <v>950000000</v>
       </c>
       <c r="D197" s="1">
-        <v>0</v>
+        <v>455211278</v>
       </c>
       <c r="E197" s="1">
         <v>494525000</v>
       </c>
       <c r="F197" s="1">
-        <v>494525000</v>
+        <v>949736278</v>
       </c>
       <c r="G197" s="1">
-        <v>455475000</v>
+        <v>263722</v>
       </c>
       <c r="H197" s="1">
         <v>0</v>
@@ -6399,16 +6399,16 @@
         <v>50000000</v>
       </c>
       <c r="D198" s="1">
-        <v>12922000</v>
+        <v>18922000</v>
       </c>
       <c r="E198" s="1">
         <v>29582400</v>
       </c>
       <c r="F198" s="1">
-        <v>42504400</v>
+        <v>48504400</v>
       </c>
       <c r="G198" s="1">
-        <v>7495600</v>
+        <v>1495600</v>
       </c>
       <c r="H198" s="1">
         <v>0</v>
@@ -6419,22 +6419,22 @@
         <v>54</v>
       </c>
       <c r="B199" s="1">
-        <v>3843300000</v>
+        <v>4350172680</v>
       </c>
       <c r="C199" s="1">
-        <v>3843300000</v>
+        <v>4350172680</v>
       </c>
       <c r="D199" s="1">
-        <v>283993800</v>
+        <v>455775000</v>
       </c>
       <c r="E199" s="1">
         <v>1207281200</v>
       </c>
       <c r="F199" s="1">
-        <v>1491275000</v>
+        <v>1663056200</v>
       </c>
       <c r="G199" s="1">
-        <v>2352025000</v>
+        <v>2687116480</v>
       </c>
       <c r="H199" s="1">
         <v>0</v>
@@ -6555,16 +6555,16 @@
         <v>320100000</v>
       </c>
       <c r="D204" s="1">
-        <v>134900000</v>
+        <v>95100000</v>
       </c>
       <c r="E204" s="1">
-        <v>71775000</v>
+        <v>107075626</v>
       </c>
       <c r="F204" s="1">
-        <v>206675000</v>
+        <v>202175626</v>
       </c>
       <c r="G204" s="1">
-        <v>113425000</v>
+        <v>117924374</v>
       </c>
       <c r="H204" s="1">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0</v>
       </c>
       <c r="E205" s="1">
-        <v>967784129</v>
+        <v>1174562640</v>
       </c>
       <c r="F205" s="1">
-        <v>967784129</v>
+        <v>1174562640</v>
       </c>
       <c r="G205" s="1">
-        <v>1602215871</v>
+        <v>1395437360</v>
       </c>
       <c r="H205" s="1">
         <v>0</v>
@@ -6633,16 +6633,16 @@
         <v>385534500</v>
       </c>
       <c r="D207" s="1">
-        <v>67242500</v>
+        <v>114895500</v>
       </c>
       <c r="E207" s="1">
         <v>139976500</v>
       </c>
       <c r="F207" s="1">
-        <v>207219000</v>
+        <v>254872000</v>
       </c>
       <c r="G207" s="1">
-        <v>178315500</v>
+        <v>130662500</v>
       </c>
       <c r="H207" s="1">
         <v>128511500</v>
@@ -6685,16 +6685,16 @@
         <v>337500000</v>
       </c>
       <c r="D209" s="1">
-        <v>35173500</v>
+        <v>25705500</v>
       </c>
       <c r="E209" s="1">
-        <v>68789300</v>
+        <v>78165454</v>
       </c>
       <c r="F209" s="1">
-        <v>103962800</v>
+        <v>103870954</v>
       </c>
       <c r="G209" s="1">
-        <v>233537200</v>
+        <v>233629046</v>
       </c>
       <c r="H209" s="1">
         <v>112500000</v>
@@ -6740,13 +6740,13 @@
         <v>0</v>
       </c>
       <c r="E211" s="1">
-        <v>126093500</v>
+        <v>126287250</v>
       </c>
       <c r="F211" s="1">
-        <v>126093500</v>
+        <v>126287250</v>
       </c>
       <c r="G211" s="1">
-        <v>62906500</v>
+        <v>62712750</v>
       </c>
       <c r="H211" s="1">
         <v>63000000</v>
@@ -6789,16 +6789,16 @@
         <v>50000000</v>
       </c>
       <c r="D213" s="1">
-        <v>0</v>
+        <v>12505500</v>
       </c>
       <c r="E213" s="1">
         <v>12431950</v>
       </c>
       <c r="F213" s="1">
-        <v>12431950</v>
+        <v>24937450</v>
       </c>
       <c r="G213" s="1">
-        <v>37568050</v>
+        <v>25062550</v>
       </c>
       <c r="H213" s="1">
         <v>0</v>
@@ -6818,13 +6818,13 @@
         <v>0</v>
       </c>
       <c r="E214" s="1">
-        <v>3964964992</v>
+        <v>4664213020</v>
       </c>
       <c r="F214" s="1">
-        <v>3964964992</v>
+        <v>4664213020</v>
       </c>
       <c r="G214" s="1">
-        <v>5858197134</v>
+        <v>5158949106</v>
       </c>
       <c r="H214" s="1">
         <v>0</v>
@@ -6844,13 +6844,13 @@
         <v>0</v>
       </c>
       <c r="E215" s="1">
-        <v>98787681</v>
+        <v>117978898</v>
       </c>
       <c r="F215" s="1">
-        <v>98787681</v>
+        <v>117978898</v>
       </c>
       <c r="G215" s="1">
-        <v>154469290</v>
+        <v>135278073</v>
       </c>
       <c r="H215" s="1">
         <v>0</v>
@@ -6870,13 +6870,13 @@
         <v>0</v>
       </c>
       <c r="E216" s="1">
-        <v>3954276065</v>
+        <v>4288573565</v>
       </c>
       <c r="F216" s="1">
-        <v>3954276065</v>
+        <v>4288573565</v>
       </c>
       <c r="G216" s="1">
-        <v>5291399307</v>
+        <v>4957101807</v>
       </c>
       <c r="H216" s="1">
         <v>0</v>
@@ -6922,13 +6922,13 @@
         <v>0</v>
       </c>
       <c r="E218" s="1">
-        <v>400232406</v>
+        <v>460918581</v>
       </c>
       <c r="F218" s="1">
-        <v>400232406</v>
+        <v>460918581</v>
       </c>
       <c r="G218" s="1">
-        <v>311429663</v>
+        <v>250743488</v>
       </c>
       <c r="H218" s="1">
         <v>0</v>
@@ -6948,13 +6948,13 @@
         <v>0</v>
       </c>
       <c r="E219" s="1">
-        <v>16018805</v>
+        <v>19224063</v>
       </c>
       <c r="F219" s="1">
-        <v>16018805</v>
+        <v>19224063</v>
       </c>
       <c r="G219" s="1">
-        <v>8683657</v>
+        <v>5478399</v>
       </c>
       <c r="H219" s="1">
         <v>0</v>
@@ -6974,13 +6974,13 @@
         <v>0</v>
       </c>
       <c r="E220" s="1">
-        <v>496508560</v>
+        <v>552903560</v>
       </c>
       <c r="F220" s="1">
-        <v>496508560</v>
+        <v>552903560</v>
       </c>
       <c r="G220" s="1">
-        <v>328657373</v>
+        <v>272262373</v>
       </c>
       <c r="H220" s="1">
         <v>0</v>
@@ -7023,16 +7023,16 @@
         <v>47499233545</v>
       </c>
       <c r="D222" s="1">
-        <v>10293663335</v>
+        <v>11354050569</v>
       </c>
       <c r="E222" s="1">
-        <v>14857234321</v>
+        <v>16287106540</v>
       </c>
       <c r="F222" s="1">
-        <v>25150897656</v>
+        <v>27641157109</v>
       </c>
       <c r="G222" s="1">
-        <v>22348335889</v>
+        <v>19858076436</v>
       </c>
       <c r="H222" s="1">
         <v>415261500</v>
@@ -7049,16 +7049,16 @@
         <v>12264606000</v>
       </c>
       <c r="D223" s="1">
-        <v>10025558730</v>
+        <v>9595108730</v>
       </c>
       <c r="E223" s="1">
-        <v>1053550000</v>
+        <v>1475580000</v>
       </c>
       <c r="F223" s="1">
-        <v>11079108730</v>
+        <v>11070688730</v>
       </c>
       <c r="G223" s="1">
-        <v>1185497270</v>
+        <v>1193917270</v>
       </c>
       <c r="H223" s="1">
         <v>0</v>
@@ -7101,16 +7101,16 @@
         <v>100000000</v>
       </c>
       <c r="D225" s="1">
-        <v>0</v>
+        <v>49998822</v>
       </c>
       <c r="E225" s="1">
         <v>0</v>
       </c>
       <c r="F225" s="1">
-        <v>0</v>
+        <v>49998822</v>
       </c>
       <c r="G225" s="1">
-        <v>100000000</v>
+        <v>50001178</v>
       </c>
       <c r="H225" s="1">
         <v>0</v>
@@ -7179,16 +7179,16 @@
         <v>1310391000</v>
       </c>
       <c r="D228" s="1">
-        <v>0</v>
+        <v>780300579</v>
       </c>
       <c r="E228" s="1">
         <v>135761588</v>
       </c>
       <c r="F228" s="1">
-        <v>135761588</v>
+        <v>916062167</v>
       </c>
       <c r="G228" s="1">
-        <v>1174629412</v>
+        <v>394328833</v>
       </c>
       <c r="H228" s="1">
         <v>0</v>
@@ -7205,16 +7205,16 @@
         <v>1380000000</v>
       </c>
       <c r="D229" s="1">
-        <v>99191500</v>
+        <v>154752855</v>
       </c>
       <c r="E229" s="1">
         <v>741651216</v>
       </c>
       <c r="F229" s="1">
-        <v>840842716</v>
+        <v>896404071</v>
       </c>
       <c r="G229" s="1">
-        <v>539157284</v>
+        <v>483595929</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
@@ -7361,10 +7361,10 @@
         <v>1155000000</v>
       </c>
       <c r="D235" s="1">
-        <v>502090950</v>
+        <v>484514950</v>
       </c>
       <c r="E235" s="1">
-        <v>485365000</v>
+        <v>502941000</v>
       </c>
       <c r="F235" s="1">
         <v>987455950</v>
@@ -7387,16 +7387,16 @@
         <v>780000000</v>
       </c>
       <c r="D236" s="1">
-        <v>0</v>
+        <v>51282000</v>
       </c>
       <c r="E236" s="1">
         <v>0</v>
       </c>
       <c r="F236" s="1">
-        <v>0</v>
+        <v>51282000</v>
       </c>
       <c r="G236" s="1">
-        <v>780000000</v>
+        <v>728718000</v>
       </c>
       <c r="H236" s="1">
         <v>260000000</v>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="E238" s="1">
-        <v>980074433</v>
+        <v>1188069768</v>
       </c>
       <c r="F238" s="1">
-        <v>980074433</v>
+        <v>1188069768</v>
       </c>
       <c r="G238" s="1">
-        <v>2083501567</v>
+        <v>1875506232</v>
       </c>
       <c r="H238" s="1">
         <v>0</v>
@@ -7465,16 +7465,16 @@
         <v>110162550</v>
       </c>
       <c r="D239" s="1">
-        <v>9595000</v>
+        <v>14575000</v>
       </c>
       <c r="E239" s="1">
         <v>36421000</v>
       </c>
       <c r="F239" s="1">
-        <v>46016000</v>
+        <v>50996000</v>
       </c>
       <c r="G239" s="1">
-        <v>64146550</v>
+        <v>59166550</v>
       </c>
       <c r="H239" s="1">
         <v>36720850</v>
@@ -7491,16 +7491,16 @@
         <v>354238500</v>
       </c>
       <c r="D240" s="1">
-        <v>71165932</v>
+        <v>81889432</v>
       </c>
       <c r="E240" s="1">
-        <v>179170400</v>
+        <v>192870400</v>
       </c>
       <c r="F240" s="1">
-        <v>250336332</v>
+        <v>274759832</v>
       </c>
       <c r="G240" s="1">
-        <v>103902168</v>
+        <v>79478668</v>
       </c>
       <c r="H240" s="1">
         <v>118079500</v>
@@ -7543,16 +7543,16 @@
         <v>732016185</v>
       </c>
       <c r="D242" s="1">
-        <v>14498000</v>
+        <v>16701000</v>
       </c>
       <c r="E242" s="1">
         <v>706940820</v>
       </c>
       <c r="F242" s="1">
-        <v>721438820</v>
+        <v>723641820</v>
       </c>
       <c r="G242" s="1">
-        <v>10577365</v>
+        <v>8374365</v>
       </c>
       <c r="H242" s="1">
         <v>42983815</v>
@@ -7572,13 +7572,13 @@
         <v>0</v>
       </c>
       <c r="E243" s="1">
-        <v>104942250</v>
+        <v>105492250</v>
       </c>
       <c r="F243" s="1">
-        <v>104942250</v>
+        <v>105492250</v>
       </c>
       <c r="G243" s="1">
-        <v>97341750</v>
+        <v>96791750</v>
       </c>
       <c r="H243" s="1">
         <v>67428000</v>
@@ -7624,13 +7624,13 @@
         <v>0</v>
       </c>
       <c r="E245" s="1">
-        <v>3956078296</v>
+        <v>4656573950</v>
       </c>
       <c r="F245" s="1">
-        <v>3956078296</v>
+        <v>4656573950</v>
       </c>
       <c r="G245" s="1">
-        <v>5869877874</v>
+        <v>5169382220</v>
       </c>
       <c r="H245" s="1">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0</v>
       </c>
       <c r="E246" s="1">
-        <v>204278520</v>
+        <v>245247184</v>
       </c>
       <c r="F246" s="1">
-        <v>204278520</v>
+        <v>245247184</v>
       </c>
       <c r="G246" s="1">
-        <v>265570058</v>
+        <v>224601394</v>
       </c>
       <c r="H246" s="1">
         <v>0</v>
@@ -7676,13 +7676,13 @@
         <v>0</v>
       </c>
       <c r="E247" s="1">
-        <v>3978411132</v>
+        <v>4317093632</v>
       </c>
       <c r="F247" s="1">
-        <v>3978411132</v>
+        <v>4317093632</v>
       </c>
       <c r="G247" s="1">
-        <v>5533694785</v>
+        <v>5195012285</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
@@ -7728,13 +7728,13 @@
         <v>0</v>
       </c>
       <c r="E249" s="1">
-        <v>429503771</v>
+        <v>498616367</v>
       </c>
       <c r="F249" s="1">
-        <v>429503771</v>
+        <v>498616367</v>
       </c>
       <c r="G249" s="1">
-        <v>565438790</v>
+        <v>496326194</v>
       </c>
       <c r="H249" s="1">
         <v>0</v>
@@ -7754,13 +7754,13 @@
         <v>0</v>
       </c>
       <c r="E250" s="1">
-        <v>17269551</v>
+        <v>20745071</v>
       </c>
       <c r="F250" s="1">
-        <v>17269551</v>
+        <v>20745071</v>
       </c>
       <c r="G250" s="1">
-        <v>16268808</v>
+        <v>12793288</v>
       </c>
       <c r="H250" s="1">
         <v>0</v>
@@ -7780,13 +7780,13 @@
         <v>0</v>
       </c>
       <c r="E251" s="1">
-        <v>513350939</v>
+        <v>571145939</v>
       </c>
       <c r="F251" s="1">
-        <v>513350939</v>
+        <v>571145939</v>
       </c>
       <c r="G251" s="1">
-        <v>586376395</v>
+        <v>528581395</v>
       </c>
       <c r="H251" s="1">
         <v>0</v>
@@ -7829,16 +7829,16 @@
         <v>48914772555</v>
       </c>
       <c r="D253" s="1">
-        <v>13670424618</v>
+        <v>14177447874</v>
       </c>
       <c r="E253" s="1">
-        <v>14356332808</v>
+        <v>16228714077</v>
       </c>
       <c r="F253" s="1">
-        <v>28026757426</v>
+        <v>30406161951</v>
       </c>
       <c r="G253" s="1">
-        <v>20888015129</v>
+        <v>18508610604</v>
       </c>
       <c r="H253" s="1">
         <v>525212165</v>
@@ -7881,16 +7881,16 @@
         <v>1540000000</v>
       </c>
       <c r="D255" s="1">
-        <v>476400000</v>
+        <v>947556189</v>
       </c>
       <c r="E255" s="1">
         <v>278199517</v>
       </c>
       <c r="F255" s="1">
-        <v>754599517</v>
+        <v>1225755706</v>
       </c>
       <c r="G255" s="1">
-        <v>785400483</v>
+        <v>314244294</v>
       </c>
       <c r="H255" s="1">
         <v>0</v>
@@ -7959,16 +7959,16 @@
         <v>875000000</v>
       </c>
       <c r="D258" s="1">
-        <v>678822622</v>
+        <v>667447822</v>
       </c>
       <c r="E258" s="1">
-        <v>25867900</v>
+        <v>35067900</v>
       </c>
       <c r="F258" s="1">
-        <v>704690522</v>
+        <v>702515722</v>
       </c>
       <c r="G258" s="1">
-        <v>170309478</v>
+        <v>172484278</v>
       </c>
       <c r="H258" s="1">
         <v>0</v>
@@ -7985,16 +7985,16 @@
         <v>3269982000</v>
       </c>
       <c r="D259" s="1">
-        <v>700693800</v>
+        <v>876067300</v>
       </c>
       <c r="E259" s="1">
-        <v>323010544</v>
+        <v>410255544</v>
       </c>
       <c r="F259" s="1">
-        <v>1023704344</v>
+        <v>1286322844</v>
       </c>
       <c r="G259" s="1">
-        <v>2246277656</v>
+        <v>1983659156</v>
       </c>
       <c r="H259" s="1">
         <v>0</v>
@@ -8037,16 +8037,16 @@
         <v>1700000000</v>
       </c>
       <c r="D261" s="1">
-        <v>54390700</v>
+        <v>92594900</v>
       </c>
       <c r="E261" s="1">
-        <v>634438355</v>
+        <v>652261855</v>
       </c>
       <c r="F261" s="1">
-        <v>688829055</v>
+        <v>744856755</v>
       </c>
       <c r="G261" s="1">
-        <v>1011170945</v>
+        <v>955143245</v>
       </c>
       <c r="H261" s="1">
         <v>0</v>
@@ -8115,16 +8115,16 @@
         <v>150000000</v>
       </c>
       <c r="D264" s="1">
-        <v>23232180</v>
+        <v>46982180</v>
       </c>
       <c r="E264" s="1">
         <v>0</v>
       </c>
       <c r="F264" s="1">
-        <v>23232180</v>
+        <v>46982180</v>
       </c>
       <c r="G264" s="1">
-        <v>126767820</v>
+        <v>103017820</v>
       </c>
       <c r="H264" s="1">
         <v>0</v>
@@ -8141,16 +8141,16 @@
         <v>2668302662</v>
       </c>
       <c r="D265" s="1">
-        <v>1273429000</v>
+        <v>1275139000</v>
       </c>
       <c r="E265" s="1">
-        <v>1262740000</v>
+        <v>1310330000</v>
       </c>
       <c r="F265" s="1">
-        <v>2536169000</v>
+        <v>2585469000</v>
       </c>
       <c r="G265" s="1">
-        <v>132133662</v>
+        <v>82833662</v>
       </c>
       <c r="H265" s="1">
         <v>0</v>
@@ -8271,16 +8271,16 @@
         <v>2260000000</v>
       </c>
       <c r="D270" s="1">
-        <v>870903229</v>
+        <v>896987669</v>
       </c>
       <c r="E270" s="1">
         <v>478228900</v>
       </c>
       <c r="F270" s="1">
-        <v>1349132129</v>
+        <v>1375216569</v>
       </c>
       <c r="G270" s="1">
-        <v>910867871</v>
+        <v>884783431</v>
       </c>
       <c r="H270" s="1">
         <v>0</v>
@@ -8349,16 +8349,16 @@
         <v>1242000000</v>
       </c>
       <c r="D273" s="1">
-        <v>942652365</v>
+        <v>979699725</v>
       </c>
       <c r="E273" s="1">
         <v>9999583</v>
       </c>
       <c r="F273" s="1">
-        <v>952651948</v>
+        <v>989699308</v>
       </c>
       <c r="G273" s="1">
-        <v>289348052</v>
+        <v>252300692</v>
       </c>
       <c r="H273" s="1">
         <v>0</v>
@@ -8430,13 +8430,13 @@
         <v>0</v>
       </c>
       <c r="E276" s="1">
-        <v>788955544</v>
+        <v>955086463</v>
       </c>
       <c r="F276" s="1">
-        <v>788955544</v>
+        <v>955086463</v>
       </c>
       <c r="G276" s="1">
-        <v>1163393748</v>
+        <v>997262829</v>
       </c>
       <c r="H276" s="1">
         <v>0</v>
@@ -8453,16 +8453,16 @@
         <v>62053350</v>
       </c>
       <c r="D277" s="1">
-        <v>6000000</v>
+        <v>12000000</v>
       </c>
       <c r="E277" s="1">
         <v>44925714</v>
       </c>
       <c r="F277" s="1">
-        <v>50925714</v>
+        <v>56925714</v>
       </c>
       <c r="G277" s="1">
-        <v>11127636</v>
+        <v>5127636</v>
       </c>
       <c r="H277" s="1">
         <v>20684450</v>
@@ -8479,16 +8479,16 @@
         <v>470406638</v>
       </c>
       <c r="D278" s="1">
-        <v>57880562</v>
+        <v>74117555</v>
       </c>
       <c r="E278" s="1">
         <v>197142333</v>
       </c>
       <c r="F278" s="1">
-        <v>255022895</v>
+        <v>271259888</v>
       </c>
       <c r="G278" s="1">
-        <v>215383743</v>
+        <v>199146750</v>
       </c>
       <c r="H278" s="1">
         <v>156802213</v>
@@ -8531,16 +8531,16 @@
         <v>707202000</v>
       </c>
       <c r="D280" s="1">
-        <v>321114000</v>
+        <v>306389783</v>
       </c>
       <c r="E280" s="1">
-        <v>70884500</v>
+        <v>87884500</v>
       </c>
       <c r="F280" s="1">
-        <v>391998500</v>
+        <v>394274283</v>
       </c>
       <c r="G280" s="1">
-        <v>315203500</v>
+        <v>312927717</v>
       </c>
       <c r="H280" s="1">
         <v>235734000</v>
@@ -8586,13 +8586,13 @@
         <v>826800</v>
       </c>
       <c r="E282" s="1">
-        <v>42459679</v>
+        <v>52039326</v>
       </c>
       <c r="F282" s="1">
-        <v>43286479</v>
+        <v>52866126</v>
       </c>
       <c r="G282" s="1">
-        <v>137857603</v>
+        <v>128277956</v>
       </c>
       <c r="H282" s="1">
         <v>0</v>
@@ -8664,13 +8664,13 @@
         <v>0</v>
       </c>
       <c r="E285" s="1">
-        <v>5058435584</v>
+        <v>5965704602</v>
       </c>
       <c r="F285" s="1">
-        <v>5058435584</v>
+        <v>5965704602</v>
       </c>
       <c r="G285" s="1">
-        <v>7564183343</v>
+        <v>6656914325</v>
       </c>
       <c r="H285" s="1">
         <v>0</v>
@@ -8690,13 +8690,13 @@
         <v>0</v>
       </c>
       <c r="E286" s="1">
-        <v>74152912</v>
+        <v>88540595</v>
       </c>
       <c r="F286" s="1">
-        <v>74152912</v>
+        <v>88540595</v>
       </c>
       <c r="G286" s="1">
-        <v>120895380</v>
+        <v>106507697</v>
       </c>
       <c r="H286" s="1">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0</v>
       </c>
       <c r="E287" s="1">
-        <v>5276620855</v>
+        <v>5731594355</v>
       </c>
       <c r="F287" s="1">
-        <v>5276620855</v>
+        <v>5731594355</v>
       </c>
       <c r="G287" s="1">
-        <v>7635096560</v>
+        <v>7180123060</v>
       </c>
       <c r="H287" s="1">
         <v>0</v>
@@ -8768,13 +8768,13 @@
         <v>0</v>
       </c>
       <c r="E289" s="1">
-        <v>469371119</v>
+        <v>540207690</v>
       </c>
       <c r="F289" s="1">
-        <v>469371119</v>
+        <v>540207690</v>
       </c>
       <c r="G289" s="1">
-        <v>791239536</v>
+        <v>720402965</v>
       </c>
       <c r="H289" s="1">
         <v>0</v>
@@ -8794,13 +8794,13 @@
         <v>0</v>
       </c>
       <c r="E290" s="1">
-        <v>11205065</v>
+        <v>13455196</v>
       </c>
       <c r="F290" s="1">
-        <v>11205065</v>
+        <v>13455196</v>
       </c>
       <c r="G290" s="1">
-        <v>16250736</v>
+        <v>14000605</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
@@ -8820,13 +8820,13 @@
         <v>0</v>
       </c>
       <c r="E291" s="1">
-        <v>613545690</v>
+        <v>687535690</v>
       </c>
       <c r="F291" s="1">
-        <v>613545690</v>
+        <v>687535690</v>
       </c>
       <c r="G291" s="1">
-        <v>946783147</v>
+        <v>872793147</v>
       </c>
       <c r="H291" s="1">
         <v>0</v>
@@ -8869,16 +8869,16 @@
         <v>63706784713</v>
       </c>
       <c r="D293" s="1">
-        <v>14894169464</v>
+        <v>15663633129</v>
       </c>
       <c r="E293" s="1">
-        <v>20073303330</v>
+        <v>21951579299</v>
       </c>
       <c r="F293" s="1">
-        <v>34967472794</v>
+        <v>37615212428</v>
       </c>
       <c r="G293" s="1">
-        <v>28739311919</v>
+        <v>26091572285</v>
       </c>
       <c r="H293" s="1">
         <v>531045413</v>
@@ -8921,10 +8921,10 @@
         <v>128850000</v>
       </c>
       <c r="D295" s="1">
-        <v>1613000</v>
+        <v>0</v>
       </c>
       <c r="E295" s="1">
-        <v>29680000</v>
+        <v>31293000</v>
       </c>
       <c r="F295" s="1">
         <v>31293000</v>
@@ -8947,16 +8947,16 @@
         <v>488774000</v>
       </c>
       <c r="D296" s="1">
-        <v>472749437</v>
+        <v>488679487</v>
       </c>
       <c r="E296" s="1">
         <v>0</v>
       </c>
       <c r="F296" s="1">
-        <v>472749437</v>
+        <v>488679487</v>
       </c>
       <c r="G296" s="1">
-        <v>16024563</v>
+        <v>94513</v>
       </c>
       <c r="H296" s="1">
         <v>0</v>
@@ -9077,10 +9077,10 @@
         <v>534300000</v>
       </c>
       <c r="D301" s="1">
-        <v>47115150</v>
+        <v>27525500</v>
       </c>
       <c r="E301" s="1">
-        <v>222839528</v>
+        <v>242429178</v>
       </c>
       <c r="F301" s="1">
         <v>269954678</v>
@@ -9181,16 +9181,16 @@
         <v>1882400000</v>
       </c>
       <c r="D305" s="1">
-        <v>1457701000</v>
+        <v>1463301000</v>
       </c>
       <c r="E305" s="1">
         <v>259764000</v>
       </c>
       <c r="F305" s="1">
-        <v>1717465000</v>
+        <v>1723065000</v>
       </c>
       <c r="G305" s="1">
-        <v>164935000</v>
+        <v>159335000</v>
       </c>
       <c r="H305" s="1">
         <v>0</v>
@@ -9207,16 +9207,16 @@
         <v>300000000</v>
       </c>
       <c r="D306" s="1">
-        <v>49281780</v>
+        <v>0</v>
       </c>
       <c r="E306" s="1">
         <v>27352000</v>
       </c>
       <c r="F306" s="1">
-        <v>76633780</v>
+        <v>27352000</v>
       </c>
       <c r="G306" s="1">
-        <v>223366220</v>
+        <v>272648000</v>
       </c>
       <c r="H306" s="1">
         <v>0</v>
@@ -9340,13 +9340,13 @@
         <v>0</v>
       </c>
       <c r="E311" s="1">
-        <v>692484040</v>
+        <v>847111419</v>
       </c>
       <c r="F311" s="1">
-        <v>692484040</v>
+        <v>847111419</v>
       </c>
       <c r="G311" s="1">
-        <v>1617515960</v>
+        <v>1462888581</v>
       </c>
       <c r="H311" s="1">
         <v>0</v>
@@ -9441,16 +9441,16 @@
         <v>385800000</v>
       </c>
       <c r="D315" s="1">
-        <v>34412000</v>
+        <v>83693780</v>
       </c>
       <c r="E315" s="1">
         <v>39634635</v>
       </c>
       <c r="F315" s="1">
-        <v>74046635</v>
+        <v>123328415</v>
       </c>
       <c r="G315" s="1">
-        <v>311753365</v>
+        <v>262471585</v>
       </c>
       <c r="H315" s="1">
         <v>128600000</v>
@@ -9470,13 +9470,13 @@
         <v>0</v>
       </c>
       <c r="E316" s="1">
-        <v>81786250</v>
+        <v>83380000</v>
       </c>
       <c r="F316" s="1">
-        <v>81786250</v>
+        <v>83380000</v>
       </c>
       <c r="G316" s="1">
-        <v>90713750</v>
+        <v>89120000</v>
       </c>
       <c r="H316" s="1">
         <v>57500000</v>
@@ -9522,13 +9522,13 @@
         <v>0</v>
       </c>
       <c r="E318" s="1">
-        <v>2753347136</v>
+        <v>3258571541</v>
       </c>
       <c r="F318" s="1">
-        <v>2753347136</v>
+        <v>3258571541</v>
       </c>
       <c r="G318" s="1">
-        <v>4300445129</v>
+        <v>3795220724</v>
       </c>
       <c r="H318" s="1">
         <v>0</v>
@@ -9548,13 +9548,13 @@
         <v>0</v>
       </c>
       <c r="E319" s="1">
-        <v>103733976</v>
+        <v>124515685</v>
       </c>
       <c r="F319" s="1">
-        <v>103733976</v>
+        <v>124515685</v>
       </c>
       <c r="G319" s="1">
-        <v>147167933</v>
+        <v>126386224</v>
       </c>
       <c r="H319" s="1">
         <v>0</v>
@@ -9574,13 +9574,13 @@
         <v>0</v>
       </c>
       <c r="E320" s="1">
-        <v>2925163505</v>
+        <v>3186308505</v>
       </c>
       <c r="F320" s="1">
-        <v>2925163505</v>
+        <v>3186308505</v>
       </c>
       <c r="G320" s="1">
-        <v>4089878916</v>
+        <v>3828733916</v>
       </c>
       <c r="H320" s="1">
         <v>0</v>
@@ -9626,13 +9626,13 @@
         <v>0</v>
       </c>
       <c r="E322" s="1">
-        <v>450702767</v>
+        <v>525161905</v>
       </c>
       <c r="F322" s="1">
-        <v>450702767</v>
+        <v>525161905</v>
       </c>
       <c r="G322" s="1">
-        <v>780509299</v>
+        <v>706050161</v>
       </c>
       <c r="H322" s="1">
         <v>0</v>
@@ -9652,13 +9652,13 @@
         <v>0</v>
       </c>
       <c r="E323" s="1">
-        <v>26780684</v>
+        <v>32168573</v>
       </c>
       <c r="F323" s="1">
-        <v>26780684</v>
+        <v>32168573</v>
       </c>
       <c r="G323" s="1">
-        <v>26655435</v>
+        <v>21267546</v>
       </c>
       <c r="H323" s="1">
         <v>0</v>
@@ -9678,13 +9678,13 @@
         <v>0</v>
       </c>
       <c r="E324" s="1">
-        <v>549255946</v>
+        <v>609963446</v>
       </c>
       <c r="F324" s="1">
-        <v>549255946</v>
+        <v>609963446</v>
       </c>
       <c r="G324" s="1">
-        <v>900456433</v>
+        <v>839748933</v>
       </c>
       <c r="H324" s="1">
         <v>0</v>
@@ -9727,16 +9727,16 @@
         <v>30454436960</v>
       </c>
       <c r="D326" s="1">
-        <v>5918840978</v>
+        <v>5919168378</v>
       </c>
       <c r="E326" s="1">
-        <v>10410072326</v>
+        <v>11515201746</v>
       </c>
       <c r="F326" s="1">
-        <v>16328913304</v>
+        <v>17434370124</v>
       </c>
       <c r="G326" s="1">
-        <v>14125523656</v>
+        <v>13020066836</v>
       </c>
       <c r="H326" s="1">
         <v>260139500</v>
@@ -9805,16 +9805,16 @@
         <v>447807006</v>
       </c>
       <c r="D329" s="1">
-        <v>447672269</v>
+        <v>439914019</v>
       </c>
       <c r="E329" s="1">
         <v>0</v>
       </c>
       <c r="F329" s="1">
-        <v>447672269</v>
+        <v>439914019</v>
       </c>
       <c r="G329" s="1">
-        <v>134737</v>
+        <v>7892987</v>
       </c>
       <c r="H329" s="1">
         <v>0</v>
@@ -9831,16 +9831,16 @@
         <v>1880742104</v>
       </c>
       <c r="D330" s="1">
-        <v>404003486</v>
+        <v>432899486</v>
       </c>
       <c r="E330" s="1">
         <v>1405666314</v>
       </c>
       <c r="F330" s="1">
-        <v>1809669800</v>
+        <v>1838565800</v>
       </c>
       <c r="G330" s="1">
-        <v>71072304</v>
+        <v>42176304</v>
       </c>
       <c r="H330" s="1">
         <v>0</v>
@@ -9909,10 +9909,10 @@
         <v>2791999194</v>
       </c>
       <c r="D333" s="1">
-        <v>375232632</v>
+        <v>366427928</v>
       </c>
       <c r="E333" s="1">
-        <v>898650975</v>
+        <v>907455679</v>
       </c>
       <c r="F333" s="1">
         <v>1273883607</v>
@@ -9935,10 +9935,10 @@
         <v>1660344000</v>
       </c>
       <c r="D334" s="1">
-        <v>405441460</v>
+        <v>319513610</v>
       </c>
       <c r="E334" s="1">
-        <v>741820428</v>
+        <v>827748278</v>
       </c>
       <c r="F334" s="1">
         <v>1147261888</v>
@@ -10065,16 +10065,16 @@
         <v>1000000000</v>
       </c>
       <c r="D339" s="1">
-        <v>707192300</v>
+        <v>696736500</v>
       </c>
       <c r="E339" s="1">
         <v>43200000</v>
       </c>
       <c r="F339" s="1">
-        <v>750392300</v>
+        <v>739936500</v>
       </c>
       <c r="G339" s="1">
-        <v>249607700</v>
+        <v>260063500</v>
       </c>
       <c r="H339" s="1">
         <v>0</v>
@@ -10143,16 +10143,16 @@
         <v>2911760000</v>
       </c>
       <c r="D342" s="1">
-        <v>298141944</v>
+        <v>292257770</v>
       </c>
       <c r="E342" s="1">
-        <v>1013062926</v>
+        <v>1243427907</v>
       </c>
       <c r="F342" s="1">
-        <v>1311204870</v>
+        <v>1535685677</v>
       </c>
       <c r="G342" s="1">
-        <v>1600555130</v>
+        <v>1376074323</v>
       </c>
       <c r="H342" s="1">
         <v>0</v>
@@ -10169,16 +10169,16 @@
         <v>135000000</v>
       </c>
       <c r="D343" s="1">
-        <v>12257200</v>
+        <v>18257198</v>
       </c>
       <c r="E343" s="1">
         <v>52037500</v>
       </c>
       <c r="F343" s="1">
-        <v>64294700</v>
+        <v>70294698</v>
       </c>
       <c r="G343" s="1">
-        <v>70705300</v>
+        <v>64705302</v>
       </c>
       <c r="H343" s="1">
         <v>45000000</v>
@@ -10195,16 +10195,16 @@
         <v>571079775</v>
       </c>
       <c r="D344" s="1">
-        <v>285748113</v>
+        <v>272502613</v>
       </c>
       <c r="E344" s="1">
-        <v>138870051</v>
+        <v>176091551</v>
       </c>
       <c r="F344" s="1">
-        <v>424618164</v>
+        <v>448594164</v>
       </c>
       <c r="G344" s="1">
-        <v>146461611</v>
+        <v>122485611</v>
       </c>
       <c r="H344" s="1">
         <v>190359925</v>
@@ -10247,16 +10247,16 @@
         <v>462375000</v>
       </c>
       <c r="D346" s="1">
-        <v>248114000</v>
+        <v>288214000</v>
       </c>
       <c r="E346" s="1">
         <v>54023971</v>
       </c>
       <c r="F346" s="1">
-        <v>302137971</v>
+        <v>342237971</v>
       </c>
       <c r="G346" s="1">
-        <v>160237029</v>
+        <v>120137029</v>
       </c>
       <c r="H346" s="1">
         <v>154125000</v>
@@ -10354,13 +10354,13 @@
         <v>0</v>
       </c>
       <c r="E350" s="1">
-        <v>4223848436</v>
+        <v>4966314368</v>
       </c>
       <c r="F350" s="1">
-        <v>4223848436</v>
+        <v>4966314368</v>
       </c>
       <c r="G350" s="1">
-        <v>6491067577</v>
+        <v>5748601645</v>
       </c>
       <c r="H350" s="1">
         <v>0</v>
@@ -10380,13 +10380,13 @@
         <v>0</v>
       </c>
       <c r="E351" s="1">
-        <v>111972247</v>
+        <v>134045088</v>
       </c>
       <c r="F351" s="1">
-        <v>111972247</v>
+        <v>134045088</v>
       </c>
       <c r="G351" s="1">
-        <v>163848185</v>
+        <v>141775344</v>
       </c>
       <c r="H351" s="1">
         <v>0</v>
@@ -10406,13 +10406,13 @@
         <v>0</v>
       </c>
       <c r="E352" s="1">
-        <v>4352649093</v>
+        <v>4723021593</v>
       </c>
       <c r="F352" s="1">
-        <v>4352649093</v>
+        <v>4723021593</v>
       </c>
       <c r="G352" s="1">
-        <v>6179515109</v>
+        <v>5809142609</v>
       </c>
       <c r="H352" s="1">
         <v>0</v>
@@ -10458,13 +10458,13 @@
         <v>0</v>
       </c>
       <c r="E354" s="1">
-        <v>461426139</v>
+        <v>541081421</v>
       </c>
       <c r="F354" s="1">
-        <v>461426139</v>
+        <v>541081421</v>
       </c>
       <c r="G354" s="1">
-        <v>830168506</v>
+        <v>750513224</v>
       </c>
       <c r="H354" s="1">
         <v>0</v>
@@ -10484,13 +10484,13 @@
         <v>0</v>
       </c>
       <c r="E355" s="1">
-        <v>19484010</v>
+        <v>23380812</v>
       </c>
       <c r="F355" s="1">
-        <v>19484010</v>
+        <v>23380812</v>
       </c>
       <c r="G355" s="1">
-        <v>27926736</v>
+        <v>24029934</v>
       </c>
       <c r="H355" s="1">
         <v>0</v>
@@ -10510,13 +10510,13 @@
         <v>0</v>
       </c>
       <c r="E356" s="1">
-        <v>580693891</v>
+        <v>645286391</v>
       </c>
       <c r="F356" s="1">
-        <v>580693891</v>
+        <v>645286391</v>
       </c>
       <c r="G356" s="1">
-        <v>942324213</v>
+        <v>877731713</v>
       </c>
       <c r="H356" s="1">
         <v>0</v>
@@ -10559,16 +10559,16 @@
         <v>57427089299</v>
       </c>
       <c r="D358" s="1">
-        <v>17382878515</v>
+        <v>17325798235</v>
       </c>
       <c r="E358" s="1">
-        <v>18882947459</v>
+        <v>20528322351</v>
       </c>
       <c r="F358" s="1">
-        <v>36265825974</v>
+        <v>37854120586</v>
       </c>
       <c r="G358" s="1">
-        <v>21161263325</v>
+        <v>19572968713</v>
       </c>
       <c r="H358" s="1">
         <v>526334925</v>
@@ -10741,10 +10741,10 @@
         <v>1714789867</v>
       </c>
       <c r="D365" s="1">
-        <v>402282172</v>
+        <v>386883381</v>
       </c>
       <c r="E365" s="1">
-        <v>330680136</v>
+        <v>346078927</v>
       </c>
       <c r="F365" s="1">
         <v>732962308</v>
@@ -10871,16 +10871,16 @@
         <v>200000000</v>
       </c>
       <c r="D370" s="1">
-        <v>55411200</v>
+        <v>49920000</v>
       </c>
       <c r="E370" s="1">
         <v>0</v>
       </c>
       <c r="F370" s="1">
-        <v>55411200</v>
+        <v>49920000</v>
       </c>
       <c r="G370" s="1">
-        <v>144588800</v>
+        <v>150080000</v>
       </c>
       <c r="H370" s="1">
         <v>0</v>
@@ -10952,13 +10952,13 @@
         <v>1827440</v>
       </c>
       <c r="E373" s="1">
-        <v>172772525</v>
+        <v>207198710</v>
       </c>
       <c r="F373" s="1">
-        <v>174599965</v>
+        <v>209026150</v>
       </c>
       <c r="G373" s="1">
-        <v>236480035</v>
+        <v>202053850</v>
       </c>
       <c r="H373" s="1">
         <v>0</v>
@@ -11001,10 +11001,10 @@
         <v>300000000</v>
       </c>
       <c r="D375" s="1">
-        <v>54400000</v>
+        <v>47950000</v>
       </c>
       <c r="E375" s="1">
-        <v>136933462</v>
+        <v>143383462</v>
       </c>
       <c r="F375" s="1">
         <v>191333462</v>
@@ -11082,13 +11082,13 @@
         <v>0</v>
       </c>
       <c r="E378" s="1">
-        <v>85494000</v>
+        <v>88344000</v>
       </c>
       <c r="F378" s="1">
-        <v>85494000</v>
+        <v>88344000</v>
       </c>
       <c r="G378" s="1">
-        <v>42531000</v>
+        <v>39681000</v>
       </c>
       <c r="H378" s="1">
         <v>42675000</v>
@@ -11186,13 +11186,13 @@
         <v>0</v>
       </c>
       <c r="E382" s="1">
-        <v>1820022182</v>
+        <v>2149565071</v>
       </c>
       <c r="F382" s="1">
-        <v>1820022182</v>
+        <v>2149565071</v>
       </c>
       <c r="G382" s="1">
-        <v>2719784736</v>
+        <v>2390241847</v>
       </c>
       <c r="H382" s="1">
         <v>0</v>
@@ -11212,13 +11212,13 @@
         <v>0</v>
       </c>
       <c r="E383" s="1">
-        <v>33316503</v>
+        <v>39195974</v>
       </c>
       <c r="F383" s="1">
-        <v>33316503</v>
+        <v>39195974</v>
       </c>
       <c r="G383" s="1">
-        <v>49738066</v>
+        <v>43858595</v>
       </c>
       <c r="H383" s="1">
         <v>0</v>
@@ -11238,13 +11238,13 @@
         <v>0</v>
       </c>
       <c r="E384" s="1">
-        <v>1858324792</v>
+        <v>2028464792</v>
       </c>
       <c r="F384" s="1">
-        <v>1858324792</v>
+        <v>2028464792</v>
       </c>
       <c r="G384" s="1">
-        <v>2811314810</v>
+        <v>2641174810</v>
       </c>
       <c r="H384" s="1">
         <v>0</v>
@@ -11290,13 +11290,13 @@
         <v>0</v>
       </c>
       <c r="E386" s="1">
-        <v>299252081</v>
+        <v>346298204</v>
       </c>
       <c r="F386" s="1">
-        <v>299252081</v>
+        <v>346298204</v>
       </c>
       <c r="G386" s="1">
-        <v>495861352</v>
+        <v>448815229</v>
       </c>
       <c r="H386" s="1">
         <v>0</v>
@@ -11316,13 +11316,13 @@
         <v>0</v>
       </c>
       <c r="E387" s="1">
-        <v>9917870</v>
+        <v>11910562</v>
       </c>
       <c r="F387" s="1">
-        <v>9917870</v>
+        <v>11910562</v>
       </c>
       <c r="G387" s="1">
-        <v>27576065</v>
+        <v>25583373</v>
       </c>
       <c r="H387" s="1">
         <v>0</v>
@@ -11342,13 +11342,13 @@
         <v>0</v>
       </c>
       <c r="E388" s="1">
-        <v>383147111</v>
+        <v>427077111</v>
       </c>
       <c r="F388" s="1">
-        <v>383147111</v>
+        <v>427077111</v>
       </c>
       <c r="G388" s="1">
-        <v>577086738</v>
+        <v>533156738</v>
       </c>
       <c r="H388" s="1">
         <v>0</v>
@@ -11391,16 +11391,16 @@
         <v>24628424376</v>
       </c>
       <c r="D390" s="1">
-        <v>5442340602</v>
+        <v>5415000611</v>
       </c>
       <c r="E390" s="1">
-        <v>7931969521</v>
+        <v>8589625672</v>
       </c>
       <c r="F390" s="1">
-        <v>13374310123</v>
+        <v>14004626283</v>
       </c>
       <c r="G390" s="1">
-        <v>11254114253</v>
+        <v>10623798093</v>
       </c>
       <c r="H390" s="1">
         <v>232675000</v>
@@ -11417,16 +11417,16 @@
         <v>2666359332</v>
       </c>
       <c r="D391" s="1">
-        <v>2094867800</v>
+        <v>2310150400</v>
       </c>
       <c r="E391" s="1">
         <v>344920370</v>
       </c>
       <c r="F391" s="1">
-        <v>2439788170</v>
+        <v>2655070770</v>
       </c>
       <c r="G391" s="1">
-        <v>226571162</v>
+        <v>11288562</v>
       </c>
       <c r="H391" s="1">
         <v>0</v>
@@ -11495,10 +11495,10 @@
         <v>2563071413</v>
       </c>
       <c r="D394" s="1">
-        <v>1919329790</v>
+        <v>1880475590</v>
       </c>
       <c r="E394" s="1">
-        <v>99478446</v>
+        <v>138332646</v>
       </c>
       <c r="F394" s="1">
         <v>2018808236</v>
@@ -11521,16 +11521,16 @@
         <v>230247015</v>
       </c>
       <c r="D395" s="1">
-        <v>0</v>
+        <v>49980000</v>
       </c>
       <c r="E395" s="1">
         <v>69308015</v>
       </c>
       <c r="F395" s="1">
-        <v>69308015</v>
+        <v>119288015</v>
       </c>
       <c r="G395" s="1">
-        <v>160939000</v>
+        <v>110959000</v>
       </c>
       <c r="H395" s="1">
         <v>0</v>
@@ -11573,10 +11573,10 @@
         <v>500000000</v>
       </c>
       <c r="D397" s="1">
-        <v>431850131</v>
+        <v>413687631</v>
       </c>
       <c r="E397" s="1">
-        <v>49811800</v>
+        <v>67974300</v>
       </c>
       <c r="F397" s="1">
         <v>481661931</v>
@@ -11599,10 +11599,10 @@
         <v>690000000</v>
       </c>
       <c r="D398" s="1">
-        <v>376703860</v>
+        <v>355363860</v>
       </c>
       <c r="E398" s="1">
-        <v>306931880</v>
+        <v>328271880</v>
       </c>
       <c r="F398" s="1">
         <v>683635740</v>
@@ -11781,10 +11781,10 @@
         <v>187500000</v>
       </c>
       <c r="D405" s="1">
-        <v>69480000</v>
+        <v>19550000</v>
       </c>
       <c r="E405" s="1">
-        <v>0</v>
+        <v>49930000</v>
       </c>
       <c r="F405" s="1">
         <v>69480000</v>
@@ -11836,13 +11836,13 @@
         <v>19315000</v>
       </c>
       <c r="E407" s="1">
-        <v>617824332</v>
+        <v>744765838</v>
       </c>
       <c r="F407" s="1">
-        <v>637139332</v>
+        <v>764080838</v>
       </c>
       <c r="G407" s="1">
-        <v>1592860668</v>
+        <v>1465919162</v>
       </c>
       <c r="H407" s="1">
         <v>0</v>
@@ -11885,16 +11885,16 @@
         <v>445223250</v>
       </c>
       <c r="D409" s="1">
-        <v>58723500</v>
+        <v>61843837</v>
       </c>
       <c r="E409" s="1">
         <v>283828950</v>
       </c>
       <c r="F409" s="1">
-        <v>342552450</v>
+        <v>345672787</v>
       </c>
       <c r="G409" s="1">
-        <v>102670800</v>
+        <v>99550463</v>
       </c>
       <c r="H409" s="1">
         <v>148407750</v>
@@ -11963,16 +11963,16 @@
         <v>351000000</v>
       </c>
       <c r="D412" s="1">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="E412" s="1">
-        <v>203498708</v>
+        <v>204048708</v>
       </c>
       <c r="F412" s="1">
-        <v>203498708</v>
+        <v>214048708</v>
       </c>
       <c r="G412" s="1">
-        <v>147501292</v>
+        <v>136951292</v>
       </c>
       <c r="H412" s="1">
         <v>117000000</v>
@@ -12070,13 +12070,13 @@
         <v>0</v>
       </c>
       <c r="E416" s="1">
-        <v>3415495008</v>
+        <v>4003737655</v>
       </c>
       <c r="F416" s="1">
-        <v>3415495008</v>
+        <v>4003737655</v>
       </c>
       <c r="G416" s="1">
-        <v>5225850703</v>
+        <v>4637608056</v>
       </c>
       <c r="H416" s="1">
         <v>0</v>
@@ -12096,13 +12096,13 @@
         <v>0</v>
       </c>
       <c r="E417" s="1">
-        <v>20306219</v>
+        <v>23561040</v>
       </c>
       <c r="F417" s="1">
-        <v>20306219</v>
+        <v>23561040</v>
       </c>
       <c r="G417" s="1">
-        <v>30517860</v>
+        <v>27263039</v>
       </c>
       <c r="H417" s="1">
         <v>0</v>
@@ -12122,13 +12122,13 @@
         <v>0</v>
       </c>
       <c r="E418" s="1">
-        <v>3567682305</v>
+        <v>3870562305</v>
       </c>
       <c r="F418" s="1">
-        <v>3567682305</v>
+        <v>3870562305</v>
       </c>
       <c r="G418" s="1">
-        <v>5811886187</v>
+        <v>5509006187</v>
       </c>
       <c r="H418" s="1">
         <v>0</v>
@@ -12174,13 +12174,13 @@
         <v>0</v>
       </c>
       <c r="E420" s="1">
-        <v>307662076</v>
+        <v>351874951</v>
       </c>
       <c r="F420" s="1">
-        <v>307662076</v>
+        <v>351874951</v>
       </c>
       <c r="G420" s="1">
-        <v>596827570</v>
+        <v>552614695</v>
       </c>
       <c r="H420" s="1">
         <v>0</v>
@@ -12200,13 +12200,13 @@
         <v>0</v>
       </c>
       <c r="E421" s="1">
-        <v>9530147</v>
+        <v>11447067</v>
       </c>
       <c r="F421" s="1">
-        <v>9530147</v>
+        <v>11447067</v>
       </c>
       <c r="G421" s="1">
-        <v>13266449</v>
+        <v>11349529</v>
       </c>
       <c r="H421" s="1">
         <v>0</v>
@@ -12226,13 +12226,13 @@
         <v>0</v>
       </c>
       <c r="E422" s="1">
-        <v>422123480</v>
+        <v>472443480</v>
       </c>
       <c r="F422" s="1">
-        <v>422123480</v>
+        <v>472443480</v>
       </c>
       <c r="G422" s="1">
-        <v>683759967</v>
+        <v>633439967</v>
       </c>
       <c r="H422" s="1">
         <v>0</v>
@@ -12275,16 +12275,16 @@
         <v>35458361640</v>
       </c>
       <c r="D424" s="1">
-        <v>7404239869</v>
+        <v>7554336106</v>
       </c>
       <c r="E424" s="1">
-        <v>10788408651</v>
+        <v>12035014120</v>
       </c>
       <c r="F424" s="1">
-        <v>18192648520</v>
+        <v>19589350226</v>
       </c>
       <c r="G424" s="1">
-        <v>17265713120</v>
+        <v>15869011414</v>
       </c>
       <c r="H424" s="1">
         <v>472807750</v>
@@ -12541,12 +12541,14 @@
         <v>208424730</v>
       </c>
       <c r="D443" s="3">
-        <v>0</v>
+        <v>180590600</v>
       </c>
       <c r="E443" s="3"/>
-      <c r="F443" s="3"/>
+      <c r="F443" s="3">
+        <v>180590600</v>
+      </c>
       <c r="G443" s="3">
-        <v>208424730</v>
+        <v>27834130</v>
       </c>
       <c r="H443" s="3">
         <v>0</v>
@@ -12615,12 +12617,14 @@
         <v>75000000</v>
       </c>
       <c r="D446" s="3">
-        <v>0</v>
+        <v>38500000</v>
       </c>
       <c r="E446" s="3"/>
-      <c r="F446" s="3"/>
+      <c r="F446" s="3">
+        <v>38500000</v>
+      </c>
       <c r="G446" s="3">
-        <v>75000000</v>
+        <v>36500000</v>
       </c>
       <c r="H446" s="3">
         <v>0</v>
@@ -12843,16 +12847,16 @@
         <v>30750000</v>
       </c>
       <c r="D461" s="3">
-        <v>993300</v>
+        <v>2064300</v>
       </c>
       <c r="E461" s="3">
         <v>3989400</v>
       </c>
       <c r="F461" s="3">
-        <v>4982700</v>
+        <v>6053700</v>
       </c>
       <c r="G461" s="3">
-        <v>25767300</v>
+        <v>24696300</v>
       </c>
       <c r="H461" s="3">
         <v>10250000</v>
@@ -12943,16 +12947,16 @@
         <v>6660000</v>
       </c>
       <c r="D465" s="3">
-        <v>1582644</v>
+        <v>2581644</v>
       </c>
       <c r="E465" s="3">
         <v>1665000</v>
       </c>
       <c r="F465" s="3">
-        <v>3247644</v>
+        <v>4246644</v>
       </c>
       <c r="G465" s="3">
-        <v>3412356</v>
+        <v>2413356</v>
       </c>
       <c r="H465" s="3">
         <v>0</v>
@@ -13152,7 +13156,7 @@
       </c>
       <c r="D480" s="3">
         <f t="shared" si="0"/>
-        <v>639865944</v>
+        <v>861026544</v>
       </c>
       <c r="E480" s="3">
         <f t="shared" si="0"/>
@@ -13160,11 +13164,11 @@
       </c>
       <c r="F480" s="3">
         <f t="shared" si="0"/>
-        <v>950816524</v>
+        <v>1171977124</v>
       </c>
       <c r="G480" s="3">
         <f t="shared" si="0"/>
-        <v>1287944206</v>
+        <v>1066783606</v>
       </c>
       <c r="H480" s="3">
         <f t="shared" si="0"/>
@@ -13182,16 +13186,16 @@
         <v>10505111000</v>
       </c>
       <c r="D481" s="1">
-        <v>6692527914</v>
+        <v>4035507574</v>
       </c>
       <c r="E481" s="1">
-        <v>3664942000</v>
+        <v>6317430000</v>
       </c>
       <c r="F481" s="1">
-        <v>10357469914</v>
+        <v>10352937574</v>
       </c>
       <c r="G481" s="1">
-        <v>147641086</v>
+        <v>152173426</v>
       </c>
       <c r="H481" s="1">
         <v>0</v>
@@ -13364,10 +13368,10 @@
         <v>2312795000</v>
       </c>
       <c r="D488" s="1">
-        <v>1276143104</v>
+        <v>1244831850</v>
       </c>
       <c r="E488" s="1">
-        <v>533499364</v>
+        <v>564810618</v>
       </c>
       <c r="F488" s="1">
         <v>1809642468</v>
@@ -13390,16 +13394,16 @@
         <v>4989900000</v>
       </c>
       <c r="D489" s="1">
-        <v>780653897</v>
+        <v>849125017</v>
       </c>
       <c r="E489" s="1">
-        <v>1002284612</v>
+        <v>1012438612</v>
       </c>
       <c r="F489" s="1">
-        <v>1782938509</v>
+        <v>1861563629</v>
       </c>
       <c r="G489" s="1">
-        <v>3206961491</v>
+        <v>3128336371</v>
       </c>
       <c r="H489" s="1">
         <v>0</v>
@@ -13442,16 +13446,16 @@
         <v>1680000000</v>
       </c>
       <c r="D491" s="1">
-        <v>590157218</v>
+        <v>588687099</v>
       </c>
       <c r="E491" s="1">
         <v>351995650</v>
       </c>
       <c r="F491" s="1">
-        <v>942152868</v>
+        <v>940682749</v>
       </c>
       <c r="G491" s="1">
-        <v>737847132</v>
+        <v>739317251</v>
       </c>
       <c r="H491" s="1">
         <v>0</v>
@@ -13468,16 +13472,16 @@
         <v>492066000</v>
       </c>
       <c r="D492" s="1">
-        <v>27101365</v>
+        <v>450629365</v>
       </c>
       <c r="E492" s="1">
         <v>12185500</v>
       </c>
       <c r="F492" s="1">
-        <v>39286865</v>
+        <v>462814865</v>
       </c>
       <c r="G492" s="1">
-        <v>452779135</v>
+        <v>29251135</v>
       </c>
       <c r="H492" s="1">
         <v>0</v>
@@ -13572,16 +13576,16 @@
         <v>745000000</v>
       </c>
       <c r="D496" s="1">
-        <v>6813800</v>
+        <v>683272388</v>
       </c>
       <c r="E496" s="1">
         <v>51881480</v>
       </c>
       <c r="F496" s="1">
-        <v>58695280</v>
+        <v>735153868</v>
       </c>
       <c r="G496" s="1">
-        <v>686304720</v>
+        <v>9846132</v>
       </c>
       <c r="H496" s="1">
         <v>0</v>
@@ -13592,22 +13596,22 @@
         <v>123</v>
       </c>
       <c r="B497" s="1">
-        <v>4029356000</v>
+        <v>7401091133</v>
       </c>
       <c r="C497" s="1">
-        <v>4029356000</v>
+        <v>7401091133</v>
       </c>
       <c r="D497" s="1">
-        <v>2960083667</v>
+        <v>571996389</v>
       </c>
       <c r="E497" s="1">
-        <v>92786500</v>
+        <v>2490585500</v>
       </c>
       <c r="F497" s="1">
-        <v>3052870167</v>
+        <v>3062581889</v>
       </c>
       <c r="G497" s="1">
-        <v>976485833</v>
+        <v>4338509244</v>
       </c>
       <c r="H497" s="1">
         <v>0</v>
@@ -13624,16 +13628,16 @@
         <v>297500000</v>
       </c>
       <c r="D498" s="1">
-        <v>37638722</v>
+        <v>43057354</v>
       </c>
       <c r="E498" s="1">
-        <v>19913990</v>
+        <v>57552712</v>
       </c>
       <c r="F498" s="1">
-        <v>57552712</v>
+        <v>100610066</v>
       </c>
       <c r="G498" s="1">
-        <v>239947288</v>
+        <v>196889934</v>
       </c>
       <c r="H498" s="1">
         <v>0</v>
@@ -13650,10 +13654,10 @@
         <v>266250000</v>
       </c>
       <c r="D499" s="1">
-        <v>149438200</v>
+        <v>102714000</v>
       </c>
       <c r="E499" s="1">
-        <v>40800000</v>
+        <v>87524200</v>
       </c>
       <c r="F499" s="1">
         <v>190238200</v>
@@ -13757,13 +13761,13 @@
         <v>10404406</v>
       </c>
       <c r="E503" s="1">
-        <v>1049343520</v>
+        <v>1252685406</v>
       </c>
       <c r="F503" s="1">
-        <v>1059747926</v>
+        <v>1263089812</v>
       </c>
       <c r="G503" s="1">
-        <v>1500252074</v>
+        <v>1296910188</v>
       </c>
       <c r="H503" s="1">
         <v>0</v>
@@ -13780,10 +13784,10 @@
         <v>668379750</v>
       </c>
       <c r="D504" s="1">
-        <v>93802000</v>
+        <v>64146000</v>
       </c>
       <c r="E504" s="1">
-        <v>63248828</v>
+        <v>92904828</v>
       </c>
       <c r="F504" s="1">
         <v>157050828</v>
@@ -13806,10 +13810,10 @@
         <v>870341250</v>
       </c>
       <c r="D505" s="1">
-        <v>192866862</v>
+        <v>181866862</v>
       </c>
       <c r="E505" s="1">
-        <v>364475810</v>
+        <v>375475810</v>
       </c>
       <c r="F505" s="1">
         <v>557342672</v>
@@ -13858,10 +13862,10 @@
         <v>422192250</v>
       </c>
       <c r="D507" s="1">
-        <v>21328000</v>
+        <v>18367000</v>
       </c>
       <c r="E507" s="1">
-        <v>38772427</v>
+        <v>41733427</v>
       </c>
       <c r="F507" s="1">
         <v>60100427</v>
@@ -13887,13 +13891,13 @@
         <v>45474698</v>
       </c>
       <c r="E508" s="1">
-        <v>201660371</v>
+        <v>202135371</v>
       </c>
       <c r="F508" s="1">
-        <v>247135069</v>
+        <v>247610069</v>
       </c>
       <c r="G508" s="1">
-        <v>269298431</v>
+        <v>268823431</v>
       </c>
       <c r="H508" s="1">
         <v>172144500</v>
@@ -14069,13 +14073,13 @@
         <v>0</v>
       </c>
       <c r="E515" s="1">
-        <v>5077849465</v>
+        <v>5967098085</v>
       </c>
       <c r="F515" s="1">
-        <v>5077849465</v>
+        <v>5967098085</v>
       </c>
       <c r="G515" s="1">
-        <v>7086432432</v>
+        <v>6197183812</v>
       </c>
       <c r="H515" s="1">
         <v>0</v>
@@ -14095,13 +14099,13 @@
         <v>0</v>
       </c>
       <c r="E516" s="1">
-        <v>46151307</v>
+        <v>55420594</v>
       </c>
       <c r="F516" s="1">
-        <v>46151307</v>
+        <v>55420594</v>
       </c>
       <c r="G516" s="1">
-        <v>65356892</v>
+        <v>56087605</v>
       </c>
       <c r="H516" s="1">
         <v>0</v>
@@ -14121,13 +14125,13 @@
         <v>0</v>
       </c>
       <c r="E517" s="1">
-        <v>4695193969</v>
+        <v>5071023969</v>
       </c>
       <c r="F517" s="1">
-        <v>4695193969</v>
+        <v>5071023969</v>
       </c>
       <c r="G517" s="1">
-        <v>6106210228</v>
+        <v>5730380228</v>
       </c>
       <c r="H517" s="1">
         <v>0</v>
@@ -14173,13 +14177,13 @@
         <v>0</v>
       </c>
       <c r="E519" s="1">
-        <v>473595210</v>
+        <v>553974458</v>
       </c>
       <c r="F519" s="1">
-        <v>473595210</v>
+        <v>553974458</v>
       </c>
       <c r="G519" s="1">
-        <v>979090029</v>
+        <v>898710781</v>
       </c>
       <c r="H519" s="1">
         <v>0</v>
@@ -14199,13 +14203,13 @@
         <v>0</v>
       </c>
       <c r="E520" s="1">
-        <v>12557313</v>
+        <v>15537750</v>
       </c>
       <c r="F520" s="1">
-        <v>12557313</v>
+        <v>15537750</v>
       </c>
       <c r="G520" s="1">
-        <v>22608085</v>
+        <v>19627648</v>
       </c>
       <c r="H520" s="1">
         <v>0</v>
@@ -14225,13 +14229,13 @@
         <v>0</v>
       </c>
       <c r="E521" s="1">
-        <v>677310359</v>
+        <v>755210359</v>
       </c>
       <c r="F521" s="1">
-        <v>677310359</v>
+        <v>755210359</v>
       </c>
       <c r="G521" s="1">
-        <v>1021438142</v>
+        <v>943538142</v>
       </c>
       <c r="H521" s="1">
         <v>0</v>
@@ -14294,22 +14298,22 @@
         <v>125</v>
       </c>
       <c r="B524" s="1">
-        <v>61498532437</v>
+        <v>64870267570</v>
       </c>
       <c r="C524" s="1">
-        <v>60647750187</v>
+        <v>64019485320</v>
       </c>
       <c r="D524" s="1">
-        <v>14009577377</v>
+        <v>10015223526</v>
       </c>
       <c r="E524" s="1">
-        <v>19843983143</v>
+        <v>26703139797</v>
       </c>
       <c r="F524" s="1">
-        <v>33853560520</v>
+        <v>36718363323</v>
       </c>
       <c r="G524" s="1">
-        <v>26794189667</v>
+        <v>27301121997</v>
       </c>
       <c r="H524" s="1">
         <v>850782250</v>
@@ -14404,16 +14408,16 @@
         <v>2639000000</v>
       </c>
       <c r="D528" s="1">
-        <v>1917348679</v>
+        <v>1875260744</v>
       </c>
       <c r="E528" s="1">
-        <v>231626548</v>
+        <v>281140148</v>
       </c>
       <c r="F528" s="1">
-        <v>2148975227</v>
+        <v>2156400892</v>
       </c>
       <c r="G528" s="1">
-        <v>490024773</v>
+        <v>482599108</v>
       </c>
       <c r="H528" s="1">
         <v>0</v>
@@ -14508,16 +14512,16 @@
         <v>2114698000</v>
       </c>
       <c r="D532" s="1">
-        <v>1148440243</v>
+        <v>1151238143</v>
       </c>
       <c r="E532" s="1">
         <v>317890973</v>
       </c>
       <c r="F532" s="1">
-        <v>1466331216</v>
+        <v>1469129116</v>
       </c>
       <c r="G532" s="1">
-        <v>648366784</v>
+        <v>645568884</v>
       </c>
       <c r="H532" s="1">
         <v>0</v>
@@ -14534,16 +14538,16 @@
         <v>1450000000</v>
       </c>
       <c r="D533" s="1">
-        <v>148480523</v>
+        <v>257512645</v>
       </c>
       <c r="E533" s="1">
         <v>199177827</v>
       </c>
       <c r="F533" s="1">
-        <v>347658350</v>
+        <v>456690472</v>
       </c>
       <c r="G533" s="1">
-        <v>1102341650</v>
+        <v>993309528</v>
       </c>
       <c r="H533" s="1">
         <v>0</v>
@@ -14638,16 +14642,16 @@
         <v>300000000</v>
       </c>
       <c r="D537" s="1">
-        <v>0</v>
+        <v>1295149</v>
       </c>
       <c r="E537" s="1">
         <v>4951687</v>
       </c>
       <c r="F537" s="1">
-        <v>4951687</v>
+        <v>6246836</v>
       </c>
       <c r="G537" s="1">
-        <v>295048313</v>
+        <v>293753164</v>
       </c>
       <c r="H537" s="1">
         <v>0</v>
@@ -14690,10 +14694,10 @@
         <v>285978663</v>
       </c>
       <c r="D539" s="1">
-        <v>86566700</v>
+        <v>58526100</v>
       </c>
       <c r="E539" s="1">
-        <v>91135000</v>
+        <v>119175600</v>
       </c>
       <c r="F539" s="1">
         <v>177701700</v>
@@ -14716,16 +14720,16 @@
         <v>1539315000</v>
       </c>
       <c r="D540" s="1">
-        <v>3699966</v>
+        <v>3368850</v>
       </c>
       <c r="E540" s="1">
-        <v>571851115</v>
+        <v>691756980</v>
       </c>
       <c r="F540" s="1">
-        <v>575551081</v>
+        <v>695125830</v>
       </c>
       <c r="G540" s="1">
-        <v>963763919</v>
+        <v>844189170</v>
       </c>
       <c r="H540" s="1">
         <v>0</v>
@@ -14742,10 +14746,10 @@
         <v>412500000</v>
       </c>
       <c r="D541" s="1">
-        <v>41887175</v>
+        <v>35830775</v>
       </c>
       <c r="E541" s="1">
-        <v>40585600</v>
+        <v>46642000</v>
       </c>
       <c r="F541" s="1">
         <v>82472775</v>
@@ -14820,16 +14824,16 @@
         <v>395748750</v>
       </c>
       <c r="D544" s="1">
-        <v>205445279</v>
+        <v>248317351</v>
       </c>
       <c r="E544" s="1">
         <v>28459950</v>
       </c>
       <c r="F544" s="1">
-        <v>233905229</v>
+        <v>276777301</v>
       </c>
       <c r="G544" s="1">
-        <v>161843521</v>
+        <v>118971449</v>
       </c>
       <c r="H544" s="1">
         <v>131916250</v>
@@ -14846,16 +14850,16 @@
         <v>336802500</v>
       </c>
       <c r="D545" s="1">
-        <v>16387601</v>
+        <v>19159601</v>
       </c>
       <c r="E545" s="1">
-        <v>151142500</v>
+        <v>153517500</v>
       </c>
       <c r="F545" s="1">
-        <v>167530101</v>
+        <v>172677101</v>
       </c>
       <c r="G545" s="1">
-        <v>169272399</v>
+        <v>164125399</v>
       </c>
       <c r="H545" s="1">
         <v>112267500</v>
@@ -14927,13 +14931,13 @@
         <v>0</v>
       </c>
       <c r="E548" s="1">
-        <v>4482665481</v>
+        <v>5261130654</v>
       </c>
       <c r="F548" s="1">
-        <v>4482665481</v>
+        <v>5261130654</v>
       </c>
       <c r="G548" s="1">
-        <v>6206251385</v>
+        <v>5427786212</v>
       </c>
       <c r="H548" s="1">
         <v>0</v>
@@ -14953,13 +14957,13 @@
         <v>0</v>
       </c>
       <c r="E549" s="1">
-        <v>42254257</v>
+        <v>50304729</v>
       </c>
       <c r="F549" s="1">
-        <v>42254257</v>
+        <v>50304729</v>
       </c>
       <c r="G549" s="1">
-        <v>63861794</v>
+        <v>55811322</v>
       </c>
       <c r="H549" s="1">
         <v>0</v>
@@ -14979,13 +14983,13 @@
         <v>0</v>
       </c>
       <c r="E550" s="1">
-        <v>3961731017</v>
+        <v>4287384517</v>
       </c>
       <c r="F550" s="1">
-        <v>3961731017</v>
+        <v>4287384517</v>
       </c>
       <c r="G550" s="1">
-        <v>5256595326</v>
+        <v>4930941826</v>
       </c>
       <c r="H550" s="1">
         <v>0</v>
@@ -15031,13 +15035,13 @@
         <v>0</v>
       </c>
       <c r="E552" s="1">
-        <v>557150695</v>
+        <v>692793874</v>
       </c>
       <c r="F552" s="1">
-        <v>557150695</v>
+        <v>692793874</v>
       </c>
       <c r="G552" s="1">
-        <v>865655258</v>
+        <v>730012079</v>
       </c>
       <c r="H552" s="1">
         <v>0</v>
@@ -15057,13 +15061,13 @@
         <v>0</v>
       </c>
       <c r="E553" s="1">
-        <v>7801082</v>
+        <v>10010689</v>
       </c>
       <c r="F553" s="1">
-        <v>7801082</v>
+        <v>10010689</v>
       </c>
       <c r="G553" s="1">
-        <v>6115676</v>
+        <v>3906069</v>
       </c>
       <c r="H553" s="1">
         <v>0</v>
@@ -15083,13 +15087,13 @@
         <v>0</v>
       </c>
       <c r="E554" s="1">
-        <v>695974504</v>
+        <v>775912004</v>
       </c>
       <c r="F554" s="1">
-        <v>695974504</v>
+        <v>775912004</v>
       </c>
       <c r="G554" s="1">
-        <v>863708257</v>
+        <v>783770757</v>
       </c>
       <c r="H554" s="1">
         <v>0</v>
@@ -15132,16 +15136,16 @@
         <v>57848682223</v>
       </c>
       <c r="D556" s="1">
-        <v>22502884655</v>
+        <v>22585137847</v>
       </c>
       <c r="E556" s="1">
-        <v>16030541713</v>
+        <v>17566392609</v>
       </c>
       <c r="F556" s="1">
-        <v>38533426368</v>
+        <v>40151530456</v>
       </c>
       <c r="G556" s="1">
-        <v>19315255855</v>
+        <v>17697151767</v>
       </c>
       <c r="H556" s="1">
         <v>720558750</v>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,15 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\6. Jun\KP\RKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{380F5882-9538-4E40-A05C-930DF4331D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0CBD8E-118F-4EF9-980C-B793F550E3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget 3 Juni 2024" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -411,7 +420,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -895,10 +904,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1258,37 +1273,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H556"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="60.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="15.796875" style="1" customWidth="1"/>
+    <col min="2" max="8" width="13.796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1303,16 +1318,16 @@
         <v>108319375668</v>
       </c>
       <c r="D2" s="1">
-        <v>107767160029</v>
+        <v>107741134603</v>
       </c>
       <c r="E2" s="1">
         <v>46437298</v>
       </c>
       <c r="F2" s="1">
-        <v>107813597327</v>
+        <v>107787571901</v>
       </c>
       <c r="G2" s="1">
-        <v>505778341</v>
+        <v>531803767</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
@@ -1459,16 +1474,16 @@
         <v>3726972261</v>
       </c>
       <c r="D8" s="1">
-        <v>3648429493</v>
+        <v>3636458369</v>
       </c>
       <c r="E8" s="1">
         <v>77164840</v>
       </c>
       <c r="F8" s="1">
-        <v>3725594333</v>
+        <v>3713623209</v>
       </c>
       <c r="G8" s="1">
-        <v>1377928</v>
+        <v>13349052</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -1719,16 +1734,16 @@
         <v>4500000000</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>82603795</v>
       </c>
       <c r="E18" s="1">
         <v>1803396630</v>
       </c>
       <c r="F18" s="1">
-        <v>1803396630</v>
+        <v>1886000425</v>
       </c>
       <c r="G18" s="1">
-        <v>2696603370</v>
+        <v>2613999575</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -1875,16 +1890,16 @@
         <v>1758555793</v>
       </c>
       <c r="D24" s="1">
-        <v>93542038</v>
+        <v>49080328</v>
       </c>
       <c r="E24" s="1">
-        <v>748802807</v>
+        <v>802464517</v>
       </c>
       <c r="F24" s="1">
-        <v>842344845</v>
+        <v>851544845</v>
       </c>
       <c r="G24" s="1">
-        <v>916210948</v>
+        <v>907010948</v>
       </c>
       <c r="H24" s="1">
         <v>625000000</v>
@@ -1956,13 +1971,13 @@
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>1755600895</v>
+        <v>1755916832</v>
       </c>
       <c r="F27" s="1">
-        <v>1755600895</v>
+        <v>1755916832</v>
       </c>
       <c r="G27" s="1">
-        <v>1701013309</v>
+        <v>1700697372</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -2265,16 +2280,16 @@
         <v>349995097631</v>
       </c>
       <c r="D39" s="1">
-        <v>241197970735</v>
+        <v>241198116270</v>
       </c>
       <c r="E39" s="1">
-        <v>69797230108</v>
+        <v>69851207755</v>
       </c>
       <c r="F39" s="1">
-        <v>310995200843</v>
+        <v>311049324025</v>
       </c>
       <c r="G39" s="1">
-        <v>38999896788</v>
+        <v>38945773606</v>
       </c>
       <c r="H39" s="1">
         <v>2417500000</v>
@@ -2291,16 +2306,16 @@
         <v>25194775704</v>
       </c>
       <c r="D40" s="1">
-        <v>21258870770</v>
+        <v>21243564480</v>
       </c>
       <c r="E40" s="1">
         <v>3568529000</v>
       </c>
       <c r="F40" s="1">
-        <v>24827399770</v>
+        <v>24812093480</v>
       </c>
       <c r="G40" s="1">
-        <v>367375934</v>
+        <v>382682224</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -2421,16 +2436,16 @@
         <v>400000000</v>
       </c>
       <c r="D45" s="1">
-        <v>379725700</v>
+        <v>376349700</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
       </c>
       <c r="F45" s="1">
-        <v>379725700</v>
+        <v>376349700</v>
       </c>
       <c r="G45" s="1">
-        <v>20274300</v>
+        <v>23650300</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -2447,16 +2462,16 @@
         <v>2000000000</v>
       </c>
       <c r="D46" s="1">
-        <v>499882234</v>
+        <v>491537500</v>
       </c>
       <c r="E46" s="1">
         <v>0</v>
       </c>
       <c r="F46" s="1">
-        <v>499882234</v>
+        <v>491537500</v>
       </c>
       <c r="G46" s="1">
-        <v>1500117766</v>
+        <v>1508462500</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -2707,10 +2722,10 @@
         <v>2620000000</v>
       </c>
       <c r="D56" s="1">
-        <v>632438367</v>
+        <v>597938367</v>
       </c>
       <c r="E56" s="1">
-        <v>377142000</v>
+        <v>411642000</v>
       </c>
       <c r="F56" s="1">
         <v>1009580367</v>
@@ -2785,16 +2800,16 @@
         <v>2500000000</v>
       </c>
       <c r="D59" s="1">
-        <v>1255850000</v>
+        <v>1249615100</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="1">
-        <v>1255850000</v>
+        <v>1249615100</v>
       </c>
       <c r="G59" s="1">
-        <v>1244150000</v>
+        <v>1250384900</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
@@ -3331,16 +3346,16 @@
         <v>110897810191</v>
       </c>
       <c r="D80" s="1">
-        <v>37700103078</v>
+        <v>37632341154</v>
       </c>
       <c r="E80" s="1">
-        <v>30903833688</v>
+        <v>30938333688</v>
       </c>
       <c r="F80" s="1">
-        <v>68603936766</v>
+        <v>68570674842</v>
       </c>
       <c r="G80" s="1">
-        <v>42293873425</v>
+        <v>42327135349</v>
       </c>
       <c r="H80" s="1">
         <v>671501500</v>
@@ -3435,16 +3450,16 @@
         <v>30639775739</v>
       </c>
       <c r="D84" s="1">
-        <v>17703310896</v>
+        <v>14089651858</v>
       </c>
       <c r="E84" s="1">
-        <v>7827327106</v>
+        <v>11540070294</v>
       </c>
       <c r="F84" s="1">
-        <v>25530638002</v>
+        <v>25629722152</v>
       </c>
       <c r="G84" s="1">
-        <v>5109137737</v>
+        <v>5010053587</v>
       </c>
       <c r="H84" s="1">
         <v>0</v>
@@ -3773,10 +3788,10 @@
         <v>419475000</v>
       </c>
       <c r="D97" s="1">
-        <v>140201000</v>
+        <v>134101000</v>
       </c>
       <c r="E97" s="1">
-        <v>39327850</v>
+        <v>45427850</v>
       </c>
       <c r="F97" s="1">
         <v>179528850</v>
@@ -3799,10 +3814,10 @@
         <v>255960000</v>
       </c>
       <c r="D98" s="1">
-        <v>116992900</v>
+        <v>94157900</v>
       </c>
       <c r="E98" s="1">
-        <v>95926500</v>
+        <v>118761500</v>
       </c>
       <c r="F98" s="1">
         <v>212919400</v>
@@ -3854,13 +3869,13 @@
         <v>97394900</v>
       </c>
       <c r="E100" s="1">
-        <v>0</v>
+        <v>28079000</v>
       </c>
       <c r="F100" s="1">
-        <v>97394900</v>
+        <v>125473900</v>
       </c>
       <c r="G100" s="1">
-        <v>194205100</v>
+        <v>166126100</v>
       </c>
       <c r="H100" s="1">
         <v>97200000</v>
@@ -4241,16 +4256,16 @@
         <v>81718644736</v>
       </c>
       <c r="D115" s="1">
-        <v>20082497637</v>
+        <v>16439903599</v>
       </c>
       <c r="E115" s="1">
-        <v>32156841601</v>
+        <v>35926598789</v>
       </c>
       <c r="F115" s="1">
-        <v>52239339238</v>
+        <v>52366502388</v>
       </c>
       <c r="G115" s="1">
-        <v>29479305498</v>
+        <v>29352142348</v>
       </c>
       <c r="H115" s="1">
         <v>475697500</v>
@@ -4371,10 +4386,10 @@
         <v>1200699000</v>
       </c>
       <c r="D120" s="1">
-        <v>383635885</v>
+        <v>377661885</v>
       </c>
       <c r="E120" s="1">
-        <v>75246975</v>
+        <v>81220975</v>
       </c>
       <c r="F120" s="1">
         <v>458882860</v>
@@ -4657,10 +4672,10 @@
         <v>118875000</v>
       </c>
       <c r="D131" s="1">
-        <v>28885900</v>
+        <v>22247900</v>
       </c>
       <c r="E131" s="1">
-        <v>33129500</v>
+        <v>39767500</v>
       </c>
       <c r="F131" s="1">
         <v>62015400</v>
@@ -4816,13 +4831,13 @@
         <v>0</v>
       </c>
       <c r="E137" s="1">
-        <v>98367250</v>
+        <v>99517250</v>
       </c>
       <c r="F137" s="1">
-        <v>98367250</v>
+        <v>99517250</v>
       </c>
       <c r="G137" s="1">
-        <v>61622750</v>
+        <v>60472750</v>
       </c>
       <c r="H137" s="1">
         <v>53330000</v>
@@ -4894,13 +4909,13 @@
         <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>4728277928</v>
+        <v>4728292928</v>
       </c>
       <c r="F140" s="1">
-        <v>4728277928</v>
+        <v>4728292928</v>
       </c>
       <c r="G140" s="1">
-        <v>5220816155</v>
+        <v>5220801155</v>
       </c>
       <c r="H140" s="1">
         <v>0</v>
@@ -5125,16 +5140,16 @@
         <v>50726099717</v>
       </c>
       <c r="D149" s="1">
-        <v>10989180456</v>
+        <v>10976568456</v>
       </c>
       <c r="E149" s="1">
-        <v>20507597529</v>
+        <v>20521374529</v>
       </c>
       <c r="F149" s="1">
-        <v>31496777985</v>
+        <v>31497942985</v>
       </c>
       <c r="G149" s="1">
-        <v>19229321732</v>
+        <v>19228156732</v>
       </c>
       <c r="H149" s="1">
         <v>411080000</v>
@@ -5151,16 +5166,16 @@
         <v>11383511000</v>
       </c>
       <c r="D150" s="1">
-        <v>6184426052</v>
+        <v>6152401052</v>
       </c>
       <c r="E150" s="1">
         <v>4240465838</v>
       </c>
       <c r="F150" s="1">
-        <v>10424891890</v>
+        <v>10392866890</v>
       </c>
       <c r="G150" s="1">
-        <v>958619110</v>
+        <v>990644110</v>
       </c>
       <c r="H150" s="1">
         <v>0</v>
@@ -5171,10 +5186,10 @@
         <v>11</v>
       </c>
       <c r="B151" s="1">
-        <v>3998040540</v>
+        <v>4687847624</v>
       </c>
       <c r="C151" s="1">
-        <v>3998040540</v>
+        <v>4687847624</v>
       </c>
       <c r="D151" s="1">
         <v>2801605891</v>
@@ -5186,7 +5201,7 @@
         <v>3248107530</v>
       </c>
       <c r="G151" s="1">
-        <v>749933010</v>
+        <v>1439740094</v>
       </c>
       <c r="H151" s="1">
         <v>0</v>
@@ -5255,16 +5270,16 @@
         <v>870437000</v>
       </c>
       <c r="D154" s="1">
-        <v>172820000</v>
+        <v>118430000</v>
       </c>
       <c r="E154" s="1">
-        <v>526892000</v>
+        <v>575892000</v>
       </c>
       <c r="F154" s="1">
-        <v>699712000</v>
+        <v>694322000</v>
       </c>
       <c r="G154" s="1">
-        <v>170725000</v>
+        <v>176115000</v>
       </c>
       <c r="H154" s="1">
         <v>0</v>
@@ -5275,10 +5290,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="1">
-        <v>393763000</v>
+        <v>10224916</v>
       </c>
       <c r="C155" s="1">
-        <v>393763000</v>
+        <v>10224916</v>
       </c>
       <c r="D155" s="1">
         <v>0</v>
@@ -5290,7 +5305,7 @@
         <v>10224916</v>
       </c>
       <c r="G155" s="1">
-        <v>383538084</v>
+        <v>0</v>
       </c>
       <c r="H155" s="1">
         <v>0</v>
@@ -5359,16 +5374,16 @@
         <v>996956000</v>
       </c>
       <c r="D158" s="1">
-        <v>541984090</v>
+        <v>503078021</v>
       </c>
       <c r="E158" s="1">
-        <v>8750000</v>
+        <v>43800510</v>
       </c>
       <c r="F158" s="1">
-        <v>550734090</v>
+        <v>546878531</v>
       </c>
       <c r="G158" s="1">
-        <v>446221910</v>
+        <v>450077469</v>
       </c>
       <c r="H158" s="1">
         <v>0</v>
@@ -5379,10 +5394,10 @@
         <v>53</v>
       </c>
       <c r="B159" s="1">
-        <v>317990000</v>
+        <v>11721000</v>
       </c>
       <c r="C159" s="1">
-        <v>317990000</v>
+        <v>11721000</v>
       </c>
       <c r="D159" s="1">
         <v>7864000</v>
@@ -5394,7 +5409,7 @@
         <v>11721000</v>
       </c>
       <c r="G159" s="1">
-        <v>306269000</v>
+        <v>0</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
@@ -5596,13 +5611,13 @@
         <v>0</v>
       </c>
       <c r="E167" s="1">
-        <v>1021791897</v>
+        <v>1022061097</v>
       </c>
       <c r="F167" s="1">
-        <v>1021791897</v>
+        <v>1022061097</v>
       </c>
       <c r="G167" s="1">
-        <v>1347208103</v>
+        <v>1346938903</v>
       </c>
       <c r="H167" s="1">
         <v>0</v>
@@ -5639,22 +5654,22 @@
         <v>26</v>
       </c>
       <c r="B169" s="1">
-        <v>545000000</v>
+        <v>731400000</v>
       </c>
       <c r="C169" s="1">
-        <v>408750000</v>
+        <v>595150000</v>
       </c>
       <c r="D169" s="1">
-        <v>98178350</v>
+        <v>79585850</v>
       </c>
       <c r="E169" s="1">
-        <v>149383644</v>
+        <v>166133644</v>
       </c>
       <c r="F169" s="1">
-        <v>247561994</v>
+        <v>245719494</v>
       </c>
       <c r="G169" s="1">
-        <v>161188006</v>
+        <v>349430506</v>
       </c>
       <c r="H169" s="1">
         <v>136250000</v>
@@ -5691,10 +5706,10 @@
         <v>28</v>
       </c>
       <c r="B171" s="1">
-        <v>586200000</v>
+        <v>399800000</v>
       </c>
       <c r="C171" s="1">
-        <v>439650000</v>
+        <v>253250000</v>
       </c>
       <c r="D171" s="1">
         <v>0</v>
@@ -5706,7 +5721,7 @@
         <v>104678200</v>
       </c>
       <c r="G171" s="1">
-        <v>334971800</v>
+        <v>148571800</v>
       </c>
       <c r="H171" s="1">
         <v>146550000</v>
@@ -5752,13 +5767,13 @@
         <v>0</v>
       </c>
       <c r="E173" s="1">
-        <v>83109750</v>
+        <v>83434750</v>
       </c>
       <c r="F173" s="1">
-        <v>83109750</v>
+        <v>83434750</v>
       </c>
       <c r="G173" s="1">
-        <v>79191750</v>
+        <v>78866750</v>
       </c>
       <c r="H173" s="1">
         <v>54100500</v>
@@ -5804,13 +5819,13 @@
         <v>0</v>
       </c>
       <c r="E175" s="1">
-        <v>3530399915</v>
+        <v>3530411165</v>
       </c>
       <c r="F175" s="1">
-        <v>3530399915</v>
+        <v>3530411165</v>
       </c>
       <c r="G175" s="1">
-        <v>3974323463</v>
+        <v>3974312213</v>
       </c>
       <c r="H175" s="1">
         <v>0</v>
@@ -6009,16 +6024,16 @@
         <v>46375593027</v>
       </c>
       <c r="D183" s="1">
-        <v>13403580307</v>
+        <v>13259666738</v>
       </c>
       <c r="E183" s="1">
-        <v>15388962900</v>
+        <v>15490368860</v>
       </c>
       <c r="F183" s="1">
-        <v>28792543207</v>
+        <v>28750035598</v>
       </c>
       <c r="G183" s="1">
-        <v>17583049820</v>
+        <v>17625557429</v>
       </c>
       <c r="H183" s="1">
         <v>449400500</v>
@@ -6347,16 +6362,16 @@
         <v>281000000</v>
       </c>
       <c r="D196" s="1">
-        <v>17423256</v>
+        <v>23458860</v>
       </c>
       <c r="E196" s="1">
         <v>30944688</v>
       </c>
       <c r="F196" s="1">
-        <v>48367944</v>
+        <v>54403548</v>
       </c>
       <c r="G196" s="1">
-        <v>232632056</v>
+        <v>226596452</v>
       </c>
       <c r="H196" s="1">
         <v>0</v>
@@ -6555,16 +6570,16 @@
         <v>320100000</v>
       </c>
       <c r="D204" s="1">
-        <v>95100000</v>
+        <v>49300000</v>
       </c>
       <c r="E204" s="1">
-        <v>107075626</v>
+        <v>147775626</v>
       </c>
       <c r="F204" s="1">
-        <v>202175626</v>
+        <v>197075626</v>
       </c>
       <c r="G204" s="1">
-        <v>117924374</v>
+        <v>123024374</v>
       </c>
       <c r="H204" s="1">
         <v>0</v>
@@ -6685,16 +6700,16 @@
         <v>337500000</v>
       </c>
       <c r="D209" s="1">
-        <v>25705500</v>
+        <v>29500500</v>
       </c>
       <c r="E209" s="1">
         <v>78165454</v>
       </c>
       <c r="F209" s="1">
-        <v>103870954</v>
+        <v>107665954</v>
       </c>
       <c r="G209" s="1">
-        <v>233629046</v>
+        <v>229834046</v>
       </c>
       <c r="H209" s="1">
         <v>112500000</v>
@@ -7023,16 +7038,16 @@
         <v>47499233545</v>
       </c>
       <c r="D222" s="1">
-        <v>11354050569</v>
+        <v>11318081173</v>
       </c>
       <c r="E222" s="1">
-        <v>16287106540</v>
+        <v>16327806540</v>
       </c>
       <c r="F222" s="1">
-        <v>27641157109</v>
+        <v>27645887713</v>
       </c>
       <c r="G222" s="1">
-        <v>19858076436</v>
+        <v>19853345832</v>
       </c>
       <c r="H222" s="1">
         <v>415261500</v>
@@ -7205,16 +7220,16 @@
         <v>1380000000</v>
       </c>
       <c r="D229" s="1">
-        <v>154752855</v>
+        <v>204436251</v>
       </c>
       <c r="E229" s="1">
         <v>741651216</v>
       </c>
       <c r="F229" s="1">
-        <v>896404071</v>
+        <v>946087467</v>
       </c>
       <c r="G229" s="1">
-        <v>483595929</v>
+        <v>433912533</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
@@ -7413,16 +7428,16 @@
         <v>250000000</v>
       </c>
       <c r="D237" s="1">
-        <v>0</v>
+        <v>49983000</v>
       </c>
       <c r="E237" s="1">
         <v>32848750</v>
       </c>
       <c r="F237" s="1">
-        <v>32848750</v>
+        <v>82831750</v>
       </c>
       <c r="G237" s="1">
-        <v>217151250</v>
+        <v>167168250</v>
       </c>
       <c r="H237" s="1">
         <v>0</v>
@@ -7829,16 +7844,16 @@
         <v>48914772555</v>
       </c>
       <c r="D253" s="1">
-        <v>14177447874</v>
+        <v>14277114270</v>
       </c>
       <c r="E253" s="1">
         <v>16228714077</v>
       </c>
       <c r="F253" s="1">
-        <v>30406161951</v>
+        <v>30505828347</v>
       </c>
       <c r="G253" s="1">
-        <v>18508610604</v>
+        <v>18408944208</v>
       </c>
       <c r="H253" s="1">
         <v>525212165</v>
@@ -8037,16 +8052,16 @@
         <v>1700000000</v>
       </c>
       <c r="D261" s="1">
-        <v>92594900</v>
+        <v>588354941</v>
       </c>
       <c r="E261" s="1">
         <v>652261855</v>
       </c>
       <c r="F261" s="1">
-        <v>744856755</v>
+        <v>1240616796</v>
       </c>
       <c r="G261" s="1">
-        <v>955143245</v>
+        <v>459383204</v>
       </c>
       <c r="H261" s="1">
         <v>0</v>
@@ -8869,16 +8884,16 @@
         <v>63706784713</v>
       </c>
       <c r="D293" s="1">
-        <v>15663633129</v>
+        <v>16159393170</v>
       </c>
       <c r="E293" s="1">
         <v>21951579299</v>
       </c>
       <c r="F293" s="1">
-        <v>37615212428</v>
+        <v>38110972469</v>
       </c>
       <c r="G293" s="1">
-        <v>26091572285</v>
+        <v>25595812244</v>
       </c>
       <c r="H293" s="1">
         <v>531045413</v>
@@ -9935,10 +9950,10 @@
         <v>1660344000</v>
       </c>
       <c r="D334" s="1">
-        <v>319513610</v>
+        <v>271172340</v>
       </c>
       <c r="E334" s="1">
-        <v>827748278</v>
+        <v>876089548</v>
       </c>
       <c r="F334" s="1">
         <v>1147261888</v>
@@ -10013,10 +10028,10 @@
         <v>1039505000</v>
       </c>
       <c r="D337" s="1">
-        <v>1013000</v>
+        <v>0</v>
       </c>
       <c r="E337" s="1">
-        <v>1021226000</v>
+        <v>1022239000</v>
       </c>
       <c r="F337" s="1">
         <v>1022239000</v>
@@ -10559,10 +10574,10 @@
         <v>57427089299</v>
       </c>
       <c r="D358" s="1">
-        <v>17325798235</v>
+        <v>17276443965</v>
       </c>
       <c r="E358" s="1">
-        <v>20528322351</v>
+        <v>20577676621</v>
       </c>
       <c r="F358" s="1">
         <v>37854120586</v>
@@ -11417,16 +11432,16 @@
         <v>2666359332</v>
       </c>
       <c r="D391" s="1">
-        <v>2310150400</v>
+        <v>2294262688</v>
       </c>
       <c r="E391" s="1">
         <v>344920370</v>
       </c>
       <c r="F391" s="1">
-        <v>2655070770</v>
+        <v>2639183058</v>
       </c>
       <c r="G391" s="1">
-        <v>11288562</v>
+        <v>27176274</v>
       </c>
       <c r="H391" s="1">
         <v>0</v>
@@ -11885,10 +11900,10 @@
         <v>445223250</v>
       </c>
       <c r="D409" s="1">
-        <v>61843837</v>
+        <v>38443837</v>
       </c>
       <c r="E409" s="1">
-        <v>283828950</v>
+        <v>307228950</v>
       </c>
       <c r="F409" s="1">
         <v>345672787</v>
@@ -12275,902 +12290,902 @@
         <v>35458361640</v>
       </c>
       <c r="D424" s="1">
-        <v>7554336106</v>
+        <v>7515048394</v>
       </c>
       <c r="E424" s="1">
-        <v>12035014120</v>
+        <v>12058414120</v>
       </c>
       <c r="F424" s="1">
-        <v>19589350226</v>
+        <v>19573462514</v>
       </c>
       <c r="G424" s="1">
-        <v>15869011414</v>
+        <v>15884899126</v>
       </c>
       <c r="H424" s="1">
         <v>472807750</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A425" s="2" t="s">
+      <c r="A425" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B425" s="3">
+      <c r="B425" s="5">
         <v>873740000</v>
       </c>
-      <c r="C425" s="3">
+      <c r="C425" s="5">
         <v>873740000</v>
       </c>
-      <c r="D425" s="3">
+      <c r="D425" s="5">
         <v>630188000</v>
       </c>
-      <c r="E425" s="3">
+      <c r="E425" s="5">
         <v>129620052</v>
       </c>
-      <c r="F425" s="3">
+      <c r="F425" s="5">
         <v>759808052</v>
       </c>
-      <c r="G425" s="3">
+      <c r="G425" s="5">
         <v>113931948</v>
       </c>
-      <c r="H425" s="3">
+      <c r="H425" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A426" s="2" t="s">
+      <c r="A426" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B426" s="3"/>
-      <c r="C426" s="3"/>
-      <c r="D426" s="3"/>
-      <c r="E426" s="3"/>
-      <c r="F426" s="3"/>
-      <c r="G426" s="3"/>
-      <c r="H426" s="3"/>
+      <c r="B426" s="5"/>
+      <c r="C426" s="5"/>
+      <c r="D426" s="5"/>
+      <c r="E426" s="5"/>
+      <c r="F426" s="5"/>
+      <c r="G426" s="5"/>
+      <c r="H426" s="5"/>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A427" s="2" t="s">
+      <c r="A427" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B427" s="3"/>
-      <c r="C427" s="3"/>
-      <c r="D427" s="3"/>
-      <c r="E427" s="3"/>
-      <c r="F427" s="3"/>
-      <c r="G427" s="3"/>
-      <c r="H427" s="3"/>
+      <c r="B427" s="5"/>
+      <c r="C427" s="5"/>
+      <c r="D427" s="5"/>
+      <c r="E427" s="5"/>
+      <c r="F427" s="5"/>
+      <c r="G427" s="5"/>
+      <c r="H427" s="5"/>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A428" s="2" t="s">
+      <c r="A428" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B428" s="3"/>
-      <c r="C428" s="3"/>
-      <c r="D428" s="3"/>
-      <c r="E428" s="3"/>
-      <c r="F428" s="3"/>
-      <c r="G428" s="3"/>
-      <c r="H428" s="3"/>
+      <c r="B428" s="5"/>
+      <c r="C428" s="5"/>
+      <c r="D428" s="5"/>
+      <c r="E428" s="5"/>
+      <c r="F428" s="5"/>
+      <c r="G428" s="5"/>
+      <c r="H428" s="5"/>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A429" s="2" t="s">
+      <c r="A429" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B429" s="3"/>
-      <c r="C429" s="3"/>
-      <c r="D429" s="3"/>
-      <c r="E429" s="3"/>
-      <c r="F429" s="3"/>
-      <c r="G429" s="3"/>
-      <c r="H429" s="3"/>
+      <c r="B429" s="5"/>
+      <c r="C429" s="5"/>
+      <c r="D429" s="5"/>
+      <c r="E429" s="5"/>
+      <c r="F429" s="5"/>
+      <c r="G429" s="5"/>
+      <c r="H429" s="5"/>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A430" s="2" t="s">
+      <c r="A430" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B430" s="3"/>
-      <c r="C430" s="3"/>
-      <c r="D430" s="3"/>
-      <c r="E430" s="3"/>
-      <c r="F430" s="3"/>
-      <c r="G430" s="3"/>
-      <c r="H430" s="3"/>
+      <c r="B430" s="5"/>
+      <c r="C430" s="5"/>
+      <c r="D430" s="5"/>
+      <c r="E430" s="5"/>
+      <c r="F430" s="5"/>
+      <c r="G430" s="5"/>
+      <c r="H430" s="5"/>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A431" s="2" t="s">
+      <c r="A431" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B431" s="3"/>
-      <c r="C431" s="3"/>
-      <c r="D431" s="3"/>
-      <c r="E431" s="3"/>
-      <c r="F431" s="3"/>
-      <c r="G431" s="3"/>
-      <c r="H431" s="3"/>
+      <c r="B431" s="5"/>
+      <c r="C431" s="5"/>
+      <c r="D431" s="5"/>
+      <c r="E431" s="5"/>
+      <c r="F431" s="5"/>
+      <c r="G431" s="5"/>
+      <c r="H431" s="5"/>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A432" s="2" t="s">
+      <c r="A432" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B432" s="3"/>
-      <c r="C432" s="3"/>
-      <c r="D432" s="3"/>
-      <c r="E432" s="3"/>
-      <c r="F432" s="3"/>
-      <c r="G432" s="3"/>
-      <c r="H432" s="3"/>
+      <c r="B432" s="5"/>
+      <c r="C432" s="5"/>
+      <c r="D432" s="5"/>
+      <c r="E432" s="5"/>
+      <c r="F432" s="5"/>
+      <c r="G432" s="5"/>
+      <c r="H432" s="5"/>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A433" s="2" t="s">
+      <c r="A433" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B433" s="3"/>
-      <c r="C433" s="3"/>
-      <c r="D433" s="3"/>
-      <c r="E433" s="3"/>
-      <c r="F433" s="3"/>
-      <c r="G433" s="3"/>
-      <c r="H433" s="3"/>
+      <c r="B433" s="5"/>
+      <c r="C433" s="5"/>
+      <c r="D433" s="5"/>
+      <c r="E433" s="5"/>
+      <c r="F433" s="5"/>
+      <c r="G433" s="5"/>
+      <c r="H433" s="5"/>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A434" s="2" t="s">
+      <c r="A434" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B434" s="3"/>
-      <c r="C434" s="3"/>
-      <c r="D434" s="3"/>
-      <c r="E434" s="3"/>
-      <c r="F434" s="3"/>
-      <c r="G434" s="3"/>
-      <c r="H434" s="3"/>
+      <c r="B434" s="5"/>
+      <c r="C434" s="5"/>
+      <c r="D434" s="5"/>
+      <c r="E434" s="5"/>
+      <c r="F434" s="5"/>
+      <c r="G434" s="5"/>
+      <c r="H434" s="5"/>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A435" s="2" t="s">
+      <c r="A435" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B435" s="3"/>
-      <c r="C435" s="3"/>
-      <c r="D435" s="3"/>
-      <c r="E435" s="3"/>
-      <c r="F435" s="3"/>
-      <c r="G435" s="3"/>
-      <c r="H435" s="3"/>
+      <c r="B435" s="5"/>
+      <c r="C435" s="5"/>
+      <c r="D435" s="5"/>
+      <c r="E435" s="5"/>
+      <c r="F435" s="5"/>
+      <c r="G435" s="5"/>
+      <c r="H435" s="5"/>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A436" s="2" t="s">
+      <c r="A436" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B436" s="3"/>
-      <c r="C436" s="3"/>
-      <c r="D436" s="3"/>
-      <c r="E436" s="3"/>
-      <c r="F436" s="3"/>
-      <c r="G436" s="3"/>
-      <c r="H436" s="3"/>
+      <c r="B436" s="5"/>
+      <c r="C436" s="5"/>
+      <c r="D436" s="5"/>
+      <c r="E436" s="5"/>
+      <c r="F436" s="5"/>
+      <c r="G436" s="5"/>
+      <c r="H436" s="5"/>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A437" s="2" t="s">
+      <c r="A437" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B437" s="3"/>
-      <c r="C437" s="3"/>
-      <c r="D437" s="3"/>
-      <c r="E437" s="3"/>
-      <c r="F437" s="3"/>
-      <c r="G437" s="3"/>
-      <c r="H437" s="3"/>
+      <c r="B437" s="5"/>
+      <c r="C437" s="5"/>
+      <c r="D437" s="5"/>
+      <c r="E437" s="5"/>
+      <c r="F437" s="5"/>
+      <c r="G437" s="5"/>
+      <c r="H437" s="5"/>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A438" s="2" t="s">
+      <c r="A438" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B438" s="3"/>
-      <c r="C438" s="3"/>
-      <c r="D438" s="3"/>
-      <c r="E438" s="3"/>
-      <c r="F438" s="3"/>
-      <c r="G438" s="3"/>
-      <c r="H438" s="3"/>
+      <c r="B438" s="5"/>
+      <c r="C438" s="5"/>
+      <c r="D438" s="5"/>
+      <c r="E438" s="5"/>
+      <c r="F438" s="5"/>
+      <c r="G438" s="5"/>
+      <c r="H438" s="5"/>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A439" s="2" t="s">
+      <c r="A439" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B439" s="3"/>
-      <c r="C439" s="3"/>
-      <c r="D439" s="3"/>
-      <c r="E439" s="3"/>
-      <c r="F439" s="3"/>
-      <c r="G439" s="3"/>
-      <c r="H439" s="3"/>
+      <c r="B439" s="5"/>
+      <c r="C439" s="5"/>
+      <c r="D439" s="5"/>
+      <c r="E439" s="5"/>
+      <c r="F439" s="5"/>
+      <c r="G439" s="5"/>
+      <c r="H439" s="5"/>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A440" s="2" t="s">
+      <c r="A440" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B440" s="3"/>
-      <c r="C440" s="3"/>
-      <c r="D440" s="3"/>
-      <c r="E440" s="3"/>
-      <c r="F440" s="3"/>
-      <c r="G440" s="3"/>
-      <c r="H440" s="3"/>
+      <c r="B440" s="5"/>
+      <c r="C440" s="5"/>
+      <c r="D440" s="5"/>
+      <c r="E440" s="5"/>
+      <c r="F440" s="5"/>
+      <c r="G440" s="5"/>
+      <c r="H440" s="5"/>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A441" s="2" t="s">
+      <c r="A441" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B441" s="3"/>
-      <c r="C441" s="3"/>
-      <c r="D441" s="3"/>
-      <c r="E441" s="3"/>
-      <c r="F441" s="3"/>
-      <c r="G441" s="3"/>
-      <c r="H441" s="3"/>
+      <c r="B441" s="5"/>
+      <c r="C441" s="5"/>
+      <c r="D441" s="5"/>
+      <c r="E441" s="5"/>
+      <c r="F441" s="5"/>
+      <c r="G441" s="5"/>
+      <c r="H441" s="5"/>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A442" s="2" t="s">
+      <c r="A442" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B442" s="3">
+      <c r="B442" s="5">
         <v>474786000</v>
       </c>
-      <c r="C442" s="3">
+      <c r="C442" s="5">
         <v>474786000</v>
       </c>
-      <c r="D442" s="3">
-        <v>0</v>
-      </c>
-      <c r="E442" s="3"/>
-      <c r="F442" s="3"/>
-      <c r="G442" s="3">
+      <c r="D442" s="5">
+        <v>0</v>
+      </c>
+      <c r="E442" s="5"/>
+      <c r="F442" s="5"/>
+      <c r="G442" s="5">
         <v>474786000</v>
       </c>
-      <c r="H442" s="3">
+      <c r="H442" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A443" s="2" t="s">
+      <c r="A443" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B443" s="3">
+      <c r="B443" s="5">
         <v>208424730</v>
       </c>
-      <c r="C443" s="3">
+      <c r="C443" s="5">
         <v>208424730</v>
       </c>
-      <c r="D443" s="3">
+      <c r="D443" s="5">
         <v>180590600</v>
       </c>
-      <c r="E443" s="3"/>
-      <c r="F443" s="3">
+      <c r="E443" s="5"/>
+      <c r="F443" s="5">
         <v>180590600</v>
       </c>
-      <c r="G443" s="3">
+      <c r="G443" s="5">
         <v>27834130</v>
       </c>
-      <c r="H443" s="3">
+      <c r="H443" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A444" s="2" t="s">
+      <c r="A444" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B444" s="3">
+      <c r="B444" s="5">
         <v>20000000</v>
       </c>
-      <c r="C444" s="3">
+      <c r="C444" s="5">
         <v>20000000</v>
       </c>
-      <c r="D444" s="3">
-        <v>0</v>
-      </c>
-      <c r="E444" s="3">
+      <c r="D444" s="5">
+        <v>0</v>
+      </c>
+      <c r="E444" s="5">
         <v>13970000</v>
       </c>
-      <c r="F444" s="3">
+      <c r="F444" s="5">
         <v>13970000</v>
       </c>
-      <c r="G444" s="3">
+      <c r="G444" s="5">
         <v>6030000</v>
       </c>
-      <c r="H444" s="3">
+      <c r="H444" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A445" s="2" t="s">
+      <c r="A445" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B445" s="3">
+      <c r="B445" s="5">
         <v>220000000</v>
       </c>
-      <c r="C445" s="3">
+      <c r="C445" s="5">
         <v>220000000</v>
       </c>
-      <c r="D445" s="3">
-        <v>0</v>
-      </c>
-      <c r="E445" s="3">
+      <c r="D445" s="5">
+        <v>0</v>
+      </c>
+      <c r="E445" s="5">
         <v>59808678</v>
       </c>
-      <c r="F445" s="3">
+      <c r="F445" s="5">
         <v>59808678</v>
       </c>
-      <c r="G445" s="3">
+      <c r="G445" s="5">
         <v>160191322</v>
       </c>
-      <c r="H445" s="3">
+      <c r="H445" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A446" s="2" t="s">
+      <c r="A446" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B446" s="3">
+      <c r="B446" s="5">
         <v>75000000</v>
       </c>
-      <c r="C446" s="3">
+      <c r="C446" s="5">
         <v>75000000</v>
       </c>
-      <c r="D446" s="3">
+      <c r="D446" s="5">
         <v>38500000</v>
       </c>
-      <c r="E446" s="3"/>
-      <c r="F446" s="3">
+      <c r="E446" s="5"/>
+      <c r="F446" s="5">
         <v>38500000</v>
       </c>
-      <c r="G446" s="3">
+      <c r="G446" s="5">
         <v>36500000</v>
       </c>
-      <c r="H446" s="3">
+      <c r="H446" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A447" s="2" t="s">
+      <c r="A447" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B447" s="3"/>
-      <c r="C447" s="3"/>
-      <c r="D447" s="3"/>
-      <c r="E447" s="3"/>
-      <c r="F447" s="3"/>
-      <c r="G447" s="3"/>
-      <c r="H447" s="3"/>
+      <c r="B447" s="5"/>
+      <c r="C447" s="5"/>
+      <c r="D447" s="5"/>
+      <c r="E447" s="5"/>
+      <c r="F447" s="5"/>
+      <c r="G447" s="5"/>
+      <c r="H447" s="5"/>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A448" s="2" t="s">
+      <c r="A448" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B448" s="3"/>
-      <c r="C448" s="3"/>
-      <c r="D448" s="3"/>
-      <c r="E448" s="3"/>
-      <c r="F448" s="3"/>
-      <c r="G448" s="3"/>
-      <c r="H448" s="3"/>
+      <c r="B448" s="5"/>
+      <c r="C448" s="5"/>
+      <c r="D448" s="5"/>
+      <c r="E448" s="5"/>
+      <c r="F448" s="5"/>
+      <c r="G448" s="5"/>
+      <c r="H448" s="5"/>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A449" s="2" t="s">
+      <c r="A449" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B449" s="3">
+      <c r="B449" s="5">
         <v>60000000</v>
       </c>
-      <c r="C449" s="3">
+      <c r="C449" s="5">
         <v>45000000</v>
       </c>
-      <c r="D449" s="3">
+      <c r="D449" s="5">
         <v>1120000</v>
       </c>
-      <c r="E449" s="3">
+      <c r="E449" s="5">
         <v>9000000</v>
       </c>
-      <c r="F449" s="3">
+      <c r="F449" s="5">
         <v>10120000</v>
       </c>
-      <c r="G449" s="3">
+      <c r="G449" s="5">
         <v>34880000</v>
       </c>
-      <c r="H449" s="3">
+      <c r="H449" s="5">
         <v>15000000</v>
       </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A450" s="2" t="s">
+      <c r="A450" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B450" s="3">
+      <c r="B450" s="5">
         <v>45150000</v>
       </c>
-      <c r="C450" s="3">
+      <c r="C450" s="5">
         <v>45150000</v>
       </c>
-      <c r="D450" s="3">
-        <v>0</v>
-      </c>
-      <c r="E450" s="3">
+      <c r="D450" s="5">
+        <v>0</v>
+      </c>
+      <c r="E450" s="5">
         <v>20796200</v>
       </c>
-      <c r="F450" s="3">
+      <c r="F450" s="5">
         <v>20796200</v>
       </c>
-      <c r="G450" s="3">
+      <c r="G450" s="5">
         <v>24353800</v>
       </c>
-      <c r="H450" s="3">
+      <c r="H450" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A451" s="2" t="s">
+      <c r="A451" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B451" s="3"/>
-      <c r="C451" s="3"/>
-      <c r="D451" s="3"/>
-      <c r="E451" s="3"/>
-      <c r="F451" s="3"/>
-      <c r="G451" s="3"/>
-      <c r="H451" s="3"/>
+      <c r="B451" s="5"/>
+      <c r="C451" s="5"/>
+      <c r="D451" s="5"/>
+      <c r="E451" s="5"/>
+      <c r="F451" s="5"/>
+      <c r="G451" s="5"/>
+      <c r="H451" s="5"/>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A452" s="2" t="s">
+      <c r="A452" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B452" s="3"/>
-      <c r="C452" s="3"/>
-      <c r="D452" s="3"/>
-      <c r="E452" s="3"/>
-      <c r="F452" s="3"/>
-      <c r="G452" s="3"/>
-      <c r="H452" s="3"/>
+      <c r="B452" s="5"/>
+      <c r="C452" s="5"/>
+      <c r="D452" s="5"/>
+      <c r="E452" s="5"/>
+      <c r="F452" s="5"/>
+      <c r="G452" s="5"/>
+      <c r="H452" s="5"/>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A453" s="2" t="s">
+      <c r="A453" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B453" s="3"/>
-      <c r="C453" s="3"/>
-      <c r="D453" s="3"/>
-      <c r="E453" s="3"/>
-      <c r="F453" s="3"/>
-      <c r="G453" s="3"/>
-      <c r="H453" s="3"/>
+      <c r="B453" s="5"/>
+      <c r="C453" s="5"/>
+      <c r="D453" s="5"/>
+      <c r="E453" s="5"/>
+      <c r="F453" s="5"/>
+      <c r="G453" s="5"/>
+      <c r="H453" s="5"/>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A454" s="2" t="s">
+      <c r="A454" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B454" s="3"/>
-      <c r="C454" s="3"/>
-      <c r="D454" s="3"/>
-      <c r="E454" s="3"/>
-      <c r="F454" s="3"/>
-      <c r="G454" s="3"/>
-      <c r="H454" s="3"/>
+      <c r="B454" s="5"/>
+      <c r="C454" s="5"/>
+      <c r="D454" s="5"/>
+      <c r="E454" s="5"/>
+      <c r="F454" s="5"/>
+      <c r="G454" s="5"/>
+      <c r="H454" s="5"/>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A455" s="2" t="s">
+      <c r="A455" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B455" s="3"/>
-      <c r="C455" s="3"/>
-      <c r="D455" s="3"/>
-      <c r="E455" s="3"/>
-      <c r="F455" s="3"/>
-      <c r="G455" s="3"/>
-      <c r="H455" s="3"/>
+      <c r="B455" s="5"/>
+      <c r="C455" s="5"/>
+      <c r="D455" s="5"/>
+      <c r="E455" s="5"/>
+      <c r="F455" s="5"/>
+      <c r="G455" s="5"/>
+      <c r="H455" s="5"/>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A456" s="2" t="s">
+      <c r="A456" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B456" s="3"/>
-      <c r="C456" s="3"/>
-      <c r="D456" s="3"/>
-      <c r="E456" s="3"/>
-      <c r="F456" s="3"/>
-      <c r="G456" s="3"/>
-      <c r="H456" s="3"/>
+      <c r="B456" s="5"/>
+      <c r="C456" s="5"/>
+      <c r="D456" s="5"/>
+      <c r="E456" s="5"/>
+      <c r="F456" s="5"/>
+      <c r="G456" s="5"/>
+      <c r="H456" s="5"/>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A457" s="2" t="s">
+      <c r="A457" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B457" s="3"/>
-      <c r="C457" s="3"/>
-      <c r="D457" s="3"/>
-      <c r="E457" s="3"/>
-      <c r="F457" s="3"/>
-      <c r="G457" s="3"/>
-      <c r="H457" s="3"/>
+      <c r="B457" s="5"/>
+      <c r="C457" s="5"/>
+      <c r="D457" s="5"/>
+      <c r="E457" s="5"/>
+      <c r="F457" s="5"/>
+      <c r="G457" s="5"/>
+      <c r="H457" s="5"/>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A458" s="2" t="s">
+      <c r="A458" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B458" s="3"/>
-      <c r="C458" s="3"/>
-      <c r="D458" s="3"/>
-      <c r="E458" s="3"/>
-      <c r="F458" s="3"/>
-      <c r="G458" s="3"/>
-      <c r="H458" s="3"/>
+      <c r="B458" s="5"/>
+      <c r="C458" s="5"/>
+      <c r="D458" s="5"/>
+      <c r="E458" s="5"/>
+      <c r="F458" s="5"/>
+      <c r="G458" s="5"/>
+      <c r="H458" s="5"/>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A459" s="2" t="s">
+      <c r="A459" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B459" s="3"/>
-      <c r="C459" s="3"/>
-      <c r="D459" s="3"/>
-      <c r="E459" s="3"/>
-      <c r="F459" s="3"/>
-      <c r="G459" s="3"/>
-      <c r="H459" s="3"/>
+      <c r="B459" s="5"/>
+      <c r="C459" s="5"/>
+      <c r="D459" s="5"/>
+      <c r="E459" s="5"/>
+      <c r="F459" s="5"/>
+      <c r="G459" s="5"/>
+      <c r="H459" s="5"/>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A460" s="2" t="s">
+      <c r="A460" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B460" s="3">
+      <c r="B460" s="5">
         <v>6000000</v>
       </c>
-      <c r="C460" s="3">
+      <c r="C460" s="5">
         <v>4500000</v>
       </c>
-      <c r="D460" s="3">
-        <v>0</v>
-      </c>
-      <c r="E460" s="3"/>
-      <c r="F460" s="3"/>
-      <c r="G460" s="3">
+      <c r="D460" s="5">
+        <v>0</v>
+      </c>
+      <c r="E460" s="5"/>
+      <c r="F460" s="5"/>
+      <c r="G460" s="5">
         <v>4500000</v>
       </c>
-      <c r="H460" s="3">
+      <c r="H460" s="5">
         <v>1500000</v>
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A461" s="2" t="s">
+      <c r="A461" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B461" s="3">
+      <c r="B461" s="5">
         <v>41000000</v>
       </c>
-      <c r="C461" s="3">
+      <c r="C461" s="5">
         <v>30750000</v>
       </c>
-      <c r="D461" s="3">
+      <c r="D461" s="5">
         <v>2064300</v>
       </c>
-      <c r="E461" s="3">
+      <c r="E461" s="5">
         <v>3989400</v>
       </c>
-      <c r="F461" s="3">
+      <c r="F461" s="5">
         <v>6053700</v>
       </c>
-      <c r="G461" s="3">
+      <c r="G461" s="5">
         <v>24696300</v>
       </c>
-      <c r="H461" s="3">
+      <c r="H461" s="5">
         <v>10250000</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A462" s="2" t="s">
+      <c r="A462" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B462" s="3">
+      <c r="B462" s="5">
         <v>12000000</v>
       </c>
-      <c r="C462" s="3">
+      <c r="C462" s="5">
         <v>3000000</v>
       </c>
-      <c r="D462" s="3">
-        <v>0</v>
-      </c>
-      <c r="E462" s="3"/>
-      <c r="F462" s="3"/>
-      <c r="G462" s="3">
+      <c r="D462" s="5">
+        <v>0</v>
+      </c>
+      <c r="E462" s="5"/>
+      <c r="F462" s="5"/>
+      <c r="G462" s="5">
         <v>3000000</v>
       </c>
-      <c r="H462" s="3">
+      <c r="H462" s="5">
         <v>9000000</v>
       </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A463" s="2" t="s">
+      <c r="A463" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B463" s="3">
+      <c r="B463" s="5">
         <v>171000000</v>
       </c>
-      <c r="C463" s="3">
+      <c r="C463" s="5">
         <v>128250000</v>
       </c>
-      <c r="D463" s="3">
-        <v>0</v>
-      </c>
-      <c r="E463" s="3">
+      <c r="D463" s="5">
+        <v>0</v>
+      </c>
+      <c r="E463" s="5">
         <v>20876000</v>
       </c>
-      <c r="F463" s="3">
+      <c r="F463" s="5">
         <v>20876000</v>
       </c>
-      <c r="G463" s="3">
+      <c r="G463" s="5">
         <v>107374000</v>
       </c>
-      <c r="H463" s="3">
+      <c r="H463" s="5">
         <v>42750000</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A464" s="2" t="s">
+      <c r="A464" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B464" s="3">
+      <c r="B464" s="5">
         <v>130000000</v>
       </c>
-      <c r="C464" s="3">
+      <c r="C464" s="5">
         <v>97500000</v>
       </c>
-      <c r="D464" s="3">
-        <v>0</v>
-      </c>
-      <c r="E464" s="3">
+      <c r="D464" s="5">
+        <v>0</v>
+      </c>
+      <c r="E464" s="5">
         <v>51225250</v>
       </c>
-      <c r="F464" s="3">
+      <c r="F464" s="5">
         <v>51225250</v>
       </c>
-      <c r="G464" s="3">
+      <c r="G464" s="5">
         <v>46274750</v>
       </c>
-      <c r="H464" s="3">
+      <c r="H464" s="5">
         <v>32500000</v>
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A465" s="2" t="s">
+      <c r="A465" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B465" s="3">
+      <c r="B465" s="5">
         <v>6660000</v>
       </c>
-      <c r="C465" s="3">
+      <c r="C465" s="5">
         <v>6660000</v>
       </c>
-      <c r="D465" s="3">
+      <c r="D465" s="5">
         <v>2581644</v>
       </c>
-      <c r="E465" s="3">
+      <c r="E465" s="5">
         <v>1665000</v>
       </c>
-      <c r="F465" s="3">
+      <c r="F465" s="5">
         <v>4246644</v>
       </c>
-      <c r="G465" s="3">
+      <c r="G465" s="5">
         <v>2413356</v>
       </c>
-      <c r="H465" s="3">
+      <c r="H465" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A466" s="2" t="s">
+      <c r="A466" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B466" s="3">
+      <c r="B466" s="5">
         <v>6000000</v>
       </c>
-      <c r="C466" s="3">
+      <c r="C466" s="5">
         <v>6000000</v>
       </c>
-      <c r="D466" s="3">
+      <c r="D466" s="5">
         <v>5982000</v>
       </c>
-      <c r="E466" s="3"/>
-      <c r="F466" s="3">
+      <c r="E466" s="5"/>
+      <c r="F466" s="5">
         <v>5982000</v>
       </c>
-      <c r="G466" s="3">
+      <c r="G466" s="5">
         <v>18000</v>
       </c>
-      <c r="H466" s="3">
+      <c r="H466" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A467" s="2" t="s">
+      <c r="A467" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B467" s="3"/>
-      <c r="C467" s="3"/>
-      <c r="D467" s="3"/>
-      <c r="E467" s="3"/>
-      <c r="F467" s="3"/>
-      <c r="G467" s="3"/>
-      <c r="H467" s="3"/>
+      <c r="B467" s="5"/>
+      <c r="C467" s="5"/>
+      <c r="D467" s="5"/>
+      <c r="E467" s="5"/>
+      <c r="F467" s="5"/>
+      <c r="G467" s="5"/>
+      <c r="H467" s="5"/>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A468" s="2" t="s">
+      <c r="A468" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B468" s="3"/>
-      <c r="C468" s="3"/>
-      <c r="D468" s="3"/>
-      <c r="E468" s="3"/>
-      <c r="F468" s="3"/>
-      <c r="G468" s="3"/>
-      <c r="H468" s="3"/>
+      <c r="B468" s="5"/>
+      <c r="C468" s="5"/>
+      <c r="D468" s="5"/>
+      <c r="E468" s="5"/>
+      <c r="F468" s="5"/>
+      <c r="G468" s="5"/>
+      <c r="H468" s="5"/>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A469" s="2" t="s">
+      <c r="A469" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B469" s="3"/>
-      <c r="C469" s="3"/>
-      <c r="D469" s="3"/>
-      <c r="E469" s="3"/>
-      <c r="F469" s="3"/>
-      <c r="G469" s="3"/>
-      <c r="H469" s="3"/>
+      <c r="B469" s="5"/>
+      <c r="C469" s="5"/>
+      <c r="D469" s="5"/>
+      <c r="E469" s="5"/>
+      <c r="F469" s="5"/>
+      <c r="G469" s="5"/>
+      <c r="H469" s="5"/>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A470" s="2" t="s">
+      <c r="A470" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B470" s="3"/>
-      <c r="C470" s="3"/>
-      <c r="D470" s="3"/>
-      <c r="E470" s="3"/>
-      <c r="F470" s="3"/>
-      <c r="G470" s="3"/>
-      <c r="H470" s="3"/>
+      <c r="B470" s="5"/>
+      <c r="C470" s="5"/>
+      <c r="D470" s="5"/>
+      <c r="E470" s="5"/>
+      <c r="F470" s="5"/>
+      <c r="G470" s="5"/>
+      <c r="H470" s="5"/>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A471" s="2" t="s">
+      <c r="A471" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B471" s="3"/>
-      <c r="C471" s="3"/>
-      <c r="D471" s="3"/>
-      <c r="E471" s="3"/>
-      <c r="F471" s="3"/>
-      <c r="G471" s="3"/>
-      <c r="H471" s="3"/>
+      <c r="B471" s="5"/>
+      <c r="C471" s="5"/>
+      <c r="D471" s="5"/>
+      <c r="E471" s="5"/>
+      <c r="F471" s="5"/>
+      <c r="G471" s="5"/>
+      <c r="H471" s="5"/>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A472" s="2" t="s">
+      <c r="A472" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B472" s="3"/>
-      <c r="C472" s="3"/>
-      <c r="D472" s="3"/>
-      <c r="E472" s="3"/>
-      <c r="F472" s="3"/>
-      <c r="G472" s="3"/>
-      <c r="H472" s="3"/>
+      <c r="B472" s="5"/>
+      <c r="C472" s="5"/>
+      <c r="D472" s="5"/>
+      <c r="E472" s="5"/>
+      <c r="F472" s="5"/>
+      <c r="G472" s="5"/>
+      <c r="H472" s="5"/>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A473" s="2" t="s">
+      <c r="A473" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B473" s="3"/>
-      <c r="C473" s="3"/>
-      <c r="D473" s="3"/>
-      <c r="E473" s="3"/>
-      <c r="F473" s="3"/>
-      <c r="G473" s="3"/>
-      <c r="H473" s="3"/>
+      <c r="B473" s="5"/>
+      <c r="C473" s="5"/>
+      <c r="D473" s="5"/>
+      <c r="E473" s="5"/>
+      <c r="F473" s="5"/>
+      <c r="G473" s="5"/>
+      <c r="H473" s="5"/>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A474" s="2" t="s">
+      <c r="A474" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B474" s="3"/>
-      <c r="C474" s="3"/>
-      <c r="D474" s="3"/>
-      <c r="E474" s="3"/>
-      <c r="F474" s="3"/>
-      <c r="G474" s="3"/>
-      <c r="H474" s="3"/>
+      <c r="B474" s="5"/>
+      <c r="C474" s="5"/>
+      <c r="D474" s="5"/>
+      <c r="E474" s="5"/>
+      <c r="F474" s="5"/>
+      <c r="G474" s="5"/>
+      <c r="H474" s="5"/>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A475" s="2" t="s">
+      <c r="A475" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B475" s="3"/>
-      <c r="C475" s="3"/>
-      <c r="D475" s="3"/>
-      <c r="E475" s="3"/>
-      <c r="F475" s="3"/>
-      <c r="G475" s="3"/>
-      <c r="H475" s="3"/>
+      <c r="B475" s="5"/>
+      <c r="C475" s="5"/>
+      <c r="D475" s="5"/>
+      <c r="E475" s="5"/>
+      <c r="F475" s="5"/>
+      <c r="G475" s="5"/>
+      <c r="H475" s="5"/>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A476" s="2" t="s">
+      <c r="A476" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B476" s="3"/>
-      <c r="C476" s="3"/>
-      <c r="D476" s="3"/>
-      <c r="E476" s="3"/>
-      <c r="F476" s="3"/>
-      <c r="G476" s="3"/>
-      <c r="H476" s="3"/>
+      <c r="B476" s="5"/>
+      <c r="C476" s="5"/>
+      <c r="D476" s="5"/>
+      <c r="E476" s="5"/>
+      <c r="F476" s="5"/>
+      <c r="G476" s="5"/>
+      <c r="H476" s="5"/>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A477" s="2" t="s">
+      <c r="A477" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B477" s="3"/>
-      <c r="C477" s="3"/>
-      <c r="D477" s="3"/>
-      <c r="E477" s="3"/>
-      <c r="F477" s="3"/>
-      <c r="G477" s="3"/>
-      <c r="H477" s="3"/>
+      <c r="B477" s="5"/>
+      <c r="C477" s="5"/>
+      <c r="D477" s="5"/>
+      <c r="E477" s="5"/>
+      <c r="F477" s="5"/>
+      <c r="G477" s="5"/>
+      <c r="H477" s="5"/>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A478" s="2" t="s">
+      <c r="A478" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B478" s="3"/>
-      <c r="C478" s="3"/>
-      <c r="D478" s="3"/>
-      <c r="E478" s="3"/>
-      <c r="F478" s="3"/>
-      <c r="G478" s="3"/>
-      <c r="H478" s="3"/>
+      <c r="B478" s="5"/>
+      <c r="C478" s="5"/>
+      <c r="D478" s="5"/>
+      <c r="E478" s="5"/>
+      <c r="F478" s="5"/>
+      <c r="G478" s="5"/>
+      <c r="H478" s="5"/>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A479" s="2" t="s">
+      <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B479" s="3"/>
-      <c r="C479" s="3"/>
-      <c r="D479" s="3"/>
-      <c r="E479" s="3"/>
-      <c r="F479" s="3"/>
-      <c r="G479" s="3"/>
-      <c r="H479" s="3"/>
+      <c r="B479" s="5"/>
+      <c r="C479" s="5"/>
+      <c r="D479" s="5"/>
+      <c r="E479" s="5"/>
+      <c r="F479" s="5"/>
+      <c r="G479" s="5"/>
+      <c r="H479" s="5"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A480" s="2" t="s">
+      <c r="A480" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B480" s="3">
+      <c r="B480" s="5">
         <f>SUM(B425:B479)</f>
         <v>2349760730</v>
       </c>
-      <c r="C480" s="3">
+      <c r="C480" s="5">
         <f t="shared" ref="C480:H480" si="0">SUM(C425:C479)</f>
         <v>2238760730</v>
       </c>
-      <c r="D480" s="3">
+      <c r="D480" s="5">
         <f t="shared" si="0"/>
         <v>861026544</v>
       </c>
-      <c r="E480" s="3">
+      <c r="E480" s="5">
         <f t="shared" si="0"/>
         <v>310950580</v>
       </c>
-      <c r="F480" s="3">
+      <c r="F480" s="5">
         <f t="shared" si="0"/>
         <v>1171977124</v>
       </c>
-      <c r="G480" s="3">
+      <c r="G480" s="5">
         <f t="shared" si="0"/>
         <v>1066783606</v>
       </c>
-      <c r="H480" s="3">
+      <c r="H480" s="5">
         <f t="shared" si="0"/>
         <v>111000000</v>
       </c>
@@ -13394,10 +13409,10 @@
         <v>4989900000</v>
       </c>
       <c r="D489" s="1">
-        <v>849125017</v>
+        <v>840425017</v>
       </c>
       <c r="E489" s="1">
-        <v>1012438612</v>
+        <v>1021138612</v>
       </c>
       <c r="F489" s="1">
         <v>1861563629</v>
@@ -13732,10 +13747,10 @@
         <v>1016150000</v>
       </c>
       <c r="D502" s="1">
-        <v>150990000</v>
+        <v>39900000</v>
       </c>
       <c r="E502" s="1">
-        <v>216310000</v>
+        <v>327400000</v>
       </c>
       <c r="F502" s="1">
         <v>367300000</v>
@@ -13784,10 +13799,10 @@
         <v>668379750</v>
       </c>
       <c r="D504" s="1">
-        <v>64146000</v>
+        <v>52961000</v>
       </c>
       <c r="E504" s="1">
-        <v>92904828</v>
+        <v>104089828</v>
       </c>
       <c r="F504" s="1">
         <v>157050828</v>
@@ -13810,16 +13825,16 @@
         <v>870341250</v>
       </c>
       <c r="D505" s="1">
-        <v>181866862</v>
+        <v>92046380</v>
       </c>
       <c r="E505" s="1">
-        <v>375475810</v>
+        <v>465198890</v>
       </c>
       <c r="F505" s="1">
-        <v>557342672</v>
+        <v>557245270</v>
       </c>
       <c r="G505" s="1">
-        <v>312998578</v>
+        <v>313095980</v>
       </c>
       <c r="H505" s="1">
         <v>290113750</v>
@@ -14304,16 +14319,16 @@
         <v>64019485320</v>
       </c>
       <c r="D524" s="1">
-        <v>10015223526</v>
+        <v>9794428044</v>
       </c>
       <c r="E524" s="1">
-        <v>26703139797</v>
+        <v>26923837877</v>
       </c>
       <c r="F524" s="1">
-        <v>36718363323</v>
+        <v>36718265921</v>
       </c>
       <c r="G524" s="1">
-        <v>27301121997</v>
+        <v>27301219399</v>
       </c>
       <c r="H524" s="1">
         <v>850782250</v>
@@ -14408,16 +14423,16 @@
         <v>2639000000</v>
       </c>
       <c r="D528" s="1">
-        <v>1875260744</v>
+        <v>1906839377</v>
       </c>
       <c r="E528" s="1">
         <v>281140148</v>
       </c>
       <c r="F528" s="1">
-        <v>2156400892</v>
+        <v>2187979525</v>
       </c>
       <c r="G528" s="1">
-        <v>482599108</v>
+        <v>451020475</v>
       </c>
       <c r="H528" s="1">
         <v>0</v>
@@ -14486,16 +14501,16 @@
         <v>9794675000</v>
       </c>
       <c r="D531" s="1">
-        <v>8981514669</v>
+        <v>8988260287</v>
       </c>
       <c r="E531" s="1">
         <v>3607897</v>
       </c>
       <c r="F531" s="1">
-        <v>8985122566</v>
+        <v>8991868184</v>
       </c>
       <c r="G531" s="1">
-        <v>809552434</v>
+        <v>802806816</v>
       </c>
       <c r="H531" s="1">
         <v>0</v>
@@ -14538,16 +14553,16 @@
         <v>1450000000</v>
       </c>
       <c r="D533" s="1">
-        <v>257512645</v>
+        <v>357049495</v>
       </c>
       <c r="E533" s="1">
         <v>199177827</v>
       </c>
       <c r="F533" s="1">
-        <v>456690472</v>
+        <v>556227322</v>
       </c>
       <c r="G533" s="1">
-        <v>993309528</v>
+        <v>893772678</v>
       </c>
       <c r="H533" s="1">
         <v>0</v>
@@ -14694,16 +14709,16 @@
         <v>285978663</v>
       </c>
       <c r="D539" s="1">
-        <v>58526100</v>
+        <v>79854750</v>
       </c>
       <c r="E539" s="1">
         <v>119175600</v>
       </c>
       <c r="F539" s="1">
-        <v>177701700</v>
+        <v>199030350</v>
       </c>
       <c r="G539" s="1">
-        <v>108276963</v>
+        <v>86948313</v>
       </c>
       <c r="H539" s="1">
         <v>0</v>
@@ -14720,16 +14735,16 @@
         <v>1539315000</v>
       </c>
       <c r="D540" s="1">
-        <v>3368850</v>
+        <v>6368850</v>
       </c>
       <c r="E540" s="1">
         <v>691756980</v>
       </c>
       <c r="F540" s="1">
-        <v>695125830</v>
+        <v>698125830</v>
       </c>
       <c r="G540" s="1">
-        <v>844189170</v>
+        <v>841189170</v>
       </c>
       <c r="H540" s="1">
         <v>0</v>
@@ -14746,16 +14761,16 @@
         <v>412500000</v>
       </c>
       <c r="D541" s="1">
-        <v>35830775</v>
+        <v>41887175</v>
       </c>
       <c r="E541" s="1">
         <v>46642000</v>
       </c>
       <c r="F541" s="1">
-        <v>82472775</v>
+        <v>88529175</v>
       </c>
       <c r="G541" s="1">
-        <v>330027225</v>
+        <v>323970825</v>
       </c>
       <c r="H541" s="1">
         <v>137500000</v>
@@ -14772,16 +14787,16 @@
         <v>532875000</v>
       </c>
       <c r="D542" s="1">
-        <v>39103970</v>
+        <v>65512965</v>
       </c>
       <c r="E542" s="1">
         <v>102100789</v>
       </c>
       <c r="F542" s="1">
-        <v>141204759</v>
+        <v>167613754</v>
       </c>
       <c r="G542" s="1">
-        <v>391670241</v>
+        <v>365261246</v>
       </c>
       <c r="H542" s="1">
         <v>177625000</v>
@@ -14824,16 +14839,16 @@
         <v>395748750</v>
       </c>
       <c r="D544" s="1">
-        <v>248317351</v>
+        <v>329133247</v>
       </c>
       <c r="E544" s="1">
         <v>28459950</v>
       </c>
       <c r="F544" s="1">
-        <v>276777301</v>
+        <v>357593197</v>
       </c>
       <c r="G544" s="1">
-        <v>118971449</v>
+        <v>38155553</v>
       </c>
       <c r="H544" s="1">
         <v>131916250</v>
@@ -14850,10 +14865,10 @@
         <v>336802500</v>
       </c>
       <c r="D545" s="1">
-        <v>19159601</v>
+        <v>17175101</v>
       </c>
       <c r="E545" s="1">
-        <v>153517500</v>
+        <v>155502000</v>
       </c>
       <c r="F545" s="1">
         <v>172677101</v>
@@ -15136,16 +15151,16 @@
         <v>57848682223</v>
       </c>
       <c r="D556" s="1">
-        <v>22585137847</v>
+        <v>22858624389</v>
       </c>
       <c r="E556" s="1">
-        <v>17566392609</v>
+        <v>17568377109</v>
       </c>
       <c r="F556" s="1">
-        <v>40151530456</v>
+        <v>40427001498</v>
       </c>
       <c r="G556" s="1">
-        <v>17697151767</v>
+        <v>17421680725</v>
       </c>
       <c r="H556" s="1">
         <v>720558750</v>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,15 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\7. Jul\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90D6A75B-57B0-4114-A51C-2B73CD330785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B49D59-E505-4D1B-ACAA-C4BEDE9FFC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget 3 Juni 2024" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -420,7 +429,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -557,7 +566,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -737,6 +746,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -898,9 +913,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1257,7 +1276,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H561"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -12396,1459 +12415,890 @@
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A429" t="s">
+      <c r="A429" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B429" s="1">
-        <v>3181468670</v>
-      </c>
-      <c r="C429" s="1">
-        <v>3181468670</v>
-      </c>
-      <c r="D429" s="1">
-        <v>2150610250</v>
-      </c>
-      <c r="E429" s="1">
-        <v>892980052</v>
-      </c>
-      <c r="F429" s="1">
-        <v>3043590302</v>
-      </c>
-      <c r="G429" s="1">
-        <v>137878368</v>
-      </c>
-      <c r="H429" s="1">
+      <c r="B429" s="3">
+        <v>873740000</v>
+      </c>
+      <c r="C429" s="3">
+        <v>873740000</v>
+      </c>
+      <c r="D429" s="3">
+        <v>630188000</v>
+      </c>
+      <c r="E429" s="3">
+        <v>129620052</v>
+      </c>
+      <c r="F429" s="3">
+        <v>759808052</v>
+      </c>
+      <c r="G429" s="3">
+        <v>113931948</v>
+      </c>
+      <c r="H429" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A430" t="s">
+      <c r="A430" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B430" s="1">
-        <v>0</v>
-      </c>
-      <c r="C430" s="1">
-        <v>0</v>
-      </c>
-      <c r="D430" s="1">
-        <v>0</v>
-      </c>
-      <c r="E430" s="1">
-        <v>-5912124</v>
-      </c>
-      <c r="F430" s="1">
-        <v>-5912124</v>
-      </c>
-      <c r="G430" s="1">
-        <v>5912124</v>
-      </c>
-      <c r="H430" s="1">
-        <v>0</v>
-      </c>
+      <c r="B430" s="3"/>
+      <c r="C430" s="3"/>
+      <c r="D430" s="3"/>
+      <c r="E430" s="3"/>
+      <c r="F430" s="3"/>
+      <c r="G430" s="3"/>
+      <c r="H430" s="3"/>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A431" t="s">
+      <c r="A431" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B431" s="1">
-        <v>649744265</v>
-      </c>
-      <c r="C431" s="1">
-        <v>649744265</v>
-      </c>
-      <c r="D431" s="1">
-        <v>231703040</v>
-      </c>
-      <c r="E431" s="1">
-        <v>0</v>
-      </c>
-      <c r="F431" s="1">
-        <v>231703040</v>
-      </c>
-      <c r="G431" s="1">
-        <v>418041225</v>
-      </c>
-      <c r="H431" s="1">
-        <v>0</v>
-      </c>
+      <c r="B431" s="3"/>
+      <c r="C431" s="3"/>
+      <c r="D431" s="3"/>
+      <c r="E431" s="3"/>
+      <c r="F431" s="3"/>
+      <c r="G431" s="3"/>
+      <c r="H431" s="3"/>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A432" t="s">
+      <c r="A432" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B432" s="1">
-        <v>478795476</v>
-      </c>
-      <c r="C432" s="1">
-        <v>478795476</v>
-      </c>
-      <c r="D432" s="1">
-        <v>0</v>
-      </c>
-      <c r="E432" s="1">
-        <v>0</v>
-      </c>
-      <c r="F432" s="1">
-        <v>0</v>
-      </c>
-      <c r="G432" s="1">
-        <v>478795476</v>
-      </c>
-      <c r="H432" s="1">
-        <v>0</v>
-      </c>
+      <c r="B432" s="3"/>
+      <c r="C432" s="3"/>
+      <c r="D432" s="3"/>
+      <c r="E432" s="3"/>
+      <c r="F432" s="3"/>
+      <c r="G432" s="3"/>
+      <c r="H432" s="3"/>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A433" t="s">
+      <c r="A433" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B433" s="1">
-        <v>209603780</v>
-      </c>
-      <c r="C433" s="1">
-        <v>209603780</v>
-      </c>
-      <c r="D433" s="1">
-        <v>114400000</v>
-      </c>
-      <c r="E433" s="1">
-        <v>0</v>
-      </c>
-      <c r="F433" s="1">
-        <v>114400000</v>
-      </c>
-      <c r="G433" s="1">
-        <v>95203780</v>
-      </c>
-      <c r="H433" s="1">
-        <v>0</v>
-      </c>
+      <c r="B433" s="3"/>
+      <c r="C433" s="3"/>
+      <c r="D433" s="3"/>
+      <c r="E433" s="3"/>
+      <c r="F433" s="3"/>
+      <c r="G433" s="3"/>
+      <c r="H433" s="3"/>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A434" t="s">
+      <c r="A434" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B434" s="1">
-        <v>421647439</v>
-      </c>
-      <c r="C434" s="1">
-        <v>421647439</v>
-      </c>
-      <c r="D434" s="1">
-        <v>0</v>
-      </c>
-      <c r="E434" s="1">
-        <v>0</v>
-      </c>
-      <c r="F434" s="1">
-        <v>0</v>
-      </c>
-      <c r="G434" s="1">
-        <v>421647439</v>
-      </c>
-      <c r="H434" s="1">
-        <v>0</v>
-      </c>
+      <c r="B434" s="3"/>
+      <c r="C434" s="3"/>
+      <c r="D434" s="3"/>
+      <c r="E434" s="3"/>
+      <c r="F434" s="3"/>
+      <c r="G434" s="3"/>
+      <c r="H434" s="3"/>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A435" t="s">
+      <c r="A435" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B435" s="1">
-        <v>444444687</v>
-      </c>
-      <c r="C435" s="1">
-        <v>444444687</v>
-      </c>
-      <c r="D435" s="1">
-        <v>444284724</v>
-      </c>
-      <c r="E435" s="1">
-        <v>0</v>
-      </c>
-      <c r="F435" s="1">
-        <v>444284724</v>
-      </c>
-      <c r="G435" s="1">
-        <v>159963</v>
-      </c>
-      <c r="H435" s="1">
-        <v>0</v>
-      </c>
+      <c r="B435" s="3"/>
+      <c r="C435" s="3"/>
+      <c r="D435" s="3"/>
+      <c r="E435" s="3"/>
+      <c r="F435" s="3"/>
+      <c r="G435" s="3"/>
+      <c r="H435" s="3"/>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A436" t="s">
+      <c r="A436" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B436" s="1">
-        <v>510000000</v>
-      </c>
-      <c r="C436" s="1">
-        <v>510000000</v>
-      </c>
-      <c r="D436" s="1">
-        <v>79112150</v>
-      </c>
-      <c r="E436" s="1">
-        <v>223377100</v>
-      </c>
-      <c r="F436" s="1">
-        <v>302489250</v>
-      </c>
-      <c r="G436" s="1">
-        <v>207510750</v>
-      </c>
-      <c r="H436" s="1">
-        <v>0</v>
-      </c>
+      <c r="B436" s="3"/>
+      <c r="C436" s="3"/>
+      <c r="D436" s="3"/>
+      <c r="E436" s="3"/>
+      <c r="F436" s="3"/>
+      <c r="G436" s="3"/>
+      <c r="H436" s="3"/>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A437" t="s">
+      <c r="A437" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B437" s="1">
-        <v>346777836</v>
-      </c>
-      <c r="C437" s="1">
-        <v>346777836</v>
-      </c>
-      <c r="D437" s="1">
-        <v>346671023</v>
-      </c>
-      <c r="E437" s="1">
-        <v>0</v>
-      </c>
-      <c r="F437" s="1">
-        <v>346671023</v>
-      </c>
-      <c r="G437" s="1">
-        <v>106813</v>
-      </c>
-      <c r="H437" s="1">
-        <v>0</v>
-      </c>
+      <c r="B437" s="3"/>
+      <c r="C437" s="3"/>
+      <c r="D437" s="3"/>
+      <c r="E437" s="3"/>
+      <c r="F437" s="3"/>
+      <c r="G437" s="3"/>
+      <c r="H437" s="3"/>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A438" t="s">
+      <c r="A438" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B438" s="1">
-        <v>774442214</v>
-      </c>
-      <c r="C438" s="1">
-        <v>774442214</v>
-      </c>
-      <c r="D438" s="1">
-        <v>30334100</v>
-      </c>
-      <c r="E438" s="1">
-        <v>141062150</v>
-      </c>
-      <c r="F438" s="1">
-        <v>171396250</v>
-      </c>
-      <c r="G438" s="1">
-        <v>603045964</v>
-      </c>
-      <c r="H438" s="1">
-        <v>0</v>
-      </c>
+      <c r="B438" s="3"/>
+      <c r="C438" s="3"/>
+      <c r="D438" s="3"/>
+      <c r="E438" s="3"/>
+      <c r="F438" s="3"/>
+      <c r="G438" s="3"/>
+      <c r="H438" s="3"/>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A439" t="s">
+      <c r="A439" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B439" s="1">
-        <v>1701858579</v>
-      </c>
-      <c r="C439" s="1">
-        <v>1701858579</v>
-      </c>
-      <c r="D439" s="1">
-        <v>778616054</v>
-      </c>
-      <c r="E439" s="1">
-        <v>923242525</v>
-      </c>
-      <c r="F439" s="1">
-        <v>1701858579</v>
-      </c>
-      <c r="G439" s="1">
-        <v>0</v>
-      </c>
-      <c r="H439" s="1">
-        <v>0</v>
-      </c>
+      <c r="B439" s="3"/>
+      <c r="C439" s="3"/>
+      <c r="D439" s="3"/>
+      <c r="E439" s="3"/>
+      <c r="F439" s="3"/>
+      <c r="G439" s="3"/>
+      <c r="H439" s="3"/>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A440" t="s">
+      <c r="A440" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B440" s="1">
-        <v>28251276</v>
-      </c>
-      <c r="C440" s="1">
-        <v>28251276</v>
-      </c>
-      <c r="D440" s="1">
-        <v>0</v>
-      </c>
-      <c r="E440" s="1">
-        <v>12825800</v>
-      </c>
-      <c r="F440" s="1">
-        <v>12825800</v>
-      </c>
-      <c r="G440" s="1">
-        <v>15425476</v>
-      </c>
-      <c r="H440" s="1">
-        <v>0</v>
-      </c>
+      <c r="B440" s="3"/>
+      <c r="C440" s="3"/>
+      <c r="D440" s="3"/>
+      <c r="E440" s="3"/>
+      <c r="F440" s="3"/>
+      <c r="G440" s="3"/>
+      <c r="H440" s="3"/>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A441" t="s">
+      <c r="A441" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B441" s="1">
-        <v>807000067</v>
-      </c>
-      <c r="C441" s="1">
-        <v>807000067</v>
-      </c>
-      <c r="D441" s="1">
-        <v>513294063</v>
-      </c>
-      <c r="E441" s="1">
-        <v>152058600</v>
-      </c>
-      <c r="F441" s="1">
-        <v>665352663</v>
-      </c>
-      <c r="G441" s="1">
-        <v>141647404</v>
-      </c>
-      <c r="H441" s="1">
-        <v>0</v>
-      </c>
+      <c r="B441" s="3"/>
+      <c r="C441" s="3"/>
+      <c r="D441" s="3"/>
+      <c r="E441" s="3"/>
+      <c r="F441" s="3"/>
+      <c r="G441" s="3"/>
+      <c r="H441" s="3"/>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A442" t="s">
+      <c r="A442" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B442" s="1">
-        <v>295744751</v>
-      </c>
-      <c r="C442" s="1">
-        <v>295744751</v>
-      </c>
-      <c r="D442" s="1">
-        <v>0</v>
-      </c>
-      <c r="E442" s="1">
-        <v>0</v>
-      </c>
-      <c r="F442" s="1">
-        <v>0</v>
-      </c>
-      <c r="G442" s="1">
-        <v>295744751</v>
-      </c>
-      <c r="H442" s="1">
-        <v>0</v>
-      </c>
+      <c r="B442" s="3"/>
+      <c r="C442" s="3"/>
+      <c r="D442" s="3"/>
+      <c r="E442" s="3"/>
+      <c r="F442" s="3"/>
+      <c r="G442" s="3"/>
+      <c r="H442" s="3"/>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A443" t="s">
+      <c r="A443" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B443" s="1">
-        <v>171667707</v>
-      </c>
-      <c r="C443" s="1">
-        <v>171667707</v>
-      </c>
-      <c r="D443" s="1">
-        <v>0</v>
-      </c>
-      <c r="E443" s="1">
-        <v>0</v>
-      </c>
-      <c r="F443" s="1">
-        <v>0</v>
-      </c>
-      <c r="G443" s="1">
-        <v>171667707</v>
-      </c>
-      <c r="H443" s="1">
-        <v>0</v>
-      </c>
+      <c r="B443" s="3"/>
+      <c r="C443" s="3"/>
+      <c r="D443" s="3"/>
+      <c r="E443" s="3"/>
+      <c r="F443" s="3"/>
+      <c r="G443" s="3"/>
+      <c r="H443" s="3"/>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A444" t="s">
+      <c r="A444" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B444" s="1">
-        <v>334991880</v>
-      </c>
-      <c r="C444" s="1">
-        <v>334991880</v>
-      </c>
-      <c r="D444" s="1">
-        <v>334851906</v>
-      </c>
-      <c r="E444" s="1">
-        <v>0</v>
-      </c>
-      <c r="F444" s="1">
-        <v>334851906</v>
-      </c>
-      <c r="G444" s="1">
-        <v>139974</v>
-      </c>
-      <c r="H444" s="1">
-        <v>0</v>
-      </c>
+      <c r="B444" s="3"/>
+      <c r="C444" s="3"/>
+      <c r="D444" s="3"/>
+      <c r="E444" s="3"/>
+      <c r="F444" s="3"/>
+      <c r="G444" s="3"/>
+      <c r="H444" s="3"/>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A445" t="s">
+      <c r="A445" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B445" s="1">
-        <v>591179333</v>
-      </c>
-      <c r="C445" s="1">
-        <v>591179333</v>
-      </c>
-      <c r="D445" s="1">
-        <v>361300878</v>
-      </c>
-      <c r="E445" s="1">
-        <v>197740774</v>
-      </c>
-      <c r="F445" s="1">
-        <v>559041652</v>
-      </c>
-      <c r="G445" s="1">
-        <v>32137681</v>
-      </c>
-      <c r="H445" s="1">
-        <v>0</v>
-      </c>
+      <c r="B445" s="3"/>
+      <c r="C445" s="3"/>
+      <c r="D445" s="3"/>
+      <c r="E445" s="3"/>
+      <c r="F445" s="3"/>
+      <c r="G445" s="3"/>
+      <c r="H445" s="3"/>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A446" t="s">
+      <c r="A446" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B446" s="1">
+      <c r="B446" s="3">
         <v>474786000</v>
       </c>
-      <c r="C446" s="1">
+      <c r="C446" s="3">
         <v>474786000</v>
       </c>
-      <c r="D446" s="1">
+      <c r="D446" s="3">
         <v>474154600</v>
       </c>
-      <c r="E446" s="1">
-        <v>0</v>
-      </c>
-      <c r="F446" s="1">
+      <c r="E446" s="3"/>
+      <c r="F446" s="3">
         <v>474154600</v>
       </c>
-      <c r="G446" s="1">
+      <c r="G446" s="3">
         <v>631400</v>
       </c>
-      <c r="H446" s="1">
+      <c r="H446" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A447" t="s">
+      <c r="A447" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B447" s="1">
+      <c r="B447" s="3">
         <v>208424730</v>
       </c>
-      <c r="C447" s="1">
+      <c r="C447" s="3">
         <v>208424730</v>
       </c>
-      <c r="D447" s="1">
+      <c r="D447" s="3">
         <v>180590600</v>
       </c>
-      <c r="E447" s="1">
-        <v>0</v>
-      </c>
-      <c r="F447" s="1">
+      <c r="E447" s="3"/>
+      <c r="F447" s="3">
         <v>180590600</v>
       </c>
-      <c r="G447" s="1">
+      <c r="G447" s="3">
         <v>27834130</v>
       </c>
-      <c r="H447" s="1">
+      <c r="H447" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A448" t="s">
+      <c r="A448" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B448" s="1">
+      <c r="B448" s="3">
         <v>20000000</v>
       </c>
-      <c r="C448" s="1">
+      <c r="C448" s="3">
         <v>20000000</v>
       </c>
-      <c r="D448" s="1">
-        <v>0</v>
-      </c>
-      <c r="E448" s="1">
+      <c r="D448" s="3">
+        <v>0</v>
+      </c>
+      <c r="E448" s="3">
         <v>13970000</v>
       </c>
-      <c r="F448" s="1">
+      <c r="F448" s="3">
         <v>13970000</v>
       </c>
-      <c r="G448" s="1">
+      <c r="G448" s="3">
         <v>6030000</v>
       </c>
-      <c r="H448" s="1">
+      <c r="H448" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A449" t="s">
+      <c r="A449" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B449" s="1">
+      <c r="B449" s="3">
         <v>220000000</v>
       </c>
-      <c r="C449" s="1">
+      <c r="C449" s="3">
         <v>220000000</v>
       </c>
-      <c r="D449" s="1">
+      <c r="D449" s="3">
         <v>78580000</v>
       </c>
-      <c r="E449" s="1">
+      <c r="E449" s="3">
         <v>59808678</v>
       </c>
-      <c r="F449" s="1">
+      <c r="F449" s="3">
         <v>138388678</v>
       </c>
-      <c r="G449" s="1">
+      <c r="G449" s="3">
         <v>81611322</v>
       </c>
-      <c r="H449" s="1">
+      <c r="H449" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A450" t="s">
+      <c r="A450" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B450" s="1">
+      <c r="B450" s="3">
         <v>75000000</v>
       </c>
-      <c r="C450" s="1">
+      <c r="C450" s="3">
         <v>75000000</v>
       </c>
-      <c r="D450" s="1">
+      <c r="D450" s="3">
         <v>38500000</v>
       </c>
-      <c r="E450" s="1">
-        <v>0</v>
-      </c>
-      <c r="F450" s="1">
+      <c r="E450" s="3"/>
+      <c r="F450" s="3">
         <v>38500000</v>
       </c>
-      <c r="G450" s="1">
+      <c r="G450" s="3">
         <v>36500000</v>
       </c>
-      <c r="H450" s="1">
+      <c r="H450" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A451" t="s">
+      <c r="A451" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B451" s="1">
-        <v>1233358275</v>
-      </c>
-      <c r="C451" s="1">
-        <v>925018706</v>
-      </c>
-      <c r="D451" s="1">
-        <v>297635000</v>
-      </c>
-      <c r="E451" s="1">
-        <v>587746900</v>
-      </c>
-      <c r="F451" s="1">
-        <v>885381900</v>
-      </c>
-      <c r="G451" s="1">
-        <v>39636806</v>
-      </c>
-      <c r="H451" s="1">
-        <v>308339569</v>
-      </c>
+      <c r="B451" s="3"/>
+      <c r="C451" s="3"/>
+      <c r="D451" s="3"/>
+      <c r="E451" s="3"/>
+      <c r="F451" s="3"/>
+      <c r="G451" s="3"/>
+      <c r="H451" s="3"/>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A452" t="s">
+      <c r="A452" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B452" s="1">
-        <v>100000000</v>
-      </c>
-      <c r="C452" s="1">
-        <v>100000000</v>
-      </c>
-      <c r="D452" s="1">
-        <v>0</v>
-      </c>
-      <c r="E452" s="1">
-        <v>0</v>
-      </c>
-      <c r="F452" s="1">
-        <v>0</v>
-      </c>
-      <c r="G452" s="1">
-        <v>100000000</v>
-      </c>
-      <c r="H452" s="1">
-        <v>0</v>
-      </c>
+      <c r="B452" s="3"/>
+      <c r="C452" s="3"/>
+      <c r="D452" s="3"/>
+      <c r="E452" s="3"/>
+      <c r="F452" s="3"/>
+      <c r="G452" s="3"/>
+      <c r="H452" s="3"/>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A453" t="s">
+      <c r="A453" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B453" s="1">
+      <c r="B453" s="3">
         <v>60000000</v>
       </c>
-      <c r="C453" s="1">
+      <c r="C453" s="3">
         <v>45000000</v>
       </c>
-      <c r="D453" s="1">
-        <v>7388000</v>
-      </c>
-      <c r="E453" s="1">
-        <v>10120000</v>
-      </c>
-      <c r="F453" s="1">
+      <c r="D453" s="3">
+        <v>8508000</v>
+      </c>
+      <c r="E453" s="3">
+        <v>9000000</v>
+      </c>
+      <c r="F453" s="3">
         <v>17508000</v>
       </c>
-      <c r="G453" s="1">
+      <c r="G453" s="3">
         <v>27492000</v>
       </c>
-      <c r="H453" s="1">
+      <c r="H453" s="3">
         <v>15000000</v>
       </c>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A454" t="s">
+      <c r="A454" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B454" s="1">
-        <v>646607100</v>
-      </c>
-      <c r="C454" s="1">
-        <v>646607100</v>
-      </c>
-      <c r="D454" s="1">
-        <v>0</v>
-      </c>
-      <c r="E454" s="1">
-        <v>242044624</v>
-      </c>
-      <c r="F454" s="1">
-        <v>242044624</v>
-      </c>
-      <c r="G454" s="1">
-        <v>404562476</v>
-      </c>
-      <c r="H454" s="1">
+      <c r="B454" s="3">
+        <v>45150000</v>
+      </c>
+      <c r="C454" s="3">
+        <v>45150000</v>
+      </c>
+      <c r="D454" s="3">
+        <v>0</v>
+      </c>
+      <c r="E454" s="3">
+        <v>20796200</v>
+      </c>
+      <c r="F454" s="3">
+        <v>20796200</v>
+      </c>
+      <c r="G454" s="3">
+        <v>24353800</v>
+      </c>
+      <c r="H454" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A455" t="s">
+      <c r="A455" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B455" s="1">
-        <v>66000000</v>
-      </c>
-      <c r="C455" s="1">
-        <v>49500000</v>
-      </c>
-      <c r="D455" s="1">
-        <v>20108293</v>
-      </c>
-      <c r="E455" s="1">
-        <v>17329000</v>
-      </c>
-      <c r="F455" s="1">
-        <v>37437293</v>
-      </c>
-      <c r="G455" s="1">
-        <v>12062707</v>
-      </c>
-      <c r="H455" s="1">
-        <v>16500000</v>
-      </c>
+      <c r="B455" s="3"/>
+      <c r="C455" s="3"/>
+      <c r="D455" s="3"/>
+      <c r="E455" s="3"/>
+      <c r="F455" s="3"/>
+      <c r="G455" s="3"/>
+      <c r="H455" s="3"/>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A456" t="s">
+      <c r="A456" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B456" s="1">
-        <v>420141700</v>
-      </c>
-      <c r="C456" s="1">
-        <v>315106275</v>
-      </c>
-      <c r="D456" s="1">
-        <v>95527850</v>
-      </c>
-      <c r="E456" s="1">
-        <v>205273154</v>
-      </c>
-      <c r="F456" s="1">
-        <v>300801004</v>
-      </c>
-      <c r="G456" s="1">
-        <v>14305271</v>
-      </c>
-      <c r="H456" s="1">
-        <v>105035425</v>
-      </c>
+      <c r="B456" s="3"/>
+      <c r="C456" s="3"/>
+      <c r="D456" s="3"/>
+      <c r="E456" s="3"/>
+      <c r="F456" s="3"/>
+      <c r="G456" s="3"/>
+      <c r="H456" s="3"/>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A457" t="s">
+      <c r="A457" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B457" s="1">
-        <v>106000000</v>
-      </c>
-      <c r="C457" s="1">
-        <v>106000000</v>
-      </c>
-      <c r="D457" s="1">
-        <v>1707311</v>
-      </c>
-      <c r="E457" s="1">
-        <v>50018804</v>
-      </c>
-      <c r="F457" s="1">
-        <v>51726115</v>
-      </c>
-      <c r="G457" s="1">
-        <v>54273885</v>
-      </c>
-      <c r="H457" s="1">
-        <v>0</v>
-      </c>
+      <c r="B457" s="3"/>
+      <c r="C457" s="3"/>
+      <c r="D457" s="3"/>
+      <c r="E457" s="3"/>
+      <c r="F457" s="3"/>
+      <c r="G457" s="3"/>
+      <c r="H457" s="3"/>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A458" t="s">
+      <c r="A458" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B458" s="1">
-        <v>45000000</v>
-      </c>
-      <c r="C458" s="1">
-        <v>45000000</v>
-      </c>
-      <c r="D458" s="1">
-        <v>44997500</v>
-      </c>
-      <c r="E458" s="1">
-        <v>0</v>
-      </c>
-      <c r="F458" s="1">
-        <v>44997500</v>
-      </c>
-      <c r="G458" s="1">
-        <v>2500</v>
-      </c>
-      <c r="H458" s="1">
-        <v>0</v>
-      </c>
+      <c r="B458" s="3"/>
+      <c r="C458" s="3"/>
+      <c r="D458" s="3"/>
+      <c r="E458" s="3"/>
+      <c r="F458" s="3"/>
+      <c r="G458" s="3"/>
+      <c r="H458" s="3"/>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A459" t="s">
+      <c r="A459" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B459" s="1">
-        <v>127735796</v>
-      </c>
-      <c r="C459" s="1">
-        <v>122205221</v>
-      </c>
-      <c r="D459" s="1">
-        <v>60000000</v>
-      </c>
-      <c r="E459" s="1">
-        <v>0</v>
-      </c>
-      <c r="F459" s="1">
-        <v>60000000</v>
-      </c>
-      <c r="G459" s="1">
-        <v>62205221</v>
-      </c>
-      <c r="H459" s="1">
-        <v>5530575</v>
-      </c>
+      <c r="B459" s="3"/>
+      <c r="C459" s="3"/>
+      <c r="D459" s="3"/>
+      <c r="E459" s="3"/>
+      <c r="F459" s="3"/>
+      <c r="G459" s="3"/>
+      <c r="H459" s="3"/>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A460" t="s">
+      <c r="A460" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B460" s="1">
-        <v>48000000</v>
-      </c>
-      <c r="C460" s="1">
-        <v>48000000</v>
-      </c>
-      <c r="D460" s="1">
-        <v>0</v>
-      </c>
-      <c r="E460" s="1">
-        <v>26965795</v>
-      </c>
-      <c r="F460" s="1">
-        <v>26965795</v>
-      </c>
-      <c r="G460" s="1">
-        <v>21034205</v>
-      </c>
-      <c r="H460" s="1">
-        <v>0</v>
-      </c>
+      <c r="B460" s="3"/>
+      <c r="C460" s="3"/>
+      <c r="D460" s="3"/>
+      <c r="E460" s="3"/>
+      <c r="F460" s="3"/>
+      <c r="G460" s="3"/>
+      <c r="H460" s="3"/>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A461" t="s">
+      <c r="A461" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B461" s="1">
-        <v>99500000</v>
-      </c>
-      <c r="C461" s="1">
-        <v>74625000</v>
-      </c>
-      <c r="D461" s="1">
-        <v>51194126</v>
-      </c>
-      <c r="E461" s="1">
-        <v>8150000</v>
-      </c>
-      <c r="F461" s="1">
-        <v>59344126</v>
-      </c>
-      <c r="G461" s="1">
-        <v>15280874</v>
-      </c>
-      <c r="H461" s="1">
-        <v>24875000</v>
-      </c>
+      <c r="B461" s="3"/>
+      <c r="C461" s="3"/>
+      <c r="D461" s="3"/>
+      <c r="E461" s="3"/>
+      <c r="F461" s="3"/>
+      <c r="G461" s="3"/>
+      <c r="H461" s="3"/>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A462" t="s">
+      <c r="A462" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B462" s="1">
-        <v>40000000</v>
-      </c>
-      <c r="C462" s="1">
-        <v>30000000</v>
-      </c>
-      <c r="D462" s="1">
-        <v>0</v>
-      </c>
-      <c r="E462" s="1">
-        <v>0</v>
-      </c>
-      <c r="F462" s="1">
-        <v>0</v>
-      </c>
-      <c r="G462" s="1">
-        <v>30000000</v>
-      </c>
-      <c r="H462" s="1">
-        <v>10000000</v>
-      </c>
+      <c r="B462" s="3"/>
+      <c r="C462" s="3"/>
+      <c r="D462" s="3"/>
+      <c r="E462" s="3"/>
+      <c r="F462" s="3"/>
+      <c r="G462" s="3"/>
+      <c r="H462" s="3"/>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A463" t="s">
+      <c r="A463" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B463" s="1">
-        <v>4174295716</v>
-      </c>
-      <c r="C463" s="1">
-        <v>4174295716</v>
-      </c>
-      <c r="D463" s="1">
-        <v>1912975167</v>
-      </c>
-      <c r="E463" s="1">
-        <v>2261320549</v>
-      </c>
-      <c r="F463" s="1">
-        <v>4174295716</v>
-      </c>
-      <c r="G463" s="1">
-        <v>0</v>
-      </c>
-      <c r="H463" s="1">
-        <v>0</v>
-      </c>
+      <c r="B463" s="3"/>
+      <c r="C463" s="3"/>
+      <c r="D463" s="3"/>
+      <c r="E463" s="3"/>
+      <c r="F463" s="3"/>
+      <c r="G463" s="3"/>
+      <c r="H463" s="3"/>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A464" t="s">
+      <c r="A464" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B464" s="1">
+      <c r="B464" s="3">
         <v>6000000</v>
       </c>
-      <c r="C464" s="1">
+      <c r="C464" s="3">
         <v>4500000</v>
       </c>
-      <c r="D464" s="1">
-        <v>0</v>
-      </c>
-      <c r="E464" s="1">
-        <v>0</v>
-      </c>
-      <c r="F464" s="1">
-        <v>0</v>
-      </c>
-      <c r="G464" s="1">
+      <c r="D464" s="3">
+        <v>0</v>
+      </c>
+      <c r="E464" s="3"/>
+      <c r="F464" s="3"/>
+      <c r="G464" s="3">
         <v>4500000</v>
       </c>
-      <c r="H464" s="1">
+      <c r="H464" s="3">
         <v>1500000</v>
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A465" t="s">
+      <c r="A465" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B465" s="1">
+      <c r="B465" s="3">
         <v>41000000</v>
       </c>
-      <c r="C465" s="1">
+      <c r="C465" s="3">
         <v>30750000</v>
       </c>
-      <c r="D465" s="1">
+      <c r="D465" s="3">
         <v>5091000</v>
       </c>
-      <c r="E465" s="1">
+      <c r="E465" s="3">
         <v>4982700</v>
       </c>
-      <c r="F465" s="1">
+      <c r="F465" s="3">
         <v>10073700</v>
       </c>
-      <c r="G465" s="1">
+      <c r="G465" s="3">
         <v>20676300</v>
       </c>
-      <c r="H465" s="1">
+      <c r="H465" s="3">
         <v>10250000</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A466" t="s">
+      <c r="A466" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B466" s="1">
+      <c r="B466" s="3">
         <v>12000000</v>
       </c>
-      <c r="C466" s="1">
-        <v>12000000</v>
-      </c>
-      <c r="D466" s="1">
-        <v>0</v>
-      </c>
-      <c r="E466" s="1">
-        <v>0</v>
-      </c>
-      <c r="F466" s="1">
-        <v>0</v>
-      </c>
-      <c r="G466" s="1">
-        <v>12000000</v>
-      </c>
-      <c r="H466" s="1">
-        <v>0</v>
+      <c r="C466" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="D466" s="3">
+        <v>0</v>
+      </c>
+      <c r="E466" s="3"/>
+      <c r="F466" s="3"/>
+      <c r="G466" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="H466" s="3">
+        <v>9000000</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A467" t="s">
+      <c r="A467" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B467" s="1">
+      <c r="B467" s="3">
         <v>171000000</v>
       </c>
-      <c r="C467" s="1">
+      <c r="C467" s="3">
         <v>128250000</v>
       </c>
-      <c r="D467" s="1">
+      <c r="D467" s="3">
         <v>17585000</v>
       </c>
-      <c r="E467" s="1">
+      <c r="E467" s="3">
         <v>20876000</v>
       </c>
-      <c r="F467" s="1">
+      <c r="F467" s="3">
         <v>38461000</v>
       </c>
-      <c r="G467" s="1">
+      <c r="G467" s="3">
         <v>89789000</v>
       </c>
-      <c r="H467" s="1">
+      <c r="H467" s="3">
         <v>42750000</v>
       </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A468" t="s">
+      <c r="A468" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B468" s="1">
+      <c r="B468" s="3">
         <v>130000000</v>
       </c>
-      <c r="C468" s="1">
+      <c r="C468" s="3">
         <v>97500000</v>
       </c>
-      <c r="D468" s="1">
-        <v>0</v>
-      </c>
-      <c r="E468" s="1">
+      <c r="D468" s="3">
+        <v>0</v>
+      </c>
+      <c r="E468" s="3">
         <v>54869000</v>
       </c>
-      <c r="F468" s="1">
+      <c r="F468" s="3">
         <v>54869000</v>
       </c>
-      <c r="G468" s="1">
+      <c r="G468" s="3">
         <v>42631000</v>
       </c>
-      <c r="H468" s="1">
+      <c r="H468" s="3">
         <v>32500000</v>
       </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A469" t="s">
+      <c r="A469" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B469" s="1">
+      <c r="B469" s="3">
         <v>6660000</v>
       </c>
-      <c r="C469" s="1">
+      <c r="C469" s="3">
         <v>6660000</v>
       </c>
-      <c r="D469" s="1">
+      <c r="D469" s="3">
         <v>999000</v>
       </c>
-      <c r="E469" s="1">
+      <c r="E469" s="3">
         <v>3247644</v>
       </c>
-      <c r="F469" s="1">
+      <c r="F469" s="3">
         <v>4246644</v>
       </c>
-      <c r="G469" s="1">
+      <c r="G469" s="3">
         <v>2413356</v>
       </c>
-      <c r="H469" s="1">
+      <c r="H469" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A470" t="s">
+      <c r="A470" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B470" s="1">
+      <c r="B470" s="3">
         <v>6000000</v>
       </c>
-      <c r="C470" s="1">
+      <c r="C470" s="3">
         <v>6000000</v>
       </c>
-      <c r="D470" s="1">
+      <c r="D470" s="3">
         <v>5982000</v>
       </c>
-      <c r="E470" s="1">
-        <v>0</v>
-      </c>
-      <c r="F470" s="1">
+      <c r="E470" s="3"/>
+      <c r="F470" s="3">
         <v>5982000</v>
       </c>
-      <c r="G470" s="1">
+      <c r="G470" s="3">
         <v>18000</v>
       </c>
-      <c r="H470" s="1">
+      <c r="H470" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A471" t="s">
+      <c r="A471" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B471" s="1">
-        <v>0</v>
-      </c>
-      <c r="C471" s="1">
-        <v>0</v>
-      </c>
-      <c r="D471" s="1">
-        <v>0</v>
-      </c>
-      <c r="E471" s="1">
-        <v>15070219</v>
-      </c>
-      <c r="F471" s="1">
-        <v>15070219</v>
-      </c>
-      <c r="G471" s="1">
-        <v>-15070219</v>
-      </c>
-      <c r="H471" s="1">
-        <v>0</v>
-      </c>
+      <c r="B471" s="3"/>
+      <c r="C471" s="3"/>
+      <c r="D471" s="3"/>
+      <c r="E471" s="3"/>
+      <c r="F471" s="3"/>
+      <c r="G471" s="3"/>
+      <c r="H471" s="3"/>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A472" t="s">
+      <c r="A472" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B472" s="1">
-        <v>0</v>
-      </c>
-      <c r="C472" s="1">
-        <v>0</v>
-      </c>
-      <c r="D472" s="1">
-        <v>0</v>
-      </c>
-      <c r="E472" s="1">
-        <v>10588577</v>
-      </c>
-      <c r="F472" s="1">
-        <v>10588577</v>
-      </c>
-      <c r="G472" s="1">
-        <v>-10588577</v>
-      </c>
-      <c r="H472" s="1">
-        <v>0</v>
-      </c>
+      <c r="B472" s="3"/>
+      <c r="C472" s="3"/>
+      <c r="D472" s="3"/>
+      <c r="E472" s="3"/>
+      <c r="F472" s="3"/>
+      <c r="G472" s="3"/>
+      <c r="H472" s="3"/>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A473" t="s">
+      <c r="A473" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B473" s="1">
-        <v>1051363504</v>
-      </c>
-      <c r="C473" s="1">
-        <v>1051363504</v>
-      </c>
-      <c r="D473" s="1">
-        <v>0</v>
-      </c>
-      <c r="E473" s="1">
-        <v>678518579</v>
-      </c>
-      <c r="F473" s="1">
-        <v>678518579</v>
-      </c>
-      <c r="G473" s="1">
-        <v>372844925</v>
-      </c>
-      <c r="H473" s="1">
-        <v>0</v>
-      </c>
+      <c r="B473" s="3"/>
+      <c r="C473" s="3"/>
+      <c r="D473" s="3"/>
+      <c r="E473" s="3"/>
+      <c r="F473" s="3"/>
+      <c r="G473" s="3"/>
+      <c r="H473" s="3"/>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A474" t="s">
+      <c r="A474" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B474" s="1">
-        <v>820339482</v>
-      </c>
-      <c r="C474" s="1">
-        <v>820339482</v>
-      </c>
-      <c r="D474" s="1">
-        <v>0</v>
-      </c>
-      <c r="E474" s="1">
-        <v>696831688</v>
-      </c>
-      <c r="F474" s="1">
-        <v>696831688</v>
-      </c>
-      <c r="G474" s="1">
-        <v>123507794</v>
-      </c>
-      <c r="H474" s="1">
-        <v>0</v>
-      </c>
+      <c r="B474" s="3"/>
+      <c r="C474" s="3"/>
+      <c r="D474" s="3"/>
+      <c r="E474" s="3"/>
+      <c r="F474" s="3"/>
+      <c r="G474" s="3"/>
+      <c r="H474" s="3"/>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A475" t="s">
+      <c r="A475" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B475" s="1">
-        <v>7701176</v>
-      </c>
-      <c r="C475" s="1">
-        <v>7701176</v>
-      </c>
-      <c r="D475" s="1">
-        <v>0</v>
-      </c>
-      <c r="E475" s="1">
-        <v>0</v>
-      </c>
-      <c r="F475" s="1">
-        <v>0</v>
-      </c>
-      <c r="G475" s="1">
-        <v>7701176</v>
-      </c>
-      <c r="H475" s="1">
-        <v>0</v>
-      </c>
+      <c r="B475" s="3"/>
+      <c r="C475" s="3"/>
+      <c r="D475" s="3"/>
+      <c r="E475" s="3"/>
+      <c r="F475" s="3"/>
+      <c r="G475" s="3"/>
+      <c r="H475" s="3"/>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A476" t="s">
+      <c r="A476" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B476" s="1">
-        <v>8609254113</v>
-      </c>
-      <c r="C476" s="1">
-        <v>8609254113</v>
-      </c>
-      <c r="D476" s="1">
-        <v>0</v>
-      </c>
-      <c r="E476" s="1">
-        <v>4052825755</v>
-      </c>
-      <c r="F476" s="1">
-        <v>4052825755</v>
-      </c>
-      <c r="G476" s="1">
-        <v>4556428358</v>
-      </c>
-      <c r="H476" s="1">
-        <v>0</v>
-      </c>
+      <c r="B476" s="3"/>
+      <c r="C476" s="3"/>
+      <c r="D476" s="3"/>
+      <c r="E476" s="3"/>
+      <c r="F476" s="3"/>
+      <c r="G476" s="3"/>
+      <c r="H476" s="3"/>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A477" t="s">
+      <c r="A477" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B477" s="1">
-        <v>101794620</v>
-      </c>
-      <c r="C477" s="1">
-        <v>101794620</v>
-      </c>
-      <c r="D477" s="1">
-        <v>0</v>
-      </c>
-      <c r="E477" s="1">
-        <v>50786832</v>
-      </c>
-      <c r="F477" s="1">
-        <v>50786832</v>
-      </c>
-      <c r="G477" s="1">
-        <v>51007788</v>
-      </c>
-      <c r="H477" s="1">
-        <v>0</v>
-      </c>
+      <c r="B477" s="3"/>
+      <c r="C477" s="3"/>
+      <c r="D477" s="3"/>
+      <c r="E477" s="3"/>
+      <c r="F477" s="3"/>
+      <c r="G477" s="3"/>
+      <c r="H477" s="3"/>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A478" t="s">
+      <c r="A478" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B478" s="1">
-        <v>7845520107</v>
-      </c>
-      <c r="C478" s="1">
-        <v>7845520107</v>
-      </c>
-      <c r="D478" s="1">
-        <v>0</v>
-      </c>
-      <c r="E478" s="1">
-        <v>5941239906</v>
-      </c>
-      <c r="F478" s="1">
-        <v>5941239906</v>
-      </c>
-      <c r="G478" s="1">
-        <v>1904280201</v>
-      </c>
-      <c r="H478" s="1">
-        <v>0</v>
-      </c>
+      <c r="B478" s="3"/>
+      <c r="C478" s="3"/>
+      <c r="D478" s="3"/>
+      <c r="E478" s="3"/>
+      <c r="F478" s="3"/>
+      <c r="G478" s="3"/>
+      <c r="H478" s="3"/>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A479" t="s">
+      <c r="A479" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B479" s="1">
-        <v>56658654</v>
-      </c>
-      <c r="C479" s="1">
-        <v>56658654</v>
-      </c>
-      <c r="D479" s="1">
-        <v>0</v>
-      </c>
-      <c r="E479" s="1">
-        <v>0</v>
-      </c>
-      <c r="F479" s="1">
-        <v>0</v>
-      </c>
-      <c r="G479" s="1">
-        <v>56658654</v>
-      </c>
-      <c r="H479" s="1">
-        <v>0</v>
-      </c>
+      <c r="B479" s="3"/>
+      <c r="C479" s="3"/>
+      <c r="D479" s="3"/>
+      <c r="E479" s="3"/>
+      <c r="F479" s="3"/>
+      <c r="G479" s="3"/>
+      <c r="H479" s="3"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A480" t="s">
+      <c r="A480" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B480" s="1">
-        <v>897620618</v>
-      </c>
-      <c r="C480" s="1">
-        <v>897620618</v>
-      </c>
-      <c r="D480" s="1">
-        <v>0</v>
-      </c>
-      <c r="E480" s="1">
-        <v>363366128</v>
-      </c>
-      <c r="F480" s="1">
-        <v>363366128</v>
-      </c>
-      <c r="G480" s="1">
-        <v>534254490</v>
-      </c>
-      <c r="H480" s="1">
-        <v>0</v>
-      </c>
+      <c r="B480" s="3"/>
+      <c r="C480" s="3"/>
+      <c r="D480" s="3"/>
+      <c r="E480" s="3"/>
+      <c r="F480" s="3"/>
+      <c r="G480" s="3"/>
+      <c r="H480" s="3"/>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A481" t="s">
+      <c r="A481" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B481" s="1">
-        <v>1118633978</v>
-      </c>
-      <c r="C481" s="1">
-        <v>1118633978</v>
-      </c>
-      <c r="D481" s="1">
-        <v>0</v>
-      </c>
-      <c r="E481" s="1">
-        <v>735666613</v>
-      </c>
-      <c r="F481" s="1">
-        <v>735666613</v>
-      </c>
-      <c r="G481" s="1">
-        <v>382967365</v>
-      </c>
-      <c r="H481" s="1">
-        <v>0</v>
-      </c>
+      <c r="B481" s="3"/>
+      <c r="C481" s="3"/>
+      <c r="D481" s="3"/>
+      <c r="E481" s="3"/>
+      <c r="F481" s="3"/>
+      <c r="G481" s="3"/>
+      <c r="H481" s="3"/>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A482" t="s">
+      <c r="A482" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B482" s="1">
-        <v>3850588</v>
-      </c>
-      <c r="C482" s="1">
-        <v>3850588</v>
-      </c>
-      <c r="D482" s="1">
-        <v>0</v>
-      </c>
-      <c r="E482" s="1">
-        <v>0</v>
-      </c>
-      <c r="F482" s="1">
-        <v>0</v>
-      </c>
-      <c r="G482" s="1">
-        <v>3850588</v>
-      </c>
-      <c r="H482" s="1">
-        <v>0</v>
-      </c>
+      <c r="B482" s="3"/>
+      <c r="C482" s="3"/>
+      <c r="D482" s="3"/>
+      <c r="E482" s="3"/>
+      <c r="F482" s="3"/>
+      <c r="G482" s="3"/>
+      <c r="H482" s="3"/>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A483" t="s">
+      <c r="A483" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B483" s="1">
-        <v>0</v>
-      </c>
-      <c r="C483" s="1">
-        <v>0</v>
-      </c>
-      <c r="D483" s="1">
-        <v>0</v>
-      </c>
-      <c r="E483" s="1">
-        <v>69640000</v>
-      </c>
-      <c r="F483" s="1">
-        <v>69640000</v>
-      </c>
-      <c r="G483" s="1">
-        <v>-69640000</v>
-      </c>
-      <c r="H483" s="1">
-        <v>0</v>
-      </c>
+      <c r="B483" s="3"/>
+      <c r="C483" s="3"/>
+      <c r="D483" s="3"/>
+      <c r="E483" s="3"/>
+      <c r="F483" s="3"/>
+      <c r="G483" s="3"/>
+      <c r="H483" s="3"/>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A484" t="s">
+      <c r="A484" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B484" s="1">
-        <v>39997864117</v>
-      </c>
-      <c r="C484" s="1">
-        <v>39425583548</v>
-      </c>
-      <c r="D484" s="1">
-        <v>8678193635</v>
-      </c>
-      <c r="E484" s="1">
-        <v>18718632022</v>
-      </c>
-      <c r="F484" s="1">
-        <v>27396825657</v>
-      </c>
-      <c r="G484" s="1">
-        <v>12028757891</v>
-      </c>
-      <c r="H484" s="1">
-        <v>572280569</v>
+      <c r="B484" s="3">
+        <f>SUM(B429:B483)</f>
+        <v>2349760730</v>
+      </c>
+      <c r="C484" s="3">
+        <f t="shared" ref="C484:H484" si="0">SUM(C429:C483)</f>
+        <v>2238760730</v>
+      </c>
+      <c r="D484" s="3">
+        <f t="shared" si="0"/>
+        <v>1440178200</v>
+      </c>
+      <c r="E484" s="3">
+        <f t="shared" si="0"/>
+        <v>317170274</v>
+      </c>
+      <c r="F484" s="3">
+        <f t="shared" si="0"/>
+        <v>1757348474</v>
+      </c>
+      <c r="G484" s="3">
+        <f t="shared" si="0"/>
+        <v>481412256</v>
+      </c>
+      <c r="H484" s="3">
+        <f t="shared" si="0"/>
+        <v>111000000</v>
       </c>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.45">

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\7. Jul\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{E8A3A027-6FEB-4652-85F9-B1183EECAC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{65B6187B-0812-4B8E-9E00-F0BDDD170EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975"/>
   </bookViews>
@@ -903,7 +903,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1267,9 +1269,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="60.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="15.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="15.06640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1309,16 +1309,16 @@
         <v>109317656175</v>
       </c>
       <c r="D2" s="1">
-        <v>103628196635</v>
+        <v>103927752479</v>
       </c>
       <c r="E2" s="1">
         <v>4659227266</v>
       </c>
       <c r="F2" s="1">
-        <v>108287423901</v>
+        <v>108586979745</v>
       </c>
       <c r="G2" s="1">
-        <v>1030232274</v>
+        <v>730676430</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
@@ -1673,16 +1673,16 @@
         <v>1200000000</v>
       </c>
       <c r="D16" s="1">
-        <v>74343900</v>
+        <v>65779500</v>
       </c>
       <c r="E16" s="1">
         <v>92721500</v>
       </c>
       <c r="F16" s="1">
-        <v>167065400</v>
+        <v>158501000</v>
       </c>
       <c r="G16" s="1">
-        <v>1032934600</v>
+        <v>1041499000</v>
       </c>
       <c r="H16" s="1">
         <v>400000000</v>
@@ -1725,16 +1725,16 @@
         <v>4500000000</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>651492204</v>
       </c>
       <c r="E18" s="1">
         <v>1886000425</v>
       </c>
       <c r="F18" s="1">
-        <v>1886000425</v>
+        <v>2537492629</v>
       </c>
       <c r="G18" s="1">
-        <v>2613999575</v>
+        <v>1962507371</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -1777,10 +1777,10 @@
         <v>510385000</v>
       </c>
       <c r="D20" s="1">
-        <v>39417000</v>
+        <v>20067000</v>
       </c>
       <c r="E20" s="1">
-        <v>61915312</v>
+        <v>81265312</v>
       </c>
       <c r="F20" s="1">
         <v>101332312</v>
@@ -1829,16 +1829,16 @@
         <v>622597314</v>
       </c>
       <c r="D22" s="1">
-        <v>518139520</v>
+        <v>526703920</v>
       </c>
       <c r="E22" s="1">
         <v>95725294</v>
       </c>
       <c r="F22" s="1">
-        <v>613864814</v>
+        <v>622429214</v>
       </c>
       <c r="G22" s="1">
-        <v>8732500</v>
+        <v>168100</v>
       </c>
       <c r="H22" s="1">
         <v>125000000</v>
@@ -1855,10 +1855,10 @@
         <v>600000000</v>
       </c>
       <c r="D23" s="1">
-        <v>49122159</v>
+        <v>2917400</v>
       </c>
       <c r="E23" s="1">
-        <v>151276000</v>
+        <v>197480759</v>
       </c>
       <c r="F23" s="1">
         <v>200398159</v>
@@ -1884,13 +1884,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>908966243</v>
+        <v>927522493</v>
       </c>
       <c r="F24" s="1">
-        <v>908966243</v>
+        <v>927522493</v>
       </c>
       <c r="G24" s="1">
-        <v>814930178</v>
+        <v>796373928</v>
       </c>
       <c r="H24" s="1">
         <v>625000000</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>-17300000</v>
+        <v>-25600000</v>
       </c>
       <c r="F26" s="1">
-        <v>-17300000</v>
+        <v>-25600000</v>
       </c>
       <c r="G26" s="1">
-        <v>17300000</v>
+        <v>25600000</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -1962,13 +1962,13 @@
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>1758927143</v>
+        <v>2528787484</v>
       </c>
       <c r="F27" s="1">
-        <v>1758927143</v>
+        <v>2528787484</v>
       </c>
       <c r="G27" s="1">
-        <v>1697687061</v>
+        <v>927826720</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -1988,13 +1988,13 @@
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>32914812</v>
+        <v>41730129</v>
       </c>
       <c r="F28" s="1">
-        <v>32914812</v>
+        <v>41730129</v>
       </c>
       <c r="G28" s="1">
-        <v>19913811</v>
+        <v>11098494</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>3229407187</v>
+        <v>3441841687</v>
       </c>
       <c r="F29" s="1">
-        <v>3229407187</v>
+        <v>3441841687</v>
       </c>
       <c r="G29" s="1">
-        <v>848862848</v>
+        <v>636428348</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -2066,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>3942404244</v>
+        <v>5874228668</v>
       </c>
       <c r="F31" s="1">
-        <v>3942404244</v>
+        <v>5874228668</v>
       </c>
       <c r="G31" s="1">
-        <v>7005071011</v>
+        <v>5073246587</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>131299737</v>
+        <v>152711468</v>
       </c>
       <c r="F32" s="1">
-        <v>131299737</v>
+        <v>152711468</v>
       </c>
       <c r="G32" s="1">
-        <v>116790265</v>
+        <v>95378534</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -2118,13 +2118,13 @@
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>8845043347</v>
+        <v>9453377073</v>
       </c>
       <c r="F33" s="1">
-        <v>8845043347</v>
+        <v>9453377073</v>
       </c>
       <c r="G33" s="1">
-        <v>5125022699</v>
+        <v>4516688973</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2196,13 +2196,13 @@
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>-15948637</v>
+        <v>24175869</v>
       </c>
       <c r="F36" s="1">
-        <v>-15948637</v>
+        <v>24175869</v>
       </c>
       <c r="G36" s="1">
-        <v>15948637</v>
+        <v>-24175869</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -2222,13 +2222,13 @@
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>66546895</v>
+        <v>75736895</v>
       </c>
       <c r="F37" s="1">
-        <v>66546895</v>
+        <v>75736895</v>
       </c>
       <c r="G37" s="1">
-        <v>-66546895</v>
+        <v>-75736895</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -2323,16 +2323,16 @@
         <v>348402857407</v>
       </c>
       <c r="D41" s="1">
-        <v>242279184508</v>
+        <v>243164677797</v>
       </c>
       <c r="E41" s="1">
-        <v>79737900262</v>
+        <v>83415705816</v>
       </c>
       <c r="F41" s="1">
-        <v>322017084770</v>
+        <v>326580383613</v>
       </c>
       <c r="G41" s="1">
-        <v>26385772637</v>
+        <v>21822473794</v>
       </c>
       <c r="H41" s="1">
         <v>2417500000</v>
@@ -2343,22 +2343,22 @@
         <v>8</v>
       </c>
       <c r="B42" s="1">
-        <v>25194775704</v>
+        <v>26681487101</v>
       </c>
       <c r="C42" s="1">
-        <v>25194775704</v>
+        <v>26681487101</v>
       </c>
       <c r="D42" s="1">
-        <v>19191458060</v>
+        <v>20623989101</v>
       </c>
       <c r="E42" s="1">
         <v>5598748000</v>
       </c>
       <c r="F42" s="1">
-        <v>24790206060</v>
+        <v>26222737101</v>
       </c>
       <c r="G42" s="1">
-        <v>404569644</v>
+        <v>458750000</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -2609,16 +2609,16 @@
         <v>6000000000</v>
       </c>
       <c r="D52" s="1">
-        <v>5047435763</v>
+        <v>5047644028</v>
       </c>
       <c r="E52" s="1">
         <v>520835965</v>
       </c>
       <c r="F52" s="1">
-        <v>5568271728</v>
+        <v>5568479993</v>
       </c>
       <c r="G52" s="1">
-        <v>431728272</v>
+        <v>431520007</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -2635,16 +2635,16 @@
         <v>4260000000</v>
       </c>
       <c r="D53" s="1">
-        <v>1149719123</v>
+        <v>1301255823</v>
       </c>
       <c r="E53" s="1">
         <v>1615809729</v>
       </c>
       <c r="F53" s="1">
-        <v>2765528852</v>
+        <v>2917065552</v>
       </c>
       <c r="G53" s="1">
-        <v>1494471148</v>
+        <v>1342934448</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -2687,16 +2687,16 @@
         <v>2500000000</v>
       </c>
       <c r="D55" s="1">
-        <v>490906350</v>
+        <v>973190350</v>
       </c>
       <c r="E55" s="1">
         <v>572278341</v>
       </c>
       <c r="F55" s="1">
-        <v>1063184691</v>
+        <v>1545468691</v>
       </c>
       <c r="G55" s="1">
-        <v>1436815309</v>
+        <v>954531309</v>
       </c>
       <c r="H55" s="1">
         <v>0</v>
@@ -2713,16 +2713,16 @@
         <v>250000000</v>
       </c>
       <c r="D56" s="1">
-        <v>20144260</v>
+        <v>85514461</v>
       </c>
       <c r="E56" s="1">
         <v>64039200</v>
       </c>
       <c r="F56" s="1">
-        <v>84183460</v>
+        <v>149553661</v>
       </c>
       <c r="G56" s="1">
-        <v>165816540</v>
+        <v>100446339</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="1">
-        <v>6850000000</v>
+        <v>5363288603</v>
       </c>
       <c r="C57" s="1">
-        <v>6850000000</v>
+        <v>5363288603</v>
       </c>
       <c r="D57" s="1">
         <v>4448521280</v>
@@ -2748,7 +2748,7 @@
         <v>4805266740</v>
       </c>
       <c r="G57" s="1">
-        <v>2044733260</v>
+        <v>558021863</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -2765,16 +2765,16 @@
         <v>2620000000</v>
       </c>
       <c r="D58" s="1">
-        <v>668471317</v>
+        <v>675395317</v>
       </c>
       <c r="E58" s="1">
         <v>545850367</v>
       </c>
       <c r="F58" s="1">
-        <v>1214321684</v>
+        <v>1221245684</v>
       </c>
       <c r="G58" s="1">
-        <v>1405678316</v>
+        <v>1398754316</v>
       </c>
       <c r="H58" s="1">
         <v>0</v>
@@ -2843,16 +2843,16 @@
         <v>2500000000</v>
       </c>
       <c r="D61" s="1">
-        <v>1298260100</v>
+        <v>1847310100</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
       </c>
       <c r="F61" s="1">
-        <v>1298260100</v>
+        <v>1847310100</v>
       </c>
       <c r="G61" s="1">
-        <v>1201739900</v>
+        <v>652689900</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
@@ -2895,10 +2895,10 @@
         <v>180000150</v>
       </c>
       <c r="D63" s="1">
-        <v>120143600</v>
+        <v>9176000</v>
       </c>
       <c r="E63" s="1">
-        <v>28710000</v>
+        <v>139677600</v>
       </c>
       <c r="F63" s="1">
         <v>148853600</v>
@@ -2973,10 +2973,10 @@
         <v>335175000</v>
       </c>
       <c r="D66" s="1">
-        <v>75797509</v>
+        <v>63709511</v>
       </c>
       <c r="E66" s="1">
-        <v>153635516</v>
+        <v>165723514</v>
       </c>
       <c r="F66" s="1">
         <v>229433025</v>
@@ -3080,13 +3080,13 @@
         <v>46676000</v>
       </c>
       <c r="E70" s="1">
-        <v>219515500</v>
+        <v>223290500</v>
       </c>
       <c r="F70" s="1">
-        <v>266191500</v>
+        <v>269966500</v>
       </c>
       <c r="G70" s="1">
-        <v>88033500</v>
+        <v>84258500</v>
       </c>
       <c r="H70" s="1">
         <v>118075000</v>
@@ -3158,13 +3158,13 @@
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>11034143993</v>
+        <v>14865921347</v>
       </c>
       <c r="F73" s="1">
-        <v>11034143993</v>
+        <v>14865921347</v>
       </c>
       <c r="G73" s="1">
-        <v>11897463236</v>
+        <v>8065685882</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -3184,13 +3184,13 @@
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>263841279</v>
+        <v>307147040</v>
       </c>
       <c r="F74" s="1">
-        <v>263841279</v>
+        <v>307147040</v>
       </c>
       <c r="G74" s="1">
-        <v>341113878</v>
+        <v>297808117</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>9566218</v>
       </c>
       <c r="E75" s="1">
-        <v>16304148722</v>
+        <v>17076241722</v>
       </c>
       <c r="F75" s="1">
-        <v>16313714940</v>
+        <v>17085807940</v>
       </c>
       <c r="G75" s="1">
-        <v>4653706590</v>
+        <v>3881613590</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -3262,13 +3262,13 @@
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>855595328</v>
+        <v>1232007053</v>
       </c>
       <c r="F77" s="1">
-        <v>855595328</v>
+        <v>1232007053</v>
       </c>
       <c r="G77" s="1">
-        <v>793831257</v>
+        <v>417419532</v>
       </c>
       <c r="H77" s="1">
         <v>0</v>
@@ -3288,13 +3288,13 @@
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>32902472</v>
+        <v>38393968</v>
       </c>
       <c r="F78" s="1">
-        <v>32902472</v>
+        <v>38393968</v>
       </c>
       <c r="G78" s="1">
-        <v>20757651</v>
+        <v>15266155</v>
       </c>
       <c r="H78" s="1">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         <v>165657</v>
       </c>
       <c r="E79" s="1">
-        <v>1659671681</v>
+        <v>1761534181</v>
       </c>
       <c r="F79" s="1">
-        <v>1659837338</v>
+        <v>1761699838</v>
       </c>
       <c r="G79" s="1">
-        <v>277281190</v>
+        <v>175418690</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
@@ -3389,16 +3389,16 @@
         <v>110881210191</v>
       </c>
       <c r="D82" s="1">
-        <v>35214633990</v>
+        <v>37779482599</v>
       </c>
       <c r="E82" s="1">
-        <v>42902167059</v>
+        <v>48159939493</v>
       </c>
       <c r="F82" s="1">
-        <v>78116801049</v>
+        <v>85939422092</v>
       </c>
       <c r="G82" s="1">
-        <v>32764409142</v>
+        <v>24941788099</v>
       </c>
       <c r="H82" s="1">
         <v>671501500</v>
@@ -3519,16 +3519,16 @@
         <v>30639775739</v>
       </c>
       <c r="D87" s="1">
-        <v>14186214659</v>
+        <v>14182217859</v>
       </c>
       <c r="E87" s="1">
         <v>11612015432</v>
       </c>
       <c r="F87" s="1">
-        <v>25798230091</v>
+        <v>25794233291</v>
       </c>
       <c r="G87" s="1">
-        <v>4841545648</v>
+        <v>4845542448</v>
       </c>
       <c r="H87" s="1">
         <v>0</v>
@@ -3545,16 +3545,16 @@
         <v>288221000</v>
       </c>
       <c r="D88" s="1">
-        <v>0</v>
+        <v>288220996</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
       </c>
       <c r="F88" s="1">
-        <v>0</v>
+        <v>288220996</v>
       </c>
       <c r="G88" s="1">
-        <v>288221000</v>
+        <v>4</v>
       </c>
       <c r="H88" s="1">
         <v>0</v>
@@ -3597,16 +3597,16 @@
         <v>1210765056</v>
       </c>
       <c r="D90" s="1">
-        <v>24308000</v>
+        <v>396801940</v>
       </c>
       <c r="E90" s="1">
         <v>122034440</v>
       </c>
       <c r="F90" s="1">
-        <v>146342440</v>
+        <v>518836380</v>
       </c>
       <c r="G90" s="1">
-        <v>1064422616</v>
+        <v>691928676</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -3649,16 +3649,16 @@
         <v>2796520000</v>
       </c>
       <c r="D92" s="1">
-        <v>461263770</v>
+        <v>733907689</v>
       </c>
       <c r="E92" s="1">
-        <v>1787423867</v>
+        <v>1795051867</v>
       </c>
       <c r="F92" s="1">
-        <v>2248687637</v>
+        <v>2528959556</v>
       </c>
       <c r="G92" s="1">
-        <v>547832363</v>
+        <v>267560444</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -3701,16 +3701,16 @@
         <v>180831882</v>
       </c>
       <c r="D94" s="1">
-        <v>0</v>
+        <v>49487057</v>
       </c>
       <c r="E94" s="1">
         <v>0</v>
       </c>
       <c r="F94" s="1">
-        <v>0</v>
+        <v>49487057</v>
       </c>
       <c r="G94" s="1">
-        <v>180831882</v>
+        <v>131344825</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
@@ -3727,16 +3727,16 @@
         <v>400000000</v>
       </c>
       <c r="D95" s="1">
-        <v>151845850</v>
+        <v>183045850</v>
       </c>
       <c r="E95" s="1">
         <v>216768377</v>
       </c>
       <c r="F95" s="1">
-        <v>368614227</v>
+        <v>399814227</v>
       </c>
       <c r="G95" s="1">
-        <v>31385773</v>
+        <v>185773</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -3753,16 +3753,16 @@
         <v>289155000</v>
       </c>
       <c r="D96" s="1">
-        <v>0</v>
+        <v>57100000</v>
       </c>
       <c r="E96" s="1">
         <v>0</v>
       </c>
       <c r="F96" s="1">
-        <v>0</v>
+        <v>57100000</v>
       </c>
       <c r="G96" s="1">
-        <v>289155000</v>
+        <v>232055000</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
@@ -3779,16 +3779,16 @@
         <v>360000000</v>
       </c>
       <c r="D97" s="1">
-        <v>2540000</v>
+        <v>66273976</v>
       </c>
       <c r="E97" s="1">
         <v>199678000</v>
       </c>
       <c r="F97" s="1">
-        <v>202218000</v>
+        <v>265951976</v>
       </c>
       <c r="G97" s="1">
-        <v>157782000</v>
+        <v>94048024</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
@@ -3805,16 +3805,16 @@
         <v>1710494400</v>
       </c>
       <c r="D98" s="1">
-        <v>734772280</v>
+        <v>913483280</v>
       </c>
       <c r="E98" s="1">
         <v>537988506</v>
       </c>
       <c r="F98" s="1">
-        <v>1272760786</v>
+        <v>1451471786</v>
       </c>
       <c r="G98" s="1">
-        <v>437733614</v>
+        <v>259022614</v>
       </c>
       <c r="H98" s="1">
         <v>0</v>
@@ -3857,16 +3857,16 @@
         <v>394475000</v>
       </c>
       <c r="D100" s="1">
-        <v>109101000</v>
+        <v>119148000</v>
       </c>
       <c r="E100" s="1">
         <v>45427850</v>
       </c>
       <c r="F100" s="1">
-        <v>154528850</v>
+        <v>164575850</v>
       </c>
       <c r="G100" s="1">
-        <v>239946150</v>
+        <v>229899150</v>
       </c>
       <c r="H100" s="1">
         <v>139825000</v>
@@ -3883,16 +3883,16 @@
         <v>255960000</v>
       </c>
       <c r="D101" s="1">
-        <v>94157900</v>
+        <v>118242050</v>
       </c>
       <c r="E101" s="1">
         <v>118761500</v>
       </c>
       <c r="F101" s="1">
-        <v>212919400</v>
+        <v>237003550</v>
       </c>
       <c r="G101" s="1">
-        <v>43040600</v>
+        <v>18956450</v>
       </c>
       <c r="H101" s="1">
         <v>85320000</v>
@@ -3990,13 +3990,13 @@
         <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>248858068</v>
+        <v>249908068</v>
       </c>
       <c r="F105" s="1">
-        <v>248858068</v>
+        <v>249908068</v>
       </c>
       <c r="G105" s="1">
-        <v>46199432</v>
+        <v>45149432</v>
       </c>
       <c r="H105" s="1">
         <v>98352500</v>
@@ -4120,13 +4120,13 @@
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>8061650206</v>
+        <v>10705515196</v>
       </c>
       <c r="F110" s="1">
-        <v>8061650206</v>
+        <v>10705515196</v>
       </c>
       <c r="G110" s="1">
-        <v>8161994647</v>
+        <v>5518129657</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -4146,13 +4146,13 @@
         <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>98408130</v>
+        <v>114204508</v>
       </c>
       <c r="F111" s="1">
-        <v>98408130</v>
+        <v>114204508</v>
       </c>
       <c r="G111" s="1">
-        <v>103182932</v>
+        <v>87386554</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -4172,13 +4172,13 @@
         <v>9868545</v>
       </c>
       <c r="E112" s="1">
-        <v>11750086031</v>
+        <v>12261628031</v>
       </c>
       <c r="F112" s="1">
-        <v>11759954576</v>
+        <v>12271496576</v>
       </c>
       <c r="G112" s="1">
-        <v>2738225372</v>
+        <v>2226683372</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -4224,13 +4224,13 @@
         <v>0</v>
       </c>
       <c r="E114" s="1">
-        <v>648492006</v>
+        <v>945989944</v>
       </c>
       <c r="F114" s="1">
-        <v>648492006</v>
+        <v>945989944</v>
       </c>
       <c r="G114" s="1">
-        <v>1315980990</v>
+        <v>1018483052</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
@@ -4250,13 +4250,13 @@
         <v>0</v>
       </c>
       <c r="E115" s="1">
-        <v>20146384</v>
+        <v>23490285</v>
       </c>
       <c r="F115" s="1">
-        <v>20146384</v>
+        <v>23490285</v>
       </c>
       <c r="G115" s="1">
-        <v>20766232</v>
+        <v>17422331</v>
       </c>
       <c r="H115" s="1">
         <v>0</v>
@@ -4276,13 +4276,13 @@
         <v>0</v>
       </c>
       <c r="E116" s="1">
-        <v>1321728184</v>
+        <v>1407653184</v>
       </c>
       <c r="F116" s="1">
-        <v>1321728184</v>
+        <v>1407653184</v>
       </c>
       <c r="G116" s="1">
-        <v>606932690</v>
+        <v>521007690</v>
       </c>
       <c r="H116" s="1">
         <v>0</v>
@@ -4325,16 +4325,16 @@
         <v>81693644736</v>
       </c>
       <c r="D118" s="1">
-        <v>16596000831</v>
+        <v>17939726069</v>
       </c>
       <c r="E118" s="1">
-        <v>41738039021</v>
+        <v>45304687228</v>
       </c>
       <c r="F118" s="1">
-        <v>58334039852</v>
+        <v>63244413297</v>
       </c>
       <c r="G118" s="1">
-        <v>23359604884</v>
+        <v>18449231439</v>
       </c>
       <c r="H118" s="1">
         <v>475697500</v>
@@ -4377,10 +4377,10 @@
         <v>1494332364</v>
       </c>
       <c r="D120" s="1">
-        <v>536949716</v>
+        <v>498831216</v>
       </c>
       <c r="E120" s="1">
-        <v>89465211</v>
+        <v>127583711</v>
       </c>
       <c r="F120" s="1">
         <v>626414927</v>
@@ -4429,10 +4429,10 @@
         <v>929147000</v>
       </c>
       <c r="D122" s="1">
-        <v>1485168</v>
+        <v>0</v>
       </c>
       <c r="E122" s="1">
-        <v>503379314</v>
+        <v>504864482</v>
       </c>
       <c r="F122" s="1">
         <v>504864482</v>
@@ -4533,10 +4533,10 @@
         <v>1665000000</v>
       </c>
       <c r="D126" s="1">
-        <v>265433148</v>
+        <v>223833148</v>
       </c>
       <c r="E126" s="1">
-        <v>513322246</v>
+        <v>554922246</v>
       </c>
       <c r="F126" s="1">
         <v>778755394</v>
@@ -4819,16 +4819,16 @@
         <v>265950000</v>
       </c>
       <c r="D137" s="1">
-        <v>19400000</v>
+        <v>47639000</v>
       </c>
       <c r="E137" s="1">
-        <v>144959200</v>
+        <v>153359200</v>
       </c>
       <c r="F137" s="1">
-        <v>164359200</v>
+        <v>200998200</v>
       </c>
       <c r="G137" s="1">
-        <v>101590800</v>
+        <v>64951800</v>
       </c>
       <c r="H137" s="1">
         <v>88650000</v>
@@ -4871,16 +4871,16 @@
         <v>203550000</v>
       </c>
       <c r="D139" s="1">
-        <v>53284500</v>
+        <v>555000</v>
       </c>
       <c r="E139" s="1">
-        <v>127197932</v>
+        <v>175147932</v>
       </c>
       <c r="F139" s="1">
-        <v>180482432</v>
+        <v>175702932</v>
       </c>
       <c r="G139" s="1">
-        <v>23067568</v>
+        <v>27847068</v>
       </c>
       <c r="H139" s="1">
         <v>67850000</v>
@@ -4900,13 +4900,13 @@
         <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>106204750</v>
+        <v>120680750</v>
       </c>
       <c r="F140" s="1">
-        <v>106204750</v>
+        <v>120680750</v>
       </c>
       <c r="G140" s="1">
-        <v>53785250</v>
+        <v>39309250</v>
       </c>
       <c r="H140" s="1">
         <v>53330000</v>
@@ -4978,13 +4978,13 @@
         <v>0</v>
       </c>
       <c r="E143" s="1">
-        <v>4728418553</v>
+        <v>6354419036</v>
       </c>
       <c r="F143" s="1">
-        <v>4728418553</v>
+        <v>6354419036</v>
       </c>
       <c r="G143" s="1">
-        <v>5220675530</v>
+        <v>3594675047</v>
       </c>
       <c r="H143" s="1">
         <v>0</v>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="E144" s="1">
-        <v>192290838</v>
+        <v>224568402</v>
       </c>
       <c r="F144" s="1">
-        <v>192290838</v>
+        <v>224568402</v>
       </c>
       <c r="G144" s="1">
-        <v>194274564</v>
+        <v>161997000</v>
       </c>
       <c r="H144" s="1">
         <v>0</v>
@@ -5030,13 +5030,13 @@
         <v>0</v>
       </c>
       <c r="E145" s="1">
-        <v>7610688710</v>
+        <v>7956996210</v>
       </c>
       <c r="F145" s="1">
-        <v>7610688710</v>
+        <v>7956996210</v>
       </c>
       <c r="G145" s="1">
-        <v>2159161181</v>
+        <v>1812853681</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
@@ -5082,13 +5082,13 @@
         <v>0</v>
       </c>
       <c r="E147" s="1">
-        <v>477550123</v>
+        <v>723780456</v>
       </c>
       <c r="F147" s="1">
-        <v>477550123</v>
+        <v>723780456</v>
       </c>
       <c r="G147" s="1">
-        <v>930961880</v>
+        <v>684731547</v>
       </c>
       <c r="H147" s="1">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0</v>
       </c>
       <c r="E148" s="1">
-        <v>12938124</v>
+        <v>15094478</v>
       </c>
       <c r="F148" s="1">
-        <v>12938124</v>
+        <v>15094478</v>
       </c>
       <c r="G148" s="1">
-        <v>25381265</v>
+        <v>23224911</v>
       </c>
       <c r="H148" s="1">
         <v>0</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="E149" s="1">
-        <v>954263788</v>
+        <v>1012283788</v>
       </c>
       <c r="F149" s="1">
-        <v>954263788</v>
+        <v>1012283788</v>
       </c>
       <c r="G149" s="1">
-        <v>376053751</v>
+        <v>318033751</v>
       </c>
       <c r="H149" s="1">
         <v>0</v>
@@ -5209,16 +5209,16 @@
         <v>52173056175</v>
       </c>
       <c r="D152" s="1">
-        <v>12571751652</v>
+        <v>12466057484</v>
       </c>
       <c r="E152" s="1">
-        <v>24541234609</v>
+        <v>27004256511</v>
       </c>
       <c r="F152" s="1">
-        <v>37112986261</v>
+        <v>39470313995</v>
       </c>
       <c r="G152" s="1">
-        <v>15060069914</v>
+        <v>12702742180</v>
       </c>
       <c r="H152" s="1">
         <v>411080000</v>
@@ -5261,16 +5261,16 @@
         <v>4687847624</v>
       </c>
       <c r="D154" s="1">
-        <v>2702138971</v>
+        <v>3652869061</v>
       </c>
       <c r="E154" s="1">
-        <v>545938559</v>
+        <v>1000139013</v>
       </c>
       <c r="F154" s="1">
-        <v>3248077530</v>
+        <v>4653008074</v>
       </c>
       <c r="G154" s="1">
-        <v>1439770094</v>
+        <v>34839550</v>
       </c>
       <c r="H154" s="1">
         <v>0</v>
@@ -5391,16 +5391,16 @@
         <v>1702406000</v>
       </c>
       <c r="D159" s="1">
-        <v>220162954</v>
+        <v>207174354</v>
       </c>
       <c r="E159" s="1">
-        <v>694338830</v>
+        <v>707301975</v>
       </c>
       <c r="F159" s="1">
-        <v>914501784</v>
+        <v>914476329</v>
       </c>
       <c r="G159" s="1">
-        <v>787904216</v>
+        <v>787929671</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
@@ -5443,16 +5443,16 @@
         <v>996956000</v>
       </c>
       <c r="D161" s="1">
-        <v>497168932</v>
+        <v>481950000</v>
       </c>
       <c r="E161" s="1">
-        <v>43800510</v>
+        <v>58072672</v>
       </c>
       <c r="F161" s="1">
-        <v>540969442</v>
+        <v>540022672</v>
       </c>
       <c r="G161" s="1">
-        <v>455986558</v>
+        <v>456933328</v>
       </c>
       <c r="H161" s="1">
         <v>0</v>
@@ -5521,16 +5521,16 @@
         <v>500000000</v>
       </c>
       <c r="D164" s="1">
-        <v>124128929</v>
+        <v>50817909</v>
       </c>
       <c r="E164" s="1">
-        <v>71874588</v>
+        <v>140006588</v>
       </c>
       <c r="F164" s="1">
-        <v>196003517</v>
+        <v>190824497</v>
       </c>
       <c r="G164" s="1">
-        <v>303996483</v>
+        <v>309175503</v>
       </c>
       <c r="H164" s="1">
         <v>0</v>
@@ -5625,10 +5625,10 @@
         <v>90090000</v>
       </c>
       <c r="D168" s="1">
-        <v>21080000</v>
+        <v>0</v>
       </c>
       <c r="E168" s="1">
-        <v>40500000</v>
+        <v>61580000</v>
       </c>
       <c r="F168" s="1">
         <v>61580000</v>
@@ -5651,16 +5651,16 @@
         <v>132300000</v>
       </c>
       <c r="D169" s="1">
-        <v>43706250</v>
+        <v>0</v>
       </c>
       <c r="E169" s="1">
-        <v>0</v>
+        <v>39375000</v>
       </c>
       <c r="F169" s="1">
-        <v>43706250</v>
+        <v>39375000</v>
       </c>
       <c r="G169" s="1">
-        <v>88593750</v>
+        <v>92925000</v>
       </c>
       <c r="H169" s="1">
         <v>0</v>
@@ -5680,13 +5680,13 @@
         <v>0</v>
       </c>
       <c r="E170" s="1">
-        <v>1199295573</v>
+        <v>1198080153</v>
       </c>
       <c r="F170" s="1">
-        <v>1199295573</v>
+        <v>1198080153</v>
       </c>
       <c r="G170" s="1">
-        <v>1169704427</v>
+        <v>1170919847</v>
       </c>
       <c r="H170" s="1">
         <v>0</v>
@@ -5706,13 +5706,13 @@
         <v>10000000</v>
       </c>
       <c r="E171" s="1">
-        <v>31244591</v>
+        <v>36244591</v>
       </c>
       <c r="F171" s="1">
-        <v>41244591</v>
+        <v>46244591</v>
       </c>
       <c r="G171" s="1">
-        <v>93755409</v>
+        <v>88755409</v>
       </c>
       <c r="H171" s="1">
         <v>45000000</v>
@@ -5729,16 +5729,16 @@
         <v>595150000</v>
       </c>
       <c r="D172" s="1">
-        <v>269040750</v>
+        <v>268493400</v>
       </c>
       <c r="E172" s="1">
-        <v>188144644</v>
+        <v>215128244</v>
       </c>
       <c r="F172" s="1">
-        <v>457185394</v>
+        <v>483621644</v>
       </c>
       <c r="G172" s="1">
-        <v>137964606</v>
+        <v>111528356</v>
       </c>
       <c r="H172" s="1">
         <v>136250000</v>
@@ -5836,13 +5836,13 @@
         <v>0</v>
       </c>
       <c r="E176" s="1">
-        <v>99078250</v>
+        <v>99653250</v>
       </c>
       <c r="F176" s="1">
-        <v>99078250</v>
+        <v>99653250</v>
       </c>
       <c r="G176" s="1">
-        <v>63223250</v>
+        <v>62648250</v>
       </c>
       <c r="H176" s="1">
         <v>54100500</v>
@@ -5888,13 +5888,13 @@
         <v>0</v>
       </c>
       <c r="E178" s="1">
-        <v>3531246065</v>
+        <v>4784592545</v>
       </c>
       <c r="F178" s="1">
-        <v>3531246065</v>
+        <v>4784592545</v>
       </c>
       <c r="G178" s="1">
-        <v>3973477313</v>
+        <v>2720130833</v>
       </c>
       <c r="H178" s="1">
         <v>0</v>
@@ -5914,13 +5914,13 @@
         <v>0</v>
       </c>
       <c r="E179" s="1">
-        <v>107638248</v>
+        <v>123692252</v>
       </c>
       <c r="F179" s="1">
-        <v>107638248</v>
+        <v>123692252</v>
       </c>
       <c r="G179" s="1">
-        <v>118697822</v>
+        <v>102643818</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
@@ -5940,13 +5940,13 @@
         <v>0</v>
       </c>
       <c r="E180" s="1">
-        <v>5589381741</v>
+        <v>5846514241</v>
       </c>
       <c r="F180" s="1">
-        <v>5589381741</v>
+        <v>5846514241</v>
       </c>
       <c r="G180" s="1">
-        <v>1739256759</v>
+        <v>1482124259</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
@@ -5992,13 +5992,13 @@
         <v>0</v>
       </c>
       <c r="E182" s="1">
-        <v>469983993</v>
+        <v>705676834</v>
       </c>
       <c r="F182" s="1">
-        <v>469983993</v>
+        <v>705676834</v>
       </c>
       <c r="G182" s="1">
-        <v>816035340</v>
+        <v>580342499</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
@@ -6018,13 +6018,13 @@
         <v>0</v>
       </c>
       <c r="E183" s="1">
-        <v>12414117</v>
+        <v>13549986</v>
       </c>
       <c r="F183" s="1">
-        <v>12414117</v>
+        <v>13549986</v>
       </c>
       <c r="G183" s="1">
-        <v>24404623</v>
+        <v>23268754</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -6044,13 +6044,13 @@
         <v>0</v>
       </c>
       <c r="E184" s="1">
-        <v>949926373</v>
+        <v>1009477373</v>
       </c>
       <c r="F184" s="1">
-        <v>949926373</v>
+        <v>1009477373</v>
       </c>
       <c r="G184" s="1">
-        <v>421493536</v>
+        <v>361942536</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
@@ -6093,16 +6093,16 @@
         <v>46375593027</v>
       </c>
       <c r="D186" s="1">
-        <v>9939948600</v>
+        <v>10723826538</v>
       </c>
       <c r="E186" s="1">
-        <v>22972440916</v>
+        <v>25436719551</v>
       </c>
       <c r="F186" s="1">
-        <v>32912389516</v>
+        <v>36160546089</v>
       </c>
       <c r="G186" s="1">
-        <v>13463203511</v>
+        <v>10215046938</v>
       </c>
       <c r="H186" s="1">
         <v>449400500</v>
@@ -6119,16 +6119,16 @@
         <v>7317456560</v>
       </c>
       <c r="D187" s="1">
-        <v>5742974420</v>
+        <v>5880749420</v>
       </c>
       <c r="E187" s="1">
         <v>1212495000</v>
       </c>
       <c r="F187" s="1">
-        <v>6955469420</v>
+        <v>7093244420</v>
       </c>
       <c r="G187" s="1">
-        <v>361987140</v>
+        <v>224212140</v>
       </c>
       <c r="H187" s="1">
         <v>0</v>
@@ -6301,16 +6301,16 @@
         <v>455000000</v>
       </c>
       <c r="D194" s="1">
-        <v>0</v>
+        <v>177662833</v>
       </c>
       <c r="E194" s="1">
         <v>5081445</v>
       </c>
       <c r="F194" s="1">
-        <v>5081445</v>
+        <v>182744278</v>
       </c>
       <c r="G194" s="1">
-        <v>449918555</v>
+        <v>272255722</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
@@ -6405,16 +6405,16 @@
         <v>1862650000</v>
       </c>
       <c r="D198" s="1">
-        <v>298895308</v>
+        <v>231743141</v>
       </c>
       <c r="E198" s="1">
-        <v>1108749065</v>
+        <v>1211363232</v>
       </c>
       <c r="F198" s="1">
-        <v>1407644373</v>
+        <v>1443106373</v>
       </c>
       <c r="G198" s="1">
-        <v>455005627</v>
+        <v>419543627</v>
       </c>
       <c r="H198" s="1">
         <v>0</v>
@@ -6431,10 +6431,10 @@
         <v>281000000</v>
       </c>
       <c r="D199" s="1">
-        <v>23458860</v>
+        <v>0</v>
       </c>
       <c r="E199" s="1">
-        <v>30944688</v>
+        <v>54403548</v>
       </c>
       <c r="F199" s="1">
         <v>54403548</v>
@@ -6483,10 +6483,10 @@
         <v>50000000</v>
       </c>
       <c r="D201" s="1">
-        <v>18922000</v>
+        <v>6000000</v>
       </c>
       <c r="E201" s="1">
-        <v>29582400</v>
+        <v>42504400</v>
       </c>
       <c r="F201" s="1">
         <v>48504400</v>
@@ -6509,16 +6509,16 @@
         <v>4350172680</v>
       </c>
       <c r="D202" s="1">
-        <v>3110710000</v>
+        <v>3139710000</v>
       </c>
       <c r="E202" s="1">
         <v>1207281200</v>
       </c>
       <c r="F202" s="1">
-        <v>4317991200</v>
+        <v>4346991200</v>
       </c>
       <c r="G202" s="1">
-        <v>32181480</v>
+        <v>3181480</v>
       </c>
       <c r="H202" s="1">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>40000000</v>
       </c>
       <c r="D203" s="1">
-        <v>6535000</v>
+        <v>0</v>
       </c>
       <c r="E203" s="1">
-        <v>6475000</v>
+        <v>13010000</v>
       </c>
       <c r="F203" s="1">
         <v>13010000</v>
@@ -6561,16 +6561,16 @@
         <v>100000000</v>
       </c>
       <c r="D204" s="1">
-        <v>0</v>
+        <v>81904680</v>
       </c>
       <c r="E204" s="1">
         <v>0</v>
       </c>
       <c r="F204" s="1">
-        <v>0</v>
+        <v>81904680</v>
       </c>
       <c r="G204" s="1">
-        <v>100000000</v>
+        <v>18095320</v>
       </c>
       <c r="H204" s="1">
         <v>0</v>
@@ -6587,16 +6587,16 @@
         <v>509000000</v>
       </c>
       <c r="D205" s="1">
-        <v>0</v>
+        <v>417794208</v>
       </c>
       <c r="E205" s="1">
         <v>64227787</v>
       </c>
       <c r="F205" s="1">
-        <v>64227787</v>
+        <v>482021995</v>
       </c>
       <c r="G205" s="1">
-        <v>444772213</v>
+        <v>26978005</v>
       </c>
       <c r="H205" s="1">
         <v>0</v>
@@ -6717,10 +6717,10 @@
         <v>385534500</v>
       </c>
       <c r="D210" s="1">
-        <v>115441000</v>
+        <v>89208500</v>
       </c>
       <c r="E210" s="1">
-        <v>163042000</v>
+        <v>189274500</v>
       </c>
       <c r="F210" s="1">
         <v>278483000</v>
@@ -6769,16 +6769,16 @@
         <v>337500000</v>
       </c>
       <c r="D212" s="1">
-        <v>34133500</v>
+        <v>32112390</v>
       </c>
       <c r="E212" s="1">
-        <v>95600954</v>
+        <v>103870954</v>
       </c>
       <c r="F212" s="1">
-        <v>129734454</v>
+        <v>135983344</v>
       </c>
       <c r="G212" s="1">
-        <v>207765546</v>
+        <v>201516656</v>
       </c>
       <c r="H212" s="1">
         <v>112500000</v>
@@ -6824,13 +6824,13 @@
         <v>0</v>
       </c>
       <c r="E214" s="1">
-        <v>145209500</v>
+        <v>146534500</v>
       </c>
       <c r="F214" s="1">
-        <v>145209500</v>
+        <v>146534500</v>
       </c>
       <c r="G214" s="1">
-        <v>43790500</v>
+        <v>42465500</v>
       </c>
       <c r="H214" s="1">
         <v>63000000</v>
@@ -6847,16 +6847,16 @@
         <v>18000000</v>
       </c>
       <c r="D215" s="1">
-        <v>3590000</v>
+        <v>1795000</v>
       </c>
       <c r="E215" s="1">
-        <v>6888508</v>
+        <v>7935118</v>
       </c>
       <c r="F215" s="1">
-        <v>10478508</v>
+        <v>9730118</v>
       </c>
       <c r="G215" s="1">
-        <v>7521492</v>
+        <v>8269882</v>
       </c>
       <c r="H215" s="1">
         <v>0</v>
@@ -6902,13 +6902,13 @@
         <v>0</v>
       </c>
       <c r="E217" s="1">
-        <v>4665211548</v>
+        <v>6347204203</v>
       </c>
       <c r="F217" s="1">
-        <v>4665211548</v>
+        <v>6347204203</v>
       </c>
       <c r="G217" s="1">
-        <v>5157950578</v>
+        <v>3475957923</v>
       </c>
       <c r="H217" s="1">
         <v>0</v>
@@ -6928,13 +6928,13 @@
         <v>0</v>
       </c>
       <c r="E218" s="1">
-        <v>117978898</v>
+        <v>136976378</v>
       </c>
       <c r="F218" s="1">
-        <v>117978898</v>
+        <v>136976378</v>
       </c>
       <c r="G218" s="1">
-        <v>135278073</v>
+        <v>116280593</v>
       </c>
       <c r="H218" s="1">
         <v>0</v>
@@ -6954,13 +6954,13 @@
         <v>0</v>
       </c>
       <c r="E219" s="1">
-        <v>7548442692</v>
+        <v>7882790192</v>
       </c>
       <c r="F219" s="1">
-        <v>7548442692</v>
+        <v>7882790192</v>
       </c>
       <c r="G219" s="1">
-        <v>1697232680</v>
+        <v>1362885180</v>
       </c>
       <c r="H219" s="1">
         <v>0</v>
@@ -7006,13 +7006,13 @@
         <v>0</v>
       </c>
       <c r="E221" s="1">
-        <v>460918581</v>
+        <v>661241519</v>
       </c>
       <c r="F221" s="1">
-        <v>460918581</v>
+        <v>661241519</v>
       </c>
       <c r="G221" s="1">
-        <v>250743488</v>
+        <v>50420550</v>
       </c>
       <c r="H221" s="1">
         <v>0</v>
@@ -7032,13 +7032,13 @@
         <v>0</v>
       </c>
       <c r="E222" s="1">
-        <v>19224063</v>
+        <v>22429321</v>
       </c>
       <c r="F222" s="1">
-        <v>19224063</v>
+        <v>22429321</v>
       </c>
       <c r="G222" s="1">
-        <v>5478399</v>
+        <v>2273141</v>
       </c>
       <c r="H222" s="1">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         <v>0</v>
       </c>
       <c r="E223" s="1">
-        <v>916381476</v>
+        <v>972776476</v>
       </c>
       <c r="F223" s="1">
-        <v>916381476</v>
+        <v>972776476</v>
       </c>
       <c r="G223" s="1">
-        <v>-91215543</v>
+        <v>-147610543</v>
       </c>
       <c r="H223" s="1">
         <v>0</v>
@@ -7107,16 +7107,16 @@
         <v>47499233545</v>
       </c>
       <c r="D225" s="1">
-        <v>13488047051</v>
+        <v>14192067135</v>
       </c>
       <c r="E225" s="1">
-        <v>20904249077</v>
+        <v>23381914045</v>
       </c>
       <c r="F225" s="1">
-        <v>34392296128</v>
+        <v>37573981180</v>
       </c>
       <c r="G225" s="1">
-        <v>13106937417</v>
+        <v>9925252365</v>
       </c>
       <c r="H225" s="1">
         <v>415261500</v>
@@ -7159,16 +7159,16 @@
         <v>1126306000</v>
       </c>
       <c r="D227" s="1">
-        <v>612235000</v>
+        <v>1084360853</v>
       </c>
       <c r="E227" s="1">
         <v>8751007</v>
       </c>
       <c r="F227" s="1">
-        <v>620986007</v>
+        <v>1093111860</v>
       </c>
       <c r="G227" s="1">
-        <v>505319993</v>
+        <v>33194140</v>
       </c>
       <c r="H227" s="1">
         <v>0</v>
@@ -7185,10 +7185,10 @@
         <v>100000000</v>
       </c>
       <c r="D228" s="1">
+        <v>0</v>
+      </c>
+      <c r="E228" s="1">
         <v>49998822</v>
-      </c>
-      <c r="E228" s="1">
-        <v>0</v>
       </c>
       <c r="F228" s="1">
         <v>49998822</v>
@@ -7263,16 +7263,16 @@
         <v>1310391000</v>
       </c>
       <c r="D231" s="1">
-        <v>780300579</v>
+        <v>761569037</v>
       </c>
       <c r="E231" s="1">
         <v>135761588</v>
       </c>
       <c r="F231" s="1">
-        <v>916062167</v>
+        <v>897330625</v>
       </c>
       <c r="G231" s="1">
-        <v>394328833</v>
+        <v>413060375</v>
       </c>
       <c r="H231" s="1">
         <v>0</v>
@@ -7289,16 +7289,16 @@
         <v>1380000000</v>
       </c>
       <c r="D232" s="1">
-        <v>61137000</v>
+        <v>64997000</v>
       </c>
       <c r="E232" s="1">
-        <v>936407467</v>
+        <v>946087467</v>
       </c>
       <c r="F232" s="1">
-        <v>997544467</v>
+        <v>1011084467</v>
       </c>
       <c r="G232" s="1">
-        <v>382455533</v>
+        <v>368915533</v>
       </c>
       <c r="H232" s="1">
         <v>0</v>
@@ -7393,16 +7393,16 @@
         <v>2264065000</v>
       </c>
       <c r="D236" s="1">
-        <v>1342600000</v>
+        <v>1528195000</v>
       </c>
       <c r="E236" s="1">
         <v>659562000</v>
       </c>
       <c r="F236" s="1">
-        <v>2002162000</v>
+        <v>2187757000</v>
       </c>
       <c r="G236" s="1">
-        <v>261903000</v>
+        <v>76308000</v>
       </c>
       <c r="H236" s="1">
         <v>0</v>
@@ -7549,16 +7549,16 @@
         <v>110162550</v>
       </c>
       <c r="D242" s="1">
-        <v>27360000</v>
+        <v>28110000</v>
       </c>
       <c r="E242" s="1">
         <v>46016000</v>
       </c>
       <c r="F242" s="1">
-        <v>73376000</v>
+        <v>74126000</v>
       </c>
       <c r="G242" s="1">
-        <v>36786550</v>
+        <v>36036550</v>
       </c>
       <c r="H242" s="1">
         <v>36720850</v>
@@ -7575,16 +7575,16 @@
         <v>354238500</v>
       </c>
       <c r="D243" s="1">
-        <v>53861500</v>
+        <v>64647000</v>
       </c>
       <c r="E243" s="1">
-        <v>237375400</v>
+        <v>252489400</v>
       </c>
       <c r="F243" s="1">
-        <v>291236900</v>
+        <v>317136400</v>
       </c>
       <c r="G243" s="1">
-        <v>63001600</v>
+        <v>37102100</v>
       </c>
       <c r="H243" s="1">
         <v>118079500</v>
@@ -7627,10 +7627,10 @@
         <v>732016185</v>
       </c>
       <c r="D245" s="1">
-        <v>11943000</v>
+        <v>7203000</v>
       </c>
       <c r="E245" s="1">
-        <v>711698820</v>
+        <v>716438820</v>
       </c>
       <c r="F245" s="1">
         <v>723641820</v>
@@ -7656,13 +7656,13 @@
         <v>0</v>
       </c>
       <c r="E246" s="1">
-        <v>123657000</v>
+        <v>124288250</v>
       </c>
       <c r="F246" s="1">
-        <v>123657000</v>
+        <v>124288250</v>
       </c>
       <c r="G246" s="1">
-        <v>78627000</v>
+        <v>77995750</v>
       </c>
       <c r="H246" s="1">
         <v>67428000</v>
@@ -7708,13 +7708,13 @@
         <v>0</v>
       </c>
       <c r="E248" s="1">
-        <v>4657536473</v>
+        <v>6265678102</v>
       </c>
       <c r="F248" s="1">
-        <v>4657536473</v>
+        <v>6265678102</v>
       </c>
       <c r="G248" s="1">
-        <v>5168419697</v>
+        <v>3560278068</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
@@ -7734,13 +7734,13 @@
         <v>0</v>
       </c>
       <c r="E249" s="1">
-        <v>245247184</v>
+        <v>286215848</v>
       </c>
       <c r="F249" s="1">
-        <v>245247184</v>
+        <v>286215848</v>
       </c>
       <c r="G249" s="1">
-        <v>224601394</v>
+        <v>183632730</v>
       </c>
       <c r="H249" s="1">
         <v>0</v>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="E250" s="1">
-        <v>7317275702</v>
+        <v>7655958202</v>
       </c>
       <c r="F250" s="1">
-        <v>7317275702</v>
+        <v>7655958202</v>
       </c>
       <c r="G250" s="1">
-        <v>2194830215</v>
+        <v>1856147715</v>
       </c>
       <c r="H250" s="1">
         <v>0</v>
@@ -7812,13 +7812,13 @@
         <v>0</v>
       </c>
       <c r="E252" s="1">
-        <v>498616367</v>
+        <v>712073752</v>
       </c>
       <c r="F252" s="1">
-        <v>498616367</v>
+        <v>712073752</v>
       </c>
       <c r="G252" s="1">
-        <v>496326194</v>
+        <v>282868809</v>
       </c>
       <c r="H252" s="1">
         <v>0</v>
@@ -7838,13 +7838,13 @@
         <v>0</v>
       </c>
       <c r="E253" s="1">
-        <v>20745071</v>
+        <v>24220591</v>
       </c>
       <c r="F253" s="1">
-        <v>20745071</v>
+        <v>24220591</v>
       </c>
       <c r="G253" s="1">
-        <v>12793288</v>
+        <v>9317768</v>
       </c>
       <c r="H253" s="1">
         <v>0</v>
@@ -7864,13 +7864,13 @@
         <v>0</v>
       </c>
       <c r="E254" s="1">
-        <v>941269593</v>
+        <v>999064593</v>
       </c>
       <c r="F254" s="1">
-        <v>941269593</v>
+        <v>999064593</v>
       </c>
       <c r="G254" s="1">
-        <v>158457741</v>
+        <v>100662741</v>
       </c>
       <c r="H254" s="1">
         <v>0</v>
@@ -7939,16 +7939,16 @@
         <v>48914772555</v>
       </c>
       <c r="D257" s="1">
-        <v>13981435891</v>
+        <v>14581081880</v>
       </c>
       <c r="E257" s="1">
-        <v>20892376265</v>
+        <v>23235061035</v>
       </c>
       <c r="F257" s="1">
-        <v>34873812156</v>
+        <v>37816142915</v>
       </c>
       <c r="G257" s="1">
-        <v>14040960399</v>
+        <v>11098629640</v>
       </c>
       <c r="H257" s="1">
         <v>525212165</v>
@@ -8069,16 +8069,16 @@
         <v>875000000</v>
       </c>
       <c r="D262" s="1">
-        <v>584811986</v>
+        <v>427164315</v>
       </c>
       <c r="E262" s="1">
-        <v>117703736</v>
+        <v>182953936</v>
       </c>
       <c r="F262" s="1">
-        <v>702515722</v>
+        <v>610118251</v>
       </c>
       <c r="G262" s="1">
-        <v>172484278</v>
+        <v>264881749</v>
       </c>
       <c r="H262" s="1">
         <v>0</v>
@@ -8147,16 +8147,16 @@
         <v>1700000000</v>
       </c>
       <c r="D265" s="1">
-        <v>588151541</v>
+        <v>564695250</v>
       </c>
       <c r="E265" s="1">
-        <v>672190255</v>
+        <v>695612755</v>
       </c>
       <c r="F265" s="1">
-        <v>1260341796</v>
+        <v>1260308005</v>
       </c>
       <c r="G265" s="1">
-        <v>439658204</v>
+        <v>439691995</v>
       </c>
       <c r="H265" s="1">
         <v>0</v>
@@ -8225,10 +8225,10 @@
         <v>150000000</v>
       </c>
       <c r="D268" s="1">
-        <v>23232180</v>
+        <v>0</v>
       </c>
       <c r="E268" s="1">
-        <v>23750000</v>
+        <v>46982180</v>
       </c>
       <c r="F268" s="1">
         <v>46982180</v>
@@ -8381,16 +8381,16 @@
         <v>2260000000</v>
       </c>
       <c r="D274" s="1">
-        <v>851491169</v>
+        <v>1517918816</v>
       </c>
       <c r="E274" s="1">
-        <v>533723900</v>
+        <v>553698340</v>
       </c>
       <c r="F274" s="1">
-        <v>1385215069</v>
+        <v>2071617156</v>
       </c>
       <c r="G274" s="1">
-        <v>874784931</v>
+        <v>188382844</v>
       </c>
       <c r="H274" s="1">
         <v>0</v>
@@ -8459,10 +8459,10 @@
         <v>1242000000</v>
       </c>
       <c r="D277" s="1">
-        <v>959687225</v>
+        <v>922639865</v>
       </c>
       <c r="E277" s="1">
-        <v>9999583</v>
+        <v>47046943</v>
       </c>
       <c r="F277" s="1">
         <v>969686808</v>
@@ -8641,10 +8641,10 @@
         <v>707202000</v>
       </c>
       <c r="D284" s="1">
-        <v>280916000</v>
+        <v>276882000</v>
       </c>
       <c r="E284" s="1">
-        <v>110213811</v>
+        <v>114247811</v>
       </c>
       <c r="F284" s="1">
         <v>391129811</v>
@@ -8670,13 +8670,13 @@
         <v>0</v>
       </c>
       <c r="E285" s="1">
-        <v>181159750</v>
+        <v>182584750</v>
       </c>
       <c r="F285" s="1">
-        <v>181159750</v>
+        <v>182584750</v>
       </c>
       <c r="G285" s="1">
-        <v>22314500</v>
+        <v>20889500</v>
       </c>
       <c r="H285" s="1">
         <v>67824750</v>
@@ -8774,13 +8774,13 @@
         <v>0</v>
       </c>
       <c r="E289" s="1">
-        <v>5967233118</v>
+        <v>8030973538</v>
       </c>
       <c r="F289" s="1">
-        <v>5967233118</v>
+        <v>8030973538</v>
       </c>
       <c r="G289" s="1">
-        <v>6655385809</v>
+        <v>4591645389</v>
       </c>
       <c r="H289" s="1">
         <v>0</v>
@@ -8800,13 +8800,13 @@
         <v>0</v>
       </c>
       <c r="E290" s="1">
-        <v>88540595</v>
+        <v>102928278</v>
       </c>
       <c r="F290" s="1">
-        <v>88540595</v>
+        <v>102928278</v>
       </c>
       <c r="G290" s="1">
-        <v>106507697</v>
+        <v>92120014</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
@@ -8826,13 +8826,13 @@
         <v>0</v>
       </c>
       <c r="E291" s="1">
-        <v>9814509378</v>
+        <v>10269482878</v>
       </c>
       <c r="F291" s="1">
-        <v>9814509378</v>
+        <v>10269482878</v>
       </c>
       <c r="G291" s="1">
-        <v>3097208037</v>
+        <v>2642234537</v>
       </c>
       <c r="H291" s="1">
         <v>0</v>
@@ -8878,13 +8878,13 @@
         <v>0</v>
       </c>
       <c r="E293" s="1">
-        <v>540207690</v>
+        <v>785684826</v>
       </c>
       <c r="F293" s="1">
-        <v>540207690</v>
+        <v>785684826</v>
       </c>
       <c r="G293" s="1">
-        <v>720402965</v>
+        <v>474925829</v>
       </c>
       <c r="H293" s="1">
         <v>0</v>
@@ -8904,13 +8904,13 @@
         <v>0</v>
       </c>
       <c r="E294" s="1">
-        <v>13455196</v>
+        <v>15675701</v>
       </c>
       <c r="F294" s="1">
-        <v>13455196</v>
+        <v>15675701</v>
       </c>
       <c r="G294" s="1">
-        <v>14000605</v>
+        <v>11780100</v>
       </c>
       <c r="H294" s="1">
         <v>0</v>
@@ -8930,13 +8930,13 @@
         <v>0</v>
       </c>
       <c r="E295" s="1">
-        <v>1134812162</v>
+        <v>1208802162</v>
       </c>
       <c r="F295" s="1">
-        <v>1134812162</v>
+        <v>1208802162</v>
       </c>
       <c r="G295" s="1">
-        <v>425516675</v>
+        <v>351526675</v>
       </c>
       <c r="H295" s="1">
         <v>0</v>
@@ -8979,16 +8979,16 @@
         <v>63706784713</v>
       </c>
       <c r="D297" s="1">
-        <v>15876528004</v>
+        <v>16297538149</v>
       </c>
       <c r="E297" s="1">
-        <v>27769208957</v>
+        <v>30798383881</v>
       </c>
       <c r="F297" s="1">
-        <v>43645736961</v>
+        <v>47095922030</v>
       </c>
       <c r="G297" s="1">
-        <v>20061047752</v>
+        <v>16610862683</v>
       </c>
       <c r="H297" s="1">
         <v>531045413</v>
@@ -9109,16 +9109,16 @@
         <v>298750000</v>
       </c>
       <c r="D302" s="1">
-        <v>30579244</v>
+        <v>232802244</v>
       </c>
       <c r="E302" s="1">
         <v>35247626</v>
       </c>
       <c r="F302" s="1">
-        <v>65826870</v>
+        <v>268049870</v>
       </c>
       <c r="G302" s="1">
-        <v>232923130</v>
+        <v>30700130</v>
       </c>
       <c r="H302" s="1">
         <v>0</v>
@@ -9135,16 +9135,16 @@
         <v>193000000</v>
       </c>
       <c r="D303" s="1">
-        <v>122716000</v>
+        <v>192716000</v>
       </c>
       <c r="E303" s="1">
         <v>0</v>
       </c>
       <c r="F303" s="1">
-        <v>122716000</v>
+        <v>192716000</v>
       </c>
       <c r="G303" s="1">
-        <v>70284000</v>
+        <v>284000</v>
       </c>
       <c r="H303" s="1">
         <v>0</v>
@@ -9161,16 +9161,16 @@
         <v>1222108000</v>
       </c>
       <c r="D304" s="1">
-        <v>0</v>
+        <v>155450000</v>
       </c>
       <c r="E304" s="1">
         <v>1066657271</v>
       </c>
       <c r="F304" s="1">
-        <v>1066657271</v>
+        <v>1222107271</v>
       </c>
       <c r="G304" s="1">
-        <v>155450729</v>
+        <v>729</v>
       </c>
       <c r="H304" s="1">
         <v>0</v>
@@ -9213,16 +9213,16 @@
         <v>145000000</v>
       </c>
       <c r="D306" s="1">
-        <v>0</v>
+        <v>114740165</v>
       </c>
       <c r="E306" s="1">
         <v>30259835</v>
       </c>
       <c r="F306" s="1">
-        <v>30259835</v>
+        <v>145000000</v>
       </c>
       <c r="G306" s="1">
-        <v>114740165</v>
+        <v>0</v>
       </c>
       <c r="H306" s="1">
         <v>0</v>
@@ -9239,16 +9239,16 @@
         <v>174000000</v>
       </c>
       <c r="D307" s="1">
-        <v>12784969</v>
+        <v>129869969</v>
       </c>
       <c r="E307" s="1">
         <v>44129340</v>
       </c>
       <c r="F307" s="1">
-        <v>56914309</v>
+        <v>173999309</v>
       </c>
       <c r="G307" s="1">
-        <v>117085691</v>
+        <v>691</v>
       </c>
       <c r="H307" s="1">
         <v>0</v>
@@ -9291,16 +9291,16 @@
         <v>1882400000</v>
       </c>
       <c r="D309" s="1">
-        <v>25120000</v>
+        <v>174690000</v>
       </c>
       <c r="E309" s="1">
         <v>1707705000</v>
       </c>
       <c r="F309" s="1">
-        <v>1732825000</v>
+        <v>1882395000</v>
       </c>
       <c r="G309" s="1">
-        <v>149575000</v>
+        <v>5000</v>
       </c>
       <c r="H309" s="1">
         <v>0</v>
@@ -9317,16 +9317,16 @@
         <v>300000000</v>
       </c>
       <c r="D310" s="1">
-        <v>0</v>
+        <v>272645000</v>
       </c>
       <c r="E310" s="1">
         <v>27352000</v>
       </c>
       <c r="F310" s="1">
-        <v>27352000</v>
+        <v>299997000</v>
       </c>
       <c r="G310" s="1">
-        <v>272648000</v>
+        <v>3000</v>
       </c>
       <c r="H310" s="1">
         <v>0</v>
@@ -9473,16 +9473,16 @@
         <v>64614000</v>
       </c>
       <c r="D316" s="1">
-        <v>23200300</v>
+        <v>24245600</v>
       </c>
       <c r="E316" s="1">
         <v>19017971</v>
       </c>
       <c r="F316" s="1">
-        <v>42218271</v>
+        <v>43263571</v>
       </c>
       <c r="G316" s="1">
-        <v>22395729</v>
+        <v>21350429</v>
       </c>
       <c r="H316" s="1">
         <v>21538000</v>
@@ -9499,16 +9499,16 @@
         <v>82504500</v>
       </c>
       <c r="D317" s="1">
-        <v>12506000</v>
+        <v>19356000</v>
       </c>
       <c r="E317" s="1">
         <v>42167500</v>
       </c>
       <c r="F317" s="1">
-        <v>54673500</v>
+        <v>61523500</v>
       </c>
       <c r="G317" s="1">
-        <v>27831000</v>
+        <v>20981000</v>
       </c>
       <c r="H317" s="1">
         <v>27501500</v>
@@ -9551,16 +9551,16 @@
         <v>385800000</v>
       </c>
       <c r="D319" s="1">
-        <v>42272000</v>
+        <v>43815000</v>
       </c>
       <c r="E319" s="1">
         <v>76374635</v>
       </c>
       <c r="F319" s="1">
-        <v>118646635</v>
+        <v>120189635</v>
       </c>
       <c r="G319" s="1">
-        <v>267153365</v>
+        <v>265610365</v>
       </c>
       <c r="H319" s="1">
         <v>128600000</v>
@@ -9580,13 +9580,13 @@
         <v>0</v>
       </c>
       <c r="E320" s="1">
-        <v>89567500</v>
+        <v>112313250</v>
       </c>
       <c r="F320" s="1">
-        <v>89567500</v>
+        <v>112313250</v>
       </c>
       <c r="G320" s="1">
-        <v>82932500</v>
+        <v>60186750</v>
       </c>
       <c r="H320" s="1">
         <v>57500000</v>
@@ -9632,13 +9632,13 @@
         <v>0</v>
       </c>
       <c r="E322" s="1">
-        <v>3258677480</v>
+        <v>4437742748</v>
       </c>
       <c r="F322" s="1">
-        <v>3258677480</v>
+        <v>4437742748</v>
       </c>
       <c r="G322" s="1">
-        <v>3795114785</v>
+        <v>2616049517</v>
       </c>
       <c r="H322" s="1">
         <v>0</v>
@@ -9658,13 +9658,13 @@
         <v>0</v>
       </c>
       <c r="E323" s="1">
-        <v>124515685</v>
+        <v>145297394</v>
       </c>
       <c r="F323" s="1">
-        <v>124515685</v>
+        <v>145297394</v>
       </c>
       <c r="G323" s="1">
-        <v>126386224</v>
+        <v>105604515</v>
       </c>
       <c r="H323" s="1">
         <v>0</v>
@@ -9684,13 +9684,13 @@
         <v>0</v>
       </c>
       <c r="E324" s="1">
-        <v>5338624178</v>
+        <v>5599769178</v>
       </c>
       <c r="F324" s="1">
-        <v>5338624178</v>
+        <v>5599769178</v>
       </c>
       <c r="G324" s="1">
-        <v>1676418243</v>
+        <v>1415273243</v>
       </c>
       <c r="H324" s="1">
         <v>0</v>
@@ -9736,13 +9736,13 @@
         <v>0</v>
       </c>
       <c r="E326" s="1">
-        <v>525161905</v>
+        <v>749151645</v>
       </c>
       <c r="F326" s="1">
-        <v>525161905</v>
+        <v>749151645</v>
       </c>
       <c r="G326" s="1">
-        <v>706050161</v>
+        <v>482060421</v>
       </c>
       <c r="H326" s="1">
         <v>0</v>
@@ -9762,13 +9762,13 @@
         <v>0</v>
       </c>
       <c r="E327" s="1">
-        <v>32168573</v>
+        <v>37523444</v>
       </c>
       <c r="F327" s="1">
-        <v>32168573</v>
+        <v>37523444</v>
       </c>
       <c r="G327" s="1">
-        <v>21267546</v>
+        <v>15912675</v>
       </c>
       <c r="H327" s="1">
         <v>0</v>
@@ -9788,13 +9788,13 @@
         <v>0</v>
       </c>
       <c r="E328" s="1">
-        <v>1022173460</v>
+        <v>1082880960</v>
       </c>
       <c r="F328" s="1">
-        <v>1022173460</v>
+        <v>1082880960</v>
       </c>
       <c r="G328" s="1">
-        <v>427538919</v>
+        <v>366831419</v>
       </c>
       <c r="H328" s="1">
         <v>0</v>
@@ -9837,16 +9837,16 @@
         <v>30454436960</v>
       </c>
       <c r="D330" s="1">
-        <v>2576505585</v>
+        <v>3667657050</v>
       </c>
       <c r="E330" s="1">
-        <v>17690651772</v>
+        <v>19464441610</v>
       </c>
       <c r="F330" s="1">
-        <v>20267157357</v>
+        <v>23132098660</v>
       </c>
       <c r="G330" s="1">
-        <v>10187279603</v>
+        <v>7322338300</v>
       </c>
       <c r="H330" s="1">
         <v>260139500</v>
@@ -9941,16 +9941,16 @@
         <v>2593734264</v>
       </c>
       <c r="D334" s="1">
-        <v>925070052</v>
+        <v>1145566052</v>
       </c>
       <c r="E334" s="1">
         <v>1405666314</v>
       </c>
       <c r="F334" s="1">
-        <v>2330736366</v>
+        <v>2551232366</v>
       </c>
       <c r="G334" s="1">
-        <v>262997898</v>
+        <v>42501898</v>
       </c>
       <c r="H334" s="1">
         <v>0</v>
@@ -10045,16 +10045,16 @@
         <v>1748195004</v>
       </c>
       <c r="D338" s="1">
-        <v>275446897</v>
+        <v>325116897</v>
       </c>
       <c r="E338" s="1">
         <v>1012207888</v>
       </c>
       <c r="F338" s="1">
-        <v>1287654785</v>
+        <v>1337324785</v>
       </c>
       <c r="G338" s="1">
-        <v>460540219</v>
+        <v>410870219</v>
       </c>
       <c r="H338" s="1">
         <v>0</v>
@@ -10227,10 +10227,10 @@
         <v>141550000</v>
       </c>
       <c r="D345" s="1">
-        <v>49022800</v>
+        <v>0</v>
       </c>
       <c r="E345" s="1">
-        <v>31377000</v>
+        <v>80399800</v>
       </c>
       <c r="F345" s="1">
         <v>80399800</v>
@@ -10279,10 +10279,10 @@
         <v>135000000</v>
       </c>
       <c r="D347" s="1">
-        <v>21249098</v>
+        <v>14991898</v>
       </c>
       <c r="E347" s="1">
-        <v>58037500</v>
+        <v>64294700</v>
       </c>
       <c r="F347" s="1">
         <v>79286598</v>
@@ -10386,13 +10386,13 @@
         <v>0</v>
       </c>
       <c r="E351" s="1">
-        <v>145523500</v>
+        <v>147286000</v>
       </c>
       <c r="F351" s="1">
-        <v>145523500</v>
+        <v>147286000</v>
       </c>
       <c r="G351" s="1">
-        <v>115026500</v>
+        <v>113264000</v>
       </c>
       <c r="H351" s="1">
         <v>86850000</v>
@@ -10409,10 +10409,10 @@
         <v>6000000</v>
       </c>
       <c r="D352" s="1">
-        <v>628830</v>
+        <v>268575</v>
       </c>
       <c r="E352" s="1">
-        <v>871340</v>
+        <v>1231595</v>
       </c>
       <c r="F352" s="1">
         <v>1500170</v>
@@ -10464,13 +10464,13 @@
         <v>0</v>
       </c>
       <c r="E354" s="1">
-        <v>4967444319</v>
+        <v>6701681878</v>
       </c>
       <c r="F354" s="1">
-        <v>4967444319</v>
+        <v>6701681878</v>
       </c>
       <c r="G354" s="1">
-        <v>5747471694</v>
+        <v>4013234135</v>
       </c>
       <c r="H354" s="1">
         <v>0</v>
@@ -10490,13 +10490,13 @@
         <v>0</v>
       </c>
       <c r="E355" s="1">
-        <v>134045088</v>
+        <v>156117929</v>
       </c>
       <c r="F355" s="1">
-        <v>134045088</v>
+        <v>156117929</v>
       </c>
       <c r="G355" s="1">
-        <v>141775344</v>
+        <v>119702503</v>
       </c>
       <c r="H355" s="1">
         <v>0</v>
@@ -10516,13 +10516,13 @@
         <v>0</v>
       </c>
       <c r="E356" s="1">
-        <v>8068579974</v>
+        <v>8438952474</v>
       </c>
       <c r="F356" s="1">
-        <v>8068579974</v>
+        <v>8438952474</v>
       </c>
       <c r="G356" s="1">
-        <v>2463584228</v>
+        <v>2093211728</v>
       </c>
       <c r="H356" s="1">
         <v>0</v>
@@ -10568,13 +10568,13 @@
         <v>0</v>
       </c>
       <c r="E358" s="1">
-        <v>541081421</v>
+        <v>785700027</v>
       </c>
       <c r="F358" s="1">
-        <v>541081421</v>
+        <v>785700027</v>
       </c>
       <c r="G358" s="1">
-        <v>750513224</v>
+        <v>505894618</v>
       </c>
       <c r="H358" s="1">
         <v>0</v>
@@ -10594,13 +10594,13 @@
         <v>0</v>
       </c>
       <c r="E359" s="1">
-        <v>23380812</v>
+        <v>27277614</v>
       </c>
       <c r="F359" s="1">
-        <v>23380812</v>
+        <v>27277614</v>
       </c>
       <c r="G359" s="1">
-        <v>24029934</v>
+        <v>20133132</v>
       </c>
       <c r="H359" s="1">
         <v>0</v>
@@ -10620,13 +10620,13 @@
         <v>0</v>
       </c>
       <c r="E360" s="1">
-        <v>1101129909</v>
+        <v>1168247409</v>
       </c>
       <c r="F360" s="1">
-        <v>1101129909</v>
+        <v>1168247409</v>
       </c>
       <c r="G360" s="1">
-        <v>421888195</v>
+        <v>354770695</v>
       </c>
       <c r="H360" s="1">
         <v>0</v>
@@ -10669,16 +10669,16 @@
         <v>57427089299</v>
       </c>
       <c r="D362" s="1">
-        <v>9773301146</v>
+        <v>9987826891</v>
       </c>
       <c r="E362" s="1">
-        <v>33917143793</v>
+        <v>36416862356</v>
       </c>
       <c r="F362" s="1">
-        <v>43690444939</v>
+        <v>46404689247</v>
       </c>
       <c r="G362" s="1">
-        <v>13736644360</v>
+        <v>11022400052</v>
       </c>
       <c r="H362" s="1">
         <v>526334925</v>
@@ -10799,10 +10799,10 @@
         <v>149777000</v>
       </c>
       <c r="D367" s="1">
-        <v>47765611</v>
+        <v>0</v>
       </c>
       <c r="E367" s="1">
-        <v>99744921</v>
+        <v>147510532</v>
       </c>
       <c r="F367" s="1">
         <v>147510532</v>
@@ -10877,16 +10877,16 @@
         <v>1400000000</v>
       </c>
       <c r="D370" s="1">
-        <v>159090844</v>
+        <v>249706844</v>
       </c>
       <c r="E370" s="1">
         <v>380974750</v>
       </c>
       <c r="F370" s="1">
-        <v>540065594</v>
+        <v>630681594</v>
       </c>
       <c r="G370" s="1">
-        <v>859934406</v>
+        <v>769318406</v>
       </c>
       <c r="H370" s="1">
         <v>0</v>
@@ -10903,16 +10903,16 @@
         <v>290550000</v>
       </c>
       <c r="D371" s="1">
-        <v>0</v>
+        <v>290377764</v>
       </c>
       <c r="E371" s="1">
         <v>0</v>
       </c>
       <c r="F371" s="1">
-        <v>0</v>
+        <v>290377764</v>
       </c>
       <c r="G371" s="1">
-        <v>290550000</v>
+        <v>172236</v>
       </c>
       <c r="H371" s="1">
         <v>0</v>
@@ -10981,10 +10981,10 @@
         <v>200000000</v>
       </c>
       <c r="D374" s="1">
-        <v>199999500</v>
+        <v>150079500</v>
       </c>
       <c r="E374" s="1">
-        <v>0</v>
+        <v>49920000</v>
       </c>
       <c r="F374" s="1">
         <v>199999500</v>
@@ -11059,10 +11059,10 @@
         <v>411080000</v>
       </c>
       <c r="D377" s="1">
-        <v>1827440</v>
+        <v>1337650</v>
       </c>
       <c r="E377" s="1">
-        <v>239847303</v>
+        <v>240337093</v>
       </c>
       <c r="F377" s="1">
         <v>241674743</v>
@@ -11192,13 +11192,13 @@
         <v>0</v>
       </c>
       <c r="E382" s="1">
-        <v>103360500</v>
+        <v>105335500</v>
       </c>
       <c r="F382" s="1">
-        <v>103360500</v>
+        <v>105335500</v>
       </c>
       <c r="G382" s="1">
-        <v>24664500</v>
+        <v>22689500</v>
       </c>
       <c r="H382" s="1">
         <v>42675000</v>
@@ -11296,13 +11296,13 @@
         <v>0</v>
       </c>
       <c r="E386" s="1">
-        <v>2150184235</v>
+        <v>2849172763</v>
       </c>
       <c r="F386" s="1">
-        <v>2150184235</v>
+        <v>2849172763</v>
       </c>
       <c r="G386" s="1">
-        <v>2389622683</v>
+        <v>1690634155</v>
       </c>
       <c r="H386" s="1">
         <v>0</v>
@@ -11322,13 +11322,13 @@
         <v>0</v>
       </c>
       <c r="E387" s="1">
-        <v>39195974</v>
+        <v>45075445</v>
       </c>
       <c r="F387" s="1">
-        <v>39195974</v>
+        <v>45075445</v>
       </c>
       <c r="G387" s="1">
-        <v>43858595</v>
+        <v>37979124</v>
       </c>
       <c r="H387" s="1">
         <v>0</v>
@@ -11348,13 +11348,13 @@
         <v>0</v>
       </c>
       <c r="E388" s="1">
-        <v>3368662147</v>
+        <v>3538827147</v>
       </c>
       <c r="F388" s="1">
-        <v>3368662147</v>
+        <v>3538827147</v>
       </c>
       <c r="G388" s="1">
-        <v>1300977455</v>
+        <v>1130812455</v>
       </c>
       <c r="H388" s="1">
         <v>0</v>
@@ -11400,13 +11400,13 @@
         <v>0</v>
       </c>
       <c r="E390" s="1">
-        <v>346298204</v>
+        <v>496709820</v>
       </c>
       <c r="F390" s="1">
-        <v>346298204</v>
+        <v>496709820</v>
       </c>
       <c r="G390" s="1">
-        <v>448815229</v>
+        <v>298403613</v>
       </c>
       <c r="H390" s="1">
         <v>0</v>
@@ -11426,13 +11426,13 @@
         <v>0</v>
       </c>
       <c r="E391" s="1">
-        <v>11910562</v>
+        <v>13903254</v>
       </c>
       <c r="F391" s="1">
-        <v>11910562</v>
+        <v>13903254</v>
       </c>
       <c r="G391" s="1">
-        <v>25583373</v>
+        <v>23590681</v>
       </c>
       <c r="H391" s="1">
         <v>0</v>
@@ -11452,13 +11452,13 @@
         <v>0</v>
       </c>
       <c r="E392" s="1">
-        <v>705293046</v>
+        <v>749223046</v>
       </c>
       <c r="F392" s="1">
-        <v>705293046</v>
+        <v>749223046</v>
       </c>
       <c r="G392" s="1">
-        <v>254940803</v>
+        <v>211010803</v>
       </c>
       <c r="H392" s="1">
         <v>0</v>
@@ -11501,16 +11501,16 @@
         <v>24628424376</v>
       </c>
       <c r="D394" s="1">
-        <v>3407445948</v>
+        <v>3690264311</v>
       </c>
       <c r="E394" s="1">
-        <v>13054814150</v>
+        <v>14226331858</v>
       </c>
       <c r="F394" s="1">
-        <v>16462260098</v>
+        <v>17916596169</v>
       </c>
       <c r="G394" s="1">
-        <v>8166164278</v>
+        <v>6711828207</v>
       </c>
       <c r="H394" s="1">
         <v>232675000</v>
@@ -11787,16 +11787,16 @@
         <v>50000000</v>
       </c>
       <c r="D405" s="1">
+        <v>11200000</v>
+      </c>
+      <c r="E405" s="1">
         <v>4900000</v>
       </c>
-      <c r="E405" s="1">
-        <v>0</v>
-      </c>
       <c r="F405" s="1">
-        <v>4900000</v>
+        <v>16100000</v>
       </c>
       <c r="G405" s="1">
-        <v>45100000</v>
+        <v>33900000</v>
       </c>
       <c r="H405" s="1">
         <v>0</v>
@@ -11943,16 +11943,16 @@
         <v>2230000000</v>
       </c>
       <c r="D411" s="1">
-        <v>19315000</v>
+        <v>28077420</v>
       </c>
       <c r="E411" s="1">
-        <v>874488459</v>
+        <v>874803459</v>
       </c>
       <c r="F411" s="1">
-        <v>893803459</v>
+        <v>902880879</v>
       </c>
       <c r="G411" s="1">
-        <v>1336196541</v>
+        <v>1327119121</v>
       </c>
       <c r="H411" s="1">
         <v>0</v>
@@ -11995,16 +11995,16 @@
         <v>445223250</v>
       </c>
       <c r="D413" s="1">
-        <v>73987437</v>
+        <v>97193700</v>
       </c>
       <c r="E413" s="1">
-        <v>324629350</v>
+        <v>341791216</v>
       </c>
       <c r="F413" s="1">
-        <v>398616787</v>
+        <v>438984916</v>
       </c>
       <c r="G413" s="1">
-        <v>46606463</v>
+        <v>6238334</v>
       </c>
       <c r="H413" s="1">
         <v>148407750</v>
@@ -12076,13 +12076,13 @@
         <v>29995500</v>
       </c>
       <c r="E416" s="1">
-        <v>269685091</v>
+        <v>270260091</v>
       </c>
       <c r="F416" s="1">
-        <v>299680591</v>
+        <v>300255591</v>
       </c>
       <c r="G416" s="1">
-        <v>71314909</v>
+        <v>70739909</v>
       </c>
       <c r="H416" s="1">
         <v>117000000</v>
@@ -12180,13 +12180,13 @@
         <v>0</v>
       </c>
       <c r="E420" s="1">
-        <v>4004719171</v>
+        <v>5289975251</v>
       </c>
       <c r="F420" s="1">
-        <v>4004719171</v>
+        <v>5289975251</v>
       </c>
       <c r="G420" s="1">
-        <v>4636626540</v>
+        <v>3351370460</v>
       </c>
       <c r="H420" s="1">
         <v>0</v>
@@ -12206,13 +12206,13 @@
         <v>0</v>
       </c>
       <c r="E421" s="1">
-        <v>23561040</v>
+        <v>26815861</v>
       </c>
       <c r="F421" s="1">
-        <v>23561040</v>
+        <v>26815861</v>
       </c>
       <c r="G421" s="1">
-        <v>27263039</v>
+        <v>24008218</v>
       </c>
       <c r="H421" s="1">
         <v>0</v>
@@ -12232,13 +12232,13 @@
         <v>0</v>
       </c>
       <c r="E422" s="1">
-        <v>6590831677</v>
+        <v>6893736677</v>
       </c>
       <c r="F422" s="1">
-        <v>6590831677</v>
+        <v>6893736677</v>
       </c>
       <c r="G422" s="1">
-        <v>2788736815</v>
+        <v>2485831815</v>
       </c>
       <c r="H422" s="1">
         <v>0</v>
@@ -12284,13 +12284,13 @@
         <v>0</v>
       </c>
       <c r="E424" s="1">
-        <v>351874951</v>
+        <v>510417643</v>
       </c>
       <c r="F424" s="1">
-        <v>351874951</v>
+        <v>510417643</v>
       </c>
       <c r="G424" s="1">
-        <v>552614695</v>
+        <v>394072003</v>
       </c>
       <c r="H424" s="1">
         <v>0</v>
@@ -12310,13 +12310,13 @@
         <v>0</v>
       </c>
       <c r="E425" s="1">
-        <v>11447067</v>
+        <v>13363987</v>
       </c>
       <c r="F425" s="1">
-        <v>11447067</v>
+        <v>13363987</v>
       </c>
       <c r="G425" s="1">
-        <v>11349529</v>
+        <v>9432609</v>
       </c>
       <c r="H425" s="1">
         <v>0</v>
@@ -12336,13 +12336,13 @@
         <v>0</v>
       </c>
       <c r="E426" s="1">
-        <v>758588632</v>
+        <v>808908632</v>
       </c>
       <c r="F426" s="1">
-        <v>758588632</v>
+        <v>808908632</v>
       </c>
       <c r="G426" s="1">
-        <v>347294815</v>
+        <v>296974815</v>
       </c>
       <c r="H426" s="1">
         <v>0</v>
@@ -12385,16 +12385,16 @@
         <v>35458361640</v>
       </c>
       <c r="D428" s="1">
-        <v>7419051437</v>
+        <v>7457320120</v>
       </c>
       <c r="E428" s="1">
-        <v>15975937382</v>
+        <v>17801084761</v>
       </c>
       <c r="F428" s="1">
-        <v>23394988819</v>
+        <v>25258404881</v>
       </c>
       <c r="G428" s="1">
-        <v>12063372821</v>
+        <v>10199956759</v>
       </c>
       <c r="H428" s="1">
         <v>472807750</v>
@@ -13298,16 +13298,16 @@
         <v>10505111000</v>
       </c>
       <c r="D485" s="1">
-        <v>3690138527</v>
+        <v>3672287927</v>
       </c>
       <c r="E485" s="1">
         <v>6807699047</v>
       </c>
       <c r="F485" s="1">
-        <v>10497837574</v>
+        <v>10479986974</v>
       </c>
       <c r="G485" s="1">
-        <v>7273426</v>
+        <v>25124026</v>
       </c>
       <c r="H485" s="1">
         <v>0</v>
@@ -13480,16 +13480,16 @@
         <v>2312795000</v>
       </c>
       <c r="D492" s="1">
-        <v>1244831850</v>
+        <v>1282815186</v>
       </c>
       <c r="E492" s="1">
         <v>564810618</v>
       </c>
       <c r="F492" s="1">
-        <v>1809642468</v>
+        <v>1847625804</v>
       </c>
       <c r="G492" s="1">
-        <v>503152532</v>
+        <v>465169196</v>
       </c>
       <c r="H492" s="1">
         <v>0</v>
@@ -13506,16 +13506,16 @@
         <v>4989900000</v>
       </c>
       <c r="D493" s="1">
-        <v>1014286725</v>
+        <v>1035950677</v>
       </c>
       <c r="E493" s="1">
         <v>1195602104</v>
       </c>
       <c r="F493" s="1">
-        <v>2209888829</v>
+        <v>2231552781</v>
       </c>
       <c r="G493" s="1">
-        <v>2780011171</v>
+        <v>2758347219</v>
       </c>
       <c r="H493" s="1">
         <v>0</v>
@@ -13610,16 +13610,16 @@
         <v>624500000</v>
       </c>
       <c r="D497" s="1">
-        <v>457025656</v>
+        <v>451541348</v>
       </c>
       <c r="E497" s="1">
         <v>0</v>
       </c>
       <c r="F497" s="1">
-        <v>457025656</v>
+        <v>451541348</v>
       </c>
       <c r="G497" s="1">
-        <v>167474344</v>
+        <v>172958652</v>
       </c>
       <c r="H497" s="1">
         <v>0</v>
@@ -13688,16 +13688,16 @@
         <v>745000000</v>
       </c>
       <c r="D500" s="1">
-        <v>683272388</v>
+        <v>679970734</v>
       </c>
       <c r="E500" s="1">
         <v>51881480</v>
       </c>
       <c r="F500" s="1">
-        <v>735153868</v>
+        <v>731852214</v>
       </c>
       <c r="G500" s="1">
-        <v>9846132</v>
+        <v>13147786</v>
       </c>
       <c r="H500" s="1">
         <v>0</v>
@@ -13714,16 +13714,16 @@
         <v>7401091133</v>
       </c>
       <c r="D501" s="1">
-        <v>4296192926</v>
+        <v>4569235826</v>
       </c>
       <c r="E501" s="1">
         <v>2552015067</v>
       </c>
       <c r="F501" s="1">
-        <v>6848207993</v>
+        <v>7121250893</v>
       </c>
       <c r="G501" s="1">
-        <v>552883140</v>
+        <v>279840240</v>
       </c>
       <c r="H501" s="1">
         <v>0</v>
@@ -13792,10 +13792,10 @@
         <v>1350000000</v>
       </c>
       <c r="D504" s="1">
-        <v>496191000</v>
+        <v>0</v>
       </c>
       <c r="E504" s="1">
-        <v>254916868</v>
+        <v>751107868</v>
       </c>
       <c r="F504" s="1">
         <v>751107868</v>
@@ -13844,16 +13844,16 @@
         <v>1016150000</v>
       </c>
       <c r="D506" s="1">
-        <v>39900000</v>
+        <v>60050000</v>
       </c>
       <c r="E506" s="1">
         <v>327400000</v>
       </c>
       <c r="F506" s="1">
-        <v>367300000</v>
+        <v>387450000</v>
       </c>
       <c r="G506" s="1">
-        <v>648850000</v>
+        <v>628700000</v>
       </c>
       <c r="H506" s="1">
         <v>0</v>
@@ -13873,13 +13873,13 @@
         <v>10404406</v>
       </c>
       <c r="E507" s="1">
-        <v>1457222870</v>
+        <v>1462801099</v>
       </c>
       <c r="F507" s="1">
-        <v>1467627276</v>
+        <v>1473205505</v>
       </c>
       <c r="G507" s="1">
-        <v>1092372724</v>
+        <v>1086794495</v>
       </c>
       <c r="H507" s="1">
         <v>0</v>
@@ -13896,10 +13896,10 @@
         <v>668379750</v>
       </c>
       <c r="D508" s="1">
-        <v>64146000</v>
+        <v>11185000</v>
       </c>
       <c r="E508" s="1">
-        <v>104089828</v>
+        <v>157050828</v>
       </c>
       <c r="F508" s="1">
         <v>168235828</v>
@@ -13922,10 +13922,10 @@
         <v>870341250</v>
       </c>
       <c r="D509" s="1">
-        <v>189276900</v>
+        <v>134830520</v>
       </c>
       <c r="E509" s="1">
-        <v>465198890</v>
+        <v>519645270</v>
       </c>
       <c r="F509" s="1">
         <v>654475790</v>
@@ -13974,16 +13974,16 @@
         <v>422192250</v>
       </c>
       <c r="D511" s="1">
-        <v>18367000</v>
+        <v>18886000</v>
       </c>
       <c r="E511" s="1">
-        <v>41733427</v>
+        <v>45923427</v>
       </c>
       <c r="F511" s="1">
-        <v>60100427</v>
+        <v>64809427</v>
       </c>
       <c r="G511" s="1">
-        <v>362091823</v>
+        <v>357382823</v>
       </c>
       <c r="H511" s="1">
         <v>140730750</v>
@@ -14000,16 +14000,16 @@
         <v>516433500</v>
       </c>
       <c r="D512" s="1">
-        <v>14085081</v>
+        <v>21701117</v>
       </c>
       <c r="E512" s="1">
-        <v>244420930</v>
+        <v>246597911</v>
       </c>
       <c r="F512" s="1">
-        <v>258506011</v>
+        <v>268299028</v>
       </c>
       <c r="G512" s="1">
-        <v>257927489</v>
+        <v>248134472</v>
       </c>
       <c r="H512" s="1">
         <v>172144500</v>
@@ -14026,10 +14026,10 @@
         <v>36180000</v>
       </c>
       <c r="D513" s="1">
-        <v>1720000</v>
+        <v>0</v>
       </c>
       <c r="E513" s="1">
-        <v>8658562</v>
+        <v>10378562</v>
       </c>
       <c r="F513" s="1">
         <v>10378562</v>
@@ -14052,16 +14052,16 @@
         <v>61741000</v>
       </c>
       <c r="D514" s="1">
-        <v>1300000</v>
+        <v>1950000</v>
       </c>
       <c r="E514" s="1">
         <v>38905444</v>
       </c>
       <c r="F514" s="1">
-        <v>40205444</v>
+        <v>40855444</v>
       </c>
       <c r="G514" s="1">
-        <v>21535556</v>
+        <v>20885556</v>
       </c>
       <c r="H514" s="1">
         <v>0</v>
@@ -14185,13 +14185,13 @@
         <v>0</v>
       </c>
       <c r="E519" s="1">
-        <v>5967890649</v>
+        <v>7900359380</v>
       </c>
       <c r="F519" s="1">
-        <v>5967890649</v>
+        <v>7900359380</v>
       </c>
       <c r="G519" s="1">
-        <v>6196391248</v>
+        <v>4263922517</v>
       </c>
       <c r="H519" s="1">
         <v>0</v>
@@ -14211,13 +14211,13 @@
         <v>0</v>
       </c>
       <c r="E520" s="1">
-        <v>55420594</v>
+        <v>64689881</v>
       </c>
       <c r="F520" s="1">
-        <v>55420594</v>
+        <v>64689881</v>
       </c>
       <c r="G520" s="1">
-        <v>56087605</v>
+        <v>46818318</v>
       </c>
       <c r="H520" s="1">
         <v>0</v>
@@ -14237,13 +14237,13 @@
         <v>0</v>
       </c>
       <c r="E521" s="1">
-        <v>8912760459</v>
+        <v>9288590459</v>
       </c>
       <c r="F521" s="1">
-        <v>8912760459</v>
+        <v>9288590459</v>
       </c>
       <c r="G521" s="1">
-        <v>1888643738</v>
+        <v>1512813738</v>
       </c>
       <c r="H521" s="1">
         <v>0</v>
@@ -14289,13 +14289,13 @@
         <v>0</v>
       </c>
       <c r="E523" s="1">
-        <v>553974458</v>
+        <v>837687932</v>
       </c>
       <c r="F523" s="1">
-        <v>553974458</v>
+        <v>837687932</v>
       </c>
       <c r="G523" s="1">
-        <v>898710781</v>
+        <v>614997307</v>
       </c>
       <c r="H523" s="1">
         <v>0</v>
@@ -14315,13 +14315,13 @@
         <v>0</v>
       </c>
       <c r="E524" s="1">
-        <v>15537750</v>
+        <v>18569241</v>
       </c>
       <c r="F524" s="1">
-        <v>15537750</v>
+        <v>18569241</v>
       </c>
       <c r="G524" s="1">
-        <v>19627648</v>
+        <v>16596157</v>
       </c>
       <c r="H524" s="1">
         <v>0</v>
@@ -14341,13 +14341,13 @@
         <v>0</v>
       </c>
       <c r="E525" s="1">
-        <v>1241566245</v>
+        <v>1319466245</v>
       </c>
       <c r="F525" s="1">
-        <v>1241566245</v>
+        <v>1319466245</v>
       </c>
       <c r="G525" s="1">
-        <v>457182256</v>
+        <v>379282256</v>
       </c>
       <c r="H525" s="1">
         <v>0</v>
@@ -14416,16 +14416,16 @@
         <v>64019485320</v>
       </c>
       <c r="D528" s="1">
-        <v>13432964007</v>
+        <v>13162634289</v>
       </c>
       <c r="E528" s="1">
-        <v>32586786639</v>
+        <v>35886263212</v>
       </c>
       <c r="F528" s="1">
-        <v>46019750646</v>
+        <v>49048897501</v>
       </c>
       <c r="G528" s="1">
-        <v>17999734674</v>
+        <v>14970587819</v>
       </c>
       <c r="H528" s="1">
         <v>850782250</v>
@@ -14436,10 +14436,10 @@
         <v>8</v>
       </c>
       <c r="B529" s="1">
-        <v>5574698000</v>
+        <v>5572131338</v>
       </c>
       <c r="C529" s="1">
-        <v>5574698000</v>
+        <v>5572131338</v>
       </c>
       <c r="D529" s="1">
         <v>3145457538</v>
@@ -14451,7 +14451,7 @@
         <v>5572131338</v>
       </c>
       <c r="G529" s="1">
-        <v>2566662</v>
+        <v>0</v>
       </c>
       <c r="H529" s="1">
         <v>0</v>
@@ -14462,10 +14462,10 @@
         <v>11</v>
       </c>
       <c r="B530" s="1">
-        <v>1521000000</v>
+        <v>1439636880</v>
       </c>
       <c r="C530" s="1">
-        <v>1521000000</v>
+        <v>1439636880</v>
       </c>
       <c r="D530" s="1">
         <v>1436308580</v>
@@ -14477,7 +14477,7 @@
         <v>1439636880</v>
       </c>
       <c r="G530" s="1">
-        <v>81363120</v>
+        <v>0</v>
       </c>
       <c r="H530" s="1">
         <v>0</v>
@@ -14488,10 +14488,10 @@
         <v>12</v>
       </c>
       <c r="B531" s="1">
-        <v>1694175000</v>
+        <v>1674171093</v>
       </c>
       <c r="C531" s="1">
-        <v>1694175000</v>
+        <v>1674171093</v>
       </c>
       <c r="D531" s="1">
         <v>1290186093</v>
@@ -14503,7 +14503,7 @@
         <v>1674171093</v>
       </c>
       <c r="G531" s="1">
-        <v>20003907</v>
+        <v>0</v>
       </c>
       <c r="H531" s="1">
         <v>0</v>
@@ -14514,10 +14514,10 @@
         <v>52</v>
       </c>
       <c r="B532" s="1">
-        <v>2639000000</v>
+        <v>2166235262</v>
       </c>
       <c r="C532" s="1">
-        <v>2639000000</v>
+        <v>2166235262</v>
       </c>
       <c r="D532" s="1">
         <v>1768857899</v>
@@ -14529,7 +14529,7 @@
         <v>2166235262</v>
       </c>
       <c r="G532" s="1">
-        <v>472764738</v>
+        <v>0</v>
       </c>
       <c r="H532" s="1">
         <v>0</v>
@@ -14540,10 +14540,10 @@
         <v>13</v>
       </c>
       <c r="B533" s="1">
-        <v>150000000</v>
+        <v>27646777</v>
       </c>
       <c r="C533" s="1">
-        <v>150000000</v>
+        <v>27646777</v>
       </c>
       <c r="D533" s="1">
         <v>0</v>
@@ -14555,7 +14555,7 @@
         <v>27646777</v>
       </c>
       <c r="G533" s="1">
-        <v>122353223</v>
+        <v>0</v>
       </c>
       <c r="H533" s="1">
         <v>0</v>
@@ -14566,10 +14566,10 @@
         <v>14</v>
       </c>
       <c r="B534" s="1">
-        <v>2721193000</v>
+        <v>2679984002</v>
       </c>
       <c r="C534" s="1">
-        <v>2721193000</v>
+        <v>2679984002</v>
       </c>
       <c r="D534" s="1">
         <v>1888261307</v>
@@ -14581,7 +14581,7 @@
         <v>2679984002</v>
       </c>
       <c r="G534" s="1">
-        <v>41208998</v>
+        <v>0</v>
       </c>
       <c r="H534" s="1">
         <v>0</v>
@@ -14592,22 +14592,22 @@
         <v>15</v>
       </c>
       <c r="B535" s="1">
-        <v>9794675000</v>
+        <v>11576266001</v>
       </c>
       <c r="C535" s="1">
-        <v>9794675000</v>
+        <v>11576266001</v>
       </c>
       <c r="D535" s="1">
-        <v>8938573516</v>
+        <v>11444220479</v>
       </c>
       <c r="E535" s="1">
         <v>43594190</v>
       </c>
       <c r="F535" s="1">
-        <v>8982167706</v>
+        <v>11487814669</v>
       </c>
       <c r="G535" s="1">
-        <v>812507294</v>
+        <v>88451332</v>
       </c>
       <c r="H535" s="1">
         <v>0</v>
@@ -14618,10 +14618,10 @@
         <v>16</v>
       </c>
       <c r="B536" s="1">
-        <v>2114698000</v>
+        <v>2103744312</v>
       </c>
       <c r="C536" s="1">
-        <v>2114698000</v>
+        <v>2103744312</v>
       </c>
       <c r="D536" s="1">
         <v>1190805480</v>
@@ -14633,7 +14633,7 @@
         <v>1518642716</v>
       </c>
       <c r="G536" s="1">
-        <v>596055284</v>
+        <v>585101596</v>
       </c>
       <c r="H536" s="1">
         <v>0</v>
@@ -14644,10 +14644,10 @@
         <v>53</v>
       </c>
       <c r="B537" s="1">
-        <v>1450000000</v>
+        <v>606227322</v>
       </c>
       <c r="C537" s="1">
-        <v>1450000000</v>
+        <v>606227322</v>
       </c>
       <c r="D537" s="1">
         <v>208568972</v>
@@ -14659,7 +14659,7 @@
         <v>556227322</v>
       </c>
       <c r="G537" s="1">
-        <v>893772678</v>
+        <v>50000000</v>
       </c>
       <c r="H537" s="1">
         <v>0</v>
@@ -14696,10 +14696,10 @@
         <v>56</v>
       </c>
       <c r="B539" s="1">
-        <v>915811000</v>
+        <v>768471624</v>
       </c>
       <c r="C539" s="1">
-        <v>915811000</v>
+        <v>768471624</v>
       </c>
       <c r="D539" s="1">
         <v>691400000</v>
@@ -14711,7 +14711,7 @@
         <v>768471624</v>
       </c>
       <c r="G539" s="1">
-        <v>147339376</v>
+        <v>0</v>
       </c>
       <c r="H539" s="1">
         <v>0</v>
@@ -14722,10 +14722,10 @@
         <v>17</v>
       </c>
       <c r="B540" s="1">
-        <v>1750000000</v>
+        <v>1710735389</v>
       </c>
       <c r="C540" s="1">
-        <v>1750000000</v>
+        <v>1710735389</v>
       </c>
       <c r="D540" s="1">
         <v>384000000</v>
@@ -14737,7 +14737,7 @@
         <v>1710735389</v>
       </c>
       <c r="G540" s="1">
-        <v>39264611</v>
+        <v>0</v>
       </c>
       <c r="H540" s="1">
         <v>0</v>
@@ -14748,10 +14748,10 @@
         <v>81</v>
       </c>
       <c r="B541" s="1">
-        <v>300000000</v>
+        <v>6265063</v>
       </c>
       <c r="C541" s="1">
-        <v>300000000</v>
+        <v>6265063</v>
       </c>
       <c r="D541" s="1">
         <v>1295149</v>
@@ -14763,7 +14763,7 @@
         <v>6246836</v>
       </c>
       <c r="G541" s="1">
-        <v>293753164</v>
+        <v>18227</v>
       </c>
       <c r="H541" s="1">
         <v>0</v>
@@ -14800,10 +14800,10 @@
         <v>61</v>
       </c>
       <c r="B543" s="1">
-        <v>285978663</v>
+        <v>579713600</v>
       </c>
       <c r="C543" s="1">
-        <v>285978663</v>
+        <v>579713600</v>
       </c>
       <c r="D543" s="1">
         <v>21328650</v>
@@ -14815,7 +14815,7 @@
         <v>199030350</v>
       </c>
       <c r="G543" s="1">
-        <v>86948313</v>
+        <v>380683250</v>
       </c>
       <c r="H543" s="1">
         <v>0</v>
@@ -14832,10 +14832,10 @@
         <v>1539315000</v>
       </c>
       <c r="D544" s="1">
-        <v>3687389</v>
+        <v>3318539</v>
       </c>
       <c r="E544" s="1">
-        <v>808621344</v>
+        <v>808990194</v>
       </c>
       <c r="F544" s="1">
         <v>812308733</v>
@@ -14884,16 +14884,16 @@
         <v>532875000</v>
       </c>
       <c r="D546" s="1">
-        <v>46098995</v>
+        <v>17793970</v>
       </c>
       <c r="E546" s="1">
-        <v>121482569</v>
+        <v>149777154</v>
       </c>
       <c r="F546" s="1">
-        <v>167581564</v>
+        <v>167571124</v>
       </c>
       <c r="G546" s="1">
-        <v>365293436</v>
+        <v>365303876</v>
       </c>
       <c r="H546" s="1">
         <v>177625000</v>
@@ -14936,10 +14936,10 @@
         <v>395748750</v>
       </c>
       <c r="D548" s="1">
-        <v>142166468</v>
+        <v>131203468</v>
       </c>
       <c r="E548" s="1">
-        <v>214876729</v>
+        <v>225839729</v>
       </c>
       <c r="F548" s="1">
         <v>357043197</v>
@@ -14962,16 +14962,16 @@
         <v>336802500</v>
       </c>
       <c r="D549" s="1">
-        <v>5243290</v>
+        <v>2471290</v>
       </c>
       <c r="E549" s="1">
-        <v>196277561</v>
+        <v>200293311</v>
       </c>
       <c r="F549" s="1">
-        <v>201520851</v>
+        <v>202764601</v>
       </c>
       <c r="G549" s="1">
-        <v>135281649</v>
+        <v>134037899</v>
       </c>
       <c r="H549" s="1">
         <v>112267500</v>
@@ -15043,13 +15043,13 @@
         <v>0</v>
       </c>
       <c r="E552" s="1">
-        <v>5262368341</v>
+        <v>6946029697</v>
       </c>
       <c r="F552" s="1">
-        <v>5262368341</v>
+        <v>6946029697</v>
       </c>
       <c r="G552" s="1">
-        <v>5426548525</v>
+        <v>3742887169</v>
       </c>
       <c r="H552" s="1">
         <v>0</v>
@@ -15069,13 +15069,13 @@
         <v>0</v>
       </c>
       <c r="E553" s="1">
-        <v>50304729</v>
+        <v>58355201</v>
       </c>
       <c r="F553" s="1">
-        <v>50304729</v>
+        <v>58355201</v>
       </c>
       <c r="G553" s="1">
-        <v>55811322</v>
+        <v>47760850</v>
       </c>
       <c r="H553" s="1">
         <v>0</v>
@@ -15095,13 +15095,13 @@
         <v>0</v>
       </c>
       <c r="E554" s="1">
-        <v>7412827109</v>
+        <v>7738480609</v>
       </c>
       <c r="F554" s="1">
-        <v>7412827109</v>
+        <v>7738480609</v>
       </c>
       <c r="G554" s="1">
-        <v>1805499234</v>
+        <v>1479845734</v>
       </c>
       <c r="H554" s="1">
         <v>0</v>
@@ -15147,13 +15147,13 @@
         <v>0</v>
       </c>
       <c r="E556" s="1">
-        <v>692793874</v>
+        <v>964916045</v>
       </c>
       <c r="F556" s="1">
-        <v>692793874</v>
+        <v>964916045</v>
       </c>
       <c r="G556" s="1">
-        <v>730012079</v>
+        <v>457889908</v>
       </c>
       <c r="H556" s="1">
         <v>0</v>
@@ -15173,13 +15173,13 @@
         <v>0</v>
       </c>
       <c r="E557" s="1">
-        <v>10010689</v>
+        <v>12220296</v>
       </c>
       <c r="F557" s="1">
-        <v>10010689</v>
+        <v>12220296</v>
       </c>
       <c r="G557" s="1">
-        <v>3906069</v>
+        <v>1696462</v>
       </c>
       <c r="H557" s="1">
         <v>0</v>
@@ -15199,13 +15199,13 @@
         <v>0</v>
       </c>
       <c r="E558" s="1">
-        <v>1257409047</v>
+        <v>1337346547</v>
       </c>
       <c r="F558" s="1">
-        <v>1257409047</v>
+        <v>1337346547</v>
       </c>
       <c r="G558" s="1">
-        <v>302273714</v>
+        <v>222336214</v>
       </c>
       <c r="H558" s="1">
         <v>0</v>
@@ -15248,16 +15248,16 @@
         <v>57848682223</v>
       </c>
       <c r="D560" s="1">
-        <v>21283695726</v>
+        <v>23746933814</v>
       </c>
       <c r="E560" s="1">
-        <v>22879065992</v>
+        <v>25294342783</v>
       </c>
       <c r="F560" s="1">
-        <v>44162761718</v>
+        <v>49041276597</v>
       </c>
       <c r="G560" s="1">
-        <v>13685920505</v>
+        <v>8807405626</v>
       </c>
       <c r="H560" s="1">
         <v>720558750</v>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -1,22 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\7. Jul\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\1. Laporan Bulanan\2026\7. Jul\KP\RKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{65B6187B-0812-4B8E-9E00-F0BDDD170EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3790B252-3F86-4C26-9421-B0DEAB74CDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget 3 Juni 2024" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="130">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -413,11 +422,14 @@
   <si>
     <t>35022000  Sintelis Divre IV Tanjungkarang</t>
   </si>
+  <si>
+    <t>FdsCtr/CmmtItem</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1264,12 +1276,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H560"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H561"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="60.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="15.06640625" style="1" customWidth="1"/>
+    <col min="2" max="8" width="16.796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1881,16 +1893,16 @@
         <v>1723896421</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>1312700</v>
       </c>
       <c r="E24" s="1">
-        <v>927522493</v>
+        <v>938034993</v>
       </c>
       <c r="F24" s="1">
-        <v>927522493</v>
+        <v>939347693</v>
       </c>
       <c r="G24" s="1">
-        <v>796373928</v>
+        <v>784548728</v>
       </c>
       <c r="H24" s="1">
         <v>625000000</v>
@@ -1907,10 +1919,10 @@
         <v>220000000</v>
       </c>
       <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
         <v>28132588</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0</v>
       </c>
       <c r="F25" s="1">
         <v>28132588</v>
@@ -1962,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>2528787484</v>
+        <v>2529214984</v>
       </c>
       <c r="F27" s="1">
-        <v>2528787484</v>
+        <v>2529214984</v>
       </c>
       <c r="G27" s="1">
-        <v>927826720</v>
+        <v>927399220</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -2323,16 +2335,16 @@
         <v>348402857407</v>
       </c>
       <c r="D41" s="1">
-        <v>243164677797</v>
+        <v>243137857909</v>
       </c>
       <c r="E41" s="1">
-        <v>83415705816</v>
+        <v>83454778404</v>
       </c>
       <c r="F41" s="1">
-        <v>326580383613</v>
+        <v>326592636313</v>
       </c>
       <c r="G41" s="1">
-        <v>21822473794</v>
+        <v>21810221094</v>
       </c>
       <c r="H41" s="1">
         <v>2417500000</v>
@@ -2609,16 +2621,16 @@
         <v>6000000000</v>
       </c>
       <c r="D52" s="1">
-        <v>5047644028</v>
+        <v>5273666938</v>
       </c>
       <c r="E52" s="1">
         <v>520835965</v>
       </c>
       <c r="F52" s="1">
-        <v>5568479993</v>
+        <v>5794502903</v>
       </c>
       <c r="G52" s="1">
-        <v>431520007</v>
+        <v>205497097</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -2765,16 +2777,16 @@
         <v>2620000000</v>
       </c>
       <c r="D58" s="1">
-        <v>675395317</v>
+        <v>734158067</v>
       </c>
       <c r="E58" s="1">
         <v>545850367</v>
       </c>
       <c r="F58" s="1">
-        <v>1221245684</v>
+        <v>1280008434</v>
       </c>
       <c r="G58" s="1">
-        <v>1398754316</v>
+        <v>1339991566</v>
       </c>
       <c r="H58" s="1">
         <v>0</v>
@@ -2947,16 +2959,16 @@
         <v>400400000</v>
       </c>
       <c r="D65" s="1">
-        <v>82850500</v>
+        <v>92180500</v>
       </c>
       <c r="E65" s="1">
         <v>111326422</v>
       </c>
       <c r="F65" s="1">
-        <v>194176922</v>
+        <v>203506922</v>
       </c>
       <c r="G65" s="1">
-        <v>206223078</v>
+        <v>196893078</v>
       </c>
       <c r="H65" s="1">
         <v>139000000</v>
@@ -2973,10 +2985,10 @@
         <v>335175000</v>
       </c>
       <c r="D66" s="1">
-        <v>63709511</v>
+        <v>48828000</v>
       </c>
       <c r="E66" s="1">
-        <v>165723514</v>
+        <v>180605025</v>
       </c>
       <c r="F66" s="1">
         <v>229433025</v>
@@ -3158,13 +3170,13 @@
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>14865921347</v>
+        <v>14911785024</v>
       </c>
       <c r="F73" s="1">
-        <v>14865921347</v>
+        <v>14911785024</v>
       </c>
       <c r="G73" s="1">
-        <v>8065685882</v>
+        <v>8019822205</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -3210,13 +3222,13 @@
         <v>9566218</v>
       </c>
       <c r="E75" s="1">
-        <v>17076241722</v>
+        <v>17181241722</v>
       </c>
       <c r="F75" s="1">
-        <v>17085807940</v>
+        <v>17190807940</v>
       </c>
       <c r="G75" s="1">
-        <v>3881613590</v>
+        <v>3776613590</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -3262,13 +3274,13 @@
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>1232007053</v>
+        <v>1242480138</v>
       </c>
       <c r="F77" s="1">
-        <v>1232007053</v>
+        <v>1242480138</v>
       </c>
       <c r="G77" s="1">
-        <v>417419532</v>
+        <v>406946447</v>
       </c>
       <c r="H77" s="1">
         <v>0</v>
@@ -3314,13 +3326,13 @@
         <v>165657</v>
       </c>
       <c r="E79" s="1">
-        <v>1761534181</v>
+        <v>1786534181</v>
       </c>
       <c r="F79" s="1">
-        <v>1761699838</v>
+        <v>1786699838</v>
       </c>
       <c r="G79" s="1">
-        <v>175418690</v>
+        <v>150418690</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
@@ -3389,16 +3401,16 @@
         <v>110881210191</v>
       </c>
       <c r="D82" s="1">
-        <v>37779482599</v>
+        <v>38058716748</v>
       </c>
       <c r="E82" s="1">
-        <v>48159939493</v>
+        <v>48361157766</v>
       </c>
       <c r="F82" s="1">
-        <v>85939422092</v>
+        <v>86419874514</v>
       </c>
       <c r="G82" s="1">
-        <v>24941788099</v>
+        <v>24461335677</v>
       </c>
       <c r="H82" s="1">
         <v>671501500</v>
@@ -3883,10 +3895,10 @@
         <v>255960000</v>
       </c>
       <c r="D101" s="1">
-        <v>118242050</v>
+        <v>83999650</v>
       </c>
       <c r="E101" s="1">
-        <v>118761500</v>
+        <v>153003900</v>
       </c>
       <c r="F101" s="1">
         <v>237003550</v>
@@ -3935,16 +3947,16 @@
         <v>291600000</v>
       </c>
       <c r="D103" s="1">
-        <v>222421700</v>
+        <v>220821700</v>
       </c>
       <c r="E103" s="1">
         <v>28079000</v>
       </c>
       <c r="F103" s="1">
-        <v>250500700</v>
+        <v>248900700</v>
       </c>
       <c r="G103" s="1">
-        <v>41099300</v>
+        <v>42699300</v>
       </c>
       <c r="H103" s="1">
         <v>97200000</v>
@@ -4120,13 +4132,13 @@
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>10705515196</v>
+        <v>10799701015</v>
       </c>
       <c r="F110" s="1">
-        <v>10705515196</v>
+        <v>10799701015</v>
       </c>
       <c r="G110" s="1">
-        <v>5518129657</v>
+        <v>5423943838</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -4172,13 +4184,13 @@
         <v>9868545</v>
       </c>
       <c r="E112" s="1">
-        <v>12261628031</v>
+        <v>12481628031</v>
       </c>
       <c r="F112" s="1">
-        <v>12271496576</v>
+        <v>12491496576</v>
       </c>
       <c r="G112" s="1">
-        <v>2226683372</v>
+        <v>2006683372</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -4325,16 +4337,16 @@
         <v>81693644736</v>
       </c>
       <c r="D118" s="1">
-        <v>17939726069</v>
+        <v>17903883669</v>
       </c>
       <c r="E118" s="1">
-        <v>45304687228</v>
+        <v>45653115447</v>
       </c>
       <c r="F118" s="1">
-        <v>63244413297</v>
+        <v>63556999116</v>
       </c>
       <c r="G118" s="1">
-        <v>18449231439</v>
+        <v>18136645620</v>
       </c>
       <c r="H118" s="1">
         <v>475697500</v>
@@ -4533,16 +4545,16 @@
         <v>1665000000</v>
       </c>
       <c r="D126" s="1">
-        <v>223833148</v>
+        <v>213393598</v>
       </c>
       <c r="E126" s="1">
-        <v>554922246</v>
+        <v>564327246</v>
       </c>
       <c r="F126" s="1">
-        <v>778755394</v>
+        <v>777720844</v>
       </c>
       <c r="G126" s="1">
-        <v>886244606</v>
+        <v>887279156</v>
       </c>
       <c r="H126" s="1">
         <v>0</v>
@@ -4793,10 +4805,10 @@
         <v>75000000</v>
       </c>
       <c r="D136" s="1">
-        <v>34776000</v>
+        <v>0</v>
       </c>
       <c r="E136" s="1">
-        <v>39627889</v>
+        <v>74403889</v>
       </c>
       <c r="F136" s="1">
         <v>74403889</v>
@@ -4978,13 +4990,13 @@
         <v>0</v>
       </c>
       <c r="E143" s="1">
-        <v>6354419036</v>
+        <v>6376753257</v>
       </c>
       <c r="F143" s="1">
-        <v>6354419036</v>
+        <v>6376753257</v>
       </c>
       <c r="G143" s="1">
-        <v>3594675047</v>
+        <v>3572340826</v>
       </c>
       <c r="H143" s="1">
         <v>0</v>
@@ -5030,13 +5042,13 @@
         <v>0</v>
       </c>
       <c r="E145" s="1">
-        <v>7956996210</v>
+        <v>8006996210</v>
       </c>
       <c r="F145" s="1">
-        <v>7956996210</v>
+        <v>8006996210</v>
       </c>
       <c r="G145" s="1">
-        <v>1812853681</v>
+        <v>1762853681</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
@@ -5209,16 +5221,16 @@
         <v>52173056175</v>
       </c>
       <c r="D152" s="1">
-        <v>12466057484</v>
+        <v>12420841934</v>
       </c>
       <c r="E152" s="1">
-        <v>27004256511</v>
+        <v>27120771732</v>
       </c>
       <c r="F152" s="1">
-        <v>39470313995</v>
+        <v>39541613666</v>
       </c>
       <c r="G152" s="1">
-        <v>12702742180</v>
+        <v>12631442509</v>
       </c>
       <c r="H152" s="1">
         <v>411080000</v>
@@ -5313,16 +5325,16 @@
         <v>499675000</v>
       </c>
       <c r="D156" s="1">
-        <v>320260088</v>
+        <v>342537088</v>
       </c>
       <c r="E156" s="1">
         <v>154012000</v>
       </c>
       <c r="F156" s="1">
-        <v>474272088</v>
+        <v>496549088</v>
       </c>
       <c r="G156" s="1">
-        <v>25402912</v>
+        <v>3125912</v>
       </c>
       <c r="H156" s="1">
         <v>0</v>
@@ -5391,16 +5403,16 @@
         <v>1702406000</v>
       </c>
       <c r="D159" s="1">
-        <v>207174354</v>
+        <v>214072799</v>
       </c>
       <c r="E159" s="1">
         <v>707301975</v>
       </c>
       <c r="F159" s="1">
-        <v>914476329</v>
+        <v>921374774</v>
       </c>
       <c r="G159" s="1">
-        <v>787929671</v>
+        <v>781031226</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
@@ -5888,13 +5900,13 @@
         <v>0</v>
       </c>
       <c r="E178" s="1">
-        <v>4784592545</v>
+        <v>4796175128</v>
       </c>
       <c r="F178" s="1">
-        <v>4784592545</v>
+        <v>4796175128</v>
       </c>
       <c r="G178" s="1">
-        <v>2720130833</v>
+        <v>2708548250</v>
       </c>
       <c r="H178" s="1">
         <v>0</v>
@@ -5940,13 +5952,13 @@
         <v>0</v>
       </c>
       <c r="E180" s="1">
-        <v>5846514241</v>
+        <v>5871514241</v>
       </c>
       <c r="F180" s="1">
-        <v>5846514241</v>
+        <v>5871514241</v>
       </c>
       <c r="G180" s="1">
-        <v>1482124259</v>
+        <v>1457124259</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
@@ -6093,16 +6105,16 @@
         <v>46375593027</v>
       </c>
       <c r="D186" s="1">
-        <v>10723826538</v>
+        <v>10753001983</v>
       </c>
       <c r="E186" s="1">
-        <v>25436719551</v>
+        <v>25473302134</v>
       </c>
       <c r="F186" s="1">
-        <v>36160546089</v>
+        <v>36226304117</v>
       </c>
       <c r="G186" s="1">
-        <v>10215046938</v>
+        <v>10149288910</v>
       </c>
       <c r="H186" s="1">
         <v>449400500</v>
@@ -6327,16 +6339,16 @@
         <v>469000000</v>
       </c>
       <c r="D195" s="1">
-        <v>10107434</v>
+        <v>41109084</v>
       </c>
       <c r="E195" s="1">
         <v>53995000</v>
       </c>
       <c r="F195" s="1">
-        <v>64102434</v>
+        <v>95104084</v>
       </c>
       <c r="G195" s="1">
-        <v>404897566</v>
+        <v>373895916</v>
       </c>
       <c r="H195" s="1">
         <v>0</v>
@@ -6353,16 +6365,16 @@
         <v>400000000</v>
       </c>
       <c r="D196" s="1">
-        <v>126141599</v>
+        <v>81111299</v>
       </c>
       <c r="E196" s="1">
-        <v>51500000</v>
+        <v>101044000</v>
       </c>
       <c r="F196" s="1">
-        <v>177641599</v>
+        <v>182155299</v>
       </c>
       <c r="G196" s="1">
-        <v>222358401</v>
+        <v>217844701</v>
       </c>
       <c r="H196" s="1">
         <v>0</v>
@@ -6405,16 +6417,16 @@
         <v>1862650000</v>
       </c>
       <c r="D198" s="1">
-        <v>231743141</v>
+        <v>346980441</v>
       </c>
       <c r="E198" s="1">
         <v>1211363232</v>
       </c>
       <c r="F198" s="1">
-        <v>1443106373</v>
+        <v>1558343673</v>
       </c>
       <c r="G198" s="1">
-        <v>419543627</v>
+        <v>304306327</v>
       </c>
       <c r="H198" s="1">
         <v>0</v>
@@ -6769,16 +6781,16 @@
         <v>337500000</v>
       </c>
       <c r="D212" s="1">
-        <v>32112390</v>
+        <v>35907390</v>
       </c>
       <c r="E212" s="1">
         <v>103870954</v>
       </c>
       <c r="F212" s="1">
-        <v>135983344</v>
+        <v>139778344</v>
       </c>
       <c r="G212" s="1">
-        <v>201516656</v>
+        <v>197721656</v>
       </c>
       <c r="H212" s="1">
         <v>112500000</v>
@@ -7107,16 +7119,16 @@
         <v>47499233545</v>
       </c>
       <c r="D225" s="1">
-        <v>14192067135</v>
+        <v>14297070785</v>
       </c>
       <c r="E225" s="1">
-        <v>23381914045</v>
+        <v>23431458045</v>
       </c>
       <c r="F225" s="1">
-        <v>37573981180</v>
+        <v>37728528830</v>
       </c>
       <c r="G225" s="1">
-        <v>9925252365</v>
+        <v>9770704715</v>
       </c>
       <c r="H225" s="1">
         <v>415261500</v>
@@ -7263,16 +7275,16 @@
         <v>1310391000</v>
       </c>
       <c r="D231" s="1">
-        <v>761569037</v>
+        <v>1174438503</v>
       </c>
       <c r="E231" s="1">
         <v>135761588</v>
       </c>
       <c r="F231" s="1">
-        <v>897330625</v>
+        <v>1310200091</v>
       </c>
       <c r="G231" s="1">
-        <v>413060375</v>
+        <v>190909</v>
       </c>
       <c r="H231" s="1">
         <v>0</v>
@@ -7289,16 +7301,16 @@
         <v>1380000000</v>
       </c>
       <c r="D232" s="1">
-        <v>64997000</v>
+        <v>90034500</v>
       </c>
       <c r="E232" s="1">
         <v>946087467</v>
       </c>
       <c r="F232" s="1">
-        <v>1011084467</v>
+        <v>1036121967</v>
       </c>
       <c r="G232" s="1">
-        <v>368915533</v>
+        <v>343878033</v>
       </c>
       <c r="H232" s="1">
         <v>0</v>
@@ -7497,10 +7509,10 @@
         <v>250000000</v>
       </c>
       <c r="D240" s="1">
-        <v>49983000</v>
+        <v>0</v>
       </c>
       <c r="E240" s="1">
-        <v>32848750</v>
+        <v>82831750</v>
       </c>
       <c r="F240" s="1">
         <v>82831750</v>
@@ -7812,13 +7824,13 @@
         <v>0</v>
       </c>
       <c r="E252" s="1">
-        <v>712073752</v>
+        <v>729859543</v>
       </c>
       <c r="F252" s="1">
-        <v>712073752</v>
+        <v>729859543</v>
       </c>
       <c r="G252" s="1">
-        <v>282868809</v>
+        <v>265083018</v>
       </c>
       <c r="H252" s="1">
         <v>0</v>
@@ -7864,13 +7876,13 @@
         <v>0</v>
       </c>
       <c r="E254" s="1">
-        <v>999064593</v>
+        <v>1039064593</v>
       </c>
       <c r="F254" s="1">
-        <v>999064593</v>
+        <v>1039064593</v>
       </c>
       <c r="G254" s="1">
-        <v>100662741</v>
+        <v>60662741</v>
       </c>
       <c r="H254" s="1">
         <v>0</v>
@@ -7939,16 +7951,16 @@
         <v>48914772555</v>
       </c>
       <c r="D257" s="1">
-        <v>14581081880</v>
+        <v>14969005846</v>
       </c>
       <c r="E257" s="1">
-        <v>23235061035</v>
+        <v>23342829826</v>
       </c>
       <c r="F257" s="1">
-        <v>37816142915</v>
+        <v>38311835672</v>
       </c>
       <c r="G257" s="1">
-        <v>11098629640</v>
+        <v>10602936883</v>
       </c>
       <c r="H257" s="1">
         <v>525212165</v>
@@ -8069,10 +8081,10 @@
         <v>875000000</v>
       </c>
       <c r="D262" s="1">
-        <v>427164315</v>
+        <v>232794713</v>
       </c>
       <c r="E262" s="1">
-        <v>182953936</v>
+        <v>377323538</v>
       </c>
       <c r="F262" s="1">
         <v>610118251</v>
@@ -8147,10 +8159,10 @@
         <v>1700000000</v>
       </c>
       <c r="D265" s="1">
-        <v>564695250</v>
+        <v>552265250</v>
       </c>
       <c r="E265" s="1">
-        <v>695612755</v>
+        <v>708042755</v>
       </c>
       <c r="F265" s="1">
         <v>1260308005</v>
@@ -8381,10 +8393,10 @@
         <v>2260000000</v>
       </c>
       <c r="D274" s="1">
-        <v>1517918816</v>
+        <v>1511808816</v>
       </c>
       <c r="E274" s="1">
-        <v>553698340</v>
+        <v>559808340</v>
       </c>
       <c r="F274" s="1">
         <v>2071617156</v>
@@ -8670,13 +8682,13 @@
         <v>0</v>
       </c>
       <c r="E285" s="1">
-        <v>182584750</v>
+        <v>182966000</v>
       </c>
       <c r="F285" s="1">
-        <v>182584750</v>
+        <v>182966000</v>
       </c>
       <c r="G285" s="1">
-        <v>20889500</v>
+        <v>20508250</v>
       </c>
       <c r="H285" s="1">
         <v>67824750</v>
@@ -8774,13 +8786,13 @@
         <v>0</v>
       </c>
       <c r="E289" s="1">
-        <v>8030973538</v>
+        <v>8052760854</v>
       </c>
       <c r="F289" s="1">
-        <v>8030973538</v>
+        <v>8052760854</v>
       </c>
       <c r="G289" s="1">
-        <v>4591645389</v>
+        <v>4569858073</v>
       </c>
       <c r="H289" s="1">
         <v>0</v>
@@ -8826,13 +8838,13 @@
         <v>0</v>
       </c>
       <c r="E291" s="1">
-        <v>10269482878</v>
+        <v>10319482878</v>
       </c>
       <c r="F291" s="1">
-        <v>10269482878</v>
+        <v>10319482878</v>
       </c>
       <c r="G291" s="1">
-        <v>2642234537</v>
+        <v>2592234537</v>
       </c>
       <c r="H291" s="1">
         <v>0</v>
@@ -8979,16 +8991,16 @@
         <v>63706784713</v>
       </c>
       <c r="D297" s="1">
-        <v>16297538149</v>
+        <v>16084628547</v>
       </c>
       <c r="E297" s="1">
-        <v>30798383881</v>
+        <v>31083462049</v>
       </c>
       <c r="F297" s="1">
-        <v>47095922030</v>
+        <v>47168090596</v>
       </c>
       <c r="G297" s="1">
-        <v>16610862683</v>
+        <v>16538694117</v>
       </c>
       <c r="H297" s="1">
         <v>531045413</v>
@@ -9031,16 +9043,16 @@
         <v>128850000</v>
       </c>
       <c r="D299" s="1">
-        <v>0</v>
+        <v>97550000</v>
       </c>
       <c r="E299" s="1">
         <v>31293000</v>
       </c>
       <c r="F299" s="1">
-        <v>31293000</v>
+        <v>128843000</v>
       </c>
       <c r="G299" s="1">
-        <v>97557000</v>
+        <v>7000</v>
       </c>
       <c r="H299" s="1">
         <v>0</v>
@@ -9109,16 +9121,16 @@
         <v>298750000</v>
       </c>
       <c r="D302" s="1">
-        <v>232802244</v>
+        <v>263444571</v>
       </c>
       <c r="E302" s="1">
         <v>35247626</v>
       </c>
       <c r="F302" s="1">
-        <v>268049870</v>
+        <v>298692197</v>
       </c>
       <c r="G302" s="1">
-        <v>30700130</v>
+        <v>57803</v>
       </c>
       <c r="H302" s="1">
         <v>0</v>
@@ -9135,10 +9147,10 @@
         <v>193000000</v>
       </c>
       <c r="D303" s="1">
-        <v>192716000</v>
+        <v>95816000</v>
       </c>
       <c r="E303" s="1">
-        <v>0</v>
+        <v>96900000</v>
       </c>
       <c r="F303" s="1">
         <v>192716000</v>
@@ -9187,16 +9199,16 @@
         <v>534300000</v>
       </c>
       <c r="D305" s="1">
-        <v>9898250</v>
+        <v>138450750</v>
       </c>
       <c r="E305" s="1">
         <v>269954678</v>
       </c>
       <c r="F305" s="1">
-        <v>279852928</v>
+        <v>408405428</v>
       </c>
       <c r="G305" s="1">
-        <v>254447072</v>
+        <v>125894572</v>
       </c>
       <c r="H305" s="1">
         <v>0</v>
@@ -9369,16 +9381,16 @@
         <v>463000000</v>
       </c>
       <c r="D312" s="1">
-        <v>462718152</v>
+        <v>382000000</v>
       </c>
       <c r="E312" s="1">
-        <v>0</v>
+        <v>45600000</v>
       </c>
       <c r="F312" s="1">
-        <v>462718152</v>
+        <v>427600000</v>
       </c>
       <c r="G312" s="1">
-        <v>281848</v>
+        <v>35400000</v>
       </c>
       <c r="H312" s="1">
         <v>0</v>
@@ -9632,13 +9644,13 @@
         <v>0</v>
       </c>
       <c r="E322" s="1">
-        <v>4437742748</v>
+        <v>4481414657</v>
       </c>
       <c r="F322" s="1">
-        <v>4437742748</v>
+        <v>4481414657</v>
       </c>
       <c r="G322" s="1">
-        <v>2616049517</v>
+        <v>2572377608</v>
       </c>
       <c r="H322" s="1">
         <v>0</v>
@@ -9684,13 +9696,13 @@
         <v>0</v>
       </c>
       <c r="E324" s="1">
-        <v>5599769178</v>
+        <v>5699769178</v>
       </c>
       <c r="F324" s="1">
-        <v>5599769178</v>
+        <v>5699769178</v>
       </c>
       <c r="G324" s="1">
-        <v>1415273243</v>
+        <v>1315273243</v>
       </c>
       <c r="H324" s="1">
         <v>0</v>
@@ -9837,16 +9849,16 @@
         <v>30454436960</v>
       </c>
       <c r="D330" s="1">
-        <v>3667657050</v>
+        <v>3746783725</v>
       </c>
       <c r="E330" s="1">
-        <v>19464441610</v>
+        <v>19750613519</v>
       </c>
       <c r="F330" s="1">
-        <v>23132098660</v>
+        <v>23497397244</v>
       </c>
       <c r="G330" s="1">
-        <v>7322338300</v>
+        <v>6957039716</v>
       </c>
       <c r="H330" s="1">
         <v>260139500</v>
@@ -9941,16 +9953,16 @@
         <v>2593734264</v>
       </c>
       <c r="D334" s="1">
-        <v>1145566052</v>
+        <v>1183776552</v>
       </c>
       <c r="E334" s="1">
         <v>1405666314</v>
       </c>
       <c r="F334" s="1">
-        <v>2551232366</v>
+        <v>2589442866</v>
       </c>
       <c r="G334" s="1">
-        <v>42501898</v>
+        <v>4291398</v>
       </c>
       <c r="H334" s="1">
         <v>0</v>
@@ -10045,16 +10057,16 @@
         <v>1748195004</v>
       </c>
       <c r="D338" s="1">
-        <v>325116897</v>
+        <v>392006508</v>
       </c>
       <c r="E338" s="1">
         <v>1012207888</v>
       </c>
       <c r="F338" s="1">
-        <v>1337324785</v>
+        <v>1404214396</v>
       </c>
       <c r="G338" s="1">
-        <v>410870219</v>
+        <v>343980608</v>
       </c>
       <c r="H338" s="1">
         <v>0</v>
@@ -10071,16 +10083,16 @@
         <v>327155000</v>
       </c>
       <c r="D339" s="1">
-        <v>0</v>
+        <v>40400000</v>
       </c>
       <c r="E339" s="1">
         <v>260006680</v>
       </c>
       <c r="F339" s="1">
-        <v>260006680</v>
+        <v>300406680</v>
       </c>
       <c r="G339" s="1">
-        <v>67148320</v>
+        <v>26748320</v>
       </c>
       <c r="H339" s="1">
         <v>0</v>
@@ -10123,16 +10135,16 @@
         <v>1515585000</v>
       </c>
       <c r="D341" s="1">
-        <v>175000000</v>
+        <v>479436000</v>
       </c>
       <c r="E341" s="1">
         <v>1022239000</v>
       </c>
       <c r="F341" s="1">
-        <v>1197239000</v>
+        <v>1501675000</v>
       </c>
       <c r="G341" s="1">
-        <v>318346000</v>
+        <v>13910000</v>
       </c>
       <c r="H341" s="1">
         <v>0</v>
@@ -10305,16 +10317,16 @@
         <v>571079775</v>
       </c>
       <c r="D348" s="1">
-        <v>263360170</v>
+        <v>282860170</v>
       </c>
       <c r="E348" s="1">
         <v>217598494</v>
       </c>
       <c r="F348" s="1">
-        <v>480958664</v>
+        <v>500458664</v>
       </c>
       <c r="G348" s="1">
-        <v>90121111</v>
+        <v>70621111</v>
       </c>
       <c r="H348" s="1">
         <v>190359925</v>
@@ -10669,16 +10681,16 @@
         <v>57427089299</v>
       </c>
       <c r="D362" s="1">
-        <v>9987826891</v>
+        <v>10457263002</v>
       </c>
       <c r="E362" s="1">
         <v>36416862356</v>
       </c>
       <c r="F362" s="1">
-        <v>46404689247</v>
+        <v>46874125358</v>
       </c>
       <c r="G362" s="1">
-        <v>11022400052</v>
+        <v>10552963941</v>
       </c>
       <c r="H362" s="1">
         <v>526334925</v>
@@ -10773,10 +10785,10 @@
         <v>2467762918</v>
       </c>
       <c r="D366" s="1">
-        <v>924727965</v>
+        <v>892606546</v>
       </c>
       <c r="E366" s="1">
-        <v>430332206</v>
+        <v>462453625</v>
       </c>
       <c r="F366" s="1">
         <v>1355060171</v>
@@ -10851,16 +10863,16 @@
         <v>1714789867</v>
       </c>
       <c r="D369" s="1">
-        <v>348734360</v>
+        <v>848353936</v>
       </c>
       <c r="E369" s="1">
         <v>732962308</v>
       </c>
       <c r="F369" s="1">
-        <v>1081696668</v>
+        <v>1581316244</v>
       </c>
       <c r="G369" s="1">
-        <v>633093199</v>
+        <v>133473623</v>
       </c>
       <c r="H369" s="1">
         <v>0</v>
@@ -11033,10 +11045,10 @@
         <v>99980000</v>
       </c>
       <c r="D376" s="1">
-        <v>32108000</v>
+        <v>0</v>
       </c>
       <c r="E376" s="1">
-        <v>19823200</v>
+        <v>51931200</v>
       </c>
       <c r="F376" s="1">
         <v>51931200</v>
@@ -11059,10 +11071,10 @@
         <v>411080000</v>
       </c>
       <c r="D377" s="1">
-        <v>1337650</v>
+        <v>0</v>
       </c>
       <c r="E377" s="1">
-        <v>240337093</v>
+        <v>241674743</v>
       </c>
       <c r="F377" s="1">
         <v>241674743</v>
@@ -11085,10 +11097,10 @@
         <v>120000000</v>
       </c>
       <c r="D378" s="1">
-        <v>23824605</v>
+        <v>22112105</v>
       </c>
       <c r="E378" s="1">
-        <v>27435500</v>
+        <v>29148000</v>
       </c>
       <c r="F378" s="1">
         <v>51260105</v>
@@ -11192,13 +11204,13 @@
         <v>0</v>
       </c>
       <c r="E382" s="1">
-        <v>105335500</v>
+        <v>105810500</v>
       </c>
       <c r="F382" s="1">
-        <v>105335500</v>
+        <v>105810500</v>
       </c>
       <c r="G382" s="1">
-        <v>22689500</v>
+        <v>22214500</v>
       </c>
       <c r="H382" s="1">
         <v>42675000</v>
@@ -11296,13 +11308,13 @@
         <v>0</v>
       </c>
       <c r="E386" s="1">
-        <v>2849172763</v>
+        <v>2882862486</v>
       </c>
       <c r="F386" s="1">
-        <v>2849172763</v>
+        <v>2882862486</v>
       </c>
       <c r="G386" s="1">
-        <v>1690634155</v>
+        <v>1656944432</v>
       </c>
       <c r="H386" s="1">
         <v>0</v>
@@ -11348,13 +11360,13 @@
         <v>0</v>
       </c>
       <c r="E388" s="1">
-        <v>3538827147</v>
+        <v>3613827147</v>
       </c>
       <c r="F388" s="1">
-        <v>3538827147</v>
+        <v>3613827147</v>
       </c>
       <c r="G388" s="1">
-        <v>1130812455</v>
+        <v>1055812455</v>
       </c>
       <c r="H388" s="1">
         <v>0</v>
@@ -11501,16 +11513,16 @@
         <v>24628424376</v>
       </c>
       <c r="D394" s="1">
-        <v>3690264311</v>
+        <v>4122604318</v>
       </c>
       <c r="E394" s="1">
-        <v>14226331858</v>
+        <v>14402776150</v>
       </c>
       <c r="F394" s="1">
-        <v>17916596169</v>
+        <v>18525380468</v>
       </c>
       <c r="G394" s="1">
-        <v>6711828207</v>
+        <v>6103043908</v>
       </c>
       <c r="H394" s="1">
         <v>232675000</v>
@@ -11943,16 +11955,16 @@
         <v>2230000000</v>
       </c>
       <c r="D411" s="1">
-        <v>28077420</v>
+        <v>37577420</v>
       </c>
       <c r="E411" s="1">
         <v>874803459</v>
       </c>
       <c r="F411" s="1">
-        <v>902880879</v>
+        <v>912380879</v>
       </c>
       <c r="G411" s="1">
-        <v>1327119121</v>
+        <v>1317619121</v>
       </c>
       <c r="H411" s="1">
         <v>0</v>
@@ -11969,16 +11981,16 @@
         <v>145200000</v>
       </c>
       <c r="D412" s="1">
-        <v>21012000</v>
+        <v>29448000</v>
       </c>
       <c r="E412" s="1">
         <v>58873500</v>
       </c>
       <c r="F412" s="1">
-        <v>79885500</v>
+        <v>88321500</v>
       </c>
       <c r="G412" s="1">
-        <v>65314500</v>
+        <v>56878500</v>
       </c>
       <c r="H412" s="1">
         <v>48400000</v>
@@ -12180,13 +12192,13 @@
         <v>0</v>
       </c>
       <c r="E420" s="1">
-        <v>5289975251</v>
+        <v>5321500975</v>
       </c>
       <c r="F420" s="1">
-        <v>5289975251</v>
+        <v>5321500975</v>
       </c>
       <c r="G420" s="1">
-        <v>3351370460</v>
+        <v>3319844736</v>
       </c>
       <c r="H420" s="1">
         <v>0</v>
@@ -12232,13 +12244,13 @@
         <v>0</v>
       </c>
       <c r="E422" s="1">
-        <v>6893736677</v>
+        <v>6968736677</v>
       </c>
       <c r="F422" s="1">
-        <v>6893736677</v>
+        <v>6968736677</v>
       </c>
       <c r="G422" s="1">
-        <v>2485831815</v>
+        <v>2410831815</v>
       </c>
       <c r="H422" s="1">
         <v>0</v>
@@ -12284,13 +12296,13 @@
         <v>0</v>
       </c>
       <c r="E424" s="1">
-        <v>510417643</v>
+        <v>528519217</v>
       </c>
       <c r="F424" s="1">
-        <v>510417643</v>
+        <v>528519217</v>
       </c>
       <c r="G424" s="1">
-        <v>394072003</v>
+        <v>375970429</v>
       </c>
       <c r="H424" s="1">
         <v>0</v>
@@ -12336,13 +12348,13 @@
         <v>0</v>
       </c>
       <c r="E426" s="1">
-        <v>808908632</v>
+        <v>848908632</v>
       </c>
       <c r="F426" s="1">
-        <v>808908632</v>
+        <v>848908632</v>
       </c>
       <c r="G426" s="1">
-        <v>296974815</v>
+        <v>256974815</v>
       </c>
       <c r="H426" s="1">
         <v>0</v>
@@ -12385,16 +12397,16 @@
         <v>35458361640</v>
       </c>
       <c r="D428" s="1">
-        <v>7457320120</v>
+        <v>7475256120</v>
       </c>
       <c r="E428" s="1">
-        <v>17801084761</v>
+        <v>17965712059</v>
       </c>
       <c r="F428" s="1">
-        <v>25258404881</v>
+        <v>25440968179</v>
       </c>
       <c r="G428" s="1">
-        <v>10199956759</v>
+        <v>10017393461</v>
       </c>
       <c r="H428" s="1">
         <v>472807750</v>
@@ -12777,10 +12789,10 @@
         <v>45000000</v>
       </c>
       <c r="D453" s="3">
-        <v>8508000</v>
+        <v>7388000</v>
       </c>
       <c r="E453" s="3">
-        <v>9000000</v>
+        <v>10120000</v>
       </c>
       <c r="F453" s="3">
         <v>17508000</v>
@@ -13033,16 +13045,16 @@
         <v>97500000</v>
       </c>
       <c r="D468" s="3">
-        <v>0</v>
+        <v>23953308</v>
       </c>
       <c r="E468" s="3">
         <v>54869000</v>
       </c>
       <c r="F468" s="3">
-        <v>54869000</v>
+        <v>78822308</v>
       </c>
       <c r="G468" s="3">
-        <v>42631000</v>
+        <v>18677692</v>
       </c>
       <c r="H468" s="3">
         <v>32500000</v>
@@ -13268,19 +13280,19 @@
       </c>
       <c r="D484" s="3">
         <f t="shared" si="0"/>
-        <v>1440178200</v>
+        <v>1463011508</v>
       </c>
       <c r="E484" s="3">
         <f t="shared" si="0"/>
-        <v>317170274</v>
+        <v>318290274</v>
       </c>
       <c r="F484" s="3">
         <f t="shared" si="0"/>
-        <v>1757348474</v>
+        <v>1781301782</v>
       </c>
       <c r="G484" s="3">
         <f t="shared" si="0"/>
-        <v>481412256</v>
+        <v>457458948</v>
       </c>
       <c r="H484" s="3">
         <f t="shared" si="0"/>
@@ -13480,16 +13492,16 @@
         <v>2312795000</v>
       </c>
       <c r="D492" s="1">
-        <v>1282815186</v>
+        <v>1332515186</v>
       </c>
       <c r="E492" s="1">
         <v>564810618</v>
       </c>
       <c r="F492" s="1">
-        <v>1847625804</v>
+        <v>1897325804</v>
       </c>
       <c r="G492" s="1">
-        <v>465169196</v>
+        <v>415469196</v>
       </c>
       <c r="H492" s="1">
         <v>0</v>
@@ -13558,16 +13570,16 @@
         <v>1680000000</v>
       </c>
       <c r="D495" s="1">
-        <v>525312099</v>
+        <v>545114599</v>
       </c>
       <c r="E495" s="1">
         <v>415370650</v>
       </c>
       <c r="F495" s="1">
-        <v>940682749</v>
+        <v>960485249</v>
       </c>
       <c r="G495" s="1">
-        <v>739317251</v>
+        <v>719514751</v>
       </c>
       <c r="H495" s="1">
         <v>0</v>
@@ -13844,10 +13856,10 @@
         <v>1016150000</v>
       </c>
       <c r="D506" s="1">
-        <v>60050000</v>
+        <v>20150000</v>
       </c>
       <c r="E506" s="1">
-        <v>327400000</v>
+        <v>367300000</v>
       </c>
       <c r="F506" s="1">
         <v>387450000</v>
@@ -13922,10 +13934,10 @@
         <v>870341250</v>
       </c>
       <c r="D509" s="1">
-        <v>134830520</v>
+        <v>97230520</v>
       </c>
       <c r="E509" s="1">
-        <v>519645270</v>
+        <v>557245270</v>
       </c>
       <c r="F509" s="1">
         <v>654475790</v>
@@ -13974,10 +13986,10 @@
         <v>422192250</v>
       </c>
       <c r="D511" s="1">
-        <v>18886000</v>
+        <v>4709000</v>
       </c>
       <c r="E511" s="1">
-        <v>45923427</v>
+        <v>60100427</v>
       </c>
       <c r="F511" s="1">
         <v>64809427</v>
@@ -14052,10 +14064,10 @@
         <v>61741000</v>
       </c>
       <c r="D514" s="1">
-        <v>1950000</v>
+        <v>1300000</v>
       </c>
       <c r="E514" s="1">
-        <v>38905444</v>
+        <v>39555444</v>
       </c>
       <c r="F514" s="1">
         <v>40855444</v>
@@ -14185,13 +14197,13 @@
         <v>0</v>
       </c>
       <c r="E519" s="1">
-        <v>7900359380</v>
+        <v>7941734968</v>
       </c>
       <c r="F519" s="1">
-        <v>7900359380</v>
+        <v>7941734968</v>
       </c>
       <c r="G519" s="1">
-        <v>4263922517</v>
+        <v>4222546929</v>
       </c>
       <c r="H519" s="1">
         <v>0</v>
@@ -14237,13 +14249,13 @@
         <v>0</v>
       </c>
       <c r="E521" s="1">
-        <v>9288590459</v>
+        <v>9388590459</v>
       </c>
       <c r="F521" s="1">
-        <v>9288590459</v>
+        <v>9388590459</v>
       </c>
       <c r="G521" s="1">
-        <v>1512813738</v>
+        <v>1412813738</v>
       </c>
       <c r="H521" s="1">
         <v>0</v>
@@ -14416,16 +14428,16 @@
         <v>64019485320</v>
       </c>
       <c r="D528" s="1">
-        <v>13162634289</v>
+        <v>13139809789</v>
       </c>
       <c r="E528" s="1">
-        <v>35886263212</v>
+        <v>36119965800</v>
       </c>
       <c r="F528" s="1">
-        <v>49048897501</v>
+        <v>49259775589</v>
       </c>
       <c r="G528" s="1">
-        <v>14970587819</v>
+        <v>14759709731</v>
       </c>
       <c r="H528" s="1">
         <v>850782250</v>
@@ -14520,10 +14532,10 @@
         <v>2166235262</v>
       </c>
       <c r="D532" s="1">
-        <v>1768857899</v>
+        <v>1761432234</v>
       </c>
       <c r="E532" s="1">
-        <v>397377363</v>
+        <v>404803028</v>
       </c>
       <c r="F532" s="1">
         <v>2166235262</v>
@@ -14624,16 +14636,16 @@
         <v>2103744312</v>
       </c>
       <c r="D536" s="1">
-        <v>1190805480</v>
+        <v>1279968780</v>
       </c>
       <c r="E536" s="1">
         <v>327837236</v>
       </c>
       <c r="F536" s="1">
-        <v>1518642716</v>
+        <v>1607806016</v>
       </c>
       <c r="G536" s="1">
-        <v>585101596</v>
+        <v>495938296</v>
       </c>
       <c r="H536" s="1">
         <v>0</v>
@@ -14650,10 +14662,10 @@
         <v>606227322</v>
       </c>
       <c r="D537" s="1">
-        <v>208568972</v>
+        <v>160208972</v>
       </c>
       <c r="E537" s="1">
-        <v>347658350</v>
+        <v>396018350</v>
       </c>
       <c r="F537" s="1">
         <v>556227322</v>
@@ -14806,16 +14818,16 @@
         <v>579713600</v>
       </c>
       <c r="D543" s="1">
-        <v>21328650</v>
+        <v>42657300</v>
       </c>
       <c r="E543" s="1">
         <v>177701700</v>
       </c>
       <c r="F543" s="1">
-        <v>199030350</v>
+        <v>220359000</v>
       </c>
       <c r="G543" s="1">
-        <v>380683250</v>
+        <v>359354600</v>
       </c>
       <c r="H543" s="1">
         <v>0</v>
@@ -14832,16 +14844,16 @@
         <v>1539315000</v>
       </c>
       <c r="D544" s="1">
-        <v>3318539</v>
+        <v>6318539</v>
       </c>
       <c r="E544" s="1">
         <v>808990194</v>
       </c>
       <c r="F544" s="1">
-        <v>812308733</v>
+        <v>815308733</v>
       </c>
       <c r="G544" s="1">
-        <v>727006267</v>
+        <v>724006267</v>
       </c>
       <c r="H544" s="1">
         <v>0</v>
@@ -14884,16 +14896,16 @@
         <v>532875000</v>
       </c>
       <c r="D546" s="1">
-        <v>17793970</v>
+        <v>35546200</v>
       </c>
       <c r="E546" s="1">
         <v>149777154</v>
       </c>
       <c r="F546" s="1">
-        <v>167571124</v>
+        <v>185323354</v>
       </c>
       <c r="G546" s="1">
-        <v>365303876</v>
+        <v>347551646</v>
       </c>
       <c r="H546" s="1">
         <v>177625000</v>
@@ -14962,10 +14974,10 @@
         <v>336802500</v>
       </c>
       <c r="D549" s="1">
-        <v>2471290</v>
+        <v>0</v>
       </c>
       <c r="E549" s="1">
-        <v>200293311</v>
+        <v>202764601</v>
       </c>
       <c r="F549" s="1">
         <v>202764601</v>
@@ -15043,13 +15055,13 @@
         <v>0</v>
       </c>
       <c r="E552" s="1">
-        <v>6946029697</v>
+        <v>6977716141</v>
       </c>
       <c r="F552" s="1">
-        <v>6946029697</v>
+        <v>6977716141</v>
       </c>
       <c r="G552" s="1">
-        <v>3742887169</v>
+        <v>3711200725</v>
       </c>
       <c r="H552" s="1">
         <v>0</v>
@@ -15095,13 +15107,13 @@
         <v>0</v>
       </c>
       <c r="E554" s="1">
-        <v>7738480609</v>
+        <v>7813480609</v>
       </c>
       <c r="F554" s="1">
-        <v>7738480609</v>
+        <v>7813480609</v>
       </c>
       <c r="G554" s="1">
-        <v>1479845734</v>
+        <v>1404845734</v>
       </c>
       <c r="H554" s="1">
         <v>0</v>
@@ -15248,19 +15260,45 @@
         <v>57848682223</v>
       </c>
       <c r="D560" s="1">
-        <v>23746933814</v>
+        <v>23819921039</v>
       </c>
       <c r="E560" s="1">
-        <v>25294342783</v>
+        <v>25459286182</v>
       </c>
       <c r="F560" s="1">
-        <v>49041276597</v>
+        <v>49279207221</v>
       </c>
       <c r="G560" s="1">
-        <v>8807405626</v>
+        <v>8569475002</v>
       </c>
       <c r="H560" s="1">
         <v>720558750</v>
+      </c>
+    </row>
+    <row r="561" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A561" t="s">
+        <v>129</v>
+      </c>
+      <c r="B561" s="1">
+        <v>1118587579611</v>
+      </c>
+      <c r="C561" s="1">
+        <v>1109055302289</v>
+      </c>
+      <c r="D561" s="1">
+        <v>438279661593</v>
+      </c>
+      <c r="E561" s="1">
+        <v>479828455814</v>
+      </c>
+      <c r="F561" s="1">
+        <v>918108117407</v>
+      </c>
+      <c r="G561" s="1">
+        <v>190947184882</v>
+      </c>
+      <c r="H561" s="1">
+        <v>9532277322</v>
       </c>
     </row>
   </sheetData>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E6BF05B-A57B-4520-9AD2-9DDBDA2C0F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{30D458A9-4667-4C07-809A-F1462F6B9E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="3360" yWindow="3096" windowWidth="17280" windowHeight="9180"/>
   </bookViews>
   <sheets>
-    <sheet name="20260818 All Daerah" sheetId="1" r:id="rId1"/>
+    <sheet name="20260820 SAP" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -557,7 +557,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -737,6 +737,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -900,7 +906,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1298,20 +1304,20 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1">
-        <v>109318000000</v>
-      </c>
-      <c r="C2" s="1">
-        <v>109318000000</v>
-      </c>
-      <c r="D2" s="1">
-        <v>102172000000</v>
+      <c r="B2">
+        <v>109317656175</v>
+      </c>
+      <c r="C2">
+        <v>109317656175</v>
+      </c>
+      <c r="D2">
+        <v>102171671229</v>
       </c>
       <c r="E2">
         <v>6903708916</v>
       </c>
-      <c r="F2" s="1">
-        <v>109075000000</v>
+      <c r="F2">
+        <v>109075380145</v>
       </c>
       <c r="G2">
         <v>242276030</v>
@@ -1747,16 +1753,16 @@
         <v>4500000000</v>
       </c>
       <c r="D19">
-        <v>392481098</v>
+        <v>712280958</v>
       </c>
       <c r="E19">
-        <v>2171456531</v>
+        <v>2197901531</v>
       </c>
       <c r="F19">
-        <v>2563937629</v>
+        <v>2910182489</v>
       </c>
       <c r="G19">
-        <v>1936062371</v>
+        <v>1589817511</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -1906,13 +1912,13 @@
         <v>1842700</v>
       </c>
       <c r="E25">
-        <v>985422493</v>
+        <v>989684993</v>
       </c>
       <c r="F25">
-        <v>987265193</v>
+        <v>991527693</v>
       </c>
       <c r="G25">
-        <v>736631228</v>
+        <v>732368728</v>
       </c>
       <c r="H25">
         <v>625000000</v>
@@ -1984,13 +1990,13 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2531269044</v>
+        <v>2531501544</v>
       </c>
       <c r="F28">
-        <v>2531269044</v>
+        <v>2531501544</v>
       </c>
       <c r="G28">
-        <v>925345160</v>
+        <v>925112660</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2338,23 +2344,23 @@
       <c r="A42" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="1">
-        <v>350810000000</v>
-      </c>
-      <c r="C42" s="1">
-        <v>348392000000</v>
-      </c>
-      <c r="D42" s="1">
-        <v>240240000000</v>
+      <c r="B42">
+        <v>350809641207</v>
+      </c>
+      <c r="C42">
+        <v>348392141207</v>
+      </c>
+      <c r="D42">
+        <v>240559911763</v>
       </c>
       <c r="E42">
-        <v>90336497122</v>
-      </c>
-      <c r="F42" s="1">
-        <v>330577000000</v>
+        <v>90367437122</v>
+      </c>
+      <c r="F42">
+        <v>330927348885</v>
       </c>
       <c r="G42">
-        <v>17815532182</v>
+        <v>17464792322</v>
       </c>
       <c r="H42">
         <v>2417500000</v>
@@ -2579,10 +2585,10 @@
         <v>100000000</v>
       </c>
       <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
         <v>44401500</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
       </c>
       <c r="F51">
         <v>44401500</v>
@@ -2657,10 +2663,10 @@
         <v>6000000000</v>
       </c>
       <c r="D54">
-        <v>5273666938</v>
+        <v>5252888358</v>
       </c>
       <c r="E54">
-        <v>520835965</v>
+        <v>541614545</v>
       </c>
       <c r="F54">
         <v>5794502903</v>
@@ -2683,10 +2689,10 @@
         <v>4260000000</v>
       </c>
       <c r="D55">
-        <v>1104189625</v>
+        <v>1084689625</v>
       </c>
       <c r="E55">
-        <v>1879277927</v>
+        <v>1898777927</v>
       </c>
       <c r="F55">
         <v>2983467552</v>
@@ -2735,10 +2741,10 @@
         <v>2500000000</v>
       </c>
       <c r="D57">
-        <v>973190350</v>
+        <v>482284000</v>
       </c>
       <c r="E57">
-        <v>572278341</v>
+        <v>1063184691</v>
       </c>
       <c r="F57">
         <v>1545468691</v>
@@ -2891,10 +2897,10 @@
         <v>2500000000</v>
       </c>
       <c r="D63">
-        <v>1847310100</v>
+        <v>1798665100</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>48645000</v>
       </c>
       <c r="F63">
         <v>1847310100</v>
@@ -2995,10 +3001,10 @@
         <v>400400000</v>
       </c>
       <c r="D67">
-        <v>96893010</v>
+        <v>89162510</v>
       </c>
       <c r="E67">
-        <v>111326422</v>
+        <v>119056922</v>
       </c>
       <c r="F67">
         <v>208219432</v>
@@ -3021,10 +3027,10 @@
         <v>335175000</v>
       </c>
       <c r="D68">
-        <v>71811850</v>
+        <v>68211850</v>
       </c>
       <c r="E68">
-        <v>180605025</v>
+        <v>184205025</v>
       </c>
       <c r="F68">
         <v>252416875</v>
@@ -3430,17 +3436,17 @@
       <c r="A84" t="s">
         <v>66</v>
       </c>
-      <c r="B84" s="1">
-        <v>111553000000</v>
-      </c>
-      <c r="C84" s="1">
-        <v>110881000000</v>
+      <c r="B84">
+        <v>111552711691</v>
+      </c>
+      <c r="C84">
+        <v>110881210191</v>
       </c>
       <c r="D84">
-        <v>36889758101</v>
+        <v>36254196171</v>
       </c>
       <c r="E84">
-        <v>50017721665</v>
+        <v>50653283595</v>
       </c>
       <c r="F84">
         <v>86907479766</v>
@@ -3567,10 +3573,10 @@
         <v>30639775739</v>
       </c>
       <c r="D89">
-        <v>14067170534</v>
+        <v>13930855381</v>
       </c>
       <c r="E89">
-        <v>11787239668</v>
+        <v>11923554821</v>
       </c>
       <c r="F89">
         <v>25854410202</v>
@@ -3671,10 +3677,10 @@
         <v>720219728</v>
       </c>
       <c r="D93">
-        <v>38005000</v>
+        <v>0</v>
       </c>
       <c r="E93">
-        <v>682214569</v>
+        <v>720219569</v>
       </c>
       <c r="F93">
         <v>720219569</v>
@@ -3697,16 +3703,16 @@
         <v>2796520000</v>
       </c>
       <c r="D94">
-        <v>672522069</v>
+        <v>762748514</v>
       </c>
       <c r="E94">
         <v>1905663067</v>
       </c>
       <c r="F94">
-        <v>2578185136</v>
+        <v>2668411581</v>
       </c>
       <c r="G94">
-        <v>218334864</v>
+        <v>128108419</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -4399,16 +4405,16 @@
         <v>81693644736</v>
       </c>
       <c r="D121">
-        <v>16917986717</v>
+        <v>16833893009</v>
       </c>
       <c r="E121">
-        <v>47487614421</v>
+        <v>47661934574</v>
       </c>
       <c r="F121">
-        <v>64405601138</v>
+        <v>64495827583</v>
       </c>
       <c r="G121">
-        <v>17288043598</v>
+        <v>17197817153</v>
       </c>
       <c r="H121">
         <v>475697500</v>
@@ -4425,16 +4431,16 @@
         <v>8995670000</v>
       </c>
       <c r="D122">
-        <v>4764712520</v>
+        <v>5186052520</v>
       </c>
       <c r="E122">
         <v>3020023792</v>
       </c>
       <c r="F122">
-        <v>7784736312</v>
+        <v>8206076312</v>
       </c>
       <c r="G122">
-        <v>1210933688</v>
+        <v>789593688</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -4607,10 +4613,10 @@
         <v>1665000000</v>
       </c>
       <c r="D129">
-        <v>158797838</v>
+        <v>148801838</v>
       </c>
       <c r="E129">
-        <v>628697246</v>
+        <v>638693246</v>
       </c>
       <c r="F129">
         <v>787495084</v>
@@ -5283,16 +5289,16 @@
         <v>52173056175</v>
       </c>
       <c r="D155">
-        <v>11882401954</v>
+        <v>12293745954</v>
       </c>
       <c r="E155">
-        <v>27830336694</v>
+        <v>27840332694</v>
       </c>
       <c r="F155">
-        <v>39712738648</v>
+        <v>40134078648</v>
       </c>
       <c r="G155">
-        <v>12460317527</v>
+        <v>12038977527</v>
       </c>
       <c r="H155">
         <v>411080000</v>
@@ -5910,13 +5916,13 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>113634250</v>
+        <v>114184250</v>
       </c>
       <c r="F179">
-        <v>113634250</v>
+        <v>114184250</v>
       </c>
       <c r="G179">
-        <v>48667250</v>
+        <v>48117250</v>
       </c>
       <c r="H179">
         <v>54100500</v>
@@ -5962,13 +5968,13 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>4796980028</v>
+        <v>4797002528</v>
       </c>
       <c r="F181">
-        <v>4796980028</v>
+        <v>4797002528</v>
       </c>
       <c r="G181">
-        <v>2707743350</v>
+        <v>2707720850</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -6170,13 +6176,13 @@
         <v>10621302092</v>
       </c>
       <c r="E189">
-        <v>25736710184</v>
+        <v>25737282684</v>
       </c>
       <c r="F189">
-        <v>36358012276</v>
+        <v>36358584776</v>
       </c>
       <c r="G189">
-        <v>10017580751</v>
+        <v>10017008251</v>
       </c>
       <c r="H189">
         <v>449400500</v>
@@ -6193,16 +6199,16 @@
         <v>7317456560</v>
       </c>
       <c r="D190">
-        <v>5880749420</v>
+        <v>6099432947</v>
       </c>
       <c r="E190">
         <v>1212495000</v>
       </c>
       <c r="F190">
-        <v>7093244420</v>
+        <v>7311927947</v>
       </c>
       <c r="G190">
-        <v>224212140</v>
+        <v>5528613</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -6323,16 +6329,16 @@
         <v>3919663677</v>
       </c>
       <c r="D195">
-        <v>2884499457</v>
+        <v>3271708605</v>
       </c>
       <c r="E195">
         <v>480523683</v>
       </c>
       <c r="F195">
-        <v>3365023140</v>
+        <v>3752232288</v>
       </c>
       <c r="G195">
-        <v>554640537</v>
+        <v>167431389</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -6349,16 +6355,16 @@
         <v>450000000</v>
       </c>
       <c r="D196">
-        <v>0</v>
+        <v>449936266</v>
       </c>
       <c r="E196">
         <v>0</v>
       </c>
       <c r="F196">
-        <v>0</v>
+        <v>449936266</v>
       </c>
       <c r="G196">
-        <v>450000000</v>
+        <v>63734</v>
       </c>
       <c r="H196">
         <v>0</v>
@@ -6453,10 +6459,10 @@
         <v>609000000</v>
       </c>
       <c r="D200">
-        <v>318655787</v>
+        <v>295740587</v>
       </c>
       <c r="E200">
-        <v>252257975</v>
+        <v>275173175</v>
       </c>
       <c r="F200">
         <v>570913762</v>
@@ -6479,16 +6485,16 @@
         <v>1862650000</v>
       </c>
       <c r="D201">
-        <v>460343541</v>
+        <v>437563067</v>
       </c>
       <c r="E201">
-        <v>1211363232</v>
+        <v>1239143706</v>
       </c>
       <c r="F201">
-        <v>1671706773</v>
+        <v>1676706773</v>
       </c>
       <c r="G201">
-        <v>190943227</v>
+        <v>185943227</v>
       </c>
       <c r="H201">
         <v>0</v>
@@ -6739,10 +6745,10 @@
         <v>2570000000</v>
       </c>
       <c r="D211">
-        <v>9379908</v>
+        <v>0</v>
       </c>
       <c r="E211">
-        <v>1375291087</v>
+        <v>1384670995</v>
       </c>
       <c r="F211">
         <v>1384670995</v>
@@ -6843,16 +6849,16 @@
         <v>337500000</v>
       </c>
       <c r="D215">
-        <v>56013890</v>
+        <v>55213890</v>
       </c>
       <c r="E215">
         <v>103870954</v>
       </c>
       <c r="F215">
-        <v>159884844</v>
+        <v>159084844</v>
       </c>
       <c r="G215">
-        <v>177615156</v>
+        <v>178415156</v>
       </c>
       <c r="H215">
         <v>112500000</v>
@@ -7181,16 +7187,16 @@
         <v>47499233545</v>
       </c>
       <c r="D228">
-        <v>14286774401</v>
+        <v>15286727760</v>
       </c>
       <c r="E228">
-        <v>23634850759</v>
+        <v>23694926341</v>
       </c>
       <c r="F228">
-        <v>37921625160</v>
+        <v>38981654101</v>
       </c>
       <c r="G228">
-        <v>9577608385</v>
+        <v>8517579444</v>
       </c>
       <c r="H228">
         <v>415261500</v>
@@ -7363,16 +7369,16 @@
         <v>1380000000</v>
       </c>
       <c r="D235">
-        <v>178825000</v>
+        <v>124902500</v>
       </c>
       <c r="E235">
-        <v>946087467</v>
+        <v>1004784967</v>
       </c>
       <c r="F235">
-        <v>1124912467</v>
+        <v>1129687467</v>
       </c>
       <c r="G235">
-        <v>255087533</v>
+        <v>250312533</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -7493,16 +7499,16 @@
         <v>30000000</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>13100000</v>
       </c>
       <c r="E240">
         <v>0</v>
       </c>
       <c r="F240">
-        <v>0</v>
+        <v>13100000</v>
       </c>
       <c r="G240">
-        <v>30000000</v>
+        <v>16900000</v>
       </c>
       <c r="H240">
         <v>0</v>
@@ -7649,16 +7655,16 @@
         <v>354238500</v>
       </c>
       <c r="D246">
-        <v>53399500</v>
+        <v>54733500</v>
       </c>
       <c r="E246">
         <v>263736900</v>
       </c>
       <c r="F246">
-        <v>317136400</v>
+        <v>318470400</v>
       </c>
       <c r="G246">
-        <v>37102100</v>
+        <v>35768100</v>
       </c>
       <c r="H246">
         <v>118079500</v>
@@ -8013,16 +8019,16 @@
         <v>48914772555</v>
       </c>
       <c r="D260">
-        <v>12188305065</v>
+        <v>12148816565</v>
       </c>
       <c r="E260">
-        <v>26303595044</v>
+        <v>26362292544</v>
       </c>
       <c r="F260">
-        <v>38491900109</v>
+        <v>38511109109</v>
       </c>
       <c r="G260">
-        <v>10422872446</v>
+        <v>10403663446</v>
       </c>
       <c r="H260">
         <v>525212165</v>
@@ -8169,10 +8175,10 @@
         <v>3269982000</v>
       </c>
       <c r="D266">
-        <v>879759300</v>
+        <v>855739300</v>
       </c>
       <c r="E266">
-        <v>480407044</v>
+        <v>504427044</v>
       </c>
       <c r="F266">
         <v>1360166344</v>
@@ -8325,10 +8331,10 @@
         <v>2668302662</v>
       </c>
       <c r="D272">
-        <v>572539000</v>
+        <v>523239000</v>
       </c>
       <c r="E272">
-        <v>2040330000</v>
+        <v>2089630000</v>
       </c>
       <c r="F272">
         <v>2612869000</v>
@@ -8351,10 +8357,10 @@
         <v>547536000</v>
       </c>
       <c r="D273">
-        <v>488100000</v>
+        <v>443300000</v>
       </c>
       <c r="E273">
-        <v>0</v>
+        <v>44800000</v>
       </c>
       <c r="F273">
         <v>488100000</v>
@@ -8585,10 +8591,10 @@
         <v>346377600</v>
       </c>
       <c r="D282">
-        <v>129819980</v>
+        <v>104209980</v>
       </c>
       <c r="E282">
-        <v>128580000</v>
+        <v>154190000</v>
       </c>
       <c r="F282">
         <v>258399980</v>
@@ -8744,13 +8750,13 @@
         <v>0</v>
       </c>
       <c r="E288">
-        <v>187647250</v>
+        <v>188422250</v>
       </c>
       <c r="F288">
-        <v>187647250</v>
+        <v>188422250</v>
       </c>
       <c r="G288">
-        <v>15827000</v>
+        <v>15052000</v>
       </c>
       <c r="H288">
         <v>67824750</v>
@@ -8845,16 +8851,16 @@
         <v>12622618927</v>
       </c>
       <c r="D292">
-        <v>15000000</v>
+        <v>0</v>
       </c>
       <c r="E292">
-        <v>8052870543</v>
+        <v>8067904293</v>
       </c>
       <c r="F292">
-        <v>8067870543</v>
+        <v>8067904293</v>
       </c>
       <c r="G292">
-        <v>4554748384</v>
+        <v>4554714634</v>
       </c>
       <c r="H292">
         <v>0</v>
@@ -8897,10 +8903,10 @@
         <v>12911717415</v>
       </c>
       <c r="D294">
-        <v>29878127</v>
+        <v>0</v>
       </c>
       <c r="E294">
-        <v>10319482878</v>
+        <v>10349361005</v>
       </c>
       <c r="F294">
         <v>10349361005</v>
@@ -9001,10 +9007,10 @@
         <v>1560328837</v>
       </c>
       <c r="D298">
-        <v>388391</v>
+        <v>0</v>
       </c>
       <c r="E298">
-        <v>1208802162</v>
+        <v>1209190553</v>
       </c>
       <c r="F298">
         <v>1209190553</v>
@@ -9053,16 +9059,16 @@
         <v>63706784713</v>
       </c>
       <c r="D300">
-        <v>14686030676</v>
+        <v>14497034158</v>
       </c>
       <c r="E300">
-        <v>32806304959</v>
+        <v>32996110227</v>
       </c>
       <c r="F300">
-        <v>47492335635</v>
+        <v>47493144385</v>
       </c>
       <c r="G300">
-        <v>16214449078</v>
+        <v>16213640328</v>
       </c>
       <c r="H300">
         <v>531045413</v>
@@ -9079,10 +9085,10 @@
         <v>3628073000</v>
       </c>
       <c r="D301">
-        <v>1716026000</v>
+        <v>1305682100</v>
       </c>
       <c r="E301">
-        <v>1912045000</v>
+        <v>2322388900</v>
       </c>
       <c r="F301">
         <v>3628071000</v>
@@ -9131,10 +9137,10 @@
         <v>488774000</v>
       </c>
       <c r="D303">
-        <v>15930050</v>
+        <v>0</v>
       </c>
       <c r="E303">
-        <v>472749437</v>
+        <v>488679487</v>
       </c>
       <c r="F303">
         <v>488679487</v>
@@ -9183,16 +9189,16 @@
         <v>298750000</v>
       </c>
       <c r="D305">
-        <v>263444571</v>
+        <v>259144571</v>
       </c>
       <c r="E305">
         <v>35247626</v>
       </c>
       <c r="F305">
-        <v>298692197</v>
+        <v>294392197</v>
       </c>
       <c r="G305">
-        <v>57803</v>
+        <v>4357803</v>
       </c>
       <c r="H305">
         <v>0</v>
@@ -9235,16 +9241,16 @@
         <v>1222108000</v>
       </c>
       <c r="D307">
-        <v>155450000</v>
+        <v>151226000</v>
       </c>
       <c r="E307">
         <v>1066657271</v>
       </c>
       <c r="F307">
-        <v>1222107271</v>
+        <v>1217883271</v>
       </c>
       <c r="G307">
-        <v>729</v>
+        <v>4224729</v>
       </c>
       <c r="H307">
         <v>0</v>
@@ -9261,16 +9267,16 @@
         <v>534300000</v>
       </c>
       <c r="D308">
-        <v>138450750</v>
+        <v>148445515</v>
       </c>
       <c r="E308">
         <v>269954678</v>
       </c>
       <c r="F308">
-        <v>408405428</v>
+        <v>418400193</v>
       </c>
       <c r="G308">
-        <v>125894572</v>
+        <v>115899807</v>
       </c>
       <c r="H308">
         <v>0</v>
@@ -9365,10 +9371,10 @@
         <v>1882400000</v>
       </c>
       <c r="D312">
-        <v>174690000</v>
+        <v>169090000</v>
       </c>
       <c r="E312">
-        <v>1707705000</v>
+        <v>1713305000</v>
       </c>
       <c r="F312">
         <v>1882395000</v>
@@ -9547,16 +9553,16 @@
         <v>64614000</v>
       </c>
       <c r="D319">
-        <v>18526300</v>
+        <v>19590250</v>
       </c>
       <c r="E319">
         <v>24737271</v>
       </c>
       <c r="F319">
-        <v>43263571</v>
+        <v>44327521</v>
       </c>
       <c r="G319">
-        <v>21350429</v>
+        <v>20286479</v>
       </c>
       <c r="H319">
         <v>21538000</v>
@@ -9911,16 +9917,16 @@
         <v>30454436960</v>
       </c>
       <c r="D333">
-        <v>3678772905</v>
+        <v>3249433670</v>
       </c>
       <c r="E333">
-        <v>19854601614</v>
+        <v>20286475564</v>
       </c>
       <c r="F333">
-        <v>23533374519</v>
+        <v>23535909234</v>
       </c>
       <c r="G333">
-        <v>6921062441</v>
+        <v>6918527726</v>
       </c>
       <c r="H333">
         <v>260139500</v>
@@ -9937,10 +9943,10 @@
         <v>13755471000</v>
       </c>
       <c r="D334">
-        <v>2713344960</v>
+        <v>2663944960</v>
       </c>
       <c r="E334">
-        <v>10993987055</v>
+        <v>11043387055</v>
       </c>
       <c r="F334">
         <v>13707332015</v>
@@ -10119,16 +10125,16 @@
         <v>1748195004</v>
       </c>
       <c r="D341">
-        <v>550721958</v>
+        <v>511194948</v>
       </c>
       <c r="E341">
-        <v>1032262638</v>
+        <v>1081786638</v>
       </c>
       <c r="F341">
-        <v>1582984596</v>
+        <v>1592981586</v>
       </c>
       <c r="G341">
-        <v>165210408</v>
+        <v>155213418</v>
       </c>
       <c r="H341">
         <v>0</v>
@@ -10249,10 +10255,10 @@
         <v>1000000000</v>
       </c>
       <c r="D346">
-        <v>954060500</v>
+        <v>464560500</v>
       </c>
       <c r="E346">
-        <v>43200000</v>
+        <v>532700000</v>
       </c>
       <c r="F346">
         <v>997260500</v>
@@ -10275,16 +10281,16 @@
         <v>150000000</v>
       </c>
       <c r="D347">
-        <v>20000000</v>
+        <v>58802000</v>
       </c>
       <c r="E347">
         <v>0</v>
       </c>
       <c r="F347">
-        <v>20000000</v>
+        <v>58802000</v>
       </c>
       <c r="G347">
-        <v>130000000</v>
+        <v>91198000</v>
       </c>
       <c r="H347">
         <v>50000000</v>
@@ -10379,10 +10385,10 @@
         <v>571079775</v>
       </c>
       <c r="D351">
-        <v>278147670</v>
+        <v>258647670</v>
       </c>
       <c r="E351">
-        <v>230462994</v>
+        <v>249962994</v>
       </c>
       <c r="F351">
         <v>508610664</v>
@@ -10460,13 +10466,13 @@
         <v>0</v>
       </c>
       <c r="E354">
-        <v>164411500</v>
+        <v>166586500</v>
       </c>
       <c r="F354">
-        <v>164411500</v>
+        <v>166586500</v>
       </c>
       <c r="G354">
-        <v>96138500</v>
+        <v>93963500</v>
       </c>
       <c r="H354">
         <v>86850000</v>
@@ -10483,16 +10489,16 @@
         <v>6000000</v>
       </c>
       <c r="D355">
-        <v>467370</v>
+        <v>286620</v>
       </c>
       <c r="E355">
         <v>1500170</v>
       </c>
       <c r="F355">
-        <v>1967540</v>
+        <v>1786790</v>
       </c>
       <c r="G355">
-        <v>4032460</v>
+        <v>4213210</v>
       </c>
       <c r="H355">
         <v>0</v>
@@ -10538,13 +10544,13 @@
         <v>0</v>
       </c>
       <c r="E357">
-        <v>6702726516</v>
+        <v>6702754642</v>
       </c>
       <c r="F357">
-        <v>6702726516</v>
+        <v>6702754642</v>
       </c>
       <c r="G357">
-        <v>4012189497</v>
+        <v>4012161371</v>
       </c>
       <c r="H357">
         <v>0</v>
@@ -10743,16 +10749,16 @@
         <v>57427089299</v>
       </c>
       <c r="D365">
-        <v>10828493721</v>
+        <v>10269187961</v>
       </c>
       <c r="E365">
-        <v>36567321317</v>
+        <v>37177448443</v>
       </c>
       <c r="F365">
-        <v>47395815038</v>
+        <v>47446636404</v>
       </c>
       <c r="G365">
-        <v>10031274261</v>
+        <v>9980452895</v>
       </c>
       <c r="H365">
         <v>526334925</v>
@@ -10847,16 +10853,16 @@
         <v>2467762918</v>
       </c>
       <c r="D369">
-        <v>892606546</v>
+        <v>937400549</v>
       </c>
       <c r="E369">
-        <v>462453625</v>
+        <v>481810055</v>
       </c>
       <c r="F369">
-        <v>1355060171</v>
+        <v>1419210604</v>
       </c>
       <c r="G369">
-        <v>1112702747</v>
+        <v>1048552314</v>
       </c>
       <c r="H369">
         <v>0</v>
@@ -10951,16 +10957,16 @@
         <v>1400000000</v>
       </c>
       <c r="D373">
-        <v>235706844</v>
+        <v>375454314</v>
       </c>
       <c r="E373">
         <v>394974750</v>
       </c>
       <c r="F373">
-        <v>630681594</v>
+        <v>770429064</v>
       </c>
       <c r="G373">
-        <v>769318406</v>
+        <v>629570936</v>
       </c>
       <c r="H373">
         <v>0</v>
@@ -11185,16 +11191,16 @@
         <v>300000000</v>
       </c>
       <c r="D382">
-        <v>66105500</v>
+        <v>68105500</v>
       </c>
       <c r="E382">
         <v>172833462</v>
       </c>
       <c r="F382">
-        <v>238938962</v>
+        <v>240938962</v>
       </c>
       <c r="G382">
-        <v>61061038</v>
+        <v>59061038</v>
       </c>
       <c r="H382">
         <v>100000000</v>
@@ -11266,13 +11272,13 @@
         <v>0</v>
       </c>
       <c r="E385">
-        <v>109135500</v>
+        <v>109610500</v>
       </c>
       <c r="F385">
-        <v>109135500</v>
+        <v>109610500</v>
       </c>
       <c r="G385">
-        <v>18889500</v>
+        <v>18414500</v>
       </c>
       <c r="H385">
         <v>42675000</v>
@@ -11370,13 +11376,13 @@
         <v>0</v>
       </c>
       <c r="E389">
-        <v>2882971236</v>
+        <v>2882978736</v>
       </c>
       <c r="F389">
-        <v>2882971236</v>
+        <v>2882978736</v>
       </c>
       <c r="G389">
-        <v>1656835682</v>
+        <v>1656828182</v>
       </c>
       <c r="H389">
         <v>0</v>
@@ -11575,16 +11581,16 @@
         <v>24628424376</v>
       </c>
       <c r="D397">
-        <v>4167440408</v>
+        <v>4353981881</v>
       </c>
       <c r="E397">
-        <v>14452635570</v>
+        <v>14472474500</v>
       </c>
       <c r="F397">
-        <v>18620075978</v>
+        <v>18826456381</v>
       </c>
       <c r="G397">
-        <v>6008348398</v>
+        <v>5801967995</v>
       </c>
       <c r="H397">
         <v>232675000</v>
@@ -11835,10 +11841,10 @@
         <v>455131000</v>
       </c>
       <c r="D407">
+        <v>0</v>
+      </c>
+      <c r="E407">
         <v>450384488</v>
-      </c>
-      <c r="E407">
-        <v>0</v>
       </c>
       <c r="F407">
         <v>450384488</v>
@@ -12459,10 +12465,10 @@
         <v>35458361640</v>
       </c>
       <c r="D431">
-        <v>6384932024</v>
+        <v>5934547536</v>
       </c>
       <c r="E431">
-        <v>19149508242</v>
+        <v>19599892730</v>
       </c>
       <c r="F431">
         <v>25534440266</v>
@@ -12478,128 +12484,241 @@
       <c r="A432" t="s">
         <v>8</v>
       </c>
-      <c r="B432">
+      <c r="B432" s="1">
         <v>873740000</v>
       </c>
-      <c r="C432">
+      <c r="C432" s="1">
         <v>873740000</v>
       </c>
-      <c r="D432">
+      <c r="D432" s="1">
         <v>255557500</v>
       </c>
-      <c r="E432">
+      <c r="E432" s="1">
         <v>589750552</v>
       </c>
-      <c r="F432">
+      <c r="F432" s="1">
         <v>845308052</v>
       </c>
-      <c r="G432">
+      <c r="G432" s="1">
         <v>28431948</v>
       </c>
-      <c r="H432">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="H432" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B433" s="1"/>
+      <c r="C433" s="1"/>
+      <c r="D433" s="1"/>
+      <c r="E433" s="1"/>
+      <c r="F433" s="1"/>
+      <c r="G433" s="1"/>
+      <c r="H433" s="1"/>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B434" s="1"/>
+      <c r="C434" s="1"/>
+      <c r="D434" s="1"/>
+      <c r="E434" s="1"/>
+      <c r="F434" s="1"/>
+      <c r="G434" s="1"/>
+      <c r="H434" s="1"/>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B435" s="1"/>
+      <c r="C435" s="1"/>
+      <c r="D435" s="1"/>
+      <c r="E435" s="1"/>
+      <c r="F435" s="1"/>
+      <c r="G435" s="1"/>
+      <c r="H435" s="1"/>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="437" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B436" s="1"/>
+      <c r="C436" s="1"/>
+      <c r="D436" s="1"/>
+      <c r="E436" s="1"/>
+      <c r="F436" s="1"/>
+      <c r="G436" s="1"/>
+      <c r="H436" s="1"/>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="438" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B437" s="1"/>
+      <c r="C437" s="1"/>
+      <c r="D437" s="1"/>
+      <c r="E437" s="1"/>
+      <c r="F437" s="1"/>
+      <c r="G437" s="1"/>
+      <c r="H437" s="1"/>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="439" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B438" s="1"/>
+      <c r="C438" s="1"/>
+      <c r="D438" s="1"/>
+      <c r="E438" s="1"/>
+      <c r="F438" s="1"/>
+      <c r="G438" s="1"/>
+      <c r="H438" s="1"/>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="440" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B439" s="1"/>
+      <c r="C439" s="1"/>
+      <c r="D439" s="1"/>
+      <c r="E439" s="1"/>
+      <c r="F439" s="1"/>
+      <c r="G439" s="1"/>
+      <c r="H439" s="1"/>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="441" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B440" s="1"/>
+      <c r="C440" s="1"/>
+      <c r="D440" s="1"/>
+      <c r="E440" s="1"/>
+      <c r="F440" s="1"/>
+      <c r="G440" s="1"/>
+      <c r="H440" s="1"/>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="442" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B441" s="1"/>
+      <c r="C441" s="1"/>
+      <c r="D441" s="1"/>
+      <c r="E441" s="1"/>
+      <c r="F441" s="1"/>
+      <c r="G441" s="1"/>
+      <c r="H441" s="1"/>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="443" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B442" s="1"/>
+      <c r="C442" s="1"/>
+      <c r="D442" s="1"/>
+      <c r="E442" s="1"/>
+      <c r="F442" s="1"/>
+      <c r="G442" s="1"/>
+      <c r="H442" s="1"/>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="444" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B443" s="1"/>
+      <c r="C443" s="1"/>
+      <c r="D443" s="1"/>
+      <c r="E443" s="1"/>
+      <c r="F443" s="1"/>
+      <c r="G443" s="1"/>
+      <c r="H443" s="1"/>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="445" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B444" s="1"/>
+      <c r="C444" s="1"/>
+      <c r="D444" s="1"/>
+      <c r="E444" s="1"/>
+      <c r="F444" s="1"/>
+      <c r="G444" s="1"/>
+      <c r="H444" s="1"/>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="446" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B445" s="1"/>
+      <c r="C445" s="1"/>
+      <c r="D445" s="1"/>
+      <c r="E445" s="1"/>
+      <c r="F445" s="1"/>
+      <c r="G445" s="1"/>
+      <c r="H445" s="1"/>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="447" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B446" s="1"/>
+      <c r="C446" s="1"/>
+      <c r="D446" s="1"/>
+      <c r="E446" s="1"/>
+      <c r="F446" s="1"/>
+      <c r="G446" s="1"/>
+      <c r="H446" s="1"/>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="448" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B447" s="1"/>
+      <c r="C447" s="1"/>
+      <c r="D447" s="1"/>
+      <c r="E447" s="1"/>
+      <c r="F447" s="1"/>
+      <c r="G447" s="1"/>
+      <c r="H447" s="1"/>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>106</v>
       </c>
+      <c r="B448" s="1"/>
+      <c r="C448" s="1"/>
+      <c r="D448" s="1"/>
+      <c r="E448" s="1"/>
+      <c r="F448" s="1"/>
+      <c r="G448" s="1"/>
+      <c r="H448" s="1"/>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>54</v>
       </c>
-      <c r="B449">
+      <c r="B449" s="1">
         <v>474786000</v>
       </c>
-      <c r="C449">
+      <c r="C449" s="1">
         <v>474786000</v>
       </c>
-      <c r="D449">
+      <c r="D449" s="1">
         <v>474154600</v>
       </c>
-      <c r="F449">
+      <c r="E449" s="1"/>
+      <c r="F449" s="1">
         <v>474154600</v>
       </c>
-      <c r="G449">
+      <c r="G449" s="1">
         <v>631400</v>
       </c>
-      <c r="H449">
+      <c r="H449" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12607,22 +12726,23 @@
       <c r="A450" t="s">
         <v>13</v>
       </c>
-      <c r="B450">
+      <c r="B450" s="1">
         <v>208424730</v>
       </c>
-      <c r="C450">
+      <c r="C450" s="1">
         <v>208424730</v>
       </c>
-      <c r="D450">
+      <c r="D450" s="1">
         <v>180590600</v>
       </c>
-      <c r="F450">
+      <c r="E450" s="1"/>
+      <c r="F450" s="1">
         <v>180590600</v>
       </c>
-      <c r="G450">
+      <c r="G450" s="1">
         <v>27834130</v>
       </c>
-      <c r="H450">
+      <c r="H450" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12630,25 +12750,25 @@
       <c r="A451" t="s">
         <v>15</v>
       </c>
-      <c r="B451">
+      <c r="B451" s="1">
         <v>20000000</v>
       </c>
-      <c r="C451">
+      <c r="C451" s="1">
         <v>20000000</v>
       </c>
-      <c r="D451">
-        <v>0</v>
-      </c>
-      <c r="E451">
+      <c r="D451" s="1">
+        <v>0</v>
+      </c>
+      <c r="E451" s="1">
         <v>13970000</v>
       </c>
-      <c r="F451">
+      <c r="F451" s="1">
         <v>13970000</v>
       </c>
-      <c r="G451">
+      <c r="G451" s="1">
         <v>6030000</v>
       </c>
-      <c r="H451">
+      <c r="H451" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12656,25 +12776,25 @@
       <c r="A452" t="s">
         <v>16</v>
       </c>
-      <c r="B452">
+      <c r="B452" s="1">
         <v>220000000</v>
       </c>
-      <c r="C452">
+      <c r="C452" s="1">
         <v>220000000</v>
       </c>
-      <c r="D452">
+      <c r="D452" s="1">
         <v>78580000</v>
       </c>
-      <c r="E452">
+      <c r="E452" s="1">
         <v>59808678</v>
       </c>
-      <c r="F452">
+      <c r="F452" s="1">
         <v>138388678</v>
       </c>
-      <c r="G452">
+      <c r="G452" s="1">
         <v>81611322</v>
       </c>
-      <c r="H452">
+      <c r="H452" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12682,22 +12802,23 @@
       <c r="A453" t="s">
         <v>58</v>
       </c>
-      <c r="B453">
+      <c r="B453" s="1">
         <v>75000000</v>
       </c>
-      <c r="C453">
+      <c r="C453" s="1">
         <v>75000000</v>
       </c>
-      <c r="D453">
+      <c r="D453" s="1">
         <v>38500000</v>
       </c>
-      <c r="F453">
+      <c r="E453" s="1"/>
+      <c r="F453" s="1">
         <v>38500000</v>
       </c>
-      <c r="G453">
+      <c r="G453" s="1">
         <v>36500000</v>
       </c>
-      <c r="H453">
+      <c r="H453" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12705,35 +12826,49 @@
       <c r="A454" t="s">
         <v>107</v>
       </c>
+      <c r="B454" s="1"/>
+      <c r="C454" s="1"/>
+      <c r="D454" s="1"/>
+      <c r="E454" s="1"/>
+      <c r="F454" s="1"/>
+      <c r="G454" s="1"/>
+      <c r="H454" s="1"/>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>108</v>
       </c>
+      <c r="B455" s="1"/>
+      <c r="C455" s="1"/>
+      <c r="D455" s="1"/>
+      <c r="E455" s="1"/>
+      <c r="F455" s="1"/>
+      <c r="G455" s="1"/>
+      <c r="H455" s="1"/>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>23</v>
       </c>
-      <c r="B456">
+      <c r="B456" s="1">
         <v>60000000</v>
       </c>
-      <c r="C456">
+      <c r="C456" s="1">
         <v>45000000</v>
       </c>
-      <c r="D456">
+      <c r="D456" s="1">
         <v>7388000</v>
       </c>
-      <c r="E456">
+      <c r="E456" s="1">
         <v>10120000</v>
       </c>
-      <c r="F456">
+      <c r="F456" s="1">
         <v>17508000</v>
       </c>
-      <c r="G456">
+      <c r="G456" s="1">
         <v>27492000</v>
       </c>
-      <c r="H456">
+      <c r="H456" s="1">
         <v>15000000</v>
       </c>
     </row>
@@ -12741,25 +12876,25 @@
       <c r="A457" t="s">
         <v>63</v>
       </c>
-      <c r="B457">
+      <c r="B457" s="1">
         <v>45150000</v>
       </c>
-      <c r="C457">
+      <c r="C457" s="1">
         <v>45150000</v>
       </c>
-      <c r="D457">
+      <c r="D457" s="1">
         <v>7130850</v>
       </c>
-      <c r="E457">
+      <c r="E457" s="1">
         <v>20796200</v>
       </c>
-      <c r="F457">
+      <c r="F457" s="1">
         <v>27927050</v>
       </c>
-      <c r="G457">
+      <c r="G457" s="1">
         <v>17222950</v>
       </c>
-      <c r="H457">
+      <c r="H457" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12767,64 +12902,129 @@
       <c r="A458" t="s">
         <v>24</v>
       </c>
+      <c r="B458" s="1"/>
+      <c r="C458" s="1"/>
+      <c r="D458" s="1"/>
+      <c r="E458" s="1"/>
+      <c r="F458" s="1"/>
+      <c r="G458" s="1"/>
+      <c r="H458" s="1"/>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>109</v>
       </c>
+      <c r="B459" s="1"/>
+      <c r="C459" s="1"/>
+      <c r="D459" s="1"/>
+      <c r="E459" s="1"/>
+      <c r="F459" s="1"/>
+      <c r="G459" s="1"/>
+      <c r="H459" s="1"/>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>110</v>
       </c>
+      <c r="B460" s="1"/>
+      <c r="C460" s="1"/>
+      <c r="D460" s="1"/>
+      <c r="E460" s="1"/>
+      <c r="F460" s="1"/>
+      <c r="G460" s="1"/>
+      <c r="H460" s="1"/>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>111</v>
       </c>
+      <c r="B461" s="1"/>
+      <c r="C461" s="1"/>
+      <c r="D461" s="1"/>
+      <c r="E461" s="1"/>
+      <c r="F461" s="1"/>
+      <c r="G461" s="1"/>
+      <c r="H461" s="1"/>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>112</v>
       </c>
+      <c r="B462" s="1"/>
+      <c r="C462" s="1"/>
+      <c r="D462" s="1"/>
+      <c r="E462" s="1"/>
+      <c r="F462" s="1"/>
+      <c r="G462" s="1"/>
+      <c r="H462" s="1"/>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>113</v>
       </c>
+      <c r="B463" s="1"/>
+      <c r="C463" s="1"/>
+      <c r="D463" s="1"/>
+      <c r="E463" s="1"/>
+      <c r="F463" s="1"/>
+      <c r="G463" s="1"/>
+      <c r="H463" s="1"/>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>114</v>
       </c>
+      <c r="B464" s="1"/>
+      <c r="C464" s="1"/>
+      <c r="D464" s="1"/>
+      <c r="E464" s="1"/>
+      <c r="F464" s="1"/>
+      <c r="G464" s="1"/>
+      <c r="H464" s="1"/>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>115</v>
       </c>
+      <c r="B465" s="1"/>
+      <c r="C465" s="1"/>
+      <c r="D465" s="1"/>
+      <c r="E465" s="1"/>
+      <c r="F465" s="1"/>
+      <c r="G465" s="1"/>
+      <c r="H465" s="1"/>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>116</v>
       </c>
+      <c r="B466" s="1"/>
+      <c r="C466" s="1"/>
+      <c r="D466" s="1"/>
+      <c r="E466" s="1"/>
+      <c r="F466" s="1"/>
+      <c r="G466" s="1"/>
+      <c r="H466" s="1"/>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>26</v>
       </c>
-      <c r="B467">
+      <c r="B467" s="1">
         <v>6000000</v>
       </c>
-      <c r="C467">
+      <c r="C467" s="1">
         <v>4500000</v>
       </c>
-      <c r="D467">
-        <v>0</v>
-      </c>
-      <c r="G467">
+      <c r="D467" s="1">
+        <v>0</v>
+      </c>
+      <c r="E467" s="1"/>
+      <c r="F467" s="1"/>
+      <c r="G467" s="1">
         <v>4500000</v>
       </c>
-      <c r="H467">
+      <c r="H467" s="1">
         <v>1500000</v>
       </c>
     </row>
@@ -12832,25 +13032,25 @@
       <c r="A468" t="s">
         <v>27</v>
       </c>
-      <c r="B468">
+      <c r="B468" s="1">
         <v>41000000</v>
       </c>
-      <c r="C468">
+      <c r="C468" s="1">
         <v>30750000</v>
       </c>
-      <c r="D468">
+      <c r="D468" s="1">
         <v>5091000</v>
       </c>
-      <c r="E468">
+      <c r="E468" s="1">
         <v>4982700</v>
       </c>
-      <c r="F468">
+      <c r="F468" s="1">
         <v>10073700</v>
       </c>
-      <c r="G468">
+      <c r="G468" s="1">
         <v>20676300</v>
       </c>
-      <c r="H468">
+      <c r="H468" s="1">
         <v>10250000</v>
       </c>
     </row>
@@ -12858,19 +13058,21 @@
       <c r="A469" t="s">
         <v>28</v>
       </c>
-      <c r="B469">
+      <c r="B469" s="1">
         <v>12000000</v>
       </c>
-      <c r="C469">
+      <c r="C469" s="1">
         <v>3000000</v>
       </c>
-      <c r="D469">
-        <v>0</v>
-      </c>
-      <c r="G469">
+      <c r="D469" s="1">
+        <v>0</v>
+      </c>
+      <c r="E469" s="1"/>
+      <c r="F469" s="1"/>
+      <c r="G469" s="1">
         <v>3000000</v>
       </c>
-      <c r="H469">
+      <c r="H469" s="1">
         <v>9000000</v>
       </c>
     </row>
@@ -12878,25 +13080,25 @@
       <c r="A470" t="s">
         <v>29</v>
       </c>
-      <c r="B470">
+      <c r="B470" s="1">
         <v>171000000</v>
       </c>
-      <c r="C470">
+      <c r="C470" s="1">
         <v>128250000</v>
       </c>
-      <c r="D470">
+      <c r="D470" s="1">
         <v>17585000</v>
       </c>
-      <c r="E470">
+      <c r="E470" s="1">
         <v>20876000</v>
       </c>
-      <c r="F470">
+      <c r="F470" s="1">
         <v>38461000</v>
       </c>
-      <c r="G470">
+      <c r="G470" s="1">
         <v>89789000</v>
       </c>
-      <c r="H470">
+      <c r="H470" s="1">
         <v>42750000</v>
       </c>
     </row>
@@ -12904,25 +13106,25 @@
       <c r="A471" t="s">
         <v>31</v>
       </c>
-      <c r="B471">
+      <c r="B471" s="1">
         <v>130000000</v>
       </c>
-      <c r="C471">
+      <c r="C471" s="1">
         <v>97500000</v>
       </c>
-      <c r="D471">
+      <c r="D471" s="1">
         <v>23953308</v>
       </c>
-      <c r="E471">
+      <c r="E471" s="1">
         <v>59537750</v>
       </c>
-      <c r="F471">
+      <c r="F471" s="1">
         <v>83491058</v>
       </c>
-      <c r="G471">
+      <c r="G471" s="1">
         <v>14008942</v>
       </c>
-      <c r="H471">
+      <c r="H471" s="1">
         <v>32500000</v>
       </c>
     </row>
@@ -12930,25 +13132,25 @@
       <c r="A472" t="s">
         <v>83</v>
       </c>
-      <c r="B472">
+      <c r="B472" s="1">
         <v>6660000</v>
       </c>
-      <c r="C472">
+      <c r="C472" s="1">
         <v>6660000</v>
       </c>
-      <c r="D472">
-        <v>0</v>
-      </c>
-      <c r="E472">
+      <c r="D472" s="1">
+        <v>0</v>
+      </c>
+      <c r="E472" s="1">
         <v>4246644</v>
       </c>
-      <c r="F472">
+      <c r="F472" s="1">
         <v>4246644</v>
       </c>
-      <c r="G472">
+      <c r="G472" s="1">
         <v>2413356</v>
       </c>
-      <c r="H472">
+      <c r="H472" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12956,25 +13158,25 @@
       <c r="A473" t="s">
         <v>32</v>
       </c>
-      <c r="B473">
+      <c r="B473" s="1">
         <v>6000000</v>
       </c>
-      <c r="C473">
+      <c r="C473" s="1">
         <v>6000000</v>
       </c>
-      <c r="D473">
-        <v>0</v>
-      </c>
-      <c r="E473">
+      <c r="D473" s="1">
+        <v>0</v>
+      </c>
+      <c r="E473" s="1">
         <v>5982000</v>
       </c>
-      <c r="F473">
+      <c r="F473" s="1">
         <v>5982000</v>
       </c>
-      <c r="G473">
+      <c r="G473" s="1">
         <v>18000</v>
       </c>
-      <c r="H473">
+      <c r="H473" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12982,71 +13184,169 @@
       <c r="A474" t="s">
         <v>77</v>
       </c>
+      <c r="B474" s="1"/>
+      <c r="C474" s="1"/>
+      <c r="D474" s="1"/>
+      <c r="E474" s="1"/>
+      <c r="F474" s="1"/>
+      <c r="G474" s="1"/>
+      <c r="H474" s="1"/>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>65</v>
       </c>
+      <c r="B475" s="1"/>
+      <c r="C475" s="1"/>
+      <c r="D475" s="1"/>
+      <c r="E475" s="1"/>
+      <c r="F475" s="1"/>
+      <c r="G475" s="1"/>
+      <c r="H475" s="1"/>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>33</v>
       </c>
+      <c r="B476" s="1"/>
+      <c r="C476" s="1"/>
+      <c r="D476" s="1"/>
+      <c r="E476" s="1"/>
+      <c r="F476" s="1"/>
+      <c r="G476" s="1"/>
+      <c r="H476" s="1"/>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>78</v>
       </c>
+      <c r="B477" s="1"/>
+      <c r="C477" s="1"/>
+      <c r="D477" s="1"/>
+      <c r="E477" s="1"/>
+      <c r="F477" s="1"/>
+      <c r="G477" s="1"/>
+      <c r="H477" s="1"/>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>117</v>
       </c>
+      <c r="B478" s="1"/>
+      <c r="C478" s="1"/>
+      <c r="D478" s="1"/>
+      <c r="E478" s="1"/>
+      <c r="F478" s="1"/>
+      <c r="G478" s="1"/>
+      <c r="H478" s="1"/>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>34</v>
       </c>
+      <c r="B479" s="1"/>
+      <c r="C479" s="1"/>
+      <c r="D479" s="1"/>
+      <c r="E479" s="1"/>
+      <c r="F479" s="1"/>
+      <c r="G479" s="1"/>
+      <c r="H479" s="1"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>35</v>
       </c>
+      <c r="B480" s="1"/>
+      <c r="C480" s="1"/>
+      <c r="D480" s="1"/>
+      <c r="E480" s="1"/>
+      <c r="F480" s="1"/>
+      <c r="G480" s="1"/>
+      <c r="H480" s="1"/>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>36</v>
       </c>
+      <c r="B481" s="1"/>
+      <c r="C481" s="1"/>
+      <c r="D481" s="1"/>
+      <c r="E481" s="1"/>
+      <c r="F481" s="1"/>
+      <c r="G481" s="1"/>
+      <c r="H481" s="1"/>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>37</v>
       </c>
+      <c r="B482" s="1"/>
+      <c r="C482" s="1"/>
+      <c r="D482" s="1"/>
+      <c r="E482" s="1"/>
+      <c r="F482" s="1"/>
+      <c r="G482" s="1"/>
+      <c r="H482" s="1"/>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>38</v>
       </c>
+      <c r="B483" s="1"/>
+      <c r="C483" s="1"/>
+      <c r="D483" s="1"/>
+      <c r="E483" s="1"/>
+      <c r="F483" s="1"/>
+      <c r="G483" s="1"/>
+      <c r="H483" s="1"/>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>40</v>
       </c>
+      <c r="B484" s="1"/>
+      <c r="C484" s="1"/>
+      <c r="D484" s="1"/>
+      <c r="E484" s="1"/>
+      <c r="F484" s="1"/>
+      <c r="G484" s="1"/>
+      <c r="H484" s="1"/>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>41</v>
       </c>
+      <c r="B485" s="1"/>
+      <c r="C485" s="1"/>
+      <c r="D485" s="1"/>
+      <c r="E485" s="1"/>
+      <c r="F485" s="1"/>
+      <c r="G485" s="1"/>
+      <c r="H485" s="1"/>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>47</v>
       </c>
+      <c r="B486" s="1"/>
+      <c r="C486" s="1"/>
+      <c r="D486" s="1"/>
+      <c r="E486" s="1"/>
+      <c r="F486" s="1"/>
+      <c r="G486" s="1"/>
+      <c r="H486" s="1"/>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>118</v>
       </c>
+      <c r="B487" s="1"/>
+      <c r="C487" s="1"/>
+      <c r="D487" s="1"/>
+      <c r="E487" s="1"/>
+      <c r="F487" s="1"/>
+      <c r="G487" s="1"/>
+      <c r="H487" s="1"/>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
@@ -13267,16 +13567,16 @@
         <v>4989900000</v>
       </c>
       <c r="D496">
-        <v>1084501677</v>
+        <v>2356509177</v>
       </c>
       <c r="E496">
-        <v>1195602104</v>
+        <v>1304104604</v>
       </c>
       <c r="F496">
-        <v>2280103781</v>
+        <v>3660613781</v>
       </c>
       <c r="G496">
-        <v>2709796219</v>
+        <v>1329286219</v>
       </c>
       <c r="H496">
         <v>0</v>
@@ -13371,16 +13671,16 @@
         <v>624500000</v>
       </c>
       <c r="D500">
-        <v>451541348</v>
+        <v>619585348</v>
       </c>
       <c r="E500">
         <v>0</v>
       </c>
       <c r="F500">
-        <v>451541348</v>
+        <v>619585348</v>
       </c>
       <c r="G500">
-        <v>172958652</v>
+        <v>4914652</v>
       </c>
       <c r="H500">
         <v>0</v>
@@ -13631,10 +13931,10 @@
         <v>2560000000</v>
       </c>
       <c r="D510">
-        <v>27679647</v>
+        <v>10404406</v>
       </c>
       <c r="E510">
-        <v>1462801099</v>
+        <v>1480076340</v>
       </c>
       <c r="F510">
         <v>1490480746</v>
@@ -13764,13 +14064,13 @@
         <v>55116560</v>
       </c>
       <c r="E515">
-        <v>296898428</v>
+        <v>296973428</v>
       </c>
       <c r="F515">
-        <v>352014988</v>
+        <v>352089988</v>
       </c>
       <c r="G515">
-        <v>164418512</v>
+        <v>164343512</v>
       </c>
       <c r="H515">
         <v>172144500</v>
@@ -13787,10 +14087,10 @@
         <v>36180000</v>
       </c>
       <c r="D516">
-        <v>2943006</v>
+        <v>2747000</v>
       </c>
       <c r="E516">
-        <v>10378562</v>
+        <v>10574568</v>
       </c>
       <c r="F516">
         <v>13321568</v>
@@ -13946,13 +14246,13 @@
         <v>446366</v>
       </c>
       <c r="E522">
-        <v>7944037280</v>
+        <v>7944041030</v>
       </c>
       <c r="F522">
-        <v>7944483646</v>
+        <v>7944487396</v>
       </c>
       <c r="G522">
-        <v>4219798251</v>
+        <v>4219794501</v>
       </c>
       <c r="H522">
         <v>0</v>
@@ -14177,16 +14477,16 @@
         <v>64019485320</v>
       </c>
       <c r="D531">
-        <v>14148938452</v>
+        <v>15571518705</v>
       </c>
       <c r="E531">
-        <v>36388885827</v>
+        <v>36514938324</v>
       </c>
       <c r="F531">
-        <v>50537824279</v>
+        <v>52086457029</v>
       </c>
       <c r="G531">
-        <v>13481661041</v>
+        <v>11933028291</v>
       </c>
       <c r="H531">
         <v>850782250</v>
@@ -15028,23 +15328,23 @@
       <c r="A564" t="s">
         <v>129</v>
       </c>
-      <c r="B564" s="1">
-        <v>1118580000000</v>
-      </c>
-      <c r="C564" s="1">
-        <v>1109040000000</v>
-      </c>
-      <c r="D564" s="1">
-        <v>427398000000</v>
-      </c>
-      <c r="E564" s="1">
-        <v>500024000000</v>
-      </c>
-      <c r="F564" s="1">
-        <v>927422000000</v>
-      </c>
-      <c r="G564" s="1">
-        <v>181623000000</v>
+      <c r="B564">
+        <v>1118576863411</v>
+      </c>
+      <c r="C564">
+        <v>1109044586089</v>
+      </c>
+      <c r="D564">
+        <v>429038071112</v>
+      </c>
+      <c r="E564">
+        <v>502822598015</v>
+      </c>
+      <c r="F564">
+        <v>931860669127</v>
+      </c>
+      <c r="G564">
+        <v>177183916962</v>
       </c>
       <c r="H564">
         <v>9532277322</v>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{30D458A9-4667-4C07-809A-F1462F6B9E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{DF2C92B1-0A59-4505-9E68-3664D19B70A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="3096" windowWidth="17280" windowHeight="9180"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="20260820 SAP" sheetId="1" r:id="rId1"/>
+    <sheet name="20260821 SAP" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -1311,16 +1311,16 @@
         <v>109317656175</v>
       </c>
       <c r="D2">
-        <v>102171671229</v>
+        <v>99268647251</v>
       </c>
       <c r="E2">
-        <v>6903708916</v>
+        <v>8267348916</v>
       </c>
       <c r="F2">
-        <v>109075380145</v>
+        <v>107535996167</v>
       </c>
       <c r="G2">
-        <v>242276030</v>
+        <v>1781660008</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1519,16 +1519,16 @@
         <v>579317296</v>
       </c>
       <c r="D10">
-        <v>147606375</v>
+        <v>197598375</v>
       </c>
       <c r="E10">
         <v>192718055</v>
       </c>
       <c r="F10">
-        <v>340324430</v>
+        <v>390316430</v>
       </c>
       <c r="G10">
-        <v>238992866</v>
+        <v>189000866</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1805,10 +1805,10 @@
         <v>510385000</v>
       </c>
       <c r="D21">
-        <v>59254000</v>
+        <v>56515100</v>
       </c>
       <c r="E21">
-        <v>81818137</v>
+        <v>84557037</v>
       </c>
       <c r="F21">
         <v>141072137</v>
@@ -1903,22 +1903,22 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>2348896421</v>
+        <v>2330417149</v>
       </c>
       <c r="C25">
-        <v>1723896421</v>
+        <v>1705417149</v>
       </c>
       <c r="D25">
-        <v>1842700</v>
+        <v>21639448</v>
       </c>
       <c r="E25">
-        <v>989684993</v>
+        <v>995797493</v>
       </c>
       <c r="F25">
-        <v>991527693</v>
+        <v>1017436941</v>
       </c>
       <c r="G25">
-        <v>732368728</v>
+        <v>687980208</v>
       </c>
       <c r="H25">
         <v>625000000</v>
@@ -1990,13 +1990,13 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2531501544</v>
+        <v>2531752794</v>
       </c>
       <c r="F28">
-        <v>2531501544</v>
+        <v>2531752794</v>
       </c>
       <c r="G28">
-        <v>925112660</v>
+        <v>924861410</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2345,22 +2345,22 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>350809641207</v>
+        <v>350791161935</v>
       </c>
       <c r="C42">
-        <v>348392141207</v>
+        <v>348373661935</v>
       </c>
       <c r="D42">
-        <v>240559911763</v>
+        <v>237723937633</v>
       </c>
       <c r="E42">
-        <v>90367437122</v>
+        <v>91740179772</v>
       </c>
       <c r="F42">
-        <v>330927348885</v>
+        <v>329464117405</v>
       </c>
       <c r="G42">
-        <v>17464792322</v>
+        <v>18909544530</v>
       </c>
       <c r="H42">
         <v>2417500000</v>
@@ -2377,10 +2377,10 @@
         <v>26681487101</v>
       </c>
       <c r="D43">
-        <v>19821699101</v>
+        <v>19324699101</v>
       </c>
       <c r="E43">
-        <v>6401038000</v>
+        <v>6898038000</v>
       </c>
       <c r="F43">
         <v>26222737101</v>
@@ -2689,10 +2689,10 @@
         <v>4260000000</v>
       </c>
       <c r="D55">
-        <v>1084689625</v>
+        <v>972608694</v>
       </c>
       <c r="E55">
-        <v>1898777927</v>
+        <v>2010858858</v>
       </c>
       <c r="F55">
         <v>2983467552</v>
@@ -2767,10 +2767,10 @@
         <v>250000000</v>
       </c>
       <c r="D58">
-        <v>85514462</v>
+        <v>75748702</v>
       </c>
       <c r="E58">
-        <v>64039200</v>
+        <v>73804960</v>
       </c>
       <c r="F58">
         <v>149553662</v>
@@ -3134,13 +3134,13 @@
         <v>46676000</v>
       </c>
       <c r="E72">
-        <v>251265500</v>
+        <v>252103000</v>
       </c>
       <c r="F72">
-        <v>297941500</v>
+        <v>298779000</v>
       </c>
       <c r="G72">
-        <v>56283500</v>
+        <v>55446000</v>
       </c>
       <c r="H72">
         <v>118075000</v>
@@ -3212,13 +3212,13 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>14912382774</v>
+        <v>14912409024</v>
       </c>
       <c r="F75">
-        <v>14912382774</v>
+        <v>14912409024</v>
       </c>
       <c r="G75">
-        <v>8019224455</v>
+        <v>8019198205</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -3443,16 +3443,16 @@
         <v>110881210191</v>
       </c>
       <c r="D84">
-        <v>36254196171</v>
+        <v>35635349480</v>
       </c>
       <c r="E84">
-        <v>50653283595</v>
+        <v>51272994036</v>
       </c>
       <c r="F84">
-        <v>86907479766</v>
+        <v>86908343516</v>
       </c>
       <c r="G84">
-        <v>23973730425</v>
+        <v>23972866675</v>
       </c>
       <c r="H84">
         <v>671501500</v>
@@ -3651,10 +3651,10 @@
         <v>1210765056</v>
       </c>
       <c r="D92">
-        <v>484301940</v>
+        <v>470801940</v>
       </c>
       <c r="E92">
-        <v>122034440</v>
+        <v>135534440</v>
       </c>
       <c r="F92">
         <v>606336380</v>
@@ -3703,16 +3703,16 @@
         <v>2796520000</v>
       </c>
       <c r="D94">
-        <v>762748514</v>
+        <v>814560594</v>
       </c>
       <c r="E94">
         <v>1905663067</v>
       </c>
       <c r="F94">
-        <v>2668411581</v>
+        <v>2720223661</v>
       </c>
       <c r="G94">
-        <v>128108419</v>
+        <v>76296339</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -4044,13 +4044,13 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>289653568</v>
+        <v>290028568</v>
       </c>
       <c r="F107">
-        <v>289653568</v>
+        <v>290028568</v>
       </c>
       <c r="G107">
-        <v>5403932</v>
+        <v>5028932</v>
       </c>
       <c r="H107">
         <v>98352500</v>
@@ -4174,13 +4174,13 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>10802556465</v>
+        <v>10802575215</v>
       </c>
       <c r="F112">
-        <v>10802556465</v>
+        <v>10802575215</v>
       </c>
       <c r="G112">
-        <v>5421088388</v>
+        <v>5421069638</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -4405,16 +4405,16 @@
         <v>81693644736</v>
       </c>
       <c r="D121">
-        <v>16833893009</v>
+        <v>16872205089</v>
       </c>
       <c r="E121">
-        <v>47661934574</v>
+        <v>47675828324</v>
       </c>
       <c r="F121">
-        <v>64495827583</v>
+        <v>64548033413</v>
       </c>
       <c r="G121">
-        <v>17197817153</v>
+        <v>17145611323</v>
       </c>
       <c r="H121">
         <v>475697500</v>
@@ -4769,10 +4769,10 @@
         <v>700000000</v>
       </c>
       <c r="D135">
-        <v>303621218</v>
+        <v>0</v>
       </c>
       <c r="E135">
-        <v>388459396</v>
+        <v>692080614</v>
       </c>
       <c r="F135">
         <v>692080614</v>
@@ -4899,16 +4899,16 @@
         <v>265950000</v>
       </c>
       <c r="D140">
-        <v>56039000</v>
+        <v>20030924</v>
       </c>
       <c r="E140">
-        <v>164359200</v>
+        <v>200998200</v>
       </c>
       <c r="F140">
-        <v>220398200</v>
+        <v>221029124</v>
       </c>
       <c r="G140">
-        <v>45551800</v>
+        <v>44920876</v>
       </c>
       <c r="H140">
         <v>88650000</v>
@@ -4980,13 +4980,13 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>136134750</v>
+        <v>136422250</v>
       </c>
       <c r="F143">
-        <v>136134750</v>
+        <v>136422250</v>
       </c>
       <c r="G143">
-        <v>23855250</v>
+        <v>23567750</v>
       </c>
       <c r="H143">
         <v>53330000</v>
@@ -5058,13 +5058,13 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>6377668982</v>
+        <v>6377672732</v>
       </c>
       <c r="F146">
-        <v>6377668982</v>
+        <v>6377672732</v>
       </c>
       <c r="G146">
-        <v>3571425101</v>
+        <v>3571421351</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -5289,16 +5289,16 @@
         <v>52173056175</v>
       </c>
       <c r="D155">
-        <v>12293745954</v>
+        <v>11954116660</v>
       </c>
       <c r="E155">
-        <v>27840332694</v>
+        <v>28180884162</v>
       </c>
       <c r="F155">
-        <v>40134078648</v>
+        <v>40135000822</v>
       </c>
       <c r="G155">
-        <v>12038977527</v>
+        <v>12038055353</v>
       </c>
       <c r="H155">
         <v>411080000</v>
@@ -6199,16 +6199,16 @@
         <v>7317456560</v>
       </c>
       <c r="D190">
-        <v>6099432947</v>
+        <v>6104309220</v>
       </c>
       <c r="E190">
         <v>1212495000</v>
       </c>
       <c r="F190">
-        <v>7311927947</v>
+        <v>7316804220</v>
       </c>
       <c r="G190">
-        <v>5528613</v>
+        <v>652340</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>3919663677</v>
       </c>
       <c r="D195">
-        <v>3271708605</v>
+        <v>3221908605</v>
       </c>
       <c r="E195">
-        <v>480523683</v>
+        <v>530323683</v>
       </c>
       <c r="F195">
         <v>3752232288</v>
@@ -6771,16 +6771,16 @@
         <v>97500000</v>
       </c>
       <c r="D212">
-        <v>12638456</v>
+        <v>16038456</v>
       </c>
       <c r="E212">
         <v>61832951</v>
       </c>
       <c r="F212">
-        <v>74471407</v>
+        <v>77871407</v>
       </c>
       <c r="G212">
-        <v>23028593</v>
+        <v>19628593</v>
       </c>
       <c r="H212">
         <v>32500000</v>
@@ -6797,16 +6797,16 @@
         <v>385534500</v>
       </c>
       <c r="D213">
-        <v>29096000</v>
+        <v>51096000</v>
       </c>
       <c r="E213">
         <v>250862000</v>
       </c>
       <c r="F213">
-        <v>279958000</v>
+        <v>301958000</v>
       </c>
       <c r="G213">
-        <v>105576500</v>
+        <v>83576500</v>
       </c>
       <c r="H213">
         <v>128511500</v>
@@ -6849,16 +6849,16 @@
         <v>337500000</v>
       </c>
       <c r="D215">
-        <v>55213890</v>
+        <v>71493039</v>
       </c>
       <c r="E215">
         <v>103870954</v>
       </c>
       <c r="F215">
-        <v>159084844</v>
+        <v>175363993</v>
       </c>
       <c r="G215">
-        <v>178415156</v>
+        <v>162136007</v>
       </c>
       <c r="H215">
         <v>112500000</v>
@@ -6904,13 +6904,13 @@
         <v>0</v>
       </c>
       <c r="E217">
-        <v>165588000</v>
+        <v>165969250</v>
       </c>
       <c r="F217">
-        <v>165588000</v>
+        <v>165969250</v>
       </c>
       <c r="G217">
-        <v>23412000</v>
+        <v>23030750</v>
       </c>
       <c r="H217">
         <v>63000000</v>
@@ -6927,16 +6927,16 @@
         <v>18000000</v>
       </c>
       <c r="D218">
-        <v>1795000</v>
+        <v>3590000</v>
       </c>
       <c r="E218">
         <v>7935118</v>
       </c>
       <c r="F218">
-        <v>9730118</v>
+        <v>11525118</v>
       </c>
       <c r="G218">
-        <v>8269882</v>
+        <v>6474882</v>
       </c>
       <c r="H218">
         <v>0</v>
@@ -6982,13 +6982,13 @@
         <v>0</v>
       </c>
       <c r="E220">
-        <v>6348287104</v>
+        <v>6348292729</v>
       </c>
       <c r="F220">
-        <v>6348287104</v>
+        <v>6348292729</v>
       </c>
       <c r="G220">
-        <v>3474875022</v>
+        <v>3474869397</v>
       </c>
       <c r="H220">
         <v>0</v>
@@ -7187,16 +7187,16 @@
         <v>47499233545</v>
       </c>
       <c r="D228">
-        <v>15286727760</v>
+        <v>15285278182</v>
       </c>
       <c r="E228">
-        <v>23694926341</v>
+        <v>23745113216</v>
       </c>
       <c r="F228">
-        <v>38981654101</v>
+        <v>39030391398</v>
       </c>
       <c r="G228">
-        <v>8517579444</v>
+        <v>8468842147</v>
       </c>
       <c r="H228">
         <v>415261500</v>
@@ -7239,10 +7239,10 @@
         <v>1126306000</v>
       </c>
       <c r="D230">
-        <v>1105008967</v>
+        <v>1101323967</v>
       </c>
       <c r="E230">
-        <v>8751007</v>
+        <v>12436007</v>
       </c>
       <c r="F230">
         <v>1113759974</v>
@@ -7369,16 +7369,16 @@
         <v>1380000000</v>
       </c>
       <c r="D235">
-        <v>124902500</v>
+        <v>114445500</v>
       </c>
       <c r="E235">
-        <v>1004784967</v>
+        <v>1022581967</v>
       </c>
       <c r="F235">
-        <v>1129687467</v>
+        <v>1137027467</v>
       </c>
       <c r="G235">
-        <v>250312533</v>
+        <v>242972533</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -7395,10 +7395,10 @@
         <v>350000000</v>
       </c>
       <c r="D236">
+        <v>0</v>
+      </c>
+      <c r="E236">
         <v>11786500</v>
-      </c>
-      <c r="E236">
-        <v>0</v>
       </c>
       <c r="F236">
         <v>11786500</v>
@@ -7473,10 +7473,10 @@
         <v>2264065000</v>
       </c>
       <c r="D239">
-        <v>188515000</v>
+        <v>185595000</v>
       </c>
       <c r="E239">
-        <v>1999242000</v>
+        <v>2002162000</v>
       </c>
       <c r="F239">
         <v>2187757000</v>
@@ -8019,16 +8019,16 @@
         <v>48914772555</v>
       </c>
       <c r="D260">
-        <v>12148816565</v>
+        <v>12119968065</v>
       </c>
       <c r="E260">
-        <v>26362292544</v>
+        <v>26398481044</v>
       </c>
       <c r="F260">
-        <v>38511109109</v>
+        <v>38518449109</v>
       </c>
       <c r="G260">
-        <v>10403663446</v>
+        <v>10396323446</v>
       </c>
       <c r="H260">
         <v>525212165</v>
@@ -8045,10 +8045,10 @@
         <v>5695069150</v>
       </c>
       <c r="D261">
-        <v>4883299600</v>
+        <v>4688699600</v>
       </c>
       <c r="E261">
-        <v>718522000</v>
+        <v>913122000</v>
       </c>
       <c r="F261">
         <v>5601821600</v>
@@ -8071,10 +8071,10 @@
         <v>1540000000</v>
       </c>
       <c r="D262">
-        <v>471156189</v>
+        <v>441312000</v>
       </c>
       <c r="E262">
-        <v>754599517</v>
+        <v>784443706</v>
       </c>
       <c r="F262">
         <v>1225755706</v>
@@ -8227,16 +8227,16 @@
         <v>1700000000</v>
       </c>
       <c r="D268">
-        <v>719209140</v>
+        <v>730395140</v>
       </c>
       <c r="E268">
-        <v>727767755</v>
+        <v>764581755</v>
       </c>
       <c r="F268">
-        <v>1446976895</v>
+        <v>1494976895</v>
       </c>
       <c r="G268">
-        <v>253023105</v>
+        <v>205023105</v>
       </c>
       <c r="H268">
         <v>0</v>
@@ -8279,10 +8279,10 @@
         <v>1240000000</v>
       </c>
       <c r="D270">
-        <v>900484492</v>
+        <v>883234492</v>
       </c>
       <c r="E270">
-        <v>99633614</v>
+        <v>116883614</v>
       </c>
       <c r="F270">
         <v>1000118106</v>
@@ -8331,10 +8331,10 @@
         <v>2668302662</v>
       </c>
       <c r="D272">
-        <v>523239000</v>
+        <v>0</v>
       </c>
       <c r="E272">
-        <v>2089630000</v>
+        <v>2612869000</v>
       </c>
       <c r="F272">
         <v>2612869000</v>
@@ -8461,10 +8461,10 @@
         <v>2260000000</v>
       </c>
       <c r="D277">
-        <v>1511808816</v>
+        <v>1501810316</v>
       </c>
       <c r="E277">
-        <v>559808340</v>
+        <v>569806840</v>
       </c>
       <c r="F277">
         <v>2071617156</v>
@@ -8617,16 +8617,16 @@
         <v>1952349292</v>
       </c>
       <c r="D283">
-        <v>0</v>
+        <v>828300</v>
       </c>
       <c r="E283">
         <v>1107715962</v>
       </c>
       <c r="F283">
-        <v>1107715962</v>
+        <v>1108544262</v>
       </c>
       <c r="G283">
-        <v>844633330</v>
+        <v>843805030</v>
       </c>
       <c r="H283">
         <v>0</v>
@@ -8669,10 +8669,10 @@
         <v>470406638</v>
       </c>
       <c r="D285">
-        <v>70626500</v>
+        <v>51507500</v>
       </c>
       <c r="E285">
-        <v>263757433</v>
+        <v>282876433</v>
       </c>
       <c r="F285">
         <v>334383933</v>
@@ -9059,16 +9059,16 @@
         <v>63706784713</v>
       </c>
       <c r="D300">
-        <v>14497034158</v>
+        <v>13714997769</v>
       </c>
       <c r="E300">
-        <v>32996110227</v>
+        <v>33826974916</v>
       </c>
       <c r="F300">
-        <v>47493144385</v>
+        <v>47541972685</v>
       </c>
       <c r="G300">
-        <v>16213640328</v>
+        <v>16164812028</v>
       </c>
       <c r="H300">
         <v>531045413</v>
@@ -9215,10 +9215,10 @@
         <v>193000000</v>
       </c>
       <c r="D306">
-        <v>95816000</v>
+        <v>70000000</v>
       </c>
       <c r="E306">
-        <v>96900000</v>
+        <v>122716000</v>
       </c>
       <c r="F306">
         <v>192716000</v>
@@ -9917,10 +9917,10 @@
         <v>30454436960</v>
       </c>
       <c r="D333">
-        <v>3249433670</v>
+        <v>3223617670</v>
       </c>
       <c r="E333">
-        <v>20286475564</v>
+        <v>20312291564</v>
       </c>
       <c r="F333">
         <v>23535909234</v>
@@ -10021,16 +10021,16 @@
         <v>2593734264</v>
       </c>
       <c r="D337">
-        <v>1147212896</v>
+        <v>1159171896</v>
       </c>
       <c r="E337">
         <v>1434562314</v>
       </c>
       <c r="F337">
-        <v>2581775210</v>
+        <v>2593734210</v>
       </c>
       <c r="G337">
-        <v>11959054</v>
+        <v>54</v>
       </c>
       <c r="H337">
         <v>0</v>
@@ -10125,16 +10125,16 @@
         <v>1748195004</v>
       </c>
       <c r="D341">
-        <v>511194948</v>
+        <v>521192372</v>
       </c>
       <c r="E341">
         <v>1081786638</v>
       </c>
       <c r="F341">
-        <v>1592981586</v>
+        <v>1602979010</v>
       </c>
       <c r="G341">
-        <v>155213418</v>
+        <v>145215994</v>
       </c>
       <c r="H341">
         <v>0</v>
@@ -10229,16 +10229,16 @@
         <v>600000000</v>
       </c>
       <c r="D345">
-        <v>0</v>
+        <v>478435648</v>
       </c>
       <c r="E345">
         <v>0</v>
       </c>
       <c r="F345">
-        <v>0</v>
+        <v>478435648</v>
       </c>
       <c r="G345">
-        <v>600000000</v>
+        <v>121564352</v>
       </c>
       <c r="H345">
         <v>0</v>
@@ -10281,16 +10281,16 @@
         <v>150000000</v>
       </c>
       <c r="D347">
-        <v>58802000</v>
+        <v>101481590</v>
       </c>
       <c r="E347">
         <v>0</v>
       </c>
       <c r="F347">
-        <v>58802000</v>
+        <v>101481590</v>
       </c>
       <c r="G347">
-        <v>91198000</v>
+        <v>48518410</v>
       </c>
       <c r="H347">
         <v>50000000</v>
@@ -10333,16 +10333,16 @@
         <v>2911760000</v>
       </c>
       <c r="D349">
-        <v>292320270</v>
+        <v>292802040</v>
       </c>
       <c r="E349">
         <v>1449936173</v>
       </c>
       <c r="F349">
-        <v>1742256443</v>
+        <v>1742738213</v>
       </c>
       <c r="G349">
-        <v>1169503557</v>
+        <v>1169021787</v>
       </c>
       <c r="H349">
         <v>0</v>
@@ -10385,10 +10385,10 @@
         <v>571079775</v>
       </c>
       <c r="D351">
-        <v>258647670</v>
+        <v>233791670</v>
       </c>
       <c r="E351">
-        <v>249962994</v>
+        <v>274818994</v>
       </c>
       <c r="F351">
         <v>508610664</v>
@@ -10437,10 +10437,10 @@
         <v>462375000</v>
       </c>
       <c r="D353">
-        <v>253540312</v>
+        <v>250302912</v>
       </c>
       <c r="E353">
-        <v>87397971</v>
+        <v>90635371</v>
       </c>
       <c r="F353">
         <v>340938283</v>
@@ -10489,16 +10489,16 @@
         <v>6000000</v>
       </c>
       <c r="D355">
-        <v>286620</v>
+        <v>467190</v>
       </c>
       <c r="E355">
         <v>1500170</v>
       </c>
       <c r="F355">
-        <v>1786790</v>
+        <v>1967360</v>
       </c>
       <c r="G355">
-        <v>4213210</v>
+        <v>4032640</v>
       </c>
       <c r="H355">
         <v>0</v>
@@ -10593,10 +10593,10 @@
         <v>10532164202</v>
       </c>
       <c r="D359">
-        <v>24952043</v>
+        <v>0</v>
       </c>
       <c r="E359">
-        <v>8438952474</v>
+        <v>8463904517</v>
       </c>
       <c r="F359">
         <v>8463904517</v>
@@ -10697,10 +10697,10 @@
         <v>1523018104</v>
       </c>
       <c r="D363">
-        <v>811692</v>
+        <v>0</v>
       </c>
       <c r="E363">
-        <v>1168247409</v>
+        <v>1169059101</v>
       </c>
       <c r="F363">
         <v>1169059101</v>
@@ -10749,16 +10749,16 @@
         <v>57427089299</v>
       </c>
       <c r="D365">
-        <v>10269187961</v>
+        <v>10759064828</v>
       </c>
       <c r="E365">
-        <v>37177448443</v>
+        <v>37231305578</v>
       </c>
       <c r="F365">
-        <v>47446636404</v>
+        <v>47990370406</v>
       </c>
       <c r="G365">
-        <v>9980452895</v>
+        <v>9436718893</v>
       </c>
       <c r="H365">
         <v>526334925</v>
@@ -10853,16 +10853,16 @@
         <v>2467762918</v>
       </c>
       <c r="D369">
-        <v>937400549</v>
+        <v>917380377</v>
       </c>
       <c r="E369">
-        <v>481810055</v>
+        <v>509828868</v>
       </c>
       <c r="F369">
-        <v>1419210604</v>
+        <v>1427209245</v>
       </c>
       <c r="G369">
-        <v>1048552314</v>
+        <v>1040553673</v>
       </c>
       <c r="H369">
         <v>0</v>
@@ -10931,16 +10931,16 @@
         <v>1714789867</v>
       </c>
       <c r="D372">
-        <v>848353936</v>
+        <v>871435271</v>
       </c>
       <c r="E372">
         <v>732962308</v>
       </c>
       <c r="F372">
-        <v>1581316244</v>
+        <v>1604397579</v>
       </c>
       <c r="G372">
-        <v>133473623</v>
+        <v>110392288</v>
       </c>
       <c r="H372">
         <v>0</v>
@@ -10957,10 +10957,10 @@
         <v>1400000000</v>
       </c>
       <c r="D373">
-        <v>375454314</v>
+        <v>329738314</v>
       </c>
       <c r="E373">
-        <v>394974750</v>
+        <v>440690750</v>
       </c>
       <c r="F373">
         <v>770429064</v>
@@ -11191,10 +11191,10 @@
         <v>300000000</v>
       </c>
       <c r="D382">
-        <v>68105500</v>
+        <v>57624250</v>
       </c>
       <c r="E382">
-        <v>172833462</v>
+        <v>183314712</v>
       </c>
       <c r="F382">
         <v>240938962</v>
@@ -11581,16 +11581,16 @@
         <v>24628424376</v>
       </c>
       <c r="D397">
-        <v>4353981881</v>
+        <v>4300845794</v>
       </c>
       <c r="E397">
-        <v>14472474500</v>
+        <v>14556690563</v>
       </c>
       <c r="F397">
-        <v>18826456381</v>
+        <v>18857536357</v>
       </c>
       <c r="G397">
-        <v>5801967995</v>
+        <v>5770888019</v>
       </c>
       <c r="H397">
         <v>232675000</v>
@@ -12309,10 +12309,10 @@
         <v>9379568492</v>
       </c>
       <c r="D425">
-        <v>21725412</v>
+        <v>0</v>
       </c>
       <c r="E425">
-        <v>6968736677</v>
+        <v>6990462089</v>
       </c>
       <c r="F425">
         <v>6990462089</v>
@@ -12465,10 +12465,10 @@
         <v>35458361640</v>
       </c>
       <c r="D431">
-        <v>5934547536</v>
+        <v>5912822124</v>
       </c>
       <c r="E431">
-        <v>19599892730</v>
+        <v>19621618142</v>
       </c>
       <c r="F431">
         <v>25534440266</v>
@@ -13567,16 +13567,16 @@
         <v>4989900000</v>
       </c>
       <c r="D496">
-        <v>2356509177</v>
+        <v>2351193977</v>
       </c>
       <c r="E496">
         <v>1304104604</v>
       </c>
       <c r="F496">
-        <v>3660613781</v>
+        <v>3655298581</v>
       </c>
       <c r="G496">
-        <v>1329286219</v>
+        <v>1334601419</v>
       </c>
       <c r="H496">
         <v>0</v>
@@ -13619,10 +13619,10 @@
         <v>1680000000</v>
       </c>
       <c r="D498">
-        <v>545114599</v>
+        <v>52561000</v>
       </c>
       <c r="E498">
-        <v>415370650</v>
+        <v>907924249</v>
       </c>
       <c r="F498">
         <v>960485249</v>
@@ -13645,16 +13645,16 @@
         <v>492066000</v>
       </c>
       <c r="D499">
-        <v>423528000</v>
+        <v>417924000</v>
       </c>
       <c r="E499">
         <v>39286865</v>
       </c>
       <c r="F499">
-        <v>462814865</v>
+        <v>457210865</v>
       </c>
       <c r="G499">
-        <v>29251135</v>
+        <v>34855135</v>
       </c>
       <c r="H499">
         <v>0</v>
@@ -13905,16 +13905,16 @@
         <v>1016150000</v>
       </c>
       <c r="D509">
-        <v>82615000</v>
+        <v>102765000</v>
       </c>
       <c r="E509">
         <v>367300000</v>
       </c>
       <c r="F509">
-        <v>449915000</v>
+        <v>470065000</v>
       </c>
       <c r="G509">
-        <v>566235000</v>
+        <v>546085000</v>
       </c>
       <c r="H509">
         <v>0</v>
@@ -13957,10 +13957,10 @@
         <v>668379750</v>
       </c>
       <c r="D511">
-        <v>22370000</v>
+        <v>11185000</v>
       </c>
       <c r="E511">
-        <v>157050828</v>
+        <v>168235828</v>
       </c>
       <c r="F511">
         <v>179420828</v>
@@ -13983,10 +13983,10 @@
         <v>870341250</v>
       </c>
       <c r="D512">
-        <v>193948300</v>
+        <v>192671560</v>
       </c>
       <c r="E512">
-        <v>557245270</v>
+        <v>558522010</v>
       </c>
       <c r="F512">
         <v>751193570</v>
@@ -14061,16 +14061,16 @@
         <v>516433500</v>
       </c>
       <c r="D515">
-        <v>55116560</v>
+        <v>52951868</v>
       </c>
       <c r="E515">
-        <v>296973428</v>
+        <v>300638120</v>
       </c>
       <c r="F515">
-        <v>352089988</v>
+        <v>353589988</v>
       </c>
       <c r="G515">
-        <v>164343512</v>
+        <v>162843512</v>
       </c>
       <c r="H515">
         <v>172144500</v>
@@ -14246,13 +14246,13 @@
         <v>446366</v>
       </c>
       <c r="E522">
-        <v>7944041030</v>
+        <v>7944074780</v>
       </c>
       <c r="F522">
-        <v>7944487396</v>
+        <v>7944521146</v>
       </c>
       <c r="G522">
-        <v>4219794501</v>
+        <v>4219760751</v>
       </c>
       <c r="H522">
         <v>0</v>
@@ -14477,16 +14477,16 @@
         <v>64019485320</v>
       </c>
       <c r="D531">
-        <v>15571518705</v>
+        <v>15073569474</v>
       </c>
       <c r="E531">
-        <v>36514938324</v>
+        <v>37023652105</v>
       </c>
       <c r="F531">
-        <v>52086457029</v>
+        <v>52097221579</v>
       </c>
       <c r="G531">
-        <v>11933028291</v>
+        <v>11922263741</v>
       </c>
       <c r="H531">
         <v>850782250</v>
@@ -14867,16 +14867,16 @@
         <v>579713600</v>
       </c>
       <c r="D546">
-        <v>45808650</v>
+        <v>62278650</v>
       </c>
       <c r="E546">
         <v>199030350</v>
       </c>
       <c r="F546">
-        <v>244839000</v>
+        <v>261309000</v>
       </c>
       <c r="G546">
-        <v>334874600</v>
+        <v>318404600</v>
       </c>
       <c r="H546">
         <v>0</v>
@@ -14997,10 +14997,10 @@
         <v>395748750</v>
       </c>
       <c r="D551">
-        <v>126180768</v>
+        <v>83308696</v>
       </c>
       <c r="E551">
-        <v>233355129</v>
+        <v>276227201</v>
       </c>
       <c r="F551">
         <v>359535897</v>
@@ -15026,13 +15026,13 @@
         <v>13070734</v>
       </c>
       <c r="E552">
-        <v>221624601</v>
+        <v>224462101</v>
       </c>
       <c r="F552">
-        <v>234695335</v>
+        <v>237532835</v>
       </c>
       <c r="G552">
-        <v>102107165</v>
+        <v>99269665</v>
       </c>
       <c r="H552">
         <v>112267500</v>
@@ -15104,13 +15104,13 @@
         <v>0</v>
       </c>
       <c r="E555">
-        <v>6978608079</v>
+        <v>6978673704</v>
       </c>
       <c r="F555">
-        <v>6978608079</v>
+        <v>6978673704</v>
       </c>
       <c r="G555">
-        <v>3710308787</v>
+        <v>3710243162</v>
       </c>
       <c r="H555">
         <v>0</v>
@@ -15309,16 +15309,16 @@
         <v>57848682223</v>
       </c>
       <c r="D563">
-        <v>22441341833</v>
+        <v>22414939761</v>
       </c>
       <c r="E563">
-        <v>27061756394</v>
+        <v>27107531591</v>
       </c>
       <c r="F563">
-        <v>49503098227</v>
+        <v>49522471352</v>
       </c>
       <c r="G563">
-        <v>8345583996</v>
+        <v>8326210871</v>
       </c>
       <c r="H563">
         <v>720558750</v>
@@ -15329,22 +15329,22 @@
         <v>129</v>
       </c>
       <c r="B564">
-        <v>1118576863411</v>
+        <v>1118558384139</v>
       </c>
       <c r="C564">
-        <v>1109044586089</v>
+        <v>1109026106817</v>
       </c>
       <c r="D564">
-        <v>429038071112</v>
+        <v>424256894525</v>
       </c>
       <c r="E564">
-        <v>502822598015</v>
+        <v>506904392126</v>
       </c>
       <c r="F564">
-        <v>931860669127</v>
+        <v>931161286651</v>
       </c>
       <c r="G564">
-        <v>177183916962</v>
+        <v>177864820166</v>
       </c>
       <c r="H564">
         <v>9532277322</v>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{DF2C92B1-0A59-4505-9E68-3664D19B70A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{B3676C9E-F774-481B-820D-0C24EC30FDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="20260821 SAP" sheetId="1" r:id="rId1"/>
+    <sheet name="20260821 SAP NEW" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -2689,16 +2689,16 @@
         <v>4260000000</v>
       </c>
       <c r="D55">
-        <v>972608694</v>
+        <v>1129885579</v>
       </c>
       <c r="E55">
         <v>2010858858</v>
       </c>
       <c r="F55">
-        <v>2983467552</v>
+        <v>3140744437</v>
       </c>
       <c r="G55">
-        <v>1276532448</v>
+        <v>1119255563</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -2819,16 +2819,16 @@
         <v>2620000000</v>
       </c>
       <c r="D60">
-        <v>621312317</v>
+        <v>659712317</v>
       </c>
       <c r="E60">
         <v>704024117</v>
       </c>
       <c r="F60">
-        <v>1325336434</v>
+        <v>1363736434</v>
       </c>
       <c r="G60">
-        <v>1294663566</v>
+        <v>1256263566</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -3443,16 +3443,16 @@
         <v>110881210191</v>
       </c>
       <c r="D84">
-        <v>35635349480</v>
+        <v>35831026365</v>
       </c>
       <c r="E84">
         <v>51272994036</v>
       </c>
       <c r="F84">
-        <v>86908343516</v>
+        <v>87104020401</v>
       </c>
       <c r="G84">
-        <v>23972866675</v>
+        <v>23777189790</v>
       </c>
       <c r="H84">
         <v>671501500</v>
@@ -10853,16 +10853,16 @@
         <v>2467762918</v>
       </c>
       <c r="D369">
-        <v>917380377</v>
+        <v>1013929129</v>
       </c>
       <c r="E369">
         <v>509828868</v>
       </c>
       <c r="F369">
-        <v>1427209245</v>
+        <v>1523757997</v>
       </c>
       <c r="G369">
-        <v>1040553673</v>
+        <v>944004921</v>
       </c>
       <c r="H369">
         <v>0</v>
@@ -10931,16 +10931,16 @@
         <v>1714789867</v>
       </c>
       <c r="D372">
-        <v>871435271</v>
+        <v>920522269</v>
       </c>
       <c r="E372">
         <v>732962308</v>
       </c>
       <c r="F372">
-        <v>1604397579</v>
+        <v>1653484577</v>
       </c>
       <c r="G372">
-        <v>110392288</v>
+        <v>61305290</v>
       </c>
       <c r="H372">
         <v>0</v>
@@ -10957,16 +10957,16 @@
         <v>1400000000</v>
       </c>
       <c r="D373">
-        <v>329738314</v>
+        <v>372383814</v>
       </c>
       <c r="E373">
         <v>440690750</v>
       </c>
       <c r="F373">
-        <v>770429064</v>
+        <v>813074564</v>
       </c>
       <c r="G373">
-        <v>629570936</v>
+        <v>586925436</v>
       </c>
       <c r="H373">
         <v>0</v>
@@ -11581,16 +11581,16 @@
         <v>24628424376</v>
       </c>
       <c r="D397">
-        <v>4300845794</v>
+        <v>4489127044</v>
       </c>
       <c r="E397">
         <v>14556690563</v>
       </c>
       <c r="F397">
-        <v>18857536357</v>
+        <v>19045817607</v>
       </c>
       <c r="G397">
-        <v>5770888019</v>
+        <v>5582606769</v>
       </c>
       <c r="H397">
         <v>232675000</v>
@@ -12783,10 +12783,10 @@
         <v>220000000</v>
       </c>
       <c r="D452" s="1">
-        <v>78580000</v>
+        <v>48700000</v>
       </c>
       <c r="E452" s="1">
-        <v>59808678</v>
+        <v>89688678</v>
       </c>
       <c r="F452" s="1">
         <v>138388678</v>
@@ -15335,16 +15335,16 @@
         <v>1109026106817</v>
       </c>
       <c r="D564">
-        <v>424256894525</v>
+        <v>424640852660</v>
       </c>
       <c r="E564">
         <v>506904392126</v>
       </c>
       <c r="F564">
-        <v>931161286651</v>
+        <v>931545244786</v>
       </c>
       <c r="G564">
-        <v>177864820166</v>
+        <v>177480862031</v>
       </c>
       <c r="H564">
         <v>9532277322</v>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{B3676C9E-F774-481B-820D-0C24EC30FDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{3D820F8D-01D9-4924-A5FD-2937C2CEBE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="4752" yWindow="3060" windowWidth="17280" windowHeight="9180"/>
   </bookViews>
   <sheets>
-    <sheet name="20260821 SAP NEW" sheetId="1" r:id="rId1"/>
+    <sheet name="20260826 SAP ZFM01" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -171,7 +171,7 @@
     <t>5400000000  Penyusutan AT Lainnya (Fasilitas Umum)</t>
   </si>
   <si>
-    <t>10025000  Signalling, Telecomm &amp; Electricity</t>
+    <t>10025000  Signalling, Telecom &amp; Electricity Area 1</t>
   </si>
   <si>
     <t>4123110010  Gaji &amp;Tunjangan Pegawai Operasi Sarana</t>
@@ -1805,16 +1805,16 @@
         <v>510385000</v>
       </c>
       <c r="D21">
-        <v>56515100</v>
+        <v>75773600</v>
       </c>
       <c r="E21">
         <v>84557037</v>
       </c>
       <c r="F21">
-        <v>141072137</v>
+        <v>160330637</v>
       </c>
       <c r="G21">
-        <v>369312863</v>
+        <v>350054363</v>
       </c>
       <c r="H21">
         <v>192500000</v>
@@ -1912,13 +1912,13 @@
         <v>21639448</v>
       </c>
       <c r="E25">
-        <v>995797493</v>
+        <v>999834993</v>
       </c>
       <c r="F25">
-        <v>1017436941</v>
+        <v>1021474441</v>
       </c>
       <c r="G25">
-        <v>687980208</v>
+        <v>683942708</v>
       </c>
       <c r="H25">
         <v>625000000</v>
@@ -1990,13 +1990,13 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2531752794</v>
+        <v>2832001403</v>
       </c>
       <c r="F28">
-        <v>2531752794</v>
+        <v>2832001403</v>
       </c>
       <c r="G28">
-        <v>924861410</v>
+        <v>624612801</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2016,13 +2016,13 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>41730129</v>
+        <v>50545446</v>
       </c>
       <c r="F29">
-        <v>41730129</v>
+        <v>50545446</v>
       </c>
       <c r="G29">
-        <v>11098494</v>
+        <v>2283177</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2042,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>3449473687</v>
+        <v>3661908187</v>
       </c>
       <c r="F30">
-        <v>3449473687</v>
+        <v>3661908187</v>
       </c>
       <c r="G30">
-        <v>628796348</v>
+        <v>416361848</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2094,13 +2094,13 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>5874228668</v>
+        <v>6405217551</v>
       </c>
       <c r="F32">
-        <v>5874228668</v>
+        <v>6405217551</v>
       </c>
       <c r="G32">
-        <v>5073246587</v>
+        <v>4542257704</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -2120,13 +2120,13 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>152711468</v>
+        <v>174123199</v>
       </c>
       <c r="F33">
-        <v>152711468</v>
+        <v>174123199</v>
       </c>
       <c r="G33">
-        <v>95378534</v>
+        <v>73966803</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2146,13 +2146,13 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>9457324073</v>
+        <v>10058200960</v>
       </c>
       <c r="F34">
-        <v>9457324073</v>
+        <v>10058200960</v>
       </c>
       <c r="G34">
-        <v>4512741973</v>
+        <v>3911865086</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2224,13 +2224,13 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>24175869</v>
+        <v>33178790</v>
       </c>
       <c r="F37">
-        <v>24175869</v>
+        <v>33178790</v>
       </c>
       <c r="G37">
-        <v>-24175869</v>
+        <v>-33178790</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -2250,13 +2250,13 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>75736895</v>
+        <v>84926895</v>
       </c>
       <c r="F38">
-        <v>75736895</v>
+        <v>84926895</v>
       </c>
       <c r="G38">
-        <v>-75736895</v>
+        <v>-84926895</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2351,16 +2351,16 @@
         <v>348373661935</v>
       </c>
       <c r="D42">
-        <v>237723937633</v>
+        <v>237743196133</v>
       </c>
       <c r="E42">
-        <v>91740179772</v>
+        <v>93437186120</v>
       </c>
       <c r="F42">
-        <v>329464117405</v>
+        <v>331180382253</v>
       </c>
       <c r="G42">
-        <v>18909544530</v>
+        <v>17193279682</v>
       </c>
       <c r="H42">
         <v>2417500000</v>
@@ -2637,10 +2637,10 @@
         <v>1300000000</v>
       </c>
       <c r="D53">
-        <v>484962973</v>
+        <v>471888236</v>
       </c>
       <c r="E53">
-        <v>456944400</v>
+        <v>470019137</v>
       </c>
       <c r="F53">
         <v>941907373</v>
@@ -2689,10 +2689,10 @@
         <v>4260000000</v>
       </c>
       <c r="D55">
-        <v>1129885579</v>
+        <v>1100095959</v>
       </c>
       <c r="E55">
-        <v>2010858858</v>
+        <v>2040648478</v>
       </c>
       <c r="F55">
         <v>3140744437</v>
@@ -2819,16 +2819,16 @@
         <v>2620000000</v>
       </c>
       <c r="D60">
-        <v>659712317</v>
+        <v>633371738</v>
       </c>
       <c r="E60">
-        <v>704024117</v>
+        <v>738524117</v>
       </c>
       <c r="F60">
-        <v>1363736434</v>
+        <v>1371895855</v>
       </c>
       <c r="G60">
-        <v>1256263566</v>
+        <v>1248104145</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -3001,16 +3001,16 @@
         <v>400400000</v>
       </c>
       <c r="D67">
-        <v>89162510</v>
+        <v>14042510</v>
       </c>
       <c r="E67">
         <v>119056922</v>
       </c>
       <c r="F67">
-        <v>208219432</v>
+        <v>133099432</v>
       </c>
       <c r="G67">
-        <v>192180568</v>
+        <v>267300568</v>
       </c>
       <c r="H67">
         <v>139000000</v>
@@ -3079,16 +3079,16 @@
         <v>608104500</v>
       </c>
       <c r="D70">
-        <v>144996720</v>
+        <v>47700000</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>144996720</v>
+        <v>47700000</v>
       </c>
       <c r="G70">
-        <v>463107780</v>
+        <v>560404500</v>
       </c>
       <c r="H70">
         <v>202701500</v>
@@ -3212,13 +3212,13 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>14912409024</v>
+        <v>16582271780</v>
       </c>
       <c r="F75">
-        <v>14912409024</v>
+        <v>16582271780</v>
       </c>
       <c r="G75">
-        <v>8019198205</v>
+        <v>6349335449</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -3238,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>307147040</v>
+        <v>349754600</v>
       </c>
       <c r="F76">
-        <v>307147040</v>
+        <v>349754600</v>
       </c>
       <c r="G76">
-        <v>297808117</v>
+        <v>255200557</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -3264,13 +3264,13 @@
         <v>9566218</v>
       </c>
       <c r="E77">
-        <v>17224444339</v>
+        <v>17994131226</v>
       </c>
       <c r="F77">
-        <v>17234010557</v>
+        <v>18003697444</v>
       </c>
       <c r="G77">
-        <v>3733410973</v>
+        <v>2963724086</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -3316,13 +3316,13 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>1242480138</v>
+        <v>1397646431</v>
       </c>
       <c r="F79">
-        <v>1242480138</v>
+        <v>1397646431</v>
       </c>
       <c r="G79">
-        <v>406946447</v>
+        <v>251780154</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3342,13 +3342,13 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>38393968</v>
+        <v>43885464</v>
       </c>
       <c r="F80">
-        <v>38393968</v>
+        <v>43885464</v>
       </c>
       <c r="G80">
-        <v>15266155</v>
+        <v>9774659</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -3368,13 +3368,13 @@
         <v>165657</v>
       </c>
       <c r="E81">
-        <v>1787404575</v>
+        <v>1889267075</v>
       </c>
       <c r="F81">
-        <v>1787570232</v>
+        <v>1889432732</v>
       </c>
       <c r="G81">
-        <v>149548296</v>
+        <v>47685796</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -3443,16 +3443,16 @@
         <v>110881210191</v>
       </c>
       <c r="D84">
-        <v>35831026365</v>
+        <v>35589404709</v>
       </c>
       <c r="E84">
-        <v>51272994036</v>
+        <v>54095035885</v>
       </c>
       <c r="F84">
-        <v>87104020401</v>
+        <v>89684440594</v>
       </c>
       <c r="G84">
-        <v>23777189790</v>
+        <v>21196769597</v>
       </c>
       <c r="H84">
         <v>671501500</v>
@@ -3703,16 +3703,16 @@
         <v>2796520000</v>
       </c>
       <c r="D94">
-        <v>814560594</v>
+        <v>838415594</v>
       </c>
       <c r="E94">
         <v>1905663067</v>
       </c>
       <c r="F94">
-        <v>2720223661</v>
+        <v>2744078661</v>
       </c>
       <c r="G94">
-        <v>76296339</v>
+        <v>52441339</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -3859,16 +3859,16 @@
         <v>1710494400</v>
       </c>
       <c r="D100">
-        <v>383970280</v>
+        <v>629986580</v>
       </c>
       <c r="E100">
         <v>1067501506</v>
       </c>
       <c r="F100">
-        <v>1451471786</v>
+        <v>1697488086</v>
       </c>
       <c r="G100">
-        <v>259022614</v>
+        <v>13006314</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -4044,13 +4044,13 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>290028568</v>
+        <v>290216068</v>
       </c>
       <c r="F107">
-        <v>290028568</v>
+        <v>290216068</v>
       </c>
       <c r="G107">
-        <v>5028932</v>
+        <v>4841432</v>
       </c>
       <c r="H107">
         <v>98352500</v>
@@ -4174,13 +4174,13 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>10802575215</v>
+        <v>11991989449</v>
       </c>
       <c r="F112">
-        <v>10802575215</v>
+        <v>11991989449</v>
       </c>
       <c r="G112">
-        <v>5421069638</v>
+        <v>4231655404</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0</v>
       </c>
       <c r="E113">
-        <v>114204508</v>
+        <v>130000886</v>
       </c>
       <c r="F113">
-        <v>114204508</v>
+        <v>130000886</v>
       </c>
       <c r="G113">
-        <v>87386554</v>
+        <v>71590176</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -4226,13 +4226,13 @@
         <v>9868545</v>
       </c>
       <c r="E114">
-        <v>12517646571</v>
+        <v>13036981539</v>
       </c>
       <c r="F114">
-        <v>12527515116</v>
+        <v>13046850084</v>
       </c>
       <c r="G114">
-        <v>1970664832</v>
+        <v>1451329864</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -4278,13 +4278,13 @@
         <v>0</v>
       </c>
       <c r="E116">
-        <v>945989944</v>
+        <v>1028011673</v>
       </c>
       <c r="F116">
-        <v>945989944</v>
+        <v>1028011673</v>
       </c>
       <c r="G116">
-        <v>1018483052</v>
+        <v>936461323</v>
       </c>
       <c r="H116">
         <v>0</v>
@@ -4304,13 +4304,13 @@
         <v>0</v>
       </c>
       <c r="E117">
-        <v>23490285</v>
+        <v>26834186</v>
       </c>
       <c r="F117">
-        <v>23490285</v>
+        <v>26834186</v>
       </c>
       <c r="G117">
-        <v>17422331</v>
+        <v>14078430</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -4330,13 +4330,13 @@
         <v>0</v>
       </c>
       <c r="E118">
-        <v>1407855716</v>
+        <v>1493780716</v>
       </c>
       <c r="F118">
-        <v>1407855716</v>
+        <v>1493780716</v>
       </c>
       <c r="G118">
-        <v>520805158</v>
+        <v>434880158</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -4405,16 +4405,16 @@
         <v>81693644736</v>
       </c>
       <c r="D121">
-        <v>16872205089</v>
+        <v>17142076389</v>
       </c>
       <c r="E121">
-        <v>47675828324</v>
+        <v>49571852034</v>
       </c>
       <c r="F121">
-        <v>64548033413</v>
+        <v>66713928423</v>
       </c>
       <c r="G121">
-        <v>17145611323</v>
+        <v>14979716313</v>
       </c>
       <c r="H121">
         <v>475697500</v>
@@ -4431,16 +4431,16 @@
         <v>8995670000</v>
       </c>
       <c r="D122">
-        <v>5186052520</v>
+        <v>5683860320</v>
       </c>
       <c r="E122">
         <v>3020023792</v>
       </c>
       <c r="F122">
-        <v>8206076312</v>
+        <v>8703884112</v>
       </c>
       <c r="G122">
-        <v>789593688</v>
+        <v>291785888</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -4457,16 +4457,16 @@
         <v>1494332364</v>
       </c>
       <c r="D123">
-        <v>498831216</v>
+        <v>491000000</v>
       </c>
       <c r="E123">
         <v>127583711</v>
       </c>
       <c r="F123">
-        <v>626414927</v>
+        <v>618583711</v>
       </c>
       <c r="G123">
-        <v>867917437</v>
+        <v>875748653</v>
       </c>
       <c r="H123">
         <v>0</v>
@@ -4613,10 +4613,10 @@
         <v>1665000000</v>
       </c>
       <c r="D129">
-        <v>148801838</v>
+        <v>135800338</v>
       </c>
       <c r="E129">
-        <v>638693246</v>
+        <v>651694746</v>
       </c>
       <c r="F129">
         <v>787495084</v>
@@ -5058,13 +5058,13 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>6377672732</v>
+        <v>7119228325</v>
       </c>
       <c r="F146">
-        <v>6377672732</v>
+        <v>7119228325</v>
       </c>
       <c r="G146">
-        <v>3571421351</v>
+        <v>2829865758</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -5084,13 +5084,13 @@
         <v>0</v>
       </c>
       <c r="E147">
-        <v>224568402</v>
+        <v>256049373</v>
       </c>
       <c r="F147">
-        <v>224568402</v>
+        <v>256049373</v>
       </c>
       <c r="G147">
-        <v>161997000</v>
+        <v>130516029</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>8027816419</v>
+        <v>8371186419</v>
       </c>
       <c r="F148">
-        <v>8027816419</v>
+        <v>8371186419</v>
       </c>
       <c r="G148">
-        <v>1742033472</v>
+        <v>1398663472</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -5162,13 +5162,13 @@
         <v>0</v>
       </c>
       <c r="E150">
-        <v>723780456</v>
+        <v>787104074</v>
       </c>
       <c r="F150">
-        <v>723780456</v>
+        <v>787104074</v>
       </c>
       <c r="G150">
-        <v>684731547</v>
+        <v>621407929</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -5188,13 +5188,13 @@
         <v>0</v>
       </c>
       <c r="E151">
-        <v>15094478</v>
+        <v>17250832</v>
       </c>
       <c r="F151">
-        <v>15094478</v>
+        <v>17250832</v>
       </c>
       <c r="G151">
-        <v>23224911</v>
+        <v>21068557</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -5214,13 +5214,13 @@
         <v>0</v>
       </c>
       <c r="E152">
-        <v>1013695901</v>
+        <v>1071715901</v>
       </c>
       <c r="F152">
-        <v>1013695901</v>
+        <v>1071715901</v>
       </c>
       <c r="G152">
-        <v>316621638</v>
+        <v>258601638</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -5289,16 +5289,16 @@
         <v>52173056175</v>
       </c>
       <c r="D155">
-        <v>11954116660</v>
+        <v>12431091744</v>
       </c>
       <c r="E155">
-        <v>28180884162</v>
+        <v>29433792198</v>
       </c>
       <c r="F155">
-        <v>40135000822</v>
+        <v>41864883942</v>
       </c>
       <c r="G155">
-        <v>12038055353</v>
+        <v>10308172233</v>
       </c>
       <c r="H155">
         <v>411080000</v>
@@ -5471,10 +5471,10 @@
         <v>1702406000</v>
       </c>
       <c r="D162">
-        <v>319144551</v>
+        <v>268394551</v>
       </c>
       <c r="E162">
-        <v>707301975</v>
+        <v>758051975</v>
       </c>
       <c r="F162">
         <v>1026446526</v>
@@ -5916,13 +5916,13 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>114184250</v>
+        <v>114659250</v>
       </c>
       <c r="F179">
-        <v>114184250</v>
+        <v>114659250</v>
       </c>
       <c r="G179">
-        <v>48117250</v>
+        <v>47642250</v>
       </c>
       <c r="H179">
         <v>54100500</v>
@@ -5968,13 +5968,13 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>4797002528</v>
+        <v>5304757088</v>
       </c>
       <c r="F181">
-        <v>4797002528</v>
+        <v>5304757088</v>
       </c>
       <c r="G181">
-        <v>2707720850</v>
+        <v>2199966290</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -5994,13 +5994,13 @@
         <v>0</v>
       </c>
       <c r="E182">
-        <v>123692252</v>
+        <v>139746256</v>
       </c>
       <c r="F182">
-        <v>123692252</v>
+        <v>139746256</v>
       </c>
       <c r="G182">
-        <v>102643818</v>
+        <v>86589814</v>
       </c>
       <c r="H182">
         <v>0</v>
@@ -6020,13 +6020,13 @@
         <v>0</v>
       </c>
       <c r="E183">
-        <v>5871514241</v>
+        <v>6128646741</v>
       </c>
       <c r="F183">
-        <v>5871514241</v>
+        <v>6128646741</v>
       </c>
       <c r="G183">
-        <v>1457124259</v>
+        <v>1199991759</v>
       </c>
       <c r="H183">
         <v>0</v>
@@ -6072,13 +6072,13 @@
         <v>0</v>
       </c>
       <c r="E185">
-        <v>705676834</v>
+        <v>769243740</v>
       </c>
       <c r="F185">
-        <v>705676834</v>
+        <v>769243740</v>
       </c>
       <c r="G185">
-        <v>580342499</v>
+        <v>516775593</v>
       </c>
       <c r="H185">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0</v>
       </c>
       <c r="E186">
-        <v>13549986</v>
+        <v>14685855</v>
       </c>
       <c r="F186">
-        <v>13549986</v>
+        <v>14685855</v>
       </c>
       <c r="G186">
-        <v>23268754</v>
+        <v>22132885</v>
       </c>
       <c r="H186">
         <v>0</v>
@@ -6124,13 +6124,13 @@
         <v>0</v>
       </c>
       <c r="E187">
-        <v>1009477373</v>
+        <v>1069028373</v>
       </c>
       <c r="F187">
-        <v>1009477373</v>
+        <v>1069028373</v>
       </c>
       <c r="G187">
-        <v>361942536</v>
+        <v>302391536</v>
       </c>
       <c r="H187">
         <v>0</v>
@@ -6173,16 +6173,16 @@
         <v>46375593027</v>
       </c>
       <c r="D189">
-        <v>10621302092</v>
+        <v>10570552092</v>
       </c>
       <c r="E189">
-        <v>25737282684</v>
+        <v>26693702523</v>
       </c>
       <c r="F189">
-        <v>36358584776</v>
+        <v>37264254615</v>
       </c>
       <c r="G189">
-        <v>10017008251</v>
+        <v>9111338412</v>
       </c>
       <c r="H189">
         <v>449400500</v>
@@ -6199,10 +6199,10 @@
         <v>7317456560</v>
       </c>
       <c r="D190">
-        <v>6104309220</v>
+        <v>3256309220</v>
       </c>
       <c r="E190">
-        <v>1212495000</v>
+        <v>4060495000</v>
       </c>
       <c r="F190">
         <v>7316804220</v>
@@ -6485,10 +6485,10 @@
         <v>1862650000</v>
       </c>
       <c r="D201">
-        <v>437563067</v>
+        <v>414113067</v>
       </c>
       <c r="E201">
-        <v>1239143706</v>
+        <v>1262593706</v>
       </c>
       <c r="F201">
         <v>1676706773</v>
@@ -6982,13 +6982,13 @@
         <v>0</v>
       </c>
       <c r="E220">
-        <v>6348292729</v>
+        <v>7090253342</v>
       </c>
       <c r="F220">
-        <v>6348292729</v>
+        <v>7090253342</v>
       </c>
       <c r="G220">
-        <v>3474869397</v>
+        <v>2732908784</v>
       </c>
       <c r="H220">
         <v>0</v>
@@ -7008,13 +7008,13 @@
         <v>0</v>
       </c>
       <c r="E221">
-        <v>136976378</v>
+        <v>155973858</v>
       </c>
       <c r="F221">
-        <v>136976378</v>
+        <v>155973858</v>
       </c>
       <c r="G221">
-        <v>116280593</v>
+        <v>97283113</v>
       </c>
       <c r="H221">
         <v>0</v>
@@ -7034,13 +7034,13 @@
         <v>0</v>
       </c>
       <c r="E222">
-        <v>7906932486</v>
+        <v>8241279986</v>
       </c>
       <c r="F222">
-        <v>7906932486</v>
+        <v>8241279986</v>
       </c>
       <c r="G222">
-        <v>1338742886</v>
+        <v>1004395386</v>
       </c>
       <c r="H222">
         <v>0</v>
@@ -7086,13 +7086,13 @@
         <v>0</v>
       </c>
       <c r="E224">
-        <v>661241519</v>
+        <v>721927694</v>
       </c>
       <c r="F224">
-        <v>661241519</v>
+        <v>721927694</v>
       </c>
       <c r="G224">
-        <v>50420550</v>
+        <v>-10265625</v>
       </c>
       <c r="H224">
         <v>0</v>
@@ -7112,13 +7112,13 @@
         <v>0</v>
       </c>
       <c r="E225">
-        <v>22429321</v>
+        <v>25634579</v>
       </c>
       <c r="F225">
-        <v>22429321</v>
+        <v>25634579</v>
       </c>
       <c r="G225">
-        <v>2273141</v>
+        <v>-932117</v>
       </c>
       <c r="H225">
         <v>0</v>
@@ -7138,13 +7138,13 @@
         <v>0</v>
       </c>
       <c r="E226">
-        <v>973280511</v>
+        <v>1029675511</v>
       </c>
       <c r="F226">
-        <v>973280511</v>
+        <v>1029675511</v>
       </c>
       <c r="G226">
-        <v>-148114578</v>
+        <v>-204509578</v>
       </c>
       <c r="H226">
         <v>0</v>
@@ -7187,16 +7187,16 @@
         <v>47499233545</v>
       </c>
       <c r="D228">
-        <v>15285278182</v>
+        <v>12413828182</v>
       </c>
       <c r="E228">
-        <v>23745113216</v>
+        <v>27832155242</v>
       </c>
       <c r="F228">
-        <v>39030391398</v>
+        <v>40245983424</v>
       </c>
       <c r="G228">
-        <v>8468842147</v>
+        <v>7253250121</v>
       </c>
       <c r="H228">
         <v>415261500</v>
@@ -7265,16 +7265,16 @@
         <v>100000000</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>48758426</v>
       </c>
       <c r="E231">
         <v>49998822</v>
       </c>
       <c r="F231">
-        <v>49998822</v>
+        <v>98757248</v>
       </c>
       <c r="G231">
-        <v>50001178</v>
+        <v>1242752</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -7369,16 +7369,16 @@
         <v>1380000000</v>
       </c>
       <c r="D235">
-        <v>114445500</v>
+        <v>154853460</v>
       </c>
       <c r="E235">
         <v>1022581967</v>
       </c>
       <c r="F235">
-        <v>1137027467</v>
+        <v>1177435427</v>
       </c>
       <c r="G235">
-        <v>242972533</v>
+        <v>202564573</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -7447,16 +7447,16 @@
         <v>100000000</v>
       </c>
       <c r="D238">
-        <v>24248500</v>
+        <v>24518500</v>
       </c>
       <c r="E238">
         <v>17745000</v>
       </c>
       <c r="F238">
-        <v>41993500</v>
+        <v>42263500</v>
       </c>
       <c r="G238">
-        <v>58006500</v>
+        <v>57736500</v>
       </c>
       <c r="H238">
         <v>0</v>
@@ -7499,16 +7499,16 @@
         <v>30000000</v>
       </c>
       <c r="D240">
-        <v>13100000</v>
+        <v>25599200</v>
       </c>
       <c r="E240">
         <v>0</v>
       </c>
       <c r="F240">
-        <v>13100000</v>
+        <v>25599200</v>
       </c>
       <c r="G240">
-        <v>16900000</v>
+        <v>4400800</v>
       </c>
       <c r="H240">
         <v>0</v>
@@ -7629,16 +7629,16 @@
         <v>110162550</v>
       </c>
       <c r="D245">
-        <v>22380000</v>
+        <v>27360000</v>
       </c>
       <c r="E245">
         <v>51746000</v>
       </c>
       <c r="F245">
-        <v>74126000</v>
+        <v>79106000</v>
       </c>
       <c r="G245">
-        <v>36036550</v>
+        <v>31056550</v>
       </c>
       <c r="H245">
         <v>36720850</v>
@@ -7655,16 +7655,16 @@
         <v>354238500</v>
       </c>
       <c r="D246">
-        <v>54733500</v>
+        <v>65924000</v>
       </c>
       <c r="E246">
-        <v>263736900</v>
+        <v>276936900</v>
       </c>
       <c r="F246">
-        <v>318470400</v>
+        <v>342860900</v>
       </c>
       <c r="G246">
-        <v>35768100</v>
+        <v>11377600</v>
       </c>
       <c r="H246">
         <v>118079500</v>
@@ -7707,16 +7707,16 @@
         <v>732016185</v>
       </c>
       <c r="D248">
-        <v>8885000</v>
+        <v>10130000</v>
       </c>
       <c r="E248">
         <v>718641820</v>
       </c>
       <c r="F248">
-        <v>727526820</v>
+        <v>728771820</v>
       </c>
       <c r="G248">
-        <v>4489365</v>
+        <v>3244365</v>
       </c>
       <c r="H248">
         <v>42983815</v>
@@ -7736,13 +7736,13 @@
         <v>0</v>
       </c>
       <c r="E249">
-        <v>139781750</v>
+        <v>140931750</v>
       </c>
       <c r="F249">
-        <v>139781750</v>
+        <v>140931750</v>
       </c>
       <c r="G249">
-        <v>62502250</v>
+        <v>61352250</v>
       </c>
       <c r="H249">
         <v>67428000</v>
@@ -7788,13 +7788,13 @@
         <v>0</v>
       </c>
       <c r="E251">
-        <v>6266587377</v>
+        <v>6995374202</v>
       </c>
       <c r="F251">
-        <v>6266587377</v>
+        <v>6995374202</v>
       </c>
       <c r="G251">
-        <v>3559368793</v>
+        <v>2830581968</v>
       </c>
       <c r="H251">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0</v>
       </c>
       <c r="E252">
-        <v>286215848</v>
+        <v>327225146</v>
       </c>
       <c r="F252">
-        <v>286215848</v>
+        <v>327225146</v>
       </c>
       <c r="G252">
-        <v>183632730</v>
+        <v>142623432</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -7840,13 +7840,13 @@
         <v>0</v>
       </c>
       <c r="E253">
-        <v>7679665645</v>
+        <v>8018348145</v>
       </c>
       <c r="F253">
-        <v>7679665645</v>
+        <v>8018348145</v>
       </c>
       <c r="G253">
-        <v>1832440272</v>
+        <v>1493757772</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -7892,13 +7892,13 @@
         <v>0</v>
       </c>
       <c r="E255">
-        <v>729859543</v>
+        <v>794562499</v>
       </c>
       <c r="F255">
-        <v>729859543</v>
+        <v>794562499</v>
       </c>
       <c r="G255">
-        <v>265083018</v>
+        <v>200380062</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -7918,13 +7918,13 @@
         <v>0</v>
       </c>
       <c r="E256">
-        <v>24220591</v>
+        <v>27696111</v>
       </c>
       <c r="F256">
-        <v>24220591</v>
+        <v>27696111</v>
       </c>
       <c r="G256">
-        <v>9317768</v>
+        <v>5842248</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -7944,13 +7944,13 @@
         <v>0</v>
       </c>
       <c r="E257">
-        <v>1039064593</v>
+        <v>1096859593</v>
       </c>
       <c r="F257">
-        <v>1039064593</v>
+        <v>1096859593</v>
       </c>
       <c r="G257">
-        <v>60662741</v>
+        <v>2867741</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -8019,16 +8019,16 @@
         <v>48914772555</v>
       </c>
       <c r="D260">
-        <v>12119968065</v>
+        <v>12239319151</v>
       </c>
       <c r="E260">
-        <v>26398481044</v>
+        <v>27647283143</v>
       </c>
       <c r="F260">
-        <v>38518449109</v>
+        <v>39886602294</v>
       </c>
       <c r="G260">
-        <v>10396323446</v>
+        <v>9028170261</v>
       </c>
       <c r="H260">
         <v>525212165</v>
@@ -8461,16 +8461,16 @@
         <v>2260000000</v>
       </c>
       <c r="D277">
-        <v>1501810316</v>
+        <v>1501969916</v>
       </c>
       <c r="E277">
         <v>569806840</v>
       </c>
       <c r="F277">
-        <v>2071617156</v>
+        <v>2071776756</v>
       </c>
       <c r="G277">
-        <v>188382844</v>
+        <v>188223244</v>
       </c>
       <c r="H277">
         <v>0</v>
@@ -8669,16 +8669,16 @@
         <v>470406638</v>
       </c>
       <c r="D285">
-        <v>51507500</v>
+        <v>52841500</v>
       </c>
       <c r="E285">
         <v>282876433</v>
       </c>
       <c r="F285">
-        <v>334383933</v>
+        <v>335717933</v>
       </c>
       <c r="G285">
-        <v>136022705</v>
+        <v>134688705</v>
       </c>
       <c r="H285">
         <v>156802213</v>
@@ -8715,10 +8715,10 @@
         <v>29</v>
       </c>
       <c r="B287">
-        <v>942936000</v>
+        <v>797936000</v>
       </c>
       <c r="C287">
-        <v>707202000</v>
+        <v>562202000</v>
       </c>
       <c r="D287">
         <v>107601000</v>
@@ -8730,7 +8730,7 @@
         <v>223730811</v>
       </c>
       <c r="G287">
-        <v>483471189</v>
+        <v>338471189</v>
       </c>
       <c r="H287">
         <v>235734000</v>
@@ -8741,22 +8741,22 @@
         <v>31</v>
       </c>
       <c r="B288">
-        <v>271299000</v>
+        <v>416299000</v>
       </c>
       <c r="C288">
-        <v>203474250</v>
+        <v>348474250</v>
       </c>
       <c r="D288">
         <v>0</v>
       </c>
       <c r="E288">
-        <v>188422250</v>
+        <v>202811000</v>
       </c>
       <c r="F288">
-        <v>188422250</v>
+        <v>202811000</v>
       </c>
       <c r="G288">
-        <v>15052000</v>
+        <v>145663250</v>
       </c>
       <c r="H288">
         <v>67824750</v>
@@ -8854,13 +8854,13 @@
         <v>0</v>
       </c>
       <c r="E292">
-        <v>8067904293</v>
+        <v>8983131709</v>
       </c>
       <c r="F292">
-        <v>8067904293</v>
+        <v>8983131709</v>
       </c>
       <c r="G292">
-        <v>4554714634</v>
+        <v>3639487218</v>
       </c>
       <c r="H292">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0</v>
       </c>
       <c r="E293">
-        <v>102928278</v>
+        <v>117315961</v>
       </c>
       <c r="F293">
-        <v>102928278</v>
+        <v>117315961</v>
       </c>
       <c r="G293">
-        <v>92120014</v>
+        <v>77732331</v>
       </c>
       <c r="H293">
         <v>0</v>
@@ -8906,13 +8906,13 @@
         <v>0</v>
       </c>
       <c r="E294">
-        <v>10349361005</v>
+        <v>10802659505</v>
       </c>
       <c r="F294">
-        <v>10349361005</v>
+        <v>10802659505</v>
       </c>
       <c r="G294">
-        <v>2562356410</v>
+        <v>2109057910</v>
       </c>
       <c r="H294">
         <v>0</v>
@@ -8958,13 +8958,13 @@
         <v>0</v>
       </c>
       <c r="E296">
-        <v>785684826</v>
+        <v>886238632</v>
       </c>
       <c r="F296">
-        <v>785684826</v>
+        <v>886238632</v>
       </c>
       <c r="G296">
-        <v>474925829</v>
+        <v>374372023</v>
       </c>
       <c r="H296">
         <v>0</v>
@@ -8984,13 +8984,13 @@
         <v>0</v>
       </c>
       <c r="E297">
-        <v>15675701</v>
+        <v>17896206</v>
       </c>
       <c r="F297">
-        <v>15675701</v>
+        <v>17896206</v>
       </c>
       <c r="G297">
-        <v>11780100</v>
+        <v>9559595</v>
       </c>
       <c r="H297">
         <v>0</v>
@@ -9010,13 +9010,13 @@
         <v>0</v>
       </c>
       <c r="E298">
-        <v>1209190553</v>
+        <v>1283180553</v>
       </c>
       <c r="F298">
-        <v>1209190553</v>
+        <v>1283180553</v>
       </c>
       <c r="G298">
-        <v>351138284</v>
+        <v>277148284</v>
       </c>
       <c r="H298">
         <v>0</v>
@@ -9059,16 +9059,16 @@
         <v>63706784713</v>
       </c>
       <c r="D300">
-        <v>13714997769</v>
+        <v>13716491369</v>
       </c>
       <c r="E300">
-        <v>33826974916</v>
+        <v>35401041576</v>
       </c>
       <c r="F300">
-        <v>47541972685</v>
+        <v>49117532945</v>
       </c>
       <c r="G300">
-        <v>16164812028</v>
+        <v>14589251768</v>
       </c>
       <c r="H300">
         <v>531045413</v>
@@ -9189,10 +9189,10 @@
         <v>298750000</v>
       </c>
       <c r="D305">
-        <v>259144571</v>
+        <v>228565327</v>
       </c>
       <c r="E305">
-        <v>35247626</v>
+        <v>65826870</v>
       </c>
       <c r="F305">
         <v>294392197</v>
@@ -9712,13 +9712,13 @@
         <v>0</v>
       </c>
       <c r="E325">
-        <v>4482185246</v>
+        <v>4997571872</v>
       </c>
       <c r="F325">
-        <v>4482185246</v>
+        <v>4997571872</v>
       </c>
       <c r="G325">
-        <v>2571607019</v>
+        <v>2056220393</v>
       </c>
       <c r="H325">
         <v>0</v>
@@ -9738,13 +9738,13 @@
         <v>0</v>
       </c>
       <c r="E326">
-        <v>145297394</v>
+        <v>166079103</v>
       </c>
       <c r="F326">
-        <v>145297394</v>
+        <v>166079103</v>
       </c>
       <c r="G326">
-        <v>105604515</v>
+        <v>84822806</v>
       </c>
       <c r="H326">
         <v>0</v>
@@ -9764,13 +9764,13 @@
         <v>0</v>
       </c>
       <c r="E327">
-        <v>5715012047</v>
+        <v>5976157047</v>
       </c>
       <c r="F327">
-        <v>5715012047</v>
+        <v>5976157047</v>
       </c>
       <c r="G327">
-        <v>1300030374</v>
+        <v>1038885374</v>
       </c>
       <c r="H327">
         <v>0</v>
@@ -9816,13 +9816,13 @@
         <v>0</v>
       </c>
       <c r="E329">
-        <v>749151645</v>
+        <v>836657643</v>
       </c>
       <c r="F329">
-        <v>749151645</v>
+        <v>836657643</v>
       </c>
       <c r="G329">
-        <v>482060421</v>
+        <v>394554423</v>
       </c>
       <c r="H329">
         <v>0</v>
@@ -9842,13 +9842,13 @@
         <v>0</v>
       </c>
       <c r="E330">
-        <v>37523444</v>
+        <v>42900076</v>
       </c>
       <c r="F330">
-        <v>37523444</v>
+        <v>42900076</v>
       </c>
       <c r="G330">
-        <v>15912675</v>
+        <v>10536043</v>
       </c>
       <c r="H330">
         <v>0</v>
@@ -9868,13 +9868,13 @@
         <v>0</v>
       </c>
       <c r="E331">
-        <v>1083487547</v>
+        <v>1144195047</v>
       </c>
       <c r="F331">
-        <v>1083487547</v>
+        <v>1144195047</v>
       </c>
       <c r="G331">
-        <v>366224832</v>
+        <v>305517332</v>
       </c>
       <c r="H331">
         <v>0</v>
@@ -9917,16 +9917,16 @@
         <v>30454436960</v>
       </c>
       <c r="D333">
-        <v>3223617670</v>
+        <v>3193038426</v>
       </c>
       <c r="E333">
-        <v>20312291564</v>
+        <v>21293774273</v>
       </c>
       <c r="F333">
-        <v>23535909234</v>
+        <v>24486812699</v>
       </c>
       <c r="G333">
-        <v>6918527726</v>
+        <v>5967624261</v>
       </c>
       <c r="H333">
         <v>260139500</v>
@@ -10021,10 +10021,10 @@
         <v>2593734264</v>
       </c>
       <c r="D337">
-        <v>1159171896</v>
+        <v>1120961396</v>
       </c>
       <c r="E337">
-        <v>1434562314</v>
+        <v>1472772814</v>
       </c>
       <c r="F337">
         <v>2593734210</v>
@@ -10125,10 +10125,10 @@
         <v>1748195004</v>
       </c>
       <c r="D341">
-        <v>521192372</v>
+        <v>450378225</v>
       </c>
       <c r="E341">
-        <v>1081786638</v>
+        <v>1152600785</v>
       </c>
       <c r="F341">
         <v>1602979010</v>
@@ -10544,13 +10544,13 @@
         <v>0</v>
       </c>
       <c r="E357">
-        <v>6702754642</v>
+        <v>7461261168</v>
       </c>
       <c r="F357">
-        <v>6702754642</v>
+        <v>7461261168</v>
       </c>
       <c r="G357">
-        <v>4012161371</v>
+        <v>3253654845</v>
       </c>
       <c r="H357">
         <v>0</v>
@@ -10570,13 +10570,13 @@
         <v>0</v>
       </c>
       <c r="E358">
-        <v>156117929</v>
+        <v>178190770</v>
       </c>
       <c r="F358">
-        <v>156117929</v>
+        <v>178190770</v>
       </c>
       <c r="G358">
-        <v>119702503</v>
+        <v>97629662</v>
       </c>
       <c r="H358">
         <v>0</v>
@@ -10596,13 +10596,13 @@
         <v>0</v>
       </c>
       <c r="E359">
-        <v>8463904517</v>
+        <v>8834277017</v>
       </c>
       <c r="F359">
-        <v>8463904517</v>
+        <v>8834277017</v>
       </c>
       <c r="G359">
-        <v>2068259685</v>
+        <v>1697887185</v>
       </c>
       <c r="H359">
         <v>0</v>
@@ -10648,13 +10648,13 @@
         <v>0</v>
       </c>
       <c r="E361">
-        <v>785700027</v>
+        <v>877080231</v>
       </c>
       <c r="F361">
-        <v>785700027</v>
+        <v>877080231</v>
       </c>
       <c r="G361">
-        <v>505894618</v>
+        <v>414514414</v>
       </c>
       <c r="H361">
         <v>0</v>
@@ -10674,13 +10674,13 @@
         <v>0</v>
       </c>
       <c r="E362">
-        <v>27277614</v>
+        <v>31174416</v>
       </c>
       <c r="F362">
-        <v>27277614</v>
+        <v>31174416</v>
       </c>
       <c r="G362">
-        <v>20133132</v>
+        <v>16236330</v>
       </c>
       <c r="H362">
         <v>0</v>
@@ -10700,13 +10700,13 @@
         <v>0</v>
       </c>
       <c r="E363">
-        <v>1169059101</v>
+        <v>1236176601</v>
       </c>
       <c r="F363">
-        <v>1169059101</v>
+        <v>1236176601</v>
       </c>
       <c r="G363">
-        <v>353959003</v>
+        <v>286841503</v>
       </c>
       <c r="H363">
         <v>0</v>
@@ -10749,16 +10749,16 @@
         <v>57427089299</v>
       </c>
       <c r="D365">
-        <v>10759064828</v>
+        <v>10650040181</v>
       </c>
       <c r="E365">
-        <v>37231305578</v>
+        <v>38653676598</v>
       </c>
       <c r="F365">
-        <v>47990370406</v>
+        <v>49303716779</v>
       </c>
       <c r="G365">
-        <v>9436718893</v>
+        <v>8123372520</v>
       </c>
       <c r="H365">
         <v>526334925</v>
@@ -10957,10 +10957,10 @@
         <v>1400000000</v>
       </c>
       <c r="D373">
-        <v>372383814</v>
+        <v>340127864</v>
       </c>
       <c r="E373">
-        <v>440690750</v>
+        <v>472946700</v>
       </c>
       <c r="F373">
         <v>813074564</v>
@@ -11165,16 +11165,16 @@
         <v>120000000</v>
       </c>
       <c r="D381">
-        <v>23824605</v>
+        <v>34092480</v>
       </c>
       <c r="E381">
         <v>29148000</v>
       </c>
       <c r="F381">
-        <v>52972605</v>
+        <v>63240480</v>
       </c>
       <c r="G381">
-        <v>67027395</v>
+        <v>56759520</v>
       </c>
       <c r="H381">
         <v>40000000</v>
@@ -11376,13 +11376,13 @@
         <v>0</v>
       </c>
       <c r="E389">
-        <v>2882978736</v>
+        <v>3205034550</v>
       </c>
       <c r="F389">
-        <v>2882978736</v>
+        <v>3205034550</v>
       </c>
       <c r="G389">
-        <v>1656828182</v>
+        <v>1334772368</v>
       </c>
       <c r="H389">
         <v>0</v>
@@ -11402,13 +11402,13 @@
         <v>0</v>
       </c>
       <c r="E390">
-        <v>45075445</v>
+        <v>50954916</v>
       </c>
       <c r="F390">
-        <v>45075445</v>
+        <v>50954916</v>
       </c>
       <c r="G390">
-        <v>37979124</v>
+        <v>32099653</v>
       </c>
       <c r="H390">
         <v>0</v>
@@ -11428,13 +11428,13 @@
         <v>0</v>
       </c>
       <c r="E391">
-        <v>3613827147</v>
+        <v>3783992147</v>
       </c>
       <c r="F391">
-        <v>3613827147</v>
+        <v>3783992147</v>
       </c>
       <c r="G391">
-        <v>1055812455</v>
+        <v>885647455</v>
       </c>
       <c r="H391">
         <v>0</v>
@@ -11480,13 +11480,13 @@
         <v>0</v>
       </c>
       <c r="E393">
-        <v>496709820</v>
+        <v>543755943</v>
       </c>
       <c r="F393">
-        <v>496709820</v>
+        <v>543755943</v>
       </c>
       <c r="G393">
-        <v>298403613</v>
+        <v>251357490</v>
       </c>
       <c r="H393">
         <v>0</v>
@@ -11506,13 +11506,13 @@
         <v>0</v>
       </c>
       <c r="E394">
-        <v>13903254</v>
+        <v>15895946</v>
       </c>
       <c r="F394">
-        <v>13903254</v>
+        <v>15895946</v>
       </c>
       <c r="G394">
-        <v>23590681</v>
+        <v>21597989</v>
       </c>
       <c r="H394">
         <v>0</v>
@@ -11532,13 +11532,13 @@
         <v>0</v>
       </c>
       <c r="E395">
-        <v>749223046</v>
+        <v>793153046</v>
       </c>
       <c r="F395">
-        <v>749223046</v>
+        <v>793153046</v>
       </c>
       <c r="G395">
-        <v>211010803</v>
+        <v>167080803</v>
       </c>
       <c r="H395">
         <v>0</v>
@@ -11581,16 +11581,16 @@
         <v>24628424376</v>
       </c>
       <c r="D397">
-        <v>4489127044</v>
+        <v>4467138969</v>
       </c>
       <c r="E397">
-        <v>14556690563</v>
+        <v>15180015613</v>
       </c>
       <c r="F397">
-        <v>19045817607</v>
+        <v>19647154582</v>
       </c>
       <c r="G397">
-        <v>5582606769</v>
+        <v>4981269794</v>
       </c>
       <c r="H397">
         <v>232675000</v>
@@ -12260,13 +12260,13 @@
         <v>0</v>
       </c>
       <c r="E423">
-        <v>5322356250</v>
+        <v>5978595221</v>
       </c>
       <c r="F423">
-        <v>5322356250</v>
+        <v>5978595221</v>
       </c>
       <c r="G423">
-        <v>3318989461</v>
+        <v>2662750490</v>
       </c>
       <c r="H423">
         <v>0</v>
@@ -12286,13 +12286,13 @@
         <v>0</v>
       </c>
       <c r="E424">
-        <v>26815861</v>
+        <v>30070682</v>
       </c>
       <c r="F424">
-        <v>26815861</v>
+        <v>30070682</v>
       </c>
       <c r="G424">
-        <v>24008218</v>
+        <v>20753397</v>
       </c>
       <c r="H424">
         <v>0</v>
@@ -12312,13 +12312,13 @@
         <v>0</v>
       </c>
       <c r="E425">
-        <v>6990462089</v>
+        <v>7295042089</v>
       </c>
       <c r="F425">
-        <v>6990462089</v>
+        <v>7295042089</v>
       </c>
       <c r="G425">
-        <v>2389106403</v>
+        <v>2084526403</v>
       </c>
       <c r="H425">
         <v>0</v>
@@ -12364,13 +12364,13 @@
         <v>0</v>
       </c>
       <c r="E427">
-        <v>528519217</v>
+        <v>572732092</v>
       </c>
       <c r="F427">
-        <v>528519217</v>
+        <v>572732092</v>
       </c>
       <c r="G427">
-        <v>375970429</v>
+        <v>331757554</v>
       </c>
       <c r="H427">
         <v>0</v>
@@ -12390,13 +12390,13 @@
         <v>0</v>
       </c>
       <c r="E428">
-        <v>13363987</v>
+        <v>15280907</v>
       </c>
       <c r="F428">
-        <v>13363987</v>
+        <v>15280907</v>
       </c>
       <c r="G428">
-        <v>9432609</v>
+        <v>7515689</v>
       </c>
       <c r="H428">
         <v>0</v>
@@ -12416,13 +12416,13 @@
         <v>0</v>
       </c>
       <c r="E429">
-        <v>848908632</v>
+        <v>899228632</v>
       </c>
       <c r="F429">
-        <v>848908632</v>
+        <v>899228632</v>
       </c>
       <c r="G429">
-        <v>256974815</v>
+        <v>206654815</v>
       </c>
       <c r="H429">
         <v>0</v>
@@ -12468,13 +12468,13 @@
         <v>5912822124</v>
       </c>
       <c r="E431">
-        <v>19621618142</v>
+        <v>20682141729</v>
       </c>
       <c r="F431">
-        <v>25534440266</v>
+        <v>26594963853</v>
       </c>
       <c r="G431">
-        <v>9923921374</v>
+        <v>8863397787</v>
       </c>
       <c r="H431">
         <v>472807750</v>
@@ -13541,10 +13541,10 @@
         <v>2312795000</v>
       </c>
       <c r="D495">
-        <v>1335015186</v>
+        <v>1297031850</v>
       </c>
       <c r="E495">
-        <v>564810618</v>
+        <v>602793954</v>
       </c>
       <c r="F495">
         <v>1899825804</v>
@@ -13567,16 +13567,16 @@
         <v>4989900000</v>
       </c>
       <c r="D496">
-        <v>2351193977</v>
+        <v>2540611977</v>
       </c>
       <c r="E496">
-        <v>1304104604</v>
+        <v>1331606604</v>
       </c>
       <c r="F496">
-        <v>3655298581</v>
+        <v>3872218581</v>
       </c>
       <c r="G496">
-        <v>1334601419</v>
+        <v>1117681419</v>
       </c>
       <c r="H496">
         <v>0</v>
@@ -13619,16 +13619,16 @@
         <v>1680000000</v>
       </c>
       <c r="D498">
-        <v>52561000</v>
+        <v>0</v>
       </c>
       <c r="E498">
-        <v>907924249</v>
+        <v>927726749</v>
       </c>
       <c r="F498">
-        <v>960485249</v>
+        <v>927726749</v>
       </c>
       <c r="G498">
-        <v>719514751</v>
+        <v>752273251</v>
       </c>
       <c r="H498">
         <v>0</v>
@@ -13749,16 +13749,16 @@
         <v>745000000</v>
       </c>
       <c r="D503">
-        <v>679970734</v>
+        <v>678944934</v>
       </c>
       <c r="E503">
         <v>51881480</v>
       </c>
       <c r="F503">
-        <v>731852214</v>
+        <v>730826414</v>
       </c>
       <c r="G503">
-        <v>13147786</v>
+        <v>14173586</v>
       </c>
       <c r="H503">
         <v>0</v>
@@ -13775,10 +13775,10 @@
         <v>7401091133</v>
       </c>
       <c r="D504">
-        <v>4709108116</v>
+        <v>4676900116</v>
       </c>
       <c r="E504">
-        <v>2575531789</v>
+        <v>2607739789</v>
       </c>
       <c r="F504">
         <v>7284639905</v>
@@ -13905,16 +13905,16 @@
         <v>1016150000</v>
       </c>
       <c r="D509">
-        <v>102765000</v>
+        <v>122915000</v>
       </c>
       <c r="E509">
         <v>367300000</v>
       </c>
       <c r="F509">
-        <v>470065000</v>
+        <v>490215000</v>
       </c>
       <c r="G509">
-        <v>546085000</v>
+        <v>525935000</v>
       </c>
       <c r="H509">
         <v>0</v>
@@ -13931,16 +13931,16 @@
         <v>2560000000</v>
       </c>
       <c r="D510">
-        <v>10404406</v>
+        <v>8404406</v>
       </c>
       <c r="E510">
         <v>1480076340</v>
       </c>
       <c r="F510">
-        <v>1490480746</v>
+        <v>1488480746</v>
       </c>
       <c r="G510">
-        <v>1069519254</v>
+        <v>1071519254</v>
       </c>
       <c r="H510">
         <v>0</v>
@@ -14061,16 +14061,16 @@
         <v>516433500</v>
       </c>
       <c r="D515">
-        <v>52951868</v>
+        <v>1480000</v>
       </c>
       <c r="E515">
-        <v>300638120</v>
+        <v>341354080</v>
       </c>
       <c r="F515">
-        <v>353589988</v>
+        <v>342834080</v>
       </c>
       <c r="G515">
-        <v>162843512</v>
+        <v>173599420</v>
       </c>
       <c r="H515">
         <v>172144500</v>
@@ -14246,13 +14246,13 @@
         <v>446366</v>
       </c>
       <c r="E522">
-        <v>7944074780</v>
+        <v>8955396549</v>
       </c>
       <c r="F522">
-        <v>7944521146</v>
+        <v>8955842915</v>
       </c>
       <c r="G522">
-        <v>4219760751</v>
+        <v>3208438982</v>
       </c>
       <c r="H522">
         <v>0</v>
@@ -14272,13 +14272,13 @@
         <v>0</v>
       </c>
       <c r="E523">
-        <v>64689881</v>
+        <v>73959168</v>
       </c>
       <c r="F523">
-        <v>64689881</v>
+        <v>73959168</v>
       </c>
       <c r="G523">
-        <v>46818318</v>
+        <v>37549031</v>
       </c>
       <c r="H523">
         <v>0</v>
@@ -14298,13 +14298,13 @@
         <v>34095622</v>
       </c>
       <c r="E524">
-        <v>9388590459</v>
+        <v>9762745459</v>
       </c>
       <c r="F524">
-        <v>9422686081</v>
+        <v>9796841081</v>
       </c>
       <c r="G524">
-        <v>1378718116</v>
+        <v>1004563116</v>
       </c>
       <c r="H524">
         <v>0</v>
@@ -14350,13 +14350,13 @@
         <v>0</v>
       </c>
       <c r="E526">
-        <v>837687932</v>
+        <v>904971540</v>
       </c>
       <c r="F526">
-        <v>837687932</v>
+        <v>904971540</v>
       </c>
       <c r="G526">
-        <v>614997307</v>
+        <v>547713699</v>
       </c>
       <c r="H526">
         <v>0</v>
@@ -14376,13 +14376,13 @@
         <v>0</v>
       </c>
       <c r="E527">
-        <v>18569241</v>
+        <v>20463742</v>
       </c>
       <c r="F527">
-        <v>18569241</v>
+        <v>20463742</v>
       </c>
       <c r="G527">
-        <v>16596157</v>
+        <v>14701656</v>
       </c>
       <c r="H527">
         <v>0</v>
@@ -14402,13 +14402,13 @@
         <v>0</v>
       </c>
       <c r="E528">
-        <v>1319466245</v>
+        <v>1383516245</v>
       </c>
       <c r="F528">
-        <v>1319466245</v>
+        <v>1383516245</v>
       </c>
       <c r="G528">
-        <v>379282256</v>
+        <v>315232256</v>
       </c>
       <c r="H528">
         <v>0</v>
@@ -14477,16 +14477,16 @@
         <v>64019485320</v>
       </c>
       <c r="D531">
-        <v>15073569474</v>
+        <v>15105887470</v>
       </c>
       <c r="E531">
-        <v>37023652105</v>
+        <v>38709838066</v>
       </c>
       <c r="F531">
-        <v>52097221579</v>
+        <v>53815725536</v>
       </c>
       <c r="G531">
-        <v>11922263741</v>
+        <v>10203759784</v>
       </c>
       <c r="H531">
         <v>850782250</v>
@@ -14503,16 +14503,16 @@
         <v>5572131338</v>
       </c>
       <c r="D532">
-        <v>3145457538</v>
+        <v>2544873068</v>
       </c>
       <c r="E532">
-        <v>2426673800</v>
+        <v>3019133270</v>
       </c>
       <c r="F532">
-        <v>5572131338</v>
+        <v>5564006338</v>
       </c>
       <c r="G532">
-        <v>0</v>
+        <v>8125000</v>
       </c>
       <c r="H532">
         <v>0</v>
@@ -14685,16 +14685,16 @@
         <v>2103744312</v>
       </c>
       <c r="D539">
-        <v>1312533715</v>
+        <v>1300493715</v>
       </c>
       <c r="E539">
         <v>330635136</v>
       </c>
       <c r="F539">
-        <v>1643168851</v>
+        <v>1631128851</v>
       </c>
       <c r="G539">
-        <v>460575461</v>
+        <v>472615461</v>
       </c>
       <c r="H539">
         <v>0</v>
@@ -14893,16 +14893,16 @@
         <v>1539315000</v>
       </c>
       <c r="D547">
-        <v>6318539</v>
+        <v>6662233</v>
       </c>
       <c r="E547">
         <v>808990194</v>
       </c>
       <c r="F547">
-        <v>815308733</v>
+        <v>815652427</v>
       </c>
       <c r="G547">
-        <v>724006267</v>
+        <v>723662573</v>
       </c>
       <c r="H547">
         <v>0</v>
@@ -15023,16 +15023,16 @@
         <v>336802500</v>
       </c>
       <c r="D552">
-        <v>13070734</v>
+        <v>1037234</v>
       </c>
       <c r="E552">
-        <v>224462101</v>
+        <v>237070601</v>
       </c>
       <c r="F552">
-        <v>237532835</v>
+        <v>238107835</v>
       </c>
       <c r="G552">
-        <v>99269665</v>
+        <v>98694665</v>
       </c>
       <c r="H552">
         <v>112267500</v>
@@ -15104,13 +15104,13 @@
         <v>0</v>
       </c>
       <c r="E555">
-        <v>6978673704</v>
+        <v>7783248643</v>
       </c>
       <c r="F555">
-        <v>6978673704</v>
+        <v>7783248643</v>
       </c>
       <c r="G555">
-        <v>3710243162</v>
+        <v>2905668223</v>
       </c>
       <c r="H555">
         <v>0</v>
@@ -15130,13 +15130,13 @@
         <v>0</v>
       </c>
       <c r="E556">
-        <v>58355201</v>
+        <v>66405673</v>
       </c>
       <c r="F556">
-        <v>58355201</v>
+        <v>66405673</v>
       </c>
       <c r="G556">
-        <v>47760850</v>
+        <v>39710378</v>
       </c>
       <c r="H556">
         <v>0</v>
@@ -15156,13 +15156,13 @@
         <v>0</v>
       </c>
       <c r="E557">
-        <v>7813480609</v>
+        <v>8138428109</v>
       </c>
       <c r="F557">
-        <v>7813480609</v>
+        <v>8138428109</v>
       </c>
       <c r="G557">
-        <v>1404845734</v>
+        <v>1079898234</v>
       </c>
       <c r="H557">
         <v>0</v>
@@ -15208,13 +15208,13 @@
         <v>0</v>
       </c>
       <c r="E559">
-        <v>964916045</v>
+        <v>1070667022</v>
       </c>
       <c r="F559">
-        <v>964916045</v>
+        <v>1070667022</v>
       </c>
       <c r="G559">
-        <v>457889908</v>
+        <v>352138931</v>
       </c>
       <c r="H559">
         <v>0</v>
@@ -15234,13 +15234,13 @@
         <v>0</v>
       </c>
       <c r="E560">
-        <v>12220296</v>
+        <v>14429903</v>
       </c>
       <c r="F560">
-        <v>12220296</v>
+        <v>14429903</v>
       </c>
       <c r="G560">
-        <v>1696462</v>
+        <v>-513145</v>
       </c>
       <c r="H560">
         <v>0</v>
@@ -15260,13 +15260,13 @@
         <v>0</v>
       </c>
       <c r="E561">
-        <v>1337346547</v>
+        <v>1417284047</v>
       </c>
       <c r="F561">
-        <v>1337346547</v>
+        <v>1417284047</v>
       </c>
       <c r="G561">
-        <v>222336214</v>
+        <v>142398714</v>
       </c>
       <c r="H561">
         <v>0</v>
@@ -15309,16 +15309,16 @@
         <v>57848682223</v>
       </c>
       <c r="D563">
-        <v>22414939761</v>
+        <v>21790625485</v>
       </c>
       <c r="E563">
-        <v>27107531591</v>
+        <v>29038070556</v>
       </c>
       <c r="F563">
-        <v>49522471352</v>
+        <v>50828696041</v>
       </c>
       <c r="G563">
-        <v>8326210871</v>
+        <v>7019986182</v>
       </c>
       <c r="H563">
         <v>720558750</v>
@@ -15335,16 +15335,16 @@
         <v>1109026106817</v>
       </c>
       <c r="D564">
-        <v>424640852660</v>
+        <v>421610814578</v>
       </c>
       <c r="E564">
-        <v>506904392126</v>
+        <v>531269049789</v>
       </c>
       <c r="F564">
-        <v>931545244786</v>
+        <v>952879864367</v>
       </c>
       <c r="G564">
-        <v>177480862031</v>
+        <v>156146242450</v>
       </c>
       <c r="H564">
         <v>9532277322</v>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{3D820F8D-01D9-4924-A5FD-2937C2CEBE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{2798F89F-2E75-4145-ADF4-908F93DE8936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4752" yWindow="3060" windowWidth="17280" windowHeight="9180"/>
+    <workbookView xWindow="1476" yWindow="2508" windowWidth="17280" windowHeight="9180"/>
   </bookViews>
   <sheets>
-    <sheet name="20260826 SAP ZFM01" sheetId="1" r:id="rId1"/>
+    <sheet name="20260828 SAP ZFM01" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -1753,10 +1753,10 @@
         <v>4500000000</v>
       </c>
       <c r="D19">
-        <v>712280958</v>
+        <v>346244860</v>
       </c>
       <c r="E19">
-        <v>2197901531</v>
+        <v>2563937629</v>
       </c>
       <c r="F19">
         <v>2910182489</v>
@@ -1883,10 +1883,10 @@
         <v>600000000</v>
       </c>
       <c r="D24">
-        <v>48909273</v>
+        <v>45991873</v>
       </c>
       <c r="E24">
-        <v>197480759</v>
+        <v>200398159</v>
       </c>
       <c r="F24">
         <v>246390032</v>
@@ -1903,22 +1903,22 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>2330417149</v>
+        <v>2312674754</v>
       </c>
       <c r="C25">
-        <v>1705417149</v>
+        <v>1687674754</v>
       </c>
       <c r="D25">
-        <v>21639448</v>
+        <v>24624440</v>
       </c>
       <c r="E25">
-        <v>999834993</v>
+        <v>1016652693</v>
       </c>
       <c r="F25">
-        <v>1021474441</v>
+        <v>1041277133</v>
       </c>
       <c r="G25">
-        <v>683942708</v>
+        <v>646397621</v>
       </c>
       <c r="H25">
         <v>625000000</v>
@@ -1964,13 +1964,13 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>-25600000</v>
+        <v>-33900000</v>
       </c>
       <c r="F27">
-        <v>-25600000</v>
+        <v>-33900000</v>
       </c>
       <c r="G27">
-        <v>25600000</v>
+        <v>33900000</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1990,13 +1990,13 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2832001403</v>
+        <v>2832626715</v>
       </c>
       <c r="F28">
-        <v>2832001403</v>
+        <v>2832626715</v>
       </c>
       <c r="G28">
-        <v>624612801</v>
+        <v>623987489</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2345,22 +2345,22 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>350791161935</v>
+        <v>350773419540</v>
       </c>
       <c r="C42">
-        <v>348373661935</v>
+        <v>348355919540</v>
       </c>
       <c r="D42">
-        <v>237743196133</v>
+        <v>237377227627</v>
       </c>
       <c r="E42">
-        <v>93437186120</v>
+        <v>93815282630</v>
       </c>
       <c r="F42">
-        <v>331180382253</v>
+        <v>331192510257</v>
       </c>
       <c r="G42">
-        <v>17193279682</v>
+        <v>17163409283</v>
       </c>
       <c r="H42">
         <v>2417500000</v>
@@ -2377,10 +2377,10 @@
         <v>26681487101</v>
       </c>
       <c r="D43">
-        <v>19324699101</v>
+        <v>16927499101</v>
       </c>
       <c r="E43">
-        <v>6898038000</v>
+        <v>9295238000</v>
       </c>
       <c r="F43">
         <v>26222737101</v>
@@ -2689,16 +2689,16 @@
         <v>4260000000</v>
       </c>
       <c r="D55">
-        <v>1100095959</v>
+        <v>1334548459</v>
       </c>
       <c r="E55">
         <v>2040648478</v>
       </c>
       <c r="F55">
-        <v>3140744437</v>
+        <v>3375196937</v>
       </c>
       <c r="G55">
-        <v>1119255563</v>
+        <v>884803063</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -2793,16 +2793,16 @@
         <v>5363288603</v>
       </c>
       <c r="D59">
-        <v>4411417920</v>
+        <v>4905141920</v>
       </c>
       <c r="E59">
         <v>393848820</v>
       </c>
       <c r="F59">
-        <v>4805266740</v>
+        <v>5298990740</v>
       </c>
       <c r="G59">
-        <v>558021863</v>
+        <v>64297863</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -2819,16 +2819,16 @@
         <v>2620000000</v>
       </c>
       <c r="D60">
-        <v>633371738</v>
+        <v>635195738</v>
       </c>
       <c r="E60">
         <v>738524117</v>
       </c>
       <c r="F60">
-        <v>1371895855</v>
+        <v>1373719855</v>
       </c>
       <c r="G60">
-        <v>1248104145</v>
+        <v>1246280145</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -2897,16 +2897,16 @@
         <v>2500000000</v>
       </c>
       <c r="D63">
-        <v>1798665100</v>
+        <v>2292561100</v>
       </c>
       <c r="E63">
         <v>48645000</v>
       </c>
       <c r="F63">
-        <v>1847310100</v>
+        <v>2341206100</v>
       </c>
       <c r="G63">
-        <v>652689900</v>
+        <v>158793900</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -2978,13 +2978,13 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>1710653853</v>
+        <v>1973296791</v>
       </c>
       <c r="F66">
-        <v>1710653853</v>
+        <v>1973296791</v>
       </c>
       <c r="G66">
-        <v>1789346147</v>
+        <v>1526703209</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -3001,16 +3001,16 @@
         <v>400400000</v>
       </c>
       <c r="D67">
-        <v>14042510</v>
+        <v>23372510</v>
       </c>
       <c r="E67">
         <v>119056922</v>
       </c>
       <c r="F67">
-        <v>133099432</v>
+        <v>142429432</v>
       </c>
       <c r="G67">
-        <v>267300568</v>
+        <v>257970568</v>
       </c>
       <c r="H67">
         <v>139000000</v>
@@ -3079,16 +3079,16 @@
         <v>608104500</v>
       </c>
       <c r="D70">
+        <v>547662078</v>
+      </c>
+      <c r="E70">
         <v>47700000</v>
       </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
       <c r="F70">
-        <v>47700000</v>
+        <v>595362078</v>
       </c>
       <c r="G70">
-        <v>560404500</v>
+        <v>12742422</v>
       </c>
       <c r="H70">
         <v>202701500</v>
@@ -3134,13 +3134,13 @@
         <v>46676000</v>
       </c>
       <c r="E72">
-        <v>252103000</v>
+        <v>253203000</v>
       </c>
       <c r="F72">
-        <v>298779000</v>
+        <v>299879000</v>
       </c>
       <c r="G72">
-        <v>55446000</v>
+        <v>54346000</v>
       </c>
       <c r="H72">
         <v>118075000</v>
@@ -3212,13 +3212,13 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>16582271780</v>
+        <v>16582316780</v>
       </c>
       <c r="F75">
-        <v>16582271780</v>
+        <v>16582316780</v>
       </c>
       <c r="G75">
-        <v>6349335449</v>
+        <v>6349290449</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -3443,16 +3443,16 @@
         <v>110881210191</v>
       </c>
       <c r="D84">
-        <v>35589404709</v>
+        <v>34925393287</v>
       </c>
       <c r="E84">
-        <v>54095035885</v>
+        <v>56803723823</v>
       </c>
       <c r="F84">
-        <v>89684440594</v>
+        <v>91729117110</v>
       </c>
       <c r="G84">
-        <v>21196769597</v>
+        <v>19152093081</v>
       </c>
       <c r="H84">
         <v>671501500</v>
@@ -3547,16 +3547,16 @@
         <v>2171936232</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1867836847</v>
       </c>
       <c r="E88">
         <v>169548600</v>
       </c>
       <c r="F88">
-        <v>169548600</v>
+        <v>2037385447</v>
       </c>
       <c r="G88">
-        <v>2002387632</v>
+        <v>134550785</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -3573,16 +3573,16 @@
         <v>30639775739</v>
       </c>
       <c r="D89">
-        <v>13930855381</v>
+        <v>13999803457</v>
       </c>
       <c r="E89">
         <v>11923554821</v>
       </c>
       <c r="F89">
-        <v>25854410202</v>
+        <v>25923358278</v>
       </c>
       <c r="G89">
-        <v>4785365537</v>
+        <v>4716417461</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -3651,16 +3651,16 @@
         <v>1210765056</v>
       </c>
       <c r="D92">
-        <v>470801940</v>
+        <v>519559940</v>
       </c>
       <c r="E92">
-        <v>135534440</v>
+        <v>159842440</v>
       </c>
       <c r="F92">
-        <v>606336380</v>
+        <v>679402380</v>
       </c>
       <c r="G92">
-        <v>604428676</v>
+        <v>531362676</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -3703,10 +3703,10 @@
         <v>2796520000</v>
       </c>
       <c r="D94">
-        <v>838415594</v>
+        <v>779640794</v>
       </c>
       <c r="E94">
-        <v>1905663067</v>
+        <v>1964437867</v>
       </c>
       <c r="F94">
         <v>2744078661</v>
@@ -3781,10 +3781,10 @@
         <v>400000000</v>
       </c>
       <c r="D97">
-        <v>133155850</v>
+        <v>36520000</v>
       </c>
       <c r="E97">
-        <v>266658377</v>
+        <v>363294227</v>
       </c>
       <c r="F97">
         <v>399814227</v>
@@ -3807,10 +3807,10 @@
         <v>289155000</v>
       </c>
       <c r="D98">
-        <v>50584000</v>
+        <v>20359000</v>
       </c>
       <c r="E98">
-        <v>26875000</v>
+        <v>57100000</v>
       </c>
       <c r="F98">
         <v>77459000</v>
@@ -3833,10 +3833,10 @@
         <v>360000000</v>
       </c>
       <c r="D99">
-        <v>109591976</v>
+        <v>105051976</v>
       </c>
       <c r="E99">
-        <v>199678000</v>
+        <v>204218000</v>
       </c>
       <c r="F99">
         <v>309269976</v>
@@ -4044,13 +4044,13 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>290216068</v>
+        <v>291178568</v>
       </c>
       <c r="F107">
-        <v>290216068</v>
+        <v>291178568</v>
       </c>
       <c r="G107">
-        <v>4841432</v>
+        <v>3878932</v>
       </c>
       <c r="H107">
         <v>98352500</v>
@@ -4174,13 +4174,13 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>11991989449</v>
+        <v>11992032574</v>
       </c>
       <c r="F112">
-        <v>11991989449</v>
+        <v>11992032574</v>
       </c>
       <c r="G112">
-        <v>4231655404</v>
+        <v>4231612279</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -4405,16 +4405,16 @@
         <v>81693644736</v>
       </c>
       <c r="D121">
-        <v>17142076389</v>
+        <v>18937443662</v>
       </c>
       <c r="E121">
-        <v>49571852034</v>
+        <v>49787341309</v>
       </c>
       <c r="F121">
-        <v>66713928423</v>
+        <v>68724784971</v>
       </c>
       <c r="G121">
-        <v>14979716313</v>
+        <v>12968859765</v>
       </c>
       <c r="H121">
         <v>475697500</v>
@@ -4613,16 +4613,16 @@
         <v>1665000000</v>
       </c>
       <c r="D129">
-        <v>135800338</v>
+        <v>131959351</v>
       </c>
       <c r="E129">
-        <v>651694746</v>
+        <v>665520348</v>
       </c>
       <c r="F129">
-        <v>787495084</v>
+        <v>797479699</v>
       </c>
       <c r="G129">
-        <v>877504916</v>
+        <v>867520301</v>
       </c>
       <c r="H129">
         <v>0</v>
@@ -4665,16 +4665,16 @@
         <v>1178928488</v>
       </c>
       <c r="D131">
-        <v>498928488</v>
+        <v>488102720</v>
       </c>
       <c r="E131">
         <v>504755234</v>
       </c>
       <c r="F131">
-        <v>1003683722</v>
+        <v>992857954</v>
       </c>
       <c r="G131">
-        <v>175244766</v>
+        <v>186070534</v>
       </c>
       <c r="H131">
         <v>0</v>
@@ -4850,13 +4850,13 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>1129154141</v>
+        <v>1290704313</v>
       </c>
       <c r="F138">
-        <v>1129154141</v>
+        <v>1290704313</v>
       </c>
       <c r="G138">
-        <v>1130845859</v>
+        <v>969295687</v>
       </c>
       <c r="H138">
         <v>0</v>
@@ -4899,16 +4899,16 @@
         <v>265950000</v>
       </c>
       <c r="D140">
-        <v>20030924</v>
+        <v>14000000</v>
       </c>
       <c r="E140">
-        <v>200998200</v>
+        <v>206966600</v>
       </c>
       <c r="F140">
-        <v>221029124</v>
+        <v>220966600</v>
       </c>
       <c r="G140">
-        <v>44920876</v>
+        <v>44983400</v>
       </c>
       <c r="H140">
         <v>88650000</v>
@@ -4951,16 +4951,16 @@
         <v>203550000</v>
       </c>
       <c r="D142">
-        <v>1556050</v>
+        <v>2380000</v>
       </c>
       <c r="E142">
-        <v>175647932</v>
+        <v>177203982</v>
       </c>
       <c r="F142">
-        <v>177203982</v>
+        <v>179583982</v>
       </c>
       <c r="G142">
-        <v>26346018</v>
+        <v>23966018</v>
       </c>
       <c r="H142">
         <v>67850000</v>
@@ -4980,13 +4980,13 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>136422250</v>
+        <v>137234750</v>
       </c>
       <c r="F143">
-        <v>136422250</v>
+        <v>137234750</v>
       </c>
       <c r="G143">
-        <v>23567750</v>
+        <v>22755250</v>
       </c>
       <c r="H143">
         <v>53330000</v>
@@ -5058,13 +5058,13 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>7119228325</v>
+        <v>7119258325</v>
       </c>
       <c r="F146">
-        <v>7119228325</v>
+        <v>7119258325</v>
       </c>
       <c r="G146">
-        <v>2829865758</v>
+        <v>2829835758</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -5289,16 +5289,16 @@
         <v>52173056175</v>
       </c>
       <c r="D155">
-        <v>12431091744</v>
+        <v>12411218015</v>
       </c>
       <c r="E155">
-        <v>29433792198</v>
+        <v>29617534922</v>
       </c>
       <c r="F155">
-        <v>41864883942</v>
+        <v>42028752937</v>
       </c>
       <c r="G155">
-        <v>10308172233</v>
+        <v>10144303238</v>
       </c>
       <c r="H155">
         <v>411080000</v>
@@ -5315,16 +5315,16 @@
         <v>11383511000</v>
       </c>
       <c r="D156">
-        <v>2446592692</v>
+        <v>2790092692</v>
       </c>
       <c r="E156">
         <v>8419849198</v>
       </c>
       <c r="F156">
-        <v>10866441890</v>
+        <v>11209941890</v>
       </c>
       <c r="G156">
-        <v>517069110</v>
+        <v>173569110</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -5471,16 +5471,16 @@
         <v>1702406000</v>
       </c>
       <c r="D162">
-        <v>268394551</v>
+        <v>279213423</v>
       </c>
       <c r="E162">
-        <v>758051975</v>
+        <v>807533375</v>
       </c>
       <c r="F162">
-        <v>1026446526</v>
+        <v>1086746798</v>
       </c>
       <c r="G162">
-        <v>675959474</v>
+        <v>615659202</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -5575,16 +5575,16 @@
         <v>2427860000</v>
       </c>
       <c r="D166">
-        <v>1946134200</v>
+        <v>2301645594</v>
       </c>
       <c r="E166">
         <v>43500000</v>
       </c>
       <c r="F166">
-        <v>1989634200</v>
+        <v>2345145594</v>
       </c>
       <c r="G166">
-        <v>438225800</v>
+        <v>82714406</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -5601,16 +5601,16 @@
         <v>500000000</v>
       </c>
       <c r="D167">
-        <v>50817909</v>
+        <v>54664725</v>
       </c>
       <c r="E167">
-        <v>140006588</v>
+        <v>185788488</v>
       </c>
       <c r="F167">
-        <v>190824497</v>
+        <v>240453213</v>
       </c>
       <c r="G167">
-        <v>309175503</v>
+        <v>259546787</v>
       </c>
       <c r="H167">
         <v>0</v>
@@ -5760,13 +5760,13 @@
         <v>0</v>
       </c>
       <c r="E173">
-        <v>1198080153</v>
+        <v>1367627182</v>
       </c>
       <c r="F173">
-        <v>1198080153</v>
+        <v>1367627182</v>
       </c>
       <c r="G173">
-        <v>1170919847</v>
+        <v>1001372818</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -5783,16 +5783,16 @@
         <v>135000000</v>
       </c>
       <c r="D174">
-        <v>5000000</v>
+        <v>13921000</v>
       </c>
       <c r="E174">
         <v>41244591</v>
       </c>
       <c r="F174">
-        <v>46244591</v>
+        <v>55165591</v>
       </c>
       <c r="G174">
-        <v>88755409</v>
+        <v>79834409</v>
       </c>
       <c r="H174">
         <v>45000000</v>
@@ -5809,16 +5809,16 @@
         <v>595150000</v>
       </c>
       <c r="D175">
-        <v>39155650</v>
+        <v>67876400</v>
       </c>
       <c r="E175">
         <v>451500394</v>
       </c>
       <c r="F175">
-        <v>490656044</v>
+        <v>519376794</v>
       </c>
       <c r="G175">
-        <v>104493956</v>
+        <v>75773206</v>
       </c>
       <c r="H175">
         <v>136250000</v>
@@ -5861,16 +5861,16 @@
         <v>253250000</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>47650000</v>
       </c>
       <c r="E177">
         <v>104678200</v>
       </c>
       <c r="F177">
-        <v>104678200</v>
+        <v>152328200</v>
       </c>
       <c r="G177">
-        <v>148571800</v>
+        <v>100921800</v>
       </c>
       <c r="H177">
         <v>146550000</v>
@@ -5916,13 +5916,13 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>114659250</v>
+        <v>114946750</v>
       </c>
       <c r="F179">
-        <v>114659250</v>
+        <v>114946750</v>
       </c>
       <c r="G179">
-        <v>47642250</v>
+        <v>47354750</v>
       </c>
       <c r="H179">
         <v>54100500</v>
@@ -5968,13 +5968,13 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>5304757088</v>
+        <v>5304760838</v>
       </c>
       <c r="F181">
-        <v>5304757088</v>
+        <v>5304760838</v>
       </c>
       <c r="G181">
-        <v>2199966290</v>
+        <v>2199962540</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -6173,16 +6173,16 @@
         <v>46375593027</v>
       </c>
       <c r="D189">
-        <v>10570552092</v>
+        <v>11369520924</v>
       </c>
       <c r="E189">
-        <v>26693702523</v>
+        <v>26958804102</v>
       </c>
       <c r="F189">
-        <v>37264254615</v>
+        <v>38328325026</v>
       </c>
       <c r="G189">
-        <v>9111338412</v>
+        <v>8047268001</v>
       </c>
       <c r="H189">
         <v>449400500</v>
@@ -6329,16 +6329,16 @@
         <v>3919663677</v>
       </c>
       <c r="D195">
-        <v>3221908605</v>
+        <v>3191872380</v>
       </c>
       <c r="E195">
         <v>530323683</v>
       </c>
       <c r="F195">
-        <v>3752232288</v>
+        <v>3722196063</v>
       </c>
       <c r="G195">
-        <v>167431389</v>
+        <v>197467614</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -6433,10 +6433,10 @@
         <v>400000000</v>
       </c>
       <c r="D199">
-        <v>31779299</v>
+        <v>21270500</v>
       </c>
       <c r="E199">
-        <v>150376000</v>
+        <v>160884799</v>
       </c>
       <c r="F199">
         <v>182155299</v>
@@ -6485,16 +6485,16 @@
         <v>1862650000</v>
       </c>
       <c r="D201">
-        <v>414113067</v>
+        <v>444024067</v>
       </c>
       <c r="E201">
         <v>1262593706</v>
       </c>
       <c r="F201">
-        <v>1676706773</v>
+        <v>1706617773</v>
       </c>
       <c r="G201">
-        <v>185943227</v>
+        <v>156032227</v>
       </c>
       <c r="H201">
         <v>0</v>
@@ -6537,16 +6537,16 @@
         <v>950000000</v>
       </c>
       <c r="D203">
-        <v>455211272</v>
+        <v>447164894</v>
       </c>
       <c r="E203">
         <v>494525000</v>
       </c>
       <c r="F203">
-        <v>949736272</v>
+        <v>941689894</v>
       </c>
       <c r="G203">
-        <v>263728</v>
+        <v>8310106</v>
       </c>
       <c r="H203">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0</v>
       </c>
       <c r="E211">
-        <v>1384670995</v>
+        <v>1584133830</v>
       </c>
       <c r="F211">
-        <v>1384670995</v>
+        <v>1584133830</v>
       </c>
       <c r="G211">
-        <v>1185329005</v>
+        <v>985866170</v>
       </c>
       <c r="H211">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>97500000</v>
       </c>
       <c r="D212">
-        <v>16038456</v>
+        <v>6800000</v>
       </c>
       <c r="E212">
-        <v>61832951</v>
+        <v>71071407</v>
       </c>
       <c r="F212">
         <v>77871407</v>
@@ -6797,10 +6797,10 @@
         <v>385534500</v>
       </c>
       <c r="D213">
-        <v>51096000</v>
+        <v>49485000</v>
       </c>
       <c r="E213">
-        <v>250862000</v>
+        <v>252473000</v>
       </c>
       <c r="F213">
         <v>301958000</v>
@@ -6849,10 +6849,10 @@
         <v>337500000</v>
       </c>
       <c r="D215">
-        <v>71493039</v>
+        <v>60860539</v>
       </c>
       <c r="E215">
-        <v>103870954</v>
+        <v>114503454</v>
       </c>
       <c r="F215">
         <v>175363993</v>
@@ -6904,13 +6904,13 @@
         <v>0</v>
       </c>
       <c r="E217">
-        <v>165969250</v>
+        <v>166331750</v>
       </c>
       <c r="F217">
-        <v>165969250</v>
+        <v>166331750</v>
       </c>
       <c r="G217">
-        <v>23030750</v>
+        <v>22668250</v>
       </c>
       <c r="H217">
         <v>63000000</v>
@@ -6982,13 +6982,13 @@
         <v>0</v>
       </c>
       <c r="E220">
-        <v>7090253342</v>
+        <v>7090260842</v>
       </c>
       <c r="F220">
-        <v>7090253342</v>
+        <v>7090260842</v>
       </c>
       <c r="G220">
-        <v>2732908784</v>
+        <v>2732901284</v>
       </c>
       <c r="H220">
         <v>0</v>
@@ -7187,16 +7187,16 @@
         <v>47499233545</v>
       </c>
       <c r="D228">
-        <v>12413828182</v>
+        <v>12373665824</v>
       </c>
       <c r="E228">
-        <v>27832155242</v>
+        <v>28063978832</v>
       </c>
       <c r="F228">
-        <v>40245983424</v>
+        <v>40437644656</v>
       </c>
       <c r="G228">
-        <v>7253250121</v>
+        <v>7061588889</v>
       </c>
       <c r="H228">
         <v>415261500</v>
@@ -7213,16 +7213,16 @@
         <v>12264606000</v>
       </c>
       <c r="D229">
-        <v>7825292730</v>
+        <v>8206842730</v>
       </c>
       <c r="E229">
         <v>3238064000</v>
       </c>
       <c r="F229">
-        <v>11063356730</v>
+        <v>11444906730</v>
       </c>
       <c r="G229">
-        <v>1201249270</v>
+        <v>819699270</v>
       </c>
       <c r="H229">
         <v>0</v>
@@ -7239,16 +7239,16 @@
         <v>1126306000</v>
       </c>
       <c r="D230">
-        <v>1101323967</v>
+        <v>1108174121</v>
       </c>
       <c r="E230">
         <v>12436007</v>
       </c>
       <c r="F230">
-        <v>1113759974</v>
+        <v>1120610128</v>
       </c>
       <c r="G230">
-        <v>12546026</v>
+        <v>5695872</v>
       </c>
       <c r="H230">
         <v>0</v>
@@ -7317,16 +7317,16 @@
         <v>200000000</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>111648138</v>
       </c>
       <c r="E233">
         <v>80120815</v>
       </c>
       <c r="F233">
-        <v>80120815</v>
+        <v>191768953</v>
       </c>
       <c r="G233">
-        <v>119879185</v>
+        <v>8231047</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -7369,16 +7369,16 @@
         <v>1380000000</v>
       </c>
       <c r="D235">
-        <v>154853460</v>
+        <v>195458460</v>
       </c>
       <c r="E235">
-        <v>1022581967</v>
+        <v>1036121967</v>
       </c>
       <c r="F235">
-        <v>1177435427</v>
+        <v>1231580427</v>
       </c>
       <c r="G235">
-        <v>202564573</v>
+        <v>148419573</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -7473,16 +7473,16 @@
         <v>2264065000</v>
       </c>
       <c r="D239">
-        <v>185595000</v>
+        <v>216195000</v>
       </c>
       <c r="E239">
         <v>2002162000</v>
       </c>
       <c r="F239">
-        <v>2187757000</v>
+        <v>2218357000</v>
       </c>
       <c r="G239">
-        <v>76308000</v>
+        <v>45708000</v>
       </c>
       <c r="H239">
         <v>0</v>
@@ -7606,13 +7606,13 @@
         <v>0</v>
       </c>
       <c r="E244">
-        <v>1384380487</v>
+        <v>1577808685</v>
       </c>
       <c r="F244">
-        <v>1384380487</v>
+        <v>1577808685</v>
       </c>
       <c r="G244">
-        <v>1679195513</v>
+        <v>1485767315</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -7629,10 +7629,10 @@
         <v>110162550</v>
       </c>
       <c r="D245">
-        <v>27360000</v>
+        <v>4980000</v>
       </c>
       <c r="E245">
-        <v>51746000</v>
+        <v>74126000</v>
       </c>
       <c r="F245">
         <v>79106000</v>
@@ -7655,10 +7655,10 @@
         <v>354238500</v>
       </c>
       <c r="D246">
-        <v>65924000</v>
+        <v>38424000</v>
       </c>
       <c r="E246">
-        <v>276936900</v>
+        <v>304436900</v>
       </c>
       <c r="F246">
         <v>342860900</v>
@@ -7736,13 +7736,13 @@
         <v>0</v>
       </c>
       <c r="E249">
-        <v>140931750</v>
+        <v>141694250</v>
       </c>
       <c r="F249">
-        <v>140931750</v>
+        <v>141694250</v>
       </c>
       <c r="G249">
-        <v>61352250</v>
+        <v>60589750</v>
       </c>
       <c r="H249">
         <v>67428000</v>
@@ -7788,13 +7788,13 @@
         <v>0</v>
       </c>
       <c r="E251">
-        <v>6995374202</v>
+        <v>6995383577</v>
       </c>
       <c r="F251">
-        <v>6995374202</v>
+        <v>6995383577</v>
       </c>
       <c r="G251">
-        <v>2830581968</v>
+        <v>2830572593</v>
       </c>
       <c r="H251">
         <v>0</v>
@@ -8019,16 +8019,16 @@
         <v>48914772555</v>
       </c>
       <c r="D260">
-        <v>12239319151</v>
+        <v>12760692443</v>
       </c>
       <c r="E260">
-        <v>27647283143</v>
+        <v>27904903216</v>
       </c>
       <c r="F260">
-        <v>39886602294</v>
+        <v>40665595659</v>
       </c>
       <c r="G260">
-        <v>9028170261</v>
+        <v>8249176896</v>
       </c>
       <c r="H260">
         <v>525212165</v>
@@ -8227,16 +8227,16 @@
         <v>1700000000</v>
       </c>
       <c r="D268">
-        <v>730395140</v>
+        <v>768957140</v>
       </c>
       <c r="E268">
         <v>764581755</v>
       </c>
       <c r="F268">
-        <v>1494976895</v>
+        <v>1533538895</v>
       </c>
       <c r="G268">
-        <v>205023105</v>
+        <v>166461105</v>
       </c>
       <c r="H268">
         <v>0</v>
@@ -8383,16 +8383,16 @@
         <v>5267324000</v>
       </c>
       <c r="D274">
-        <v>1361253881</v>
+        <v>1361253848</v>
       </c>
       <c r="E274">
         <v>3875257936</v>
       </c>
       <c r="F274">
-        <v>5236511817</v>
+        <v>5236511784</v>
       </c>
       <c r="G274">
-        <v>30812183</v>
+        <v>30812216</v>
       </c>
       <c r="H274">
         <v>0</v>
@@ -8620,13 +8620,13 @@
         <v>828300</v>
       </c>
       <c r="E283">
-        <v>1107715962</v>
+        <v>1255815642</v>
       </c>
       <c r="F283">
-        <v>1108544262</v>
+        <v>1256643942</v>
       </c>
       <c r="G283">
-        <v>843805030</v>
+        <v>695705350</v>
       </c>
       <c r="H283">
         <v>0</v>
@@ -8750,13 +8750,13 @@
         <v>0</v>
       </c>
       <c r="E288">
-        <v>202811000</v>
+        <v>205292250</v>
       </c>
       <c r="F288">
-        <v>202811000</v>
+        <v>205292250</v>
       </c>
       <c r="G288">
-        <v>145663250</v>
+        <v>143182000</v>
       </c>
       <c r="H288">
         <v>67824750</v>
@@ -8776,13 +8776,13 @@
         <v>0</v>
       </c>
       <c r="E289">
-        <v>61530618</v>
+        <v>68787618</v>
       </c>
       <c r="F289">
-        <v>61530618</v>
+        <v>68787618</v>
       </c>
       <c r="G289">
-        <v>119613464</v>
+        <v>112356464</v>
       </c>
       <c r="H289">
         <v>0</v>
@@ -8854,13 +8854,13 @@
         <v>0</v>
       </c>
       <c r="E292">
-        <v>8983131709</v>
+        <v>8983187960</v>
       </c>
       <c r="F292">
-        <v>8983131709</v>
+        <v>8983187960</v>
       </c>
       <c r="G292">
-        <v>3639487218</v>
+        <v>3639430967</v>
       </c>
       <c r="H292">
         <v>0</v>
@@ -9059,16 +9059,16 @@
         <v>63706784713</v>
       </c>
       <c r="D300">
-        <v>13716491369</v>
+        <v>13755053336</v>
       </c>
       <c r="E300">
-        <v>35401041576</v>
+        <v>35558935757</v>
       </c>
       <c r="F300">
-        <v>49117532945</v>
+        <v>49313989093</v>
       </c>
       <c r="G300">
-        <v>14589251768</v>
+        <v>14392795620</v>
       </c>
       <c r="H300">
         <v>531045413</v>
@@ -9267,10 +9267,10 @@
         <v>534300000</v>
       </c>
       <c r="D308">
-        <v>148445515</v>
+        <v>129476765</v>
       </c>
       <c r="E308">
-        <v>269954678</v>
+        <v>288923428</v>
       </c>
       <c r="F308">
         <v>418400193</v>
@@ -9530,13 +9530,13 @@
         <v>0</v>
       </c>
       <c r="E318">
-        <v>991958412</v>
+        <v>1130633380</v>
       </c>
       <c r="F318">
-        <v>991958412</v>
+        <v>1130633380</v>
       </c>
       <c r="G318">
-        <v>1318041588</v>
+        <v>1179366620</v>
       </c>
       <c r="H318">
         <v>0</v>
@@ -9631,16 +9631,16 @@
         <v>385800000</v>
       </c>
       <c r="D322">
-        <v>32715000</v>
+        <v>45228000</v>
       </c>
       <c r="E322">
         <v>86374635</v>
       </c>
       <c r="F322">
-        <v>119089635</v>
+        <v>131602635</v>
       </c>
       <c r="G322">
-        <v>266710365</v>
+        <v>254197365</v>
       </c>
       <c r="H322">
         <v>128600000</v>
@@ -9917,16 +9917,16 @@
         <v>30454436960</v>
       </c>
       <c r="D333">
-        <v>3193038426</v>
+        <v>3186582676</v>
       </c>
       <c r="E333">
-        <v>21293774273</v>
+        <v>21451417991</v>
       </c>
       <c r="F333">
-        <v>24486812699</v>
+        <v>24638000667</v>
       </c>
       <c r="G333">
-        <v>5967624261</v>
+        <v>5816436293</v>
       </c>
       <c r="H333">
         <v>260139500</v>
@@ -10047,16 +10047,16 @@
         <v>213056448</v>
       </c>
       <c r="D338">
-        <v>0</v>
+        <v>177539800</v>
       </c>
       <c r="E338">
         <v>33060600</v>
       </c>
       <c r="F338">
-        <v>33060600</v>
+        <v>210600400</v>
       </c>
       <c r="G338">
-        <v>179995848</v>
+        <v>2456048</v>
       </c>
       <c r="H338">
         <v>0</v>
@@ -10203,16 +10203,16 @@
         <v>1515585000</v>
       </c>
       <c r="D344">
-        <v>472000000</v>
+        <v>469000000</v>
       </c>
       <c r="E344">
         <v>1022239000</v>
       </c>
       <c r="F344">
-        <v>1494239000</v>
+        <v>1491239000</v>
       </c>
       <c r="G344">
-        <v>21346000</v>
+        <v>24346000</v>
       </c>
       <c r="H344">
         <v>0</v>
@@ -10333,16 +10333,16 @@
         <v>2911760000</v>
       </c>
       <c r="D349">
-        <v>292802040</v>
+        <v>292257770</v>
       </c>
       <c r="E349">
-        <v>1449936173</v>
+        <v>1650655501</v>
       </c>
       <c r="F349">
-        <v>1742738213</v>
+        <v>1942913271</v>
       </c>
       <c r="G349">
-        <v>1169021787</v>
+        <v>968846729</v>
       </c>
       <c r="H349">
         <v>0</v>
@@ -10359,10 +10359,10 @@
         <v>135000000</v>
       </c>
       <c r="D350">
-        <v>8991900</v>
+        <v>6000000</v>
       </c>
       <c r="E350">
-        <v>76294698</v>
+        <v>79286598</v>
       </c>
       <c r="F350">
         <v>85286598</v>
@@ -10437,16 +10437,16 @@
         <v>462375000</v>
       </c>
       <c r="D353">
-        <v>250302912</v>
+        <v>238973912</v>
       </c>
       <c r="E353">
-        <v>90635371</v>
+        <v>99414371</v>
       </c>
       <c r="F353">
-        <v>340938283</v>
+        <v>338388283</v>
       </c>
       <c r="G353">
-        <v>121436717</v>
+        <v>123986717</v>
       </c>
       <c r="H353">
         <v>154125000</v>
@@ -10515,16 +10515,16 @@
         <v>56157000</v>
       </c>
       <c r="D356">
-        <v>26940400</v>
+        <v>0</v>
       </c>
       <c r="E356">
-        <v>15178108</v>
+        <v>40788063</v>
       </c>
       <c r="F356">
-        <v>42118508</v>
+        <v>40788063</v>
       </c>
       <c r="G356">
-        <v>14038492</v>
+        <v>15368937</v>
       </c>
       <c r="H356">
         <v>0</v>
@@ -10749,16 +10749,16 @@
         <v>57427089299</v>
       </c>
       <c r="D365">
-        <v>10650040181</v>
+        <v>10782774411</v>
       </c>
       <c r="E365">
-        <v>38653676598</v>
+        <v>38891776781</v>
       </c>
       <c r="F365">
-        <v>49303716779</v>
+        <v>49674551192</v>
       </c>
       <c r="G365">
-        <v>8123372520</v>
+        <v>7752538107</v>
       </c>
       <c r="H365">
         <v>526334925</v>
@@ -10853,16 +10853,16 @@
         <v>2467762918</v>
       </c>
       <c r="D369">
-        <v>1013929129</v>
+        <v>1170491278</v>
       </c>
       <c r="E369">
         <v>509828868</v>
       </c>
       <c r="F369">
-        <v>1523757997</v>
+        <v>1680320146</v>
       </c>
       <c r="G369">
-        <v>944004921</v>
+        <v>787442772</v>
       </c>
       <c r="H369">
         <v>0</v>
@@ -10957,10 +10957,10 @@
         <v>1400000000</v>
       </c>
       <c r="D373">
-        <v>340127864</v>
+        <v>252821062</v>
       </c>
       <c r="E373">
-        <v>472946700</v>
+        <v>560253502</v>
       </c>
       <c r="F373">
         <v>813074564</v>
@@ -11139,16 +11139,16 @@
         <v>411080000</v>
       </c>
       <c r="D380">
-        <v>1827440</v>
+        <v>1337650</v>
       </c>
       <c r="E380">
-        <v>241674743</v>
+        <v>279958254</v>
       </c>
       <c r="F380">
-        <v>243502183</v>
+        <v>281295904</v>
       </c>
       <c r="G380">
-        <v>167577817</v>
+        <v>129784096</v>
       </c>
       <c r="H380">
         <v>0</v>
@@ -11165,16 +11165,16 @@
         <v>120000000</v>
       </c>
       <c r="D381">
-        <v>34092480</v>
+        <v>27345375</v>
       </c>
       <c r="E381">
-        <v>29148000</v>
+        <v>36260105</v>
       </c>
       <c r="F381">
-        <v>63240480</v>
+        <v>63605480</v>
       </c>
       <c r="G381">
-        <v>56759520</v>
+        <v>56394520</v>
       </c>
       <c r="H381">
         <v>40000000</v>
@@ -11581,16 +11581,16 @@
         <v>24628424376</v>
       </c>
       <c r="D397">
-        <v>4467138969</v>
+        <v>4529157421</v>
       </c>
       <c r="E397">
-        <v>15180015613</v>
+        <v>15312718031</v>
       </c>
       <c r="F397">
-        <v>19647154582</v>
+        <v>19841875452</v>
       </c>
       <c r="G397">
-        <v>4981269794</v>
+        <v>4786548924</v>
       </c>
       <c r="H397">
         <v>232675000</v>
@@ -11763,10 +11763,10 @@
         <v>500000000</v>
       </c>
       <c r="D404">
-        <v>413687631</v>
+        <v>0</v>
       </c>
       <c r="E404">
-        <v>67974300</v>
+        <v>481661931</v>
       </c>
       <c r="F404">
         <v>481661931</v>
@@ -12023,16 +12023,16 @@
         <v>2230000000</v>
       </c>
       <c r="D414">
-        <v>19315000</v>
+        <v>19000000</v>
       </c>
       <c r="E414">
-        <v>891610783</v>
+        <v>1017375537</v>
       </c>
       <c r="F414">
-        <v>910925783</v>
+        <v>1036375537</v>
       </c>
       <c r="G414">
-        <v>1319074217</v>
+        <v>1193624463</v>
       </c>
       <c r="H414">
         <v>0</v>
@@ -12153,16 +12153,16 @@
         <v>370995500</v>
       </c>
       <c r="D419">
-        <v>29995500</v>
+        <v>48167497</v>
       </c>
       <c r="E419">
-        <v>284286091</v>
+        <v>285961091</v>
       </c>
       <c r="F419">
-        <v>314281591</v>
+        <v>334128588</v>
       </c>
       <c r="G419">
-        <v>56713909</v>
+        <v>36866912</v>
       </c>
       <c r="H419">
         <v>117000000</v>
@@ -12260,13 +12260,13 @@
         <v>0</v>
       </c>
       <c r="E423">
-        <v>5978595221</v>
+        <v>5978628971</v>
       </c>
       <c r="F423">
-        <v>5978595221</v>
+        <v>5978628971</v>
       </c>
       <c r="G423">
-        <v>2662750490</v>
+        <v>2662716740</v>
       </c>
       <c r="H423">
         <v>0</v>
@@ -12465,16 +12465,16 @@
         <v>35458361640</v>
       </c>
       <c r="D431">
-        <v>5912822124</v>
+        <v>5516991490</v>
       </c>
       <c r="E431">
-        <v>20682141729</v>
+        <v>21223302864</v>
       </c>
       <c r="F431">
-        <v>26594963853</v>
+        <v>26740294354</v>
       </c>
       <c r="G431">
-        <v>8863397787</v>
+        <v>8718067286</v>
       </c>
       <c r="H431">
         <v>472807750</v>
@@ -13039,16 +13039,16 @@
         <v>30750000</v>
       </c>
       <c r="D468" s="1">
-        <v>5091000</v>
+        <v>6869550</v>
       </c>
       <c r="E468" s="1">
         <v>4982700</v>
       </c>
       <c r="F468" s="1">
-        <v>10073700</v>
+        <v>11852250</v>
       </c>
       <c r="G468" s="1">
-        <v>20676300</v>
+        <v>18897750</v>
       </c>
       <c r="H468" s="1">
         <v>10250000</v>
@@ -13139,16 +13139,16 @@
         <v>6660000</v>
       </c>
       <c r="D472" s="1">
-        <v>0</v>
+        <v>2240000</v>
       </c>
       <c r="E472" s="1">
         <v>4246644</v>
       </c>
       <c r="F472" s="1">
-        <v>4246644</v>
+        <v>6486644</v>
       </c>
       <c r="G472" s="1">
-        <v>2413356</v>
+        <v>173356</v>
       </c>
       <c r="H472" s="1">
         <v>0</v>
@@ -13567,16 +13567,16 @@
         <v>4989900000</v>
       </c>
       <c r="D496">
-        <v>2540611977</v>
+        <v>3039997152</v>
       </c>
       <c r="E496">
         <v>1331606604</v>
       </c>
       <c r="F496">
-        <v>3872218581</v>
+        <v>4371603756</v>
       </c>
       <c r="G496">
-        <v>1117681419</v>
+        <v>618296244</v>
       </c>
       <c r="H496">
         <v>0</v>
@@ -13749,16 +13749,16 @@
         <v>745000000</v>
       </c>
       <c r="D503">
-        <v>678944934</v>
+        <v>673853563</v>
       </c>
       <c r="E503">
         <v>51881480</v>
       </c>
       <c r="F503">
-        <v>730826414</v>
+        <v>725735043</v>
       </c>
       <c r="G503">
-        <v>14173586</v>
+        <v>19264957</v>
       </c>
       <c r="H503">
         <v>0</v>
@@ -13775,16 +13775,16 @@
         <v>7401091133</v>
       </c>
       <c r="D504">
-        <v>4676900116</v>
+        <v>4673665116</v>
       </c>
       <c r="E504">
         <v>2607739789</v>
       </c>
       <c r="F504">
-        <v>7284639905</v>
+        <v>7281404905</v>
       </c>
       <c r="G504">
-        <v>116451228</v>
+        <v>119686228</v>
       </c>
       <c r="H504">
         <v>0</v>
@@ -13934,13 +13934,13 @@
         <v>8404406</v>
       </c>
       <c r="E510">
-        <v>1480076340</v>
+        <v>1687140714</v>
       </c>
       <c r="F510">
-        <v>1488480746</v>
+        <v>1695545120</v>
       </c>
       <c r="G510">
-        <v>1071519254</v>
+        <v>864454880</v>
       </c>
       <c r="H510">
         <v>0</v>
@@ -14061,16 +14061,16 @@
         <v>516433500</v>
       </c>
       <c r="D515">
-        <v>1480000</v>
+        <v>21491715</v>
       </c>
       <c r="E515">
         <v>341354080</v>
       </c>
       <c r="F515">
-        <v>342834080</v>
+        <v>362845795</v>
       </c>
       <c r="G515">
-        <v>173599420</v>
+        <v>153587705</v>
       </c>
       <c r="H515">
         <v>172144500</v>
@@ -14191,10 +14191,10 @@
         <v>0</v>
       </c>
       <c r="D520">
-        <v>8585</v>
+        <v>0</v>
       </c>
       <c r="E520">
-        <v>739556</v>
+        <v>748141</v>
       </c>
       <c r="F520">
         <v>748141</v>
@@ -14217,10 +14217,10 @@
         <v>0</v>
       </c>
       <c r="D521">
-        <v>568000</v>
+        <v>0</v>
       </c>
       <c r="E521">
-        <v>114614625</v>
+        <v>115182625</v>
       </c>
       <c r="F521">
         <v>115182625</v>
@@ -14243,10 +14243,10 @@
         <v>12164281897</v>
       </c>
       <c r="D522">
-        <v>446366</v>
+        <v>0</v>
       </c>
       <c r="E522">
-        <v>8955396549</v>
+        <v>8955842915</v>
       </c>
       <c r="F522">
         <v>8955842915</v>
@@ -14295,10 +14295,10 @@
         <v>10801404197</v>
       </c>
       <c r="D524">
-        <v>34095622</v>
+        <v>0</v>
       </c>
       <c r="E524">
-        <v>9762745459</v>
+        <v>9796841081</v>
       </c>
       <c r="F524">
         <v>9796841081</v>
@@ -14477,16 +14477,16 @@
         <v>64019485320</v>
       </c>
       <c r="D531">
-        <v>15105887470</v>
+        <v>15581839416</v>
       </c>
       <c r="E531">
-        <v>38709838066</v>
+        <v>38952021013</v>
       </c>
       <c r="F531">
-        <v>53815725536</v>
+        <v>54533860429</v>
       </c>
       <c r="G531">
-        <v>10203759784</v>
+        <v>9485624891</v>
       </c>
       <c r="H531">
         <v>850782250</v>
@@ -14529,10 +14529,10 @@
         <v>1439636880</v>
       </c>
       <c r="D533">
-        <v>1436308580</v>
+        <v>0</v>
       </c>
       <c r="E533">
-        <v>3328300</v>
+        <v>1439636880</v>
       </c>
       <c r="F533">
         <v>1439636880</v>
@@ -14659,16 +14659,16 @@
         <v>11576266001</v>
       </c>
       <c r="D538">
-        <v>11227988861</v>
+        <v>11196770846</v>
       </c>
       <c r="E538">
         <v>259825808</v>
       </c>
       <c r="F538">
-        <v>11487814669</v>
+        <v>11456596654</v>
       </c>
       <c r="G538">
-        <v>88451332</v>
+        <v>119669347</v>
       </c>
       <c r="H538">
         <v>0</v>
@@ -14685,16 +14685,16 @@
         <v>2103744312</v>
       </c>
       <c r="D539">
-        <v>1300493715</v>
+        <v>1288384905</v>
       </c>
       <c r="E539">
         <v>330635136</v>
       </c>
       <c r="F539">
-        <v>1631128851</v>
+        <v>1619020041</v>
       </c>
       <c r="G539">
-        <v>472615461</v>
+        <v>484724271</v>
       </c>
       <c r="H539">
         <v>0</v>
@@ -14896,13 +14896,13 @@
         <v>6662233</v>
       </c>
       <c r="E547">
-        <v>808990194</v>
+        <v>929753360</v>
       </c>
       <c r="F547">
-        <v>815652427</v>
+        <v>936415593</v>
       </c>
       <c r="G547">
-        <v>723662573</v>
+        <v>602899407</v>
       </c>
       <c r="H547">
         <v>0</v>
@@ -15309,16 +15309,16 @@
         <v>57848682223</v>
       </c>
       <c r="D563">
-        <v>21790625485</v>
+        <v>20310990080</v>
       </c>
       <c r="E563">
-        <v>29038070556</v>
+        <v>30595142302</v>
       </c>
       <c r="F563">
-        <v>50828696041</v>
+        <v>50906132382</v>
       </c>
       <c r="G563">
-        <v>7019986182</v>
+        <v>6942549841</v>
       </c>
       <c r="H563">
         <v>720558750</v>
@@ -15329,25 +15329,25 @@
         <v>129</v>
       </c>
       <c r="B564">
-        <v>1118558384139</v>
+        <v>1118540641744</v>
       </c>
       <c r="C564">
-        <v>1109026106817</v>
+        <v>1109231301920</v>
       </c>
       <c r="D564">
-        <v>421610814578</v>
+        <v>422407000311</v>
       </c>
       <c r="E564">
-        <v>531269049789</v>
+        <v>538598341819</v>
       </c>
       <c r="F564">
-        <v>952879864367</v>
+        <v>961005342130</v>
       </c>
       <c r="G564">
-        <v>156146242450</v>
+        <v>148225959790</v>
       </c>
       <c r="H564">
-        <v>9532277322</v>
+        <v>9309339824</v>
       </c>
     </row>
   </sheetData>
